--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -482,28 +482,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mengenal "clean eating" beserta manfaat dan hal yang perlu diwaspadai</t>
+          <t>Kemendag: Camilan RI tembus pasar Arab Saudi, hasil penjajakan bisnis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:03:28 +0700</t>
+          <t>Wed, 05 Aug 2026 12:12:59 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pola makan "clean eating" semakin dikenal seiring meningkatnya perhatian terhadap dampak konsumsi makanan ...</t>
+          <t>Kementerian Perdagangan (Kemendag) menyebut salah satu produk camilan Indonesia berhasil menembus pasar Arab Saudi ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680525/mengenal-clean-eating-beserta-manfaat-dan-hal-yang-perlu-diwaspadai</t>
+          <t>https://www.antaranews.com/berita/5680543/kemendag-camilan-ri-tembus-pasar-arab-saudi-hasil-penjajakan-bisnis</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Gizi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0942.jpeg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -520,28 +520,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Menteri PPN: Pengembangan singkong di Indonesia miliki prospek besar</t>
+          <t>10 ide lomba 17 Agustus di kantor yang seru, lucu, dan bikin karyawan kompak</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:59 +0700</t>
+          <t>Wed, 05 Aug 2026 12:11:11 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 semakin dekat. Selain menjadi ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680521/menteri-ppn-pengembangan-singkong-di-indonesia-miliki-prospek-besar</t>
+          <t>https://www.antaranews.com/berita/5680540/10-ide-lomba-17-agustus-di-kantor-yang-seru-lucu-dan-bikin-karyawan-kompak</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/PPN-bappenas-lampung.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/InShot_20260622_143213404.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,28 +558,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Waspadai penyakit saat musim kemarau</t>
+          <t>Momentum ekonomi di balik kunjungan PM Thailand ke Indonesia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:10:26 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Udara panas dan kekeringan saat musim kemarau memicu penyebaran sejumlah penyakit yang dapat membahayakan kesehatan. ...</t>
+          <t>Perdana Menteri Thailand Anutin Charnvirakul yang tiba di Pangkalan Udara Halim Perdanakusuma pada Senin ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/infografik/5680467/waspadai-penyakit-saat-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5680539/momentum-ekonomi-di-balik-kunjungan-pm-thailand-ke-indonesia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260805-Waspadai-penyakit-saat-musim-kemarau_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -596,28 +596,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pemkab Banyumas upayakan operasional Trans Banyumas tetap berlanjut</t>
+          <t>Karhutla di Gunung Bromo belum padam dengan luas lahan terbakar 10 ha</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:59:47 +0700</t>
+          <t>Wed, 05 Aug 2026 12:08:46 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Banyumas, Jawa Tengah, terus mengupayakan keberlanjutan operasional Bus Buy The Service (BTS) ...</t>
+          <t>Kebakaran hutan dan lahan (karhutla) di Gunung Bromo, Jawa Timur belum padam dengan luas lahan yang terbakar ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680519/pemkab-banyumas-upayakan-operasional-trans-banyumas-tetap-berlanjut</t>
+          <t>https://www.antaranews.com/berita/5680535/karhutla-di-gunung-bromo-belum-padam-dengan-luas-lahan-terbakar-10-ha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001093491.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-09.18.39.jpeg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,28 +634,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KAI Layani 13.920 Ton Pupuk hingga Juli 2026, Perkuat Rantai Pasok Pertanian dan Ketahanan Pangan</t>
+          <t>WhatsApp hadirkan tiga pembaruan di layanan chat grup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:59:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:07:58 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat perannya dalam rantai pasok pertanian nasional melalui pelayanan ...</t>
+          <t>WhatsApp menghadirkan tiga pembaruan fitur di layanan chat grup, termasuk fitur jajak pendapat dan pembuat obrolan ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680516/kai-layani-13920-ton-pupuk-hingga-juli-2026-perkuat-rantai-pasok-pertanian-dan-ketahanan-pangan</t>
+          <t>https://www.antaranews.com/berita/5680532/whatsapp-hadirkan-tiga-pembaruan-di-layanan-chat-grup</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.38.20.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_104732163.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -672,28 +672,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pulau Untung Jawa gelar lomba meriahkan HUT Kemerdekaan RI</t>
+          <t>Menjelajahi Situs Peninggalan Arkeologi Nasional Niuheliang di China</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:54:56 +0700</t>
+          <t>Wed, 05 Aug 2026 12:07:21 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pemerintah Kelurahan Pulau Untung Jawa resmi membuka rangkaian perlombaan dalam rangka memeriahkan Hari Ulang Tahun ...</t>
+          <t>Taman Situs Peninggalan Arkeologi Nasional Niuheliang dibangun di Situs Niuheliang, sebuah kompleks ritual dan ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680512/pulau-untung-jawa-gelar-lomba-meriahkan-hut-kemerdekaan-ri</t>
+          <t>https://www.antaranews.com/berita/5680529/menjelajahi-situs-peninggalan-arkeologi-nasional-niuheliang-di-china</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a8ea0e8e-b465-4832-9dee-22d911db4b0e.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000003_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -710,28 +710,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pemprov Papua bukukan transaksi UMK 50,65 persen melalui e-Katalog</t>
+          <t>OJK Sulteng tingkatkan literasi keuangan nelayan melalui pelatihan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:54:36 +0700</t>
+          <t>Wed, 05 Aug 2026 12:05:16 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Papua melalui Biro Pengadaan Barang dan Jasa (BPBJ) setempat membukukan nilai transaksi Usaha ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) Provinsi Sulawesi Tengah (Sulteng) meningkatkan literasi dan inklusi keuangan bagi para ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680509/pemprov-papua-bukukan-transaksi-umk-5065-persen-melalui-e-katalog</t>
+          <t>https://www.antaranews.com/berita/5680527/ojk-sulteng-tingkatkan-literasi-keuangan-nelayan-melalui-pelatihan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002065915.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-37.jpeg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -748,28 +748,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5 tips positive parenting agar anak percaya diri</t>
+          <t>Mengenal "clean eating" beserta manfaat dan hal yang perlu diwaspadai</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:53:39 +0700</t>
+          <t>Wed, 05 Aug 2026 12:03:28 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pola asuh positif atau positive parenting dinilai dapat membantu anak tumbuh dengan rasa aman, percaya diri, dan mampu ...</t>
+          <t>Pola makan "clean eating" semakin dikenal seiring meningkatnya perhatian terhadap dampak konsumsi makanan ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680507/5-tips-positive-parenting-agar-anak-percaya-diri</t>
+          <t>https://www.antaranews.com/berita/5680525/mengenal-clean-eating-beserta-manfaat-dan-hal-yang-perlu-diwaspadai</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/02/11/pexels-emma-bauso-2253879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Gizi.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -786,28 +786,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AS cabut visa Dubes Brasil di tengah perselisihan diplomatik</t>
+          <t>Menteri PPN: Pengembangan singkong di Indonesia miliki prospek besar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:53:27 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:59 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pemerintah Amerika Serikat (AS) mencabut visa Duta Besar Brasil untuk Mario Luiza Ribeiro Viotti memperpanjang ...</t>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680504/as-cabut-visa-dubes-brasil-di-tengah-perselisihan-diplomatik</t>
+          <t>https://www.antaranews.com/berita/5680521/menteri-ppn-pengembangan-singkong-di-indonesia-miliki-prospek-besar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000005_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/PPN-bappenas-lampung.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -824,28 +824,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Customer Focus, KAI Libatkan Suara Pelanggan untuk Tingkatkan Layanan; CSI Semester I 2026 Capai 4,53</t>
+          <t>Waspadai penyakit saat musim kemarau</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:51:39 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat kualitas pelayanan dengan menempatkan pelanggan sebagai pusat ...</t>
+          <t>Udara panas dan kekeringan saat musim kemarau memicu penyebaran sejumlah penyakit yang dapat membahayakan kesehatan. ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680503/customer-focus-kai-libatkan-suara-pelanggan-untuk-tingkatkan-layanan-csi-semester-i-2026-capai-453</t>
+          <t>https://www.antaranews.com/infografik/5680467/waspadai-penyakit-saat-musim-kemarau</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.27.26.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260805-Waspadai-penyakit-saat-musim-kemarau_1.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -862,28 +862,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POCO M8 Power hadir dengan Snapdragon 4 Gen 4 dan baterai 8.000 mAh</t>
+          <t>Pemkab Banyumas upayakan operasional Trans Banyumas tetap berlanjut</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:50:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:59:47 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponsel POCO M8 Power, model keempat dalam seri POCO M8 yang diperkenalkan di pasar India, hadir dengan chip Snapdragon ...</t>
+          <t>Pemerintah Kabupaten Banyumas, Jawa Tengah, terus mengupayakan keberlanjutan operasional Bus Buy The Service (BTS) ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680499/poco-m8-power-hadir-dengan-snapdragon-4-gen-4-dan-baterai-8000-mah</t>
+          <t>https://www.antaranews.com/berita/5680519/pemkab-banyumas-upayakan-operasional-trans-banyumas-tetap-berlanjut</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_111842114.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001093491.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -900,28 +900,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>China luncurkan standar keselamatan sistem kemudi otonom</t>
+          <t>KAI Layani 13.920 Ton Pupuk hingga Juli 2026, Perkuat Rantai Pasok Pertanian dan Ketahanan Pangan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:48:26 +0700</t>
+          <t>Wed, 05 Aug 2026 11:59:00 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>China meluncurkan standar nasional wajib mengenai persyaratan keselamatan bagi sistem kemudi otonom, demikian diumumkan ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat perannya dalam rantai pasok pertanian nasional melalui pelayanan ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5680496/china-luncurkan-standar-keselamatan-sistem-kemudi-otonom</t>
+          <t>https://www.antaranews.com/berita/5680516/kai-layani-13920-ton-pupuk-hingga-juli-2026-perkuat-rantai-pasok-pertanian-dan-ketahanan-pangan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000002_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.38.20.jpeg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -938,28 +938,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gelombang panas keempat tahun ini di Italia picu respons darurat</t>
+          <t>Pulau Untung Jawa gelar lomba meriahkan HUT Kemerdekaan RI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:45:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:54:56 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Italia sedang menghadapi gelombang panas besar keempat pada musim panas tahun ini, dengan suhu di sejumlah wilayah ...</t>
+          <t>Pemerintah Kelurahan Pulau Untung Jawa resmi membuka rangkaian perlombaan dalam rangka memeriahkan Hari Ulang Tahun ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680493/gelombang-panas-keempat-tahun-ini-di-italia-picu-respons-darurat</t>
+          <t>https://www.antaranews.com/berita/5680512/pulau-untung-jawa-gelar-lomba-meriahkan-hut-kemerdekaan-ri</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000004_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a8ea0e8e-b465-4832-9dee-22d911db4b0e.jpeg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -976,28 +976,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kaltara tawarkan peluang investasi strategis kepada belasan duta besar</t>
+          <t>Pemprov Papua bukukan transaksi UMK 50,65 persen melalui e-Katalog</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:44:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:54:36 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gubernur Kalimantan Utara (Kaltara) Zainal A. Paliwang menawarkan berbagai peluang investasi strategis di hadapan ...</t>
+          <t>Pemerintah Provinsi Papua melalui Biro Pengadaan Barang dan Jasa (BPBJ) setempat membukukan nilai transaksi Usaha ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680492/kaltara-tawarkan-peluang-investasi-strategis-kepada-belasan-duta-besar</t>
+          <t>https://www.antaranews.com/berita/5680509/pemprov-papua-bukukan-transaksi-umk-5065-persen-melalui-e-katalog</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000575462.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002065915.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1014,28 +1014,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tenaga ahli usulkan kejahatan lingkungan masuk RUU Perampasan Aset</t>
+          <t>5 tips positive parenting agar anak percaya diri</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:11 +0700</t>
+          <t>Wed, 05 Aug 2026 11:53:39 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tenaga Ahli Menteri Lingkungan Hidup Bidang Advokasi dan Penguatan Partisipasi Publik Yudi Syamhudi Suyuti mengusulkan ...</t>
+          <t>Pola asuh positif atau positive parenting dinilai dapat membantu anak tumbuh dengan rasa aman, percaya diri, dan mampu ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680488/tenaga-ahli-usulkan-kejahatan-lingkungan-masuk-ruu-perampasan-aset</t>
+          <t>https://www.antaranews.com/berita/5680507/5-tips-positive-parenting-agar-anak-percaya-diri</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/IMG_20260420_115241_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/11/pexels-emma-bauso-2253879.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1052,28 +1052,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemendukbangga perkuat peran keluarga wujudkan ruang aman bagi anak</t>
+          <t>AS cabut visa Dubes Brasil di tengah perselisihan diplomatik</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:53:27 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN terus memperkuat peran keluarga sebagai ...</t>
+          <t>Pemerintah Amerika Serikat (AS) mencabut visa Duta Besar Brasil untuk Mario Luiza Ribeiro Viotti memperpanjang ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680484/kemendukbangga-perkuat-peran-keluarga-wujudkan-ruang-aman-bagi-anak</t>
+          <t>https://www.antaranews.com/berita/5680504/as-cabut-visa-dubes-brasil-di-tengah-perselisihan-diplomatik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-7.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000005_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1090,28 +1090,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Panas ekstrem surutkan air Sungai Danube, ganggu pengiriman kargo</t>
+          <t>Customer Focus, KAI Libatkan Suara Pelanggan untuk Tingkatkan Layanan; CSI Semester I 2026 Capai 4,53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:42:28 +0700</t>
+          <t>Wed, 05 Aug 2026 11:51:39 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pemerintah Austria menyatakan pengiriman kargo di sepanjang Sungai Danube yang melintasi wilayah negara itu nyaris ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat kualitas pelayanan dengan menempatkan pelanggan sebagai pusat ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680483/panas-ekstrem-surutkan-air-sungai-danube-ganggu-pengiriman-kargo</t>
+          <t>https://www.antaranews.com/berita/5680503/customer-focus-kai-libatkan-suara-pelanggan-untuk-tingkatkan-layanan-csi-semester-i-2026-capai-453</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/CmxztpE000018_20260620_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.27.26.jpeg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1128,28 +1128,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AS cabut visa dubes Brasil karena tolak calon dubes usulan Trump</t>
+          <t>POCO M8 Power hadir dengan Snapdragon 4 Gen 4 dan baterai 8.000 mAh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:41:05 +0700</t>
+          <t>Wed, 05 Aug 2026 11:50:39 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amerika Serikat mencabut visa Duta Besar Brasil untuk Washington setelah pemerintah Brasil belum memberikan persetujuan ...</t>
+          <t>Ponsel POCO M8 Power, model keempat dalam seri POCO M8 yang diperkenalkan di pasar India, hadir dengan chip Snapdragon ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680481/as-cabut-visa-dubes-brasil-karena-tolak-calon-dubes-usulan-trump</t>
+          <t>https://www.antaranews.com/berita/5680499/poco-m8-power-hadir-dengan-snapdragon-4-gen-4-dan-baterai-8000-mah</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_111842114.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pertamina Patra Niaga menghadirkan kompetisi masak nasional BGCC 2026</t>
+          <t>China luncurkan standar keselamatan sistem kemudi otonom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:40:14 +0700</t>
+          <t>Wed, 05 Aug 2026 11:48:26 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PT Pertamina Patra Niaga menghadirkan kompetisi memasak tingkat nasional Bright Gas Cooking Competition (BGCC) 2026 ...</t>
+          <t>China meluncurkan standar nasional wajib mengenai persyaratan keselamatan bagi sistem kemudi otonom, demikian diumumkan ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680477/pertamina-patra-niaga-menghadirkan-kompetisi-masak-nasional-bgcc-2026</t>
+          <t>https://otomotif.antaranews.com/berita/5680496/china-luncurkan-standar-keselamatan-sistem-kemudi-otonom</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000402887.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000002_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1204,28 +1204,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bappenas: Indonesia punya modal kuat kembangkan ekosistem tokenisasi</t>
+          <t>Gelombang panas keempat tahun ini di Italia picu respons darurat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:38:07 +0700</t>
+          <t>Wed, 05 Aug 2026 11:45:01 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+          <t>Italia sedang menghadapi gelombang panas besar keempat pada musim panas tahun ini, dengan suhu di sejumlah wilayah ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680475/bappenas-indonesia-punya-modal-kuat-kembangkan-ekosistem-tokenisasi</t>
+          <t>https://www.antaranews.com/berita/5680493/gelombang-panas-keempat-tahun-ini-di-italia-picu-respons-darurat</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bappenas-Tokenisasi.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000004_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1242,28 +1242,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kimia Farma bukukan laba bersih "unaudited" Rp54,07 miliar</t>
+          <t>Kaltara tawarkan peluang investasi strategis kepada belasan duta besar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:38 +0700</t>
+          <t>Wed, 05 Aug 2026 11:44:18 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PT Kimia Farma (Persero) Tbk (KAEF) membukukan laba bersih unaudited sebesar Rp54,07 miliar pada semester ...</t>
+          <t>Gubernur Kalimantan Utara (Kaltara) Zainal A. Paliwang menawarkan berbagai peluang investasi strategis di hadapan ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680471/kimia-farma-bukukan-laba-bersih-unaudited-rp5407-miliar</t>
+          <t>https://www.antaranews.com/berita/5680492/kaltara-tawarkan-peluang-investasi-strategis-kepada-belasan-duta-besar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/DSC_0637.JPG-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000575462.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1280,28 +1280,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rutinitas malam yang bisa bantu kurangi risiko perut kembung</t>
+          <t>Tenaga ahli usulkan kejahatan lingkungan masuk RUU Perampasan Aset</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:36:55 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:11 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ahli gizi Ava Safir menyampaikan bahwa perut bisa terasa lebih penuh menjelang malam hari karena saluran ...</t>
+          <t>Tenaga Ahli Menteri Lingkungan Hidup Bidang Advokasi dan Penguatan Partisipasi Publik Yudi Syamhudi Suyuti mengusulkan ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680463/rutinitas-malam-yang-bisa-bantu-kurangi-risiko-perut-kembung</t>
+          <t>https://www.antaranews.com/berita/5680488/tenaga-ahli-usulkan-kejahatan-lingkungan-masuk-ruu-perampasan-aset</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/07/02/kembung.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/IMG_20260420_115241_1.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1318,28 +1318,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brasil turunkan tingkat hubungan diplomatik dengan Argentina</t>
+          <t>Kemendukbangga perkuat peran keluarga wujudkan ruang aman bagi anak</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:35:10 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:01 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brasil memutuskan untuk menurunkan tingkat hubungan diplomatiknya dengan Argentina menjadi hanya perwakilan diplomatik ...</t>
+          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN terus memperkuat peran keluarga sebagai ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680460/brasil-turunkan-tingkat-hubungan-diplomatik-dengan-argentina</t>
+          <t>https://www.antaranews.com/berita/5680484/kemendukbangga-perkuat-peran-keluarga-wujudkan-ruang-aman-bagi-anak</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/12/01/CjkinzN007014_20231201_CBMFN0A001_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-7.jpeg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1356,28 +1356,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bea Cukai gagalkan penyeludupan Harley Davidson bekas asal China</t>
+          <t>Panas ekstrem surutkan air Sungai Danube, ganggu pengiriman kargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:33:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:42:28 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok berhasil menggagalkan upaya penyelundupan barang impor ilegal berupa lima unit sepeda motor ...</t>
+          <t>Pemerintah Austria menyatakan pengiriman kargo di sepanjang Sungai Danube yang melintasi wilayah negara itu nyaris ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680459/bea-cukai-gagalkan-penyeludupan-harley-davidson-bekas-asal-china</t>
+          <t>https://www.antaranews.com/berita/5680483/panas-ekstrem-surutkan-air-sungai-danube-ganggu-pengiriman-kargo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_112229.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/CmxztpE000018_20260620_PEPFN0A001.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10 Kebiasaan sebelum tidur yang bisa tingkatkan kualitas istirahat</t>
+          <t>AS cabut visa dubes Brasil karena tolak calon dubes usulan Trump</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:31:46 +0700</t>
+          <t>Wed, 05 Aug 2026 11:41:05 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tidur yang berkualitas bukan hanya ditentukan oleh durasinya, tetapi juga oleh kebiasaan yang dilakukan sebelum ...</t>
+          <t>Amerika Serikat mencabut visa Duta Besar Brasil untuk Washington setelah pemerintah Brasil belum memberikan persetujuan ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680455/10-kebiasaan-sebelum-tidur-yang-bisa-tingkatkan-kualitas-istirahat</t>
+          <t>https://www.antaranews.com/berita/5680481/as-cabut-visa-dubes-brasil-karena-tolak-calon-dubes-usulan-trump</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/03/12/tidur.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1432,28 +1432,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mendag genjot perdagangan RI-Thailand dengan diversifikasi ekspor</t>
+          <t>Pertamina Patra Niaga menghadirkan kompetisi masak nasional BGCC 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:21 +0700</t>
+          <t>Wed, 05 Aug 2026 11:40:14 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Menteri Perdagangan (Mendag) Budi Santoso menegaskan pemerintah terus mendorong penguatan perdagangan bilateral ...</t>
+          <t>PT Pertamina Patra Niaga menghadirkan kompetisi memasak tingkat nasional Bright Gas Cooking Competition (BGCC) 2026 ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680453/mendag-genjot-perdagangan-ri-thailand-dengan-diversifikasi-ekspor</t>
+          <t>https://www.antaranews.com/berita/5680477/pertamina-patra-niaga-menghadirkan-kompetisi-masak-nasional-bgcc-2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0926.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000402887.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1470,28 +1470,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CENTCOM klaim telah kawal 1.000 kapal lewati Selat Hormuz</t>
+          <t>Bappenas: Indonesia punya modal kuat kembangkan ekosistem tokenisasi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:16 +0700</t>
+          <t>Wed, 05 Aug 2026 11:38:07 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Komando Pusat Amerika Serikat (CENTCOM) mengeklaim pihaknya telah membantu lebih dari 1.000 kapal komersial melintasi ...</t>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680451/centcom-klaim-telah-kawal-1000-kapal-lewati-selat-hormuz</t>
+          <t>https://www.antaranews.com/berita/5680475/bappenas-indonesia-punya-modal-kuat-kembangkan-ekosistem-tokenisasi</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_0df8b22d772e3fff389166ac7f3553b1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bappenas-Tokenisasi.jpeg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1508,28 +1508,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BPS: Ekonomi Indonesia tumbuh 5,29 persen pada triwulan II 2026</t>
+          <t>Kimia Farma bukukan laba bersih "unaudited" Rp54,07 miliar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:27:10 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:38 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia tumbuh 5,29 persen (year on year/yoy) pada triwulan II ...</t>
+          <t>PT Kimia Farma (Persero) Tbk (KAEF) membukukan laba bersih unaudited sebesar Rp54,07 miliar pada semester ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680447/bps-ekonomi-indonesia-tumbuh-529-persen-pada-triwulan-ii-2026</t>
+          <t>https://www.antaranews.com/berita/5680471/kimia-farma-bukukan-laba-bersih-unaudited-rp5407-miliar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-10.58.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/DSC_0637.JPG-1.jpeg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1546,28 +1546,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kuota undangan upacara HUT Ke-81 RI hari pertama langsung penuh</t>
+          <t>Rutinitas malam yang bisa bantu kurangi risiko perut kembung</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:25:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:36:55 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kuota pendaftaran undangan Upacara Peringatan HUT Ke-81 Kemerdekaan RI di Istana Merdeka untuk hari pertama, Rabu, ...</t>
+          <t>Ahli gizi Ava Safir menyampaikan bahwa perut bisa terasa lebih penuh menjelang malam hari karena saluran ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680445/kuota-undangan-upacara-hut-ke-81-ri-hari-pertama-langsung-penuh</t>
+          <t>https://www.antaranews.com/berita/5680463/rutinitas-malam-yang-bisa-bantu-kurangi-risiko-perut-kembung</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000034647.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/02/kembung.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1584,28 +1584,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WHO sebut risiko penyebaran virus Bourbon di AS masih rendah</t>
+          <t>Brasil turunkan tingkat hubungan diplomatik dengan Argentina</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:24:48 +0700</t>
+          <t>Wed, 05 Aug 2026 11:35:10 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Organisasi Kesehatan Dunia (WHO) telah mengetahui adanya kasus infeksi virus Bourbon yang dilaporkan di Amerika Serikat ...</t>
+          <t>Brasil memutuskan untuk menurunkan tingkat hubungan diplomatiknya dengan Argentina menjadi hanya perwakilan diplomatik ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680441/who-sebut-risiko-penyebaran-virus-bourbon-di-as-masih-rendah</t>
+          <t>https://www.antaranews.com/berita/5680460/brasil-turunkan-tingkat-hubungan-diplomatik-dengan-argentina</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/07/22/reuters_cdc-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/12/01/CjkinzN007014_20231201_CBMFN0A001_1.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Menteri PKP: BTN salurkan KPR subsidi terbanyak hingga Juli 2026</t>
+          <t>Bea Cukai gagalkan penyeludupan Harley Davidson bekas asal China</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:24:28 +0700</t>
+          <t>Wed, 05 Aug 2026 11:33:25 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait mengatakan PT Bank Tabungan Negara (Persero) Tbk (BTN) ...</t>
+          <t>Bea Cukai Tanjung Priok berhasil menggagalkan upaya penyelundupan barang impor ilegal berupa lima unit sepeda motor ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680437/menteri-pkp-btn-salurkan-kpr-subsidi-terbanyak-hingga-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5680459/bea-cukai-gagalkan-penyeludupan-harley-davidson-bekas-asal-china</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/percepatan-pembangunan-rumah-subsidi-2828057.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_112229.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1660,28 +1660,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Koster temui Gubernur DKI belajar soal pembiayaan inovatif</t>
+          <t>10 Kebiasaan sebelum tidur yang bisa tingkatkan kualitas istirahat</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:22:36 +0700</t>
+          <t>Wed, 05 Aug 2026 11:31:46 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Bali mempelajari skema pembiayaan inovatif dari Pemerintah Provinsi DKI Jakarta, termasuk ...</t>
+          <t>Tidur yang berkualitas bukan hanya ditentukan oleh durasinya, tetapi juga oleh kebiasaan yang dilakukan sebelum ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680433/koster-temui-gubernur-dki-belajar-soal-pembiayaan-inovatif</t>
+          <t>https://www.antaranews.com/berita/5680455/10-kebiasaan-sebelum-tidur-yang-bisa-tingkatkan-kualitas-istirahat</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/794ac169-206a-4fd7-a0f6-8e065b9d2615.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/12/tidur.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1698,28 +1698,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Saudi, Qatar, Yordania berpeluang masuk jalur gas Eropa via Turki</t>
+          <t>Mendag genjot perdagangan RI-Thailand dengan diversifikasi ekspor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:16:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:21 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qatar, Arab Saudi, dan Yordania berpeluang menjadi bagian dari rute baru penyaluran gas alam menuju Turki dan ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso menegaskan pemerintah terus mendorong penguatan perdagangan bilateral ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680431/saudi-qatar-yordania-berpeluang-masuk-jalur-gas-eropa-via-turki</t>
+          <t>https://www.antaranews.com/berita/5680453/mendag-genjot-perdagangan-ri-thailand-dengan-diversifikasi-ekspor</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0926.jpeg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1736,28 +1736,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kronologi temuan mayat dalam karung di Depok hingga penangkapan pelaku</t>
+          <t>CENTCOM klaim telah kawal 1.000 kapal lewati Selat Hormuz</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:15:54 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:16 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kasus penemuan mayat termutilasi yang terbungkus di dalam karung di kawasan Tanah Merah, Kelurahan Pancoran Mas, Kota ...</t>
+          <t>Komando Pusat Amerika Serikat (CENTCOM) mengeklaim pihaknya telah membantu lebih dari 1.000 kapal komersial melintasi ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680429/kronologi-temuan-mayat-dalam-karung-di-depok-hingga-penangkapan-pelaku</t>
+          <t>https://www.antaranews.com/berita/5680451/centcom-klaim-telah-kawal-1000-kapal-lewati-selat-hormuz</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_0df8b22d772e3fff389166ac7f3553b1.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1774,28 +1774,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Legislator: Sensus Ekonomi 2026 perkuat kebijakan UMKM</t>
+          <t>BPS: Ekonomi Indonesia tumbuh 5,29 persen pada triwulan II 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
+          <t>Wed, 05 Aug 2026 11:27:10 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anggota Komisi X DPR RI Adela Kanasya Adies mengatakan Sensus Ekonomi 2026 akan menjadi dasar penyusunan kebijakan ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia tumbuh 5,29 persen (year on year/yoy) pada triwulan II ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680427/legislator-sensus-ekonomi-2026-perkuat-kebijakan-umkm</t>
+          <t>https://www.antaranews.com/berita/5680447/bps-ekonomi-indonesia-tumbuh-529-persen-pada-triwulan-ii-2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001219476.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-10.58.55.jpeg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1812,28 +1812,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pendaftaran upacara HUT RI di Istana dibuka, ini dokumen yang wajib disiapkan</t>
+          <t>Kuota undangan upacara HUT Ke-81 RI hari pertama langsung penuh</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:25:27 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Badan Komunikasi Pemerintah (Bakom) RI menyarankan masyarakat menyiapkan seluruh dokumen persyaratan sebelum mendaftar ...</t>
+          <t>Kuota pendaftaran undangan Upacara Peringatan HUT Ke-81 Kemerdekaan RI di Istana Merdeka untuk hari pertama, Rabu, ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680423/pendaftaran-upacara-hut-ri-di-istana-dibuka-ini-dokumen-yang-wajib-disiapkan</t>
+          <t>https://www.antaranews.com/berita/5680445/kuota-undangan-upacara-hut-ke-81-ri-hari-pertama-langsung-penuh</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000034647.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1850,28 +1850,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Survei Herbalife: Budaya "Wellness" Kian Menguat di Asia Pasifik, Empat dari Lima Konsumen Prioritaskan Kesehatan Holistik</t>
+          <t>WHO sebut risiko penyebaran virus Bourbon di AS masih rendah</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:12:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:24:48 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Budaya gaya hidup sehat (wellness) semakin mengakar di kawasan Asia Pasifik (APAC). Hal itu terungkap dalam survei ...</t>
+          <t>Organisasi Kesehatan Dunia (WHO) telah mengetahui adanya kasus infeksi virus Bourbon yang dilaporkan di Amerika Serikat ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680420/survei-herbalife-budaya-wellness-kian-menguat-di-asia-pasifik-empat-dari-lima-konsumen-prioritaskan-kesehatan-holistik</t>
+          <t>https://www.antaranews.com/berita/5680441/who-sebut-risiko-penyebaran-virus-bourbon-di-as-masih-rendah</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Budaya-Wellness-Asia.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/07/22/reuters_cdc-1.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1888,28 +1888,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warga bentangkan bendera Merah Putih sepanjang 400 meter sambut HUT ke-81 RI di Tangerang</t>
+          <t>Menteri PKP: BTN salurkan KPR subsidi terbanyak hingga Juli 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:11:44 +0700</t>
+          <t>Wed, 05 Aug 2026 11:24:28 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Foto udara bendera Merah Putih membentang menutupi jalan di Perumahan Puri Dewata Indah, Cipondoh, Kota Tangerang, ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait mengatakan PT Bank Tabungan Negara (Persero) Tbk (BTN) ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5680417/warga-bentangkan-bendera-merah-putih-sepanjang-400-meter-sambut-hut-ke-81-ri-di-tangerang</t>
+          <t>https://www.antaranews.com/berita/5680437/menteri-pkp-btn-salurkan-kpr-subsidi-terbanyak-hingga-juli-2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bendera-Merah-Putih-sepanjang-400-meter-di-Tangerang-482026-pma-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/percepatan-pembangunan-rumah-subsidi-2828057.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1926,28 +1926,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Irak akan bangun infrastruktur pipa minyak baru ke Turki dan Suriah</t>
+          <t>Koster temui Gubernur DKI belajar soal pembiayaan inovatif</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:11:24 +0700</t>
+          <t>Wed, 05 Aug 2026 11:22:36 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Irak berencana segera memulai pembangunan pipa minyak baru menuju Suriah dan Turki guna mendiversifikasi rute ekspor ...</t>
+          <t>Pemerintah Provinsi Bali mempelajari skema pembiayaan inovatif dari Pemerintah Provinsi DKI Jakarta, termasuk ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680415/irak-akan-bangun-infrastruktur-pipa-minyak-baru-ke-turki-dan-suriah</t>
+          <t>https://www.antaranews.com/berita/5680433/koster-temui-gubernur-dki-belajar-soal-pembiayaan-inovatif</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/794ac169-206a-4fd7-a0f6-8e065b9d2615.jpeg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1964,28 +1964,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pemprov DKI bekali warga Jakpus keterampilan berwirausaha</t>
+          <t>Saudi, Qatar, Yordania berpeluang masuk jalur gas Eropa via Turki</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:08:43 +0700</t>
+          <t>Wed, 05 Aug 2026 11:16:25 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta membekali warga Jakarta Pusat (Jakpus) dengan keterampilan tata boga untuk ...</t>
+          <t>Qatar, Arab Saudi, dan Yordania berpeluang menjadi bagian dari rute baru penyaluran gas alam menuju Turki dan ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680411/pemprov-dki-bekali-warga-jakpus-keterampilan-berwirausaha</t>
+          <t>https://www.antaranews.com/berita/5680431/saudi-qatar-yordania-berpeluang-masuk-jalur-gas-eropa-via-turki</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260731_152649.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2002,28 +2002,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KY tuntaskan wawancara 9 calon hakim agung kamar pidana</t>
+          <t>Kronologi temuan mayat dalam karung di Depok hingga penangkapan pelaku</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:06:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:15:54 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Komisi Yudisial (KY) menuntaskan wawancara terhadap sembilan calon hakim agung kamar pidana dalam seleksi terbuka calon ...</t>
+          <t>Kasus penemuan mayat termutilasi yang terbungkus di dalam karung di kawasan Tanah Merah, Kelurahan Pancoran Mas, Kota ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680407/ky-tuntaskan-wawancara-9-calon-hakim-agung-kamar-pidana</t>
+          <t>https://www.antaranews.com/berita/5680429/kronologi-temuan-mayat-dalam-karung-di-depok-hingga-penangkapan-pelaku</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001843500.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2040,28 +2040,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Naik MRT Jakarta kini lebih praktis dengan BRI Kartu Kredit Contactless</t>
+          <t>Legislator: Sensus Ekonomi 2026 perkuat kebijakan UMKM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:04:09 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mobilitas masyarakat perkotaan yang dinamis menuntut efisiensi di berbagai lini kehidupan, termasuk dalam hal ...</t>
+          <t>Anggota Komisi X DPR RI Adela Kanasya Adies mengatakan Sensus Ekonomi 2026 akan menjadi dasar penyusunan kebijakan ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680404/naik-mrt-jakarta-kini-lebih-praktis-dengan-bri-kartu-kredit-contactless</t>
+          <t>https://www.antaranews.com/berita/5680427/legislator-sensus-ekonomi-2026-perkuat-kebijakan-umkm</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pembayaran-mrt-dengan-kartu-kredit-nirkontak-2829800.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001219476.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2078,28 +2078,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Slovakia: Uni Eropa harus proteksi perbatasan Schengen</t>
+          <t>Pendaftaran upacara HUT RI di Istana dibuka, ini dokumen yang wajib disiapkan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:03:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:15 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Menteri Dalam Negeri (Mendagri) Slovakia, Matus Sutaj Estok mengatakan Uni Eropa harus memprioritaskan ...</t>
+          <t>Badan Komunikasi Pemerintah (Bakom) RI menyarankan masyarakat menyiapkan seluruh dokumen persyaratan sebelum mendaftar ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680400/slovakia-uni-eropa-harus-proteksi-perbatasan-schengen</t>
+          <t>https://www.antaranews.com/berita/5680423/pendaftaran-upacara-hut-ri-di-istana-dibuka-ini-dokumen-yang-wajib-disiapkan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_163e90d67c855177fcf9553fd9012181.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2116,28 +2116,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rublev tersingkir, De Minaur ke babak ketiga ATP Masters 1000 Montreal</t>
+          <t>Survei Herbalife: Budaya "Wellness" Kian Menguat di Asia Pasifik, Empat dari Lima Konsumen Prioritaskan Kesehatan Holistik</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:02:59 +0700</t>
+          <t>Wed, 05 Aug 2026 11:12:18 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unggulan ke-10 Andrey Rublev tersingkir secara dramatis dari National Bank Open di Montreal, Kanada, setelah dikalahkan ...</t>
+          <t>Budaya gaya hidup sehat (wellness) semakin mengakar di kawasan Asia Pasifik (APAC). Hal itu terungkap dalam survei ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680399/rublev-tersingkir-de-minaur-ke-babak-ketiga-atp-masters-1000-montreal</t>
+          <t>https://www.antaranews.com/berita/5680420/survei-herbalife-budaya-wellness-kian-menguat-di-asia-pasifik-empat-dari-lima-konsumen-prioritaskan-kesehatan-holistik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0148.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Budaya-Wellness-Asia.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2154,28 +2154,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Polisi tangkap pelaku pembuang mayat dalam karung di Depok</t>
+          <t>Warga bentangkan bendera Merah Putih sepanjang 400 meter sambut HUT ke-81 RI di Tangerang</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:45 +0700</t>
+          <t>Wed, 05 Aug 2026 11:11:44 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kepolisian menangkap pria berinisial SA yang diduga melakukan pembunuhan dalam kasus penemuan mayat dalam karung di ...</t>
+          <t>Foto udara bendera Merah Putih membentang menutupi jalan di Perumahan Puri Dewata Indah, Cipondoh, Kota Tangerang, ...</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680397/polisi-tangkap-pelaku-pembuang-mayat-dalam-karung-di-depok</t>
+          <t>https://www.antaranews.com/foto/5680417/warga-bentangkan-bendera-merah-putih-sepanjang-400-meter-sambut-hut-ke-81-ri-di-tangerang</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/25/Ilustrassi-penangkapan-pelaku.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bendera-Merah-Putih-sepanjang-400-meter-di-Tangerang-482026-pma-1.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Komisi Eropa sebut migrasi ilegal turun 55 persen dalam dua tahun</t>
+          <t>Irak akan bangun infrastruktur pipa minyak baru ke Turki dan Suriah</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:37 +0700</t>
+          <t>Wed, 05 Aug 2026 11:11:24 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Komisaris Eropa Urusan Dalam Negeri dan Migrasi, Magnus Brunner, mengatakan jumlah penyeberangan ilegal di perbatasan ...</t>
+          <t>Irak berencana segera memulai pembangunan pipa minyak baru menuju Suriah dan Turki guna mendiversifikasi rute ekspor ...</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680393/komisi-eropa-sebut-migrasi-ilegal-turun-55-persen-dalam-dua-tahun</t>
+          <t>https://www.antaranews.com/berita/5680415/irak-akan-bangun-infrastruktur-pipa-minyak-baru-ke-turki-dan-suriah</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/02/06/kapal-pengungsi-karam-di-pulau-Yunani.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk_1.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sabalenka dan Swiatek mulus ke babak ketiga WTA 1000 Toronto</t>
+          <t>Pemprov DKI bekali warga Jakpus keterampilan berwirausaha</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:55:49 +0700</t>
+          <t>Wed, 05 Aug 2026 11:08:43 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Unggulan pertama Aryna Sabalenka dan unggulan ketujuh Iga Swiatek melangkah mulus ke babak ketiga WTA 1000 National ...</t>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta membekali warga Jakarta Pusat (Jakpus) dengan keterampilan tata boga untuk ...</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680389/sabalenka-dan-swiatek-mulus-ke-babak-ketiga-wta-1000-toronto</t>
+          <t>https://www.antaranews.com/berita/5680411/pemprov-dki-bekali-warga-jakpus-keterampilan-berwirausaha</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0146.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260731_152649.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2268,28 +2268,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dirut SIG pastikan pasokan dan distribusi semen kembali normal di Aceh</t>
+          <t>KY tuntaskan wawancara 9 calon hakim agung kamar pidana</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:54:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:06:06 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Direktur Utama PT Semen Indonesia (Persero) Tbk (SIG) Indrieffouny Indra memastikan pasokan dan distribusi semen di ...</t>
+          <t>Komisi Yudisial (KY) menuntaskan wawancara terhadap sembilan calon hakim agung kamar pidana dalam seleksi terbuka calon ...</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680385/dirut-sig-pastikan-pasokan-dan-distribusi-semen-kembali-normal-di-aceh</t>
+          <t>https://www.antaranews.com/berita/5680407/ky-tuntaskan-wawancara-9-calon-hakim-agung-kamar-pidana</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/3AD3E101-3A97-4CD5-A234-92FC00F364DE.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001843500.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Demi dua siswa, Ali menjaga pintu PAUD tetap terbuka</t>
+          <t>Naik MRT Jakarta kini lebih praktis dengan BRI Kartu Kredit Contactless</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:54:02 +0700</t>
+          <t>Wed, 05 Aug 2026 11:04:09 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aroma asinan Betawi, nasi uduk, telur dadar, dan gorengan memenuhi gang-gang sempit di Bidara Cina, Jakarta Timur. ...</t>
+          <t>Mobilitas masyarakat perkotaan yang dinamis menuntut efisiensi di berbagai lini kehidupan, termasuk dalam hal ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680384/demi-dua-siswa-ali-menjaga-pintu-paud-tetap-terbuka</t>
+          <t>https://www.antaranews.com/berita/5680404/naik-mrt-jakarta-kini-lebih-praktis-dengan-bri-kartu-kredit-contactless</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/paud-az-zahro-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pembayaran-mrt-dengan-kartu-kredit-nirkontak-2829800.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2344,28 +2344,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Prancis matikan tiga reaktor nuklir akibat kekeringan</t>
+          <t>Slovakia: Uni Eropa harus proteksi perbatasan Schengen</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:53:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:03:06 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Perusahaan energi Prancis EDF mematikan tiga reaktor nuklir setelah kondisi kekeringan mengurangi debit air di Sungai ...</t>
+          <t>Menteri Dalam Negeri (Mendagri) Slovakia, Matus Sutaj Estok mengatakan Uni Eropa harus memprioritaskan ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680380/prancis-matikan-tiga-reaktor-nuklir-akibat-kekeringan</t>
+          <t>https://www.antaranews.com/berita/5680400/slovakia-uni-eropa-harus-proteksi-perbatasan-schengen</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/gelombang-panas-di-Prancis.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_163e90d67c855177fcf9553fd9012181.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2377,33 +2377,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Politik</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CPNS 2026 sudah dibuka? Ini penjelasan resmi BKN dan jadwal terbarunya</t>
+          <t>Pemprov DKI libatkan lintas lembaga susun Indeks Demokrasi 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:11:38 +0700</t>
+          <t>Wed, 05 Aug 2026 10:46:18 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Informasi mengenai jadwal pembukaan CPNS 2026 masih menjadi perhatian masyarakat, terutama bagi para pencari kerja yang ...</t>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta melibatkan Badan Pusat Statistik (BPS), kalangan akademisi, lembaga ...</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680245/cpns-2026-sudah-dibuka-ini-penjelasan-resmi-bkn-dan-jadwal-terbarunya</t>
+          <t>https://www.antaranews.com/berita/5680371/pemprov-dki-libatkan-lintas-lembaga-susun-indeks-demokrasi-2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/WhatsApp-Image-2026-07-01-at-16.51.39.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/26/1000130888.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2415,456 +2415,456 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kronologi Kunaefi Dimutilasi Kenalan di Medsos hingga Pelaku Ditangkap</t>
+          <t>Korlantas terapkan "face recognition" pada ETLE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:02:08 +0700</t>
+          <t>Wed, 05 Aug 2026 10:10:38 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Penemuan jasad mutilasi Kunaefi di Depok menggegerkan warga. Pelaku Saepul, kenalan di media sosial, ditangkap setelah membunuh dan memutilasi korban.</t>
+          <t>Korps Lalu Lintas Polri menerapkan teknologi pengenalan wajah (face recognition) pada sistem Electronic Traffic Law ...</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605079/kronologi-kunaefi-dimutilasi-kenalan-di-medsos-hingga-pelaku-ditangkap</t>
+          <t>https://www.antaranews.com/berita/5680351/korlantas-terapkan-face-recognition-pada-etle</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/08/jumlah-pelanggaran-etle-meningkat-2724782.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bareskrim Limpahkan Tersangka Kasus Narkoba 'The Doctor' ke Kejari Jaksel</t>
+          <t>Menko Pangan tawarkan peluang investasi dalam program strategis pangan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:56:39 +0700</t>
+          <t>Wed, 05 Aug 2026 09:57:28 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bareskrim melimpahkan tersangka kasus narkoba, Andre Fernando Tjandra alias Charlie alias 'The Doctor', ke Kejaksaan Negeri Jakarta Selatan.</t>
+          <t>Menteri Koordinator (Menko) Bidang Pangan Zulkifli Hasan (Zulhas) menawarkan peluang investasi kepada dunia usaha ...</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605073/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel</t>
+          <t>https://www.antaranews.com/berita/5680336/menko-pangan-tawarkan-peluang-investasi-dalam-program-strategis-pangan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel-dok-polri-1785905794036_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000177508_1.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DPD RI Bangun Kantor di Serang Banten, Siap Tampung Aspirasi Warga</t>
+          <t>Kemenko IPK: Ada kajian awal perpanjangan kereta cepat ke Surabaya</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:55:56 +0700</t>
+          <t>Wed, 05 Aug 2026 09:50:53 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DPd RI akan membangun kantor perwakilan di Kota Serang, Banten. Kantor tersebut dibangun untuk mempermudah masyarakat Banten menyampaikan aspirasinya.</t>
+          <t>Kementerian Koordinator Bidang Infrastruktur dan Pembangunan Kewilayahan (Kemenko IPK) mengungkapkan sudah ada kajian ...</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605072/dpd-ri-bangun-kantor-di-serang-banten-siap-tampung-aspirasi-warga</t>
+          <t>https://www.antaranews.com/berita/5680329/kemenko-ipk-ada-kajian-awal-perpanjangan-kereta-cepat-ke-surabaya</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-ri-sultan-najamudin-di-acara-groundbreaking-kantor-perwakilan-dpd-ri-di-kota-serang-ariefdetikcom-1785905595298_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-09.36.24_1.jpeg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jepang Perkuat Militernya, Adik Kim Jong Un Murka!</t>
+          <t>Rupiah pada Rabu pagi menguat jadi Rp17.972 per dolar AS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:49:16 +0700</t>
+          <t>Wed, 05 Aug 2026 09:09:56 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
+          <t>Nilai tukar rupiah pada Rabu pagi bergerak menguat 55 poin atau 0,31 persen menjadi Rp17.972 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8605067/jepang-perkuat-militernya-adik-kim-jong-un-murka</t>
+          <t>https://www.antaranews.com/berita/5680283/rupiah-pada-rabu-pagi-menguat-jadi-rp17972-per-dolar-as</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/12/33bee726-0042-4c52-9a21-c328504ce2ff_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828851.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dalam Kontainer dari China</t>
+          <t>Nadiem jalani sidang perdana banding kasus Chromebook</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:15 +0700</t>
+          <t>Wed, 05 Aug 2026 08:50:07 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok gagalkan penyelundupan sepeda motor Harley-Davidson bekas. Penindakan dilakukan berkat teknologi pemindaian dan analisis intelijen.</t>
+          <t>Mantan Menteri Pendidikan, Kebudayaan, Riset, dan Teknologi Nadiem Anwar Makarim dijadwalkan menjalani sidang perdana ...</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605050/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china</t>
+          <t>https://www.antaranews.com/berita/5680267/nadiem-jalani-sidang-perdana-banding-kasus-chromebook</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china-1785904973977_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/Putusan-perkara-korupsi-pengadaan-chromebook-300626-TAL-6.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gempa M 6,4 Guncang Pulau Karatung Sulut</t>
+          <t>Persebaya tantang Persib Bandung di final Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:03 +0700</t>
+          <t>Wed, 05 Aug 2026 07:18:46 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gempa bumi dengan kekuatan magnitudo (M) 6,4 mengguncang kawasan Pulau Karatung, Sulawesi Utara. Gempa tak berpotensi tsunami.</t>
+          <t>Pesepak bola Persebaya Surabaya Yuran Fernandes berselebrasi usai mencetak gol ke gawang Arema FC pada pertandingan ...</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605028/gempa-m-6-4-guncang-pulau-karatung-sulut</t>
+          <t>https://www.antaranews.com/foto/5680215/persebaya-tantang-persib-bandung-di-final-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Persebaya-melaju-ke-final-Piala-Presiden-2026-040826-rzl-7.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Relawan SPPG di Kuningan Diseruduk Saat Cegah Babi Hutan Serang Anak-anak</t>
+          <t>Potret gelombang panas dan karhutla di Eropa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:00 +0700</t>
+          <t>Wed, 05 Aug 2026 03:29:29 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Video viral menunjukkan Anas, relawan SPPG, berjuang menahan babi hutan di Kuningan. Ia tersungkur dan terluka saat berupaya melindungi anak-anak.</t>
+          <t>Eropa sedang menghadapi gelombang panas berkepanjangan dan kekeringan yang meluas. Kondisi tersebut semakin menambah ...</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605027/relawan-sppg-di-kuningan-diseruduk-saat-cegah-babi-hutan-serang-anak-anak</t>
+          <t>https://www.antaranews.com/berita/5680159/potret-gelombang-panas-dan-karhutla-di-eropa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tangkapan-layar-babi-seruduk-warga-di-kuningan-1785814645532_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000022_20260804_CBMFN0A001a.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Momen Haru Pasutri dan 2 Anak Bertemu Lagi Usai Lompat dari KM Mutiara Sentosa</t>
+          <t>Ajax resmi umumkan kedatangan Marc ter Stegen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:35:32 +0700</t>
+          <t>Wed, 05 Aug 2026 00:36:51 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kebakaran KM Mutiara Sentosa 2 di Sumenep sempat memisahkan satu keluarga. Setelah evakuasi, mereka akhirnya berkumpul kembali di RS PHC Surabaya.</t>
+          <t>Klub Liga Belanda Ajax resmi mengumumkan kedatangan penjaga gawang senior Marc-Andre ter Stegen dari klub Liga Spanyol ...</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605021/momen-haru-pasutri-dan-2-anak-bertemu-lagi-usai-lompat-dari-km-mutiara-sentosa</t>
+          <t>https://www.antaranews.com/berita/5680139/ajax-resmi-umumkan-kedatangan-marc-ter-stegen</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-terbakar-1785849470687_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/image-36.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Politik</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kunaefi Korban Mutilasi di Depok Sempat Dilaporkan Hilang oleh Istri</t>
+          <t>CPNS 2026 sudah dibuka? Ini penjelasan resmi BKN dan jadwal terbarunya</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:42 +0700</t>
+          <t>Wed, 05 Aug 2026 08:11:38 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Polisi mengungkap kasus mutilasi di Depok. Korban Kunaefi ditemukan setelah dilaporkan hilang. Pelaku, Saepul, dikenal melalui media sosial.</t>
+          <t>Informasi mengenai jadwal pembukaan CPNS 2026 masih menjadi perhatian masyarakat, terutama bagi para pencari kerja yang ...</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605002/kunaefi-korban-mutilasi-di-depok-sempat-dilaporkan-hilang-oleh-istri</t>
+          <t>https://www.antaranews.com/berita/5680245/cpns-2026-sudah-dibuka-ini-penjelasan-resmi-bkn-dan-jadwal-terbarunya</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/WhatsApp-Image-2026-07-01-at-16.51.39.jpeg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Ekonomi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pria Tangerang Dipaksa Onani dan Direkam Bos, Video Disebar untuk Ancaman</t>
+          <t>Magang Kemenkeu 2026 dibuka, simak syarat, jadwal, dan cara daftarnya</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:23:58 +0700</t>
+          <t>Wed, 05 Aug 2026 07:59:00 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kasus pria dianiaya dan dilecehkan mencuat usai beredar video korban dalam kondisi terluka dan diduga sedang dipaksa masturbasi. Video itu direkam bos korban.</t>
+          <t>Kementerian Keuangan (Kemenkeu) kembali membuka Program Magang Reguler Mahasiswa Periode II Tahun 2026. Program ini ...</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604995/pria-tangerang-dipaksa-onani-dan-direkam-bos-video-disebar-untuk-ancaman</t>
+          <t>https://www.antaranews.com/berita/5680237/magang-kemenkeu-2026-dibuka-simak-syarat-jadwal-dan-cara-daftarnya</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/KUM2.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Hiburan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modus Adaptif Promosi Judi Online: Menunggangi Algoritma Konten Viral</t>
+          <t>Top 10 film Netflix Indonesia terpopuler Agustus 2026, wajib masuk watchlist</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:20:04 +0700</t>
+          <t>Wed, 05 Aug 2026 08:03:43 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Spam judi online naik 128 persen di medsos. Algoritma yang mengutamakan keramaian interaksi ternyata tanpa sadar ikut menyuburkan penyebarannya.</t>
+          <t>Sejumlah film dari berbagai genre masuk daftar Top 10 Netflix Indonesia pada Agustus 2026. Mulai dari horor, aksi, ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://news.detik.com/kolom/d-8604992/modus-adaptif-promosi-judi-online-menunggangi-algoritma-konten-viral</t>
+          <t>https://www.antaranews.com/berita/5680239/top-10-film-netflix-indonesia-terpopuler-agustus-2026-wajib-masuk-watchlist</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/20/ilustrasi-judi-online-lagi_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/12/20/Screenshot_2019-12-20-09-25-04-83-01-1024x683_1.jpeg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trump Ancam Serang Iran Besar-besaran Jika Hormuz Tak Dibuka Segera</t>
+          <t>iOS 27 kapan rilis? Ini daftar iPhone yang kebagian dan fitur barunya</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:17:29 +0700</t>
+          <t>Wed, 05 Aug 2026 08:08:05 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Donald Trump mengatakan bahwa Selat Hormuz akan dibuka segera. Trump mengancam bahwa Iran akan diserang besar-besaran jika selat itu tidak dibuka.</t>
+          <t>Apple resmi memperkenalkan sederet fitur baru yang akan hadir melalui sistem operasi iOS 27. Pembaruan ini membawa ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604989/trump-ancam-serang-iran-besar-besaran-jika-hormuz-tak-dibuka-segera</t>
+          <t>https://www.antaranews.com/berita/5680241/ios-27-kapan-rilis-ini-daftar-iphone-yang-kebagian-dan-fitur-barunya</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/conversation_fcthp95t7kqe_large_2x.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
@@ -2876,28 +2876,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BNN Dorong Penguatan Resiliensi Generasi Muda Lewat Kuliah Umum</t>
+          <t>Mahasiswa Makassar Diserang Busur Panah Usai Tegur Pemotor Kerap Geber Motor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:15:14 +0700</t>
+          <t>Wed, 05 Aug 2026 12:05:59 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BNN RI menggelar Kuliah Umum Nasional tentang resiliensi generasi muda menghadapi narkotika pada 6 Agustus 2026 di Universitas Majalengka.</t>
+          <t>Polisi menangkap pria berinisial NS alias J (22) usai memanah seorang mahasiswa bernama Agus Wirakusuma (21) di Kota Makassar, Sulawesi Selatan (Sulsel).</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604985/bnn-dorong-penguatan-resiliensi-generasi-muda-lewat-kuliah-umum</t>
+          <t>https://news.detik.com/berita/d-8605085/mahasiswa-makassar-diserang-busur-panah-usai-tegur-pemotor-kerap-geber-motor</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/promo-bnn-1785903275205_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/10/makassar_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2914,28 +2914,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Saepul Mutilasi Pria di Depok gegara Cekcok, Potongan Kaki Dibuang ke Kali</t>
+          <t>Golkar Jawab PDIP Soal Politik Bukan Cari Enak, Hormati Parpol Luar Pemerintah</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
+          <t>Wed, 05 Aug 2026 12:04:36 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Polisi telah menangkap Saepul (26) yang diduga melakukan mutilasi terhadap pria bernama Kunaefi (51) di Pancoran Mas, Kota Depok.</t>
+          <t>Waketum Golkar, Ahmad Doli, menegaskan partainya tak pernah jadi oposisi dan konsisten mendukung pembangunan. Golkar menghargai semua posisi partai politik.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604983/saepul-mutilasi-pria-di-depok-gegara-cekcok-potongan-kaki-dibuang-ke-kali</t>
+          <t>https://news.detik.com/berita/d-8605082/golkar-jawab-pdip-soal-politik-bukan-cari-enak-hormati-parpol-luar-pemerintah</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/17/waketum-partai-golkar-ahmad-doli-kurnia_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2952,28 +2952,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pengusaha Singkawang Tewas Ditembak Pembunuh Bayaran, Dalangnya Adik Kandung</t>
+          <t>Kronologi Kunaefi Dimutilasi Kenalan di Medsos hingga Pelaku Ditangkap</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:02:48 +0700</t>
+          <t>Wed, 05 Aug 2026 12:02:08 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Seorang pengusaha bernama Cung Su Liat alias Aliat (55) ditemukan tewas mengenaskan dengan luka tembak di halaman rumahnya Kota Singkawang, Kalimantan Barat.</t>
+          <t>Penemuan jasad mutilasi Kunaefi di Depok menggegerkan warga. Pelaku Saepul, kenalan di media sosial, ditangkap setelah membunuh dan memutilasi korban.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604972/pengusaha-singkawang-tewas-ditembak-pembunuh-bayaran-dalangnya-adik-kandung</t>
+          <t>https://news.detik.com/berita/d-8605079/kronologi-kunaefi-dimutilasi-kenalan-di-medsos-hingga-pelaku-ditangkap</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eksekutor-penembak-pengusaha-di-singkawang-hingga-tewas-dok-resmob-polda-kalbar-1785844579501_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2990,28 +2990,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Terpeleset Saat Cari Ikan, Bocah 5 Tahun Tewas Terseret Arus Kali Ciliwung</t>
+          <t>Bareskrim Limpahkan Tersangka Kasus Narkoba 'The Doctor' ke Kejari Jaksel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:01:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:56:39 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bocah berusia 5 tahun berinisial S tewas setelah terseret arus Kali Ciliwung, Depok. Korban bersama dua temannya awalnya hendak mencari ikan di lokasi.</t>
+          <t>Bareskrim melimpahkan tersangka kasus narkoba, Andre Fernando Tjandra alias Charlie alias 'The Doctor', ke Kejaksaan Negeri Jakarta Selatan.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604971/terpeleset-saat-cari-ikan-bocah-5-tahun-tewas-terseret-arus-kali-ciliwung</t>
+          <t>https://news.detik.com/berita/d-8605073/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/ilustrasi-orang-tenggelam-1781518248434_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel-dok-polri-1785905794036_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3028,28 +3028,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pertahankan Opini WTP, Setjen MPR RI Perkuat Tata Kelola Keuangan</t>
+          <t>DPD RI Bangun Kantor di Serang Banten, Siap Tampung Aspirasi Warga</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:49 +0700</t>
+          <t>Wed, 05 Aug 2026 11:55:56 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Setjen MPR RI mempertahankan opini WTP atas Laporan Keuangan 2025. Deputi Heri Herawan apresiasi transparansi dan akuntabilitas dalam pengelolaan keuangan.</t>
+          <t>DPd RI akan membangun kantor perwakilan di Kota Serang, Banten. Kantor tersebut dibangun untuk mempermudah masyarakat Banten menyampaikan aspirasinya.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604969/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan</t>
+          <t>https://news.detik.com/berita/d-8605072/dpd-ri-bangun-kantor-di-serang-banten-siap-tampung-aspirasi-warga</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan-1785902413926_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-ri-sultan-najamudin-di-acara-groundbreaking-kantor-perwakilan-dpd-ri-di-kota-serang-ariefdetikcom-1785905595298_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3066,28 +3066,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Korban Mutilasi di Depok Ternyata Dibunuh Pria Kenalan di Medsos</t>
+          <t>Jepang Perkuat Militernya, Adik Kim Jong Un Murka!</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:49:16 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya menangkap Saepul, pelaku mutilasi Kunaefi. Korban dan pelaku berkenalan lewat media sosial sebelum pertemuan berujung mutilasi.</t>
+          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604968/korban-mutilasi-di-depok-ternyata-dibunuh-pria-kenalan-di-medsos</t>
+          <t>https://news.detik.com/internasional/d-8605067/jepang-perkuat-militernya-adik-kim-jong-un-murka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/12/33bee726-0042-4c52-9a21-c328504ce2ff_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3104,28 +3104,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Merah Putih Membelah Jalan Tangerang, Aksi Warga Sambut Kemerdekaan RI Bikin Takjub</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dalam Kontainer dari China</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:15 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Warga Tangerang membentangkan bendera Merah Putih sepanjang 400 meter di jalan perumahan untuk menyambut HUT ke-81 Kemerdekaan RI.</t>
+          <t>Bea Cukai Tanjung Priok gagalkan penyelundupan sepeda motor Harley-Davidson bekas. Penindakan dilakukan berkat teknologi pemindaian dan analisis intelijen.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8604436/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub</t>
+          <t>https://news.detik.com/berita/d-8605050/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub-1785847891040_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china-1785904973977_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3142,28 +3142,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ayah dan Paman Pemerkosa Gadis di Situbondo Divonis 20 Tahun Penjara</t>
+          <t>Gempa M 6,4 Guncang Pulau Karatung Sulut</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:58:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:03 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Majelis hakim Pengadilan Negeri Situbondo, Jawa Timur, menjatuhkan vonis masing-masing 20 tahun penjara kepada BH (42) dan BS (42).</t>
+          <t>Gempa bumi dengan kekuatan magnitudo (M) 6,4 mengguncang kawasan Pulau Karatung, Sulawesi Utara. Gempa tak berpotensi tsunami.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604966/ayah-dan-paman-pemerkosa-gadis-di-situbondo-divonis-20-tahun-penjara</t>
+          <t>https://news.detik.com/berita/d-8605028/gempa-m-6-4-guncang-pulau-karatung-sulut</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/04/04/2e7993e1-d03b-49c3-9f3d-8a913c8dc5d2_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina Luka di Wajah dan Kepala Usai Diduga Dianiaya Pacar</t>
+          <t>Relawan SPPG di Kuningan Diseruduk Saat Cegah Babi Hutan Serang Anak-anak</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:57:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:00 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina diduga dianiaya kekasihnya, KB, di Jakarta Selatan. Ia mengalami luka di wajah dan kepala.</t>
+          <t>Video viral menunjukkan Anas, relawan SPPG, berjuang menahan babi hutan di Kuningan. Ia tersungkur dan terluka saat berupaya melindungi anak-anak.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604961/aktris-sali-irsalina-luka-di-wajah-dan-kepala-usai-diduga-dianiaya-pacar</t>
+          <t>https://news.detik.com/berita/d-8605027/relawan-sppg-di-kuningan-diseruduk-saat-cegah-babi-hutan-serang-anak-anak</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/19/penganiayaan-mantan-pacar-di-gianyar_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tangkapan-layar-babi-seruduk-warga-di-kuningan-1785814645532_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Identitas Mayat Tanpa Kaki di Depok Terungkap, Namanya Kunaefi</t>
+          <t>Momen Haru Pasutri dan 2 Anak Bertemu Lagi Usai Lompat dari KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:56:09 +0700</t>
+          <t>Wed, 05 Aug 2026 11:35:32 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kasus mutilasi di Depok terungkap. Korban Kunaefi (51) ditemukan dalam karung. Pelaku, Saepul (26), ditangkap saat melarikan diri ke Pandeglang.</t>
+          <t>Kebakaran KM Mutiara Sentosa 2 di Sumenep sempat memisahkan satu keluarga. Setelah evakuasi, mereka akhirnya berkumpul kembali di RS PHC Surabaya.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604959/identitas-mayat-tanpa-kaki-di-depok-terungkap-namanya-kunaefi</t>
+          <t>https://news.detik.com/berita/d-8605021/momen-haru-pasutri-dan-2-anak-bertemu-lagi-usai-lompat-dari-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-terbakar-1785849470687_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3256,28 +3256,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Penjual Miras di Lokananta Gugat Pemkot Solo Usai Dirazia</t>
+          <t>Kunaefi Korban Mutilasi di Depok Sempat Dilaporkan Hilang oleh Istri</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:53:36 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:42 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Manajemen kafe Ruang Bahagia menggugat Pemkot Solo setelah dirazia oleh Satpol PP.</t>
+          <t>Polisi mengungkap kasus mutilasi di Depok. Korban Kunaefi ditemukan setelah dilaporkan hilang. Pelaku, Saepul, dikenal melalui media sosial.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604956/penjual-miras-di-lokananta-gugat-pemkot-solo-usai-dirazia</t>
+          <t>https://news.detik.com/berita/d-8605002/kunaefi-korban-mutilasi-di-depok-sempat-dilaporkan-hilang-oleh-istri</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sidang-di-pn-solo-1785834131308_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3294,28 +3294,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ramai Kabar Amunisi AS Menipis Gegara Perang Iran, Trump Bilang Gini</t>
+          <t>Pria Tangerang Dipaksa Onani dan Direkam Bos, Video Disebar untuk Ancaman</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:52:07 +0700</t>
+          <t>Wed, 05 Aug 2026 11:23:58 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pasokan amunisi AS dilaporkan semakin menipis hingga ke level yang mengkhawatirkan akibat perang Iran. Trump buka suara.</t>
+          <t>Kasus pria dianiaya dan dilecehkan mencuat usai beredar video korban dalam kondisi terluka dan diduga sedang dipaksa masturbasi. Video itu direkam bos korban.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604954/ramai-kabar-amunisi-as-menipis-gegara-perang-iran-trump-bilang-gini</t>
+          <t>https://news.detik.com/berita/d-8604995/pria-tangerang-dipaksa-onani-dan-direkam-bos-video-disebar-untuk-ancaman</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/29/44d7a464-752c-4519-91cd-6e13284a464c_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2 Truk Tabrakan di Gunungputri Bogor, Sopir Terjepit di Kabin Kemudi</t>
+          <t>Modus Adaptif Promosi Judi Online: Menunggangi Algoritma Konten Viral</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:48:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:20:04 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dua truk terlibat kecelakaan di Jalan Raya Wanaherang, Bogor. Sopir truk mengalami luka ringan setelah terjepit di ruang kemudi dan dilarikan ke rumah sakit.</t>
+          <t>Spam judi online naik 128 persen di medsos. Algoritma yang mengutamakan keramaian interaksi ternyata tanpa sadar ikut menyuburkan penyebarannya.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604951/2-truk-tabrakan-di-gunungputri-bogor-sopir-terjepit-di-kabin-kemudi</t>
+          <t>https://news.detik.com/kolom/d-8604992/modus-adaptif-promosi-judi-online-menunggangi-algoritma-konten-viral</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/20/ilustrasi-judi-online-lagi_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3370,28 +3370,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pilu Pemuda Jabar Jadi Love Scammer di Kamboja: Tak Digaji-Dicambuk Sesama WNI</t>
+          <t>Trump Ancam Serang Iran Besar-besaran Jika Hormuz Tak Dibuka Segera</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:41:05 +0700</t>
+          <t>Wed, 05 Aug 2026 11:17:29 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pemuda asal Kecamatan Dayeuhkolot, Kabupaten Bandung, ini mengaku tidak digaji selama bekerja di sana hingga mendapatkan beragam penganiayaan fisik.</t>
+          <t>Donald Trump mengatakan bahwa Selat Hormuz akan dibuka segera. Trump mengancam bahwa Iran akan diserang besar-besaran jika selat itu tidak dibuka.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604941/pilu-pemuda-jabar-jadi-love-scammer-di-kamboja-tak-digaji-dicambuk-sesama-wni</t>
+          <t>https://news.detik.com/internasional/d-8604989/trump-ancam-serang-iran-besar-besaran-jika-hormuz-tak-dibuka-segera</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/rizki-nur-fadhilah-20-saat-berbincang-di-kabupaten-bandung-1785833506651_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3408,28 +3408,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Anggota DPRD Tangsel Ahmad Andi Wibowo Meninggal Akibat Kecelakaan di Cipali</t>
+          <t>BNN Dorong Penguatan Resiliensi Generasi Muda Lewat Kuliah Umum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:40:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:15:14 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Anggota DPRD Tangerang Selatan dari fraksi PKB, Ahmad Andi Wibowo, meninggal dunia. Ahmad Andi meninggal dunia akibat kecelakaan di Tol Cipali Km 72.</t>
+          <t>BNN RI menggelar Kuliah Umum Nasional tentang resiliensi generasi muda menghadapi narkotika pada 6 Agustus 2026 di Universitas Majalengka.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604940/anggota-dprd-tangsel-ahmad-andi-wibowo-meninggal-akibat-kecelakaan-di-cipali</t>
+          <t>https://news.detik.com/berita/d-8604985/bnn-dorong-penguatan-resiliensi-generasi-muda-lewat-kuliah-umum</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ahmad-andi-wibowo-dok-istimewa-1785901183190_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/promo-bnn-1785903275205_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3446,28 +3446,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Proyek Jembatan Rusia-Korut Bikin Waswas Ukraina</t>
+          <t>Saepul Mutilasi Pria di Depok gegara Cekcok, Potongan Kaki Dibuang ke Kali</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:37:24 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Di wilayah terpencil di perbatasan Rusia-Korut, kedua negara sedang membangun jembatan. Proyek ini membuat Ukraina, yang terletak sejauh 10.000 km, waswas.</t>
+          <t>Polisi telah menangkap Saepul (26) yang diduga melakukan mutilasi terhadap pria bernama Kunaefi (51) di Pancoran Mas, Kota Depok.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://news.detik.com/dw/d-8604936/proyek-jembatan-rusia-korut-bikin-waswas-ukraina</t>
+          <t>https://news.detik.com/berita/d-8604983/saepul-mutilasi-pria-di-depok-gegara-cekcok-potongan-kaki-dibuang-ke-kali</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kenapa-ukraina-waspadai-proyek-jembatan-rusia-korut-1785901044051.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3484,28 +3484,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Diduga Dianiaya Pacar, Aktris Sinetron Sali Irsalina Lapor Polisi</t>
+          <t>Pengusaha Singkawang Tewas Ditembak Pembunuh Bayaran, Dalangnya Adik Kandung</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:33:20 +0700</t>
+          <t>Wed, 05 Aug 2026 11:02:48 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina melaporkan dugaan penganiayaan oleh kekasihnya ke Polres Metro Jakarta Selatan. Ia mengalami luka akibat kekerasan fisik.</t>
+          <t>Seorang pengusaha bernama Cung Su Liat alias Aliat (55) ditemukan tewas mengenaskan dengan luka tembak di halaman rumahnya Kota Singkawang, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604926/diduga-dianiaya-pacar-aktris-sinetron-sali-irsalina-lapor-polisi</t>
+          <t>https://news.detik.com/berita/d-8604972/pengusaha-singkawang-tewas-ditembak-pembunuh-bayaran-dalangnya-adik-kandung</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/11/ilustrasi-kekerasan-terhadap-perempuan-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eksekutor-penembak-pengusaha-di-singkawang-hingga-tewas-dok-resmob-polda-kalbar-1785844579501_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3522,28 +3522,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kapolda Sumsel Serahkan Penghargaan WBK &amp;amp; Pelayanan Prima kepada 11 Satuan</t>
+          <t>Terpeleset Saat Cari Ikan, Bocah 5 Tahun Tewas Terseret Arus Kali Ciliwung</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:25:23 +0700</t>
+          <t>Wed, 05 Aug 2026 11:01:27 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kapolda Sumsel, Irjen Pol. Sandi Nugroho, menyerahkan penghargaan WBK dan Pelayanan Publik Prima kepada 11 satuan kerja.</t>
+          <t>Bocah berusia 5 tahun berinisial S tewas setelah terseret arus Kali Ciliwung, Depok. Korban bersama dua temannya awalnya hendak mencari ikan di lokasi.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8604921/kapolda-sumsel-serahkan-penghargaan-wbk-pelayanan-prima-kepada-11-satuan</t>
+          <t>https://news.detik.com/berita/d-8604971/terpeleset-saat-cari-ikan-bocah-5-tahun-tewas-terseret-arus-kali-ciliwung</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polda-sumsel-1785900305377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/ilustrasi-orang-tenggelam-1781518248434_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3560,28 +3560,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kuda Pacu Pemenang Kejurnas Hangus Terbakar di KM Mutiara Sentosa</t>
+          <t>Pertahankan Opini WTP, Setjen MPR RI Perkuat Tata Kelola Keuangan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:23:20 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:49 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kuda pacu yang baru meraih juara nasional milik warga Kabupaten Jeneponto, Sulsel, ikut terbakar dalam insiden KM Mutiara Sentosa 2 di perairan utara Madura.</t>
+          <t>Setjen MPR RI mempertahankan opini WTP atas Laporan Keuangan 2025. Deputi Heri Herawan apresiasi transparansi dan akuntabilitas dalam pengelolaan keuangan.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604917/kuda-pacu-pemenang-kejurnas-hangus-terbakar-di-km-mutiara-sentosa</t>
+          <t>https://news.detik.com/berita/d-8604969/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan-1785902413926_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3598,28 +3598,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pria Ber-hoodie Pembakar Bendera Juga Sasar Bangunan di Bandung dan Cimahi</t>
+          <t>Korban Mutilasi di Depok Ternyata Dibunuh Pria Kenalan di Medsos</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:19:45 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:27 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heboh aksi pria membakar bendera Merah Putih di sebuah rumah di Maleber, Kecamatan Andir, Kota Bandung, Jabar. Pria itu diduga membakar bangunan di tempat lain.</t>
+          <t>Polda Metro Jaya menangkap Saepul, pelaku mutilasi Kunaefi. Korban dan pelaku berkenalan lewat media sosial sebelum pertemuan berujung mutilasi.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604913/pria-ber-hoodie-pembakar-bendera-juga-sasar-bangunan-di-bandung-dan-cimahi</t>
+          <t>https://news.detik.com/berita/d-8604968/korban-mutilasi-di-depok-ternyata-dibunuh-pria-kenalan-di-medsos</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/viral-aksi-pembakaran-bendera-merah-putih-di-bandung-1785755169202_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3636,28 +3636,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pelaku Mutilasi di Depok Ditangkap Saat Kabur ke Pandeglang</t>
+          <t>Merah Putih Membelah Jalan Tangerang, Aksi Warga Sambut Kemerdekaan RI Bikin Takjub</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:17:26 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:06 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tim Resmob Polda Metro Jaya menangkap pelaku mutilasi di Depok, berinisial SA, saat melarikan diri ke Banten. Jasad korban ditemukan di lahan kosong.</t>
+          <t>Warga Tangerang membentangkan bendera Merah Putih sepanjang 400 meter di jalan perumahan untuk menyambut HUT ke-81 Kemerdekaan RI.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604903/pelaku-mutilasi-di-depok-ditangkap-saat-kabur-ke-pandeglang</t>
+          <t>https://news.detik.com/foto-news/d-8604436/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub-1785847891040_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3674,28 +3674,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Viral Sejumlah Pemotor Jatuh gegara Tetesan Air Lindi di Bantargebang</t>
+          <t>Ayah dan Paman Pemerkosa Gadis di Situbondo Divonis 20 Tahun Penjara</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:13:21 +0700</t>
+          <t>Wed, 05 Aug 2026 10:58:57 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sejumlah pemotor terjatuh di Jalan Siliwangi Pangkalan 5, Bantargebang, Kota Bekasi. Peristiwa itu diduga terjadi akibat jalan linci karena tetesan air lindi.</t>
+          <t>Majelis hakim Pengadilan Negeri Situbondo, Jawa Timur, menjatuhkan vonis masing-masing 20 tahun penjara kepada BH (42) dan BS (42).</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604899/viral-sejumlah-pemotor-jatuh-gegara-tetesan-air-lindi-di-bantargebang</t>
+          <t>https://news.detik.com/berita/d-8604966/ayah-dan-paman-pemerkosa-gadis-di-situbondo-divonis-20-tahun-penjara</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sejumlah-pemotor-berjatuhan-di-bantargebang-kota-bekasi-akibat-tetesan-air-lindi-1785899556055_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/04/04/2e7993e1-d03b-49c3-9f3d-8a913c8dc5d2_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3712,28 +3712,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Berkas Lengkap, 3 Tersangka Kasus Tambang Emas Ilegal Segera Disidang</t>
+          <t>Aktris Sali Irsalina Luka di Wajah dan Kepala Usai Diduga Dianiaya Pacar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:07:53 +0700</t>
+          <t>Wed, 05 Aug 2026 10:57:57 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polisi menetapkan 5 tersangka dalam kasus tambang emas ilegal. Tiga berkas perkara telah lengkap dan siap disidang, sementara dua lainnya masih dalam proses.</t>
+          <t>Aktris Sali Irsalina diduga dianiaya kekasihnya, KB, di Jakarta Selatan. Ia mengalami luka di wajah dan kepala.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604893/berkas-lengkap-3-tersangka-kasus-tambang-emas-ilegal-segera-disidang</t>
+          <t>https://news.detik.com/berita/d-8604961/aktris-sali-irsalina-luka-di-wajah-dan-kepala-usai-diduga-dianiaya-pacar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-polri-bongkar-kasus-tambang-emas-ilegal-1785899230949_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/19/penganiayaan-mantan-pacar-di-gianyar_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3750,28 +3750,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Resmob Polda Metro Jaya Tangkap Pelaku Mutilasi di Depok!</t>
+          <t>Identitas Mayat Tanpa Kaki di Depok Terungkap, Namanya Kunaefi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:06:11 +0700</t>
+          <t>Wed, 05 Aug 2026 10:56:09 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kasus mayat mutilasi di Pancoran Mas, Depok terungkap. Polisi telah menangkap pelaku, sementara motif pembunuhan masih didalami kepolisian.</t>
+          <t>Kasus mutilasi di Depok terungkap. Korban Kunaefi (51) ditemukan dalam karung. Pelaku, Saepul (26), ditangkap saat melarikan diri ke Pandeglang.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604889/resmob-polda-metro-jaya-tangkap-pelaku-mutilasi-di-depok</t>
+          <t>https://news.detik.com/berita/d-8604959/identitas-mayat-tanpa-kaki-di-depok-terungkap-namanya-kunaefi</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3788,28 +3788,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Air Embung Surut, Nasib Ratusan Hektare Sawah Indramayu di Ujung Ancaman</t>
+          <t>Penjual Miras di Lokananta Gugat Pemkot Solo Usai Dirazia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:00:59 +0700</t>
+          <t>Wed, 05 Aug 2026 10:53:36 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Embung irigasi Balongan, Indramayu, mengering akibat minim hujan. Dasar embung terlihat kering hingga menyisakan bangkai ikan.</t>
+          <t>Manajemen kafe Ruang Bahagia menggugat Pemkot Solo setelah dirazia oleh Satpol PP.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8604424/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman</t>
+          <t>https://news.detik.com/berita/d-8604956/penjual-miras-di-lokananta-gugat-pemkot-solo-usai-dirazia</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman-1785847218259_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sidang-di-pn-solo-1785834131308_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3826,28 +3826,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Daftar Upacara HUT ke-81 RI di Istana: Jadwal, Cara, Syarat</t>
+          <t>Ramai Kabar Amunisi AS Menipis Gegara Perang Iran, Trump Bilang Gini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:59:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:52:07 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pendaftaran upacara HUT ke-81 RI dibuka 5-7 Agustus 2026. Siapkan dokumen dan ikuti syarat untuk mendaftar secara gratis di Istana Merdeka.</t>
+          <t>Pasokan amunisi AS dilaporkan semakin menipis hingga ke level yang mengkhawatirkan akibat perang Iran. Trump buka suara.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604878/daftar-upacara-hut-ke-81-ri-di-istana-jadwal-cara-syarat</t>
+          <t>https://news.detik.com/internasional/d-8604954/ramai-kabar-amunisi-as-menipis-gegara-perang-iran-trump-bilang-gini</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/17/momen-upacara-detik-detik-proklamasi-di-istana-merdeka-1755407430559_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/29/44d7a464-752c-4519-91cd-6e13284a464c_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3864,28 +3864,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kapal India Tenggelam Usai Diserang di Laut Merah, 14 ABK Selamat</t>
+          <t>2 Truk Tabrakan di Gunungputri Bogor, Sopir Terjepit di Kabin Kemudi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:57:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:48:18 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sebuah kapal komersial berbendera India tenggelam setelah dihantam serangan di Laut Merah. Untungnya, semua ABK berhasil diselamatkan.</t>
+          <t>Dua truk terlibat kecelakaan di Jalan Raya Wanaherang, Bogor. Sopir truk mengalami luka ringan setelah terjepit di ruang kemudi dan dilarikan ke rumah sakit.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604874/kapal-india-tenggelam-usai-diserang-di-laut-merah-14-abk-selamat</t>
+          <t>https://news.detik.com/berita/d-8604951/2-truk-tabrakan-di-gunungputri-bogor-sopir-terjepit-di-kabin-kemudi</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/iran-crisisyemen-red-sea-1784214791940_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3902,28 +3902,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mesin Mati Mendadak, Mobil Terbakar di Tol Jagorawi Arah Jakarta</t>
+          <t>Pilu Pemuda Jabar Jadi Love Scammer di Kamboja: Tak Digaji-Dicambuk Sesama WNI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:52:13 +0700</t>
+          <t>Wed, 05 Aug 2026 10:41:05 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Satu unit mobil SUV terbakar di Km 43/100 Tol Jagorawi, Bogor Timur, Kota Bogor. Kebakaran usai mesin mobil mati dan muncul api dari bawah kap depan.</t>
+          <t>Pemuda asal Kecamatan Dayeuhkolot, Kabupaten Bandung, ini mengaku tidak digaji selama bekerja di sana hingga mendapatkan beragam penganiayaan fisik.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604866/mesin-mati-mendadak-mobil-terbakar-di-tol-jagorawi-arah-jakarta</t>
+          <t>https://news.detik.com/berita/d-8604941/pilu-pemuda-jabar-jadi-love-scammer-di-kamboja-tak-digaji-dicambuk-sesama-wni</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satu-unit-mobil-suv-terbakar-di-km-43100-tol-jagorawi-bogor-timur-kota-bogor-dok-istimewa-1785898155496_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/rizki-nur-fadhilah-20-saat-berbincang-di-kabupaten-bandung-1785833506651_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kondisi Mayat Mutilasi di Depok: Tangan Terikat dan Leher Luka Sayat</t>
+          <t>Anggota DPRD Tangsel Ahmad Andi Wibowo Meninggal Akibat Kecelakaan di Cipali</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:42:22 +0700</t>
+          <t>Wed, 05 Aug 2026 10:40:01 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pihak kepolisian menyelidiki penemuan mayat mutilasi di Pancoran Mas, Depok. Korban ditemukan tanpa kaki, terikat, dan dalam kondisi mengenaskan.</t>
+          <t>Anggota DPRD Tangerang Selatan dari fraksi PKB, Ahmad Andi Wibowo, meninggal dunia. Ahmad Andi meninggal dunia akibat kecelakaan di Tol Cipali Km 72.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604858/kondisi-mayat-mutilasi-di-depok-tangan-terikat-dan-leher-luka-sayat</t>
+          <t>https://news.detik.com/berita/d-8604940/anggota-dprd-tangsel-ahmad-andi-wibowo-meninggal-akibat-kecelakaan-di-cipali</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ahmad-andi-wibowo-dok-istimewa-1785901183190_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3978,28 +3978,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trump Cabut Visa Duta Besar Brasil untuk AS, Ada Apa?</t>
+          <t>Proyek Jembatan Rusia-Korut Bikin Waswas Ukraina</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:34:55 +0700</t>
+          <t>Wed, 05 Aug 2026 10:37:24 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pemerintahan Trump mencabut visa DUbes Brasil untuk AS, Maria Luiz Ribeiro Viotti. Apa alasannya?</t>
+          <t>Di wilayah terpencil di perbatasan Rusia-Korut, kedua negara sedang membangun jembatan. Proyek ini membuat Ukraina, yang terletak sejauh 10.000 km, waswas.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604850/trump-cabut-visa-duta-besar-brasil-untuk-as-ada-apa</t>
+          <t>https://news.detik.com/dw/d-8604936/proyek-jembatan-rusia-korut-bikin-waswas-ukraina</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dubes-brasil-untuk-as-maria-luiza-ribeiro-viotti-1785897254293_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kenapa-ukraina-waspadai-proyek-jembatan-rusia-korut-1785901044051.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4016,28 +4016,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Misteri Mayat Mutilasi di Depok Dibuang 12 Hari Lalu</t>
+          <t>Diduga Dianiaya Pacar, Aktris Sinetron Sali Irsalina Lapor Polisi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:26:42 +0700</t>
+          <t>Wed, 05 Aug 2026 10:33:20 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jasad pria mutilasi ditemukan di Pancoran Mas, Depok, setelah 12 hari. Identitas korban belum diketahui, polisi masih menyelidiki kasus ini.</t>
+          <t>Aktris Sali Irsalina melaporkan dugaan penganiayaan oleh kekasihnya ke Polres Metro Jakarta Selatan. Ia mengalami luka akibat kekerasan fisik.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604839/misteri-mayat-mutilasi-di-depok-dibuang-12-hari-lalu</t>
+          <t>https://news.detik.com/berita/d-8604926/diduga-dianiaya-pacar-aktris-sinetron-sali-irsalina-lapor-polisi</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/11/ilustrasi-kekerasan-terhadap-perempuan-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4054,28 +4054,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RI Kecam Keras Israel Serang Gaza Lagi: Sengaja Hambat Peace Plan</t>
+          <t>Kapolda Sumsel Serahkan Penghargaan WBK &amp;amp; Pelayanan Prima kepada 11 Satuan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:23:19 +0700</t>
+          <t>Wed, 05 Aug 2026 10:25:23 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Indonesia mengecam serangan Israel ke Gaza yang menghambat kesepakatan perdamaian. Kemlu mendesak Israel menghentikan serangan dan memenuhi komitmen perjanjian.</t>
+          <t>Kapolda Sumsel, Irjen Pol. Sandi Nugroho, menyerahkan penghargaan WBK dan Pelayanan Publik Prima kepada 11 satuan kerja.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604835/ri-kecam-keras-israel-serang-gaza-lagi-sengaja-hambat-peace-plan</t>
+          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8604921/kapolda-sumsel-serahkan-penghargaan-wbk-pelayanan-prima-kepada-11-satuan</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/09/11/gedung-pancasila-di-kemlu_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polda-sumsel-1785900305377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4092,28 +4092,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Siap-siap War! Tiket Upacara HUT ke-81 RI di Istana Dibuka Hari Ini Pukul 10.00</t>
+          <t>Kuda Pacu Pemenang Kejurnas Hangus Terbakar di KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:21:08 +0700</t>
+          <t>Wed, 05 Aug 2026 10:23:20 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pemerintah sudah membuka pendaftaran upacara HUT ke-81 RI di Istana Merdeka Jakarta. Siap-siap war!</t>
+          <t>Kuda pacu yang baru meraih juara nasional milik warga Kabupaten Jeneponto, Sulsel, ikut terbakar dalam insiden KM Mutiara Sentosa 2 di perairan utara Madura.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604828/siap-siap-war-tiket-upacara-hut-ke-81-ri-di-istana-dibuka-hari-ini-pukul-10-00</t>
+          <t>https://news.detik.com/berita/d-8604917/kuda-pacu-pemenang-kejurnas-hangus-terbakar-di-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/01/31/85d6b0ca-c154-414b-a198-62b91ce4debc_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4130,28 +4130,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jakarta Selatan Diprediksi Hujan Ringan Sore Ini</t>
+          <t>Pria Ber-hoodie Pembakar Bendera Juga Sasar Bangunan di Bandung dan Cimahi</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:56:17 +0700</t>
+          <t>Wed, 05 Aug 2026 10:19:45 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BMKG mengungkap sebagian wilayah di Jakarta Selatan berpotensi hujan ringan hari ini.</t>
+          <t>Heboh aksi pria membakar bendera Merah Putih di sebuah rumah di Maleber, Kecamatan Andir, Kota Bandung, Jabar. Pria itu diduga membakar bangunan di tempat lain.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604809/jakarta-selatan-diprediksi-hujan-ringan-sore-ini</t>
+          <t>https://news.detik.com/berita/d-8604913/pria-ber-hoodie-pembakar-bendera-juga-sasar-bangunan-di-bandung-dan-cimahi</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/30/ilustrasi-hujan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/viral-aksi-pembakaran-bendera-merah-putih-di-bandung-1785755169202_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4168,28 +4168,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MKD DPR Gelar Rapim Pekan Depan Bahas Laporan 'Kayak Sirkus' ke Deddy Sitorus</t>
+          <t>Pelaku Mutilasi di Depok Ditangkap Saat Kabur ke Pandeglang</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:53:44 +0700</t>
+          <t>Wed, 05 Aug 2026 10:17:26 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mahkamah Kehormatan Dewan DPR RI akan rapat menindaklanjuti laporan wartawan terhadap Deddy Sitorus.</t>
+          <t>Tim Resmob Polda Metro Jaya menangkap pelaku mutilasi di Depok, berinisial SA, saat melarikan diri ke Banten. Jasad korban ditemukan di lahan kosong.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604811/mkd-dpr-gelar-rapim-pekan-depan-bahas-laporan-kayak-sirkus-ke-deddy-sitorus</t>
+          <t>https://news.detik.com/berita/d-8604903/pelaku-mutilasi-di-depok-ditangkap-saat-kabur-ke-pandeglang</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mkd-1785865852673_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4206,28 +4206,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mendagri Wanti-wanti Kepala Daerah Jaga Integritas demi Cegah Korupsi</t>
+          <t>Viral Sejumlah Pemotor Jatuh gegara Tetesan Air Lindi di Bantargebang</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:51:47 +0700</t>
+          <t>Wed, 05 Aug 2026 10:13:21 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mendagri Tito Karnavian menekankan pentingnya integritas kepala daerah dalam mencegah korupsi. Rakor di Surabaya bertujuan memperkuat tata kelola pemerintahan.</t>
+          <t>Sejumlah pemotor terjatuh di Jalan Siliwangi Pangkalan 5, Bantargebang, Kota Bekasi. Peristiwa itu diduga terjadi akibat jalan linci karena tetesan air lindi.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604793/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi</t>
+          <t>https://news.detik.com/berita/d-8604899/viral-sejumlah-pemotor-jatuh-gegara-tetesan-air-lindi-di-bantargebang</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sejumlah-pemotor-berjatuhan-di-bantargebang-kota-bekasi-akibat-tetesan-air-lindi-1785899556055_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4244,28 +4244,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LRT Dukung Pramono Hubungkan 2 JPO Viral Dekat tapi Tak Tersambung di Rasuna</t>
+          <t>Berkas Lengkap, 3 Tersangka Kasus Tambang Emas Ilegal Segera Disidang</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:45:13 +0700</t>
+          <t>Wed, 05 Aug 2026 10:07:53 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gubernur DKI Pramono berjanji menyambungkan dua JPO yang viral di Jalan HR Rasuna Said. LRT Jabodebek siap berkoordinasi.</t>
+          <t>Polisi menetapkan 5 tersangka dalam kasus tambang emas ilegal. Tiga berkas perkara telah lengkap dan siap disidang, sementara dua lainnya masih dalam proses.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604779/lrt-dukung-pramono-hubungkan-2-jpo-viral-dekat-tapi-tak-tersambung-di-rasuna</t>
+          <t>https://news.detik.com/berita/d-8604893/berkas-lengkap-3-tersangka-kasus-tambang-emas-ilegal-segera-disidang</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313180_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-polri-bongkar-kasus-tambang-emas-ilegal-1785899230949_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4282,28 +4282,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Komisi V DPR Bakal Panggil Kemenhub Buntut Kebakaran KMP Mutiara Sentosa</t>
+          <t>Resmob Polda Metro Jaya Tangkap Pelaku Mutilasi di Depok!</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:35:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:06:11 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Komisi V DPR RI akan memanggil Kemenhub terkait kebakaran KMP Mutiara Sentosa 2. Rapat dengan Kemenhub digelar seusai reses DPR RI.</t>
+          <t>Kasus mayat mutilasi di Pancoran Mas, Depok terungkap. Polisi telah menangkap pelaku, sementara motif pembunuhan masih didalami kepolisian.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604773/komisi-v-dpr-bakal-panggil-kemenhub-buntut-kebakaran-kmp-mutiara-sentosa</t>
+          <t>https://news.detik.com/berita/d-8604889/resmob-polda-metro-jaya-tangkap-pelaku-mutilasi-di-depok</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4320,28 +4320,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jelang Kunjungan Trump, Pria Bersenjata Ditangkap di Lapangan Golf Los Angeles</t>
+          <t>Air Embung Surut, Nasib Ratusan Hektare Sawah Indramayu di Ujung Ancaman</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:34:23 +0700</t>
+          <t>Wed, 05 Aug 2026 10:00:59 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Seorang pria bersenjata ditangkap di lapangan golf Trump di LA, dua hari sebelum kunjungannya. Penyelidik menemukan senjata dan catatan mencurigakan.</t>
+          <t>Embung irigasi Balongan, Indramayu, mengering akibat minim hujan. Dasar embung terlihat kering hingga menyisakan bangkai ikan.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604771/jelang-kunjungan-trump-pria-bersenjata-ditangkap-di-lapangan-golf-los-angeles</t>
+          <t>https://news.detik.com/foto-news/d-8604424/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/trump-saat-berpidato-di-gedung-putih-pada-kamis-167-malam-1784277022942_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman-1785847218259_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-turn Depan Stasiun Depok Ditutup, Lalin Arah Jakarta Lancar Pagi Ini</t>
+          <t>Daftar Upacara HUT ke-81 RI di Istana: Jadwal, Cara, Syarat</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:43 +0700</t>
+          <t>Wed, 05 Aug 2026 09:59:39 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Satlantas Polres Metro Depok dan Dishub menutup U-turn di Jalan Kartini untuk mengurangi kemacetan. Penutupan berlaku pada jam sibuk, efektif mulai 3 Agustus.</t>
+          <t>Pendaftaran upacara HUT ke-81 RI dibuka 5-7 Agustus 2026. Siapkan dokumen dan ikuti syarat untuk mendaftar secara gratis di Istana Merdeka.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604766/u-turn-depan-stasiun-depok-ditutup-lalin-arah-jakarta-lancar-pagi-ini</t>
+          <t>https://news.detik.com/berita/d-8604878/daftar-upacara-hut-ke-81-ri-di-istana-jadwal-cara-syarat</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/u-turn-putaran-balik-di-jalan-kartini-depok-ditutup-1785893424229_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/17/momen-upacara-detik-detik-proklamasi-di-istana-merdeka-1755407430559_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4396,28 +4396,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sekda Konawe Selatan Tabrak Adik Saat Digerebek Bareng Selingkuhan di Mobil</t>
+          <t>Kapal India Tenggelam Usai Diserang di Laut Merah, 14 ABK Selamat</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:40 +0700</t>
+          <t>Wed, 05 Aug 2026 09:57:39 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sekda Konawe Selatan Ichsan Porosi (56) menabrak adik kandungnya, Andriani Porosi alias AP (50), saat digerebek berduaan diduga bareng selingkuhan di mobil.</t>
+          <t>Sebuah kapal komersial berbendera India tenggelam setelah dihantam serangan di Laut Merah. Untungnya, semua ABK berhasil diselamatkan.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604765/sekda-konawe-selatan-tabrak-adik-saat-digerebek-bareng-selingkuhan-di-mobil</t>
+          <t>https://news.detik.com/internasional/d-8604874/kapal-india-tenggelam-usai-diserang-di-laut-merah-14-abk-selamat</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/iran-crisisyemen-red-sea-1784214791940_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4434,28 +4434,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Penjelasan BMKG soal Hujan di Jakarta Usai Berminggu-minggu Kering</t>
+          <t>Mesin Mati Mendadak, Mobil Terbakar di Tol Jagorawi Arah Jakarta</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:24:21 +0700</t>
+          <t>Wed, 05 Aug 2026 09:52:13 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hujan turun di Jakarta setelah kering berminggu-minggu. Ini penjelasan BMKG.</t>
+          <t>Satu unit mobil SUV terbakar di Km 43/100 Tol Jagorawi, Bogor Timur, Kota Bogor. Kebakaran usai mesin mobil mati dan muncul api dari bawah kap depan.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604764/penjelasan-bmkg-soal-hujan-di-jakarta-usai-berminggu-minggu-kering</t>
+          <t>https://news.detik.com/berita/d-8604866/mesin-mati-mendadak-mobil-terbakar-di-tol-jagorawi-arah-jakarta</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hujan-deras-guyur-jakarta-usai-berminggu-minggu-kering-1785846576327_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satu-unit-mobil-suv-terbakar-di-km-43100-tol-jagorawi-bogor-timur-kota-bogor-dok-istimewa-1785898155496_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4472,28 +4472,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Puan Berduka KM Mutiara Terbakar: Keamanan Transportasi Laut RI Masih Minim</t>
+          <t>Kondisi Mayat Mutilasi di Depok: Tangan Terikat dan Leher Luka Sayat</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:15:49 +0700</t>
+          <t>Wed, 05 Aug 2026 09:42:22 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KM Mutiara Sentosa 2 terbakar di Madura, menewaskan lima orang. Puan Maharani soroti minimnya keamanan transportasi laut.</t>
+          <t>Pihak kepolisian menyelidiki penemuan mayat mutilasi di Pancoran Mas, Depok. Korban ditemukan tanpa kaki, terikat, dan dalam kondisi mengenaskan.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604759/puan-berduka-km-mutiara-terbakar-keamanan-transportasi-laut-ri-masih-minim</t>
+          <t>https://news.detik.com/berita/d-8604858/kondisi-mayat-mutilasi-di-depok-tangan-terikat-dan-leher-luka-sayat</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/puan-maharani-1777615358543_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4510,28 +4510,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Duduk Perkara Pria di Tangerang Dipaksa Masturbasi hingga Disiksa</t>
+          <t>Trump Cabut Visa Duta Besar Brasil untuk AS, Ada Apa?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:04:14 +0700</t>
+          <t>Wed, 05 Aug 2026 09:34:55 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Seorang pria diduga dianiaya bos dan rekan kerjanya di Kabupaten Tangerang, Banten. Korban juga diduga dipaksa masturbasi sambil menonton film porno.</t>
+          <t>Pemerintahan Trump mencabut visa DUbes Brasil untuk AS, Maria Luiz Ribeiro Viotti. Apa alasannya?</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604752/duduk-perkara-pria-di-tangerang-dipaksa-masturbasi-hingga-disiksa</t>
+          <t>https://news.detik.com/internasional/d-8604850/trump-cabut-visa-duta-besar-brasil-untuk-as-ada-apa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dubes-brasil-untuk-as-maria-luiza-ribeiro-viotti-1785897254293_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4548,28 +4548,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ketua DPRD Surabaya Dorong Sinergi Warga-Aparat Jaga Kota Kondusif</t>
+          <t>Misteri Mayat Mutilasi di Depok Dibuang 12 Hari Lalu</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:02:41 +0700</t>
+          <t>Wed, 05 Aug 2026 09:26:42 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ketua DPRD Surabaya, Syaifudin Zuhri, menekankan pentingnya peran masyarakat dalam menjaga keamanan kota.</t>
+          <t>Jasad pria mutilasi ditemukan di Pancoran Mas, Depok, setelah 12 hari. Identitas korban belum diketahui, polisi masih menyelidiki kasus ini.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604677/ketua-dprd-surabaya-dorong-sinergi-warga-aparat-jaga-kota-kondusif</t>
+          <t>https://news.detik.com/berita/d-8604839/misteri-mayat-mutilasi-di-depok-dibuang-12-hari-lalu</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dprd-surabaya-1785886861092_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4586,28 +4586,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adrien Schneider, Buron High Profile Asal Prancis Ditangkap di Jakarta</t>
+          <t>RI Kecam Keras Israel Serang Gaza Lagi: Sengaja Hambat Peace Plan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:02:31 +0700</t>
+          <t>Wed, 05 Aug 2026 09:23:19 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Buron high profile Prancis, Adrien Schneider, ditangkap di Jakarta. Dia terlibat pembunuhan dan kejahatan berat, kini dalam proses deportasi ke Prancis.</t>
+          <t>Indonesia mengecam serangan Israel ke Gaza yang menghambat kesepakatan perdamaian. Kemlu mendesak Israel menghentikan serangan dan memenuhi komitmen perjanjian.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604749/adrien-schneider-buron-high-profile-asal-prancis-ditangkap-di-jakarta</t>
+          <t>https://news.detik.com/berita/d-8604835/ri-kecam-keras-israel-serang-gaza-lagi-sengaja-hambat-peace-plan</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adrien-schneider-buron-high-profile-asal-prancis-dideportasi-ke-negaranya-setelah-tertangkap-usai-bersembunyi-di-sumbawa-dan-b-1785891665606_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/09/11/gedung-pancasila-di-kemlu_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4624,28 +4624,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aksi Perekam Usher GIIAS Bikin Resah Kini Diusut Polisi</t>
+          <t>Siap-siap War! Tiket Upacara HUT ke-81 RI di Istana Dibuka Hari Ini Pukul 10.00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:55:46 +0700</t>
+          <t>Wed, 05 Aug 2026 09:21:08 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Polemik perekaman usher di GIIAS 2026 berlanjut. Polisi menyelidiki kasus ini setelah korban merasa tidak nyaman.</t>
+          <t>Pemerintah sudah membuka pendaftaran upacara HUT ke-81 RI di Istana Merdeka Jakarta. Siap-siap war!</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604735/aksi-perekam-usher-giias-bikin-resah-kini-diusut-polisi</t>
+          <t>https://news.detik.com/berita/d-8604828/siap-siap-war-tiket-upacara-hut-ke-81-ri-di-istana-dibuka-hari-ini-pukul-10-00</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/video-yang-menjadikan-usher-spg-di-giias-2026-sebagai-objek-konten-berjudul-cara-mendekati-cewek-ramai-dikritik-ppembuat-konte-1785733892086_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/01/31/85d6b0ca-c154-414b-a198-62b91ce4debc_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4662,28 +4662,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2 Pengamen Pemukul Pengunjung GTC Cirebon Ditangkap</t>
+          <t>Jakarta Selatan Diprediksi Hujan Ringan Sore Ini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:54:18 +0700</t>
+          <t>Wed, 05 Aug 2026 08:56:17 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dua pengamen ditangkap polisi di Cirebon setelah terlibat keributan dengan pengunjung. Mereka terancam hukuman lima tahun penjara akibat kekerasan.</t>
+          <t>BMKG mengungkap sebagian wilayah di Jakarta Selatan berpotensi hujan ringan hari ini.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604733/2-pengamen-pemukul-pengunjung-gtc-cirebon-ditangkap</t>
+          <t>https://news.detik.com/berita/d-8604809/jakarta-selatan-diprediksi-hujan-ringan-sore-ini</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-cirebon-kota-akbp-bimantoro-kurniawan-1785889392099_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/30/ilustrasi-hujan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4700,28 +4700,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ada Pengecoran Jalan, Jalan Raya Bogor Arah Pasar Rebo Jaktim Macet</t>
+          <t>MKD DPR Gelar Rapim Pekan Depan Bahas Laporan 'Kayak Sirkus' ke Deddy Sitorus</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:36:58 +0700</t>
+          <t>Wed, 05 Aug 2026 08:53:44 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kemacetan terjadi di Jalan Raya Bogor, Jakarta Timur (Jaktim) pagi ini. Kemacetan itu imbas adanya pengecoran jalan.</t>
+          <t>Mahkamah Kehormatan Dewan DPR RI akan rapat menindaklanjuti laporan wartawan terhadap Deddy Sitorus.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604724/ada-pengecoran-jalan-jalan-raya-bogor-arah-pasar-rebo-jaktim-macet</t>
+          <t>https://news.detik.com/berita/d-8604811/mkd-dpr-gelar-rapim-pekan-depan-bahas-laporan-kayak-sirkus-ke-deddy-sitorus</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemacetan-terjadi-di-jalan-raya-bogor-jakarta-timur-jaktim-pagi-ini-kemacetan-itu-imbas-adanya-pengecoran-jalan-dok-tmc-polda--1785890168558_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mkd-1785865852673_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4738,28 +4738,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Patgulipat Bisnis Don Ritto Tempat Cuci Uang Febrie Diungkap</t>
+          <t>Mendagri Wanti-wanti Kepala Daerah Jaga Integritas demi Cegah Korupsi</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:32:33 +0700</t>
+          <t>Wed, 05 Aug 2026 08:51:47 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kejagung mengungkap perusahaan yang diduga terkait kasus TPPU eks Jampidsus Febrie Adriansyah. Perusahaan milik Don Ritto diduga menjadi tempat pencucian.</t>
+          <t>Mendagri Tito Karnavian menekankan pentingnya integritas kepala daerah dalam mencegah korupsi. Rakor di Surabaya bertujuan memperkuat tata kelola pemerintahan.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604720/patgulipat-bisnis-don-ritto-tempat-cuci-uang-febrie-diungkap</t>
+          <t>https://news.detik.com/berita/d-8604793/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4776,28 +4776,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Momen 35 Orang Bantu Pemakaman Wanita Berbobot 300 Kg di Sragen</t>
+          <t>LRT Dukung Pramono Hubungkan 2 JPO Viral Dekat tapi Tak Tersambung di Rasuna</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:16:37 +0700</t>
+          <t>Wed, 05 Aug 2026 08:45:13 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Perempuan berbobot 300 kg berinisial I (39), warga Sragen Tengah, Kabupaten Sragen, meninggal dunia usai mengalami sesak napas.</t>
+          <t>Gubernur DKI Pramono berjanji menyambungkan dua JPO yang viral di Jalan HR Rasuna Said. LRT Jabodebek siap berkoordinasi.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604715/momen-35-orang-bantu-pemakaman-wanita-berbobot-300-kg-di-sragen</t>
+          <t>https://news.detik.com/berita/d-8604779/lrt-dukung-pramono-hubungkan-2-jpo-viral-dekat-tapi-tak-tersambung-di-rasuna</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313180_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4814,28 +4814,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Perkara Kopilot Kurir 26 Kg Ekstasi di Soetta Juga Diusut Malaysia</t>
+          <t>Komisi V DPR Bakal Panggil Kemenhub Buntut Kebakaran KMP Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:55:26 +0700</t>
+          <t>Wed, 05 Aug 2026 08:35:39 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kopilot Malaysia Airlines ditangkap di Indonesia karena menyelundupkan 70 ribu butir ekstasi. Polisi Malaysia kini menyelidiki keterlibatan petugas bandara.</t>
+          <t>Komisi V DPR RI akan memanggil Kemenhub terkait kebakaran KMP Mutiara Sentosa 2. Rapat dengan Kemenhub digelar seusai reses DPR RI.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604681/perkara-kopilot-kurir-26-kg-ekstasi-di-soetta-juga-diusut-malaysia</t>
+          <t>https://news.detik.com/berita/d-8604773/komisi-v-dpr-bakal-panggil-kemenhub-buntut-kebakaran-kmp-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4852,28 +4852,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nasib 2 JPO 'Dekat tapi Tak Jadian' di Rasuna Said</t>
+          <t>Jelang Kunjungan Trump, Pria Bersenjata Ditangkap di Lapangan Golf Los Angeles</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:36:52 +0700</t>
+          <t>Wed, 05 Aug 2026 08:34:23 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dua JPO di Jalan HR Rasuna Said, Jakarta, berdekatan tapi tak terhubung. Gubernur Pramono menindaklanjuti keluhan warga itu.</t>
+          <t>Seorang pria bersenjata ditangkap di lapangan golf Trump di LA, dua hari sebelum kunjungannya. Penyelidik menemukan senjata dan catatan mencurigakan.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604674/nasib-2-jpo-dekat-tapi-tak-jadian-di-rasuna-said</t>
+          <t>https://news.detik.com/internasional/d-8604771/jelang-kunjungan-trump-pria-bersenjata-ditangkap-di-lapangan-golf-los-angeles</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313058_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/trump-saat-berpidato-di-gedung-putih-pada-kamis-167-malam-1784277022942_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4890,28 +4890,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Drama Atlet Golf Jesslyn Wijaya Disetop Sebab Bukan Penculikan</t>
+          <t>U-turn Depan Stasiun Depok Ditutup, Lalin Arah Jakarta Lancar Pagi Ini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:59:57 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:43 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kabar atlet golf Jesslyn Wijaya (34) diculik telah terpatahkan. Penyidikan kasus itu kini akan disetop kepolisian.</t>
+          <t>Satlantas Polres Metro Depok dan Dishub menutup U-turn di Jalan Kartini untuk mengurangi kemacetan. Penutupan berlaku pada jam sibuk, efektif mulai 3 Agustus.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604657/drama-atlet-golf-jesslyn-wijaya-disetop-sebab-bukan-penculikan</t>
+          <t>https://news.detik.com/berita/d-8604766/u-turn-depan-stasiun-depok-ditutup-lalin-arah-jakarta-lancar-pagi-ini</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/atlet-golf-putri-jesslyn-wijaya-lay-dok-ig-jesswijgolf-1784630812506_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/u-turn-putaran-balik-di-jalan-kartini-depok-ditutup-1785893424229_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ultimatum Trump Sebelum 'Pancung' Iran</t>
+          <t>Sekda Konawe Selatan Tabrak Adik Saat Digerebek Bareng Selingkuhan di Mobil</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:43:04 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:40 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Trump marah pada Iran yang bantah negosiasi. Ia beri ultimatum: kesepakatan atau penyerahan total. Iran menegaskan tidak ada dialog dengan AS.</t>
+          <t>Sekda Konawe Selatan Ichsan Porosi (56) menabrak adik kandungnya, Andriani Porosi alias AP (50), saat digerebek berduaan diduga bareng selingkuhan di mobil.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604651/ultimatum-trump-sebelum-pancung-iran</t>
+          <t>https://news.detik.com/berita/d-8604765/sekda-konawe-selatan-tabrak-adik-saat-digerebek-bareng-selingkuhan-di-mobil</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/tarif-10-berakhir-trump-berlakukan-bea-masuk-baru-terhadap-60-mitra-dagang-1784889297458_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4966,28 +4966,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Korban Tewas Gelombang Migran Ilegal di Ceuta Spanyol Jadi 77 orang</t>
+          <t>Penjelasan BMKG soal Hujan di Jakarta Usai Berminggu-minggu Kering</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:31:03 +0700</t>
+          <t>Wed, 05 Aug 2026 08:24:21 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Serbuan migran ilegal dari Maroko ke Ceuta, Spanyol, menyebabkan 77 tewas. Banyak yang tenggelam saat mencoba melewati penghalang Laut Mediterania.</t>
+          <t>Hujan turun di Jakarta setelah kering berminggu-minggu. Ini penjelasan BMKG.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604650/korban-tewas-gelombang-migran-ilegal-di-ceuta-spanyol-jadi-77-orang</t>
+          <t>https://news.detik.com/berita/d-8604764/penjelasan-bmkg-soal-hujan-di-jakarta-usai-berminggu-minggu-kering</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/spanyol-kerahkan-militer-ke-ceuta-atasi-krisis-migran-1785493658510_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hujan-deras-guyur-jakarta-usai-berminggu-minggu-kering-1785846576327_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5004,28 +5004,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Operasi SAR Pencarian Korban KM Mutiara Sentosa 2 Ditutup</t>
+          <t>Puan Berduka KM Mutiara Terbakar: Keamanan Transportasi Laut RI Masih Minim</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:06:19 +0700</t>
+          <t>Wed, 05 Aug 2026 08:15:49 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Basarnas resmi menghentikan operasi SAR KM Mutiara Sentosa II setelah 238 orang berhasil didata. Operasi kini beralih ke kesiapsiagaan rutin.</t>
+          <t>KM Mutiara Sentosa 2 terbakar di Madura, menewaskan lima orang. Puan Maharani soroti minimnya keamanan transportasi laut.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604649/operasi-sar-pencarian-korban-km-mutiara-sentosa-2-ditutup</t>
+          <t>https://news.detik.com/berita/d-8604759/puan-berduka-km-mutiara-terbakar-keamanan-transportasi-laut-ri-masih-minim</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785810542046_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/puan-maharani-1777615358543_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5042,28 +5042,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gempa M 5,6 Guncang Halmahera Barat Malut</t>
+          <t>Duduk Perkara Pria di Tangerang Dipaksa Masturbasi hingga Disiksa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 03:45:22 +0700</t>
+          <t>Wed, 05 Aug 2026 08:04:14 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gempa magnitudo 5,6 mengguncang Halmahera Barat, Maluku Utara, pada kedalaman 25 km. BMKG memastikan tidak ada potensi tsunami.</t>
+          <t>Seorang pria diduga dianiaya bos dan rekan kerjanya di Kabupaten Tangerang, Banten. Korban juga diduga dipaksa masturbasi sambil menonton film porno.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604647/gempa-m-5-6-guncang-halmahera-barat-malut</t>
+          <t>https://news.detik.com/berita/d-8604752/duduk-perkara-pria-di-tangerang-dipaksa-masturbasi-hingga-disiksa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5080,28 +5080,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Staf Bandara KLIA Diduga Bantu Kopilot yang Selundupkan Narkoba ke RI</t>
+          <t>Ketua DPRD Surabaya Dorong Sinergi Warga-Aparat Jaga Kota Kondusif</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 02:26:38 +0700</t>
+          <t>Wed, 05 Aug 2026 08:02:41 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kepolisian Malaysia mengidentifikasi staf Bandara KLIA yang diduga bantu kopilot selundupkan narkoba ke Indonesia. Penyelidikan terus dilakukan.</t>
+          <t>Ketua DPRD Surabaya, Syaifudin Zuhri, menekankan pentingnya peran masyarakat dalam menjaga keamanan kota.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604644/staf-bandara-klia-diduga-bantu-kopilot-yang-selundupkan-narkoba-ke-ri</t>
+          <t>https://news.detik.com/berita/d-8604677/ketua-dprd-surabaya-dorong-sinergi-warga-aparat-jaga-kota-kondusif</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dprd-surabaya-1785886861092_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5118,28 +5118,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rumah Warga Ambruk 6 Bulan Belum Diperbaiki, Pemkot Serang Beri Bantuan</t>
+          <t>Adrien Schneider, Buron High Profile Asal Prancis Ditangkap di Jakarta</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:33:26 +0700</t>
+          <t>Wed, 05 Aug 2026 08:02:31 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rumah Nani di Serang ambruk akibat angin kencang. Pemkot Serang bantu Rp 30 juta untuk renovasi. Wali Kota kunjungi lokasi untuk pengecekan.</t>
+          <t>Buron high profile Prancis, Adrien Schneider, ditangkap di Jakarta. Dia terlibat pembunuhan dan kejahatan berat, kini dalam proses deportasi ke Prancis.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604642/rumah-warga-ambruk-6-bulan-belum-diperbaiki-pemkot-serang-beri-bantuan</t>
+          <t>https://news.detik.com/berita/d-8604749/adrien-schneider-buron-high-profile-asal-prancis-ditangkap-di-jakarta</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rumah-warga-serang-1785868326015_169.webp?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adrien-schneider-buron-high-profile-asal-prancis-dideportasi-ke-negaranya-setelah-tertangkap-usai-bersembunyi-di-sumbawa-dan-b-1785891665606_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5156,28 +5156,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pimpinan DPRD Ajak Warga Jaga Jakarta: Jadikan Rumah yang Aman bagi Semua</t>
+          <t>Aksi Perekam Usher GIIAS Bikin Resah Kini Diusut Polisi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:51:11 +0700</t>
+          <t>Wed, 05 Aug 2026 07:55:46 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Baco mendorong warga Jakarta untuk berbondong-bondong menjaga kotanya. Dia berpesan agar Jakarta menjadi rumah aman bagi semua warganya.</t>
+          <t>Polemik perekaman usher di GIIAS 2026 berlanjut. Polisi menyelidiki kasus ini setelah korban merasa tidak nyaman.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604639/pimpinan-dprd-ajak-warga-jaga-jakarta-jadikan-rumah-yang-aman-bagi-semua</t>
+          <t>https://news.detik.com/berita/d-8604735/aksi-perekam-usher-giias-bikin-resah-kini-diusut-polisi</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/15/basri-baco-1778786025155_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/video-yang-menjadikan-usher-spg-di-giias-2026-sebagai-objek-konten-berjudul-cara-mendekati-cewek-ramai-dikritik-ppembuat-konte-1785733892086_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5194,28 +5194,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Qatar Bilang Negosiasi AS-Iran Progresif, Draf Perjanjian Damai Lagi Dibahas</t>
+          <t>2 Pengamen Pemukul Pengunjung GTC Cirebon Ditangkap</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:22:56 +0700</t>
+          <t>Wed, 05 Aug 2026 07:54:18 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Qatar menyatakan upaya penyelesaian konflik AS-Iran sedang progresif. Draf perjanjian damai sedang diedarkan, dengan fokus pada resolusi jangka pendek.</t>
+          <t>Dua pengamen ditangkap polisi di Cirebon setelah terlibat keributan dengan pengunjung. Mereka terancam hukuman lima tahun penjara akibat kekerasan.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604632/qatar-bilang-negosiasi-as-iran-progresif-draf-perjanjian-damai-lagi-dibahas</t>
+          <t>https://news.detik.com/berita/d-8604733/2-pengamen-pemukul-pengunjung-gtc-cirebon-ditangkap</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/uae-iran-us-israel-war-1783871173097_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-cirebon-kota-akbp-bimantoro-kurniawan-1785889392099_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5232,28 +5232,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ngambek Keinginan Tak Dituruti Ortu, Pemuda Bandung Bakar Motor dan 3 Rumah</t>
+          <t>Ada Pengecoran Jalan, Jalan Raya Bogor Arah Pasar Rebo Jaktim Macet</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:20:10 +0700</t>
+          <t>Wed, 05 Aug 2026 07:36:58 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Polisi menangkap pemuda yang membakar motor dan tiga rumah di Babakan Ciparay. Motif pelaku lantaran keinginan tak dipenuhi ortu.</t>
+          <t>Kemacetan terjadi di Jalan Raya Bogor, Jakarta Timur (Jaktim) pagi ini. Kemacetan itu imbas adanya pengecoran jalan.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604631/ngambek-keinginan-tak-dituruti-ortu-pemuda-bandung-bakar-motor-dan-3-rumah</t>
+          <t>https://news.detik.com/berita/d-8604724/ada-pengecoran-jalan-jalan-raya-bogor-arah-pasar-rebo-jaktim-macet</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tampang-pemuda-yang-bakar-motor-hingga-api-menjalar-ke-3-rumah-1785851029166_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemacetan-terjadi-di-jalan-raya-bogor-jakarta-timur-jaktim-pagi-ini-kemacetan-itu-imbas-adanya-pengecoran-jalan-dok-tmc-polda--1785890168558_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5265,33 +5265,33 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Modus Misdeclaration Terbongkar, Harley-Davidson Bekas Ilegal Disita Bea Cukai</t>
+          <t>Patgulipat Bisnis Don Ritto Tempat Cuci Uang Febrie Diungkap</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:57:30 +0700</t>
+          <t>Wed, 05 Aug 2026 07:32:33 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok menggagalkan penyelundupan lima Harley-Davidson bekas dan 20 rangka bekas asal China dengan modus misdeclaration.</t>
+          <t>Kejagung mengungkap perusahaan yang diduga terkait kasus TPPU eks Jampidsus Febrie Adriansyah. Perusahaan milik Don Ritto diduga menjadi tempat pencucian.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8605004/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai</t>
+          <t>https://news.detik.com/berita/d-8604720/patgulipat-bisnis-don-ritto-tempat-cuci-uang-febrie-diungkap</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai-1785903653401.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5303,33 +5303,33 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jumlah Pengangguran RI Turun Jadi 7,22 Juta Orang</t>
+          <t>Momen 35 Orang Bantu Pemakaman Wanita Berbobot 300 Kg di Sragen</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:55:15 +0700</t>
+          <t>Wed, 05 Aug 2026 07:16:37 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat, jumlah pengangguran di Indonesia per Mei 2026 sebanyak 7,22 juta orang.</t>
+          <t>Perempuan berbobot 300 kg berinisial I (39), warga Sragen Tengah, Kabupaten Sragen, meninggal dunia usai mengalami sesak napas.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605071/jumlah-pengangguran-ri-turun-jadi-7-22-juta-orang</t>
+          <t>https://news.detik.com/berita/d-8604715/momen-35-orang-bantu-pemakaman-wanita-berbobot-300-kg-di-sragen</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/09/ilustrasi-pengangguran-atau-pencari-kerja-1746784722868_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5341,33 +5341,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ekonomi RI Tumbuh 5,29%, Ini Motor Penggeraknya</t>
+          <t>Perkara Kopilot Kurir 26 Kg Ekstasi di Soetta Juga Diusut Malaysia</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:33:09 +0700</t>
+          <t>Wed, 05 Aug 2026 06:55:26 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mengumumkan pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
+          <t>Kopilot Malaysia Airlines ditangkap di Indonesia karena menyelundupkan 70 ribu butir ekstasi. Polisi Malaysia kini menyelidiki keterlibatan petugas bandara.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605018/ekonomi-ri-tumbuh-5-29-ini-motor-penggeraknya</t>
+          <t>https://news.detik.com/berita/d-8604681/perkara-kopilot-kurir-26-kg-ekstasi-di-soetta-juga-diusut-malaysia</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/05/27/bangkit-dari-pandemi-ekonomi-ri-kuartal-ii-2021-diramal-tembus-7-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5379,33 +5379,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pembiayaan Komersial Bank Mega Syariah Tumbuh Jadi Rp 5,9 T</t>
+          <t>Nasib 2 JPO 'Dekat tapi Tak Jadian' di Rasuna Said</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:36 +0700</t>
+          <t>Wed, 05 Aug 2026 06:36:52 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PT Bank Mega Syariah mencatat pertumbuhan pembiayaan pada segmen komersial bank sepanjang semester I-2026.</t>
+          <t>Dua JPO di Jalan HR Rasuna Said, Jakarta, berdekatan tapi tak terhubung. Gubernur Pramono menindaklanjuti keluhan warga itu.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8605001/pembiayaan-komersial-bank-mega-syariah-tumbuh-jadi-rp-5-9-t</t>
+          <t>https://news.detik.com/berita/d-8604674/nasib-2-jpo-dekat-tapi-tak-jadian-di-rasuna-said</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/13/ini-pemenang-mobil-listrik-program-berkah-berlimpah-mega-syariah-4_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313058_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5417,33 +5417,33 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BPS Umumkan Ekonomi RI Tumbuh 5,29% di Kuartal II</t>
+          <t>Drama Atlet Golf Jesslyn Wijaya Disetop Sebab Bukan Penculikan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:17:07 +0700</t>
+          <t>Wed, 05 Aug 2026 05:59:57 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mengumumkan, pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
+          <t>Kabar atlet golf Jesslyn Wijaya (34) diculik telah terpatahkan. Penyidikan kasus itu kini akan disetop kepolisian.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604987/bps-umumkan-ekonomi-ri-tumbuh-5-29-di-kuartal-ii</t>
+          <t>https://news.detik.com/berita/d-8604657/drama-atlet-golf-jesslyn-wijaya-disetop-sebab-bukan-penculikan</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/deputi-bidang-neraca-dan-analisis-statistik-bps-edy-mahmud-1785902590386_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/atlet-golf-putri-jesslyn-wijaya-lay-dok-ig-jesswijgolf-1784630812506_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5455,33 +5455,33 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BNI Cetak Laba Bersih Rp 10,8 Triliun</t>
+          <t>Ultimatum Trump Sebelum 'Pancung' Iran</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:58:49 +0700</t>
+          <t>Wed, 05 Aug 2026 05:43:04 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PT Bank Negara Indonesia (Persero) Tbk atau BNI membukukan laba bersih sebesar Rp 10,8 triliun hingga semester I 2026.</t>
+          <t>Trump marah pada Iran yang bantah negosiasi. Ia beri ultimatum: kesepakatan atau penyerahan total. Iran menegaskan tidak ada dialog dengan AS.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604965/bni-cetak-laba-bersih-rp-10-8-triliun</t>
+          <t>https://news.detik.com/internasional/d-8604651/ultimatum-trump-sebelum-pancung-iran</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/bni-1773200307513_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/tarif-10-berakhir-trump-berlakukan-bea-masuk-baru-terhadap-60-mitra-dagang-1784889297458_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5493,33 +5493,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dari China</t>
+          <t>Korban Tewas Gelombang Migran Ilegal di Ceuta Spanyol Jadi 77 orang</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:38:16 +0700</t>
+          <t>Wed, 05 Aug 2026 05:31:03 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Barang impor ilegal tersebut berasal dari China.</t>
+          <t>Serbuan migran ilegal dari Maroko ke Ceuta, Spanyol, menyebabkan 77 tewas. Banyak yang tenggelam saat mencoba melewati penghalang Laut Mediterania.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604938/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china</t>
+          <t>https://news.detik.com/internasional/d-8604650/korban-tewas-gelombang-migran-ilegal-di-ceuta-spanyol-jadi-77-orang</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china-1785901058002_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/spanyol-kerahkan-militer-ke-ceuta-atasi-krisis-migran-1785493658510_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5531,33 +5531,33 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Harga Emas Hari Ini Turun Lagi Sentuh Rp 2,59 Juta</t>
+          <t>Operasi SAR Pencarian Korban KM Mutiara Sentosa 2 Ditutup</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:10:07 +0700</t>
+          <t>Wed, 05 Aug 2026 05:06:19 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hari ini, Rabu (5/8) harga emas Antam 24 karat turun Rp 4.000 per gram menjadi Rp 2.599.000 per gram.</t>
+          <t>Basarnas resmi menghentikan operasi SAR KM Mutiara Sentosa II setelah 238 orang berhasil didata. Operasi kini beralih ke kesiapsiagaan rutin.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604895/harga-emas-hari-ini-turun-lagi-sentuh-rp-2-59-juta</t>
+          <t>https://news.detik.com/berita/d-8604649/operasi-sar-pencarian-korban-km-mutiara-sentosa-2-ditutup</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/22/harga-emas-terjun-bebas-pasar-cikini-langsung-diserbu-pembeli-1761123863171_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785810542046_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5569,33 +5569,33 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Narkotika di Bandara Juanda</t>
+          <t>Gempa M 5,6 Guncang Halmahera Barat Malut</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:33:15 +0700</t>
+          <t>Wed, 05 Aug 2026 03:45:22 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bea Cukai kembali menggagalkan penyelundupan narkotika.</t>
+          <t>Gempa magnitudo 5,6 mengguncang Halmahera Barat, Maluku Utara, pada kedalaman 25 km. BMKG memastikan tidak ada potensi tsunami.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604848/bea-cukai-gagalkan-penyelundupan-narkotika-di-bandara-juanda</t>
+          <t>https://news.detik.com/berita/d-8604647/gempa-m-5-6-guncang-halmahera-barat-malut</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-narkotika-1785897113589_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5607,33 +5607,33 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dolar AS Melemah ke Level Rp 17.971</t>
+          <t>Staf Bandara KLIA Diduga Bantu Kopilot yang Selundupkan Narkoba ke RI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:21:24 +0700</t>
+          <t>Wed, 05 Aug 2026 02:26:38 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Nilai tukar dolar Amerika Serikat (AS) terpantau melemah terhadap rupiah.</t>
+          <t>Kepolisian Malaysia mengidentifikasi staf Bandara KLIA yang diduga bantu kopilot selundupkan narkoba ke Indonesia. Penyelidikan terus dilakukan.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604830/dolar-as-melemah-ke-level-rp-17-971</t>
+          <t>https://news.detik.com/berita/d-8604644/staf-bandara-klia-diduga-bantu-kopilot-yang-selundupkan-narkoba-ke-ri</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338213_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5645,33 +5645,33 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>IHSG Naik Tipis Pagi Ini ke Level 6.322</t>
+          <t>Rumah Warga Ambruk 6 Bulan Belum Diperbaiki, Pemkot Serang Beri Bantuan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:16:12 +0700</t>
+          <t>Wed, 05 Aug 2026 01:33:26 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
+          <t>Rumah Nani di Serang ambruk akibat angin kencang. Pemkot Serang bantu Rp 30 juta untuk renovasi. Wali Kota kunjungi lokasi untuk pengecekan.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604824/ihsg-naik-tipis-pagi-ini-ke-level-6-322</t>
+          <t>https://news.detik.com/berita/d-8604642/rumah-warga-ambruk-6-bulan-belum-diperbaiki-pemkot-serang-beri-bantuan</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/22/jelang-putusan-mk-ihsg-menguat-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rumah-warga-serang-1785868326015_169.webp?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5683,33 +5683,33 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sri Mulyani Ditunjuk Bank Dunia Jadi Ketua Penggalangan Dana buat Negara Miskin</t>
+          <t>Pimpinan DPRD Ajak Warga Jaga Jakarta: Jadikan Rumah yang Aman bagi Semua</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:42:46 +0700</t>
+          <t>Wed, 05 Aug 2026 00:51:11 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Penunjukkan Sri Mulyani bukan tanpa alasan. Eks Bendahara Negara tersebut mempunyai pengalaman dalam bidang keuangan pembangunan internasional</t>
+          <t>Baco mendorong warga Jakarta untuk berbondong-bondong menjaga kotanya. Dia berpesan agar Jakarta menjadi rumah aman bagi semua warganya.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604777/sri-mulyani-ditunjuk-bank-dunia-jadi-ketua-penggalangan-dana-buat-negara-miskin</t>
+          <t>https://news.detik.com/berita/d-8604639/pimpinan-dprd-ajak-warga-jaga-jakarta-jadikan-rumah-yang-aman-bagi-semua</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/10/mantan-menteri-keuangan-sri-mulyani-indrawati-1765362593072_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/15/basri-baco-1778786025155_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5721,33 +5721,33 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BUMI Catat Laba Bersih Semester I-2026 Naik 188%, AMAR Tetapkan Dividen Interim</t>
+          <t>Qatar Bilang Negosiasi AS-Iran Progresif, Draf Perjanjian Damai Lagi Dibahas</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:33:25 +0700</t>
+          <t>Wed, 05 Aug 2026 00:22:56 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>IHSG ditutup naik 1,37% di tengah aksi beli asing. BUMI membukukan kenaikan laba bersih semester I-2026, sementara AMAR menetapkan dividen interim.</t>
+          <t>Qatar menyatakan upaya penyelesaian konflik AS-Iran sedang progresif. Draf perjanjian damai sedang diedarkan, dengan fokus pada resolusi jangka pendek.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604770/bumi-catat-laba-bersih-semester-i-2026-naik-188-amar-tetapkan-dividen-interim</t>
+          <t>https://news.detik.com/internasional/d-8604632/qatar-bilang-negosiasi-as-iran-progresif-draf-perjanjian-damai-lagi-dibahas</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bursa-dan-valas-1785893124-1785893124406.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/uae-iran-us-israel-war-1783871173097_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5759,33 +5759,33 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Harga Minyak Turun Sedalam Ini Usai Sinyal Damai AS &amp;amp; Iran</t>
+          <t>Ngambek Keinginan Tak Dituruti Ortu, Pemuda Bandung Bakar Motor dan 3 Rumah</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:10:37 +0700</t>
+          <t>Wed, 05 Aug 2026 00:20:10 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Harga minyak mentah dunia anjlok lebih dari 5% dan bertengger di level terendahnya dalam tiga minggu terakhir pada perdagangan Selasa.</t>
+          <t>Polisi menangkap pemuda yang membakar motor dan tiga rumah di Babakan Ciparay. Motif pelaku lantaran keinginan tak dipenuhi ortu.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604727/harga-minyak-turun-sedalam-ini-usai-sinyal-damai-as-iran</t>
+          <t>https://news.detik.com/berita/d-8604631/ngambek-keinginan-tak-dituruti-ortu-pemuda-bandung-bakar-motor-dan-3-rumah</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/16/ilustrasi-pengeboran-migas-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tampang-pemuda-yang-bakar-motor-hingga-api-menjalar-ke-3-rumah-1785851029166_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5802,28 +5802,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rayuan Purbaya ke Toyota, Janji Kasih Insentif Banyak</t>
+          <t>Modus Misdeclaration Terbongkar, Harley-Davidson Bekas Ilegal Disita Bea Cukai</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:58:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:57:30 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa meminta raksasa otomotif Jepang, Toyota, memindahkan pusat manufaktur utamanya ke Indonesia.</t>
+          <t>Bea Cukai Tanjung Priok menggagalkan penyelundupan lima Harley-Davidson bekas dan 20 rangka bekas asal China dengan modus misdeclaration.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/ekonomi-bisnis/d-8604540/rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8605004/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detik-pagi-rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak-1785856135943_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai-1785903653401.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5840,28 +5840,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Purbaya Janji Ekonomi Tahun Ini Tumbuh Dekati 6%</t>
+          <t>Jumlah Pengangguran RI Turun Jadi 7,22 Juta Orang</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:24:33 +0700</t>
+          <t>Wed, 05 Aug 2026 11:55:15 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa optimistis ekonomi tahun ini bisa tumbuh mendekati angka 6%.</t>
+          <t>Badan Pusat Statistik (BPS) mencatat, jumlah pengangguran di Indonesia per Mei 2026 sebanyak 7,22 juta orang.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604612/purbaya-janji-ekonomi-tahun-ini-tumbuh-dekati-6</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605071/jumlah-pengangguran-ri-turun-jadi-7-22-juta-orang</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962228_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/09/ilustrasi-pengangguran-atau-pencari-kerja-1746784722868_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5878,28 +5878,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bank-bank di Rusia Mulai Krisis Uang Tunai</t>
+          <t>Ekonomi RI Tumbuh 5,29%, Ini Motor Penggeraknya</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:00:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:33:09 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Perbankan Rusia menghadapi tekanan likuiditas rubel, membatasi kemampuan menyerap obligasi pemerintah. Defisit anggaran membengkak.</t>
+          <t>Badan Pusat Statistik (BPS) mengumumkan pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604562/bank-bank-di-rusia-mulai-krisis-uang-tunai</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605018/ekonomi-ri-tumbuh-5-29-ini-motor-penggeraknya</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/29/g7-tolak-pembayaran-gas-rusia-dengan-mata-uang-rubel_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/05/27/bangkit-dari-pandemi-ekonomi-ri-kuartal-ii-2021-diramal-tembus-7-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5916,28 +5916,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Respons Bos BGN soal Anggaran MBG &amp;amp; Pendidikan Harus Dipisah</t>
+          <t>Pembiayaan Komersial Bank Mega Syariah Tumbuh Jadi Rp 5,9 T</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:30:38 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:36 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono merespons keputusan Mahkamah Konstitusi soal memisahkan anggaran MBG dengan pendidikan.</t>
+          <t>PT Bank Mega Syariah mencatat pertumbuhan pembiayaan pada segmen komersial bank sepanjang semester I-2026.</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604561/respons-bos-bgn-soal-anggaran-mbg-pendidikan-harus-dipisah</t>
+          <t>https://finance.detik.com/moneter/d-8605001/pembiayaan-komersial-bank-mega-syariah-tumbuh-jadi-rp-5-9-t</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/13/ini-pemenang-mobil-listrik-program-berkah-berlimpah-mega-syariah-4_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5954,28 +5954,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Era Controlled Landfill, Penghasilan Pemulung Bantargebang Merosot Drastis</t>
+          <t>BPS Umumkan Ekonomi RI Tumbuh 5,29% di Kuartal II</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:00:49 +0700</t>
+          <t>Wed, 05 Aug 2026 11:17:07 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Controlled landfill di TPST Bantargebang mengubah pemilahan sampah dan membuat penghasilan pemulung yang bergantung pada sampah menurun.</t>
+          <t>Badan Pusat Statistik (BPS) mengumumkan, pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8604299/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604987/bps-umumkan-ekonomi-ri-tumbuh-5-29-di-kuartal-ii</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis-1785843094443_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/deputi-bidang-neraca-dan-analisis-statistik-bps-edy-mahmud-1785902590386_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5992,28 +5992,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sentilan Keras Purbaya buat Moody's-Fitch</t>
+          <t>BNI Cetak Laba Bersih Rp 10,8 Triliun</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:55:23 +0700</t>
+          <t>Wed, 05 Aug 2026 10:58:49 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan sentilan keras kepada dua lembaga rating global.</t>
+          <t>PT Bank Negara Indonesia (Persero) Tbk atau BNI membukukan laba bersih sebesar Rp 10,8 triliun hingga semester I 2026.</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604558/sentilan-keras-purbaya-buat-moodys-fitch</t>
+          <t>https://finance.detik.com/moneter/d-8604965/bni-cetak-laba-bersih-rp-10-8-triliun</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786088_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/bni-1773200307513_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6025,33 +6025,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Jadwal Singapura Vs Indonesia di Piala AFF 2026</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dari China</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:10 +0700</t>
+          <t>Wed, 05 Aug 2026 10:38:16 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Timnas Indonesia bertandang ke markas Singapura dalam matchday terakhir fase grup Piala AFF 2026. Berikut jadwal pertandingan selengkapnya!</t>
+          <t>Barang impor ilegal tersebut berasal dari China.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605047/jadwal-singapura-vs-indonesia-di-piala-aff-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604938/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china-1785901058002_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6063,33 +6063,33 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
+          <t>Harga Emas Hari Ini Turun Lagi Sentuh Rp 2,59 Juta</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
+          <t>Wed, 05 Aug 2026 10:10:07 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
+          <t>Hari ini, Rabu (5/8) harga emas Antam 24 karat turun Rp 4.000 per gram menjadi Rp 2.599.000 per gram.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604895/harga-emas-hari-ini-turun-lagi-sentuh-rp-2-59-juta</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/22/harga-emas-terjun-bebas-pasar-cikini-langsung-diserbu-pembeli-1761123863171_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6101,33 +6101,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Jadwal MotoGP Inggris 2026 Akhir Pekan Ini</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Narkotika di Bandara Juanda</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:30:30 +0700</t>
+          <t>Wed, 05 Aug 2026 09:33:15 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>MotoGP 2026 akan kembali bergulir setelah jeda musim panas pada seri ke-12 di Sirkuit Silverstone, Inggris. Simak jadwalnya.</t>
+          <t>Bea Cukai kembali menggagalkan penyelundupan narkotika.</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604979/jadwal-motogp-inggris-2026-akhir-pekan-ini</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604848/bea-cukai-gagalkan-penyelundupan-narkotika-di-bandara-juanda</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-di-motogp-jerman-2026-1783857060263_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-narkotika-1785897113589_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6139,33 +6139,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jadwal Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
+          <t>Dolar AS Melemah ke Level Rp 17.971</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:20:20 +0700</t>
+          <t>Wed, 05 Aug 2026 09:21:24 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Jadwal final Piala Presiden 2026 mempertemukan Persib Bandung vs Persebaya Surabaya.</t>
+          <t>Nilai tukar dolar Amerika Serikat (AS) terpantau melemah terhadap rupiah.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604949/jadwal-final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604830/dolar-as-melemah-ke-level-rp-17-971</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338213_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6177,33 +6177,33 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Neymar di Persimpangan Jalan Kariernya</t>
+          <t>IHSG Naik Tipis Pagi Ini ke Level 6.322</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 09:16:12 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kontrak Neymar di Santos tinggal tersisa beberapa bulan lagi. Neymar tengah mempertimbangkan kelanjutan kariernya sebagai pesepakbola, lanjut main atau pensiun.</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604692/neymar-di-persimpangan-jalan-kariernya</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604824/ihsg-naik-tipis-pagi-ini-ke-level-6-322</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/neymar-menangis-akhiri-karier-bersama-timnas-brasil-1783314392616_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/22/jelang-putusan-mk-ihsg-menguat-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6215,33 +6215,33 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Presiden FIFA Gianni Infantino Gelar Rapat Darurat!</t>
+          <t>Sri Mulyani Ditunjuk Bank Dunia Jadi Ketua Penggalangan Dana buat Negara Miskin</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
+          <t>Wed, 05 Aug 2026 08:42:46 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gianni Infantino dilaporkan menggelar rapat darurat. Hal ini dilakukan di tengah desakan agar dirinya mundur dari FIFA.</t>
+          <t>Penunjukkan Sri Mulyani bukan tanpa alasan. Eks Bendahara Negara tersebut mempunyai pengalaman dalam bidang keuangan pembangunan internasional</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604767/presiden-fifa-gianni-infantino-gelar-rapat-darurat</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604777/sri-mulyani-ditunjuk-bank-dunia-jadi-ketua-penggalangan-dana-buat-negara-miskin</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/10/mantan-menteri-keuangan-sri-mulyani-indrawati-1765362593072_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6253,33 +6253,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Belum Selesai Belanja, Chelsea Siap Gaet Pengganti Cucurella</t>
+          <t>BUMI Catat Laba Bersih Semester I-2026 Naik 188%, AMAR Tetapkan Dividen Interim</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:20:00 +0700</t>
+          <t>Wed, 05 Aug 2026 08:33:25 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chelsea belum berhenti belanja musim panas ini. The Blues dilaporkan bakal mendatangkan pengganti Marc Cucurella.</t>
+          <t>IHSG ditutup naik 1,37% di tengah aksi beli asing. BUMI membukukan kenaikan laba bersih semester I-2026, sementara AMAR menetapkan dividen interim.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604768/belum-selesai-belanja-chelsea-siap-gaet-pengganti-cucurella</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604770/bumi-catat-laba-bersih-semester-i-2026-naik-188-amar-tetapkan-dividen-interim</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pep-chavarriarayo-vallecanolaligaliga-spanyolchelsea-1785891772000_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bursa-dan-valas-1785893124-1785893124406.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6291,33 +6291,33 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Amorim Jelang Milan Vs Inter: Juara Pramusim Nggak Penting</t>
+          <t>Harga Minyak Turun Sedalam Ini Usai Sinyal Damai AS &amp;amp; Iran</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:00:15 +0700</t>
+          <t>Wed, 05 Aug 2026 08:10:37 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AC Milan akan menghadapi Inter Milan di laga uji coba pramusim. Pelatih Milan Ruben Amorim menyebut hasil akhir bukan yang paling utama.</t>
+          <t>Harga minyak mentah dunia anjlok lebih dari 5% dan bertengger di level terendahnya dalam tiga minggu terakhir pada perdagangan Selasa.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604711/amorim-jelang-milan-vs-inter-juara-pramusim-nggak-penting</t>
+          <t>https://finance.detik.com/energi/d-8604727/harga-minyak-turun-sedalam-ini-usai-sinyal-damai-as-iran</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ruben-amorim-1785887341737_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/16/ilustrasi-pengeboran-migas-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6329,33 +6329,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Carragher Nilai Liverpool Belum Siap Bersaing Jadi Juara Premier League</t>
+          <t>Rayuan Purbaya ke Toyota, Janji Kasih Insentif Banyak</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:40:09 +0700</t>
+          <t>Wed, 05 Aug 2026 07:58:00 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Jamie Carragher menilai Liverpool belum cukup kuat untuk bersaing memperebutkan gelar juara Premier League. Menurutnya, skuad Liverpool belum lengkap.</t>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa meminta raksasa otomotif Jepang, Toyota, memindahkan pusat manufaktur utamanya ke Indonesia.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604726/carragher-nilai-liverpool-belum-siap-bersaing-jadi-juara-premier-league</t>
+          <t>https://finance.detik.com/ekonomi-bisnis/d-8604540/rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/andoni-iraola-1785219269838_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detik-pagi-rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak-1785856135943_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6367,33 +6367,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Kolo Muani Punya Urusan yang Belum Selesai di Juventus</t>
+          <t>Purbaya Janji Ekonomi Tahun Ini Tumbuh Dekati 6%</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:20:13 +0700</t>
+          <t>Wed, 05 Aug 2026 07:24:33 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Randal Kolo Muani amat gembira bisa kembali ke Juventus. Kolo Muani ingin menuntaskan apa yang sudah ia mulai di Turin.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa optimistis ekonomi tahun ini bisa tumbuh mendekati angka 6%.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604710/kolo-muani-punya-urusan-yang-belum-selesai-di-juventus</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604612/purbaya-janji-ekonomi-tahun-ini-tumbuh-dekati-6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/09/randal-kolo-muani-1752056032311_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962228_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6405,33 +6405,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kata-kata Erick Thohir soal Dukung Infantino Terus Pimpin FIFA</t>
+          <t>Bank-bank di Rusia Mulai Krisis Uang Tunai</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 07:00:57 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ketua Umum PSSI, Erick Thohir, bikin pernyatan soal dukungannya ke Gianni Infantino. Ia menyebut Indonesia sudah banyak dibantu Presiden FIFA tersebut.</t>
+          <t>Perbankan Rusia menghadapi tekanan likuiditas rubel, membatasi kemampuan menyerap obligasi pemerintah. Defisit anggaran membengkak.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604792/kata-kata-erick-thohir-soal-dukung-infantino-terus-pimpin-fifa</t>
+          <t>https://finance.detik.com/moneter/d-8604562/bank-bank-di-rusia-mulai-krisis-uang-tunai</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/18/erick-thohir-dan-presiden-fifa-gianni-infantino-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/29/g7-tolak-pembayaran-gas-rusia-dengan-mata-uang-rubel_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6443,33 +6443,33 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Inter Vs Milan di Pramusim, Chivu: Fokusnya ke Kebugaran</t>
+          <t>Respons Bos BGN soal Anggaran MBG &amp;amp; Pendidikan Harus Dipisah</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:21 +0700</t>
+          <t>Wed, 05 Aug 2026 06:30:38 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Inter Milan melanjutkan tur pramusimnya dengan melawan AC Milan di Australia. Pelatih Nerazzurri Cristian Chivu menegaskan fokus timnya ke membangun kebugaran.</t>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono merespons keputusan Mahkamah Konstitusi soal memisahkan anggaran MBG dengan pendidikan.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604317/inter-vs-milan-di-pramusim-chivu-fokusnya-ke-kebugaran</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604561/respons-bos-bgn-soal-anggaran-mbg-pendidikan-harus-dipisah</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6481,33 +6481,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dipercaya di Surabaya Marathon 2026, Le Minerale Hadir di 18 Water Station</t>
+          <t>Era Controlled Landfill, Penghasilan Pemulung Bantargebang Merosot Drastis</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:22:43 +0700</t>
+          <t>Wed, 05 Aug 2026 06:00:49 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Le Minerale Surabaya Marathon 2026 diikuti 7.000 pelari, mengusung konsep City Run. Acara ini mendukung sport tourism dan hidrasi optimal dengan Le Minerale.</t>
+          <t>Controlled landfill di TPST Bantargebang mengubah pemilahan sampah dan membuat penghasilan pemulung yang bergantung pada sampah menurun.</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sportstyle/d-8604762/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8604299/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station-1785892907123.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis-1785843094443_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6519,33 +6519,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mourinho Ingin Vinicius Selalu Bahagia di Madrid</t>
+          <t>Sentilan Keras Purbaya buat Moody's-Fitch</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 05:55:23 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Di tengah rumor Arsenal, Vinicius buka suara usai menjalani latihan pramusim bersama Real Madrid. Vinicius bilang Jose Mourinho ingin ia bahagia di Madrid.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan sentilan keras kepada dua lembaga rating global.</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604655/mourinho-ingin-vinicius-selalu-bahagia-di-madrid</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604558/sentilan-keras-purbaya-buat-moodys-fitch</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/15/soccer-spain-rma-rso-1771110362377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786088_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6562,28 +6562,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho Langsung 'Babak Belur' di Pramusim Aston Villa</t>
+          <t>Jadwal Singapura Vs Indonesia di Piala AFF 2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:30:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:10 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho baru pindah ke Aston Villa musim panas ini. Di laga pramusim, winger Argentina itu langsung babak belur.</t>
+          <t>Timnas Indonesia bertandang ke markas Singapura dalam matchday terakhir fase grup Piala AFF 2026. Berikut jadwal pertandingan selengkapnya!</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604654/alejandro-garnacho-langsung-babak-belur-di-pramusim-aston-villa</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605047/jadwal-singapura-vs-indonesia-di-piala-aff-2026</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/alejandro-garnachoaston-villabg-pathum-vs-aston-villapramusim-aston-villa-1785881271654_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6600,28 +6600,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Asosiasi Sepakbola Yordania Merasa Diperas FIFA!</t>
+          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Asosiasi Sepakbola Yordania (JFA) bikin pernyataan keras soal FIFA. Mereka mengaku diperas organisasi pimpinan Gianni Infantino tersebut.</t>
+          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604652/asosiasi-sepakbola-yordania-merasa-diperas-fifa</t>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/11/logo-fifa_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6638,28 +6638,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Semifinal Piala Presiden 2026 yang Aman dan Seru!</t>
+          <t>Jadwal MotoGP Inggris 2026 Akhir Pekan Ini</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:30:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:30:30 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Semifinal Piala Presiden 2026 sudah digelar. Rangkaian pertandingan berjalan aman dan seru, sesuai yang diharapkan.</t>
+          <t>MotoGP 2026 akan kembali bergulir setelah jeda musim panas pada seri ke-12 di Sirkuit Silverstone, Inggris. Simak jadwalnya.</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604648/semifinal-piala-presiden-2026-yang-aman-dan-seru</t>
+          <t>https://sport.detik.com/moto-gp/d-8604979/jadwal-motogp-inggris-2026-akhir-pekan-ini</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-semifinal-piala-presiden-2026-antara-persib-vs-persija-di-stadion-kapten-i-wayan-dipta-gianyar-bali-selasa-482026-1785862146465.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-di-motogp-jerman-2026-1783857060263_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6676,28 +6676,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mohamed Salah Menuju Trabzonspor</t>
+          <t>Jadwal Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:20:20 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mohamed Salah menuju Trabzonspor. Klub Turki itu mengonfirmasi bakal bernegosiasi dengan pemain asal Mesir tersebut.</t>
+          <t>Jadwal final Piala Presiden 2026 mempertemukan Persib Bandung vs Persebaya Surabaya.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604653/mohamed-salah-menuju-trabzonspor</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604949/jadwal-final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/mohamed-salah-1781054944371_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Edisi Kedua! Ajang Lari Rekreasional di DIY Segera Digelar Lagi</t>
+          <t>Neymar di Persimpangan Jalan Kariernya</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:15:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:00 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ajang lari rekresional di Daerah Istimewa Yogyakarta (DIY) edisi kedua, Jogja Run'nShine, akan kembali digelar. Inovasi dihadirkan dari evaluasi edisi perdana.</t>
+          <t>Kontrak Neymar di Santos tinggal tersisa beberapa bulan lagi. Neymar tengah mempertimbangkan kelanjutan kariernya sebagai pesepakbola, lanjut main atau pensiun.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604536/edisi-kedua-ajang-lari-rekreasional-di-diy-segera-digelar-lagi</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604692/neymar-di-persimpangan-jalan-kariernya</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jogja-runnshine-1785853110207_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/neymar-menangis-akhiri-karier-bersama-timnas-brasil-1783314392616_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6752,28 +6752,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FIFA Bantah Infantino 'Dicuekin' Donald Trump</t>
+          <t>Presiden FIFA Gianni Infantino Gelar Rapat Darurat!</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:00:18 +0700</t>
+          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ada kabar Gianni Infantino tak bisa menghubungi Donald Trump usai wacana menjual saham Piala Dunia batal. FIFA membantah laporan tersebut.</t>
+          <t>Gianni Infantino dilaporkan menggelar rapat darurat. Hal ini dilakukan di tengah desakan agar dirinya mundur dari FIFA.</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604623/fifa-bantah-infantino-dicuekin-donald-trump</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604767/presiden-fifa-gianni-infantino-gelar-rapat-darurat</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/trump-tampak-didampingi-presiden-fifa-gianni-infantino-saat-berbicara-dalam-acara-fifa-yang-digelar-di-trump-tower-new-york-ci-1784348679880_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6790,28 +6790,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Bernardo Silva: Saat Madrid Memanggil, Mustahil Bilang Tidak</t>
+          <t>Belum Selesai Belanja, Chelsea Siap Gaet Pengganti Cucurella</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 04:00:04 +0700</t>
+          <t>Wed, 05 Aug 2026 10:20:00 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bernardo Silva tidak berpikir dua kali saat mendapat tawaran dari Real Madrid. Menolak Madrid diakui Silva merupakan hal yang mustahil.</t>
+          <t>Chelsea belum berhenti belanja musim panas ini. The Blues dilaporkan bakal mendatangkan pengganti Marc Cucurella.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604621/bernardo-silva-saat-madrid-memanggil-mustahil-bilang-tidak</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604768/belum-selesai-belanja-chelsea-siap-gaet-pengganti-cucurella</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/bernardo-silva-1759772326382_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pep-chavarriarayo-vallecanolaligaliga-spanyolchelsea-1785891772000_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6828,28 +6828,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Hasil Uji Coba: AS Roma Gilas Newport County 4-1</t>
+          <t>Amorim Jelang Milan Vs Inter: Juara Pramusim Nggak Penting</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 03:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 10:00:15 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AS Roma mengalahkan Newport County dalam laga uji coba pramusim. Serigala Ibu Kota menang telak 4-1.</t>
+          <t>AC Milan akan menghadapi Inter Milan di laga uji coba pramusim. Pelatih Milan Ruben Amorim menyebut hasil akhir bukan yang paling utama.</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604646/hasil-uji-coba-as-roma-gilas-newport-county-4-1</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604711/amorim-jelang-milan-vs-inter-juara-pramusim-nggak-penting</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/as-romanewport-countylaga-pramusimlaga-uji-cobasantiago-castro-1785873342683_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ruben-amorim-1785887341737_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6866,28 +6866,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>'Klan' Kluivert Berlanjut</t>
+          <t>Carragher Nilai Liverpool Belum Siap Bersaing Jadi Juara Premier League</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 02:00:23 +0700</t>
+          <t>Wed, 05 Aug 2026 09:40:09 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Shane Kluivert debut di tim utama Barcelona. Shane lanjutkan jejak sang ayah Patrick Kluivert yang 28 tahun lalu juga main buat Barca.</t>
+          <t>Jamie Carragher menilai Liverpool belum cukup kuat untuk bersaing memperebutkan gelar juara Premier League. Menurutnya, skuad Liverpool belum lengkap.</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604292/klan-kluivert-berlanjut</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604726/carragher-nilai-liverpool-belum-siap-bersaing-jadi-juara-premier-league</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/shane-kluivert-1785831287018.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/andoni-iraola-1785219269838_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6904,28 +6904,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Piala Presiden 2026: Merawat Sportivitas, Menjaga Integritas</t>
+          <t>Kolo Muani Punya Urusan yang Belum Selesai di Juventus</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:26:47 +0700</t>
+          <t>Wed, 05 Aug 2026 09:20:13 +0700</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Piala Presiden 2026 diharapkan mampu menjadi teladan penyelenggaraan pertandingan resmi sepakbola nasional.</t>
+          <t>Randal Kolo Muani amat gembira bisa kembali ke Juventus. Kolo Muani ingin menuntaskan apa yang sudah ia mulai di Turin.</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604636/piala-presiden-2026-merawat-sportivitas-menjaga-integritas</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604710/kolo-muani-punya-urusan-yang-belum-selesai-di-juventus</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/piala-presiden-2026-1785863698077_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/09/randal-kolo-muani-1752056032311_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6942,28 +6942,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Terus Kejar Guimaraes, Arsenal Negosiasi Langsung dengan Newcastle</t>
+          <t>Kata-kata Erick Thohir soal Dukung Infantino Terus Pimpin FIFA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:00:23 +0700</t>
+          <t>Wed, 05 Aug 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Arsenal kini tengah bernegosiasi langsung dengan Newcastle United. Ini upaya lanjutan The Gunners untuk mendapatkan Bruno Guimaraes.</t>
+          <t>Ketua Umum PSSI, Erick Thohir, bikin pernyatan soal dukungannya ke Gianni Infantino. Ia menyebut Indonesia sudah banyak dibantu Presiden FIFA tersebut.</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604610/terus-kejar-guimaraes-arsenal-negosiasi-langsung-dengan-newcastle</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604792/kata-kata-erick-thohir-soal-dukung-infantino-terus-pimpin-fifa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/bruno-guimaraes-1783531838994_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/18/erick-thohir-dan-presiden-fifa-gianni-infantino-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6980,28 +6980,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PSSI Ikrarkan Dukungan ke Gianni Infantino Terus Pimpin FIFA</t>
+          <t>Inter Vs Milan di Pramusim, Chivu: Fokusnya ke Kebugaran</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:30:00 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:21 +0700</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan dukungannya ke Gianni Infantino. FIFA, di bawah pimpinannya, disebut membantu Indonesia.</t>
+          <t>Inter Milan melanjutkan tur pramusimnya dengan melawan AC Milan di Australia. Pelatih Nerazzurri Cristian Chivu menegaskan fokus timnya ke membangun kebugaran.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604633/pssi-ikrarkan-dukungan-ke-gianni-infantino-terus-pimpin-fifa</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604317/inter-vs-milan-di-pramusim-chivu-fokusnya-ke-kebugaran</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/23/gianni-infantino-erick-thohir_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7018,28 +7018,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Emmanuel Macron Dukung UEFA Lawan Gianni Infantino</t>
+          <t>Dipercaya di Surabaya Marathon 2026, Le Minerale Hadir di 18 Water Station</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:30 +0700</t>
+          <t>Wed, 05 Aug 2026 08:22:43 +0700</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Presiden Prancis Emmanuel Macron diketahui dukung UEFA untuk melawan Presiden FIFA Gianni Infantino. Mulai ada campur tangan politik negara-negara besar, nih!</t>
+          <t>Le Minerale Surabaya Marathon 2026 diikuti 7.000 pelari, mengusung konsep City Run. Acara ini mendukung sport tourism dan hidrasi optimal dengan Le Minerale.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604322/emmanuel-macron-dukung-uefa-lawan-gianni-infantino</t>
+          <t>https://sport.detik.com/sportstyle/d-8604762/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/presiden-prancis-emmanuel-macron-1754969579570.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station-1785892907123.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7051,600 +7051,544 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HeadlineBanding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 Miliar</t>
+          <t>Mourinho Ingin Vinicius Selalu Bahagia di Madrid</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 08:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+          <t>Di tengah rumor Arsenal, Vinicius buka suara usai menjalani latihan pramusim bersama Real Madrid. Vinicius bilang Jose Mourinho ingin ia bahagia di Madrid.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604655/mourinho-ingin-vinicius-selalu-bahagia-di-madrid</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/15/soccer-spain-rma-rso-1771110362377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BPS: Pertumbuhan Ekonomi Indonesia 5,29 Persen pada Kuartal II 2026Money</t>
+          <t>Alejandro Garnacho Langsung 'Babak Belur' di Pramusim Aston Villa</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 07:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>BPS mencatat pertumbuhan ekonomi Indonesia di Kuartal II 2026 mencapai 5,29% (yoy). Sektor pengadaan listrik &amp; gas memimpin, meski pertambangan terkontraksi.</t>
+          <t>Alejandro Garnacho baru pindah ke Aston Villa musim panas ini. Di laga pramusim, winger Argentina itu langsung babak belur.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/114132726/bps-pertumbuhan-ekonomi-indonesia-529-persen-pada-kuartal-ii-2026?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604654/alejandro-garnacho-langsung-babak-belur-di-pramusim-aston-villa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/tO31vuJAGVU9FYHw3s-ozVN7cRc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/08/05/689187ab3472b.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/alejandro-garnachoaston-villabg-pathum-vs-aston-villapramusim-aston-villa-1785881271654_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 Disebut Punya Sekoci dan Life Raft, Kenapa Penumpang Lompat ke Laut?Regional</t>
+          <t>Asosiasi Sepakbola Yordania Merasa Diperas FIFA!</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 07:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Peralatan keselamatan diklaim tidak dapat digunakan karena api dengan cepat menjalar ke bagian belakang KMP Mutiara Sentosa 2.</t>
+          <t>Asosiasi Sepakbola Yordania (JFA) bikin pernyataan keras soal FIFA. Mereka mengaku diperas organisasi pimpinan Gianni Infantino tersebut.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/08/05/114100578/kmp-mutiara-sentosa-2-disebut-punya-sekoci-dan-life-raft-kenapa-penumpang?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604652/asosiasi-sepakbola-yordania-merasa-diperas-fifa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/hlZkBMsoqbiFwrId5Gsswi-eJMk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7201b327072.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/11/logo-fifa_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Chery Ungkap Penyebab Tiggo 8 CSH Berasap di Basement ICE BSDOtomotif</t>
+          <t>Semifinal Piala Presiden 2026 yang Aman dan Seru!</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 06:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Chery memastikan asap pada Tiggo 8 CSH di basement ICE BSD dipicu salah isi bahan bakar, bukan masalah baterai atau kelistrikan.</t>
+          <t>Semifinal Piala Presiden 2026 sudah digelar. Rangkaian pertandingan berjalan aman dan seru, sesuai yang diharapkan.</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/083200115/chery-ungkap-penyebab-tiggo-8-csh-berasap-di-basement-ice-bsd?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604648/semifinal-piala-presiden-2026-yang-aman-dan-seru</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/Yx1CJ4ytDmvGio3VxuAhvw7mP8g=/150x75:1050x675/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a7266800baa4.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-semifinal-piala-presiden-2026-antara-persib-vs-persija-di-stadion-kapten-i-wayan-dipta-gianyar-bali-selasa-482026-1785862146465.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Penjelasan Kepala Desa soal Penyebab Jembatan Rusak Melengkung di KebumenRegional</t>
+          <t>Mohamed Salah Menuju Trabzonspor</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jembatan Sirnoboyo di Kebumen rusak parah akibat penurunan fondasi, mengancam akses vital Bonorowo-Mirit.</t>
+          <t>Mohamed Salah menuju Trabzonspor. Klub Turki itu mengonfirmasi bakal bernegosiasi dengan pemain asal Mesir tersebut.</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/113256178/penjelasan-kepala-desa-soal-penyebab-jembatan-rusak-melengkung-di-kebumen?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604653/mohamed-salah-menuju-trabzonspor</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/YVYF8uUEiS7TviEWS2yVBg7NEhM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72b9d1b42f7.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/mohamed-salah-1781054944371_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Korlantas Bantah Kembali Berlalukan Tilang ManualNews</t>
+          <t>Edisi Kedua! Ajang Lari Rekreasional di DIY Segera Digelar Lagi</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 05:15:25 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Korlantas Polri membantah kabar penerapan kembali tilang manual dan kenaikan denda hingga 150 persen, tipenindakan tetap utamakan ETLE</t>
+          <t>Ajang lari rekresional di Daerah Istimewa Yogyakarta (DIY) edisi kedua, Jogja Run'nShine, akan kembali digelar. Inovasi dihadirkan dari evaluasi edisi perdana.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11242771/korlantas-bantah-kembali-berlalukan-tilang-manual?source=headline</t>
+          <t>https://sport.detik.com/sport-lain/d-8604536/edisi-kedua-ajang-lari-rekreasional-di-diy-segera-digelar-lagi</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/KClVTsIhD8FAvYbBgwh17JRksb4=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/08/6a25ca9500411.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jogja-runnshine-1785853110207_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Kisah Keluarga di Padang Bertahan dari Banjir, Ban Pelampung Jadi Andalan Cari MakananRegional</t>
+          <t>FIFA Bantah Infantino 'Dicuekin' Donald Trump</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 05:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Saat banjir 2 meter merendam rumahnya, keluarga Yarman mengandalkan ban dalam bekas untuk mencari makanan dan bertahan hidup.</t>
+          <t>Ada kabar Gianni Infantino tak bisa menghubungi Donald Trump usai wacana menjual saham Piala Dunia batal. FIFA membantah laporan tersebut.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/111436278/kisah-keluarga-di-padang-bertahan-dari-banjir-ban-pelampung-jadi-andalan?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604623/fifa-bantah-infantino-dicuekin-donald-trump</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/RcVt6y0zoU3CJ6RxmgNPLf80Qzk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ab031a7a1.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/trump-tampak-didampingi-presiden-fifa-gianni-infantino-saat-berbicara-dalam-acara-fifa-yang-digelar-di-trump-tower-new-york-ci-1784348679880_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Megapolitan</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1Saat Sampah ke Bantargebang Terus Berkurang, Krisis Diam-diam Menghantui Kampung PemulungNews</t>
+          <t>Bernardo Silva: Saat Madrid Memanggil, Mustahil Bilang Tidak</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 04:00:04 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ribuan warga Ciketing Udik, Bantargebang, menggantungkan hidup dari sampah. Kini, pasokan berkurang dan penutupan TPA mengancam masa depan mereka.</t>
+          <t>Bernardo Silva tidak berpikir dua kali saat mendapat tawaran dari Real Madrid. Menolak Madrid diakui Silva merupakan hal yang mustahil.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://megapolitan.kompas.com/read/2026/08/05/09303171/saat-sampah-ke-bantargebang-terus-berkurang-krisis-diam-diam-menghantui?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604621/bernardo-silva-saat-madrid-memanggil-mustahil-bilang-tidak</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/W85u3qy33e0n8iASk-DCYVTwYVA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72980672081.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/bernardo-silva-1759772326382_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2Pengaruh Politik Jokowi Masih BesarNews</t>
+          <t>Hasil Uji Coba: AS Roma Gilas Newport County 4-1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 03:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pengaruh politik memang tidak identik dengan kekuasaan formal. Kekuasaan Jokowi sebagai presiden telah selesai, sedangkan pengaruhnya belum selesai.</t>
+          <t>AS Roma mengalahkan Newport County dalam laga uji coba pramusim. Serigala Ibu Kota menang telak 4-1.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/09290001/pengaruh-politik-jokowi-masih-besar?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604646/hasil-uji-coba-as-roma-gilas-newport-county-4-1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/t7YT9gwrldsaAdH_b9qHJv1aBYw=/311x90:996x547/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/02/6a6f1955bc8cd.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/as-romanewport-countylaga-pramusimlaga-uji-cobasantiago-castro-1785873342683_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>3Kepala Daerah Tersandung Korupsi Tak Bisa Langsung Dipecat, Tito: Bukan Anak Kemarin SoreRegional</t>
+          <t>'Klan' Kluivert Berlanjut</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 02:00:23 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Mendagri Tito Karnavian menjelaskan bahwa pemberhentian kepala daerah korup tidak bisa langsung dilakukan karena ada mekanisme prosedural yang harus dilalui.</t>
+          <t>Shane Kluivert debut di tim utama Barcelona. Shane lanjutkan jejak sang ayah Patrick Kluivert yang 28 tahun lalu juga main buat Barca.</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/08/05/103939478/kepala-daerah-tersandung-korupsi-tak-bisa-langsung-dipecat-tito-bukan-anak?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604292/klan-kluivert-berlanjut</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/5lwMUiwTHlyFZAMnUTExWLoG1Tw=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a59c24c08.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/shane-kluivert-1785831287018.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4Perputaran Uang Judi Online Tembus Rp 86,8 Triliun, PPATK: Modus Pelaku Makin CanggihMoney</t>
+          <t>Piala Presiden 2026: Merawat Sportivitas, Menjaga Integritas</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 01:26:47 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PPATK laporkan pelaku judi online makin camggih cara beroperasinya.</t>
+          <t>Piala Presiden 2026 diharapkan mampu menjadi teladan penyelenggaraan pertandingan resmi sepakbola nasional.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/094834426/perputaran-uang-judi-online-tembus-rp-868-triliun-ppatk-modus-pelaku-makin?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604636/piala-presiden-2026-merawat-sportivitas-menjaga-integritas</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/-zA-jcUu2Y7LQxrwFToq04J-o04=/112x402:1010x1000/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a7299c6e53ea.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/piala-presiden-2026-1785863698077_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5Banding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 MiliarNews</t>
+          <t>Terus Kejar Guimaraes, Arsenal Negosiasi Langsung dengan Newcastle</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 01:00:23 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+          <t>Arsenal kini tengah bernegosiasi langsung dengan Newcastle United. Ini upaya lanjutan The Gunners untuk mendapatkan Bruno Guimaraes.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604610/terus-kejar-guimaraes-arsenal-negosiasi-langsung-dengan-newcastle</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/bruno-guimaraes-1783531838994_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Komparasi Changan Nevo Q05 Vs Jaecoo J5 EV, Pilih Mana?Otomotif</t>
+          <t>PSSI Ikrarkan Dukungan ke Gianni Infantino Terus Pimpin FIFA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 00:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Duel dua SUV listrik Rp 300 jutaan. Simak perbandingan desain, fitur, baterai, jarak tempuh, performa, hingga harga.</t>
+          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan dukungannya ke Gianni Infantino. FIFA, di bawah pimpinannya, disebut membantu Indonesia.</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/110200815/komparasi-changan-nevo-q05-vs-jaecoo-j5-ev-pilih-mana-?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604633/pssi-ikrarkan-dukungan-ke-gianni-infantino-terus-pimpin-fifa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/3f4DFDwFteW4JUX_XX4XDaXxMD0=/0x0:1264x843/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a72908834b4a.png</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/23/gianni-infantino-erick-thohir_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Lifestyle</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Apa Itu Friend Bombing? Ini Ciri dan Cara MenyikapinyaLifestyle</t>
+          <t>Emmanuel Macron Dukung UEFA Lawan Gianni Infantino</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 00:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Friend-bombing menyerupai love-bombing, tetapi terjadi dalam ranah persahabatan sehingga sering kali lebih sulit disadari sejak awal.</t>
+          <t>Presiden Prancis Emmanuel Macron diketahui dukung UEFA untuk melawan Presiden FIFA Gianni Infantino. Mulai ada campur tangan politik negara-negara besar, nih!</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://lifestyle.kompas.com/read/2026/08/05/110100820/apa-itu-friend-bombing-ini-ciri-dan-cara-menyikapinya?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604322/emmanuel-macron-dukung-uefa-lawan-gianni-infantino</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/EoPbroI6It3crom92-hL9IYHOGA=/0x0:1417x945/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/29/697b90e878546.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/presiden-prancis-emmanuel-macron-1754969579570.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tren Baru di China, Orangtua Rela Bayar Rp 34 Juta agar Anak Jadi "Warren Buffett Kecil"Tren</t>
+          <t>HeadlineBanding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 Miliar</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7659,17 +7603,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Orangtua di China rela membayar Rp 34 juta untuk kursus finansial agar anak menjadi “Warren Buffett kecil”. Apa saja yang dipelajari anak-anak?</t>
+          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/tren/read/2026/08/05/110000965/tren-baru-di-china-orangtua-rela-bayar-rp-34-juta-agar-anak-jadi-warren?source=sorotan</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=headline</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/t6-jEBcH9eEWOjfSeuph37-AxtU=/0x0:4411x2941/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71bc5105128.jpg</t>
+          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -7686,7 +7630,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>OJK Tindak 15 Perusahaan Pialang Asuransi Ilegal, Sebagian Masuk Tahap SidangMoney</t>
+          <t>BPS: Pertumbuhan Ekonomi Indonesia 5,29 Persen pada Kuartal II 2026Money</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7701,17 +7645,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>OJK menemukan 15 pialang asuransi ilegal dan telah melakukan penindakan hukum. Langkah ini diikuti penguatan pengawasan melalui QR Code STDD.</t>
+          <t>BPS mencatat pertumbuhan ekonomi Indonesia di Kuartal II 2026 mencapai 5,29% (yoy). Sektor pengadaan listrik &amp; gas memimpin, meski pertambangan terkontraksi.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/111000226/ojk-tindak-15-perusahaan-pialang-asuransi-ilegal-sebagian-masuk-tahap-sidang?source=sorotan</t>
+          <t>https://money.kompas.com/read/2026/08/05/114132726/bps-pertumbuhan-ekonomi-indonesia-529-persen-pada-kuartal-ii-2026?source=headline</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/YxKhv82UZiNeBll_taObKpFfJPg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/01/23/697329f06af52.jpg</t>
+          <t>https://asset.kompas.com/crops/tO31vuJAGVU9FYHw3s-ozVN7cRc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/08/05/689187ab3472b.jpeg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -7723,12 +7667,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Surabaya</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Indra Bekti Turun Berat Badan hingga 10 Kg, Kurangi Nasi dan RotiHype</t>
+          <t>KMP Mutiara Sentosa 2 Disebut Punya Sekoci dan Life Raft, Kenapa Penumpang Lompat ke Laut?Regional</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7743,17 +7687,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Indra Bekti berhasil menurunkan 10 kg berat badan berkat pola hidup sehat, mengurangi nasi dan makanan tinggi karbohidrat. Ia kini merasa lebih nyaman dan sehat.</t>
+          <t>Peralatan keselamatan diklaim tidak dapat digunakan karena api dengan cepat menjalar ke bagian belakang KMP Mutiara Sentosa 2.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://entertainment.kompas.com/read/2026/08/05/105301166/indra-bekti-turun-berat-badan-hingga-10-kg-kurangi-nasi-dan-roti?source=sorotan</t>
+          <t>https://surabaya.kompas.com/read/2026/08/05/114100578/kmp-mutiara-sentosa-2-disebut-punya-sekoci-dan-life-raft-kenapa-penumpang?source=headline</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/HgKxpJUQrKNcgGV8Mee8gw7wU2A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/05/6a72ace08557d.jpeg</t>
+          <t>https://asset.kompas.com/crops/hlZkBMsoqbiFwrId5Gsswi-eJMk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7201b327072.jpeg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -7765,12 +7709,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Otomotif</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Regional1 menit laluApindo Bongkar Penyebab PHK Massal Tambang Kaltim, RKAB-Tekanan Global Disorot</t>
+          <t>Chery Ungkap Penyebab Tiggo 8 CSH Berasap di Basement ICE BSDOtomotif</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7785,17 +7729,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Apindo mengungkap gelombang PHK di sektor tambang Kaltim dipicu RKAB yang belum tuntas, pemangkasan kuota produksi, hingga tekanan ekonomi global.</t>
+          <t>Chery memastikan asap pada Tiggo 8 CSH di basement ICE BSD dipicu salah isi bahan bakar, bukan masalah baterai atau kelistrikan.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/120401478/apindo-bongkar-penyebab-phk-massal-tambang-kaltim-rkab-tekanan-global</t>
+          <t>https://otomotif.kompas.com/read/2026/08/05/083200115/chery-ungkap-penyebab-tiggo-8-csh-berasap-di-basement-ice-bsd?source=headline</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/AzQSgHHBPhJuBQerJvYdWoGTIZ0=/0x807:1920x2087/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bee36413e.jpg</t>
+          <t>https://asset.kompas.com/crops/Yx1CJ4ytDmvGio3VxuAhvw7mP8g=/150x75:1050x675/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a7266800baa4.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -7807,12 +7751,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bola</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Bola1 menit laluWilshere Punya Pesan untuk Lewis-Skelly di Tengah Rumor Transfer ke MU</t>
+          <t>Penjelasan Kepala Desa soal Penyebab Jembatan Rusak Melengkung di KebumenRegional</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7827,17 +7771,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Pemain muda Arsenal, Myles Lewis-Skelly  diisukan tengah jadi incaran klub Liga Inggris, Manchester United di bursa transfer.</t>
+          <t>Jembatan Sirnoboyo di Kebumen rusak parah akibat penurunan fondasi, mengancam akses vital Bonorowo-Mirit.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://bola.kompas.com/read/2026/08/05/12035258/wilshere-punya-pesan-untuk-lewis-skelly-di-tengah-rumor-transfer-ke-mu</t>
+          <t>https://regional.kompas.com/read/2026/08/05/113256178/penjelasan-kepala-desa-soal-penyebab-jembatan-rusak-melengkung-di-kebumen?source=headline</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/lneFfSI90hr2uZ0CkiybCs9a9X4=/72x0:806x489/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2025/01/29/679958d6dd5b9.jpg</t>
+          <t>https://asset.kompas.com/crops/YVYF8uUEiS7TviEWS2yVBg7NEhM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72b9d1b42f7.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -7849,12 +7793,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Megapolitan</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>News2 menit laluNiat "Resign", Pekerja Bank Keliling di Tangerang Malah Dianiaya dan Disekap Bosnya</t>
+          <t>Korlantas Bantah Kembali Berlalukan Tilang ManualNews</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7869,17 +7813,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sebelum dugaan penganiayaan memuncak pada Selasa (28/7/2026), korban PG sempat mengabari istrinya lewat pesan singkat karena merasa jiwanya terancam.</t>
+          <t>Korlantas Polri membantah kabar penerapan kembali tilang manual dan kenaikan denda hingga 150 persen, tipenindakan tetap utamakan ETLE</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://megapolitan.kompas.com/read/2026/08/05/12033681/niat-resign-pekerja-bank-keliling-di-tangerang-malah-dianiaya-dan-disekap</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/11242771/korlantas-bantah-kembali-berlalukan-tilang-manual?source=headline</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/gHRVJfPAf7MhQDx1nLckk-CEy1Y=/62x0:622x373/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2020/10/14/5f86cca13c2ef.jpeg</t>
+          <t>https://asset.kompas.com/crops/KClVTsIhD8FAvYbBgwh17JRksb4=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/08/6a25ca9500411.jpeg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7891,12 +7835,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>News3 menit laluBrankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan Rakyat</t>
+          <t>Kisah Keluarga di Padang Bertahan dari Banjir, Ban Pelampung Jadi Andalan Cari MakananRegional</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7911,17 +7855,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Perang melawan korupsi seharusnya tidak dipahami semata sebagai agenda penegakan hukum.</t>
+          <t>Saat banjir 2 meter merendam rumahnya, keluarga Yarman mengandalkan ban dalam bekas untuk mencari makanan dan bertahan hidup.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat</t>
+          <t>https://regional.kompas.com/read/2026/08/05/111436278/kisah-keluarga-di-padang-bertahan-dari-banjir-ban-pelampung-jadi-andalan?source=headline</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/BxG7N1wef22vGuge6xZA46tILF0=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/27/6a66843ea3864.jpg</t>
+          <t>https://asset.kompas.com/crops/RcVt6y0zoU3CJ6RxmgNPLf80Qzk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ab031a7a1.jpeg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -7933,12 +7877,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Megapolitan</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tren5 menit laluDukcapil Ungkap 3 Provinsi dengan Penduduk Terbanyak dan Tersedikit</t>
+          <t>1Saat Sampah ke Bantargebang Terus Berkurang, Krisis Diam-diam Menghantui Kampung PemulungNews</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7953,17 +7897,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ditjen Kependudukan dan Pencatatan Sipil (Dukcapil) Kemendagri RI membagikan jumlah penduduk Indonesia terbaru, per 30 Juni 2026.</t>
+          <t>Ribuan warga Ciketing Udik, Bantargebang, menggantungkan hidup dari sampah. Kini, pasokan berkurang dan penutupan TPA mengancam masa depan mereka.</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/tren/read/2026/08/05/120000765/dukcapil-ungkap-3-provinsi-dengan-penduduk-terbanyak-dan-tersedikit</t>
+          <t>https://megapolitan.kompas.com/read/2026/08/05/09303171/saat-sampah-ke-bantargebang-terus-berkurang-krisis-diam-diam-menghantui?source=terpopuler</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/ueTdSyaVp3-VhdmCXdwkIrRLHqU=/0x0:1279x853/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/05/06/69fafeb7096e1.jpg</t>
+          <t>https://asset.kompas.com/crops/W85u3qy33e0n8iASk-DCYVTwYVA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72980672081.jpeg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -7975,12 +7919,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Money5 menit laluApa Bedanya Lipstick Effect dan Affordable Luxury? Ini Penjelasannya</t>
+          <t>2Pengaruh Politik Jokowi Masih BesarNews</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7995,17 +7939,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ada fenomena yang kerap muncul ketika ekonomi sedang lesu, yakni meningkatnya minat terhadap produk-produk yang dapat menunjang penampilan.</t>
+          <t>Pengaruh politik memang tidak identik dengan kekuasaan formal. Kekuasaan Jokowi sebagai presiden telah selesai, sedangkan pengaruhnya belum selesai.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/120000926/apa-bedanya-lipstick-effect-dan-affordable-luxury-ini-penjelasannya</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/09290001/pengaruh-politik-jokowi-masih-besar?source=terpopuler</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/lRLIWEv9lyp_bKOEOE5pYgIyg5s=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2023/04/03/642ab28ed12d5.jpg</t>
+          <t>https://asset.kompas.com/crops/t7YT9gwrldsaAdH_b9qHJv1aBYw=/311x90:996x547/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/02/6a6f1955bc8cd.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -8017,12 +7961,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Surabaya</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Properti5 menit laluPutus Rantai Kemiskinan, Sekolah Rakyat 10 Hektar di Jepara Siap Tampung 345 Siswa</t>
+          <t>3Kepala Daerah Tersandung Korupsi Tak Bisa Langsung Dipecat, Tito: Bukan Anak Kemarin SoreRegional</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8037,17 +7981,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pembangunan Sekolah Rakyat (SR) di Jepara, Jawa Tengah, telah memasuki tahap akhir dan dipastikan siap difungsionalkan untuk kegiatan belajar mengajar</t>
+          <t>Mendagri Tito Karnavian menjelaskan bahwa pemberhentian kepala daerah korup tidak bisa langsung dilakukan karena ada mekanisme prosedural yang harus dilalui.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/properti/read/2026/08/05/120000721/putus-rantai-kemiskinan-sekolah-rakyat-10-hektar-di-jepara-siap-tampung</t>
+          <t>https://surabaya.kompas.com/read/2026/08/05/103939478/kepala-daerah-tersandung-korupsi-tak-bisa-langsung-dipecat-tito-bukan-anak?source=terpopuler</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/xdbG4nsI9ygOACgICogMsD5LF-Q=/0x0:1280x853/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/08/05/6a72a23fd3166.jpeg</t>
+          <t>https://asset.kompas.com/crops/5lwMUiwTHlyFZAMnUTExWLoG1Tw=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a59c24c08.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -8059,12 +8003,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Lifestyle</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lifestyle5 menit laluHubungan Toksik Disebut Meningkatkan Risiko Depresi, Ini Kata Psikolog</t>
+          <t>4Perputaran Uang Judi Online Tembus Rp 86,8 Triliun, PPATK: Modus Pelaku Makin CanggihMoney</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8079,17 +8023,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hubungan yang dipenuhi konflik dan minim dukungan emosional tak hanya mengganggu keharmonisan, tetapi juga disebut dapat meningkatkan risiko depresi.</t>
+          <t>PPATK laporkan pelaku judi online makin camggih cara beroperasinya.</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://lifestyle.kompas.com/read/2026/08/05/120000220/hubungan-toksik-disebut-meningkatkan-risiko-depresi-ini-kata-psikolog</t>
+          <t>https://money.kompas.com/read/2026/08/05/094834426/perputaran-uang-judi-online-tembus-rp-868-triliun-ppatk-modus-pelaku-makin?source=terpopuler</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/tOEnh9SQQYKjNm1rb40WnhVf0Lo=/0x0:1375x917/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/31/697dc89524410.jpeg</t>
+          <t>https://asset.kompas.com/crops/-zA-jcUu2Y7LQxrwFToq04J-o04=/112x402:1010x1000/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a7299c6e53ea.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -8101,12 +8045,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Regional6 menit laluDedi Mulyadi Nyatakan Perang terhadap Tramadol, Sebut Jadi Pemicu Kriminalitas</t>
+          <t>5Banding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 MiliarNews</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8121,17 +8065,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gubernur Jabar Dedi Mulyadi serukan perang terhadap tramadol dan miras. Ia sebut peredarannya memicu meningkatnya kriminalitas.</t>
+          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://bandung.kompas.com/read/2026/08/05/115927178/dedi-mulyadi-nyatakan-perang-terhadap-tramadol-sebut-jadi-pemicu</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=terpopuler</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/X6Wi6HTpMcUExofQaDLVjcUXC4U=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a71814d28e41.jpeg</t>
+          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -8143,12 +8087,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Otomotif</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Dalam Semangat Kemerdekaan, Mandiri Donor Darah Kembali Hadir Dukung Ketersediaan Darah Nasional</t>
+          <t>Komparasi Changan Nevo Q05 Vs Jaecoo J5 EV, Pilih Mana?Otomotif</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8163,17 +8107,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Menyambut HUT ke-81 RI dan usia 28 tahun melayani negeri, Bank Mandiri menggelar aksi 'Mandiri Donor Darah' serentak di 12 region se-Indonesia.</t>
+          <t>Duel dua SUV listrik Rp 300 jutaan. Simak perbandingan desain, fitur, baterai, jarak tempuh, performa, hingga harga.</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/111451426/dalam-semangat-kemerdekaan-mandiri-donor-darah-kembali-hadir-dukung</t>
+          <t>https://otomotif.kompas.com/read/2026/08/05/110200815/komparasi-changan-nevo-q05-vs-jaecoo-j5-ev-pilih-mana-?source=sorotan</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/mFkRD0H1S6NeT7co-aFE7piNn7o=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72b60386b45.jpg</t>
+          <t>https://asset.kompas.com/crops/3f4DFDwFteW4JUX_XX4XDaXxMD0=/0x0:1264x843/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a72908834b4a.png</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -8185,12 +8129,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Komisi IV DPR RI Apresiasi Langkah Mentan Amran Bongkar Dugaan Mafia Beras Fortifikasi</t>
+          <t>Apa Itu Friend Bombing? Ini Ciri dan Cara MenyikapinyaLifestyle</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8205,17 +8149,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Anggota Komisi IV DPR RI Endang S Tohari menilai praktik pengoplosan beras fortifikasi merupakan kejahatan serius yang tidak dapat ditoleransi.</t>
+          <t>Friend-bombing menyerupai love-bombing, tetapi terjadi dalam ranah persahabatan sehingga sering kali lebih sulit disadari sejak awal.</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/104408026/komisi-iv-dpr-ri-apresiasi-langkah-mentan-amran-bongkar-dugaan-mafia-beras</t>
+          <t>https://lifestyle.kompas.com/read/2026/08/05/110100820/apa-itu-friend-bombing-ini-ciri-dan-cara-menyikapinya?source=sorotan</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/B0W3J3lt6QD6y9DoQh2yxyGlFqI=/0x134:1599x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72a85e917e8.jpeg</t>
+          <t>https://asset.kompas.com/crops/EoPbroI6It3crom92-hL9IYHOGA=/0x0:1417x945/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/29/697b90e878546.jpeg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -8227,12 +8171,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Berita Utama</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mendagri: Integritas Kepala Daerah Jadi Kunci Wujudkan Tata Kelola Pemerintahan yang Bersih dan Akuntabel</t>
+          <t>Tren Baru di China, Orangtua Rela Bayar Rp 34 Juta agar Anak Jadi "Warren Buffett Kecil"Tren</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -8247,17 +8191,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Mendagri Tito menekankan, setiap kepala daerah dituntut untuk menjaga prinsip-prinsip antikorupsi serta tidak tergoda melakukan pelanggaran hukum.</t>
+          <t>Orangtua di China rela membayar Rp 34 juta untuk kursus finansial agar anak menjadi “Warren Buffett kecil”. Apa saja yang dipelajari anak-anak?</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/10061371/mendagri-integritas-kepala-daerah-jadi-kunci-wujudkan-tata-kelola</t>
+          <t>https://www.kompas.com/tren/read/2026/08/05/110000965/tren-baru-di-china-orangtua-rela-bayar-rp-34-juta-agar-anak-jadi-warren?source=sorotan</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/h9MDSqwCb1sZpxTWESiR3d6HydQ=/0x0:1599x1066/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a4a9bd443.jpeg</t>
+          <t>https://asset.kompas.com/crops/t6-jEBcH9eEWOjfSeuph37-AxtU=/0x0:4411x2941/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71bc5105128.jpg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -8269,47 +8213,635 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>OJK Tindak 15 Perusahaan Pialang Asuransi Ilegal, Sebagian Masuk Tahap SidangMoney</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>OJK menemukan 15 pialang asuransi ilegal dan telah melakukan penindakan hukum. Langkah ini diikuti penguatan pengawasan melalui QR Code STDD.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/111000226/ojk-tindak-15-perusahaan-pialang-asuransi-ilegal-sebagian-masuk-tahap-sidang?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/YxKhv82UZiNeBll_taObKpFfJPg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/01/23/697329f06af52.jpg</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Indra Bekti Turun Berat Badan hingga 10 Kg, Kurangi Nasi dan RotiHype</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Indra Bekti berhasil menurunkan 10 kg berat badan berkat pola hidup sehat, mengurangi nasi dan makanan tinggi karbohidrat. Ia kini merasa lebih nyaman dan sehat.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://entertainment.kompas.com/read/2026/08/05/105301166/indra-bekti-turun-berat-badan-hingga-10-kg-kurangi-nasi-dan-roti?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/HgKxpJUQrKNcgGV8Mee8gw7wU2A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/05/6a72ace08557d.jpeg</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Berita Utama</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Cek fakta17 detik lalu[HOAKS] Video Purbaya Bagikan Dana Bantuan Rp 50 Juta untuk 10 Orang</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Beredar video yang menampilkan Menkeu Purbaya membagikan dana bantuan Rp 50 juta untuk 10 orang. Narasi itu hoaks.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/cekfakta/read/2026/08/05/121200382/-hoaks-video-purbaya-bagikan-dana-bantuan-rp-50-juta-untuk-10-orang</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/g-VvO8HqZ-6UxzHMfISQFtcPYhQ=/0x36:1600x1103/1200x675/data/photo/2026/08/04/6a7186d6071ef.jpeg</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Otomotif17 detik laluBYD Ingatkan Dampak Pajak Mobil Listrik terhadap Adopsi EV</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>BYD khawatir pengenaan pajak mobil listrik terlalu cepat dapat menghambat tren positif elektrifikasi di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/05/121200315/byd-ingatkan-dampak-pajak-mobil-listrik-terhadap-adopsi-ev</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mmgsH0plmX9Yekj5DwbJA3VJohE=/375x233:3657x2420/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a725367f1190.jpg</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Berita Utama</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Properti41 detik laluBUMN Karya Ini Tawarkan Properti Siap Huni, Harga Mulai Rp 300 Jutaan</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Direktur Utama PT HK Realtindo, Ekwan Hadyanto, menegaskan, mayoritas proyek yang dihadirkan merupakan hunian siap huni.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/properti/read/2026/08/05/121136421/bumn-karya-ini-tawarkan-properti-siap-huni-harga-mulai-rp-300-jutaan</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/aC6ZIxrDHBj9IR3J0dWKRmVIF2A=/432x0:3942x2340/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/04/25/69ecb9a662099.jpg</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Berita Utama</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Global1 menit lalu80 Persen Stok Rudal Pencegat AS Terkuras, Trump Pilih Batal Serang Iran</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Militer AS dilaporkan telah menghabiskan hampir 80 persen amunisi pencegat untuk sistem pertahanan udara utama THAAD.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/05/121100270/80-persen-stok-rudal-pencegat-as-terkuras-trump-pilih-batal-serang-iran</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/DC_ROqcsEzmU1c0UipGQAnNR7AI=/0x0:1997x1331/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/02/03/69817653a6f21.jpg</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Regional2 menit laluBNN Bali Bongkar Paket Narkoba Jaringan Kamboja, Disamarkan dalam Knalpot Bekas</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>BNN Bali bongkar jaringan narkoba Kamboja. Pria berinisial GAS ditangkap setelah menerima paket narkoba yang disamarkan dalam knalpot motor bekas.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://denpasar.kompas.com/read/2026/08/05/121034678/bnn-bali-bongkar-paket-narkoba-jaringan-kamboja-disamarkan-dalam-knalpot</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mFzxe5sm_MIydDJW_RxfAyOBCP8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bca8504da.jpeg</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Berita Utama</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Properti7 menit lalu7 Bangunan Penjara Paling Overkapasitas di RI</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Daftar 7 bangunan penjara terpadat di Indonesia berdasarkan rasio jumlah penghuni dan kapasitasnya.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/properti/read/2026/08/05/120523321/7-bangunan-penjara-paling-overkapasitas-di-ri</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/6gl5VWOznzCxBO4GgcZsWdpXC_8=/0x0:960x640/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/06/22/6a3921c8d4c85.jpg</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Regional8 menit laluApindo Bongkar Penyebab PHK Massal Tambang Kaltim, RKAB-Tekanan Global Disorot</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Apindo mengungkap gelombang PHK di sektor tambang Kaltim dipicu RKAB yang belum tuntas, pemangkasan kuota produksi, hingga tekanan ekonomi global.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/120401478/apindo-bongkar-penyebab-phk-massal-tambang-kaltim-rkab-tekanan-global</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/AzQSgHHBPhJuBQerJvYdWoGTIZ0=/0x807:1920x2087/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bee36413e.jpg</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Bola8 menit laluWilshere Punya Pesan untuk Lewis-Skelly di Tengah Rumor Transfer ke MU</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pemain muda Arsenal, Myles Lewis-Skelly  diisukan tengah jadi incaran klub Liga Inggris, Manchester United di bursa transfer.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/05/12035258/wilshere-punya-pesan-untuk-lewis-skelly-di-tengah-rumor-transfer-ke-mu</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/lneFfSI90hr2uZ0CkiybCs9a9X4=/72x0:806x489/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2025/01/29/679958d6dd5b9.jpg</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Megapolitan</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>News9 menit laluNiat "Resign", Pekerja Bank Keliling di Tangerang Malah Dianiaya dan Disekap Bosnya</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Sebelum dugaan penganiayaan memuncak pada Selasa (28/7/2026), korban PG sempat mengabari istrinya lewat pesan singkat karena merasa jiwanya terancam.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/05/12033681/niat-resign-pekerja-bank-keliling-di-tangerang-malah-dianiaya-dan-disekap</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/gHRVJfPAf7MhQDx1nLckk-CEy1Y=/62x0:622x373/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2020/10/14/5f86cca13c2ef.jpeg</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
           <t>Nasional</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Brankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan Rakyat</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>News10 menit laluBrankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan Rakyat</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>Kompas Cyber Media</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>Perang melawan korupsi seharusnya tidak dipahami semata sebagai agenda penegakan hukum.</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat?source=kolom</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
         <is>
           <t>https://asset.kompas.com/crops/BxG7N1wef22vGuge6xZA46tILF0=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/27/6a66843ea3864.jpg</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H215" t="inlineStr">
         <is>
           <t>Kompas</t>
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Dalam Semangat Kemerdekaan, Mandiri Donor Darah Kembali Hadir Dukung Ketersediaan Darah Nasional</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Menyambut HUT ke-81 RI dan usia 28 tahun melayani negeri, Bank Mandiri menggelar aksi 'Mandiri Donor Darah' serentak di 12 region se-Indonesia.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/111451426/dalam-semangat-kemerdekaan-mandiri-donor-darah-kembali-hadir-dukung</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mFkRD0H1S6NeT7co-aFE7piNn7o=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72b60386b45.jpg</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Komisi IV DPR RI Apresiasi Langkah Mentan Amran Bongkar Dugaan Mafia Beras Fortifikasi</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Anggota Komisi IV DPR RI Endang S Tohari menilai praktik pengoplosan beras fortifikasi merupakan kejahatan serius yang tidak dapat ditoleransi.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/104408026/komisi-iv-dpr-ri-apresiasi-langkah-mentan-amran-bongkar-dugaan-mafia-beras</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/B0W3J3lt6QD6y9DoQh2yxyGlFqI=/0x134:1599x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72a85e917e8.jpeg</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Mendagri: Integritas Kepala Daerah Jadi Kunci Wujudkan Tata Kelola Pemerintahan yang Bersih dan Akuntabel</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Mendagri Tito menekankan, setiap kepala daerah dituntut untuk menjaga prinsip-prinsip antikorupsi serta tidak tergoda melakukan pelanggaran hukum.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/10061371/mendagri-integritas-kepala-daerah-jadi-kunci-wujudkan-tata-kelola</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/h9MDSqwCb1sZpxTWESiR3d6HydQ=/0x0:1599x1066/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a4a9bd443.jpeg</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H204"/>
+  <autoFilter ref="A1:H218"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -482,28 +482,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kemendag: Camilan RI tembus pasar Arab Saudi, hasil penjajakan bisnis</t>
+          <t>Cara masuk Polstat STIS 2026: Syarat, jurusan, tahapan seleksi, dan tips lolos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:12:59 +0700</t>
+          <t>Wed, 05 Aug 2026 12:14:57 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kementerian Perdagangan (Kemendag) menyebut salah satu produk camilan Indonesia berhasil menembus pasar Arab Saudi ...</t>
+          <t>Politeknik Statistika STIS (Polstat STIS) menjadi salah satu sekolah kedinasan yang paling diminati setiap tahun karena ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680543/kemendag-camilan-ri-tembus-pasar-arab-saudi-hasil-penjajakan-bisnis</t>
+          <t>https://www.antaranews.com/berita/5680547/cara-masuk-polstat-stis-2026-syarat-jurusan-tahapan-seleksi-dan-tips-lolos</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0942.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/14/BPS2.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -520,28 +520,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus di kantor yang seru, lucu, dan bikin karyawan kompak</t>
+          <t>Jenis susu yang cocok untuk pengidap diabetes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:11:11 +0700</t>
+          <t>Wed, 05 Aug 2026 12:13:41 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 semakin dekat. Selain menjadi ...</t>
+          <t>Pengidap diabetes tetap dapat mengonsumsi susu, asalkan memilih jenis yang tepat dengan memperhatikan kandungan gula, ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680540/10-ide-lomba-17-agustus-di-kantor-yang-seru-lucu-dan-bikin-karyawan-kompak</t>
+          <t>https://www.antaranews.com/berita/5680545/jenis-susu-yang-cocok-untuk-pengidap-diabetes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/InShot_20260622_143213404.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/04/10/Screenshot_2022-04-10-11-11-42-39_copy_1024x683.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,28 +558,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Momentum ekonomi di balik kunjungan PM Thailand ke Indonesia</t>
+          <t>Kemendag: Camilan RI tembus pasar Arab Saudi, hasil penjajakan bisnis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:10:26 +0700</t>
+          <t>Wed, 05 Aug 2026 12:12:59 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Perdana Menteri Thailand Anutin Charnvirakul yang tiba di Pangkalan Udara Halim Perdanakusuma pada Senin ...</t>
+          <t>Kementerian Perdagangan (Kemendag) menyebut salah satu produk camilan Indonesia berhasil menembus pasar Arab Saudi ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680539/momentum-ekonomi-di-balik-kunjungan-pm-thailand-ke-indonesia</t>
+          <t>https://www.antaranews.com/berita/5680543/kemendag-camilan-ri-tembus-pasar-arab-saudi-hasil-penjajakan-bisnis</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0942.jpeg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -596,28 +596,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karhutla di Gunung Bromo belum padam dengan luas lahan terbakar 10 ha</t>
+          <t>10 ide lomba 17 Agustus di kantor yang seru, lucu, dan bikin karyawan kompak</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:08:46 +0700</t>
+          <t>Wed, 05 Aug 2026 12:11:11 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kebakaran hutan dan lahan (karhutla) di Gunung Bromo, Jawa Timur belum padam dengan luas lahan yang terbakar ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 semakin dekat. Selain menjadi ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680535/karhutla-di-gunung-bromo-belum-padam-dengan-luas-lahan-terbakar-10-ha</t>
+          <t>https://www.antaranews.com/berita/5680540/10-ide-lomba-17-agustus-di-kantor-yang-seru-lucu-dan-bikin-karyawan-kompak</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-09.18.39.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/InShot_20260622_143213404.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,28 +634,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WhatsApp hadirkan tiga pembaruan di layanan chat grup</t>
+          <t>Momentum ekonomi di balik kunjungan PM Thailand ke Indonesia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:07:58 +0700</t>
+          <t>Wed, 05 Aug 2026 12:10:26 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WhatsApp menghadirkan tiga pembaruan fitur di layanan chat grup, termasuk fitur jajak pendapat dan pembuat obrolan ...</t>
+          <t>Perdana Menteri Thailand Anutin Charnvirakul yang tiba di Pangkalan Udara Halim Perdanakusuma pada Senin ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680532/whatsapp-hadirkan-tiga-pembaruan-di-layanan-chat-grup</t>
+          <t>https://www.antaranews.com/berita/5680539/momentum-ekonomi-di-balik-kunjungan-pm-thailand-ke-indonesia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_104732163.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -672,28 +672,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Menjelajahi Situs Peninggalan Arkeologi Nasional Niuheliang di China</t>
+          <t>Karhutla di Gunung Bromo belum padam dengan luas lahan terbakar 10 ha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:07:21 +0700</t>
+          <t>Wed, 05 Aug 2026 12:08:46 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taman Situs Peninggalan Arkeologi Nasional Niuheliang dibangun di Situs Niuheliang, sebuah kompleks ritual dan ...</t>
+          <t>Kebakaran hutan dan lahan (karhutla) di Gunung Bromo, Jawa Timur belum padam dengan luas lahan yang terbakar ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680529/menjelajahi-situs-peninggalan-arkeologi-nasional-niuheliang-di-china</t>
+          <t>https://www.antaranews.com/berita/5680535/karhutla-di-gunung-bromo-belum-padam-dengan-luas-lahan-terbakar-10-ha</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000003_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-09.18.39.jpeg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -710,28 +710,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OJK Sulteng tingkatkan literasi keuangan nelayan melalui pelatihan</t>
+          <t>WhatsApp hadirkan tiga pembaruan di layanan chat grup</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:05:16 +0700</t>
+          <t>Wed, 05 Aug 2026 12:07:58 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) Provinsi Sulawesi Tengah (Sulteng) meningkatkan literasi dan inklusi keuangan bagi para ...</t>
+          <t>WhatsApp menghadirkan tiga pembaruan fitur di layanan chat grup, termasuk fitur jajak pendapat dan pembuat obrolan ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680527/ojk-sulteng-tingkatkan-literasi-keuangan-nelayan-melalui-pelatihan</t>
+          <t>https://www.antaranews.com/berita/5680532/whatsapp-hadirkan-tiga-pembaruan-di-layanan-chat-grup</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-37.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_104732163.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -748,28 +748,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mengenal "clean eating" beserta manfaat dan hal yang perlu diwaspadai</t>
+          <t>Menjelajahi Situs Peninggalan Arkeologi Nasional Niuheliang di China</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:03:28 +0700</t>
+          <t>Wed, 05 Aug 2026 12:07:21 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pola makan "clean eating" semakin dikenal seiring meningkatnya perhatian terhadap dampak konsumsi makanan ...</t>
+          <t>Taman Situs Peninggalan Arkeologi Nasional Niuheliang dibangun di Situs Niuheliang, sebuah kompleks ritual dan ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680525/mengenal-clean-eating-beserta-manfaat-dan-hal-yang-perlu-diwaspadai</t>
+          <t>https://www.antaranews.com/berita/5680529/menjelajahi-situs-peninggalan-arkeologi-nasional-niuheliang-di-china</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Gizi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000003_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -786,28 +786,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menteri PPN: Pengembangan singkong di Indonesia miliki prospek besar</t>
+          <t>OJK Sulteng tingkatkan literasi keuangan nelayan melalui pelatihan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:59 +0700</t>
+          <t>Wed, 05 Aug 2026 12:05:16 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) Provinsi Sulawesi Tengah (Sulteng) meningkatkan literasi dan inklusi keuangan bagi para ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680521/menteri-ppn-pengembangan-singkong-di-indonesia-miliki-prospek-besar</t>
+          <t>https://www.antaranews.com/berita/5680527/ojk-sulteng-tingkatkan-literasi-keuangan-nelayan-melalui-pelatihan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/PPN-bappenas-lampung.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-37.jpeg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -824,28 +824,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waspadai penyakit saat musim kemarau</t>
+          <t>Mengenal "clean eating" beserta manfaat dan hal yang perlu diwaspadai</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:03:28 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Udara panas dan kekeringan saat musim kemarau memicu penyebaran sejumlah penyakit yang dapat membahayakan kesehatan. ...</t>
+          <t>Pola makan "clean eating" semakin dikenal seiring meningkatnya perhatian terhadap dampak konsumsi makanan ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/infografik/5680467/waspadai-penyakit-saat-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5680525/mengenal-clean-eating-beserta-manfaat-dan-hal-yang-perlu-diwaspadai</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260805-Waspadai-penyakit-saat-musim-kemarau_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Gizi.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -862,28 +862,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pemkab Banyumas upayakan operasional Trans Banyumas tetap berlanjut</t>
+          <t>Menteri PPN: Pengembangan singkong di Indonesia miliki prospek besar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:59:47 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:59 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Banyumas, Jawa Tengah, terus mengupayakan keberlanjutan operasional Bus Buy The Service (BTS) ...</t>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680519/pemkab-banyumas-upayakan-operasional-trans-banyumas-tetap-berlanjut</t>
+          <t>https://www.antaranews.com/berita/5680521/menteri-ppn-pengembangan-singkong-di-indonesia-miliki-prospek-besar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001093491.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/PPN-bappenas-lampung.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -900,28 +900,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KAI Layani 13.920 Ton Pupuk hingga Juli 2026, Perkuat Rantai Pasok Pertanian dan Ketahanan Pangan</t>
+          <t>Waspadai penyakit saat musim kemarau</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:59:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat perannya dalam rantai pasok pertanian nasional melalui pelayanan ...</t>
+          <t>Udara panas dan kekeringan saat musim kemarau memicu penyebaran sejumlah penyakit yang dapat membahayakan kesehatan. ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680516/kai-layani-13920-ton-pupuk-hingga-juli-2026-perkuat-rantai-pasok-pertanian-dan-ketahanan-pangan</t>
+          <t>https://www.antaranews.com/infografik/5680467/waspadai-penyakit-saat-musim-kemarau</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.38.20.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260805-Waspadai-penyakit-saat-musim-kemarau_1.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -938,28 +938,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pulau Untung Jawa gelar lomba meriahkan HUT Kemerdekaan RI</t>
+          <t>Pemkab Banyumas upayakan operasional Trans Banyumas tetap berlanjut</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:54:56 +0700</t>
+          <t>Wed, 05 Aug 2026 11:59:47 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pemerintah Kelurahan Pulau Untung Jawa resmi membuka rangkaian perlombaan dalam rangka memeriahkan Hari Ulang Tahun ...</t>
+          <t>Pemerintah Kabupaten Banyumas, Jawa Tengah, terus mengupayakan keberlanjutan operasional Bus Buy The Service (BTS) ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680512/pulau-untung-jawa-gelar-lomba-meriahkan-hut-kemerdekaan-ri</t>
+          <t>https://www.antaranews.com/berita/5680519/pemkab-banyumas-upayakan-operasional-trans-banyumas-tetap-berlanjut</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a8ea0e8e-b465-4832-9dee-22d911db4b0e.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001093491.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -976,28 +976,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pemprov Papua bukukan transaksi UMK 50,65 persen melalui e-Katalog</t>
+          <t>KAI Layani 13.920 Ton Pupuk hingga Juli 2026, Perkuat Rantai Pasok Pertanian dan Ketahanan Pangan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:54:36 +0700</t>
+          <t>Wed, 05 Aug 2026 11:59:00 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Papua melalui Biro Pengadaan Barang dan Jasa (BPBJ) setempat membukukan nilai transaksi Usaha ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat perannya dalam rantai pasok pertanian nasional melalui pelayanan ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680509/pemprov-papua-bukukan-transaksi-umk-5065-persen-melalui-e-katalog</t>
+          <t>https://www.antaranews.com/berita/5680516/kai-layani-13920-ton-pupuk-hingga-juli-2026-perkuat-rantai-pasok-pertanian-dan-ketahanan-pangan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002065915.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.38.20.jpeg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1014,28 +1014,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5 tips positive parenting agar anak percaya diri</t>
+          <t>Pulau Untung Jawa gelar lomba meriahkan HUT Kemerdekaan RI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:53:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:54:56 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pola asuh positif atau positive parenting dinilai dapat membantu anak tumbuh dengan rasa aman, percaya diri, dan mampu ...</t>
+          <t>Pemerintah Kelurahan Pulau Untung Jawa resmi membuka rangkaian perlombaan dalam rangka memeriahkan Hari Ulang Tahun ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680507/5-tips-positive-parenting-agar-anak-percaya-diri</t>
+          <t>https://www.antaranews.com/berita/5680512/pulau-untung-jawa-gelar-lomba-meriahkan-hut-kemerdekaan-ri</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/02/11/pexels-emma-bauso-2253879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a8ea0e8e-b465-4832-9dee-22d911db4b0e.jpeg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1052,28 +1052,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AS cabut visa Dubes Brasil di tengah perselisihan diplomatik</t>
+          <t>Pemprov Papua bukukan transaksi UMK 50,65 persen melalui e-Katalog</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:53:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:54:36 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pemerintah Amerika Serikat (AS) mencabut visa Duta Besar Brasil untuk Mario Luiza Ribeiro Viotti memperpanjang ...</t>
+          <t>Pemerintah Provinsi Papua melalui Biro Pengadaan Barang dan Jasa (BPBJ) setempat membukukan nilai transaksi Usaha ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680504/as-cabut-visa-dubes-brasil-di-tengah-perselisihan-diplomatik</t>
+          <t>https://www.antaranews.com/berita/5680509/pemprov-papua-bukukan-transaksi-umk-5065-persen-melalui-e-katalog</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000005_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002065915.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1090,28 +1090,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Customer Focus, KAI Libatkan Suara Pelanggan untuk Tingkatkan Layanan; CSI Semester I 2026 Capai 4,53</t>
+          <t>5 tips positive parenting agar anak percaya diri</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:51:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:53:39 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat kualitas pelayanan dengan menempatkan pelanggan sebagai pusat ...</t>
+          <t>Pola asuh positif atau positive parenting dinilai dapat membantu anak tumbuh dengan rasa aman, percaya diri, dan mampu ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680503/customer-focus-kai-libatkan-suara-pelanggan-untuk-tingkatkan-layanan-csi-semester-i-2026-capai-453</t>
+          <t>https://www.antaranews.com/berita/5680507/5-tips-positive-parenting-agar-anak-percaya-diri</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.27.26.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/11/pexels-emma-bauso-2253879.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1128,28 +1128,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POCO M8 Power hadir dengan Snapdragon 4 Gen 4 dan baterai 8.000 mAh</t>
+          <t>AS cabut visa Dubes Brasil di tengah perselisihan diplomatik</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:50:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:53:27 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ponsel POCO M8 Power, model keempat dalam seri POCO M8 yang diperkenalkan di pasar India, hadir dengan chip Snapdragon ...</t>
+          <t>Pemerintah Amerika Serikat (AS) mencabut visa Duta Besar Brasil untuk Mario Luiza Ribeiro Viotti memperpanjang ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680499/poco-m8-power-hadir-dengan-snapdragon-4-gen-4-dan-baterai-8000-mah</t>
+          <t>https://www.antaranews.com/berita/5680504/as-cabut-visa-dubes-brasil-di-tengah-perselisihan-diplomatik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_111842114.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000005_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>China luncurkan standar keselamatan sistem kemudi otonom</t>
+          <t>Customer Focus, KAI Libatkan Suara Pelanggan untuk Tingkatkan Layanan; CSI Semester I 2026 Capai 4,53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:48:26 +0700</t>
+          <t>Wed, 05 Aug 2026 11:51:39 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>China meluncurkan standar nasional wajib mengenai persyaratan keselamatan bagi sistem kemudi otonom, demikian diumumkan ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat kualitas pelayanan dengan menempatkan pelanggan sebagai pusat ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5680496/china-luncurkan-standar-keselamatan-sistem-kemudi-otonom</t>
+          <t>https://www.antaranews.com/berita/5680503/customer-focus-kai-libatkan-suara-pelanggan-untuk-tingkatkan-layanan-csi-semester-i-2026-capai-453</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000002_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.27.26.jpeg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1204,28 +1204,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gelombang panas keempat tahun ini di Italia picu respons darurat</t>
+          <t>POCO M8 Power hadir dengan Snapdragon 4 Gen 4 dan baterai 8.000 mAh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:45:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:50:39 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Italia sedang menghadapi gelombang panas besar keempat pada musim panas tahun ini, dengan suhu di sejumlah wilayah ...</t>
+          <t>Ponsel POCO M8 Power, model keempat dalam seri POCO M8 yang diperkenalkan di pasar India, hadir dengan chip Snapdragon ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680493/gelombang-panas-keempat-tahun-ini-di-italia-picu-respons-darurat</t>
+          <t>https://www.antaranews.com/berita/5680499/poco-m8-power-hadir-dengan-snapdragon-4-gen-4-dan-baterai-8000-mah</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000004_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_111842114.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1242,28 +1242,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kaltara tawarkan peluang investasi strategis kepada belasan duta besar</t>
+          <t>China luncurkan standar keselamatan sistem kemudi otonom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:44:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:48:26 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gubernur Kalimantan Utara (Kaltara) Zainal A. Paliwang menawarkan berbagai peluang investasi strategis di hadapan ...</t>
+          <t>China meluncurkan standar nasional wajib mengenai persyaratan keselamatan bagi sistem kemudi otonom, demikian diumumkan ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680492/kaltara-tawarkan-peluang-investasi-strategis-kepada-belasan-duta-besar</t>
+          <t>https://otomotif.antaranews.com/berita/5680496/china-luncurkan-standar-keselamatan-sistem-kemudi-otonom</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000575462.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000002_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1280,28 +1280,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tenaga ahli usulkan kejahatan lingkungan masuk RUU Perampasan Aset</t>
+          <t>Gelombang panas keempat tahun ini di Italia picu respons darurat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:11 +0700</t>
+          <t>Wed, 05 Aug 2026 11:45:01 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenaga Ahli Menteri Lingkungan Hidup Bidang Advokasi dan Penguatan Partisipasi Publik Yudi Syamhudi Suyuti mengusulkan ...</t>
+          <t>Italia sedang menghadapi gelombang panas besar keempat pada musim panas tahun ini, dengan suhu di sejumlah wilayah ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680488/tenaga-ahli-usulkan-kejahatan-lingkungan-masuk-ruu-perampasan-aset</t>
+          <t>https://www.antaranews.com/berita/5680493/gelombang-panas-keempat-tahun-ini-di-italia-picu-respons-darurat</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/IMG_20260420_115241_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000004_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1318,28 +1318,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemendukbangga perkuat peran keluarga wujudkan ruang aman bagi anak</t>
+          <t>Kaltara tawarkan peluang investasi strategis kepada belasan duta besar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:44:18 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN terus memperkuat peran keluarga sebagai ...</t>
+          <t>Gubernur Kalimantan Utara (Kaltara) Zainal A. Paliwang menawarkan berbagai peluang investasi strategis di hadapan ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680484/kemendukbangga-perkuat-peran-keluarga-wujudkan-ruang-aman-bagi-anak</t>
+          <t>https://www.antaranews.com/berita/5680492/kaltara-tawarkan-peluang-investasi-strategis-kepada-belasan-duta-besar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-7.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000575462.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1356,28 +1356,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Panas ekstrem surutkan air Sungai Danube, ganggu pengiriman kargo</t>
+          <t>Tenaga ahli usulkan kejahatan lingkungan masuk RUU Perampasan Aset</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:42:28 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:11 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pemerintah Austria menyatakan pengiriman kargo di sepanjang Sungai Danube yang melintasi wilayah negara itu nyaris ...</t>
+          <t>Tenaga Ahli Menteri Lingkungan Hidup Bidang Advokasi dan Penguatan Partisipasi Publik Yudi Syamhudi Suyuti mengusulkan ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680483/panas-ekstrem-surutkan-air-sungai-danube-ganggu-pengiriman-kargo</t>
+          <t>https://www.antaranews.com/berita/5680488/tenaga-ahli-usulkan-kejahatan-lingkungan-masuk-ruu-perampasan-aset</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/CmxztpE000018_20260620_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/IMG_20260420_115241_1.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AS cabut visa dubes Brasil karena tolak calon dubes usulan Trump</t>
+          <t>Kemendukbangga perkuat peran keluarga wujudkan ruang aman bagi anak</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:41:05 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:01 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amerika Serikat mencabut visa Duta Besar Brasil untuk Washington setelah pemerintah Brasil belum memberikan persetujuan ...</t>
+          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN terus memperkuat peran keluarga sebagai ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680481/as-cabut-visa-dubes-brasil-karena-tolak-calon-dubes-usulan-trump</t>
+          <t>https://www.antaranews.com/berita/5680484/kemendukbangga-perkuat-peran-keluarga-wujudkan-ruang-aman-bagi-anak</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-7.jpeg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1432,28 +1432,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pertamina Patra Niaga menghadirkan kompetisi masak nasional BGCC 2026</t>
+          <t>Panas ekstrem surutkan air Sungai Danube, ganggu pengiriman kargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:40:14 +0700</t>
+          <t>Wed, 05 Aug 2026 11:42:28 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PT Pertamina Patra Niaga menghadirkan kompetisi memasak tingkat nasional Bright Gas Cooking Competition (BGCC) 2026 ...</t>
+          <t>Pemerintah Austria menyatakan pengiriman kargo di sepanjang Sungai Danube yang melintasi wilayah negara itu nyaris ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680477/pertamina-patra-niaga-menghadirkan-kompetisi-masak-nasional-bgcc-2026</t>
+          <t>https://www.antaranews.com/berita/5680483/panas-ekstrem-surutkan-air-sungai-danube-ganggu-pengiriman-kargo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000402887.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/CmxztpE000018_20260620_PEPFN0A001.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1470,28 +1470,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bappenas: Indonesia punya modal kuat kembangkan ekosistem tokenisasi</t>
+          <t>AS cabut visa dubes Brasil karena tolak calon dubes usulan Trump</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:38:07 +0700</t>
+          <t>Wed, 05 Aug 2026 11:41:05 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+          <t>Amerika Serikat mencabut visa Duta Besar Brasil untuk Washington setelah pemerintah Brasil belum memberikan persetujuan ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680475/bappenas-indonesia-punya-modal-kuat-kembangkan-ekosistem-tokenisasi</t>
+          <t>https://www.antaranews.com/berita/5680481/as-cabut-visa-dubes-brasil-karena-tolak-calon-dubes-usulan-trump</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bappenas-Tokenisasi.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1508,28 +1508,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kimia Farma bukukan laba bersih "unaudited" Rp54,07 miliar</t>
+          <t>Pertamina Patra Niaga menghadirkan kompetisi masak nasional BGCC 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:38 +0700</t>
+          <t>Wed, 05 Aug 2026 11:40:14 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PT Kimia Farma (Persero) Tbk (KAEF) membukukan laba bersih unaudited sebesar Rp54,07 miliar pada semester ...</t>
+          <t>PT Pertamina Patra Niaga menghadirkan kompetisi memasak tingkat nasional Bright Gas Cooking Competition (BGCC) 2026 ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680471/kimia-farma-bukukan-laba-bersih-unaudited-rp5407-miliar</t>
+          <t>https://www.antaranews.com/berita/5680477/pertamina-patra-niaga-menghadirkan-kompetisi-masak-nasional-bgcc-2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/DSC_0637.JPG-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000402887.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1546,28 +1546,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rutinitas malam yang bisa bantu kurangi risiko perut kembung</t>
+          <t>Bappenas: Indonesia punya modal kuat kembangkan ekosistem tokenisasi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:36:55 +0700</t>
+          <t>Wed, 05 Aug 2026 11:38:07 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ahli gizi Ava Safir menyampaikan bahwa perut bisa terasa lebih penuh menjelang malam hari karena saluran ...</t>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680463/rutinitas-malam-yang-bisa-bantu-kurangi-risiko-perut-kembung</t>
+          <t>https://www.antaranews.com/berita/5680475/bappenas-indonesia-punya-modal-kuat-kembangkan-ekosistem-tokenisasi</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/07/02/kembung.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bappenas-Tokenisasi.jpeg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1584,28 +1584,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brasil turunkan tingkat hubungan diplomatik dengan Argentina</t>
+          <t>Kimia Farma bukukan laba bersih "unaudited" Rp54,07 miliar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:35:10 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:38 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brasil memutuskan untuk menurunkan tingkat hubungan diplomatiknya dengan Argentina menjadi hanya perwakilan diplomatik ...</t>
+          <t>PT Kimia Farma (Persero) Tbk (KAEF) membukukan laba bersih unaudited sebesar Rp54,07 miliar pada semester ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680460/brasil-turunkan-tingkat-hubungan-diplomatik-dengan-argentina</t>
+          <t>https://www.antaranews.com/berita/5680471/kimia-farma-bukukan-laba-bersih-unaudited-rp5407-miliar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/12/01/CjkinzN007014_20231201_CBMFN0A001_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/DSC_0637.JPG-1.jpeg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bea Cukai gagalkan penyeludupan Harley Davidson bekas asal China</t>
+          <t>Rutinitas malam yang bisa bantu kurangi risiko perut kembung</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:33:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:36:55 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok berhasil menggagalkan upaya penyelundupan barang impor ilegal berupa lima unit sepeda motor ...</t>
+          <t>Ahli gizi Ava Safir menyampaikan bahwa perut bisa terasa lebih penuh menjelang malam hari karena saluran ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680459/bea-cukai-gagalkan-penyeludupan-harley-davidson-bekas-asal-china</t>
+          <t>https://www.antaranews.com/berita/5680463/rutinitas-malam-yang-bisa-bantu-kurangi-risiko-perut-kembung</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_112229.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/02/kembung.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1660,28 +1660,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10 Kebiasaan sebelum tidur yang bisa tingkatkan kualitas istirahat</t>
+          <t>Brasil turunkan tingkat hubungan diplomatik dengan Argentina</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:31:46 +0700</t>
+          <t>Wed, 05 Aug 2026 11:35:10 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tidur yang berkualitas bukan hanya ditentukan oleh durasinya, tetapi juga oleh kebiasaan yang dilakukan sebelum ...</t>
+          <t>Brasil memutuskan untuk menurunkan tingkat hubungan diplomatiknya dengan Argentina menjadi hanya perwakilan diplomatik ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680455/10-kebiasaan-sebelum-tidur-yang-bisa-tingkatkan-kualitas-istirahat</t>
+          <t>https://www.antaranews.com/berita/5680460/brasil-turunkan-tingkat-hubungan-diplomatik-dengan-argentina</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/03/12/tidur.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/12/01/CjkinzN007014_20231201_CBMFN0A001_1.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1698,28 +1698,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mendag genjot perdagangan RI-Thailand dengan diversifikasi ekspor</t>
+          <t>Bea Cukai gagalkan penyeludupan Harley Davidson bekas asal China</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:21 +0700</t>
+          <t>Wed, 05 Aug 2026 11:33:25 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Menteri Perdagangan (Mendag) Budi Santoso menegaskan pemerintah terus mendorong penguatan perdagangan bilateral ...</t>
+          <t>Bea Cukai Tanjung Priok berhasil menggagalkan upaya penyelundupan barang impor ilegal berupa lima unit sepeda motor ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680453/mendag-genjot-perdagangan-ri-thailand-dengan-diversifikasi-ekspor</t>
+          <t>https://www.antaranews.com/berita/5680459/bea-cukai-gagalkan-penyeludupan-harley-davidson-bekas-asal-china</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0926.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_112229.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1736,28 +1736,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CENTCOM klaim telah kawal 1.000 kapal lewati Selat Hormuz</t>
+          <t>10 Kebiasaan sebelum tidur yang bisa tingkatkan kualitas istirahat</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:16 +0700</t>
+          <t>Wed, 05 Aug 2026 11:31:46 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Komando Pusat Amerika Serikat (CENTCOM) mengeklaim pihaknya telah membantu lebih dari 1.000 kapal komersial melintasi ...</t>
+          <t>Tidur yang berkualitas bukan hanya ditentukan oleh durasinya, tetapi juga oleh kebiasaan yang dilakukan sebelum ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680451/centcom-klaim-telah-kawal-1000-kapal-lewati-selat-hormuz</t>
+          <t>https://www.antaranews.com/berita/5680455/10-kebiasaan-sebelum-tidur-yang-bisa-tingkatkan-kualitas-istirahat</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_0df8b22d772e3fff389166ac7f3553b1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/12/tidur.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1774,28 +1774,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BPS: Ekonomi Indonesia tumbuh 5,29 persen pada triwulan II 2026</t>
+          <t>Mendag genjot perdagangan RI-Thailand dengan diversifikasi ekspor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:27:10 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:21 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia tumbuh 5,29 persen (year on year/yoy) pada triwulan II ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso menegaskan pemerintah terus mendorong penguatan perdagangan bilateral ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680447/bps-ekonomi-indonesia-tumbuh-529-persen-pada-triwulan-ii-2026</t>
+          <t>https://www.antaranews.com/berita/5680453/mendag-genjot-perdagangan-ri-thailand-dengan-diversifikasi-ekspor</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-10.58.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0926.jpeg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1812,28 +1812,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kuota undangan upacara HUT Ke-81 RI hari pertama langsung penuh</t>
+          <t>CENTCOM klaim telah kawal 1.000 kapal lewati Selat Hormuz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:25:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:16 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kuota pendaftaran undangan Upacara Peringatan HUT Ke-81 Kemerdekaan RI di Istana Merdeka untuk hari pertama, Rabu, ...</t>
+          <t>Komando Pusat Amerika Serikat (CENTCOM) mengeklaim pihaknya telah membantu lebih dari 1.000 kapal komersial melintasi ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680445/kuota-undangan-upacara-hut-ke-81-ri-hari-pertama-langsung-penuh</t>
+          <t>https://www.antaranews.com/berita/5680451/centcom-klaim-telah-kawal-1000-kapal-lewati-selat-hormuz</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000034647.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_0df8b22d772e3fff389166ac7f3553b1.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1850,28 +1850,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WHO sebut risiko penyebaran virus Bourbon di AS masih rendah</t>
+          <t>BPS: Ekonomi Indonesia tumbuh 5,29 persen pada triwulan II 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:24:48 +0700</t>
+          <t>Wed, 05 Aug 2026 11:27:10 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Organisasi Kesehatan Dunia (WHO) telah mengetahui adanya kasus infeksi virus Bourbon yang dilaporkan di Amerika Serikat ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia tumbuh 5,29 persen (year on year/yoy) pada triwulan II ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680441/who-sebut-risiko-penyebaran-virus-bourbon-di-as-masih-rendah</t>
+          <t>https://www.antaranews.com/berita/5680447/bps-ekonomi-indonesia-tumbuh-529-persen-pada-triwulan-ii-2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/07/22/reuters_cdc-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-10.58.55.jpeg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1888,28 +1888,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Menteri PKP: BTN salurkan KPR subsidi terbanyak hingga Juli 2026</t>
+          <t>Kuota undangan upacara HUT Ke-81 RI hari pertama langsung penuh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:24:28 +0700</t>
+          <t>Wed, 05 Aug 2026 11:25:27 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait mengatakan PT Bank Tabungan Negara (Persero) Tbk (BTN) ...</t>
+          <t>Kuota pendaftaran undangan Upacara Peringatan HUT Ke-81 Kemerdekaan RI di Istana Merdeka untuk hari pertama, Rabu, ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680437/menteri-pkp-btn-salurkan-kpr-subsidi-terbanyak-hingga-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5680445/kuota-undangan-upacara-hut-ke-81-ri-hari-pertama-langsung-penuh</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/percepatan-pembangunan-rumah-subsidi-2828057.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000034647.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1926,28 +1926,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Koster temui Gubernur DKI belajar soal pembiayaan inovatif</t>
+          <t>WHO sebut risiko penyebaran virus Bourbon di AS masih rendah</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:22:36 +0700</t>
+          <t>Wed, 05 Aug 2026 11:24:48 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Bali mempelajari skema pembiayaan inovatif dari Pemerintah Provinsi DKI Jakarta, termasuk ...</t>
+          <t>Organisasi Kesehatan Dunia (WHO) telah mengetahui adanya kasus infeksi virus Bourbon yang dilaporkan di Amerika Serikat ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680433/koster-temui-gubernur-dki-belajar-soal-pembiayaan-inovatif</t>
+          <t>https://www.antaranews.com/berita/5680441/who-sebut-risiko-penyebaran-virus-bourbon-di-as-masih-rendah</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/794ac169-206a-4fd7-a0f6-8e065b9d2615.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/07/22/reuters_cdc-1.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1964,28 +1964,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saudi, Qatar, Yordania berpeluang masuk jalur gas Eropa via Turki</t>
+          <t>Menteri PKP: BTN salurkan KPR subsidi terbanyak hingga Juli 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:16:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:24:28 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qatar, Arab Saudi, dan Yordania berpeluang menjadi bagian dari rute baru penyaluran gas alam menuju Turki dan ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait mengatakan PT Bank Tabungan Negara (Persero) Tbk (BTN) ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680431/saudi-qatar-yordania-berpeluang-masuk-jalur-gas-eropa-via-turki</t>
+          <t>https://www.antaranews.com/berita/5680437/menteri-pkp-btn-salurkan-kpr-subsidi-terbanyak-hingga-juli-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/percepatan-pembangunan-rumah-subsidi-2828057.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2002,28 +2002,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kronologi temuan mayat dalam karung di Depok hingga penangkapan pelaku</t>
+          <t>Koster temui Gubernur DKI belajar soal pembiayaan inovatif</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:15:54 +0700</t>
+          <t>Wed, 05 Aug 2026 11:22:36 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kasus penemuan mayat termutilasi yang terbungkus di dalam karung di kawasan Tanah Merah, Kelurahan Pancoran Mas, Kota ...</t>
+          <t>Pemerintah Provinsi Bali mempelajari skema pembiayaan inovatif dari Pemerintah Provinsi DKI Jakarta, termasuk ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680429/kronologi-temuan-mayat-dalam-karung-di-depok-hingga-penangkapan-pelaku</t>
+          <t>https://www.antaranews.com/berita/5680433/koster-temui-gubernur-dki-belajar-soal-pembiayaan-inovatif</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/794ac169-206a-4fd7-a0f6-8e065b9d2615.jpeg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2040,28 +2040,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Legislator: Sensus Ekonomi 2026 perkuat kebijakan UMKM</t>
+          <t>Saudi, Qatar, Yordania berpeluang masuk jalur gas Eropa via Turki</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
+          <t>Wed, 05 Aug 2026 11:16:25 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anggota Komisi X DPR RI Adela Kanasya Adies mengatakan Sensus Ekonomi 2026 akan menjadi dasar penyusunan kebijakan ...</t>
+          <t>Qatar, Arab Saudi, dan Yordania berpeluang menjadi bagian dari rute baru penyaluran gas alam menuju Turki dan ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680427/legislator-sensus-ekonomi-2026-perkuat-kebijakan-umkm</t>
+          <t>https://www.antaranews.com/berita/5680431/saudi-qatar-yordania-berpeluang-masuk-jalur-gas-eropa-via-turki</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001219476.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2078,28 +2078,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pendaftaran upacara HUT RI di Istana dibuka, ini dokumen yang wajib disiapkan</t>
+          <t>Kronologi temuan mayat dalam karung di Depok hingga penangkapan pelaku</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:15:54 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Badan Komunikasi Pemerintah (Bakom) RI menyarankan masyarakat menyiapkan seluruh dokumen persyaratan sebelum mendaftar ...</t>
+          <t>Kasus penemuan mayat termutilasi yang terbungkus di dalam karung di kawasan Tanah Merah, Kelurahan Pancoran Mas, Kota ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680423/pendaftaran-upacara-hut-ri-di-istana-dibuka-ini-dokumen-yang-wajib-disiapkan</t>
+          <t>https://www.antaranews.com/berita/5680429/kronologi-temuan-mayat-dalam-karung-di-depok-hingga-penangkapan-pelaku</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2116,28 +2116,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Survei Herbalife: Budaya "Wellness" Kian Menguat di Asia Pasifik, Empat dari Lima Konsumen Prioritaskan Kesehatan Holistik</t>
+          <t>Legislator: Sensus Ekonomi 2026 perkuat kebijakan UMKM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:12:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Budaya gaya hidup sehat (wellness) semakin mengakar di kawasan Asia Pasifik (APAC). Hal itu terungkap dalam survei ...</t>
+          <t>Anggota Komisi X DPR RI Adela Kanasya Adies mengatakan Sensus Ekonomi 2026 akan menjadi dasar penyusunan kebijakan ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680420/survei-herbalife-budaya-wellness-kian-menguat-di-asia-pasifik-empat-dari-lima-konsumen-prioritaskan-kesehatan-holistik</t>
+          <t>https://www.antaranews.com/berita/5680427/legislator-sensus-ekonomi-2026-perkuat-kebijakan-umkm</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Budaya-Wellness-Asia.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001219476.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2154,28 +2154,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Warga bentangkan bendera Merah Putih sepanjang 400 meter sambut HUT ke-81 RI di Tangerang</t>
+          <t>Pendaftaran upacara HUT RI di Istana dibuka, ini dokumen yang wajib disiapkan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:11:44 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:15 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Foto udara bendera Merah Putih membentang menutupi jalan di Perumahan Puri Dewata Indah, Cipondoh, Kota Tangerang, ...</t>
+          <t>Badan Komunikasi Pemerintah (Bakom) RI menyarankan masyarakat menyiapkan seluruh dokumen persyaratan sebelum mendaftar ...</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5680417/warga-bentangkan-bendera-merah-putih-sepanjang-400-meter-sambut-hut-ke-81-ri-di-tangerang</t>
+          <t>https://www.antaranews.com/berita/5680423/pendaftaran-upacara-hut-ri-di-istana-dibuka-ini-dokumen-yang-wajib-disiapkan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bendera-Merah-Putih-sepanjang-400-meter-di-Tangerang-482026-pma-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Irak akan bangun infrastruktur pipa minyak baru ke Turki dan Suriah</t>
+          <t>Survei Herbalife: Budaya "Wellness" Kian Menguat di Asia Pasifik, Empat dari Lima Konsumen Prioritaskan Kesehatan Holistik</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:11:24 +0700</t>
+          <t>Wed, 05 Aug 2026 11:12:18 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Irak berencana segera memulai pembangunan pipa minyak baru menuju Suriah dan Turki guna mendiversifikasi rute ekspor ...</t>
+          <t>Budaya gaya hidup sehat (wellness) semakin mengakar di kawasan Asia Pasifik (APAC). Hal itu terungkap dalam survei ...</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680415/irak-akan-bangun-infrastruktur-pipa-minyak-baru-ke-turki-dan-suriah</t>
+          <t>https://www.antaranews.com/berita/5680420/survei-herbalife-budaya-wellness-kian-menguat-di-asia-pasifik-empat-dari-lima-konsumen-prioritaskan-kesehatan-holistik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Budaya-Wellness-Asia.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pemprov DKI bekali warga Jakpus keterampilan berwirausaha</t>
+          <t>Warga bentangkan bendera Merah Putih sepanjang 400 meter sambut HUT ke-81 RI di Tangerang</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:08:43 +0700</t>
+          <t>Wed, 05 Aug 2026 11:11:44 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta membekali warga Jakarta Pusat (Jakpus) dengan keterampilan tata boga untuk ...</t>
+          <t>Foto udara bendera Merah Putih membentang menutupi jalan di Perumahan Puri Dewata Indah, Cipondoh, Kota Tangerang, ...</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680411/pemprov-dki-bekali-warga-jakpus-keterampilan-berwirausaha</t>
+          <t>https://www.antaranews.com/foto/5680417/warga-bentangkan-bendera-merah-putih-sepanjang-400-meter-sambut-hut-ke-81-ri-di-tangerang</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260731_152649.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bendera-Merah-Putih-sepanjang-400-meter-di-Tangerang-482026-pma-1.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2268,28 +2268,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KY tuntaskan wawancara 9 calon hakim agung kamar pidana</t>
+          <t>Irak akan bangun infrastruktur pipa minyak baru ke Turki dan Suriah</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:06:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:11:24 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Komisi Yudisial (KY) menuntaskan wawancara terhadap sembilan calon hakim agung kamar pidana dalam seleksi terbuka calon ...</t>
+          <t>Irak berencana segera memulai pembangunan pipa minyak baru menuju Suriah dan Turki guna mendiversifikasi rute ekspor ...</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680407/ky-tuntaskan-wawancara-9-calon-hakim-agung-kamar-pidana</t>
+          <t>https://www.antaranews.com/berita/5680415/irak-akan-bangun-infrastruktur-pipa-minyak-baru-ke-turki-dan-suriah</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001843500.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk_1.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Naik MRT Jakarta kini lebih praktis dengan BRI Kartu Kredit Contactless</t>
+          <t>Pemprov DKI bekali warga Jakpus keterampilan berwirausaha</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:04:09 +0700</t>
+          <t>Wed, 05 Aug 2026 11:08:43 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mobilitas masyarakat perkotaan yang dinamis menuntut efisiensi di berbagai lini kehidupan, termasuk dalam hal ...</t>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta membekali warga Jakarta Pusat (Jakpus) dengan keterampilan tata boga untuk ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680404/naik-mrt-jakarta-kini-lebih-praktis-dengan-bri-kartu-kredit-contactless</t>
+          <t>https://www.antaranews.com/berita/5680411/pemprov-dki-bekali-warga-jakpus-keterampilan-berwirausaha</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pembayaran-mrt-dengan-kartu-kredit-nirkontak-2829800.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260731_152649.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2344,28 +2344,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Slovakia: Uni Eropa harus proteksi perbatasan Schengen</t>
+          <t>KY tuntaskan wawancara 9 calon hakim agung kamar pidana</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:03:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:06:06 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Menteri Dalam Negeri (Mendagri) Slovakia, Matus Sutaj Estok mengatakan Uni Eropa harus memprioritaskan ...</t>
+          <t>Komisi Yudisial (KY) menuntaskan wawancara terhadap sembilan calon hakim agung kamar pidana dalam seleksi terbuka calon ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680400/slovakia-uni-eropa-harus-proteksi-perbatasan-schengen</t>
+          <t>https://www.antaranews.com/berita/5680407/ky-tuntaskan-wawancara-9-calon-hakim-agung-kamar-pidana</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_163e90d67c855177fcf9553fd9012181.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001843500.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2795,33 +2795,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hiburan</t>
+          <t>Humaniora</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Top 10 film Netflix Indonesia terpopuler Agustus 2026, wajib masuk watchlist</t>
+          <t>Cara daftar PIP 2026, lengkap syarat, besar bantuan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:03:43 +0700</t>
+          <t>Wed, 05 Aug 2026 12:18:05 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sejumlah film dari berbagai genre masuk daftar Top 10 Netflix Indonesia pada Agustus 2026. Mulai dari horor, aksi, ...</t>
+          <t>Program Indonesia Pintar (PIP) 2026 kembali menjadi salah satu bantuan pendidikan yang dinantikan peserta didik dari ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680239/top-10-film-netflix-indonesia-terpopuler-agustus-2026-wajib-masuk-watchlist</t>
+          <t>https://www.antaranews.com/berita/5680551/cara-daftar-pip-2026-lengkap-syarat-besar-bantuan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/12/20/Screenshot_2019-12-20-09-25-04-83-01-1024x683_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/pemberian-beasiswa-pip.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2833,33 +2833,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tekno</t>
+          <t>Hiburan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>iOS 27 kapan rilis? Ini daftar iPhone yang kebagian dan fitur barunya</t>
+          <t>Top 10 film Netflix Indonesia terpopuler Agustus 2026, wajib masuk watchlist</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:08:05 +0700</t>
+          <t>Wed, 05 Aug 2026 08:03:43 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Apple resmi memperkenalkan sederet fitur baru yang akan hadir melalui sistem operasi iOS 27. Pembaruan ini membawa ...</t>
+          <t>Sejumlah film dari berbagai genre masuk daftar Top 10 Netflix Indonesia pada Agustus 2026. Mulai dari horor, aksi, ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680241/ios-27-kapan-rilis-ini-daftar-iphone-yang-kebagian-dan-fitur-barunya</t>
+          <t>https://www.antaranews.com/berita/5680239/top-10-film-netflix-indonesia-terpopuler-agustus-2026-wajib-masuk-watchlist</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/conversation_fcthp95t7kqe_large_2x.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/12/20/Screenshot_2019-12-20-09-25-04-83-01-1024x683_1.jpeg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2871,38 +2871,38 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mahasiswa Makassar Diserang Busur Panah Usai Tegur Pemotor Kerap Geber Motor</t>
+          <t>iOS 27 kapan rilis? Ini daftar iPhone yang kebagian dan fitur barunya</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:05:59 +0700</t>
+          <t>Wed, 05 Aug 2026 08:08:05 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Polisi menangkap pria berinisial NS alias J (22) usai memanah seorang mahasiswa bernama Agus Wirakusuma (21) di Kota Makassar, Sulawesi Selatan (Sulsel).</t>
+          <t>Apple resmi memperkenalkan sederet fitur baru yang akan hadir melalui sistem operasi iOS 27. Pembaruan ini membawa ...</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605085/mahasiswa-makassar-diserang-busur-panah-usai-tegur-pemotor-kerap-geber-motor</t>
+          <t>https://www.antaranews.com/berita/5680241/ios-27-kapan-rilis-ini-daftar-iphone-yang-kebagian-dan-fitur-barunya</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/10/makassar_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/conversation_fcthp95t7kqe_large_2x.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
@@ -2914,28 +2914,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Golkar Jawab PDIP Soal Politik Bukan Cari Enak, Hormati Parpol Luar Pemerintah</t>
+          <t>KPK Ajukan Banding Vonis 2 Tahun Gubernur Riau Abdul Wahid</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:04:36 +0700</t>
+          <t>Wed, 05 Aug 2026 12:09:46 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waketum Golkar, Ahmad Doli, menegaskan partainya tak pernah jadi oposisi dan konsisten mendukung pembangunan. Golkar menghargai semua posisi partai politik.</t>
+          <t>KPK mengajukan banding atas vonis 2 tahun Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa lainnya.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605082/golkar-jawab-pdip-soal-politik-bukan-cari-enak-hormati-parpol-luar-pemerintah</t>
+          <t>https://news.detik.com/berita/d-8605098/kpk-ajukan-banding-vonis-2-tahun-gubernur-riau-abdul-wahid</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/17/waketum-partai-golkar-ahmad-doli-kurnia_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-2_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2952,28 +2952,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kronologi Kunaefi Dimutilasi Kenalan di Medsos hingga Pelaku Ditangkap</t>
+          <t>Jaksa Heran Nadiem Minta 14 Saksi Diperiksa Ulang di Sidang Banding</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:02:08 +0700</t>
+          <t>Wed, 05 Aug 2026 12:09:44 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Penemuan jasad mutilasi Kunaefi di Depok menggegerkan warga. Pelaku Saepul, kenalan di media sosial, ditangkap setelah membunuh dan memutilasi korban.</t>
+          <t>Nadiem meminta pemeriksaan ulang 14 orang saksi dan dua ahli dalam sidang banding. Jaksa heran dengan permintaan itu.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605079/kronologi-kunaefi-dimutilasi-kenalan-di-medsos-hingga-pelaku-ditangkap</t>
+          <t>https://news.detik.com/berita/d-8605097/jaksa-heran-nadiem-minta-14-saksi-diperiksa-ulang-di-sidang-banding</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/nadiem-ajukan-banding-minta-hakim-cermati-kejanggalan-persidangan-1785906053465_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2990,28 +2990,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bareskrim Limpahkan Tersangka Kasus Narkoba 'The Doctor' ke Kejari Jaksel</t>
+          <t>Mahasiswa Makassar Diserang Busur Panah Usai Tegur Pemotor Kerap Geber Motor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:56:39 +0700</t>
+          <t>Wed, 05 Aug 2026 12:05:59 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bareskrim melimpahkan tersangka kasus narkoba, Andre Fernando Tjandra alias Charlie alias 'The Doctor', ke Kejaksaan Negeri Jakarta Selatan.</t>
+          <t>Polisi menangkap pria berinisial NS alias J (22) usai memanah seorang mahasiswa bernama Agus Wirakusuma (21) di Kota Makassar, Sulawesi Selatan (Sulsel).</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605073/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel</t>
+          <t>https://news.detik.com/berita/d-8605085/mahasiswa-makassar-diserang-busur-panah-usai-tegur-pemotor-kerap-geber-motor</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel-dok-polri-1785905794036_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/10/makassar_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3028,28 +3028,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DPD RI Bangun Kantor di Serang Banten, Siap Tampung Aspirasi Warga</t>
+          <t>Golkar Jawab PDIP Soal Politik Bukan Cari Enak, Hormati Parpol Luar Pemerintah</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:55:56 +0700</t>
+          <t>Wed, 05 Aug 2026 12:04:36 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DPd RI akan membangun kantor perwakilan di Kota Serang, Banten. Kantor tersebut dibangun untuk mempermudah masyarakat Banten menyampaikan aspirasinya.</t>
+          <t>Waketum Golkar, Ahmad Doli, menegaskan partainya tak pernah jadi oposisi dan konsisten mendukung pembangunan. Golkar menghargai semua posisi partai politik.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605072/dpd-ri-bangun-kantor-di-serang-banten-siap-tampung-aspirasi-warga</t>
+          <t>https://news.detik.com/berita/d-8605082/golkar-jawab-pdip-soal-politik-bukan-cari-enak-hormati-parpol-luar-pemerintah</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-ri-sultan-najamudin-di-acara-groundbreaking-kantor-perwakilan-dpd-ri-di-kota-serang-ariefdetikcom-1785905595298_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/17/waketum-partai-golkar-ahmad-doli-kurnia_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3066,28 +3066,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jepang Perkuat Militernya, Adik Kim Jong Un Murka!</t>
+          <t>Kronologi Kunaefi Dimutilasi Kenalan di Medsos hingga Pelaku Ditangkap</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:49:16 +0700</t>
+          <t>Wed, 05 Aug 2026 12:02:08 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
+          <t>Penemuan jasad mutilasi Kunaefi di Depok menggegerkan warga. Pelaku Saepul, kenalan di media sosial, ditangkap setelah membunuh dan memutilasi korban.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8605067/jepang-perkuat-militernya-adik-kim-jong-un-murka</t>
+          <t>https://news.detik.com/berita/d-8605079/kronologi-kunaefi-dimutilasi-kenalan-di-medsos-hingga-pelaku-ditangkap</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/12/33bee726-0042-4c52-9a21-c328504ce2ff_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3104,28 +3104,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dalam Kontainer dari China</t>
+          <t>Bareskrim Limpahkan Tersangka Kasus Narkoba 'The Doctor' ke Kejari Jaksel</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:56:39 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok gagalkan penyelundupan sepeda motor Harley-Davidson bekas. Penindakan dilakukan berkat teknologi pemindaian dan analisis intelijen.</t>
+          <t>Bareskrim melimpahkan tersangka kasus narkoba, Andre Fernando Tjandra alias Charlie alias 'The Doctor', ke Kejaksaan Negeri Jakarta Selatan.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605050/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china</t>
+          <t>https://news.detik.com/berita/d-8605073/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china-1785904973977_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel-dok-polri-1785905794036_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3142,28 +3142,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gempa M 6,4 Guncang Pulau Karatung Sulut</t>
+          <t>DPD RI Bangun Kantor di Serang Banten, Siap Tampung Aspirasi Warga</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:03 +0700</t>
+          <t>Wed, 05 Aug 2026 11:55:56 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gempa bumi dengan kekuatan magnitudo (M) 6,4 mengguncang kawasan Pulau Karatung, Sulawesi Utara. Gempa tak berpotensi tsunami.</t>
+          <t>DPd RI akan membangun kantor perwakilan di Kota Serang, Banten. Kantor tersebut dibangun untuk mempermudah masyarakat Banten menyampaikan aspirasinya.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605028/gempa-m-6-4-guncang-pulau-karatung-sulut</t>
+          <t>https://news.detik.com/berita/d-8605072/dpd-ri-bangun-kantor-di-serang-banten-siap-tampung-aspirasi-warga</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-ri-sultan-najamudin-di-acara-groundbreaking-kantor-perwakilan-dpd-ri-di-kota-serang-ariefdetikcom-1785905595298_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Relawan SPPG di Kuningan Diseruduk Saat Cegah Babi Hutan Serang Anak-anak</t>
+          <t>Jepang Perkuat Militernya, Adik Kim Jong Un Murka!</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:49:16 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Video viral menunjukkan Anas, relawan SPPG, berjuang menahan babi hutan di Kuningan. Ia tersungkur dan terluka saat berupaya melindungi anak-anak.</t>
+          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605027/relawan-sppg-di-kuningan-diseruduk-saat-cegah-babi-hutan-serang-anak-anak</t>
+          <t>https://news.detik.com/internasional/d-8605067/jepang-perkuat-militernya-adik-kim-jong-un-murka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tangkapan-layar-babi-seruduk-warga-di-kuningan-1785814645532_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/12/33bee726-0042-4c52-9a21-c328504ce2ff_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Momen Haru Pasutri dan 2 Anak Bertemu Lagi Usai Lompat dari KM Mutiara Sentosa</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dalam Kontainer dari China</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:35:32 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:15 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kebakaran KM Mutiara Sentosa 2 di Sumenep sempat memisahkan satu keluarga. Setelah evakuasi, mereka akhirnya berkumpul kembali di RS PHC Surabaya.</t>
+          <t>Bea Cukai Tanjung Priok gagalkan penyelundupan sepeda motor Harley-Davidson bekas. Penindakan dilakukan berkat teknologi pemindaian dan analisis intelijen.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605021/momen-haru-pasutri-dan-2-anak-bertemu-lagi-usai-lompat-dari-km-mutiara-sentosa</t>
+          <t>https://news.detik.com/berita/d-8605050/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-terbakar-1785849470687_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china-1785904973977_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3256,28 +3256,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kunaefi Korban Mutilasi di Depok Sempat Dilaporkan Hilang oleh Istri</t>
+          <t>Gempa M 6,4 Guncang Pulau Karatung Sulut</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:42 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:03 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Polisi mengungkap kasus mutilasi di Depok. Korban Kunaefi ditemukan setelah dilaporkan hilang. Pelaku, Saepul, dikenal melalui media sosial.</t>
+          <t>Gempa bumi dengan kekuatan magnitudo (M) 6,4 mengguncang kawasan Pulau Karatung, Sulawesi Utara. Gempa tak berpotensi tsunami.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605002/kunaefi-korban-mutilasi-di-depok-sempat-dilaporkan-hilang-oleh-istri</t>
+          <t>https://news.detik.com/berita/d-8605028/gempa-m-6-4-guncang-pulau-karatung-sulut</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3294,28 +3294,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pria Tangerang Dipaksa Onani dan Direkam Bos, Video Disebar untuk Ancaman</t>
+          <t>Relawan SPPG di Kuningan Diseruduk Saat Cegah Babi Hutan Serang Anak-anak</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:23:58 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:00 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kasus pria dianiaya dan dilecehkan mencuat usai beredar video korban dalam kondisi terluka dan diduga sedang dipaksa masturbasi. Video itu direkam bos korban.</t>
+          <t>Video viral menunjukkan Anas, relawan SPPG, berjuang menahan babi hutan di Kuningan. Ia tersungkur dan terluka saat berupaya melindungi anak-anak.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604995/pria-tangerang-dipaksa-onani-dan-direkam-bos-video-disebar-untuk-ancaman</t>
+          <t>https://news.detik.com/berita/d-8605027/relawan-sppg-di-kuningan-diseruduk-saat-cegah-babi-hutan-serang-anak-anak</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tangkapan-layar-babi-seruduk-warga-di-kuningan-1785814645532_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Modus Adaptif Promosi Judi Online: Menunggangi Algoritma Konten Viral</t>
+          <t>Momen Haru Pasutri dan 2 Anak Bertemu Lagi Usai Lompat dari KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:20:04 +0700</t>
+          <t>Wed, 05 Aug 2026 11:35:32 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Spam judi online naik 128 persen di medsos. Algoritma yang mengutamakan keramaian interaksi ternyata tanpa sadar ikut menyuburkan penyebarannya.</t>
+          <t>Kebakaran KM Mutiara Sentosa 2 di Sumenep sempat memisahkan satu keluarga. Setelah evakuasi, mereka akhirnya berkumpul kembali di RS PHC Surabaya.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://news.detik.com/kolom/d-8604992/modus-adaptif-promosi-judi-online-menunggangi-algoritma-konten-viral</t>
+          <t>https://news.detik.com/berita/d-8605021/momen-haru-pasutri-dan-2-anak-bertemu-lagi-usai-lompat-dari-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/20/ilustrasi-judi-online-lagi_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-terbakar-1785849470687_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3370,28 +3370,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Trump Ancam Serang Iran Besar-besaran Jika Hormuz Tak Dibuka Segera</t>
+          <t>Kunaefi Korban Mutilasi di Depok Sempat Dilaporkan Hilang oleh Istri</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:17:29 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:42 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Donald Trump mengatakan bahwa Selat Hormuz akan dibuka segera. Trump mengancam bahwa Iran akan diserang besar-besaran jika selat itu tidak dibuka.</t>
+          <t>Polisi mengungkap kasus mutilasi di Depok. Korban Kunaefi ditemukan setelah dilaporkan hilang. Pelaku, Saepul, dikenal melalui media sosial.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604989/trump-ancam-serang-iran-besar-besaran-jika-hormuz-tak-dibuka-segera</t>
+          <t>https://news.detik.com/berita/d-8605002/kunaefi-korban-mutilasi-di-depok-sempat-dilaporkan-hilang-oleh-istri</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3408,28 +3408,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BNN Dorong Penguatan Resiliensi Generasi Muda Lewat Kuliah Umum</t>
+          <t>Pria Tangerang Dipaksa Onani dan Direkam Bos, Video Disebar untuk Ancaman</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:15:14 +0700</t>
+          <t>Wed, 05 Aug 2026 11:23:58 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BNN RI menggelar Kuliah Umum Nasional tentang resiliensi generasi muda menghadapi narkotika pada 6 Agustus 2026 di Universitas Majalengka.</t>
+          <t>Kasus pria dianiaya dan dilecehkan mencuat usai beredar video korban dalam kondisi terluka dan diduga sedang dipaksa masturbasi. Video itu direkam bos korban.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604985/bnn-dorong-penguatan-resiliensi-generasi-muda-lewat-kuliah-umum</t>
+          <t>https://news.detik.com/berita/d-8604995/pria-tangerang-dipaksa-onani-dan-direkam-bos-video-disebar-untuk-ancaman</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/promo-bnn-1785903275205_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3446,28 +3446,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Saepul Mutilasi Pria di Depok gegara Cekcok, Potongan Kaki Dibuang ke Kali</t>
+          <t>Modus Adaptif Promosi Judi Online: Menunggangi Algoritma Konten Viral</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
+          <t>Wed, 05 Aug 2026 11:20:04 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Polisi telah menangkap Saepul (26) yang diduga melakukan mutilasi terhadap pria bernama Kunaefi (51) di Pancoran Mas, Kota Depok.</t>
+          <t>Spam judi online naik 128 persen di medsos. Algoritma yang mengutamakan keramaian interaksi ternyata tanpa sadar ikut menyuburkan penyebarannya.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604983/saepul-mutilasi-pria-di-depok-gegara-cekcok-potongan-kaki-dibuang-ke-kali</t>
+          <t>https://news.detik.com/kolom/d-8604992/modus-adaptif-promosi-judi-online-menunggangi-algoritma-konten-viral</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/20/ilustrasi-judi-online-lagi_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3484,28 +3484,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pengusaha Singkawang Tewas Ditembak Pembunuh Bayaran, Dalangnya Adik Kandung</t>
+          <t>Trump Ancam Serang Iran Besar-besaran Jika Hormuz Tak Dibuka Segera</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:02:48 +0700</t>
+          <t>Wed, 05 Aug 2026 11:17:29 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Seorang pengusaha bernama Cung Su Liat alias Aliat (55) ditemukan tewas mengenaskan dengan luka tembak di halaman rumahnya Kota Singkawang, Kalimantan Barat.</t>
+          <t>Donald Trump mengatakan bahwa Selat Hormuz akan dibuka segera. Trump mengancam bahwa Iran akan diserang besar-besaran jika selat itu tidak dibuka.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604972/pengusaha-singkawang-tewas-ditembak-pembunuh-bayaran-dalangnya-adik-kandung</t>
+          <t>https://news.detik.com/internasional/d-8604989/trump-ancam-serang-iran-besar-besaran-jika-hormuz-tak-dibuka-segera</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eksekutor-penembak-pengusaha-di-singkawang-hingga-tewas-dok-resmob-polda-kalbar-1785844579501_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3522,28 +3522,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Terpeleset Saat Cari Ikan, Bocah 5 Tahun Tewas Terseret Arus Kali Ciliwung</t>
+          <t>BNN Dorong Penguatan Resiliensi Generasi Muda Lewat Kuliah Umum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:01:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:15:14 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bocah berusia 5 tahun berinisial S tewas setelah terseret arus Kali Ciliwung, Depok. Korban bersama dua temannya awalnya hendak mencari ikan di lokasi.</t>
+          <t>BNN RI menggelar Kuliah Umum Nasional tentang resiliensi generasi muda menghadapi narkotika pada 6 Agustus 2026 di Universitas Majalengka.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604971/terpeleset-saat-cari-ikan-bocah-5-tahun-tewas-terseret-arus-kali-ciliwung</t>
+          <t>https://news.detik.com/berita/d-8604985/bnn-dorong-penguatan-resiliensi-generasi-muda-lewat-kuliah-umum</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/ilustrasi-orang-tenggelam-1781518248434_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/promo-bnn-1785903275205_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3560,28 +3560,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pertahankan Opini WTP, Setjen MPR RI Perkuat Tata Kelola Keuangan</t>
+          <t>Saepul Mutilasi Pria di Depok gegara Cekcok, Potongan Kaki Dibuang ke Kali</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:49 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Setjen MPR RI mempertahankan opini WTP atas Laporan Keuangan 2025. Deputi Heri Herawan apresiasi transparansi dan akuntabilitas dalam pengelolaan keuangan.</t>
+          <t>Polisi telah menangkap Saepul (26) yang diduga melakukan mutilasi terhadap pria bernama Kunaefi (51) di Pancoran Mas, Kota Depok.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604969/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan</t>
+          <t>https://news.detik.com/berita/d-8604983/saepul-mutilasi-pria-di-depok-gegara-cekcok-potongan-kaki-dibuang-ke-kali</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan-1785902413926_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3598,28 +3598,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Korban Mutilasi di Depok Ternyata Dibunuh Pria Kenalan di Medsos</t>
+          <t>Pengusaha Singkawang Tewas Ditembak Pembunuh Bayaran, Dalangnya Adik Kandung</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:02:48 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya menangkap Saepul, pelaku mutilasi Kunaefi. Korban dan pelaku berkenalan lewat media sosial sebelum pertemuan berujung mutilasi.</t>
+          <t>Seorang pengusaha bernama Cung Su Liat alias Aliat (55) ditemukan tewas mengenaskan dengan luka tembak di halaman rumahnya Kota Singkawang, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604968/korban-mutilasi-di-depok-ternyata-dibunuh-pria-kenalan-di-medsos</t>
+          <t>https://news.detik.com/berita/d-8604972/pengusaha-singkawang-tewas-ditembak-pembunuh-bayaran-dalangnya-adik-kandung</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eksekutor-penembak-pengusaha-di-singkawang-hingga-tewas-dok-resmob-polda-kalbar-1785844579501_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3636,28 +3636,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Merah Putih Membelah Jalan Tangerang, Aksi Warga Sambut Kemerdekaan RI Bikin Takjub</t>
+          <t>Terpeleset Saat Cari Ikan, Bocah 5 Tahun Tewas Terseret Arus Kali Ciliwung</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:01:27 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Warga Tangerang membentangkan bendera Merah Putih sepanjang 400 meter di jalan perumahan untuk menyambut HUT ke-81 Kemerdekaan RI.</t>
+          <t>Bocah berusia 5 tahun berinisial S tewas setelah terseret arus Kali Ciliwung, Depok. Korban bersama dua temannya awalnya hendak mencari ikan di lokasi.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8604436/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub</t>
+          <t>https://news.detik.com/berita/d-8604971/terpeleset-saat-cari-ikan-bocah-5-tahun-tewas-terseret-arus-kali-ciliwung</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub-1785847891040_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/ilustrasi-orang-tenggelam-1781518248434_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3674,28 +3674,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ayah dan Paman Pemerkosa Gadis di Situbondo Divonis 20 Tahun Penjara</t>
+          <t>Pertahankan Opini WTP, Setjen MPR RI Perkuat Tata Kelola Keuangan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:58:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:49 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Majelis hakim Pengadilan Negeri Situbondo, Jawa Timur, menjatuhkan vonis masing-masing 20 tahun penjara kepada BH (42) dan BS (42).</t>
+          <t>Setjen MPR RI mempertahankan opini WTP atas Laporan Keuangan 2025. Deputi Heri Herawan apresiasi transparansi dan akuntabilitas dalam pengelolaan keuangan.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604966/ayah-dan-paman-pemerkosa-gadis-di-situbondo-divonis-20-tahun-penjara</t>
+          <t>https://news.detik.com/berita/d-8604969/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/04/04/2e7993e1-d03b-49c3-9f3d-8a913c8dc5d2_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan-1785902413926_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3712,28 +3712,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina Luka di Wajah dan Kepala Usai Diduga Dianiaya Pacar</t>
+          <t>Korban Mutilasi di Depok Ternyata Dibunuh Pria Kenalan di Medsos</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:57:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:27 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina diduga dianiaya kekasihnya, KB, di Jakarta Selatan. Ia mengalami luka di wajah dan kepala.</t>
+          <t>Polda Metro Jaya menangkap Saepul, pelaku mutilasi Kunaefi. Korban dan pelaku berkenalan lewat media sosial sebelum pertemuan berujung mutilasi.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604961/aktris-sali-irsalina-luka-di-wajah-dan-kepala-usai-diduga-dianiaya-pacar</t>
+          <t>https://news.detik.com/berita/d-8604968/korban-mutilasi-di-depok-ternyata-dibunuh-pria-kenalan-di-medsos</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/19/penganiayaan-mantan-pacar-di-gianyar_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3750,28 +3750,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Identitas Mayat Tanpa Kaki di Depok Terungkap, Namanya Kunaefi</t>
+          <t>Merah Putih Membelah Jalan Tangerang, Aksi Warga Sambut Kemerdekaan RI Bikin Takjub</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:56:09 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:06 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kasus mutilasi di Depok terungkap. Korban Kunaefi (51) ditemukan dalam karung. Pelaku, Saepul (26), ditangkap saat melarikan diri ke Pandeglang.</t>
+          <t>Warga Tangerang membentangkan bendera Merah Putih sepanjang 400 meter di jalan perumahan untuk menyambut HUT ke-81 Kemerdekaan RI.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604959/identitas-mayat-tanpa-kaki-di-depok-terungkap-namanya-kunaefi</t>
+          <t>https://news.detik.com/foto-news/d-8604436/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub-1785847891040_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3788,28 +3788,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Penjual Miras di Lokananta Gugat Pemkot Solo Usai Dirazia</t>
+          <t>Ayah dan Paman Pemerkosa Gadis di Situbondo Divonis 20 Tahun Penjara</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:53:36 +0700</t>
+          <t>Wed, 05 Aug 2026 10:58:57 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Manajemen kafe Ruang Bahagia menggugat Pemkot Solo setelah dirazia oleh Satpol PP.</t>
+          <t>Majelis hakim Pengadilan Negeri Situbondo, Jawa Timur, menjatuhkan vonis masing-masing 20 tahun penjara kepada BH (42) dan BS (42).</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604956/penjual-miras-di-lokananta-gugat-pemkot-solo-usai-dirazia</t>
+          <t>https://news.detik.com/berita/d-8604966/ayah-dan-paman-pemerkosa-gadis-di-situbondo-divonis-20-tahun-penjara</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sidang-di-pn-solo-1785834131308_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/04/04/2e7993e1-d03b-49c3-9f3d-8a913c8dc5d2_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3826,28 +3826,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ramai Kabar Amunisi AS Menipis Gegara Perang Iran, Trump Bilang Gini</t>
+          <t>Aktris Sali Irsalina Luka di Wajah dan Kepala Usai Diduga Dianiaya Pacar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:52:07 +0700</t>
+          <t>Wed, 05 Aug 2026 10:57:57 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pasokan amunisi AS dilaporkan semakin menipis hingga ke level yang mengkhawatirkan akibat perang Iran. Trump buka suara.</t>
+          <t>Aktris Sali Irsalina diduga dianiaya kekasihnya, KB, di Jakarta Selatan. Ia mengalami luka di wajah dan kepala.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604954/ramai-kabar-amunisi-as-menipis-gegara-perang-iran-trump-bilang-gini</t>
+          <t>https://news.detik.com/berita/d-8604961/aktris-sali-irsalina-luka-di-wajah-dan-kepala-usai-diduga-dianiaya-pacar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/29/44d7a464-752c-4519-91cd-6e13284a464c_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/19/penganiayaan-mantan-pacar-di-gianyar_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3864,28 +3864,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2 Truk Tabrakan di Gunungputri Bogor, Sopir Terjepit di Kabin Kemudi</t>
+          <t>Identitas Mayat Tanpa Kaki di Depok Terungkap, Namanya Kunaefi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:48:18 +0700</t>
+          <t>Wed, 05 Aug 2026 10:56:09 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dua truk terlibat kecelakaan di Jalan Raya Wanaherang, Bogor. Sopir truk mengalami luka ringan setelah terjepit di ruang kemudi dan dilarikan ke rumah sakit.</t>
+          <t>Kasus mutilasi di Depok terungkap. Korban Kunaefi (51) ditemukan dalam karung. Pelaku, Saepul (26), ditangkap saat melarikan diri ke Pandeglang.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604951/2-truk-tabrakan-di-gunungputri-bogor-sopir-terjepit-di-kabin-kemudi</t>
+          <t>https://news.detik.com/berita/d-8604959/identitas-mayat-tanpa-kaki-di-depok-terungkap-namanya-kunaefi</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3902,28 +3902,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pilu Pemuda Jabar Jadi Love Scammer di Kamboja: Tak Digaji-Dicambuk Sesama WNI</t>
+          <t>Penjual Miras di Lokananta Gugat Pemkot Solo Usai Dirazia</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:41:05 +0700</t>
+          <t>Wed, 05 Aug 2026 10:53:36 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pemuda asal Kecamatan Dayeuhkolot, Kabupaten Bandung, ini mengaku tidak digaji selama bekerja di sana hingga mendapatkan beragam penganiayaan fisik.</t>
+          <t>Manajemen kafe Ruang Bahagia menggugat Pemkot Solo setelah dirazia oleh Satpol PP.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604941/pilu-pemuda-jabar-jadi-love-scammer-di-kamboja-tak-digaji-dicambuk-sesama-wni</t>
+          <t>https://news.detik.com/berita/d-8604956/penjual-miras-di-lokananta-gugat-pemkot-solo-usai-dirazia</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/rizki-nur-fadhilah-20-saat-berbincang-di-kabupaten-bandung-1785833506651_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sidang-di-pn-solo-1785834131308_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Anggota DPRD Tangsel Ahmad Andi Wibowo Meninggal Akibat Kecelakaan di Cipali</t>
+          <t>Ramai Kabar Amunisi AS Menipis Gegara Perang Iran, Trump Bilang Gini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:40:01 +0700</t>
+          <t>Wed, 05 Aug 2026 10:52:07 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anggota DPRD Tangerang Selatan dari fraksi PKB, Ahmad Andi Wibowo, meninggal dunia. Ahmad Andi meninggal dunia akibat kecelakaan di Tol Cipali Km 72.</t>
+          <t>Pasokan amunisi AS dilaporkan semakin menipis hingga ke level yang mengkhawatirkan akibat perang Iran. Trump buka suara.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604940/anggota-dprd-tangsel-ahmad-andi-wibowo-meninggal-akibat-kecelakaan-di-cipali</t>
+          <t>https://news.detik.com/internasional/d-8604954/ramai-kabar-amunisi-as-menipis-gegara-perang-iran-trump-bilang-gini</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ahmad-andi-wibowo-dok-istimewa-1785901183190_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/29/44d7a464-752c-4519-91cd-6e13284a464c_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3978,28 +3978,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Proyek Jembatan Rusia-Korut Bikin Waswas Ukraina</t>
+          <t>2 Truk Tabrakan di Gunungputri Bogor, Sopir Terjepit di Kabin Kemudi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:37:24 +0700</t>
+          <t>Wed, 05 Aug 2026 10:48:18 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Di wilayah terpencil di perbatasan Rusia-Korut, kedua negara sedang membangun jembatan. Proyek ini membuat Ukraina, yang terletak sejauh 10.000 km, waswas.</t>
+          <t>Dua truk terlibat kecelakaan di Jalan Raya Wanaherang, Bogor. Sopir truk mengalami luka ringan setelah terjepit di ruang kemudi dan dilarikan ke rumah sakit.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://news.detik.com/dw/d-8604936/proyek-jembatan-rusia-korut-bikin-waswas-ukraina</t>
+          <t>https://news.detik.com/berita/d-8604951/2-truk-tabrakan-di-gunungputri-bogor-sopir-terjepit-di-kabin-kemudi</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kenapa-ukraina-waspadai-proyek-jembatan-rusia-korut-1785901044051.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4016,28 +4016,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Diduga Dianiaya Pacar, Aktris Sinetron Sali Irsalina Lapor Polisi</t>
+          <t>Pilu Pemuda Jabar Jadi Love Scammer di Kamboja: Tak Digaji-Dicambuk Sesama WNI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:33:20 +0700</t>
+          <t>Wed, 05 Aug 2026 10:41:05 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina melaporkan dugaan penganiayaan oleh kekasihnya ke Polres Metro Jakarta Selatan. Ia mengalami luka akibat kekerasan fisik.</t>
+          <t>Pemuda asal Kecamatan Dayeuhkolot, Kabupaten Bandung, ini mengaku tidak digaji selama bekerja di sana hingga mendapatkan beragam penganiayaan fisik.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604926/diduga-dianiaya-pacar-aktris-sinetron-sali-irsalina-lapor-polisi</t>
+          <t>https://news.detik.com/berita/d-8604941/pilu-pemuda-jabar-jadi-love-scammer-di-kamboja-tak-digaji-dicambuk-sesama-wni</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/11/ilustrasi-kekerasan-terhadap-perempuan-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/rizki-nur-fadhilah-20-saat-berbincang-di-kabupaten-bandung-1785833506651_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4054,28 +4054,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kapolda Sumsel Serahkan Penghargaan WBK &amp;amp; Pelayanan Prima kepada 11 Satuan</t>
+          <t>Anggota DPRD Tangsel Ahmad Andi Wibowo Meninggal Akibat Kecelakaan di Cipali</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:25:23 +0700</t>
+          <t>Wed, 05 Aug 2026 10:40:01 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kapolda Sumsel, Irjen Pol. Sandi Nugroho, menyerahkan penghargaan WBK dan Pelayanan Publik Prima kepada 11 satuan kerja.</t>
+          <t>Anggota DPRD Tangerang Selatan dari fraksi PKB, Ahmad Andi Wibowo, meninggal dunia. Ahmad Andi meninggal dunia akibat kecelakaan di Tol Cipali Km 72.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8604921/kapolda-sumsel-serahkan-penghargaan-wbk-pelayanan-prima-kepada-11-satuan</t>
+          <t>https://news.detik.com/berita/d-8604940/anggota-dprd-tangsel-ahmad-andi-wibowo-meninggal-akibat-kecelakaan-di-cipali</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polda-sumsel-1785900305377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ahmad-andi-wibowo-dok-istimewa-1785901183190_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4092,28 +4092,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kuda Pacu Pemenang Kejurnas Hangus Terbakar di KM Mutiara Sentosa</t>
+          <t>Proyek Jembatan Rusia-Korut Bikin Waswas Ukraina</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:23:20 +0700</t>
+          <t>Wed, 05 Aug 2026 10:37:24 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kuda pacu yang baru meraih juara nasional milik warga Kabupaten Jeneponto, Sulsel, ikut terbakar dalam insiden KM Mutiara Sentosa 2 di perairan utara Madura.</t>
+          <t>Di wilayah terpencil di perbatasan Rusia-Korut, kedua negara sedang membangun jembatan. Proyek ini membuat Ukraina, yang terletak sejauh 10.000 km, waswas.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604917/kuda-pacu-pemenang-kejurnas-hangus-terbakar-di-km-mutiara-sentosa</t>
+          <t>https://news.detik.com/dw/d-8604936/proyek-jembatan-rusia-korut-bikin-waswas-ukraina</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kenapa-ukraina-waspadai-proyek-jembatan-rusia-korut-1785901044051.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4130,28 +4130,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pria Ber-hoodie Pembakar Bendera Juga Sasar Bangunan di Bandung dan Cimahi</t>
+          <t>Diduga Dianiaya Pacar, Aktris Sinetron Sali Irsalina Lapor Polisi</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:19:45 +0700</t>
+          <t>Wed, 05 Aug 2026 10:33:20 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Heboh aksi pria membakar bendera Merah Putih di sebuah rumah di Maleber, Kecamatan Andir, Kota Bandung, Jabar. Pria itu diduga membakar bangunan di tempat lain.</t>
+          <t>Aktris Sali Irsalina melaporkan dugaan penganiayaan oleh kekasihnya ke Polres Metro Jakarta Selatan. Ia mengalami luka akibat kekerasan fisik.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604913/pria-ber-hoodie-pembakar-bendera-juga-sasar-bangunan-di-bandung-dan-cimahi</t>
+          <t>https://news.detik.com/berita/d-8604926/diduga-dianiaya-pacar-aktris-sinetron-sali-irsalina-lapor-polisi</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/viral-aksi-pembakaran-bendera-merah-putih-di-bandung-1785755169202_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/11/ilustrasi-kekerasan-terhadap-perempuan-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4168,28 +4168,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pelaku Mutilasi di Depok Ditangkap Saat Kabur ke Pandeglang</t>
+          <t>Kapolda Sumsel Serahkan Penghargaan WBK &amp;amp; Pelayanan Prima kepada 11 Satuan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:17:26 +0700</t>
+          <t>Wed, 05 Aug 2026 10:25:23 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tim Resmob Polda Metro Jaya menangkap pelaku mutilasi di Depok, berinisial SA, saat melarikan diri ke Banten. Jasad korban ditemukan di lahan kosong.</t>
+          <t>Kapolda Sumsel, Irjen Pol. Sandi Nugroho, menyerahkan penghargaan WBK dan Pelayanan Publik Prima kepada 11 satuan kerja.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604903/pelaku-mutilasi-di-depok-ditangkap-saat-kabur-ke-pandeglang</t>
+          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8604921/kapolda-sumsel-serahkan-penghargaan-wbk-pelayanan-prima-kepada-11-satuan</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polda-sumsel-1785900305377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4206,28 +4206,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Viral Sejumlah Pemotor Jatuh gegara Tetesan Air Lindi di Bantargebang</t>
+          <t>Kuda Pacu Pemenang Kejurnas Hangus Terbakar di KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:13:21 +0700</t>
+          <t>Wed, 05 Aug 2026 10:23:20 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sejumlah pemotor terjatuh di Jalan Siliwangi Pangkalan 5, Bantargebang, Kota Bekasi. Peristiwa itu diduga terjadi akibat jalan linci karena tetesan air lindi.</t>
+          <t>Kuda pacu yang baru meraih juara nasional milik warga Kabupaten Jeneponto, Sulsel, ikut terbakar dalam insiden KM Mutiara Sentosa 2 di perairan utara Madura.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604899/viral-sejumlah-pemotor-jatuh-gegara-tetesan-air-lindi-di-bantargebang</t>
+          <t>https://news.detik.com/berita/d-8604917/kuda-pacu-pemenang-kejurnas-hangus-terbakar-di-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sejumlah-pemotor-berjatuhan-di-bantargebang-kota-bekasi-akibat-tetesan-air-lindi-1785899556055_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4244,28 +4244,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Berkas Lengkap, 3 Tersangka Kasus Tambang Emas Ilegal Segera Disidang</t>
+          <t>Pria Ber-hoodie Pembakar Bendera Juga Sasar Bangunan di Bandung dan Cimahi</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:07:53 +0700</t>
+          <t>Wed, 05 Aug 2026 10:19:45 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Polisi menetapkan 5 tersangka dalam kasus tambang emas ilegal. Tiga berkas perkara telah lengkap dan siap disidang, sementara dua lainnya masih dalam proses.</t>
+          <t>Heboh aksi pria membakar bendera Merah Putih di sebuah rumah di Maleber, Kecamatan Andir, Kota Bandung, Jabar. Pria itu diduga membakar bangunan di tempat lain.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604893/berkas-lengkap-3-tersangka-kasus-tambang-emas-ilegal-segera-disidang</t>
+          <t>https://news.detik.com/berita/d-8604913/pria-ber-hoodie-pembakar-bendera-juga-sasar-bangunan-di-bandung-dan-cimahi</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-polri-bongkar-kasus-tambang-emas-ilegal-1785899230949_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/viral-aksi-pembakaran-bendera-merah-putih-di-bandung-1785755169202_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4282,28 +4282,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Resmob Polda Metro Jaya Tangkap Pelaku Mutilasi di Depok!</t>
+          <t>Pelaku Mutilasi di Depok Ditangkap Saat Kabur ke Pandeglang</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:06:11 +0700</t>
+          <t>Wed, 05 Aug 2026 10:17:26 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kasus mayat mutilasi di Pancoran Mas, Depok terungkap. Polisi telah menangkap pelaku, sementara motif pembunuhan masih didalami kepolisian.</t>
+          <t>Tim Resmob Polda Metro Jaya menangkap pelaku mutilasi di Depok, berinisial SA, saat melarikan diri ke Banten. Jasad korban ditemukan di lahan kosong.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604889/resmob-polda-metro-jaya-tangkap-pelaku-mutilasi-di-depok</t>
+          <t>https://news.detik.com/berita/d-8604903/pelaku-mutilasi-di-depok-ditangkap-saat-kabur-ke-pandeglang</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4320,28 +4320,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Air Embung Surut, Nasib Ratusan Hektare Sawah Indramayu di Ujung Ancaman</t>
+          <t>Viral Sejumlah Pemotor Jatuh gegara Tetesan Air Lindi di Bantargebang</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:00:59 +0700</t>
+          <t>Wed, 05 Aug 2026 10:13:21 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Embung irigasi Balongan, Indramayu, mengering akibat minim hujan. Dasar embung terlihat kering hingga menyisakan bangkai ikan.</t>
+          <t>Sejumlah pemotor terjatuh di Jalan Siliwangi Pangkalan 5, Bantargebang, Kota Bekasi. Peristiwa itu diduga terjadi akibat jalan linci karena tetesan air lindi.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8604424/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman</t>
+          <t>https://news.detik.com/berita/d-8604899/viral-sejumlah-pemotor-jatuh-gegara-tetesan-air-lindi-di-bantargebang</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman-1785847218259_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sejumlah-pemotor-berjatuhan-di-bantargebang-kota-bekasi-akibat-tetesan-air-lindi-1785899556055_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Daftar Upacara HUT ke-81 RI di Istana: Jadwal, Cara, Syarat</t>
+          <t>Berkas Lengkap, 3 Tersangka Kasus Tambang Emas Ilegal Segera Disidang</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:59:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:07:53 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pendaftaran upacara HUT ke-81 RI dibuka 5-7 Agustus 2026. Siapkan dokumen dan ikuti syarat untuk mendaftar secara gratis di Istana Merdeka.</t>
+          <t>Polisi menetapkan 5 tersangka dalam kasus tambang emas ilegal. Tiga berkas perkara telah lengkap dan siap disidang, sementara dua lainnya masih dalam proses.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604878/daftar-upacara-hut-ke-81-ri-di-istana-jadwal-cara-syarat</t>
+          <t>https://news.detik.com/berita/d-8604893/berkas-lengkap-3-tersangka-kasus-tambang-emas-ilegal-segera-disidang</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/17/momen-upacara-detik-detik-proklamasi-di-istana-merdeka-1755407430559_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-polri-bongkar-kasus-tambang-emas-ilegal-1785899230949_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4396,28 +4396,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kapal India Tenggelam Usai Diserang di Laut Merah, 14 ABK Selamat</t>
+          <t>Resmob Polda Metro Jaya Tangkap Pelaku Mutilasi di Depok!</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:57:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:06:11 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sebuah kapal komersial berbendera India tenggelam setelah dihantam serangan di Laut Merah. Untungnya, semua ABK berhasil diselamatkan.</t>
+          <t>Kasus mayat mutilasi di Pancoran Mas, Depok terungkap. Polisi telah menangkap pelaku, sementara motif pembunuhan masih didalami kepolisian.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604874/kapal-india-tenggelam-usai-diserang-di-laut-merah-14-abk-selamat</t>
+          <t>https://news.detik.com/berita/d-8604889/resmob-polda-metro-jaya-tangkap-pelaku-mutilasi-di-depok</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/iran-crisisyemen-red-sea-1784214791940_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4434,28 +4434,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mesin Mati Mendadak, Mobil Terbakar di Tol Jagorawi Arah Jakarta</t>
+          <t>Air Embung Surut, Nasib Ratusan Hektare Sawah Indramayu di Ujung Ancaman</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:52:13 +0700</t>
+          <t>Wed, 05 Aug 2026 10:00:59 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Satu unit mobil SUV terbakar di Km 43/100 Tol Jagorawi, Bogor Timur, Kota Bogor. Kebakaran usai mesin mobil mati dan muncul api dari bawah kap depan.</t>
+          <t>Embung irigasi Balongan, Indramayu, mengering akibat minim hujan. Dasar embung terlihat kering hingga menyisakan bangkai ikan.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604866/mesin-mati-mendadak-mobil-terbakar-di-tol-jagorawi-arah-jakarta</t>
+          <t>https://news.detik.com/foto-news/d-8604424/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satu-unit-mobil-suv-terbakar-di-km-43100-tol-jagorawi-bogor-timur-kota-bogor-dok-istimewa-1785898155496_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman-1785847218259_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4472,28 +4472,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kondisi Mayat Mutilasi di Depok: Tangan Terikat dan Leher Luka Sayat</t>
+          <t>Daftar Upacara HUT ke-81 RI di Istana: Jadwal, Cara, Syarat</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:42:22 +0700</t>
+          <t>Wed, 05 Aug 2026 09:59:39 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pihak kepolisian menyelidiki penemuan mayat mutilasi di Pancoran Mas, Depok. Korban ditemukan tanpa kaki, terikat, dan dalam kondisi mengenaskan.</t>
+          <t>Pendaftaran upacara HUT ke-81 RI dibuka 5-7 Agustus 2026. Siapkan dokumen dan ikuti syarat untuk mendaftar secara gratis di Istana Merdeka.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604858/kondisi-mayat-mutilasi-di-depok-tangan-terikat-dan-leher-luka-sayat</t>
+          <t>https://news.detik.com/berita/d-8604878/daftar-upacara-hut-ke-81-ri-di-istana-jadwal-cara-syarat</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/17/momen-upacara-detik-detik-proklamasi-di-istana-merdeka-1755407430559_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4510,28 +4510,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Trump Cabut Visa Duta Besar Brasil untuk AS, Ada Apa?</t>
+          <t>Kapal India Tenggelam Usai Diserang di Laut Merah, 14 ABK Selamat</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:34:55 +0700</t>
+          <t>Wed, 05 Aug 2026 09:57:39 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pemerintahan Trump mencabut visa DUbes Brasil untuk AS, Maria Luiz Ribeiro Viotti. Apa alasannya?</t>
+          <t>Sebuah kapal komersial berbendera India tenggelam setelah dihantam serangan di Laut Merah. Untungnya, semua ABK berhasil diselamatkan.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604850/trump-cabut-visa-duta-besar-brasil-untuk-as-ada-apa</t>
+          <t>https://news.detik.com/internasional/d-8604874/kapal-india-tenggelam-usai-diserang-di-laut-merah-14-abk-selamat</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dubes-brasil-untuk-as-maria-luiza-ribeiro-viotti-1785897254293_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/iran-crisisyemen-red-sea-1784214791940_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4548,28 +4548,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Misteri Mayat Mutilasi di Depok Dibuang 12 Hari Lalu</t>
+          <t>Mesin Mati Mendadak, Mobil Terbakar di Tol Jagorawi Arah Jakarta</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:26:42 +0700</t>
+          <t>Wed, 05 Aug 2026 09:52:13 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jasad pria mutilasi ditemukan di Pancoran Mas, Depok, setelah 12 hari. Identitas korban belum diketahui, polisi masih menyelidiki kasus ini.</t>
+          <t>Satu unit mobil SUV terbakar di Km 43/100 Tol Jagorawi, Bogor Timur, Kota Bogor. Kebakaran usai mesin mobil mati dan muncul api dari bawah kap depan.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604839/misteri-mayat-mutilasi-di-depok-dibuang-12-hari-lalu</t>
+          <t>https://news.detik.com/berita/d-8604866/mesin-mati-mendadak-mobil-terbakar-di-tol-jagorawi-arah-jakarta</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satu-unit-mobil-suv-terbakar-di-km-43100-tol-jagorawi-bogor-timur-kota-bogor-dok-istimewa-1785898155496_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4586,28 +4586,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RI Kecam Keras Israel Serang Gaza Lagi: Sengaja Hambat Peace Plan</t>
+          <t>Kondisi Mayat Mutilasi di Depok: Tangan Terikat dan Leher Luka Sayat</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:23:19 +0700</t>
+          <t>Wed, 05 Aug 2026 09:42:22 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Indonesia mengecam serangan Israel ke Gaza yang menghambat kesepakatan perdamaian. Kemlu mendesak Israel menghentikan serangan dan memenuhi komitmen perjanjian.</t>
+          <t>Pihak kepolisian menyelidiki penemuan mayat mutilasi di Pancoran Mas, Depok. Korban ditemukan tanpa kaki, terikat, dan dalam kondisi mengenaskan.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604835/ri-kecam-keras-israel-serang-gaza-lagi-sengaja-hambat-peace-plan</t>
+          <t>https://news.detik.com/berita/d-8604858/kondisi-mayat-mutilasi-di-depok-tangan-terikat-dan-leher-luka-sayat</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/09/11/gedung-pancasila-di-kemlu_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4624,28 +4624,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Siap-siap War! Tiket Upacara HUT ke-81 RI di Istana Dibuka Hari Ini Pukul 10.00</t>
+          <t>Trump Cabut Visa Duta Besar Brasil untuk AS, Ada Apa?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:21:08 +0700</t>
+          <t>Wed, 05 Aug 2026 09:34:55 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pemerintah sudah membuka pendaftaran upacara HUT ke-81 RI di Istana Merdeka Jakarta. Siap-siap war!</t>
+          <t>Pemerintahan Trump mencabut visa DUbes Brasil untuk AS, Maria Luiz Ribeiro Viotti. Apa alasannya?</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604828/siap-siap-war-tiket-upacara-hut-ke-81-ri-di-istana-dibuka-hari-ini-pukul-10-00</t>
+          <t>https://news.detik.com/internasional/d-8604850/trump-cabut-visa-duta-besar-brasil-untuk-as-ada-apa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/01/31/85d6b0ca-c154-414b-a198-62b91ce4debc_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dubes-brasil-untuk-as-maria-luiza-ribeiro-viotti-1785897254293_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4662,28 +4662,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jakarta Selatan Diprediksi Hujan Ringan Sore Ini</t>
+          <t>Misteri Mayat Mutilasi di Depok Dibuang 12 Hari Lalu</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:56:17 +0700</t>
+          <t>Wed, 05 Aug 2026 09:26:42 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BMKG mengungkap sebagian wilayah di Jakarta Selatan berpotensi hujan ringan hari ini.</t>
+          <t>Jasad pria mutilasi ditemukan di Pancoran Mas, Depok, setelah 12 hari. Identitas korban belum diketahui, polisi masih menyelidiki kasus ini.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604809/jakarta-selatan-diprediksi-hujan-ringan-sore-ini</t>
+          <t>https://news.detik.com/berita/d-8604839/misteri-mayat-mutilasi-di-depok-dibuang-12-hari-lalu</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/30/ilustrasi-hujan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4700,28 +4700,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MKD DPR Gelar Rapim Pekan Depan Bahas Laporan 'Kayak Sirkus' ke Deddy Sitorus</t>
+          <t>RI Kecam Keras Israel Serang Gaza Lagi: Sengaja Hambat Peace Plan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:53:44 +0700</t>
+          <t>Wed, 05 Aug 2026 09:23:19 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mahkamah Kehormatan Dewan DPR RI akan rapat menindaklanjuti laporan wartawan terhadap Deddy Sitorus.</t>
+          <t>Indonesia mengecam serangan Israel ke Gaza yang menghambat kesepakatan perdamaian. Kemlu mendesak Israel menghentikan serangan dan memenuhi komitmen perjanjian.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604811/mkd-dpr-gelar-rapim-pekan-depan-bahas-laporan-kayak-sirkus-ke-deddy-sitorus</t>
+          <t>https://news.detik.com/berita/d-8604835/ri-kecam-keras-israel-serang-gaza-lagi-sengaja-hambat-peace-plan</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mkd-1785865852673_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/09/11/gedung-pancasila-di-kemlu_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4738,28 +4738,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mendagri Wanti-wanti Kepala Daerah Jaga Integritas demi Cegah Korupsi</t>
+          <t>Siap-siap War! Tiket Upacara HUT ke-81 RI di Istana Dibuka Hari Ini Pukul 10.00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:51:47 +0700</t>
+          <t>Wed, 05 Aug 2026 09:21:08 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mendagri Tito Karnavian menekankan pentingnya integritas kepala daerah dalam mencegah korupsi. Rakor di Surabaya bertujuan memperkuat tata kelola pemerintahan.</t>
+          <t>Pemerintah sudah membuka pendaftaran upacara HUT ke-81 RI di Istana Merdeka Jakarta. Siap-siap war!</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604793/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi</t>
+          <t>https://news.detik.com/berita/d-8604828/siap-siap-war-tiket-upacara-hut-ke-81-ri-di-istana-dibuka-hari-ini-pukul-10-00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/01/31/85d6b0ca-c154-414b-a198-62b91ce4debc_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4776,28 +4776,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LRT Dukung Pramono Hubungkan 2 JPO Viral Dekat tapi Tak Tersambung di Rasuna</t>
+          <t>Jakarta Selatan Diprediksi Hujan Ringan Sore Ini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:45:13 +0700</t>
+          <t>Wed, 05 Aug 2026 08:56:17 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gubernur DKI Pramono berjanji menyambungkan dua JPO yang viral di Jalan HR Rasuna Said. LRT Jabodebek siap berkoordinasi.</t>
+          <t>BMKG mengungkap sebagian wilayah di Jakarta Selatan berpotensi hujan ringan hari ini.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604779/lrt-dukung-pramono-hubungkan-2-jpo-viral-dekat-tapi-tak-tersambung-di-rasuna</t>
+          <t>https://news.detik.com/berita/d-8604809/jakarta-selatan-diprediksi-hujan-ringan-sore-ini</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313180_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/30/ilustrasi-hujan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4814,28 +4814,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Komisi V DPR Bakal Panggil Kemenhub Buntut Kebakaran KMP Mutiara Sentosa</t>
+          <t>MKD DPR Gelar Rapim Pekan Depan Bahas Laporan 'Kayak Sirkus' ke Deddy Sitorus</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:35:39 +0700</t>
+          <t>Wed, 05 Aug 2026 08:53:44 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Komisi V DPR RI akan memanggil Kemenhub terkait kebakaran KMP Mutiara Sentosa 2. Rapat dengan Kemenhub digelar seusai reses DPR RI.</t>
+          <t>Mahkamah Kehormatan Dewan DPR RI akan rapat menindaklanjuti laporan wartawan terhadap Deddy Sitorus.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604773/komisi-v-dpr-bakal-panggil-kemenhub-buntut-kebakaran-kmp-mutiara-sentosa</t>
+          <t>https://news.detik.com/berita/d-8604811/mkd-dpr-gelar-rapim-pekan-depan-bahas-laporan-kayak-sirkus-ke-deddy-sitorus</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mkd-1785865852673_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4852,28 +4852,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jelang Kunjungan Trump, Pria Bersenjata Ditangkap di Lapangan Golf Los Angeles</t>
+          <t>Mendagri Wanti-wanti Kepala Daerah Jaga Integritas demi Cegah Korupsi</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:34:23 +0700</t>
+          <t>Wed, 05 Aug 2026 08:51:47 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Seorang pria bersenjata ditangkap di lapangan golf Trump di LA, dua hari sebelum kunjungannya. Penyelidik menemukan senjata dan catatan mencurigakan.</t>
+          <t>Mendagri Tito Karnavian menekankan pentingnya integritas kepala daerah dalam mencegah korupsi. Rakor di Surabaya bertujuan memperkuat tata kelola pemerintahan.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604771/jelang-kunjungan-trump-pria-bersenjata-ditangkap-di-lapangan-golf-los-angeles</t>
+          <t>https://news.detik.com/berita/d-8604793/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/trump-saat-berpidato-di-gedung-putih-pada-kamis-167-malam-1784277022942_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4890,28 +4890,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U-turn Depan Stasiun Depok Ditutup, Lalin Arah Jakarta Lancar Pagi Ini</t>
+          <t>LRT Dukung Pramono Hubungkan 2 JPO Viral Dekat tapi Tak Tersambung di Rasuna</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:43 +0700</t>
+          <t>Wed, 05 Aug 2026 08:45:13 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Satlantas Polres Metro Depok dan Dishub menutup U-turn di Jalan Kartini untuk mengurangi kemacetan. Penutupan berlaku pada jam sibuk, efektif mulai 3 Agustus.</t>
+          <t>Gubernur DKI Pramono berjanji menyambungkan dua JPO yang viral di Jalan HR Rasuna Said. LRT Jabodebek siap berkoordinasi.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604766/u-turn-depan-stasiun-depok-ditutup-lalin-arah-jakarta-lancar-pagi-ini</t>
+          <t>https://news.detik.com/berita/d-8604779/lrt-dukung-pramono-hubungkan-2-jpo-viral-dekat-tapi-tak-tersambung-di-rasuna</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/u-turn-putaran-balik-di-jalan-kartini-depok-ditutup-1785893424229_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313180_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sekda Konawe Selatan Tabrak Adik Saat Digerebek Bareng Selingkuhan di Mobil</t>
+          <t>Komisi V DPR Bakal Panggil Kemenhub Buntut Kebakaran KMP Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:40 +0700</t>
+          <t>Wed, 05 Aug 2026 08:35:39 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sekda Konawe Selatan Ichsan Porosi (56) menabrak adik kandungnya, Andriani Porosi alias AP (50), saat digerebek berduaan diduga bareng selingkuhan di mobil.</t>
+          <t>Komisi V DPR RI akan memanggil Kemenhub terkait kebakaran KMP Mutiara Sentosa 2. Rapat dengan Kemenhub digelar seusai reses DPR RI.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604765/sekda-konawe-selatan-tabrak-adik-saat-digerebek-bareng-selingkuhan-di-mobil</t>
+          <t>https://news.detik.com/berita/d-8604773/komisi-v-dpr-bakal-panggil-kemenhub-buntut-kebakaran-kmp-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4966,28 +4966,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Penjelasan BMKG soal Hujan di Jakarta Usai Berminggu-minggu Kering</t>
+          <t>Jelang Kunjungan Trump, Pria Bersenjata Ditangkap di Lapangan Golf Los Angeles</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:24:21 +0700</t>
+          <t>Wed, 05 Aug 2026 08:34:23 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hujan turun di Jakarta setelah kering berminggu-minggu. Ini penjelasan BMKG.</t>
+          <t>Seorang pria bersenjata ditangkap di lapangan golf Trump di LA, dua hari sebelum kunjungannya. Penyelidik menemukan senjata dan catatan mencurigakan.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604764/penjelasan-bmkg-soal-hujan-di-jakarta-usai-berminggu-minggu-kering</t>
+          <t>https://news.detik.com/internasional/d-8604771/jelang-kunjungan-trump-pria-bersenjata-ditangkap-di-lapangan-golf-los-angeles</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hujan-deras-guyur-jakarta-usai-berminggu-minggu-kering-1785846576327_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/trump-saat-berpidato-di-gedung-putih-pada-kamis-167-malam-1784277022942_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5004,28 +5004,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Puan Berduka KM Mutiara Terbakar: Keamanan Transportasi Laut RI Masih Minim</t>
+          <t>U-turn Depan Stasiun Depok Ditutup, Lalin Arah Jakarta Lancar Pagi Ini</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:15:49 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:43 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KM Mutiara Sentosa 2 terbakar di Madura, menewaskan lima orang. Puan Maharani soroti minimnya keamanan transportasi laut.</t>
+          <t>Satlantas Polres Metro Depok dan Dishub menutup U-turn di Jalan Kartini untuk mengurangi kemacetan. Penutupan berlaku pada jam sibuk, efektif mulai 3 Agustus.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604759/puan-berduka-km-mutiara-terbakar-keamanan-transportasi-laut-ri-masih-minim</t>
+          <t>https://news.detik.com/berita/d-8604766/u-turn-depan-stasiun-depok-ditutup-lalin-arah-jakarta-lancar-pagi-ini</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/puan-maharani-1777615358543_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/u-turn-putaran-balik-di-jalan-kartini-depok-ditutup-1785893424229_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5042,28 +5042,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Duduk Perkara Pria di Tangerang Dipaksa Masturbasi hingga Disiksa</t>
+          <t>Sekda Konawe Selatan Tabrak Adik Saat Digerebek Bareng Selingkuhan di Mobil</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:04:14 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:40 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Seorang pria diduga dianiaya bos dan rekan kerjanya di Kabupaten Tangerang, Banten. Korban juga diduga dipaksa masturbasi sambil menonton film porno.</t>
+          <t>Sekda Konawe Selatan Ichsan Porosi (56) menabrak adik kandungnya, Andriani Porosi alias AP (50), saat digerebek berduaan diduga bareng selingkuhan di mobil.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604752/duduk-perkara-pria-di-tangerang-dipaksa-masturbasi-hingga-disiksa</t>
+          <t>https://news.detik.com/berita/d-8604765/sekda-konawe-selatan-tabrak-adik-saat-digerebek-bareng-selingkuhan-di-mobil</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5080,28 +5080,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ketua DPRD Surabaya Dorong Sinergi Warga-Aparat Jaga Kota Kondusif</t>
+          <t>Penjelasan BMKG soal Hujan di Jakarta Usai Berminggu-minggu Kering</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:02:41 +0700</t>
+          <t>Wed, 05 Aug 2026 08:24:21 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ketua DPRD Surabaya, Syaifudin Zuhri, menekankan pentingnya peran masyarakat dalam menjaga keamanan kota.</t>
+          <t>Hujan turun di Jakarta setelah kering berminggu-minggu. Ini penjelasan BMKG.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604677/ketua-dprd-surabaya-dorong-sinergi-warga-aparat-jaga-kota-kondusif</t>
+          <t>https://news.detik.com/berita/d-8604764/penjelasan-bmkg-soal-hujan-di-jakarta-usai-berminggu-minggu-kering</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dprd-surabaya-1785886861092_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hujan-deras-guyur-jakarta-usai-berminggu-minggu-kering-1785846576327_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5118,28 +5118,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Adrien Schneider, Buron High Profile Asal Prancis Ditangkap di Jakarta</t>
+          <t>Puan Berduka KM Mutiara Terbakar: Keamanan Transportasi Laut RI Masih Minim</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:02:31 +0700</t>
+          <t>Wed, 05 Aug 2026 08:15:49 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Buron high profile Prancis, Adrien Schneider, ditangkap di Jakarta. Dia terlibat pembunuhan dan kejahatan berat, kini dalam proses deportasi ke Prancis.</t>
+          <t>KM Mutiara Sentosa 2 terbakar di Madura, menewaskan lima orang. Puan Maharani soroti minimnya keamanan transportasi laut.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604749/adrien-schneider-buron-high-profile-asal-prancis-ditangkap-di-jakarta</t>
+          <t>https://news.detik.com/berita/d-8604759/puan-berduka-km-mutiara-terbakar-keamanan-transportasi-laut-ri-masih-minim</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adrien-schneider-buron-high-profile-asal-prancis-dideportasi-ke-negaranya-setelah-tertangkap-usai-bersembunyi-di-sumbawa-dan-b-1785891665606_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/puan-maharani-1777615358543_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5156,28 +5156,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Aksi Perekam Usher GIIAS Bikin Resah Kini Diusut Polisi</t>
+          <t>Duduk Perkara Pria di Tangerang Dipaksa Masturbasi hingga Disiksa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:55:46 +0700</t>
+          <t>Wed, 05 Aug 2026 08:04:14 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Polemik perekaman usher di GIIAS 2026 berlanjut. Polisi menyelidiki kasus ini setelah korban merasa tidak nyaman.</t>
+          <t>Seorang pria diduga dianiaya bos dan rekan kerjanya di Kabupaten Tangerang, Banten. Korban juga diduga dipaksa masturbasi sambil menonton film porno.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604735/aksi-perekam-usher-giias-bikin-resah-kini-diusut-polisi</t>
+          <t>https://news.detik.com/berita/d-8604752/duduk-perkara-pria-di-tangerang-dipaksa-masturbasi-hingga-disiksa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/video-yang-menjadikan-usher-spg-di-giias-2026-sebagai-objek-konten-berjudul-cara-mendekati-cewek-ramai-dikritik-ppembuat-konte-1785733892086_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5194,28 +5194,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2 Pengamen Pemukul Pengunjung GTC Cirebon Ditangkap</t>
+          <t>Ketua DPRD Surabaya Dorong Sinergi Warga-Aparat Jaga Kota Kondusif</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:54:18 +0700</t>
+          <t>Wed, 05 Aug 2026 08:02:41 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dua pengamen ditangkap polisi di Cirebon setelah terlibat keributan dengan pengunjung. Mereka terancam hukuman lima tahun penjara akibat kekerasan.</t>
+          <t>Ketua DPRD Surabaya, Syaifudin Zuhri, menekankan pentingnya peran masyarakat dalam menjaga keamanan kota.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604733/2-pengamen-pemukul-pengunjung-gtc-cirebon-ditangkap</t>
+          <t>https://news.detik.com/berita/d-8604677/ketua-dprd-surabaya-dorong-sinergi-warga-aparat-jaga-kota-kondusif</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-cirebon-kota-akbp-bimantoro-kurniawan-1785889392099_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dprd-surabaya-1785886861092_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5232,28 +5232,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ada Pengecoran Jalan, Jalan Raya Bogor Arah Pasar Rebo Jaktim Macet</t>
+          <t>Adrien Schneider, Buron High Profile Asal Prancis Ditangkap di Jakarta</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:36:58 +0700</t>
+          <t>Wed, 05 Aug 2026 08:02:31 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kemacetan terjadi di Jalan Raya Bogor, Jakarta Timur (Jaktim) pagi ini. Kemacetan itu imbas adanya pengecoran jalan.</t>
+          <t>Buron high profile Prancis, Adrien Schneider, ditangkap di Jakarta. Dia terlibat pembunuhan dan kejahatan berat, kini dalam proses deportasi ke Prancis.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604724/ada-pengecoran-jalan-jalan-raya-bogor-arah-pasar-rebo-jaktim-macet</t>
+          <t>https://news.detik.com/berita/d-8604749/adrien-schneider-buron-high-profile-asal-prancis-ditangkap-di-jakarta</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemacetan-terjadi-di-jalan-raya-bogor-jakarta-timur-jaktim-pagi-ini-kemacetan-itu-imbas-adanya-pengecoran-jalan-dok-tmc-polda--1785890168558_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adrien-schneider-buron-high-profile-asal-prancis-dideportasi-ke-negaranya-setelah-tertangkap-usai-bersembunyi-di-sumbawa-dan-b-1785891665606_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5270,28 +5270,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Patgulipat Bisnis Don Ritto Tempat Cuci Uang Febrie Diungkap</t>
+          <t>Aksi Perekam Usher GIIAS Bikin Resah Kini Diusut Polisi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:32:33 +0700</t>
+          <t>Wed, 05 Aug 2026 07:55:46 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kejagung mengungkap perusahaan yang diduga terkait kasus TPPU eks Jampidsus Febrie Adriansyah. Perusahaan milik Don Ritto diduga menjadi tempat pencucian.</t>
+          <t>Polemik perekaman usher di GIIAS 2026 berlanjut. Polisi menyelidiki kasus ini setelah korban merasa tidak nyaman.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604720/patgulipat-bisnis-don-ritto-tempat-cuci-uang-febrie-diungkap</t>
+          <t>https://news.detik.com/berita/d-8604735/aksi-perekam-usher-giias-bikin-resah-kini-diusut-polisi</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/video-yang-menjadikan-usher-spg-di-giias-2026-sebagai-objek-konten-berjudul-cara-mendekati-cewek-ramai-dikritik-ppembuat-konte-1785733892086_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5308,28 +5308,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Momen 35 Orang Bantu Pemakaman Wanita Berbobot 300 Kg di Sragen</t>
+          <t>2 Pengamen Pemukul Pengunjung GTC Cirebon Ditangkap</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:16:37 +0700</t>
+          <t>Wed, 05 Aug 2026 07:54:18 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Perempuan berbobot 300 kg berinisial I (39), warga Sragen Tengah, Kabupaten Sragen, meninggal dunia usai mengalami sesak napas.</t>
+          <t>Dua pengamen ditangkap polisi di Cirebon setelah terlibat keributan dengan pengunjung. Mereka terancam hukuman lima tahun penjara akibat kekerasan.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604715/momen-35-orang-bantu-pemakaman-wanita-berbobot-300-kg-di-sragen</t>
+          <t>https://news.detik.com/berita/d-8604733/2-pengamen-pemukul-pengunjung-gtc-cirebon-ditangkap</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-cirebon-kota-akbp-bimantoro-kurniawan-1785889392099_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Perkara Kopilot Kurir 26 Kg Ekstasi di Soetta Juga Diusut Malaysia</t>
+          <t>Ada Pengecoran Jalan, Jalan Raya Bogor Arah Pasar Rebo Jaktim Macet</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:55:26 +0700</t>
+          <t>Wed, 05 Aug 2026 07:36:58 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kopilot Malaysia Airlines ditangkap di Indonesia karena menyelundupkan 70 ribu butir ekstasi. Polisi Malaysia kini menyelidiki keterlibatan petugas bandara.</t>
+          <t>Kemacetan terjadi di Jalan Raya Bogor, Jakarta Timur (Jaktim) pagi ini. Kemacetan itu imbas adanya pengecoran jalan.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604681/perkara-kopilot-kurir-26-kg-ekstasi-di-soetta-juga-diusut-malaysia</t>
+          <t>https://news.detik.com/berita/d-8604724/ada-pengecoran-jalan-jalan-raya-bogor-arah-pasar-rebo-jaktim-macet</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemacetan-terjadi-di-jalan-raya-bogor-jakarta-timur-jaktim-pagi-ini-kemacetan-itu-imbas-adanya-pengecoran-jalan-dok-tmc-polda--1785890168558_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nasib 2 JPO 'Dekat tapi Tak Jadian' di Rasuna Said</t>
+          <t>Patgulipat Bisnis Don Ritto Tempat Cuci Uang Febrie Diungkap</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:36:52 +0700</t>
+          <t>Wed, 05 Aug 2026 07:32:33 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dua JPO di Jalan HR Rasuna Said, Jakarta, berdekatan tapi tak terhubung. Gubernur Pramono menindaklanjuti keluhan warga itu.</t>
+          <t>Kejagung mengungkap perusahaan yang diduga terkait kasus TPPU eks Jampidsus Febrie Adriansyah. Perusahaan milik Don Ritto diduga menjadi tempat pencucian.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604674/nasib-2-jpo-dekat-tapi-tak-jadian-di-rasuna-said</t>
+          <t>https://news.detik.com/berita/d-8604720/patgulipat-bisnis-don-ritto-tempat-cuci-uang-febrie-diungkap</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313058_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5422,28 +5422,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Drama Atlet Golf Jesslyn Wijaya Disetop Sebab Bukan Penculikan</t>
+          <t>Momen 35 Orang Bantu Pemakaman Wanita Berbobot 300 Kg di Sragen</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:59:57 +0700</t>
+          <t>Wed, 05 Aug 2026 07:16:37 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kabar atlet golf Jesslyn Wijaya (34) diculik telah terpatahkan. Penyidikan kasus itu kini akan disetop kepolisian.</t>
+          <t>Perempuan berbobot 300 kg berinisial I (39), warga Sragen Tengah, Kabupaten Sragen, meninggal dunia usai mengalami sesak napas.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604657/drama-atlet-golf-jesslyn-wijaya-disetop-sebab-bukan-penculikan</t>
+          <t>https://news.detik.com/berita/d-8604715/momen-35-orang-bantu-pemakaman-wanita-berbobot-300-kg-di-sragen</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/atlet-golf-putri-jesslyn-wijaya-lay-dok-ig-jesswijgolf-1784630812506_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5460,28 +5460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ultimatum Trump Sebelum 'Pancung' Iran</t>
+          <t>Perkara Kopilot Kurir 26 Kg Ekstasi di Soetta Juga Diusut Malaysia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:43:04 +0700</t>
+          <t>Wed, 05 Aug 2026 06:55:26 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Trump marah pada Iran yang bantah negosiasi. Ia beri ultimatum: kesepakatan atau penyerahan total. Iran menegaskan tidak ada dialog dengan AS.</t>
+          <t>Kopilot Malaysia Airlines ditangkap di Indonesia karena menyelundupkan 70 ribu butir ekstasi. Polisi Malaysia kini menyelidiki keterlibatan petugas bandara.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604651/ultimatum-trump-sebelum-pancung-iran</t>
+          <t>https://news.detik.com/berita/d-8604681/perkara-kopilot-kurir-26-kg-ekstasi-di-soetta-juga-diusut-malaysia</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/tarif-10-berakhir-trump-berlakukan-bea-masuk-baru-terhadap-60-mitra-dagang-1784889297458_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5498,28 +5498,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Korban Tewas Gelombang Migran Ilegal di Ceuta Spanyol Jadi 77 orang</t>
+          <t>Nasib 2 JPO 'Dekat tapi Tak Jadian' di Rasuna Said</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:31:03 +0700</t>
+          <t>Wed, 05 Aug 2026 06:36:52 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Serbuan migran ilegal dari Maroko ke Ceuta, Spanyol, menyebabkan 77 tewas. Banyak yang tenggelam saat mencoba melewati penghalang Laut Mediterania.</t>
+          <t>Dua JPO di Jalan HR Rasuna Said, Jakarta, berdekatan tapi tak terhubung. Gubernur Pramono menindaklanjuti keluhan warga itu.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604650/korban-tewas-gelombang-migran-ilegal-di-ceuta-spanyol-jadi-77-orang</t>
+          <t>https://news.detik.com/berita/d-8604674/nasib-2-jpo-dekat-tapi-tak-jadian-di-rasuna-said</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/spanyol-kerahkan-militer-ke-ceuta-atasi-krisis-migran-1785493658510_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313058_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5536,28 +5536,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Operasi SAR Pencarian Korban KM Mutiara Sentosa 2 Ditutup</t>
+          <t>Drama Atlet Golf Jesslyn Wijaya Disetop Sebab Bukan Penculikan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:06:19 +0700</t>
+          <t>Wed, 05 Aug 2026 05:59:57 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Basarnas resmi menghentikan operasi SAR KM Mutiara Sentosa II setelah 238 orang berhasil didata. Operasi kini beralih ke kesiapsiagaan rutin.</t>
+          <t>Kabar atlet golf Jesslyn Wijaya (34) diculik telah terpatahkan. Penyidikan kasus itu kini akan disetop kepolisian.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604649/operasi-sar-pencarian-korban-km-mutiara-sentosa-2-ditutup</t>
+          <t>https://news.detik.com/berita/d-8604657/drama-atlet-golf-jesslyn-wijaya-disetop-sebab-bukan-penculikan</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785810542046_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/atlet-golf-putri-jesslyn-wijaya-lay-dok-ig-jesswijgolf-1784630812506_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5574,28 +5574,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gempa M 5,6 Guncang Halmahera Barat Malut</t>
+          <t>Ultimatum Trump Sebelum 'Pancung' Iran</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 03:45:22 +0700</t>
+          <t>Wed, 05 Aug 2026 05:43:04 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Gempa magnitudo 5,6 mengguncang Halmahera Barat, Maluku Utara, pada kedalaman 25 km. BMKG memastikan tidak ada potensi tsunami.</t>
+          <t>Trump marah pada Iran yang bantah negosiasi. Ia beri ultimatum: kesepakatan atau penyerahan total. Iran menegaskan tidak ada dialog dengan AS.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604647/gempa-m-5-6-guncang-halmahera-barat-malut</t>
+          <t>https://news.detik.com/internasional/d-8604651/ultimatum-trump-sebelum-pancung-iran</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/tarif-10-berakhir-trump-berlakukan-bea-masuk-baru-terhadap-60-mitra-dagang-1784889297458_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5612,28 +5612,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Staf Bandara KLIA Diduga Bantu Kopilot yang Selundupkan Narkoba ke RI</t>
+          <t>Korban Tewas Gelombang Migran Ilegal di Ceuta Spanyol Jadi 77 orang</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 02:26:38 +0700</t>
+          <t>Wed, 05 Aug 2026 05:31:03 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kepolisian Malaysia mengidentifikasi staf Bandara KLIA yang diduga bantu kopilot selundupkan narkoba ke Indonesia. Penyelidikan terus dilakukan.</t>
+          <t>Serbuan migran ilegal dari Maroko ke Ceuta, Spanyol, menyebabkan 77 tewas. Banyak yang tenggelam saat mencoba melewati penghalang Laut Mediterania.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604644/staf-bandara-klia-diduga-bantu-kopilot-yang-selundupkan-narkoba-ke-ri</t>
+          <t>https://news.detik.com/internasional/d-8604650/korban-tewas-gelombang-migran-ilegal-di-ceuta-spanyol-jadi-77-orang</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/spanyol-kerahkan-militer-ke-ceuta-atasi-krisis-migran-1785493658510_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5650,28 +5650,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Rumah Warga Ambruk 6 Bulan Belum Diperbaiki, Pemkot Serang Beri Bantuan</t>
+          <t>Operasi SAR Pencarian Korban KM Mutiara Sentosa 2 Ditutup</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:33:26 +0700</t>
+          <t>Wed, 05 Aug 2026 05:06:19 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rumah Nani di Serang ambruk akibat angin kencang. Pemkot Serang bantu Rp 30 juta untuk renovasi. Wali Kota kunjungi lokasi untuk pengecekan.</t>
+          <t>Basarnas resmi menghentikan operasi SAR KM Mutiara Sentosa II setelah 238 orang berhasil didata. Operasi kini beralih ke kesiapsiagaan rutin.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604642/rumah-warga-ambruk-6-bulan-belum-diperbaiki-pemkot-serang-beri-bantuan</t>
+          <t>https://news.detik.com/berita/d-8604649/operasi-sar-pencarian-korban-km-mutiara-sentosa-2-ditutup</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rumah-warga-serang-1785868326015_169.webp?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785810542046_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5688,28 +5688,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pimpinan DPRD Ajak Warga Jaga Jakarta: Jadikan Rumah yang Aman bagi Semua</t>
+          <t>Gempa M 5,6 Guncang Halmahera Barat Malut</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:51:11 +0700</t>
+          <t>Wed, 05 Aug 2026 03:45:22 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Baco mendorong warga Jakarta untuk berbondong-bondong menjaga kotanya. Dia berpesan agar Jakarta menjadi rumah aman bagi semua warganya.</t>
+          <t>Gempa magnitudo 5,6 mengguncang Halmahera Barat, Maluku Utara, pada kedalaman 25 km. BMKG memastikan tidak ada potensi tsunami.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604639/pimpinan-dprd-ajak-warga-jaga-jakarta-jadikan-rumah-yang-aman-bagi-semua</t>
+          <t>https://news.detik.com/berita/d-8604647/gempa-m-5-6-guncang-halmahera-barat-malut</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/15/basri-baco-1778786025155_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5726,28 +5726,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Qatar Bilang Negosiasi AS-Iran Progresif, Draf Perjanjian Damai Lagi Dibahas</t>
+          <t>Staf Bandara KLIA Diduga Bantu Kopilot yang Selundupkan Narkoba ke RI</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:22:56 +0700</t>
+          <t>Wed, 05 Aug 2026 02:26:38 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Qatar menyatakan upaya penyelesaian konflik AS-Iran sedang progresif. Draf perjanjian damai sedang diedarkan, dengan fokus pada resolusi jangka pendek.</t>
+          <t>Kepolisian Malaysia mengidentifikasi staf Bandara KLIA yang diduga bantu kopilot selundupkan narkoba ke Indonesia. Penyelidikan terus dilakukan.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604632/qatar-bilang-negosiasi-as-iran-progresif-draf-perjanjian-damai-lagi-dibahas</t>
+          <t>https://news.detik.com/berita/d-8604644/staf-bandara-klia-diduga-bantu-kopilot-yang-selundupkan-narkoba-ke-ri</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/uae-iran-us-israel-war-1783871173097_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5764,28 +5764,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ngambek Keinginan Tak Dituruti Ortu, Pemuda Bandung Bakar Motor dan 3 Rumah</t>
+          <t>Rumah Warga Ambruk 6 Bulan Belum Diperbaiki, Pemkot Serang Beri Bantuan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:20:10 +0700</t>
+          <t>Wed, 05 Aug 2026 01:33:26 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Polisi menangkap pemuda yang membakar motor dan tiga rumah di Babakan Ciparay. Motif pelaku lantaran keinginan tak dipenuhi ortu.</t>
+          <t>Rumah Nani di Serang ambruk akibat angin kencang. Pemkot Serang bantu Rp 30 juta untuk renovasi. Wali Kota kunjungi lokasi untuk pengecekan.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604631/ngambek-keinginan-tak-dituruti-ortu-pemuda-bandung-bakar-motor-dan-3-rumah</t>
+          <t>https://news.detik.com/berita/d-8604642/rumah-warga-ambruk-6-bulan-belum-diperbaiki-pemkot-serang-beri-bantuan</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tampang-pemuda-yang-bakar-motor-hingga-api-menjalar-ke-3-rumah-1785851029166_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rumah-warga-serang-1785868326015_169.webp?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5797,33 +5797,33 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Modus Misdeclaration Terbongkar, Harley-Davidson Bekas Ilegal Disita Bea Cukai</t>
+          <t>Pimpinan DPRD Ajak Warga Jaga Jakarta: Jadikan Rumah yang Aman bagi Semua</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:57:30 +0700</t>
+          <t>Wed, 05 Aug 2026 00:51:11 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok menggagalkan penyelundupan lima Harley-Davidson bekas dan 20 rangka bekas asal China dengan modus misdeclaration.</t>
+          <t>Baco mendorong warga Jakarta untuk berbondong-bondong menjaga kotanya. Dia berpesan agar Jakarta menjadi rumah aman bagi semua warganya.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8605004/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai</t>
+          <t>https://news.detik.com/berita/d-8604639/pimpinan-dprd-ajak-warga-jaga-jakarta-jadikan-rumah-yang-aman-bagi-semua</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai-1785903653401.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/15/basri-baco-1778786025155_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5835,33 +5835,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jumlah Pengangguran RI Turun Jadi 7,22 Juta Orang</t>
+          <t>Qatar Bilang Negosiasi AS-Iran Progresif, Draf Perjanjian Damai Lagi Dibahas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:55:15 +0700</t>
+          <t>Wed, 05 Aug 2026 00:22:56 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat, jumlah pengangguran di Indonesia per Mei 2026 sebanyak 7,22 juta orang.</t>
+          <t>Qatar menyatakan upaya penyelesaian konflik AS-Iran sedang progresif. Draf perjanjian damai sedang diedarkan, dengan fokus pada resolusi jangka pendek.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605071/jumlah-pengangguran-ri-turun-jadi-7-22-juta-orang</t>
+          <t>https://news.detik.com/internasional/d-8604632/qatar-bilang-negosiasi-as-iran-progresif-draf-perjanjian-damai-lagi-dibahas</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/09/ilustrasi-pengangguran-atau-pencari-kerja-1746784722868_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/uae-iran-us-israel-war-1783871173097_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5873,33 +5873,33 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ekonomi RI Tumbuh 5,29%, Ini Motor Penggeraknya</t>
+          <t>Ngambek Keinginan Tak Dituruti Ortu, Pemuda Bandung Bakar Motor dan 3 Rumah</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:33:09 +0700</t>
+          <t>Wed, 05 Aug 2026 00:20:10 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mengumumkan pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
+          <t>Polisi menangkap pemuda yang membakar motor dan tiga rumah di Babakan Ciparay. Motif pelaku lantaran keinginan tak dipenuhi ortu.</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605018/ekonomi-ri-tumbuh-5-29-ini-motor-penggeraknya</t>
+          <t>https://news.detik.com/berita/d-8604631/ngambek-keinginan-tak-dituruti-ortu-pemuda-bandung-bakar-motor-dan-3-rumah</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/05/27/bangkit-dari-pandemi-ekonomi-ri-kuartal-ii-2021-diramal-tembus-7-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tampang-pemuda-yang-bakar-motor-hingga-api-menjalar-ke-3-rumah-1785851029166_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5911,33 +5911,33 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Pembiayaan Komersial Bank Mega Syariah Tumbuh Jadi Rp 5,9 T</t>
+          <t>Jadwal Singapura Vs Indonesia di Piala AFF 2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:36 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:10 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PT Bank Mega Syariah mencatat pertumbuhan pembiayaan pada segmen komersial bank sepanjang semester I-2026.</t>
+          <t>Timnas Indonesia bertandang ke markas Singapura dalam matchday terakhir fase grup Piala AFF 2026. Berikut jadwal pertandingan selengkapnya!</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8605001/pembiayaan-komersial-bank-mega-syariah-tumbuh-jadi-rp-5-9-t</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605047/jadwal-singapura-vs-indonesia-di-piala-aff-2026</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/13/ini-pemenang-mobil-listrik-program-berkah-berlimpah-mega-syariah-4_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5949,33 +5949,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BPS Umumkan Ekonomi RI Tumbuh 5,29% di Kuartal II</t>
+          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:17:07 +0700</t>
+          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mengumumkan, pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
+          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604987/bps-umumkan-ekonomi-ri-tumbuh-5-29-di-kuartal-ii</t>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/deputi-bidang-neraca-dan-analisis-statistik-bps-edy-mahmud-1785902590386_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5987,33 +5987,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BNI Cetak Laba Bersih Rp 10,8 Triliun</t>
+          <t>Jadwal MotoGP Inggris 2026 Akhir Pekan Ini</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:58:49 +0700</t>
+          <t>Wed, 05 Aug 2026 11:30:30 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PT Bank Negara Indonesia (Persero) Tbk atau BNI membukukan laba bersih sebesar Rp 10,8 triliun hingga semester I 2026.</t>
+          <t>MotoGP 2026 akan kembali bergulir setelah jeda musim panas pada seri ke-12 di Sirkuit Silverstone, Inggris. Simak jadwalnya.</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604965/bni-cetak-laba-bersih-rp-10-8-triliun</t>
+          <t>https://sport.detik.com/moto-gp/d-8604979/jadwal-motogp-inggris-2026-akhir-pekan-ini</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/bni-1773200307513_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-di-motogp-jerman-2026-1783857060263_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6025,33 +6025,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dari China</t>
+          <t>Jadwal Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:38:16 +0700</t>
+          <t>Wed, 05 Aug 2026 11:20:20 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Barang impor ilegal tersebut berasal dari China.</t>
+          <t>Jadwal final Piala Presiden 2026 mempertemukan Persib Bandung vs Persebaya Surabaya.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604938/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604949/jadwal-final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china-1785901058002_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6063,33 +6063,33 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Harga Emas Hari Ini Turun Lagi Sentuh Rp 2,59 Juta</t>
+          <t>Neymar di Persimpangan Jalan Kariernya</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:10:07 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:00 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hari ini, Rabu (5/8) harga emas Antam 24 karat turun Rp 4.000 per gram menjadi Rp 2.599.000 per gram.</t>
+          <t>Kontrak Neymar di Santos tinggal tersisa beberapa bulan lagi. Neymar tengah mempertimbangkan kelanjutan kariernya sebagai pesepakbola, lanjut main atau pensiun.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604895/harga-emas-hari-ini-turun-lagi-sentuh-rp-2-59-juta</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604692/neymar-di-persimpangan-jalan-kariernya</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/22/harga-emas-terjun-bebas-pasar-cikini-langsung-diserbu-pembeli-1761123863171_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/neymar-menangis-akhiri-karier-bersama-timnas-brasil-1783314392616_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6101,33 +6101,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Narkotika di Bandara Juanda</t>
+          <t>Presiden FIFA Gianni Infantino Gelar Rapat Darurat!</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:33:15 +0700</t>
+          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bea Cukai kembali menggagalkan penyelundupan narkotika.</t>
+          <t>Gianni Infantino dilaporkan menggelar rapat darurat. Hal ini dilakukan di tengah desakan agar dirinya mundur dari FIFA.</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604848/bea-cukai-gagalkan-penyelundupan-narkotika-di-bandara-juanda</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604767/presiden-fifa-gianni-infantino-gelar-rapat-darurat</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-narkotika-1785897113589_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6139,33 +6139,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dolar AS Melemah ke Level Rp 17.971</t>
+          <t>Belum Selesai Belanja, Chelsea Siap Gaet Pengganti Cucurella</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:21:24 +0700</t>
+          <t>Wed, 05 Aug 2026 10:20:00 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nilai tukar dolar Amerika Serikat (AS) terpantau melemah terhadap rupiah.</t>
+          <t>Chelsea belum berhenti belanja musim panas ini. The Blues dilaporkan bakal mendatangkan pengganti Marc Cucurella.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604830/dolar-as-melemah-ke-level-rp-17-971</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604768/belum-selesai-belanja-chelsea-siap-gaet-pengganti-cucurella</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338213_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pep-chavarriarayo-vallecanolaligaliga-spanyolchelsea-1785891772000_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6177,33 +6177,33 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IHSG Naik Tipis Pagi Ini ke Level 6.322</t>
+          <t>Amorim Jelang Milan Vs Inter: Juara Pramusim Nggak Penting</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:16:12 +0700</t>
+          <t>Wed, 05 Aug 2026 10:00:15 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
+          <t>AC Milan akan menghadapi Inter Milan di laga uji coba pramusim. Pelatih Milan Ruben Amorim menyebut hasil akhir bukan yang paling utama.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604824/ihsg-naik-tipis-pagi-ini-ke-level-6-322</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604711/amorim-jelang-milan-vs-inter-juara-pramusim-nggak-penting</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/22/jelang-putusan-mk-ihsg-menguat-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ruben-amorim-1785887341737_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6215,33 +6215,33 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sri Mulyani Ditunjuk Bank Dunia Jadi Ketua Penggalangan Dana buat Negara Miskin</t>
+          <t>Carragher Nilai Liverpool Belum Siap Bersaing Jadi Juara Premier League</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:42:46 +0700</t>
+          <t>Wed, 05 Aug 2026 09:40:09 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Penunjukkan Sri Mulyani bukan tanpa alasan. Eks Bendahara Negara tersebut mempunyai pengalaman dalam bidang keuangan pembangunan internasional</t>
+          <t>Jamie Carragher menilai Liverpool belum cukup kuat untuk bersaing memperebutkan gelar juara Premier League. Menurutnya, skuad Liverpool belum lengkap.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604777/sri-mulyani-ditunjuk-bank-dunia-jadi-ketua-penggalangan-dana-buat-negara-miskin</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604726/carragher-nilai-liverpool-belum-siap-bersaing-jadi-juara-premier-league</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/10/mantan-menteri-keuangan-sri-mulyani-indrawati-1765362593072_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/andoni-iraola-1785219269838_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6253,33 +6253,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BUMI Catat Laba Bersih Semester I-2026 Naik 188%, AMAR Tetapkan Dividen Interim</t>
+          <t>Kolo Muani Punya Urusan yang Belum Selesai di Juventus</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:33:25 +0700</t>
+          <t>Wed, 05 Aug 2026 09:20:13 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>IHSG ditutup naik 1,37% di tengah aksi beli asing. BUMI membukukan kenaikan laba bersih semester I-2026, sementara AMAR menetapkan dividen interim.</t>
+          <t>Randal Kolo Muani amat gembira bisa kembali ke Juventus. Kolo Muani ingin menuntaskan apa yang sudah ia mulai di Turin.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604770/bumi-catat-laba-bersih-semester-i-2026-naik-188-amar-tetapkan-dividen-interim</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604710/kolo-muani-punya-urusan-yang-belum-selesai-di-juventus</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bursa-dan-valas-1785893124-1785893124406.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/09/randal-kolo-muani-1752056032311_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6291,33 +6291,33 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Harga Minyak Turun Sedalam Ini Usai Sinyal Damai AS &amp;amp; Iran</t>
+          <t>Kata-kata Erick Thohir soal Dukung Infantino Terus Pimpin FIFA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:10:37 +0700</t>
+          <t>Wed, 05 Aug 2026 09:00:00 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Harga minyak mentah dunia anjlok lebih dari 5% dan bertengger di level terendahnya dalam tiga minggu terakhir pada perdagangan Selasa.</t>
+          <t>Ketua Umum PSSI, Erick Thohir, bikin pernyatan soal dukungannya ke Gianni Infantino. Ia menyebut Indonesia sudah banyak dibantu Presiden FIFA tersebut.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604727/harga-minyak-turun-sedalam-ini-usai-sinyal-damai-as-iran</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604792/kata-kata-erick-thohir-soal-dukung-infantino-terus-pimpin-fifa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/16/ilustrasi-pengeboran-migas-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/18/erick-thohir-dan-presiden-fifa-gianni-infantino-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6329,33 +6329,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rayuan Purbaya ke Toyota, Janji Kasih Insentif Banyak</t>
+          <t>Inter Vs Milan di Pramusim, Chivu: Fokusnya ke Kebugaran</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:58:00 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:21 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa meminta raksasa otomotif Jepang, Toyota, memindahkan pusat manufaktur utamanya ke Indonesia.</t>
+          <t>Inter Milan melanjutkan tur pramusimnya dengan melawan AC Milan di Australia. Pelatih Nerazzurri Cristian Chivu menegaskan fokus timnya ke membangun kebugaran.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/ekonomi-bisnis/d-8604540/rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604317/inter-vs-milan-di-pramusim-chivu-fokusnya-ke-kebugaran</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detik-pagi-rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak-1785856135943_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6367,33 +6367,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Purbaya Janji Ekonomi Tahun Ini Tumbuh Dekati 6%</t>
+          <t>Dipercaya di Surabaya Marathon 2026, Le Minerale Hadir di 18 Water Station</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:24:33 +0700</t>
+          <t>Wed, 05 Aug 2026 08:22:43 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa optimistis ekonomi tahun ini bisa tumbuh mendekati angka 6%.</t>
+          <t>Le Minerale Surabaya Marathon 2026 diikuti 7.000 pelari, mengusung konsep City Run. Acara ini mendukung sport tourism dan hidrasi optimal dengan Le Minerale.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604612/purbaya-janji-ekonomi-tahun-ini-tumbuh-dekati-6</t>
+          <t>https://sport.detik.com/sportstyle/d-8604762/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962228_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station-1785892907123.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6405,33 +6405,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Bank-bank di Rusia Mulai Krisis Uang Tunai</t>
+          <t>Mourinho Ingin Vinicius Selalu Bahagia di Madrid</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:00:57 +0700</t>
+          <t>Wed, 05 Aug 2026 08:00:00 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Perbankan Rusia menghadapi tekanan likuiditas rubel, membatasi kemampuan menyerap obligasi pemerintah. Defisit anggaran membengkak.</t>
+          <t>Di tengah rumor Arsenal, Vinicius buka suara usai menjalani latihan pramusim bersama Real Madrid. Vinicius bilang Jose Mourinho ingin ia bahagia di Madrid.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604562/bank-bank-di-rusia-mulai-krisis-uang-tunai</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604655/mourinho-ingin-vinicius-selalu-bahagia-di-madrid</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/29/g7-tolak-pembayaran-gas-rusia-dengan-mata-uang-rubel_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/15/soccer-spain-rma-rso-1771110362377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6443,33 +6443,33 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Respons Bos BGN soal Anggaran MBG &amp;amp; Pendidikan Harus Dipisah</t>
+          <t>Alejandro Garnacho Langsung 'Babak Belur' di Pramusim Aston Villa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:30:38 +0700</t>
+          <t>Wed, 05 Aug 2026 07:30:00 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono merespons keputusan Mahkamah Konstitusi soal memisahkan anggaran MBG dengan pendidikan.</t>
+          <t>Alejandro Garnacho baru pindah ke Aston Villa musim panas ini. Di laga pramusim, winger Argentina itu langsung babak belur.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604561/respons-bos-bgn-soal-anggaran-mbg-pendidikan-harus-dipisah</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604654/alejandro-garnacho-langsung-babak-belur-di-pramusim-aston-villa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/alejandro-garnachoaston-villabg-pathum-vs-aston-villapramusim-aston-villa-1785881271654_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6481,33 +6481,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Era Controlled Landfill, Penghasilan Pemulung Bantargebang Merosot Drastis</t>
+          <t>Asosiasi Sepakbola Yordania Merasa Diperas FIFA!</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:00:49 +0700</t>
+          <t>Wed, 05 Aug 2026 07:00:00 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Controlled landfill di TPST Bantargebang mengubah pemilahan sampah dan membuat penghasilan pemulung yang bergantung pada sampah menurun.</t>
+          <t>Asosiasi Sepakbola Yordania (JFA) bikin pernyataan keras soal FIFA. Mereka mengaku diperas organisasi pimpinan Gianni Infantino tersebut.</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8604299/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604652/asosiasi-sepakbola-yordania-merasa-diperas-fifa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis-1785843094443_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/11/logo-fifa_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6519,33 +6519,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sentilan Keras Purbaya buat Moody's-Fitch</t>
+          <t>Semifinal Piala Presiden 2026 yang Aman dan Seru!</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:55:23 +0700</t>
+          <t>Wed, 05 Aug 2026 06:30:00 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan sentilan keras kepada dua lembaga rating global.</t>
+          <t>Semifinal Piala Presiden 2026 sudah digelar. Rangkaian pertandingan berjalan aman dan seru, sesuai yang diharapkan.</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604558/sentilan-keras-purbaya-buat-moodys-fitch</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604648/semifinal-piala-presiden-2026-yang-aman-dan-seru</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786088_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-semifinal-piala-presiden-2026-antara-persib-vs-persija-di-stadion-kapten-i-wayan-dipta-gianyar-bali-selasa-482026-1785862146465.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6562,28 +6562,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Jadwal Singapura Vs Indonesia di Piala AFF 2026</t>
+          <t>Mohamed Salah Menuju Trabzonspor</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:10 +0700</t>
+          <t>Wed, 05 Aug 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Timnas Indonesia bertandang ke markas Singapura dalam matchday terakhir fase grup Piala AFF 2026. Berikut jadwal pertandingan selengkapnya!</t>
+          <t>Mohamed Salah menuju Trabzonspor. Klub Turki itu mengonfirmasi bakal bernegosiasi dengan pemain asal Mesir tersebut.</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605047/jadwal-singapura-vs-indonesia-di-piala-aff-2026</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604653/mohamed-salah-menuju-trabzonspor</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/mohamed-salah-1781054944371_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6600,28 +6600,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
+          <t>Edisi Kedua! Ajang Lari Rekreasional di DIY Segera Digelar Lagi</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
+          <t>Wed, 05 Aug 2026 05:15:25 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
+          <t>Ajang lari rekresional di Daerah Istimewa Yogyakarta (DIY) edisi kedua, Jogja Run'nShine, akan kembali digelar. Inovasi dihadirkan dari evaluasi edisi perdana.</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
+          <t>https://sport.detik.com/sport-lain/d-8604536/edisi-kedua-ajang-lari-rekreasional-di-diy-segera-digelar-lagi</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jogja-runnshine-1785853110207_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6638,28 +6638,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jadwal MotoGP Inggris 2026 Akhir Pekan Ini</t>
+          <t>FIFA Bantah Infantino 'Dicuekin' Donald Trump</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:30:30 +0700</t>
+          <t>Wed, 05 Aug 2026 05:00:18 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>MotoGP 2026 akan kembali bergulir setelah jeda musim panas pada seri ke-12 di Sirkuit Silverstone, Inggris. Simak jadwalnya.</t>
+          <t>Ada kabar Gianni Infantino tak bisa menghubungi Donald Trump usai wacana menjual saham Piala Dunia batal. FIFA membantah laporan tersebut.</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604979/jadwal-motogp-inggris-2026-akhir-pekan-ini</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604623/fifa-bantah-infantino-dicuekin-donald-trump</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-di-motogp-jerman-2026-1783857060263_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/trump-tampak-didampingi-presiden-fifa-gianni-infantino-saat-berbicara-dalam-acara-fifa-yang-digelar-di-trump-tower-new-york-ci-1784348679880_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6676,28 +6676,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Jadwal Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
+          <t>Bernardo Silva: Saat Madrid Memanggil, Mustahil Bilang Tidak</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:20:20 +0700</t>
+          <t>Wed, 05 Aug 2026 04:00:04 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Jadwal final Piala Presiden 2026 mempertemukan Persib Bandung vs Persebaya Surabaya.</t>
+          <t>Bernardo Silva tidak berpikir dua kali saat mendapat tawaran dari Real Madrid. Menolak Madrid diakui Silva merupakan hal yang mustahil.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604949/jadwal-final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604621/bernardo-silva-saat-madrid-memanggil-mustahil-bilang-tidak</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/bernardo-silva-1759772326382_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Neymar di Persimpangan Jalan Kariernya</t>
+          <t>Hasil Uji Coba: AS Roma Gilas Newport County 4-1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 03:00:00 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Kontrak Neymar di Santos tinggal tersisa beberapa bulan lagi. Neymar tengah mempertimbangkan kelanjutan kariernya sebagai pesepakbola, lanjut main atau pensiun.</t>
+          <t>AS Roma mengalahkan Newport County dalam laga uji coba pramusim. Serigala Ibu Kota menang telak 4-1.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604692/neymar-di-persimpangan-jalan-kariernya</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604646/hasil-uji-coba-as-roma-gilas-newport-county-4-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/neymar-menangis-akhiri-karier-bersama-timnas-brasil-1783314392616_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/as-romanewport-countylaga-pramusimlaga-uji-cobasantiago-castro-1785873342683_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6752,28 +6752,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Presiden FIFA Gianni Infantino Gelar Rapat Darurat!</t>
+          <t>'Klan' Kluivert Berlanjut</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
+          <t>Wed, 05 Aug 2026 02:00:23 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Gianni Infantino dilaporkan menggelar rapat darurat. Hal ini dilakukan di tengah desakan agar dirinya mundur dari FIFA.</t>
+          <t>Shane Kluivert debut di tim utama Barcelona. Shane lanjutkan jejak sang ayah Patrick Kluivert yang 28 tahun lalu juga main buat Barca.</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604767/presiden-fifa-gianni-infantino-gelar-rapat-darurat</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604292/klan-kluivert-berlanjut</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/shane-kluivert-1785831287018.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6790,28 +6790,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Belum Selesai Belanja, Chelsea Siap Gaet Pengganti Cucurella</t>
+          <t>Piala Presiden 2026: Merawat Sportivitas, Menjaga Integritas</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:20:00 +0700</t>
+          <t>Wed, 05 Aug 2026 01:26:47 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chelsea belum berhenti belanja musim panas ini. The Blues dilaporkan bakal mendatangkan pengganti Marc Cucurella.</t>
+          <t>Piala Presiden 2026 diharapkan mampu menjadi teladan penyelenggaraan pertandingan resmi sepakbola nasional.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604768/belum-selesai-belanja-chelsea-siap-gaet-pengganti-cucurella</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604636/piala-presiden-2026-merawat-sportivitas-menjaga-integritas</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pep-chavarriarayo-vallecanolaligaliga-spanyolchelsea-1785891772000_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/piala-presiden-2026-1785863698077_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6828,28 +6828,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Amorim Jelang Milan Vs Inter: Juara Pramusim Nggak Penting</t>
+          <t>Terus Kejar Guimaraes, Arsenal Negosiasi Langsung dengan Newcastle</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:00:15 +0700</t>
+          <t>Wed, 05 Aug 2026 01:00:23 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AC Milan akan menghadapi Inter Milan di laga uji coba pramusim. Pelatih Milan Ruben Amorim menyebut hasil akhir bukan yang paling utama.</t>
+          <t>Arsenal kini tengah bernegosiasi langsung dengan Newcastle United. Ini upaya lanjutan The Gunners untuk mendapatkan Bruno Guimaraes.</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604711/amorim-jelang-milan-vs-inter-juara-pramusim-nggak-penting</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604610/terus-kejar-guimaraes-arsenal-negosiasi-langsung-dengan-newcastle</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ruben-amorim-1785887341737_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/bruno-guimaraes-1783531838994_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6866,28 +6866,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Carragher Nilai Liverpool Belum Siap Bersaing Jadi Juara Premier League</t>
+          <t>PSSI Ikrarkan Dukungan ke Gianni Infantino Terus Pimpin FIFA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:40:09 +0700</t>
+          <t>Wed, 05 Aug 2026 00:30:00 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Jamie Carragher menilai Liverpool belum cukup kuat untuk bersaing memperebutkan gelar juara Premier League. Menurutnya, skuad Liverpool belum lengkap.</t>
+          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan dukungannya ke Gianni Infantino. FIFA, di bawah pimpinannya, disebut membantu Indonesia.</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604726/carragher-nilai-liverpool-belum-siap-bersaing-jadi-juara-premier-league</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604633/pssi-ikrarkan-dukungan-ke-gianni-infantino-terus-pimpin-fifa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/andoni-iraola-1785219269838_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/23/gianni-infantino-erick-thohir_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6904,28 +6904,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Kolo Muani Punya Urusan yang Belum Selesai di Juventus</t>
+          <t>Emmanuel Macron Dukung UEFA Lawan Gianni Infantino</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:20:13 +0700</t>
+          <t>Wed, 05 Aug 2026 00:00:30 +0700</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Randal Kolo Muani amat gembira bisa kembali ke Juventus. Kolo Muani ingin menuntaskan apa yang sudah ia mulai di Turin.</t>
+          <t>Presiden Prancis Emmanuel Macron diketahui dukung UEFA untuk melawan Presiden FIFA Gianni Infantino. Mulai ada campur tangan politik negara-negara besar, nih!</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604710/kolo-muani-punya-urusan-yang-belum-selesai-di-juventus</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604322/emmanuel-macron-dukung-uefa-lawan-gianni-infantino</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/09/randal-kolo-muani-1752056032311_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/presiden-prancis-emmanuel-macron-1754969579570.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6937,658 +6937,726 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Kata-kata Erick Thohir soal Dukung Infantino Terus Pimpin FIFA</t>
+          <t>HeadlineBanding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 Miliar</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ketua Umum PSSI, Erick Thohir, bikin pernyatan soal dukungannya ke Gianni Infantino. Ia menyebut Indonesia sudah banyak dibantu Presiden FIFA tersebut.</t>
+          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604792/kata-kata-erick-thohir-soal-dukung-infantino-terus-pimpin-fifa</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=headline</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/18/erick-thohir-dan-presiden-fifa-gianni-infantino-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Inter Vs Milan di Pramusim, Chivu: Fokusnya ke Kebugaran</t>
+          <t>BPS: Pertumbuhan Ekonomi Indonesia 5,29 Persen pada Kuartal II 2026Money</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:21 +0700</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Inter Milan melanjutkan tur pramusimnya dengan melawan AC Milan di Australia. Pelatih Nerazzurri Cristian Chivu menegaskan fokus timnya ke membangun kebugaran.</t>
+          <t>BPS mencatat pertumbuhan ekonomi Indonesia di Kuartal II 2026 mencapai 5,29% (yoy). Sektor pengadaan listrik &amp; gas memimpin, meski pertambangan terkontraksi.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604317/inter-vs-milan-di-pramusim-chivu-fokusnya-ke-kebugaran</t>
+          <t>https://money.kompas.com/read/2026/08/05/114132726/bps-pertumbuhan-ekonomi-indonesia-529-persen-pada-kuartal-ii-2026?source=headline</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/tO31vuJAGVU9FYHw3s-ozVN7cRc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/08/05/689187ab3472b.jpeg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Surabaya</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dipercaya di Surabaya Marathon 2026, Le Minerale Hadir di 18 Water Station</t>
+          <t>KMP Mutiara Sentosa 2 Disebut Punya Sekoci dan Life Raft, Kenapa Penumpang Lompat ke Laut?Regional</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:22:43 +0700</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Le Minerale Surabaya Marathon 2026 diikuti 7.000 pelari, mengusung konsep City Run. Acara ini mendukung sport tourism dan hidrasi optimal dengan Le Minerale.</t>
+          <t>Peralatan keselamatan diklaim tidak dapat digunakan karena api dengan cepat menjalar ke bagian belakang KMP Mutiara Sentosa 2.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sportstyle/d-8604762/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station</t>
+          <t>https://surabaya.kompas.com/read/2026/08/05/114100578/kmp-mutiara-sentosa-2-disebut-punya-sekoci-dan-life-raft-kenapa-penumpang?source=headline</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station-1785892907123.png?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/hlZkBMsoqbiFwrId5Gsswi-eJMk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7201b327072.jpeg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Otomotif</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mourinho Ingin Vinicius Selalu Bahagia di Madrid</t>
+          <t>Chery Ungkap Penyebab Tiggo 8 CSH Berasap di Basement ICE BSDOtomotif</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Di tengah rumor Arsenal, Vinicius buka suara usai menjalani latihan pramusim bersama Real Madrid. Vinicius bilang Jose Mourinho ingin ia bahagia di Madrid.</t>
+          <t>Chery memastikan asap pada Tiggo 8 CSH di basement ICE BSD dipicu salah isi bahan bakar, bukan masalah baterai atau kelistrikan.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604655/mourinho-ingin-vinicius-selalu-bahagia-di-madrid</t>
+          <t>https://otomotif.kompas.com/read/2026/08/05/083200115/chery-ungkap-penyebab-tiggo-8-csh-berasap-di-basement-ice-bsd?source=headline</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/15/soccer-spain-rma-rso-1771110362377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/Yx1CJ4ytDmvGio3VxuAhvw7mP8g=/150x75:1050x675/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a7266800baa4.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho Langsung 'Babak Belur' di Pramusim Aston Villa</t>
+          <t>Penjelasan Kepala Desa soal Penyebab Jembatan Rusak Melengkung di KebumenRegional</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:30:00 +0700</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho baru pindah ke Aston Villa musim panas ini. Di laga pramusim, winger Argentina itu langsung babak belur.</t>
+          <t>Jembatan Sirnoboyo di Kebumen rusak parah akibat penurunan fondasi, mengancam akses vital Bonorowo-Mirit.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604654/alejandro-garnacho-langsung-babak-belur-di-pramusim-aston-villa</t>
+          <t>https://regional.kompas.com/read/2026/08/05/113256178/penjelasan-kepala-desa-soal-penyebab-jembatan-rusak-melengkung-di-kebumen?source=headline</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/alejandro-garnachoaston-villabg-pathum-vs-aston-villapramusim-aston-villa-1785881271654_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/YVYF8uUEiS7TviEWS2yVBg7NEhM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72b9d1b42f7.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Asosiasi Sepakbola Yordania Merasa Diperas FIFA!</t>
+          <t>Korlantas Bantah Kembali Berlalukan Tilang ManualNews</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Asosiasi Sepakbola Yordania (JFA) bikin pernyataan keras soal FIFA. Mereka mengaku diperas organisasi pimpinan Gianni Infantino tersebut.</t>
+          <t>Korlantas Polri membantah kabar penerapan kembali tilang manual dan kenaikan denda hingga 150 persen, tipenindakan tetap utamakan ETLE</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604652/asosiasi-sepakbola-yordania-merasa-diperas-fifa</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/11242771/korlantas-bantah-kembali-berlalukan-tilang-manual?source=headline</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/11/logo-fifa_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/KClVTsIhD8FAvYbBgwh17JRksb4=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/08/6a25ca9500411.jpeg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Semifinal Piala Presiden 2026 yang Aman dan Seru!</t>
+          <t>Kisah Keluarga di Padang Bertahan dari Banjir, Ban Pelampung Jadi Andalan Cari MakananRegional</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:30:00 +0700</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Semifinal Piala Presiden 2026 sudah digelar. Rangkaian pertandingan berjalan aman dan seru, sesuai yang diharapkan.</t>
+          <t>Saat banjir 2 meter merendam rumahnya, keluarga Yarman mengandalkan ban dalam bekas untuk mencari makanan dan bertahan hidup.</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604648/semifinal-piala-presiden-2026-yang-aman-dan-seru</t>
+          <t>https://regional.kompas.com/read/2026/08/05/111436278/kisah-keluarga-di-padang-bertahan-dari-banjir-ban-pelampung-jadi-andalan?source=headline</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-semifinal-piala-presiden-2026-antara-persib-vs-persija-di-stadion-kapten-i-wayan-dipta-gianyar-bali-selasa-482026-1785862146465.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/RcVt6y0zoU3CJ6RxmgNPLf80Qzk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ab031a7a1.jpeg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Megapolitan</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mohamed Salah Menuju Trabzonspor</t>
+          <t>1Saat Sampah ke Bantargebang Terus Berkurang, Krisis Diam-diam Menghantui Kampung PemulungNews</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mohamed Salah menuju Trabzonspor. Klub Turki itu mengonfirmasi bakal bernegosiasi dengan pemain asal Mesir tersebut.</t>
+          <t>Ribuan warga Ciketing Udik, Bantargebang, menggantungkan hidup dari sampah. Kini, pasokan berkurang dan penutupan TPA mengancam masa depan mereka.</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604653/mohamed-salah-menuju-trabzonspor</t>
+          <t>https://megapolitan.kompas.com/read/2026/08/05/09303171/saat-sampah-ke-bantargebang-terus-berkurang-krisis-diam-diam-menghantui?source=terpopuler</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/mohamed-salah-1781054944371_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/W85u3qy33e0n8iASk-DCYVTwYVA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72980672081.jpeg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Edisi Kedua! Ajang Lari Rekreasional di DIY Segera Digelar Lagi</t>
+          <t>2Pengaruh Politik Jokowi Masih BesarNews</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:15:25 +0700</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ajang lari rekresional di Daerah Istimewa Yogyakarta (DIY) edisi kedua, Jogja Run'nShine, akan kembali digelar. Inovasi dihadirkan dari evaluasi edisi perdana.</t>
+          <t>Pengaruh politik memang tidak identik dengan kekuasaan formal. Kekuasaan Jokowi sebagai presiden telah selesai, sedangkan pengaruhnya belum selesai.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604536/edisi-kedua-ajang-lari-rekreasional-di-diy-segera-digelar-lagi</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/09290001/pengaruh-politik-jokowi-masih-besar?source=terpopuler</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jogja-runnshine-1785853110207_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/t7YT9gwrldsaAdH_b9qHJv1aBYw=/311x90:996x547/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/02/6a6f1955bc8cd.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Surabaya</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FIFA Bantah Infantino 'Dicuekin' Donald Trump</t>
+          <t>3Kepala Daerah Tersandung Korupsi Tak Bisa Langsung Dipecat, Tito: Bukan Anak Kemarin SoreRegional</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:00:18 +0700</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ada kabar Gianni Infantino tak bisa menghubungi Donald Trump usai wacana menjual saham Piala Dunia batal. FIFA membantah laporan tersebut.</t>
+          <t>Mendagri Tito Karnavian menjelaskan bahwa pemberhentian kepala daerah korup tidak bisa langsung dilakukan karena ada mekanisme prosedural yang harus dilalui.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604623/fifa-bantah-infantino-dicuekin-donald-trump</t>
+          <t>https://surabaya.kompas.com/read/2026/08/05/103939478/kepala-daerah-tersandung-korupsi-tak-bisa-langsung-dipecat-tito-bukan-anak?source=terpopuler</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/trump-tampak-didampingi-presiden-fifa-gianni-infantino-saat-berbicara-dalam-acara-fifa-yang-digelar-di-trump-tower-new-york-ci-1784348679880_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/5lwMUiwTHlyFZAMnUTExWLoG1Tw=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a59c24c08.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Bernardo Silva: Saat Madrid Memanggil, Mustahil Bilang Tidak</t>
+          <t>4Perputaran Uang Judi Online Tembus Rp 86,8 Triliun, PPATK: Modus Pelaku Makin CanggihMoney</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 04:00:04 +0700</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Bernardo Silva tidak berpikir dua kali saat mendapat tawaran dari Real Madrid. Menolak Madrid diakui Silva merupakan hal yang mustahil.</t>
+          <t>PPATK laporkan pelaku judi online makin camggih cara beroperasinya.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604621/bernardo-silva-saat-madrid-memanggil-mustahil-bilang-tidak</t>
+          <t>https://money.kompas.com/read/2026/08/05/094834426/perputaran-uang-judi-online-tembus-rp-868-triliun-ppatk-modus-pelaku-makin?source=terpopuler</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/bernardo-silva-1759772326382_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/-zA-jcUu2Y7LQxrwFToq04J-o04=/112x402:1010x1000/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a7299c6e53ea.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hasil Uji Coba: AS Roma Gilas Newport County 4-1</t>
+          <t>5Banding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 MiliarNews</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 03:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AS Roma mengalahkan Newport County dalam laga uji coba pramusim. Serigala Ibu Kota menang telak 4-1.</t>
+          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604646/hasil-uji-coba-as-roma-gilas-newport-county-4-1</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=terpopuler</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/as-romanewport-countylaga-pramusimlaga-uji-cobasantiago-castro-1785873342683_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Otomotif</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>'Klan' Kluivert Berlanjut</t>
+          <t>Komparasi Changan Nevo Q05 Vs Jaecoo J5 EV, Pilih Mana?Otomotif</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 02:00:23 +0700</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shane Kluivert debut di tim utama Barcelona. Shane lanjutkan jejak sang ayah Patrick Kluivert yang 28 tahun lalu juga main buat Barca.</t>
+          <t>Duel dua SUV listrik Rp 300 jutaan. Simak perbandingan desain, fitur, baterai, jarak tempuh, performa, hingga harga.</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604292/klan-kluivert-berlanjut</t>
+          <t>https://otomotif.kompas.com/read/2026/08/05/110200815/komparasi-changan-nevo-q05-vs-jaecoo-j5-ev-pilih-mana-?source=sorotan</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/shane-kluivert-1785831287018.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/3f4DFDwFteW4JUX_XX4XDaXxMD0=/0x0:1264x843/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a72908834b4a.png</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Piala Presiden 2026: Merawat Sportivitas, Menjaga Integritas</t>
+          <t>Apa Itu Friend Bombing? Ini Ciri dan Cara MenyikapinyaLifestyle</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:26:47 +0700</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Piala Presiden 2026 diharapkan mampu menjadi teladan penyelenggaraan pertandingan resmi sepakbola nasional.</t>
+          <t>Friend-bombing menyerupai love-bombing, tetapi terjadi dalam ranah persahabatan sehingga sering kali lebih sulit disadari sejak awal.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604636/piala-presiden-2026-merawat-sportivitas-menjaga-integritas</t>
+          <t>https://lifestyle.kompas.com/read/2026/08/05/110100820/apa-itu-friend-bombing-ini-ciri-dan-cara-menyikapinya?source=sorotan</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/piala-presiden-2026-1785863698077_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/EoPbroI6It3crom92-hL9IYHOGA=/0x0:1417x945/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/29/697b90e878546.jpeg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Berita Utama</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Terus Kejar Guimaraes, Arsenal Negosiasi Langsung dengan Newcastle</t>
+          <t>Tren Baru di China, Orangtua Rela Bayar Rp 34 Juta agar Anak Jadi "Warren Buffett Kecil"Tren</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:00:23 +0700</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Arsenal kini tengah bernegosiasi langsung dengan Newcastle United. Ini upaya lanjutan The Gunners untuk mendapatkan Bruno Guimaraes.</t>
+          <t>Orangtua di China rela membayar Rp 34 juta untuk kursus finansial agar anak menjadi “Warren Buffett kecil”. Apa saja yang dipelajari anak-anak?</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604610/terus-kejar-guimaraes-arsenal-negosiasi-langsung-dengan-newcastle</t>
+          <t>https://www.kompas.com/tren/read/2026/08/05/110000965/tren-baru-di-china-orangtua-rela-bayar-rp-34-juta-agar-anak-jadi-warren?source=sorotan</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/bruno-guimaraes-1783531838994_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/t6-jEBcH9eEWOjfSeuph37-AxtU=/0x0:4411x2941/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71bc5105128.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PSSI Ikrarkan Dukungan ke Gianni Infantino Terus Pimpin FIFA</t>
+          <t>OJK Tindak 15 Perusahaan Pialang Asuransi Ilegal, Sebagian Masuk Tahap SidangMoney</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:30:00 +0700</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan dukungannya ke Gianni Infantino. FIFA, di bawah pimpinannya, disebut membantu Indonesia.</t>
+          <t>OJK menemukan 15 pialang asuransi ilegal dan telah melakukan penindakan hukum. Langkah ini diikuti penguatan pengawasan melalui QR Code STDD.</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604633/pssi-ikrarkan-dukungan-ke-gianni-infantino-terus-pimpin-fifa</t>
+          <t>https://money.kompas.com/read/2026/08/05/111000226/ojk-tindak-15-perusahaan-pialang-asuransi-ilegal-sebagian-masuk-tahap-sidang?source=sorotan</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/23/gianni-infantino-erick-thohir_169.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/YxKhv82UZiNeBll_taObKpFfJPg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/01/23/697329f06af52.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Emmanuel Macron Dukung UEFA Lawan Gianni Infantino</t>
+          <t>Indra Bekti Turun Berat Badan hingga 10 Kg, Kurangi Nasi dan RotiHype</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:30 +0700</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Presiden Prancis Emmanuel Macron diketahui dukung UEFA untuk melawan Presiden FIFA Gianni Infantino. Mulai ada campur tangan politik negara-negara besar, nih!</t>
+          <t>Indra Bekti berhasil menurunkan 10 kg berat badan berkat pola hidup sehat, mengurangi nasi dan makanan tinggi karbohidrat. Ia kini merasa lebih nyaman dan sehat.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604322/emmanuel-macron-dukung-uefa-lawan-gianni-infantino</t>
+          <t>https://entertainment.kompas.com/read/2026/08/05/105301166/indra-bekti-turun-berat-badan-hingga-10-kg-kurangi-nasi-dan-roti?source=sorotan</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/presiden-prancis-emmanuel-macron-1754969579570.jpeg?w=360&amp;q=90</t>
+          <t>https://asset.kompas.com/crops/HgKxpJUQrKNcgGV8Mee8gw7wU2A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/05/6a72ace08557d.jpeg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Kompas</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Megapolitan</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HeadlineBanding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 Miliar</t>
+          <t>News51 detik laluPria Korban Mutilasi di Depok: Kaki Dibuang ke Sungai, Badan Dibungkus Karung Beras</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7603,17 +7671,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+          <t>Dalam pemeriksaan polisi, pelaku yang bernama Saepul (26) mengaku melukai perut dan leher korban, Kunaefi (51), sebelum melakukan tindakan mutilasi.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=headline</t>
+          <t>https://megapolitan.kompas.com/read/2026/08/05/12172651/pria-korban-mutilasi-di-depok-kaki-dibuang-ke-sungai-badan-dibungkus</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+          <t>https://asset.kompas.com/crops/bYR6Jt-cK__Cvk6yd7suhr9dYl8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72c030387e5.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -7625,12 +7693,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>BPS: Pertumbuhan Ekonomi Indonesia 5,29 Persen pada Kuartal II 2026Money</t>
+          <t>Regional1 menit laluTrenggiling Masuk Permukiman di Lereng Gunung Karang, Warga Serahkan ke BPBD Pandeglang</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7645,17 +7713,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>BPS mencatat pertumbuhan ekonomi Indonesia di Kuartal II 2026 mencapai 5,29% (yoy). Sektor pengadaan listrik &amp; gas memimpin, meski pertambangan terkontraksi.</t>
+          <t>Seekor trenggiling ditemukan berkeliaran di permukiman lereng Gunung Karang, Pandeglang. Satwa dilindungi itu kemudian dievakuasi BKSDA.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/114132726/bps-pertumbuhan-ekonomi-indonesia-529-persen-pada-kuartal-ii-2026?source=headline</t>
+          <t>https://regional.kompas.com/read/2026/08/05/121711178/trenggiling-masuk-permukiman-di-lereng-gunung-karang-warga-serahkan-ke-bpbd</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/tO31vuJAGVU9FYHw3s-ozVN7cRc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/08/05/689187ab3472b.jpeg</t>
+          <t>https://asset.kompas.com/crops/BxGPdSCq9-jU04or7BRoih8cgV4=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bfc3e5d6e.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -7667,12 +7735,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 Disebut Punya Sekoci dan Life Raft, Kenapa Penumpang Lompat ke Laut?Regional</t>
+          <t>Money4 menit laluBalik Untung dari Rugi, Kimia Farma (KAEF) Cetak Laba Bersih Rp 54 Miliar</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7687,17 +7755,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Peralatan keselamatan diklaim tidak dapat digunakan karena api dengan cepat menjalar ke bagian belakang KMP Mutiara Sentosa 2.</t>
+          <t>Kimia Farma (KAEF) sukses berbalik untung Rp 54,07 miliar pada Semester I-2026 dari rugi sebelumnya, didorong penguatan fundamental dan efisiensi. Ini Berita Baik!</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/08/05/114100578/kmp-mutiara-sentosa-2-disebut-punya-sekoci-dan-life-raft-kenapa-penumpang?source=headline</t>
+          <t>https://money.kompas.com/read/2026/08/05/121400026/balik-untung-dari-rugi-kimia-farma-kaef-cetak-laba-bersih-rp-54-miliar</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/hlZkBMsoqbiFwrId5Gsswi-eJMk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7201b327072.jpeg</t>
+          <t>https://asset.kompas.com/crops/7goGruQRBbllhejL1KbWUyjtVjU=/417x64:1183x575/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/04/30/69f2ee65aa8a4.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -7709,12 +7777,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Chery Ungkap Penyebab Tiggo 8 CSH Berasap di Basement ICE BSDOtomotif</t>
+          <t>News5 menit laluKPK Ajukan Banding atas Vonis Gubernur Riau Abdul Wahid dkk</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7729,17 +7797,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Chery memastikan asap pada Tiggo 8 CSH di basement ICE BSD dipicu salah isi bahan bakar, bukan masalah baterai atau kelistrikan.</t>
+          <t>KPK ajukan banding atas vonis dua tahun bui terhadap Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa kasus korupsi lainnya.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/083200115/chery-ungkap-penyebab-tiggo-8-csh-berasap-di-basement-ice-bsd?source=headline</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/12132111/kpk-ajukan-banding-atas-vonis-gubernur-riau-abdul-wahid-dkk</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/Yx1CJ4ytDmvGio3VxuAhvw7mP8g=/150x75:1050x675/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a7266800baa4.jpg</t>
+          <t>https://asset.kompas.com/crops/lPdw0OjDmf-mtI5W44hEX1Buz4Q=/97x0:1057x640/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/19/6944ed9e2dd8c.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -7751,12 +7819,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Berita Utama</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Penjelasan Kepala Desa soal Penyebab Jembatan Rusak Melengkung di KebumenRegional</t>
+          <t>Cek fakta6 menit lalu[HOAKS] Video Purbaya Bagikan Dana Bantuan Rp 50 Juta untuk 10 Orang</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7771,17 +7839,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Jembatan Sirnoboyo di Kebumen rusak parah akibat penurunan fondasi, mengancam akses vital Bonorowo-Mirit.</t>
+          <t>Beredar video yang menampilkan Menkeu Purbaya membagikan dana bantuan Rp 50 juta untuk 10 orang. Narasi itu hoaks.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/113256178/penjelasan-kepala-desa-soal-penyebab-jembatan-rusak-melengkung-di-kebumen?source=headline</t>
+          <t>https://www.kompas.com/cekfakta/read/2026/08/05/121200382/-hoaks-video-purbaya-bagikan-dana-bantuan-rp-50-juta-untuk-10-orang</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/YVYF8uUEiS7TviEWS2yVBg7NEhM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72b9d1b42f7.jpg</t>
+          <t>https://asset.kompas.com/crops/g-VvO8HqZ-6UxzHMfISQFtcPYhQ=/0x36:1600x1103/1200x675/data/photo/2026/08/04/6a7186d6071ef.jpeg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -7793,12 +7861,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Otomotif</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Korlantas Bantah Kembali Berlalukan Tilang ManualNews</t>
+          <t>Otomotif6 menit laluBYD Ingatkan Dampak Pajak Mobil Listrik terhadap Adopsi EV</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7813,17 +7881,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Korlantas Polri membantah kabar penerapan kembali tilang manual dan kenaikan denda hingga 150 persen, tipenindakan tetap utamakan ETLE</t>
+          <t>BYD khawatir pengenaan pajak mobil listrik terlalu cepat dapat menghambat tren positif elektrifikasi di Indonesia.</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11242771/korlantas-bantah-kembali-berlalukan-tilang-manual?source=headline</t>
+          <t>https://otomotif.kompas.com/read/2026/08/05/121200315/byd-ingatkan-dampak-pajak-mobil-listrik-terhadap-adopsi-ev</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/KClVTsIhD8FAvYbBgwh17JRksb4=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/08/6a25ca9500411.jpeg</t>
+          <t>https://asset.kompas.com/crops/mmgsH0plmX9Yekj5DwbJA3VJohE=/375x233:3657x2420/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a725367f1190.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7835,12 +7903,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Berita Utama</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Kisah Keluarga di Padang Bertahan dari Banjir, Ban Pelampung Jadi Andalan Cari MakananRegional</t>
+          <t>Properti7 menit laluBUMN Karya Ini Tawarkan Properti Siap Huni, Harga Mulai Rp 300 Jutaan</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7855,17 +7923,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Saat banjir 2 meter merendam rumahnya, keluarga Yarman mengandalkan ban dalam bekas untuk mencari makanan dan bertahan hidup.</t>
+          <t>Direktur Utama PT HK Realtindo, Ekwan Hadyanto, menegaskan, mayoritas proyek yang dihadirkan merupakan hunian siap huni.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/111436278/kisah-keluarga-di-padang-bertahan-dari-banjir-ban-pelampung-jadi-andalan?source=headline</t>
+          <t>https://www.kompas.com/properti/read/2026/08/05/121136421/bumn-karya-ini-tawarkan-properti-siap-huni-harga-mulai-rp-300-jutaan</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/RcVt6y0zoU3CJ6RxmgNPLf80Qzk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ab031a7a1.jpeg</t>
+          <t>https://asset.kompas.com/crops/aC6ZIxrDHBj9IR3J0dWKRmVIF2A=/432x0:3942x2340/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/04/25/69ecb9a662099.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -7877,12 +7945,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Megapolitan</t>
+          <t>Berita Utama</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1Saat Sampah ke Bantargebang Terus Berkurang, Krisis Diam-diam Menghantui Kampung PemulungNews</t>
+          <t>Global7 menit lalu80 Persen Stok Rudal Pencegat AS Terkuras, Trump Pilih Batal Serang Iran</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7897,17 +7965,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ribuan warga Ciketing Udik, Bantargebang, menggantungkan hidup dari sampah. Kini, pasokan berkurang dan penutupan TPA mengancam masa depan mereka.</t>
+          <t>Militer AS dilaporkan telah menghabiskan hampir 80 persen amunisi pencegat untuk sistem pertahanan udara utama THAAD.</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://megapolitan.kompas.com/read/2026/08/05/09303171/saat-sampah-ke-bantargebang-terus-berkurang-krisis-diam-diam-menghantui?source=terpopuler</t>
+          <t>https://www.kompas.com/global/read/2026/08/05/121100270/80-persen-stok-rudal-pencegat-as-terkuras-trump-pilih-batal-serang-iran</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/W85u3qy33e0n8iASk-DCYVTwYVA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72980672081.jpeg</t>
+          <t>https://asset.kompas.com/crops/DC_ROqcsEzmU1c0UipGQAnNR7AI=/0x0:1997x1331/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/02/03/69817653a6f21.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -7919,12 +7987,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Denpasar</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2Pengaruh Politik Jokowi Masih BesarNews</t>
+          <t>Regional8 menit laluBNN Bali Bongkar Paket Narkoba Jaringan Kamboja, Disamarkan dalam Knalpot Bekas</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7939,17 +8007,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pengaruh politik memang tidak identik dengan kekuasaan formal. Kekuasaan Jokowi sebagai presiden telah selesai, sedangkan pengaruhnya belum selesai.</t>
+          <t>BNN Bali bongkar jaringan narkoba Kamboja. Pria berinisial GAS ditangkap setelah menerima paket narkoba yang disamarkan dalam knalpot motor bekas.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/09290001/pengaruh-politik-jokowi-masih-besar?source=terpopuler</t>
+          <t>https://denpasar.kompas.com/read/2026/08/05/121034678/bnn-bali-bongkar-paket-narkoba-jaringan-kamboja-disamarkan-dalam-knalpot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/t7YT9gwrldsaAdH_b9qHJv1aBYw=/311x90:996x547/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/02/6a6f1955bc8cd.jpg</t>
+          <t>https://asset.kompas.com/crops/mFzxe5sm_MIydDJW_RxfAyOBCP8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bca8504da.jpeg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -7961,12 +8029,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Money</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3Kepala Daerah Tersandung Korupsi Tak Bisa Langsung Dipecat, Tito: Bukan Anak Kemarin SoreRegional</t>
+          <t>Dalam Semangat Kemerdekaan, Mandiri Donor Darah Kembali Hadir Dukung Ketersediaan Darah Nasional</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7981,17 +8049,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mendagri Tito Karnavian menjelaskan bahwa pemberhentian kepala daerah korup tidak bisa langsung dilakukan karena ada mekanisme prosedural yang harus dilalui.</t>
+          <t>Menyambut HUT ke-81 RI dan usia 28 tahun melayani negeri, Bank Mandiri menggelar aksi 'Mandiri Donor Darah' serentak di 12 region se-Indonesia.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/08/05/103939478/kepala-daerah-tersandung-korupsi-tak-bisa-langsung-dipecat-tito-bukan-anak?source=terpopuler</t>
+          <t>https://money.kompas.com/read/2026/08/05/111451426/dalam-semangat-kemerdekaan-mandiri-donor-darah-kembali-hadir-dukung</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/5lwMUiwTHlyFZAMnUTExWLoG1Tw=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a59c24c08.jpg</t>
+          <t>https://asset.kompas.com/crops/mFkRD0H1S6NeT7co-aFE7piNn7o=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72b60386b45.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -8008,7 +8076,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>4Perputaran Uang Judi Online Tembus Rp 86,8 Triliun, PPATK: Modus Pelaku Makin CanggihMoney</t>
+          <t>Komisi IV DPR RI Apresiasi Langkah Mentan Amran Bongkar Dugaan Mafia Beras Fortifikasi</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8023,17 +8091,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PPATK laporkan pelaku judi online makin camggih cara beroperasinya.</t>
+          <t>Anggota Komisi IV DPR RI Endang S Tohari menilai praktik pengoplosan beras fortifikasi merupakan kejahatan serius yang tidak dapat ditoleransi.</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/094834426/perputaran-uang-judi-online-tembus-rp-868-triliun-ppatk-modus-pelaku-makin?source=terpopuler</t>
+          <t>https://money.kompas.com/read/2026/08/05/104408026/komisi-iv-dpr-ri-apresiasi-langkah-mentan-amran-bongkar-dugaan-mafia-beras</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/-zA-jcUu2Y7LQxrwFToq04J-o04=/112x402:1010x1000/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a7299c6e53ea.jpg</t>
+          <t>https://asset.kompas.com/crops/B0W3J3lt6QD6y9DoQh2yxyGlFqI=/0x134:1599x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72a85e917e8.jpeg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -8050,7 +8118,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>5Banding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 MiliarNews</t>
+          <t>Mendagri: Integritas Kepala Daerah Jadi Kunci Wujudkan Tata Kelola Pemerintahan yang Bersih dan Akuntabel</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8065,17 +8133,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+          <t>Mendagri Tito menekankan, setiap kepala daerah dituntut untuk menjaga prinsip-prinsip antikorupsi serta tidak tergoda melakukan pelanggaran hukum.</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=terpopuler</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/10061371/mendagri-integritas-kepala-daerah-jadi-kunci-wujudkan-tata-kelola</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+          <t>https://asset.kompas.com/crops/h9MDSqwCb1sZpxTWESiR3d6HydQ=/0x0:1599x1066/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a4a9bd443.jpeg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -8087,12 +8155,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Nasional</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Komparasi Changan Nevo Q05 Vs Jaecoo J5 EV, Pilih Mana?Otomotif</t>
+          <t>Brankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan Rakyat</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8107,17 +8175,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Duel dua SUV listrik Rp 300 jutaan. Simak perbandingan desain, fitur, baterai, jarak tempuh, performa, hingga harga.</t>
+          <t>Perang melawan korupsi seharusnya tidak dipahami semata sebagai agenda penegakan hukum.</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/110200815/komparasi-changan-nevo-q05-vs-jaecoo-j5-ev-pilih-mana-?source=sorotan</t>
+          <t>https://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat?source=kolom</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/3f4DFDwFteW4JUX_XX4XDaXxMD0=/0x0:1264x843/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a72908834b4a.png</t>
+          <t>https://asset.kompas.com/crops/BxG7N1wef22vGuge6xZA46tILF0=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/27/6a66843ea3864.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -8126,722 +8194,8 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Lifestyle</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Apa Itu Friend Bombing? Ini Ciri dan Cara MenyikapinyaLifestyle</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Friend-bombing menyerupai love-bombing, tetapi terjadi dalam ranah persahabatan sehingga sering kali lebih sulit disadari sejak awal.</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>https://lifestyle.kompas.com/read/2026/08/05/110100820/apa-itu-friend-bombing-ini-ciri-dan-cara-menyikapinya?source=sorotan</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/EoPbroI6It3crom92-hL9IYHOGA=/0x0:1417x945/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/29/697b90e878546.jpeg</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Berita Utama</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Tren Baru di China, Orangtua Rela Bayar Rp 34 Juta agar Anak Jadi "Warren Buffett Kecil"Tren</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Orangtua di China rela membayar Rp 34 juta untuk kursus finansial agar anak menjadi “Warren Buffett kecil”. Apa saja yang dipelajari anak-anak?</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>https://www.kompas.com/tren/read/2026/08/05/110000965/tren-baru-di-china-orangtua-rela-bayar-rp-34-juta-agar-anak-jadi-warren?source=sorotan</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/t6-jEBcH9eEWOjfSeuph37-AxtU=/0x0:4411x2941/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71bc5105128.jpg</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Money</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>OJK Tindak 15 Perusahaan Pialang Asuransi Ilegal, Sebagian Masuk Tahap SidangMoney</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>OJK menemukan 15 pialang asuransi ilegal dan telah melakukan penindakan hukum. Langkah ini diikuti penguatan pengawasan melalui QR Code STDD.</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>https://money.kompas.com/read/2026/08/05/111000226/ojk-tindak-15-perusahaan-pialang-asuransi-ilegal-sebagian-masuk-tahap-sidang?source=sorotan</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/YxKhv82UZiNeBll_taObKpFfJPg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/01/23/697329f06af52.jpg</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Indra Bekti Turun Berat Badan hingga 10 Kg, Kurangi Nasi dan RotiHype</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Indra Bekti berhasil menurunkan 10 kg berat badan berkat pola hidup sehat, mengurangi nasi dan makanan tinggi karbohidrat. Ia kini merasa lebih nyaman dan sehat.</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>https://entertainment.kompas.com/read/2026/08/05/105301166/indra-bekti-turun-berat-badan-hingga-10-kg-kurangi-nasi-dan-roti?source=sorotan</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/HgKxpJUQrKNcgGV8Mee8gw7wU2A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/05/6a72ace08557d.jpeg</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Berita Utama</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Cek fakta17 detik lalu[HOAKS] Video Purbaya Bagikan Dana Bantuan Rp 50 Juta untuk 10 Orang</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Beredar video yang menampilkan Menkeu Purbaya membagikan dana bantuan Rp 50 juta untuk 10 orang. Narasi itu hoaks.</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>https://www.kompas.com/cekfakta/read/2026/08/05/121200382/-hoaks-video-purbaya-bagikan-dana-bantuan-rp-50-juta-untuk-10-orang</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/g-VvO8HqZ-6UxzHMfISQFtcPYhQ=/0x36:1600x1103/1200x675/data/photo/2026/08/04/6a7186d6071ef.jpeg</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Otomotif</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Otomotif17 detik laluBYD Ingatkan Dampak Pajak Mobil Listrik terhadap Adopsi EV</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>BYD khawatir pengenaan pajak mobil listrik terlalu cepat dapat menghambat tren positif elektrifikasi di Indonesia.</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/121200315/byd-ingatkan-dampak-pajak-mobil-listrik-terhadap-adopsi-ev</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/mmgsH0plmX9Yekj5DwbJA3VJohE=/375x233:3657x2420/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a725367f1190.jpg</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Berita Utama</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Properti41 detik laluBUMN Karya Ini Tawarkan Properti Siap Huni, Harga Mulai Rp 300 Jutaan</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Direktur Utama PT HK Realtindo, Ekwan Hadyanto, menegaskan, mayoritas proyek yang dihadirkan merupakan hunian siap huni.</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>https://www.kompas.com/properti/read/2026/08/05/121136421/bumn-karya-ini-tawarkan-properti-siap-huni-harga-mulai-rp-300-jutaan</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/aC6ZIxrDHBj9IR3J0dWKRmVIF2A=/432x0:3942x2340/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/04/25/69ecb9a662099.jpg</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Berita Utama</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Global1 menit lalu80 Persen Stok Rudal Pencegat AS Terkuras, Trump Pilih Batal Serang Iran</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Militer AS dilaporkan telah menghabiskan hampir 80 persen amunisi pencegat untuk sistem pertahanan udara utama THAAD.</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>https://www.kompas.com/global/read/2026/08/05/121100270/80-persen-stok-rudal-pencegat-as-terkuras-trump-pilih-batal-serang-iran</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/DC_ROqcsEzmU1c0UipGQAnNR7AI=/0x0:1997x1331/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/02/03/69817653a6f21.jpg</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Denpasar</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Regional2 menit laluBNN Bali Bongkar Paket Narkoba Jaringan Kamboja, Disamarkan dalam Knalpot Bekas</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>BNN Bali bongkar jaringan narkoba Kamboja. Pria berinisial GAS ditangkap setelah menerima paket narkoba yang disamarkan dalam knalpot motor bekas.</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>https://denpasar.kompas.com/read/2026/08/05/121034678/bnn-bali-bongkar-paket-narkoba-jaringan-kamboja-disamarkan-dalam-knalpot</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/mFzxe5sm_MIydDJW_RxfAyOBCP8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bca8504da.jpeg</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Berita Utama</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Properti7 menit lalu7 Bangunan Penjara Paling Overkapasitas di RI</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Daftar 7 bangunan penjara terpadat di Indonesia berdasarkan rasio jumlah penghuni dan kapasitasnya.</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>https://www.kompas.com/properti/read/2026/08/05/120523321/7-bangunan-penjara-paling-overkapasitas-di-ri</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/6gl5VWOznzCxBO4GgcZsWdpXC_8=/0x0:960x640/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/06/22/6a3921c8d4c85.jpg</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Regional</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Regional8 menit laluApindo Bongkar Penyebab PHK Massal Tambang Kaltim, RKAB-Tekanan Global Disorot</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Apindo mengungkap gelombang PHK di sektor tambang Kaltim dipicu RKAB yang belum tuntas, pemangkasan kuota produksi, hingga tekanan ekonomi global.</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>https://regional.kompas.com/read/2026/08/05/120401478/apindo-bongkar-penyebab-phk-massal-tambang-kaltim-rkab-tekanan-global</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/AzQSgHHBPhJuBQerJvYdWoGTIZ0=/0x807:1920x2087/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bee36413e.jpg</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Bola</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Bola8 menit laluWilshere Punya Pesan untuk Lewis-Skelly di Tengah Rumor Transfer ke MU</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Pemain muda Arsenal, Myles Lewis-Skelly  diisukan tengah jadi incaran klub Liga Inggris, Manchester United di bursa transfer.</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>https://bola.kompas.com/read/2026/08/05/12035258/wilshere-punya-pesan-untuk-lewis-skelly-di-tengah-rumor-transfer-ke-mu</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/lneFfSI90hr2uZ0CkiybCs9a9X4=/72x0:806x489/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2025/01/29/679958d6dd5b9.jpg</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Megapolitan</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>News9 menit laluNiat "Resign", Pekerja Bank Keliling di Tangerang Malah Dianiaya dan Disekap Bosnya</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Sebelum dugaan penganiayaan memuncak pada Selasa (28/7/2026), korban PG sempat mengabari istrinya lewat pesan singkat karena merasa jiwanya terancam.</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>https://megapolitan.kompas.com/read/2026/08/05/12033681/niat-resign-pekerja-bank-keliling-di-tangerang-malah-dianiaya-dan-disekap</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/gHRVJfPAf7MhQDx1nLckk-CEy1Y=/62x0:622x373/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2020/10/14/5f86cca13c2ef.jpeg</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Nasional</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>News10 menit laluBrankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan Rakyat</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Perang melawan korupsi seharusnya tidak dipahami semata sebagai agenda penegakan hukum.</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/BxG7N1wef22vGuge6xZA46tILF0=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/27/6a66843ea3864.jpg</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Money</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Dalam Semangat Kemerdekaan, Mandiri Donor Darah Kembali Hadir Dukung Ketersediaan Darah Nasional</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Menyambut HUT ke-81 RI dan usia 28 tahun melayani negeri, Bank Mandiri menggelar aksi 'Mandiri Donor Darah' serentak di 12 region se-Indonesia.</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>https://money.kompas.com/read/2026/08/05/111451426/dalam-semangat-kemerdekaan-mandiri-donor-darah-kembali-hadir-dukung</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/mFkRD0H1S6NeT7co-aFE7piNn7o=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72b60386b45.jpg</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Money</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Komisi IV DPR RI Apresiasi Langkah Mentan Amran Bongkar Dugaan Mafia Beras Fortifikasi</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Anggota Komisi IV DPR RI Endang S Tohari menilai praktik pengoplosan beras fortifikasi merupakan kejahatan serius yang tidak dapat ditoleransi.</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>https://money.kompas.com/read/2026/08/05/104408026/komisi-iv-dpr-ri-apresiasi-langkah-mentan-amran-bongkar-dugaan-mafia-beras</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/B0W3J3lt6QD6y9DoQh2yxyGlFqI=/0x134:1599x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72a85e917e8.jpeg</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Nasional</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Mendagri: Integritas Kepala Daerah Jadi Kunci Wujudkan Tata Kelola Pemerintahan yang Bersih dan Akuntabel</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Mendagri Tito menekankan, setiap kepala daerah dituntut untuk menjaga prinsip-prinsip antikorupsi serta tidak tergoda melakukan pelanggaran hukum.</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/10061371/mendagri-integritas-kepala-daerah-jadi-kunci-wujudkan-tata-kelola</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/h9MDSqwCb1sZpxTWESiR3d6HydQ=/0x0:1599x1066/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a4a9bd443.jpeg</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kompas</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H218"/>
+  <autoFilter ref="A1:H201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -482,28 +482,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cara masuk Polstat STIS 2026: Syarat, jurusan, tahapan seleksi, dan tips lolos</t>
+          <t>Pemkab Jayapura selidiki gangguan kesehatan siswa usai santap MBG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:14:57 +0700</t>
+          <t>Wed, 05 Aug 2026 12:22:57 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Politeknik Statistika STIS (Polstat STIS) menjadi salah satu sekolah kedinasan yang paling diminati setiap tahun karena ...</t>
+          <t>ANTARA - Pemerintah Kabupaten Jayapura bersama aparat terkait menyelidiki penyebab gangguan kesehatan yang dialami 80 ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680547/cara-masuk-polstat-stis-2026-syarat-jurusan-tahapan-seleksi-dan-tips-lolos</t>
+          <t>https://www.antaranews.com/video/5680536/pemkab-jayapura-selidiki-gangguan-kesehatan-siswa-usai-santap-mbg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/01/14/BPS2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKAB-JAYAPURA-SELIDIKI-GANGGUAN-KESEHATAN-SISWA-USAI-SANTAP-MBG.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -520,28 +520,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jenis susu yang cocok untuk pengidap diabetes</t>
+          <t>Pemkot Jakarta Barat targetkan 18.531 siswa SD ikuti vaksinasi HPV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:13:41 +0700</t>
+          <t>Wed, 05 Aug 2026 12:20:29 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pengidap diabetes tetap dapat mengonsumsi susu, asalkan memilih jenis yang tepat dengan memperhatikan kandungan gula, ...</t>
+          <t>Siswa melakukan cek suhu sebelum vaksin Human Papillomavirus (HPV) di Sekolah Dasar Palmerah 09, Jakarta.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680545/jenis-susu-yang-cocok-untuk-pengidap-diabetes</t>
+          <t>https://www.antaranews.com/foto/5680552/pemkot-jakarta-barat-targetkan-18531-siswa-sd-ikuti-vaksinasi-hpv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/04/10/Screenshot_2022-04-10-11-11-42-39_copy_1024x683.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Vaksin-HPV-di-Jakarta-Barat-050826-RIV-1.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,28 +558,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kemendag: Camilan RI tembus pasar Arab Saudi, hasil penjajakan bisnis</t>
+          <t>Cara daftar PIP 2026, lengkap syarat, besar bantuan, dan cara cek penerima</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:12:59 +0700</t>
+          <t>Wed, 05 Aug 2026 12:18:05 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kementerian Perdagangan (Kemendag) menyebut salah satu produk camilan Indonesia berhasil menembus pasar Arab Saudi ...</t>
+          <t>Program Indonesia Pintar (PIP) 2026 kembali menjadi salah satu bantuan pendidikan yang dinantikan peserta didik dari ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680543/kemendag-camilan-ri-tembus-pasar-arab-saudi-hasil-penjajakan-bisnis</t>
+          <t>https://www.antaranews.com/berita/5680551/cara-daftar-pip-2026-lengkap-syarat-besar-bantuan-dan-cara-cek-penerima</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0942.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/pemberian-beasiswa-pip.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -596,28 +596,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus di kantor yang seru, lucu, dan bikin karyawan kompak</t>
+          <t>Cara masuk Polstat STIS 2026: Syarat, jurusan, tahapan seleksi, dan tips lolos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:11:11 +0700</t>
+          <t>Wed, 05 Aug 2026 12:14:57 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 semakin dekat. Selain menjadi ...</t>
+          <t>Politeknik Statistika STIS (Polstat STIS) menjadi salah satu sekolah kedinasan yang paling diminati setiap tahun karena ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680540/10-ide-lomba-17-agustus-di-kantor-yang-seru-lucu-dan-bikin-karyawan-kompak</t>
+          <t>https://www.antaranews.com/berita/5680547/cara-masuk-polstat-stis-2026-syarat-jurusan-tahapan-seleksi-dan-tips-lolos</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/InShot_20260622_143213404.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/14/BPS2.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,28 +634,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Momentum ekonomi di balik kunjungan PM Thailand ke Indonesia</t>
+          <t>Jenis susu yang cocok untuk pengidap diabetes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:10:26 +0700</t>
+          <t>Wed, 05 Aug 2026 12:13:41 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Perdana Menteri Thailand Anutin Charnvirakul yang tiba di Pangkalan Udara Halim Perdanakusuma pada Senin ...</t>
+          <t>Pengidap diabetes tetap dapat mengonsumsi susu, asalkan memilih jenis yang tepat dengan memperhatikan kandungan gula, ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680539/momentum-ekonomi-di-balik-kunjungan-pm-thailand-ke-indonesia</t>
+          <t>https://www.antaranews.com/berita/5680545/jenis-susu-yang-cocok-untuk-pengidap-diabetes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/04/10/Screenshot_2022-04-10-11-11-42-39_copy_1024x683.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -672,28 +672,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Karhutla di Gunung Bromo belum padam dengan luas lahan terbakar 10 ha</t>
+          <t>Kemendag: Camilan RI tembus pasar Arab Saudi, hasil penjajakan bisnis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:08:46 +0700</t>
+          <t>Wed, 05 Aug 2026 12:12:59 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kebakaran hutan dan lahan (karhutla) di Gunung Bromo, Jawa Timur belum padam dengan luas lahan yang terbakar ...</t>
+          <t>Kementerian Perdagangan (Kemendag) menyebut salah satu produk camilan Indonesia berhasil menembus pasar Arab Saudi ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680535/karhutla-di-gunung-bromo-belum-padam-dengan-luas-lahan-terbakar-10-ha</t>
+          <t>https://www.antaranews.com/berita/5680543/kemendag-camilan-ri-tembus-pasar-arab-saudi-hasil-penjajakan-bisnis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-09.18.39.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0942.jpeg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -710,28 +710,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WhatsApp hadirkan tiga pembaruan di layanan chat grup</t>
+          <t>10 ide lomba 17 Agustus di kantor yang seru, lucu, dan bikin karyawan kompak</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:07:58 +0700</t>
+          <t>Wed, 05 Aug 2026 12:11:11 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WhatsApp menghadirkan tiga pembaruan fitur di layanan chat grup, termasuk fitur jajak pendapat dan pembuat obrolan ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 semakin dekat. Selain menjadi ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680532/whatsapp-hadirkan-tiga-pembaruan-di-layanan-chat-grup</t>
+          <t>https://www.antaranews.com/berita/5680540/10-ide-lomba-17-agustus-di-kantor-yang-seru-lucu-dan-bikin-karyawan-kompak</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_104732163.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/InShot_20260622_143213404.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -748,28 +748,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Menjelajahi Situs Peninggalan Arkeologi Nasional Niuheliang di China</t>
+          <t>Momentum ekonomi di balik kunjungan PM Thailand ke Indonesia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:07:21 +0700</t>
+          <t>Wed, 05 Aug 2026 12:10:26 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Taman Situs Peninggalan Arkeologi Nasional Niuheliang dibangun di Situs Niuheliang, sebuah kompleks ritual dan ...</t>
+          <t>Perdana Menteri Thailand Anutin Charnvirakul yang tiba di Pangkalan Udara Halim Perdanakusuma pada Senin ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680529/menjelajahi-situs-peninggalan-arkeologi-nasional-niuheliang-di-china</t>
+          <t>https://www.antaranews.com/berita/5680539/momentum-ekonomi-di-balik-kunjungan-pm-thailand-ke-indonesia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000003_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -786,28 +786,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OJK Sulteng tingkatkan literasi keuangan nelayan melalui pelatihan</t>
+          <t>Karhutla di Gunung Bromo belum padam dengan luas lahan terbakar 10 ha</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:05:16 +0700</t>
+          <t>Wed, 05 Aug 2026 12:08:46 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) Provinsi Sulawesi Tengah (Sulteng) meningkatkan literasi dan inklusi keuangan bagi para ...</t>
+          <t>Kebakaran hutan dan lahan (karhutla) di Gunung Bromo, Jawa Timur belum padam dengan luas lahan yang terbakar ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680527/ojk-sulteng-tingkatkan-literasi-keuangan-nelayan-melalui-pelatihan</t>
+          <t>https://www.antaranews.com/berita/5680535/karhutla-di-gunung-bromo-belum-padam-dengan-luas-lahan-terbakar-10-ha</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-37.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-09.18.39.jpeg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -824,28 +824,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mengenal "clean eating" beserta manfaat dan hal yang perlu diwaspadai</t>
+          <t>WhatsApp hadirkan tiga pembaruan di layanan chat grup</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:03:28 +0700</t>
+          <t>Wed, 05 Aug 2026 12:07:58 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pola makan "clean eating" semakin dikenal seiring meningkatnya perhatian terhadap dampak konsumsi makanan ...</t>
+          <t>WhatsApp menghadirkan tiga pembaruan fitur di layanan chat grup, termasuk fitur jajak pendapat dan pembuat obrolan ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680525/mengenal-clean-eating-beserta-manfaat-dan-hal-yang-perlu-diwaspadai</t>
+          <t>https://www.antaranews.com/berita/5680532/whatsapp-hadirkan-tiga-pembaruan-di-layanan-chat-grup</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Gizi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_104732163.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -862,28 +862,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Menteri PPN: Pengembangan singkong di Indonesia miliki prospek besar</t>
+          <t>Menjelajahi Situs Peninggalan Arkeologi Nasional Niuheliang di China</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:59 +0700</t>
+          <t>Wed, 05 Aug 2026 12:07:21 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+          <t>Taman Situs Peninggalan Arkeologi Nasional Niuheliang dibangun di Situs Niuheliang, sebuah kompleks ritual dan ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680521/menteri-ppn-pengembangan-singkong-di-indonesia-miliki-prospek-besar</t>
+          <t>https://www.antaranews.com/berita/5680529/menjelajahi-situs-peninggalan-arkeologi-nasional-niuheliang-di-china</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/PPN-bappenas-lampung.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000003_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -900,28 +900,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Waspadai penyakit saat musim kemarau</t>
+          <t>OJK Sulteng tingkatkan literasi keuangan nelayan melalui pelatihan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:05:16 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Udara panas dan kekeringan saat musim kemarau memicu penyebaran sejumlah penyakit yang dapat membahayakan kesehatan. ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) Provinsi Sulawesi Tengah (Sulteng) meningkatkan literasi dan inklusi keuangan bagi para ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/infografik/5680467/waspadai-penyakit-saat-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5680527/ojk-sulteng-tingkatkan-literasi-keuangan-nelayan-melalui-pelatihan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260805-Waspadai-penyakit-saat-musim-kemarau_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-37.jpeg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -938,28 +938,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pemkab Banyumas upayakan operasional Trans Banyumas tetap berlanjut</t>
+          <t>Mengenal "clean eating" beserta manfaat dan hal yang perlu diwaspadai</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:59:47 +0700</t>
+          <t>Wed, 05 Aug 2026 12:03:28 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Banyumas, Jawa Tengah, terus mengupayakan keberlanjutan operasional Bus Buy The Service (BTS) ...</t>
+          <t>Pola makan "clean eating" semakin dikenal seiring meningkatnya perhatian terhadap dampak konsumsi makanan ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680519/pemkab-banyumas-upayakan-operasional-trans-banyumas-tetap-berlanjut</t>
+          <t>https://www.antaranews.com/berita/5680525/mengenal-clean-eating-beserta-manfaat-dan-hal-yang-perlu-diwaspadai</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001093491.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Gizi.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -976,28 +976,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KAI Layani 13.920 Ton Pupuk hingga Juli 2026, Perkuat Rantai Pasok Pertanian dan Ketahanan Pangan</t>
+          <t>Menteri PPN: Pengembangan singkong di Indonesia miliki prospek besar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:59:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:59 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat perannya dalam rantai pasok pertanian nasional melalui pelayanan ...</t>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680516/kai-layani-13920-ton-pupuk-hingga-juli-2026-perkuat-rantai-pasok-pertanian-dan-ketahanan-pangan</t>
+          <t>https://www.antaranews.com/berita/5680521/menteri-ppn-pengembangan-singkong-di-indonesia-miliki-prospek-besar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.38.20.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/PPN-bappenas-lampung.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1014,28 +1014,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pulau Untung Jawa gelar lomba meriahkan HUT Kemerdekaan RI</t>
+          <t>Waspadai penyakit saat musim kemarau</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:54:56 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:00 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pemerintah Kelurahan Pulau Untung Jawa resmi membuka rangkaian perlombaan dalam rangka memeriahkan Hari Ulang Tahun ...</t>
+          <t>Udara panas dan kekeringan saat musim kemarau memicu penyebaran sejumlah penyakit yang dapat membahayakan kesehatan. ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680512/pulau-untung-jawa-gelar-lomba-meriahkan-hut-kemerdekaan-ri</t>
+          <t>https://www.antaranews.com/infografik/5680467/waspadai-penyakit-saat-musim-kemarau</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a8ea0e8e-b465-4832-9dee-22d911db4b0e.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260805-Waspadai-penyakit-saat-musim-kemarau_1.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1052,28 +1052,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pemprov Papua bukukan transaksi UMK 50,65 persen melalui e-Katalog</t>
+          <t>Pemkab Banyumas upayakan operasional Trans Banyumas tetap berlanjut</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:54:36 +0700</t>
+          <t>Wed, 05 Aug 2026 11:59:47 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Papua melalui Biro Pengadaan Barang dan Jasa (BPBJ) setempat membukukan nilai transaksi Usaha ...</t>
+          <t>Pemerintah Kabupaten Banyumas, Jawa Tengah, terus mengupayakan keberlanjutan operasional Bus Buy The Service (BTS) ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680509/pemprov-papua-bukukan-transaksi-umk-5065-persen-melalui-e-katalog</t>
+          <t>https://www.antaranews.com/berita/5680519/pemkab-banyumas-upayakan-operasional-trans-banyumas-tetap-berlanjut</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002065915.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001093491.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1090,28 +1090,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5 tips positive parenting agar anak percaya diri</t>
+          <t>KAI Layani 13.920 Ton Pupuk hingga Juli 2026, Perkuat Rantai Pasok Pertanian dan Ketahanan Pangan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:53:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:59:00 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pola asuh positif atau positive parenting dinilai dapat membantu anak tumbuh dengan rasa aman, percaya diri, dan mampu ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat perannya dalam rantai pasok pertanian nasional melalui pelayanan ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680507/5-tips-positive-parenting-agar-anak-percaya-diri</t>
+          <t>https://www.antaranews.com/berita/5680516/kai-layani-13920-ton-pupuk-hingga-juli-2026-perkuat-rantai-pasok-pertanian-dan-ketahanan-pangan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/02/11/pexels-emma-bauso-2253879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.38.20.jpeg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1128,28 +1128,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AS cabut visa Dubes Brasil di tengah perselisihan diplomatik</t>
+          <t>Pulau Untung Jawa gelar lomba meriahkan HUT Kemerdekaan RI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:53:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:54:56 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pemerintah Amerika Serikat (AS) mencabut visa Duta Besar Brasil untuk Mario Luiza Ribeiro Viotti memperpanjang ...</t>
+          <t>Pemerintah Kelurahan Pulau Untung Jawa resmi membuka rangkaian perlombaan dalam rangka memeriahkan Hari Ulang Tahun ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680504/as-cabut-visa-dubes-brasil-di-tengah-perselisihan-diplomatik</t>
+          <t>https://www.antaranews.com/berita/5680512/pulau-untung-jawa-gelar-lomba-meriahkan-hut-kemerdekaan-ri</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000005_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a8ea0e8e-b465-4832-9dee-22d911db4b0e.jpeg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Customer Focus, KAI Libatkan Suara Pelanggan untuk Tingkatkan Layanan; CSI Semester I 2026 Capai 4,53</t>
+          <t>Pemprov Papua bukukan transaksi UMK 50,65 persen melalui e-Katalog</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:51:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:54:36 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat kualitas pelayanan dengan menempatkan pelanggan sebagai pusat ...</t>
+          <t>Pemerintah Provinsi Papua melalui Biro Pengadaan Barang dan Jasa (BPBJ) setempat membukukan nilai transaksi Usaha ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680503/customer-focus-kai-libatkan-suara-pelanggan-untuk-tingkatkan-layanan-csi-semester-i-2026-capai-453</t>
+          <t>https://www.antaranews.com/berita/5680509/pemprov-papua-bukukan-transaksi-umk-5065-persen-melalui-e-katalog</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.27.26.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002065915.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1204,28 +1204,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POCO M8 Power hadir dengan Snapdragon 4 Gen 4 dan baterai 8.000 mAh</t>
+          <t>5 tips positive parenting agar anak percaya diri</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:50:39 +0700</t>
+          <t>Wed, 05 Aug 2026 11:53:39 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ponsel POCO M8 Power, model keempat dalam seri POCO M8 yang diperkenalkan di pasar India, hadir dengan chip Snapdragon ...</t>
+          <t>Pola asuh positif atau positive parenting dinilai dapat membantu anak tumbuh dengan rasa aman, percaya diri, dan mampu ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680499/poco-m8-power-hadir-dengan-snapdragon-4-gen-4-dan-baterai-8000-mah</t>
+          <t>https://www.antaranews.com/berita/5680507/5-tips-positive-parenting-agar-anak-percaya-diri</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_111842114.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/11/pexels-emma-bauso-2253879.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1242,28 +1242,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>China luncurkan standar keselamatan sistem kemudi otonom</t>
+          <t>AS cabut visa Dubes Brasil di tengah perselisihan diplomatik</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:48:26 +0700</t>
+          <t>Wed, 05 Aug 2026 11:53:27 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>China meluncurkan standar nasional wajib mengenai persyaratan keselamatan bagi sistem kemudi otonom, demikian diumumkan ...</t>
+          <t>Pemerintah Amerika Serikat (AS) mencabut visa Duta Besar Brasil untuk Mario Luiza Ribeiro Viotti memperpanjang ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5680496/china-luncurkan-standar-keselamatan-sistem-kemudi-otonom</t>
+          <t>https://www.antaranews.com/berita/5680504/as-cabut-visa-dubes-brasil-di-tengah-perselisihan-diplomatik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000002_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000005_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1280,28 +1280,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gelombang panas keempat tahun ini di Italia picu respons darurat</t>
+          <t>Customer Focus, KAI Libatkan Suara Pelanggan untuk Tingkatkan Layanan; CSI Semester I 2026 Capai 4,53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:45:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:51:39 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Italia sedang menghadapi gelombang panas besar keempat pada musim panas tahun ini, dengan suhu di sejumlah wilayah ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat kualitas pelayanan dengan menempatkan pelanggan sebagai pusat ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680493/gelombang-panas-keempat-tahun-ini-di-italia-picu-respons-darurat</t>
+          <t>https://www.antaranews.com/berita/5680503/customer-focus-kai-libatkan-suara-pelanggan-untuk-tingkatkan-layanan-csi-semester-i-2026-capai-453</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000004_20260805_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-11.27.26.jpeg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1318,28 +1318,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kaltara tawarkan peluang investasi strategis kepada belasan duta besar</t>
+          <t>POCO M8 Power hadir dengan Snapdragon 4 Gen 4 dan baterai 8.000 mAh</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:44:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:50:39 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gubernur Kalimantan Utara (Kaltara) Zainal A. Paliwang menawarkan berbagai peluang investasi strategis di hadapan ...</t>
+          <t>Ponsel POCO M8 Power, model keempat dalam seri POCO M8 yang diperkenalkan di pasar India, hadir dengan chip Snapdragon ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680492/kaltara-tawarkan-peluang-investasi-strategis-kepada-belasan-duta-besar</t>
+          <t>https://www.antaranews.com/berita/5680499/poco-m8-power-hadir-dengan-snapdragon-4-gen-4-dan-baterai-8000-mah</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000575462.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_111842114.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1356,28 +1356,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tenaga ahli usulkan kejahatan lingkungan masuk RUU Perampasan Aset</t>
+          <t>China luncurkan standar keselamatan sistem kemudi otonom</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:11 +0700</t>
+          <t>Wed, 05 Aug 2026 11:48:26 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenaga Ahli Menteri Lingkungan Hidup Bidang Advokasi dan Penguatan Partisipasi Publik Yudi Syamhudi Suyuti mengusulkan ...</t>
+          <t>China meluncurkan standar nasional wajib mengenai persyaratan keselamatan bagi sistem kemudi otonom, demikian diumumkan ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680488/tenaga-ahli-usulkan-kejahatan-lingkungan-masuk-ruu-perampasan-aset</t>
+          <t>https://otomotif.antaranews.com/berita/5680496/china-luncurkan-standar-keselamatan-sistem-kemudi-otonom</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/IMG_20260420_115241_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000002_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemendukbangga perkuat peran keluarga wujudkan ruang aman bagi anak</t>
+          <t>Gelombang panas keempat tahun ini di Italia picu respons darurat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:01 +0700</t>
+          <t>Wed, 05 Aug 2026 11:45:01 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN terus memperkuat peran keluarga sebagai ...</t>
+          <t>Italia sedang menghadapi gelombang panas besar keempat pada musim panas tahun ini, dengan suhu di sejumlah wilayah ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680484/kemendukbangga-perkuat-peran-keluarga-wujudkan-ruang-aman-bagi-anak</t>
+          <t>https://www.antaranews.com/berita/5680493/gelombang-panas-keempat-tahun-ini-di-italia-picu-respons-darurat</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-7.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000004_20260805_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1432,28 +1432,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Panas ekstrem surutkan air Sungai Danube, ganggu pengiriman kargo</t>
+          <t>Kaltara tawarkan peluang investasi strategis kepada belasan duta besar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:42:28 +0700</t>
+          <t>Wed, 05 Aug 2026 11:44:18 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pemerintah Austria menyatakan pengiriman kargo di sepanjang Sungai Danube yang melintasi wilayah negara itu nyaris ...</t>
+          <t>Gubernur Kalimantan Utara (Kaltara) Zainal A. Paliwang menawarkan berbagai peluang investasi strategis di hadapan ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680483/panas-ekstrem-surutkan-air-sungai-danube-ganggu-pengiriman-kargo</t>
+          <t>https://www.antaranews.com/berita/5680492/kaltara-tawarkan-peluang-investasi-strategis-kepada-belasan-duta-besar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/CmxztpE000018_20260620_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000575462.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1470,28 +1470,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AS cabut visa dubes Brasil karena tolak calon dubes usulan Trump</t>
+          <t>Tenaga ahli usulkan kejahatan lingkungan masuk RUU Perampasan Aset</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:41:05 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:11 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amerika Serikat mencabut visa Duta Besar Brasil untuk Washington setelah pemerintah Brasil belum memberikan persetujuan ...</t>
+          <t>Tenaga Ahli Menteri Lingkungan Hidup Bidang Advokasi dan Penguatan Partisipasi Publik Yudi Syamhudi Suyuti mengusulkan ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680481/as-cabut-visa-dubes-brasil-karena-tolak-calon-dubes-usulan-trump</t>
+          <t>https://www.antaranews.com/berita/5680488/tenaga-ahli-usulkan-kejahatan-lingkungan-masuk-ruu-perampasan-aset</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/IMG_20260420_115241_1.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1508,28 +1508,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pertamina Patra Niaga menghadirkan kompetisi masak nasional BGCC 2026</t>
+          <t>Kemendukbangga perkuat peran keluarga wujudkan ruang aman bagi anak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:40:14 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:01 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PT Pertamina Patra Niaga menghadirkan kompetisi memasak tingkat nasional Bright Gas Cooking Competition (BGCC) 2026 ...</t>
+          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN terus memperkuat peran keluarga sebagai ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680477/pertamina-patra-niaga-menghadirkan-kompetisi-masak-nasional-bgcc-2026</t>
+          <t>https://www.antaranews.com/berita/5680484/kemendukbangga-perkuat-peran-keluarga-wujudkan-ruang-aman-bagi-anak</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000402887.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/upscalemedia-transformed-7.jpeg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1546,28 +1546,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bappenas: Indonesia punya modal kuat kembangkan ekosistem tokenisasi</t>
+          <t>Panas ekstrem surutkan air Sungai Danube, ganggu pengiriman kargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:38:07 +0700</t>
+          <t>Wed, 05 Aug 2026 11:42:28 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+          <t>Pemerintah Austria menyatakan pengiriman kargo di sepanjang Sungai Danube yang melintasi wilayah negara itu nyaris ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680475/bappenas-indonesia-punya-modal-kuat-kembangkan-ekosistem-tokenisasi</t>
+          <t>https://www.antaranews.com/berita/5680483/panas-ekstrem-surutkan-air-sungai-danube-ganggu-pengiriman-kargo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bappenas-Tokenisasi.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/CmxztpE000018_20260620_PEPFN0A001.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1584,28 +1584,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kimia Farma bukukan laba bersih "unaudited" Rp54,07 miliar</t>
+          <t>AS cabut visa dubes Brasil karena tolak calon dubes usulan Trump</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:38 +0700</t>
+          <t>Wed, 05 Aug 2026 11:41:05 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PT Kimia Farma (Persero) Tbk (KAEF) membukukan laba bersih unaudited sebesar Rp54,07 miliar pada semester ...</t>
+          <t>Amerika Serikat mencabut visa Duta Besar Brasil untuk Washington setelah pemerintah Brasil belum memberikan persetujuan ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680471/kimia-farma-bukukan-laba-bersih-unaudited-rp5407-miliar</t>
+          <t>https://www.antaranews.com/berita/5680481/as-cabut-visa-dubes-brasil-karena-tolak-calon-dubes-usulan-trump</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/DSC_0637.JPG-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rutinitas malam yang bisa bantu kurangi risiko perut kembung</t>
+          <t>Pertamina Patra Niaga menghadirkan kompetisi masak nasional BGCC 2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:36:55 +0700</t>
+          <t>Wed, 05 Aug 2026 11:40:14 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ahli gizi Ava Safir menyampaikan bahwa perut bisa terasa lebih penuh menjelang malam hari karena saluran ...</t>
+          <t>PT Pertamina Patra Niaga menghadirkan kompetisi memasak tingkat nasional Bright Gas Cooking Competition (BGCC) 2026 ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680463/rutinitas-malam-yang-bisa-bantu-kurangi-risiko-perut-kembung</t>
+          <t>https://www.antaranews.com/berita/5680477/pertamina-patra-niaga-menghadirkan-kompetisi-masak-nasional-bgcc-2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/07/02/kembung.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000402887.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1660,28 +1660,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brasil turunkan tingkat hubungan diplomatik dengan Argentina</t>
+          <t>Bappenas: Indonesia punya modal kuat kembangkan ekosistem tokenisasi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:35:10 +0700</t>
+          <t>Wed, 05 Aug 2026 11:38:07 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brasil memutuskan untuk menurunkan tingkat hubungan diplomatiknya dengan Argentina menjadi hanya perwakilan diplomatik ...</t>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680460/brasil-turunkan-tingkat-hubungan-diplomatik-dengan-argentina</t>
+          <t>https://www.antaranews.com/berita/5680475/bappenas-indonesia-punya-modal-kuat-kembangkan-ekosistem-tokenisasi</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/12/01/CjkinzN007014_20231201_CBMFN0A001_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bappenas-Tokenisasi.jpeg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1698,28 +1698,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bea Cukai gagalkan penyeludupan Harley Davidson bekas asal China</t>
+          <t>Kimia Farma bukukan laba bersih "unaudited" Rp54,07 miliar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:33:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:38 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok berhasil menggagalkan upaya penyelundupan barang impor ilegal berupa lima unit sepeda motor ...</t>
+          <t>PT Kimia Farma (Persero) Tbk (KAEF) membukukan laba bersih unaudited sebesar Rp54,07 miliar pada semester ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680459/bea-cukai-gagalkan-penyeludupan-harley-davidson-bekas-asal-china</t>
+          <t>https://www.antaranews.com/berita/5680471/kimia-farma-bukukan-laba-bersih-unaudited-rp5407-miliar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_112229.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/DSC_0637.JPG-1.jpeg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1736,28 +1736,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10 Kebiasaan sebelum tidur yang bisa tingkatkan kualitas istirahat</t>
+          <t>Rutinitas malam yang bisa bantu kurangi risiko perut kembung</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:31:46 +0700</t>
+          <t>Wed, 05 Aug 2026 11:36:55 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tidur yang berkualitas bukan hanya ditentukan oleh durasinya, tetapi juga oleh kebiasaan yang dilakukan sebelum ...</t>
+          <t>Ahli gizi Ava Safir menyampaikan bahwa perut bisa terasa lebih penuh menjelang malam hari karena saluran ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680455/10-kebiasaan-sebelum-tidur-yang-bisa-tingkatkan-kualitas-istirahat</t>
+          <t>https://www.antaranews.com/berita/5680463/rutinitas-malam-yang-bisa-bantu-kurangi-risiko-perut-kembung</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/03/12/tidur.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/02/kembung.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1774,28 +1774,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mendag genjot perdagangan RI-Thailand dengan diversifikasi ekspor</t>
+          <t>Brasil turunkan tingkat hubungan diplomatik dengan Argentina</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:21 +0700</t>
+          <t>Wed, 05 Aug 2026 11:35:10 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Menteri Perdagangan (Mendag) Budi Santoso menegaskan pemerintah terus mendorong penguatan perdagangan bilateral ...</t>
+          <t>Brasil memutuskan untuk menurunkan tingkat hubungan diplomatiknya dengan Argentina menjadi hanya perwakilan diplomatik ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680453/mendag-genjot-perdagangan-ri-thailand-dengan-diversifikasi-ekspor</t>
+          <t>https://www.antaranews.com/berita/5680460/brasil-turunkan-tingkat-hubungan-diplomatik-dengan-argentina</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0926.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/12/01/CjkinzN007014_20231201_CBMFN0A001_1.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1812,28 +1812,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CENTCOM klaim telah kawal 1.000 kapal lewati Selat Hormuz</t>
+          <t>Bea Cukai gagalkan penyeludupan Harley Davidson bekas asal China</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:16 +0700</t>
+          <t>Wed, 05 Aug 2026 11:33:25 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Komando Pusat Amerika Serikat (CENTCOM) mengeklaim pihaknya telah membantu lebih dari 1.000 kapal komersial melintasi ...</t>
+          <t>Bea Cukai Tanjung Priok berhasil menggagalkan upaya penyelundupan barang impor ilegal berupa lima unit sepeda motor ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680451/centcom-klaim-telah-kawal-1000-kapal-lewati-selat-hormuz</t>
+          <t>https://www.antaranews.com/berita/5680459/bea-cukai-gagalkan-penyeludupan-harley-davidson-bekas-asal-china</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_0df8b22d772e3fff389166ac7f3553b1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_112229.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1850,28 +1850,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BPS: Ekonomi Indonesia tumbuh 5,29 persen pada triwulan II 2026</t>
+          <t>10 Kebiasaan sebelum tidur yang bisa tingkatkan kualitas istirahat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:27:10 +0700</t>
+          <t>Wed, 05 Aug 2026 11:31:46 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia tumbuh 5,29 persen (year on year/yoy) pada triwulan II ...</t>
+          <t>Tidur yang berkualitas bukan hanya ditentukan oleh durasinya, tetapi juga oleh kebiasaan yang dilakukan sebelum ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680447/bps-ekonomi-indonesia-tumbuh-529-persen-pada-triwulan-ii-2026</t>
+          <t>https://www.antaranews.com/berita/5680455/10-kebiasaan-sebelum-tidur-yang-bisa-tingkatkan-kualitas-istirahat</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-10.58.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/12/tidur.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1888,28 +1888,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kuota undangan upacara HUT Ke-81 RI hari pertama langsung penuh</t>
+          <t>Mendag genjot perdagangan RI-Thailand dengan diversifikasi ekspor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:25:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:21 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kuota pendaftaran undangan Upacara Peringatan HUT Ke-81 Kemerdekaan RI di Istana Merdeka untuk hari pertama, Rabu, ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso menegaskan pemerintah terus mendorong penguatan perdagangan bilateral ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680445/kuota-undangan-upacara-hut-ke-81-ri-hari-pertama-langsung-penuh</t>
+          <t>https://www.antaranews.com/berita/5680453/mendag-genjot-perdagangan-ri-thailand-dengan-diversifikasi-ekspor</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000034647.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0926.jpeg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1926,28 +1926,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WHO sebut risiko penyebaran virus Bourbon di AS masih rendah</t>
+          <t>CENTCOM klaim telah kawal 1.000 kapal lewati Selat Hormuz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:24:48 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:16 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Organisasi Kesehatan Dunia (WHO) telah mengetahui adanya kasus infeksi virus Bourbon yang dilaporkan di Amerika Serikat ...</t>
+          <t>Komando Pusat Amerika Serikat (CENTCOM) mengeklaim pihaknya telah membantu lebih dari 1.000 kapal komersial melintasi ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680441/who-sebut-risiko-penyebaran-virus-bourbon-di-as-masih-rendah</t>
+          <t>https://www.antaranews.com/berita/5680451/centcom-klaim-telah-kawal-1000-kapal-lewati-selat-hormuz</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/07/22/reuters_cdc-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/thumbs_b_c_0df8b22d772e3fff389166ac7f3553b1.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1964,28 +1964,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Menteri PKP: BTN salurkan KPR subsidi terbanyak hingga Juli 2026</t>
+          <t>BPS: Ekonomi Indonesia tumbuh 5,29 persen pada triwulan II 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:24:28 +0700</t>
+          <t>Wed, 05 Aug 2026 11:27:10 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait mengatakan PT Bank Tabungan Negara (Persero) Tbk (BTN) ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia tumbuh 5,29 persen (year on year/yoy) pada triwulan II ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680437/menteri-pkp-btn-salurkan-kpr-subsidi-terbanyak-hingga-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5680447/bps-ekonomi-indonesia-tumbuh-529-persen-pada-triwulan-ii-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/percepatan-pembangunan-rumah-subsidi-2828057.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-10.58.55.jpeg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2002,28 +2002,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Koster temui Gubernur DKI belajar soal pembiayaan inovatif</t>
+          <t>Kuota undangan upacara HUT Ke-81 RI hari pertama langsung penuh</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:22:36 +0700</t>
+          <t>Wed, 05 Aug 2026 11:25:27 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Bali mempelajari skema pembiayaan inovatif dari Pemerintah Provinsi DKI Jakarta, termasuk ...</t>
+          <t>Kuota pendaftaran undangan Upacara Peringatan HUT Ke-81 Kemerdekaan RI di Istana Merdeka untuk hari pertama, Rabu, ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680433/koster-temui-gubernur-dki-belajar-soal-pembiayaan-inovatif</t>
+          <t>https://www.antaranews.com/berita/5680445/kuota-undangan-upacara-hut-ke-81-ri-hari-pertama-langsung-penuh</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/794ac169-206a-4fd7-a0f6-8e065b9d2615.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000034647.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2040,28 +2040,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saudi, Qatar, Yordania berpeluang masuk jalur gas Eropa via Turki</t>
+          <t>WHO sebut risiko penyebaran virus Bourbon di AS masih rendah</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:16:25 +0700</t>
+          <t>Wed, 05 Aug 2026 11:24:48 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Qatar, Arab Saudi, dan Yordania berpeluang menjadi bagian dari rute baru penyaluran gas alam menuju Turki dan ...</t>
+          <t>Organisasi Kesehatan Dunia (WHO) telah mengetahui adanya kasus infeksi virus Bourbon yang dilaporkan di Amerika Serikat ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680431/saudi-qatar-yordania-berpeluang-masuk-jalur-gas-eropa-via-turki</t>
+          <t>https://www.antaranews.com/berita/5680441/who-sebut-risiko-penyebaran-virus-bourbon-di-as-masih-rendah</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/07/22/reuters_cdc-1.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2078,28 +2078,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kronologi temuan mayat dalam karung di Depok hingga penangkapan pelaku</t>
+          <t>Menteri PKP: BTN salurkan KPR subsidi terbanyak hingga Juli 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:15:54 +0700</t>
+          <t>Wed, 05 Aug 2026 11:24:28 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kasus penemuan mayat termutilasi yang terbungkus di dalam karung di kawasan Tanah Merah, Kelurahan Pancoran Mas, Kota ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait mengatakan PT Bank Tabungan Negara (Persero) Tbk (BTN) ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680429/kronologi-temuan-mayat-dalam-karung-di-depok-hingga-penangkapan-pelaku</t>
+          <t>https://www.antaranews.com/berita/5680437/menteri-pkp-btn-salurkan-kpr-subsidi-terbanyak-hingga-juli-2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/percepatan-pembangunan-rumah-subsidi-2828057.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2116,28 +2116,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Legislator: Sensus Ekonomi 2026 perkuat kebijakan UMKM</t>
+          <t>Koster temui Gubernur DKI belajar soal pembiayaan inovatif</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
+          <t>Wed, 05 Aug 2026 11:22:36 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Anggota Komisi X DPR RI Adela Kanasya Adies mengatakan Sensus Ekonomi 2026 akan menjadi dasar penyusunan kebijakan ...</t>
+          <t>Pemerintah Provinsi Bali mempelajari skema pembiayaan inovatif dari Pemerintah Provinsi DKI Jakarta, termasuk ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680427/legislator-sensus-ekonomi-2026-perkuat-kebijakan-umkm</t>
+          <t>https://www.antaranews.com/berita/5680433/koster-temui-gubernur-dki-belajar-soal-pembiayaan-inovatif</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001219476.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/794ac169-206a-4fd7-a0f6-8e065b9d2615.jpeg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2154,28 +2154,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pendaftaran upacara HUT RI di Istana dibuka, ini dokumen yang wajib disiapkan</t>
+          <t>Saudi, Qatar, Yordania berpeluang masuk jalur gas Eropa via Turki</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:16:25 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Badan Komunikasi Pemerintah (Bakom) RI menyarankan masyarakat menyiapkan seluruh dokumen persyaratan sebelum mendaftar ...</t>
+          <t>Qatar, Arab Saudi, dan Yordania berpeluang menjadi bagian dari rute baru penyaluran gas alam menuju Turki dan ...</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680423/pendaftaran-upacara-hut-ri-di-istana-dibuka-ini-dokumen-yang-wajib-disiapkan</t>
+          <t>https://www.antaranews.com/berita/5680431/saudi-qatar-yordania-berpeluang-masuk-jalur-gas-eropa-via-turki</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Survei Herbalife: Budaya "Wellness" Kian Menguat di Asia Pasifik, Empat dari Lima Konsumen Prioritaskan Kesehatan Holistik</t>
+          <t>Kronologi temuan mayat dalam karung di Depok hingga penangkapan pelaku</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:12:18 +0700</t>
+          <t>Wed, 05 Aug 2026 11:15:54 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Budaya gaya hidup sehat (wellness) semakin mengakar di kawasan Asia Pasifik (APAC). Hal itu terungkap dalam survei ...</t>
+          <t>Kasus penemuan mayat termutilasi yang terbungkus di dalam karung di kawasan Tanah Merah, Kelurahan Pancoran Mas, Kota ...</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680420/survei-herbalife-budaya-wellness-kian-menguat-di-asia-pasifik-empat-dari-lima-konsumen-prioritaskan-kesehatan-holistik</t>
+          <t>https://www.antaranews.com/berita/5680429/kronologi-temuan-mayat-dalam-karung-di-depok-hingga-penangkapan-pelaku</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Budaya-Wellness-Asia.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Warga bentangkan bendera Merah Putih sepanjang 400 meter sambut HUT ke-81 RI di Tangerang</t>
+          <t>Legislator: Sensus Ekonomi 2026 perkuat kebijakan UMKM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:11:44 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Foto udara bendera Merah Putih membentang menutupi jalan di Perumahan Puri Dewata Indah, Cipondoh, Kota Tangerang, ...</t>
+          <t>Anggota Komisi X DPR RI Adela Kanasya Adies mengatakan Sensus Ekonomi 2026 akan menjadi dasar penyusunan kebijakan ...</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5680417/warga-bentangkan-bendera-merah-putih-sepanjang-400-meter-sambut-hut-ke-81-ri-di-tangerang</t>
+          <t>https://www.antaranews.com/berita/5680427/legislator-sensus-ekonomi-2026-perkuat-kebijakan-umkm</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bendera-Merah-Putih-sepanjang-400-meter-di-Tangerang-482026-pma-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001219476.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2268,28 +2268,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Irak akan bangun infrastruktur pipa minyak baru ke Turki dan Suriah</t>
+          <t>Pendaftaran upacara HUT RI di Istana dibuka, ini dokumen yang wajib disiapkan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:11:24 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:15 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Irak berencana segera memulai pembangunan pipa minyak baru menuju Suriah dan Turki guna mendiversifikasi rute ekspor ...</t>
+          <t>Badan Komunikasi Pemerintah (Bakom) RI menyarankan masyarakat menyiapkan seluruh dokumen persyaratan sebelum mendaftar ...</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680415/irak-akan-bangun-infrastruktur-pipa-minyak-baru-ke-turki-dan-suriah</t>
+          <t>https://www.antaranews.com/berita/5680423/pendaftaran-upacara-hut-ri-di-istana-dibuka-ini-dokumen-yang-wajib-disiapkan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/12/ilustrasi-distribusi-bahan-bakar-dari-negara-Teluk_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pemprov DKI bekali warga Jakpus keterampilan berwirausaha</t>
+          <t>Survei Herbalife: Budaya "Wellness" Kian Menguat di Asia Pasifik, Empat dari Lima Konsumen Prioritaskan Kesehatan Holistik</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:08:43 +0700</t>
+          <t>Wed, 05 Aug 2026 11:12:18 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta membekali warga Jakarta Pusat (Jakpus) dengan keterampilan tata boga untuk ...</t>
+          <t>Budaya gaya hidup sehat (wellness) semakin mengakar di kawasan Asia Pasifik (APAC). Hal itu terungkap dalam survei ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680411/pemprov-dki-bekali-warga-jakpus-keterampilan-berwirausaha</t>
+          <t>https://www.antaranews.com/berita/5680420/survei-herbalife-budaya-wellness-kian-menguat-di-asia-pasifik-empat-dari-lima-konsumen-prioritaskan-kesehatan-holistik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/20260731_152649.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Budaya-Wellness-Asia.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2344,28 +2344,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KY tuntaskan wawancara 9 calon hakim agung kamar pidana</t>
+          <t>Warga bentangkan bendera Merah Putih sepanjang 400 meter sambut HUT ke-81 RI di Tangerang</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:06:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:11:44 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Komisi Yudisial (KY) menuntaskan wawancara terhadap sembilan calon hakim agung kamar pidana dalam seleksi terbuka calon ...</t>
+          <t>Foto udara bendera Merah Putih membentang menutupi jalan di Perumahan Puri Dewata Indah, Cipondoh, Kota Tangerang, ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680407/ky-tuntaskan-wawancara-9-calon-hakim-agung-kamar-pidana</t>
+          <t>https://www.antaranews.com/foto/5680417/warga-bentangkan-bendera-merah-putih-sepanjang-400-meter-sambut-hut-ke-81-ri-di-tangerang</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001843500.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Bendera-Merah-Putih-sepanjang-400-meter-di-Tangerang-482026-pma-1.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2795,33 +2795,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Humaniora</t>
+          <t>Hiburan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cara daftar PIP 2026, lengkap syarat, besar bantuan</t>
+          <t>Top 10 film Netflix Indonesia terpopuler Agustus 2026, wajib masuk watchlist</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:18:05 +0700</t>
+          <t>Wed, 05 Aug 2026 08:03:43 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Program Indonesia Pintar (PIP) 2026 kembali menjadi salah satu bantuan pendidikan yang dinantikan peserta didik dari ...</t>
+          <t>Sejumlah film dari berbagai genre masuk daftar Top 10 Netflix Indonesia pada Agustus 2026. Mulai dari horor, aksi, ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680551/cara-daftar-pip-2026-lengkap-syarat-besar-bantuan</t>
+          <t>https://www.antaranews.com/berita/5680239/top-10-film-netflix-indonesia-terpopuler-agustus-2026-wajib-masuk-watchlist</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/pemberian-beasiswa-pip.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/12/20/Screenshot_2019-12-20-09-25-04-83-01-1024x683_1.jpeg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2833,33 +2833,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hiburan</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Top 10 film Netflix Indonesia terpopuler Agustus 2026, wajib masuk watchlist</t>
+          <t>iOS 27 kapan rilis? Ini daftar iPhone yang kebagian dan fitur barunya</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:03:43 +0700</t>
+          <t>Wed, 05 Aug 2026 08:08:05 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sejumlah film dari berbagai genre masuk daftar Top 10 Netflix Indonesia pada Agustus 2026. Mulai dari horor, aksi, ...</t>
+          <t>Apple resmi memperkenalkan sederet fitur baru yang akan hadir melalui sistem operasi iOS 27. Pembaruan ini membawa ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680239/top-10-film-netflix-indonesia-terpopuler-agustus-2026-wajib-masuk-watchlist</t>
+          <t>https://www.antaranews.com/berita/5680241/ios-27-kapan-rilis-ini-daftar-iphone-yang-kebagian-dan-fitur-barunya</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2019/12/20/Screenshot_2019-12-20-09-25-04-83-01-1024x683_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/conversation_fcthp95t7kqe_large_2x.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2871,38 +2871,38 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tekno</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>iOS 27 kapan rilis? Ini daftar iPhone yang kebagian dan fitur barunya</t>
+          <t>Kapolda Riau Bicara soal Green Policing dan Kerusakan Ekologis di Forum IMT-GT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:08:05 +0700</t>
+          <t>Wed, 05 Aug 2026 12:22:19 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Apple resmi memperkenalkan sederet fitur baru yang akan hadir melalui sistem operasi iOS 27. Pembaruan ini membawa ...</t>
+          <t>Kapolda Riau Irjen Herry Heryawan berbicara di Seminar GCMC, menekankan pentingnya Green Policing untuk mengatasi kerusakan lingkungan dan ancaman keamanan.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5680241/ios-27-kapan-rilis-ini-daftar-iphone-yang-kebagian-dan-fitur-barunya</t>
+          <t>https://news.detik.com/melindungi-tuah-marwah/d-8605116/kapolda-riau-bicara-soal-green-policing-dan-kerusakan-ekologis-di-forum-imt-gt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/conversation_fcthp95t7kqe_large_2x.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolda-riau-irjen-pol-herry-heryawan-menjadi-pembicara-di-forum-imt-gt-1785907218992_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
@@ -2914,28 +2914,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KPK Ajukan Banding Vonis 2 Tahun Gubernur Riau Abdul Wahid</t>
+          <t>Gempa M 6,3 Guncang Filipina, Warga Panik Berlarian</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:09:46 +0700</t>
+          <t>Wed, 05 Aug 2026 12:18:25 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KPK mengajukan banding atas vonis 2 tahun Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa lainnya.</t>
+          <t>Gempa bumi bermagnitudo 6,3 mengguncang wilayah lepas pantai Filipina selatan pada hari Rabu (5/8). Gempa ini membuat orang-orang panik berlarian.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605098/kpk-ajukan-banding-vonis-2-tahun-gubernur-riau-abdul-wahid</t>
+          <t>https://news.detik.com/internasional/d-8605107/gempa-m-6-3-guncang-filipina-warga-panik-berlarian</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-2_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/gempa-bumi_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2952,28 +2952,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jaksa Heran Nadiem Minta 14 Saksi Diperiksa Ulang di Sidang Banding</t>
+          <t>Basarnas Ungkap Kondisi 5 Korban Tewas KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:09:44 +0700</t>
+          <t>Wed, 05 Aug 2026 12:18:05 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nadiem meminta pemeriksaan ulang 14 orang saksi dan dua ahli dalam sidang banding. Jaksa heran dengan permintaan itu.</t>
+          <t>Basarnas mengungkap lima korban kebakaran KM Mutiara Sentosa II di perairan utara Madura bukan meninggal akibat terbakar.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605097/jaksa-heran-nadiem-minta-14-saksi-diperiksa-ulang-di-sidang-banding</t>
+          <t>https://news.detik.com/berita/d-8605106/basarnas-ungkap-kondisi-5-korban-tewas-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/nadiem-ajukan-banding-minta-hakim-cermati-kejanggalan-persidangan-1785906053465_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2990,28 +2990,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mahasiswa Makassar Diserang Busur Panah Usai Tegur Pemotor Kerap Geber Motor</t>
+          <t>Sopir Mikrotrans Dipecat Usai Ngebut dan Tabrak Lansia di Tomang</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:05:59 +0700</t>
+          <t>Wed, 05 Aug 2026 12:15:18 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Polisi menangkap pria berinisial NS alias J (22) usai memanah seorang mahasiswa bernama Agus Wirakusuma (21) di Kota Makassar, Sulawesi Selatan (Sulsel).</t>
+          <t>Sopir Mikrotrans diduga menabrak pria lansia di Tomang Utara, Jakbar. Pihak TransJ memberhentikan dengan tidak hormat pengemudi tersebut.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605085/mahasiswa-makassar-diserang-busur-panah-usai-tegur-pemotor-kerap-geber-motor</t>
+          <t>https://news.detik.com/berita/d-8605103/sopir-mikrotrans-dipecat-usai-ngebut-dan-tabrak-lansia-di-tomang</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/10/makassar_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/04/28/mikrotrans-jaklingko-siap-meluas-ke-daerah-penyangga-jakarta-1745823708793_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3028,28 +3028,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Golkar Jawab PDIP Soal Politik Bukan Cari Enak, Hormati Parpol Luar Pemerintah</t>
+          <t>KPK Ajukan Banding Vonis 2 Tahun Gubernur Riau Abdul Wahid</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:04:36 +0700</t>
+          <t>Wed, 05 Aug 2026 12:09:46 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Waketum Golkar, Ahmad Doli, menegaskan partainya tak pernah jadi oposisi dan konsisten mendukung pembangunan. Golkar menghargai semua posisi partai politik.</t>
+          <t>KPK mengajukan banding atas vonis 2 tahun Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa lainnya.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605082/golkar-jawab-pdip-soal-politik-bukan-cari-enak-hormati-parpol-luar-pemerintah</t>
+          <t>https://news.detik.com/berita/d-8605098/kpk-ajukan-banding-vonis-2-tahun-gubernur-riau-abdul-wahid</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/17/waketum-partai-golkar-ahmad-doli-kurnia_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-2_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3066,28 +3066,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kronologi Kunaefi Dimutilasi Kenalan di Medsos hingga Pelaku Ditangkap</t>
+          <t>Jaksa Heran Nadiem Minta 14 Saksi Diperiksa Ulang di Sidang Banding</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:02:08 +0700</t>
+          <t>Wed, 05 Aug 2026 12:09:44 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Penemuan jasad mutilasi Kunaefi di Depok menggegerkan warga. Pelaku Saepul, kenalan di media sosial, ditangkap setelah membunuh dan memutilasi korban.</t>
+          <t>Nadiem meminta pemeriksaan ulang 14 orang saksi dan dua ahli dalam sidang banding. Jaksa heran dengan permintaan itu.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605079/kronologi-kunaefi-dimutilasi-kenalan-di-medsos-hingga-pelaku-ditangkap</t>
+          <t>https://news.detik.com/berita/d-8605097/jaksa-heran-nadiem-minta-14-saksi-diperiksa-ulang-di-sidang-banding</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/nadiem-ajukan-banding-minta-hakim-cermati-kejanggalan-persidangan-1785906053465_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3104,28 +3104,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bareskrim Limpahkan Tersangka Kasus Narkoba 'The Doctor' ke Kejari Jaksel</t>
+          <t>Mahasiswa Makassar Diserang Busur Panah Usai Tegur Pemotor Kerap Geber Motor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:56:39 +0700</t>
+          <t>Wed, 05 Aug 2026 12:05:59 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bareskrim melimpahkan tersangka kasus narkoba, Andre Fernando Tjandra alias Charlie alias 'The Doctor', ke Kejaksaan Negeri Jakarta Selatan.</t>
+          <t>Polisi menangkap pria berinisial NS alias J (22) usai memanah seorang mahasiswa bernama Agus Wirakusuma (21) di Kota Makassar, Sulawesi Selatan (Sulsel).</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605073/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel</t>
+          <t>https://news.detik.com/berita/d-8605085/mahasiswa-makassar-diserang-busur-panah-usai-tegur-pemotor-kerap-geber-motor</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel-dok-polri-1785905794036_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/10/makassar_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3142,28 +3142,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DPD RI Bangun Kantor di Serang Banten, Siap Tampung Aspirasi Warga</t>
+          <t>Golkar Jawab PDIP Soal Politik Bukan Cari Enak, Hormati Parpol Luar Pemerintah</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:55:56 +0700</t>
+          <t>Wed, 05 Aug 2026 12:04:36 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DPd RI akan membangun kantor perwakilan di Kota Serang, Banten. Kantor tersebut dibangun untuk mempermudah masyarakat Banten menyampaikan aspirasinya.</t>
+          <t>Waketum Golkar, Ahmad Doli, menegaskan partainya tak pernah jadi oposisi dan konsisten mendukung pembangunan. Golkar menghargai semua posisi partai politik.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605072/dpd-ri-bangun-kantor-di-serang-banten-siap-tampung-aspirasi-warga</t>
+          <t>https://news.detik.com/berita/d-8605082/golkar-jawab-pdip-soal-politik-bukan-cari-enak-hormati-parpol-luar-pemerintah</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-ri-sultan-najamudin-di-acara-groundbreaking-kantor-perwakilan-dpd-ri-di-kota-serang-ariefdetikcom-1785905595298_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/17/waketum-partai-golkar-ahmad-doli-kurnia_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jepang Perkuat Militernya, Adik Kim Jong Un Murka!</t>
+          <t>Kronologi Kunaefi Dimutilasi Kenalan di Medsos hingga Pelaku Ditangkap</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:49:16 +0700</t>
+          <t>Wed, 05 Aug 2026 12:02:08 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
+          <t>Penemuan jasad mutilasi Kunaefi di Depok menggegerkan warga. Pelaku Saepul, kenalan di media sosial, ditangkap setelah membunuh dan memutilasi korban.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8605067/jepang-perkuat-militernya-adik-kim-jong-un-murka</t>
+          <t>https://news.detik.com/berita/d-8605079/kronologi-kunaefi-dimutilasi-kenalan-di-medsos-hingga-pelaku-ditangkap</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/12/33bee726-0042-4c52-9a21-c328504ce2ff_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dalam Kontainer dari China</t>
+          <t>Bareskrim Limpahkan Tersangka Kasus Narkoba 'The Doctor' ke Kejari Jaksel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:43:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:56:39 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bea Cukai Tanjung Priok gagalkan penyelundupan sepeda motor Harley-Davidson bekas. Penindakan dilakukan berkat teknologi pemindaian dan analisis intelijen.</t>
+          <t>Bareskrim melimpahkan tersangka kasus narkoba, Andre Fernando Tjandra alias Charlie alias 'The Doctor', ke Kejaksaan Negeri Jakarta Selatan.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605050/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china</t>
+          <t>https://news.detik.com/berita/d-8605073/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china-1785904973977_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-limpahkan-tersangka-kasus-narkoba-the-doctor-ke-kejari-jaksel-dok-polri-1785905794036_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3256,28 +3256,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gempa M 6,4 Guncang Pulau Karatung Sulut</t>
+          <t>DPD RI Bangun Kantor di Serang Banten, Siap Tampung Aspirasi Warga</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:03 +0700</t>
+          <t>Wed, 05 Aug 2026 11:55:56 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gempa bumi dengan kekuatan magnitudo (M) 6,4 mengguncang kawasan Pulau Karatung, Sulawesi Utara. Gempa tak berpotensi tsunami.</t>
+          <t>DPd RI akan membangun kantor perwakilan di Kota Serang, Banten. Kantor tersebut dibangun untuk mempermudah masyarakat Banten menyampaikan aspirasinya.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605028/gempa-m-6-4-guncang-pulau-karatung-sulut</t>
+          <t>https://news.detik.com/berita/d-8605072/dpd-ri-bangun-kantor-di-serang-banten-siap-tampung-aspirasi-warga</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-ri-sultan-najamudin-di-acara-groundbreaking-kantor-perwakilan-dpd-ri-di-kota-serang-ariefdetikcom-1785905595298_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3294,28 +3294,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Relawan SPPG di Kuningan Diseruduk Saat Cegah Babi Hutan Serang Anak-anak</t>
+          <t>Jepang Perkuat Militernya, Adik Kim Jong Un Murka!</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:37:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:49:16 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Video viral menunjukkan Anas, relawan SPPG, berjuang menahan babi hutan di Kuningan. Ia tersungkur dan terluka saat berupaya melindungi anak-anak.</t>
+          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605027/relawan-sppg-di-kuningan-diseruduk-saat-cegah-babi-hutan-serang-anak-anak</t>
+          <t>https://news.detik.com/internasional/d-8605067/jepang-perkuat-militernya-adik-kim-jong-un-murka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tangkapan-layar-babi-seruduk-warga-di-kuningan-1785814645532_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/12/33bee726-0042-4c52-9a21-c328504ce2ff_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Momen Haru Pasutri dan 2 Anak Bertemu Lagi Usai Lompat dari KM Mutiara Sentosa</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dalam Kontainer dari China</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:35:32 +0700</t>
+          <t>Wed, 05 Aug 2026 11:43:15 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kebakaran KM Mutiara Sentosa 2 di Sumenep sempat memisahkan satu keluarga. Setelah evakuasi, mereka akhirnya berkumpul kembali di RS PHC Surabaya.</t>
+          <t>Bea Cukai Tanjung Priok gagalkan penyelundupan sepeda motor Harley-Davidson bekas. Penindakan dilakukan berkat teknologi pemindaian dan analisis intelijen.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605021/momen-haru-pasutri-dan-2-anak-bertemu-lagi-usai-lompat-dari-km-mutiara-sentosa</t>
+          <t>https://news.detik.com/berita/d-8605050/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-terbakar-1785849470687_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dalam-kontainer-dari-china-1785904973977_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3370,28 +3370,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kunaefi Korban Mutilasi di Depok Sempat Dilaporkan Hilang oleh Istri</t>
+          <t>Gempa M 6,4 Guncang Pulau Karatung Sulut</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:28:42 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:03 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Polisi mengungkap kasus mutilasi di Depok. Korban Kunaefi ditemukan setelah dilaporkan hilang. Pelaku, Saepul, dikenal melalui media sosial.</t>
+          <t>Gempa bumi dengan kekuatan magnitudo (M) 6,4 mengguncang kawasan Pulau Karatung, Sulawesi Utara. Gempa tak berpotensi tsunami.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8605002/kunaefi-korban-mutilasi-di-depok-sempat-dilaporkan-hilang-oleh-istri</t>
+          <t>https://news.detik.com/berita/d-8605028/gempa-m-6-4-guncang-pulau-karatung-sulut</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3408,28 +3408,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pria Tangerang Dipaksa Onani dan Direkam Bos, Video Disebar untuk Ancaman</t>
+          <t>Relawan SPPG di Kuningan Diseruduk Saat Cegah Babi Hutan Serang Anak-anak</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:23:58 +0700</t>
+          <t>Wed, 05 Aug 2026 11:37:00 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kasus pria dianiaya dan dilecehkan mencuat usai beredar video korban dalam kondisi terluka dan diduga sedang dipaksa masturbasi. Video itu direkam bos korban.</t>
+          <t>Video viral menunjukkan Anas, relawan SPPG, berjuang menahan babi hutan di Kuningan. Ia tersungkur dan terluka saat berupaya melindungi anak-anak.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604995/pria-tangerang-dipaksa-onani-dan-direkam-bos-video-disebar-untuk-ancaman</t>
+          <t>https://news.detik.com/berita/d-8605027/relawan-sppg-di-kuningan-diseruduk-saat-cegah-babi-hutan-serang-anak-anak</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tangkapan-layar-babi-seruduk-warga-di-kuningan-1785814645532_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3446,28 +3446,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Modus Adaptif Promosi Judi Online: Menunggangi Algoritma Konten Viral</t>
+          <t>Momen Haru Pasutri dan 2 Anak Bertemu Lagi Usai Lompat dari KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:20:04 +0700</t>
+          <t>Wed, 05 Aug 2026 11:35:32 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spam judi online naik 128 persen di medsos. Algoritma yang mengutamakan keramaian interaksi ternyata tanpa sadar ikut menyuburkan penyebarannya.</t>
+          <t>Kebakaran KM Mutiara Sentosa 2 di Sumenep sempat memisahkan satu keluarga. Setelah evakuasi, mereka akhirnya berkumpul kembali di RS PHC Surabaya.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://news.detik.com/kolom/d-8604992/modus-adaptif-promosi-judi-online-menunggangi-algoritma-konten-viral</t>
+          <t>https://news.detik.com/berita/d-8605021/momen-haru-pasutri-dan-2-anak-bertemu-lagi-usai-lompat-dari-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/20/ilustrasi-judi-online-lagi_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-terbakar-1785849470687_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3484,28 +3484,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trump Ancam Serang Iran Besar-besaran Jika Hormuz Tak Dibuka Segera</t>
+          <t>Kunaefi Korban Mutilasi di Depok Sempat Dilaporkan Hilang oleh Istri</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:17:29 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:42 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Donald Trump mengatakan bahwa Selat Hormuz akan dibuka segera. Trump mengancam bahwa Iran akan diserang besar-besaran jika selat itu tidak dibuka.</t>
+          <t>Polisi mengungkap kasus mutilasi di Depok. Korban Kunaefi ditemukan setelah dilaporkan hilang. Pelaku, Saepul, dikenal melalui media sosial.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604989/trump-ancam-serang-iran-besar-besaran-jika-hormuz-tak-dibuka-segera</t>
+          <t>https://news.detik.com/berita/d-8605002/kunaefi-korban-mutilasi-di-depok-sempat-dilaporkan-hilang-oleh-istri</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3522,28 +3522,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BNN Dorong Penguatan Resiliensi Generasi Muda Lewat Kuliah Umum</t>
+          <t>Pria Tangerang Dipaksa Onani dan Direkam Bos, Video Disebar untuk Ancaman</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:15:14 +0700</t>
+          <t>Wed, 05 Aug 2026 11:23:58 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BNN RI menggelar Kuliah Umum Nasional tentang resiliensi generasi muda menghadapi narkotika pada 6 Agustus 2026 di Universitas Majalengka.</t>
+          <t>Kasus pria dianiaya dan dilecehkan mencuat usai beredar video korban dalam kondisi terluka dan diduga sedang dipaksa masturbasi. Video itu direkam bos korban.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604985/bnn-dorong-penguatan-resiliensi-generasi-muda-lewat-kuliah-umum</t>
+          <t>https://news.detik.com/berita/d-8604995/pria-tangerang-dipaksa-onani-dan-direkam-bos-video-disebar-untuk-ancaman</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/promo-bnn-1785903275205_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3560,28 +3560,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Saepul Mutilasi Pria di Depok gegara Cekcok, Potongan Kaki Dibuang ke Kali</t>
+          <t>Modus Adaptif Promosi Judi Online: Menunggangi Algoritma Konten Viral</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
+          <t>Wed, 05 Aug 2026 11:20:04 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Polisi telah menangkap Saepul (26) yang diduga melakukan mutilasi terhadap pria bernama Kunaefi (51) di Pancoran Mas, Kota Depok.</t>
+          <t>Spam judi online naik 128 persen di medsos. Algoritma yang mengutamakan keramaian interaksi ternyata tanpa sadar ikut menyuburkan penyebarannya.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604983/saepul-mutilasi-pria-di-depok-gegara-cekcok-potongan-kaki-dibuang-ke-kali</t>
+          <t>https://news.detik.com/kolom/d-8604992/modus-adaptif-promosi-judi-online-menunggangi-algoritma-konten-viral</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/20/ilustrasi-judi-online-lagi_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3598,28 +3598,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pengusaha Singkawang Tewas Ditembak Pembunuh Bayaran, Dalangnya Adik Kandung</t>
+          <t>Trump Ancam Serang Iran Besar-besaran Jika Hormuz Tak Dibuka Segera</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:02:48 +0700</t>
+          <t>Wed, 05 Aug 2026 11:17:29 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Seorang pengusaha bernama Cung Su Liat alias Aliat (55) ditemukan tewas mengenaskan dengan luka tembak di halaman rumahnya Kota Singkawang, Kalimantan Barat.</t>
+          <t>Donald Trump mengatakan bahwa Selat Hormuz akan dibuka segera. Trump mengancam bahwa Iran akan diserang besar-besaran jika selat itu tidak dibuka.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604972/pengusaha-singkawang-tewas-ditembak-pembunuh-bayaran-dalangnya-adik-kandung</t>
+          <t>https://news.detik.com/internasional/d-8604989/trump-ancam-serang-iran-besar-besaran-jika-hormuz-tak-dibuka-segera</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eksekutor-penembak-pengusaha-di-singkawang-hingga-tewas-dok-resmob-polda-kalbar-1785844579501_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3636,28 +3636,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Terpeleset Saat Cari Ikan, Bocah 5 Tahun Tewas Terseret Arus Kali Ciliwung</t>
+          <t>BNN Dorong Penguatan Resiliensi Generasi Muda Lewat Kuliah Umum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:01:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:15:14 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bocah berusia 5 tahun berinisial S tewas setelah terseret arus Kali Ciliwung, Depok. Korban bersama dua temannya awalnya hendak mencari ikan di lokasi.</t>
+          <t>BNN RI menggelar Kuliah Umum Nasional tentang resiliensi generasi muda menghadapi narkotika pada 6 Agustus 2026 di Universitas Majalengka.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604971/terpeleset-saat-cari-ikan-bocah-5-tahun-tewas-terseret-arus-kali-ciliwung</t>
+          <t>https://news.detik.com/berita/d-8604985/bnn-dorong-penguatan-resiliensi-generasi-muda-lewat-kuliah-umum</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/ilustrasi-orang-tenggelam-1781518248434_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/promo-bnn-1785903275205_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3674,28 +3674,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pertahankan Opini WTP, Setjen MPR RI Perkuat Tata Kelola Keuangan</t>
+          <t>Saepul Mutilasi Pria di Depok gegara Cekcok, Potongan Kaki Dibuang ke Kali</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:49 +0700</t>
+          <t>Wed, 05 Aug 2026 11:13:37 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Setjen MPR RI mempertahankan opini WTP atas Laporan Keuangan 2025. Deputi Heri Herawan apresiasi transparansi dan akuntabilitas dalam pengelolaan keuangan.</t>
+          <t>Polisi telah menangkap Saepul (26) yang diduga melakukan mutilasi terhadap pria bernama Kunaefi (51) di Pancoran Mas, Kota Depok.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604969/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan</t>
+          <t>https://news.detik.com/berita/d-8604983/saepul-mutilasi-pria-di-depok-gegara-cekcok-potongan-kaki-dibuang-ke-kali</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan-1785902413926_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3712,28 +3712,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Korban Mutilasi di Depok Ternyata Dibunuh Pria Kenalan di Medsos</t>
+          <t>Pengusaha Singkawang Tewas Ditembak Pembunuh Bayaran, Dalangnya Adik Kandung</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:27 +0700</t>
+          <t>Wed, 05 Aug 2026 11:02:48 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya menangkap Saepul, pelaku mutilasi Kunaefi. Korban dan pelaku berkenalan lewat media sosial sebelum pertemuan berujung mutilasi.</t>
+          <t>Seorang pengusaha bernama Cung Su Liat alias Aliat (55) ditemukan tewas mengenaskan dengan luka tembak di halaman rumahnya Kota Singkawang, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604968/korban-mutilasi-di-depok-ternyata-dibunuh-pria-kenalan-di-medsos</t>
+          <t>https://news.detik.com/berita/d-8604972/pengusaha-singkawang-tewas-ditembak-pembunuh-bayaran-dalangnya-adik-kandung</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eksekutor-penembak-pengusaha-di-singkawang-hingga-tewas-dok-resmob-polda-kalbar-1785844579501_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3750,28 +3750,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Merah Putih Membelah Jalan Tangerang, Aksi Warga Sambut Kemerdekaan RI Bikin Takjub</t>
+          <t>Terpeleset Saat Cari Ikan, Bocah 5 Tahun Tewas Terseret Arus Kali Ciliwung</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:06 +0700</t>
+          <t>Wed, 05 Aug 2026 11:01:27 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Warga Tangerang membentangkan bendera Merah Putih sepanjang 400 meter di jalan perumahan untuk menyambut HUT ke-81 Kemerdekaan RI.</t>
+          <t>Bocah berusia 5 tahun berinisial S tewas setelah terseret arus Kali Ciliwung, Depok. Korban bersama dua temannya awalnya hendak mencari ikan di lokasi.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8604436/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub</t>
+          <t>https://news.detik.com/berita/d-8604971/terpeleset-saat-cari-ikan-bocah-5-tahun-tewas-terseret-arus-kali-ciliwung</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub-1785847891040_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/15/ilustrasi-orang-tenggelam-1781518248434_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3788,28 +3788,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ayah dan Paman Pemerkosa Gadis di Situbondo Divonis 20 Tahun Penjara</t>
+          <t>Pertahankan Opini WTP, Setjen MPR RI Perkuat Tata Kelola Keuangan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:58:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:49 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Majelis hakim Pengadilan Negeri Situbondo, Jawa Timur, menjatuhkan vonis masing-masing 20 tahun penjara kepada BH (42) dan BS (42).</t>
+          <t>Setjen MPR RI mempertahankan opini WTP atas Laporan Keuangan 2025. Deputi Heri Herawan apresiasi transparansi dan akuntabilitas dalam pengelolaan keuangan.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604966/ayah-dan-paman-pemerkosa-gadis-di-situbondo-divonis-20-tahun-penjara</t>
+          <t>https://news.detik.com/berita/d-8604969/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/04/04/2e7993e1-d03b-49c3-9f3d-8a913c8dc5d2_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pertahankan-opini-wtp-setjen-mpr-ri-perkuat-tata-kelola-keuangan-1785902413926_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3826,28 +3826,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina Luka di Wajah dan Kepala Usai Diduga Dianiaya Pacar</t>
+          <t>Korban Mutilasi di Depok Ternyata Dibunuh Pria Kenalan di Medsos</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:57:57 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:27 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina diduga dianiaya kekasihnya, KB, di Jakarta Selatan. Ia mengalami luka di wajah dan kepala.</t>
+          <t>Polda Metro Jaya menangkap Saepul, pelaku mutilasi Kunaefi. Korban dan pelaku berkenalan lewat media sosial sebelum pertemuan berujung mutilasi.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604961/aktris-sali-irsalina-luka-di-wajah-dan-kepala-usai-diduga-dianiaya-pacar</t>
+          <t>https://news.detik.com/berita/d-8604968/korban-mutilasi-di-depok-ternyata-dibunuh-pria-kenalan-di-medsos</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/19/penganiayaan-mantan-pacar-di-gianyar_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3864,28 +3864,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Identitas Mayat Tanpa Kaki di Depok Terungkap, Namanya Kunaefi</t>
+          <t>Merah Putih Membelah Jalan Tangerang, Aksi Warga Sambut Kemerdekaan RI Bikin Takjub</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:56:09 +0700</t>
+          <t>Wed, 05 Aug 2026 11:00:06 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kasus mutilasi di Depok terungkap. Korban Kunaefi (51) ditemukan dalam karung. Pelaku, Saepul (26), ditangkap saat melarikan diri ke Pandeglang.</t>
+          <t>Warga Tangerang membentangkan bendera Merah Putih sepanjang 400 meter di jalan perumahan untuk menyambut HUT ke-81 Kemerdekaan RI.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604959/identitas-mayat-tanpa-kaki-di-depok-terungkap-namanya-kunaefi</t>
+          <t>https://news.detik.com/foto-news/d-8604436/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/merah-putih-membelah-jalan-tangerang-aksi-warga-sambut-kemerdekaan-ri-bikin-takjub-1785847891040_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3902,28 +3902,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Penjual Miras di Lokananta Gugat Pemkot Solo Usai Dirazia</t>
+          <t>Ayah dan Paman Pemerkosa Gadis di Situbondo Divonis 20 Tahun Penjara</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:53:36 +0700</t>
+          <t>Wed, 05 Aug 2026 10:58:57 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Manajemen kafe Ruang Bahagia menggugat Pemkot Solo setelah dirazia oleh Satpol PP.</t>
+          <t>Majelis hakim Pengadilan Negeri Situbondo, Jawa Timur, menjatuhkan vonis masing-masing 20 tahun penjara kepada BH (42) dan BS (42).</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604956/penjual-miras-di-lokananta-gugat-pemkot-solo-usai-dirazia</t>
+          <t>https://news.detik.com/berita/d-8604966/ayah-dan-paman-pemerkosa-gadis-di-situbondo-divonis-20-tahun-penjara</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sidang-di-pn-solo-1785834131308_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/04/04/2e7993e1-d03b-49c3-9f3d-8a913c8dc5d2_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ramai Kabar Amunisi AS Menipis Gegara Perang Iran, Trump Bilang Gini</t>
+          <t>Aktris Sali Irsalina Luka di Wajah dan Kepala Usai Diduga Dianiaya Pacar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:52:07 +0700</t>
+          <t>Wed, 05 Aug 2026 10:57:57 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pasokan amunisi AS dilaporkan semakin menipis hingga ke level yang mengkhawatirkan akibat perang Iran. Trump buka suara.</t>
+          <t>Aktris Sali Irsalina diduga dianiaya kekasihnya, KB, di Jakarta Selatan. Ia mengalami luka di wajah dan kepala.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604954/ramai-kabar-amunisi-as-menipis-gegara-perang-iran-trump-bilang-gini</t>
+          <t>https://news.detik.com/berita/d-8604961/aktris-sali-irsalina-luka-di-wajah-dan-kepala-usai-diduga-dianiaya-pacar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/29/44d7a464-752c-4519-91cd-6e13284a464c_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/19/penganiayaan-mantan-pacar-di-gianyar_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3978,28 +3978,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2 Truk Tabrakan di Gunungputri Bogor, Sopir Terjepit di Kabin Kemudi</t>
+          <t>Identitas Mayat Tanpa Kaki di Depok Terungkap, Namanya Kunaefi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:48:18 +0700</t>
+          <t>Wed, 05 Aug 2026 10:56:09 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dua truk terlibat kecelakaan di Jalan Raya Wanaherang, Bogor. Sopir truk mengalami luka ringan setelah terjepit di ruang kemudi dan dilarikan ke rumah sakit.</t>
+          <t>Kasus mutilasi di Depok terungkap. Korban Kunaefi (51) ditemukan dalam karung. Pelaku, Saepul (26), ditangkap saat melarikan diri ke Pandeglang.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604951/2-truk-tabrakan-di-gunungputri-bogor-sopir-terjepit-di-kabin-kemudi</t>
+          <t>https://news.detik.com/berita/d-8604959/identitas-mayat-tanpa-kaki-di-depok-terungkap-namanya-kunaefi</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612231_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4016,28 +4016,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pilu Pemuda Jabar Jadi Love Scammer di Kamboja: Tak Digaji-Dicambuk Sesama WNI</t>
+          <t>Penjual Miras di Lokananta Gugat Pemkot Solo Usai Dirazia</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:41:05 +0700</t>
+          <t>Wed, 05 Aug 2026 10:53:36 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pemuda asal Kecamatan Dayeuhkolot, Kabupaten Bandung, ini mengaku tidak digaji selama bekerja di sana hingga mendapatkan beragam penganiayaan fisik.</t>
+          <t>Manajemen kafe Ruang Bahagia menggugat Pemkot Solo setelah dirazia oleh Satpol PP.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604941/pilu-pemuda-jabar-jadi-love-scammer-di-kamboja-tak-digaji-dicambuk-sesama-wni</t>
+          <t>https://news.detik.com/berita/d-8604956/penjual-miras-di-lokananta-gugat-pemkot-solo-usai-dirazia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/rizki-nur-fadhilah-20-saat-berbincang-di-kabupaten-bandung-1785833506651_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sidang-di-pn-solo-1785834131308_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4054,28 +4054,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Anggota DPRD Tangsel Ahmad Andi Wibowo Meninggal Akibat Kecelakaan di Cipali</t>
+          <t>Ramai Kabar Amunisi AS Menipis Gegara Perang Iran, Trump Bilang Gini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:40:01 +0700</t>
+          <t>Wed, 05 Aug 2026 10:52:07 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anggota DPRD Tangerang Selatan dari fraksi PKB, Ahmad Andi Wibowo, meninggal dunia. Ahmad Andi meninggal dunia akibat kecelakaan di Tol Cipali Km 72.</t>
+          <t>Pasokan amunisi AS dilaporkan semakin menipis hingga ke level yang mengkhawatirkan akibat perang Iran. Trump buka suara.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604940/anggota-dprd-tangsel-ahmad-andi-wibowo-meninggal-akibat-kecelakaan-di-cipali</t>
+          <t>https://news.detik.com/internasional/d-8604954/ramai-kabar-amunisi-as-menipis-gegara-perang-iran-trump-bilang-gini</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ahmad-andi-wibowo-dok-istimewa-1785901183190_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/07/29/44d7a464-752c-4519-91cd-6e13284a464c_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4092,28 +4092,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Proyek Jembatan Rusia-Korut Bikin Waswas Ukraina</t>
+          <t>2 Truk Tabrakan di Gunungputri Bogor, Sopir Terjepit di Kabin Kemudi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:37:24 +0700</t>
+          <t>Wed, 05 Aug 2026 10:48:18 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Di wilayah terpencil di perbatasan Rusia-Korut, kedua negara sedang membangun jembatan. Proyek ini membuat Ukraina, yang terletak sejauh 10.000 km, waswas.</t>
+          <t>Dua truk terlibat kecelakaan di Jalan Raya Wanaherang, Bogor. Sopir truk mengalami luka ringan setelah terjepit di ruang kemudi dan dilarikan ke rumah sakit.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://news.detik.com/dw/d-8604936/proyek-jembatan-rusia-korut-bikin-waswas-ukraina</t>
+          <t>https://news.detik.com/berita/d-8604951/2-truk-tabrakan-di-gunungputri-bogor-sopir-terjepit-di-kabin-kemudi</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kenapa-ukraina-waspadai-proyek-jembatan-rusia-korut-1785901044051.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4130,28 +4130,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Diduga Dianiaya Pacar, Aktris Sinetron Sali Irsalina Lapor Polisi</t>
+          <t>Pilu Pemuda Jabar Jadi Love Scammer di Kamboja: Tak Digaji-Dicambuk Sesama WNI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:33:20 +0700</t>
+          <t>Wed, 05 Aug 2026 10:41:05 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aktris Sali Irsalina melaporkan dugaan penganiayaan oleh kekasihnya ke Polres Metro Jakarta Selatan. Ia mengalami luka akibat kekerasan fisik.</t>
+          <t>Pemuda asal Kecamatan Dayeuhkolot, Kabupaten Bandung, ini mengaku tidak digaji selama bekerja di sana hingga mendapatkan beragam penganiayaan fisik.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604926/diduga-dianiaya-pacar-aktris-sinetron-sali-irsalina-lapor-polisi</t>
+          <t>https://news.detik.com/berita/d-8604941/pilu-pemuda-jabar-jadi-love-scammer-di-kamboja-tak-digaji-dicambuk-sesama-wni</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/11/ilustrasi-kekerasan-terhadap-perempuan-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/rizki-nur-fadhilah-20-saat-berbincang-di-kabupaten-bandung-1785833506651_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4168,28 +4168,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kapolda Sumsel Serahkan Penghargaan WBK &amp;amp; Pelayanan Prima kepada 11 Satuan</t>
+          <t>Anggota DPRD Tangsel Ahmad Andi Wibowo Meninggal Akibat Kecelakaan di Cipali</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:25:23 +0700</t>
+          <t>Wed, 05 Aug 2026 10:40:01 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kapolda Sumsel, Irjen Pol. Sandi Nugroho, menyerahkan penghargaan WBK dan Pelayanan Publik Prima kepada 11 satuan kerja.</t>
+          <t>Anggota DPRD Tangerang Selatan dari fraksi PKB, Ahmad Andi Wibowo, meninggal dunia. Ahmad Andi meninggal dunia akibat kecelakaan di Tol Cipali Km 72.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8604921/kapolda-sumsel-serahkan-penghargaan-wbk-pelayanan-prima-kepada-11-satuan</t>
+          <t>https://news.detik.com/berita/d-8604940/anggota-dprd-tangsel-ahmad-andi-wibowo-meninggal-akibat-kecelakaan-di-cipali</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polda-sumsel-1785900305377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ahmad-andi-wibowo-dok-istimewa-1785901183190_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4206,28 +4206,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kuda Pacu Pemenang Kejurnas Hangus Terbakar di KM Mutiara Sentosa</t>
+          <t>Proyek Jembatan Rusia-Korut Bikin Waswas Ukraina</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:23:20 +0700</t>
+          <t>Wed, 05 Aug 2026 10:37:24 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kuda pacu yang baru meraih juara nasional milik warga Kabupaten Jeneponto, Sulsel, ikut terbakar dalam insiden KM Mutiara Sentosa 2 di perairan utara Madura.</t>
+          <t>Di wilayah terpencil di perbatasan Rusia-Korut, kedua negara sedang membangun jembatan. Proyek ini membuat Ukraina, yang terletak sejauh 10.000 km, waswas.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604917/kuda-pacu-pemenang-kejurnas-hangus-terbakar-di-km-mutiara-sentosa</t>
+          <t>https://news.detik.com/dw/d-8604936/proyek-jembatan-rusia-korut-bikin-waswas-ukraina</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kenapa-ukraina-waspadai-proyek-jembatan-rusia-korut-1785901044051.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4244,28 +4244,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pria Ber-hoodie Pembakar Bendera Juga Sasar Bangunan di Bandung dan Cimahi</t>
+          <t>Diduga Dianiaya Pacar, Aktris Sinetron Sali Irsalina Lapor Polisi</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:19:45 +0700</t>
+          <t>Wed, 05 Aug 2026 10:33:20 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Heboh aksi pria membakar bendera Merah Putih di sebuah rumah di Maleber, Kecamatan Andir, Kota Bandung, Jabar. Pria itu diduga membakar bangunan di tempat lain.</t>
+          <t>Aktris Sali Irsalina melaporkan dugaan penganiayaan oleh kekasihnya ke Polres Metro Jakarta Selatan. Ia mengalami luka akibat kekerasan fisik.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604913/pria-ber-hoodie-pembakar-bendera-juga-sasar-bangunan-di-bandung-dan-cimahi</t>
+          <t>https://news.detik.com/berita/d-8604926/diduga-dianiaya-pacar-aktris-sinetron-sali-irsalina-lapor-polisi</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/viral-aksi-pembakaran-bendera-merah-putih-di-bandung-1785755169202_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/11/ilustrasi-kekerasan-terhadap-perempuan-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4282,28 +4282,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pelaku Mutilasi di Depok Ditangkap Saat Kabur ke Pandeglang</t>
+          <t>Kapolda Sumsel Serahkan Penghargaan WBK &amp;amp; Pelayanan Prima kepada 11 Satuan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:17:26 +0700</t>
+          <t>Wed, 05 Aug 2026 10:25:23 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tim Resmob Polda Metro Jaya menangkap pelaku mutilasi di Depok, berinisial SA, saat melarikan diri ke Banten. Jasad korban ditemukan di lahan kosong.</t>
+          <t>Kapolda Sumsel, Irjen Pol. Sandi Nugroho, menyerahkan penghargaan WBK dan Pelayanan Publik Prima kepada 11 satuan kerja.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604903/pelaku-mutilasi-di-depok-ditangkap-saat-kabur-ke-pandeglang</t>
+          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8604921/kapolda-sumsel-serahkan-penghargaan-wbk-pelayanan-prima-kepada-11-satuan</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polda-sumsel-1785900305377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4320,28 +4320,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Viral Sejumlah Pemotor Jatuh gegara Tetesan Air Lindi di Bantargebang</t>
+          <t>Kuda Pacu Pemenang Kejurnas Hangus Terbakar di KM Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:13:21 +0700</t>
+          <t>Wed, 05 Aug 2026 10:23:20 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sejumlah pemotor terjatuh di Jalan Siliwangi Pangkalan 5, Bantargebang, Kota Bekasi. Peristiwa itu diduga terjadi akibat jalan linci karena tetesan air lindi.</t>
+          <t>Kuda pacu yang baru meraih juara nasional milik warga Kabupaten Jeneponto, Sulsel, ikut terbakar dalam insiden KM Mutiara Sentosa 2 di perairan utara Madura.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604899/viral-sejumlah-pemotor-jatuh-gegara-tetesan-air-lindi-di-bantargebang</t>
+          <t>https://news.detik.com/berita/d-8604917/kuda-pacu-pemenang-kejurnas-hangus-terbakar-di-km-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sejumlah-pemotor-berjatuhan-di-bantargebang-kota-bekasi-akibat-tetesan-air-lindi-1785899556055_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671217151_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Berkas Lengkap, 3 Tersangka Kasus Tambang Emas Ilegal Segera Disidang</t>
+          <t>Pria Ber-hoodie Pembakar Bendera Juga Sasar Bangunan di Bandung dan Cimahi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:07:53 +0700</t>
+          <t>Wed, 05 Aug 2026 10:19:45 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Polisi menetapkan 5 tersangka dalam kasus tambang emas ilegal. Tiga berkas perkara telah lengkap dan siap disidang, sementara dua lainnya masih dalam proses.</t>
+          <t>Heboh aksi pria membakar bendera Merah Putih di sebuah rumah di Maleber, Kecamatan Andir, Kota Bandung, Jabar. Pria itu diduga membakar bangunan di tempat lain.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604893/berkas-lengkap-3-tersangka-kasus-tambang-emas-ilegal-segera-disidang</t>
+          <t>https://news.detik.com/berita/d-8604913/pria-ber-hoodie-pembakar-bendera-juga-sasar-bangunan-di-bandung-dan-cimahi</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-polri-bongkar-kasus-tambang-emas-ilegal-1785899230949_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/viral-aksi-pembakaran-bendera-merah-putih-di-bandung-1785755169202_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4396,28 +4396,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Resmob Polda Metro Jaya Tangkap Pelaku Mutilasi di Depok!</t>
+          <t>Pelaku Mutilasi di Depok Ditangkap Saat Kabur ke Pandeglang</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:06:11 +0700</t>
+          <t>Wed, 05 Aug 2026 10:17:26 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kasus mayat mutilasi di Pancoran Mas, Depok terungkap. Polisi telah menangkap pelaku, sementara motif pembunuhan masih didalami kepolisian.</t>
+          <t>Tim Resmob Polda Metro Jaya menangkap pelaku mutilasi di Depok, berinisial SA, saat melarikan diri ke Banten. Jasad korban ditemukan di lahan kosong.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604889/resmob-polda-metro-jaya-tangkap-pelaku-mutilasi-di-depok</t>
+          <t>https://news.detik.com/berita/d-8604903/pelaku-mutilasi-di-depok-ditangkap-saat-kabur-ke-pandeglang</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/03/ilustrasi-pelaku-pencabulan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4434,28 +4434,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Air Embung Surut, Nasib Ratusan Hektare Sawah Indramayu di Ujung Ancaman</t>
+          <t>Viral Sejumlah Pemotor Jatuh gegara Tetesan Air Lindi di Bantargebang</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:00:59 +0700</t>
+          <t>Wed, 05 Aug 2026 10:13:21 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Embung irigasi Balongan, Indramayu, mengering akibat minim hujan. Dasar embung terlihat kering hingga menyisakan bangkai ikan.</t>
+          <t>Sejumlah pemotor terjatuh di Jalan Siliwangi Pangkalan 5, Bantargebang, Kota Bekasi. Peristiwa itu diduga terjadi akibat jalan linci karena tetesan air lindi.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8604424/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman</t>
+          <t>https://news.detik.com/berita/d-8604899/viral-sejumlah-pemotor-jatuh-gegara-tetesan-air-lindi-di-bantargebang</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman-1785847218259_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sejumlah-pemotor-berjatuhan-di-bantargebang-kota-bekasi-akibat-tetesan-air-lindi-1785899556055_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4472,28 +4472,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Daftar Upacara HUT ke-81 RI di Istana: Jadwal, Cara, Syarat</t>
+          <t>Berkas Lengkap, 3 Tersangka Kasus Tambang Emas Ilegal Segera Disidang</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:59:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:07:53 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pendaftaran upacara HUT ke-81 RI dibuka 5-7 Agustus 2026. Siapkan dokumen dan ikuti syarat untuk mendaftar secara gratis di Istana Merdeka.</t>
+          <t>Polisi menetapkan 5 tersangka dalam kasus tambang emas ilegal. Tiga berkas perkara telah lengkap dan siap disidang, sementara dua lainnya masih dalam proses.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604878/daftar-upacara-hut-ke-81-ri-di-istana-jadwal-cara-syarat</t>
+          <t>https://news.detik.com/berita/d-8604893/berkas-lengkap-3-tersangka-kasus-tambang-emas-ilegal-segera-disidang</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/17/momen-upacara-detik-detik-proklamasi-di-istana-merdeka-1755407430559_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bareskrim-polri-bongkar-kasus-tambang-emas-ilegal-1785899230949_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4510,28 +4510,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kapal India Tenggelam Usai Diserang di Laut Merah, 14 ABK Selamat</t>
+          <t>Resmob Polda Metro Jaya Tangkap Pelaku Mutilasi di Depok!</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:57:39 +0700</t>
+          <t>Wed, 05 Aug 2026 10:06:11 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sebuah kapal komersial berbendera India tenggelam setelah dihantam serangan di Laut Merah. Untungnya, semua ABK berhasil diselamatkan.</t>
+          <t>Kasus mayat mutilasi di Pancoran Mas, Depok terungkap. Polisi telah menangkap pelaku, sementara motif pembunuhan masih didalami kepolisian.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604874/kapal-india-tenggelam-usai-diserang-di-laut-merah-14-abk-selamat</t>
+          <t>https://news.detik.com/berita/d-8604889/resmob-polda-metro-jaya-tangkap-pelaku-mutilasi-di-depok</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/iran-crisisyemen-red-sea-1784214791940_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4548,28 +4548,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mesin Mati Mendadak, Mobil Terbakar di Tol Jagorawi Arah Jakarta</t>
+          <t>Air Embung Surut, Nasib Ratusan Hektare Sawah Indramayu di Ujung Ancaman</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:52:13 +0700</t>
+          <t>Wed, 05 Aug 2026 10:00:59 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Satu unit mobil SUV terbakar di Km 43/100 Tol Jagorawi, Bogor Timur, Kota Bogor. Kebakaran usai mesin mobil mati dan muncul api dari bawah kap depan.</t>
+          <t>Embung irigasi Balongan, Indramayu, mengering akibat minim hujan. Dasar embung terlihat kering hingga menyisakan bangkai ikan.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604866/mesin-mati-mendadak-mobil-terbakar-di-tol-jagorawi-arah-jakarta</t>
+          <t>https://news.detik.com/foto-news/d-8604424/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satu-unit-mobil-suv-terbakar-di-km-43100-tol-jagorawi-bogor-timur-kota-bogor-dok-istimewa-1785898155496_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/air-embung-surut-nasib-ratusan-hektare-sawah-indramayu-di-ujung-ancaman-1785847218259_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4586,28 +4586,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kondisi Mayat Mutilasi di Depok: Tangan Terikat dan Leher Luka Sayat</t>
+          <t>Daftar Upacara HUT ke-81 RI di Istana: Jadwal, Cara, Syarat</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:42:22 +0700</t>
+          <t>Wed, 05 Aug 2026 09:59:39 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pihak kepolisian menyelidiki penemuan mayat mutilasi di Pancoran Mas, Depok. Korban ditemukan tanpa kaki, terikat, dan dalam kondisi mengenaskan.</t>
+          <t>Pendaftaran upacara HUT ke-81 RI dibuka 5-7 Agustus 2026. Siapkan dokumen dan ikuti syarat untuk mendaftar secara gratis di Istana Merdeka.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604858/kondisi-mayat-mutilasi-di-depok-tangan-terikat-dan-leher-luka-sayat</t>
+          <t>https://news.detik.com/berita/d-8604878/daftar-upacara-hut-ke-81-ri-di-istana-jadwal-cara-syarat</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/17/momen-upacara-detik-detik-proklamasi-di-istana-merdeka-1755407430559_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4624,28 +4624,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trump Cabut Visa Duta Besar Brasil untuk AS, Ada Apa?</t>
+          <t>Kapal India Tenggelam Usai Diserang di Laut Merah, 14 ABK Selamat</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:34:55 +0700</t>
+          <t>Wed, 05 Aug 2026 09:57:39 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pemerintahan Trump mencabut visa DUbes Brasil untuk AS, Maria Luiz Ribeiro Viotti. Apa alasannya?</t>
+          <t>Sebuah kapal komersial berbendera India tenggelam setelah dihantam serangan di Laut Merah. Untungnya, semua ABK berhasil diselamatkan.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604850/trump-cabut-visa-duta-besar-brasil-untuk-as-ada-apa</t>
+          <t>https://news.detik.com/internasional/d-8604874/kapal-india-tenggelam-usai-diserang-di-laut-merah-14-abk-selamat</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dubes-brasil-untuk-as-maria-luiza-ribeiro-viotti-1785897254293_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/iran-crisisyemen-red-sea-1784214791940_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4662,28 +4662,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Misteri Mayat Mutilasi di Depok Dibuang 12 Hari Lalu</t>
+          <t>Mesin Mati Mendadak, Mobil Terbakar di Tol Jagorawi Arah Jakarta</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:26:42 +0700</t>
+          <t>Wed, 05 Aug 2026 09:52:13 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jasad pria mutilasi ditemukan di Pancoran Mas, Depok, setelah 12 hari. Identitas korban belum diketahui, polisi masih menyelidiki kasus ini.</t>
+          <t>Satu unit mobil SUV terbakar di Km 43/100 Tol Jagorawi, Bogor Timur, Kota Bogor. Kebakaran usai mesin mobil mati dan muncul api dari bawah kap depan.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604839/misteri-mayat-mutilasi-di-depok-dibuang-12-hari-lalu</t>
+          <t>https://news.detik.com/berita/d-8604866/mesin-mati-mendadak-mobil-terbakar-di-tol-jagorawi-arah-jakarta</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satu-unit-mobil-suv-terbakar-di-km-43100-tol-jagorawi-bogor-timur-kota-bogor-dok-istimewa-1785898155496_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4700,28 +4700,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RI Kecam Keras Israel Serang Gaza Lagi: Sengaja Hambat Peace Plan</t>
+          <t>Kondisi Mayat Mutilasi di Depok: Tangan Terikat dan Leher Luka Sayat</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:23:19 +0700</t>
+          <t>Wed, 05 Aug 2026 09:42:22 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Indonesia mengecam serangan Israel ke Gaza yang menghambat kesepakatan perdamaian. Kemlu mendesak Israel menghentikan serangan dan memenuhi komitmen perjanjian.</t>
+          <t>Pihak kepolisian menyelidiki penemuan mayat mutilasi di Pancoran Mas, Depok. Korban ditemukan tanpa kaki, terikat, dan dalam kondisi mengenaskan.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604835/ri-kecam-keras-israel-serang-gaza-lagi-sengaja-hambat-peace-plan</t>
+          <t>https://news.detik.com/berita/d-8604858/kondisi-mayat-mutilasi-di-depok-tangan-terikat-dan-leher-luka-sayat</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/09/11/gedung-pancasila-di-kemlu_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4738,28 +4738,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Siap-siap War! Tiket Upacara HUT ke-81 RI di Istana Dibuka Hari Ini Pukul 10.00</t>
+          <t>Trump Cabut Visa Duta Besar Brasil untuk AS, Ada Apa?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:21:08 +0700</t>
+          <t>Wed, 05 Aug 2026 09:34:55 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pemerintah sudah membuka pendaftaran upacara HUT ke-81 RI di Istana Merdeka Jakarta. Siap-siap war!</t>
+          <t>Pemerintahan Trump mencabut visa DUbes Brasil untuk AS, Maria Luiz Ribeiro Viotti. Apa alasannya?</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604828/siap-siap-war-tiket-upacara-hut-ke-81-ri-di-istana-dibuka-hari-ini-pukul-10-00</t>
+          <t>https://news.detik.com/internasional/d-8604850/trump-cabut-visa-duta-besar-brasil-untuk-as-ada-apa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/01/31/85d6b0ca-c154-414b-a198-62b91ce4debc_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dubes-brasil-untuk-as-maria-luiza-ribeiro-viotti-1785897254293_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4776,28 +4776,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jakarta Selatan Diprediksi Hujan Ringan Sore Ini</t>
+          <t>Misteri Mayat Mutilasi di Depok Dibuang 12 Hari Lalu</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:56:17 +0700</t>
+          <t>Wed, 05 Aug 2026 09:26:42 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BMKG mengungkap sebagian wilayah di Jakarta Selatan berpotensi hujan ringan hari ini.</t>
+          <t>Jasad pria mutilasi ditemukan di Pancoran Mas, Depok, setelah 12 hari. Identitas korban belum diketahui, polisi masih menyelidiki kasus ini.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604809/jakarta-selatan-diprediksi-hujan-ringan-sore-ini</t>
+          <t>https://news.detik.com/berita/d-8604839/misteri-mayat-mutilasi-di-depok-dibuang-12-hari-lalu</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/30/ilustrasi-hujan_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4814,28 +4814,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MKD DPR Gelar Rapim Pekan Depan Bahas Laporan 'Kayak Sirkus' ke Deddy Sitorus</t>
+          <t>RI Kecam Keras Israel Serang Gaza Lagi: Sengaja Hambat Peace Plan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:53:44 +0700</t>
+          <t>Wed, 05 Aug 2026 09:23:19 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mahkamah Kehormatan Dewan DPR RI akan rapat menindaklanjuti laporan wartawan terhadap Deddy Sitorus.</t>
+          <t>Indonesia mengecam serangan Israel ke Gaza yang menghambat kesepakatan perdamaian. Kemlu mendesak Israel menghentikan serangan dan memenuhi komitmen perjanjian.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604811/mkd-dpr-gelar-rapim-pekan-depan-bahas-laporan-kayak-sirkus-ke-deddy-sitorus</t>
+          <t>https://news.detik.com/berita/d-8604835/ri-kecam-keras-israel-serang-gaza-lagi-sengaja-hambat-peace-plan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mkd-1785865852673_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/09/11/gedung-pancasila-di-kemlu_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4852,28 +4852,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mendagri Wanti-wanti Kepala Daerah Jaga Integritas demi Cegah Korupsi</t>
+          <t>Siap-siap War! Tiket Upacara HUT ke-81 RI di Istana Dibuka Hari Ini Pukul 10.00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:51:47 +0700</t>
+          <t>Wed, 05 Aug 2026 09:21:08 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mendagri Tito Karnavian menekankan pentingnya integritas kepala daerah dalam mencegah korupsi. Rakor di Surabaya bertujuan memperkuat tata kelola pemerintahan.</t>
+          <t>Pemerintah sudah membuka pendaftaran upacara HUT ke-81 RI di Istana Merdeka Jakarta. Siap-siap war!</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604793/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi</t>
+          <t>https://news.detik.com/berita/d-8604828/siap-siap-war-tiket-upacara-hut-ke-81-ri-di-istana-dibuka-hari-ini-pukul-10-00</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/01/31/85d6b0ca-c154-414b-a198-62b91ce4debc_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4890,28 +4890,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LRT Dukung Pramono Hubungkan 2 JPO Viral Dekat tapi Tak Tersambung di Rasuna</t>
+          <t>Jakarta Selatan Diprediksi Hujan Ringan Sore Ini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:45:13 +0700</t>
+          <t>Wed, 05 Aug 2026 08:56:17 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gubernur DKI Pramono berjanji menyambungkan dua JPO yang viral di Jalan HR Rasuna Said. LRT Jabodebek siap berkoordinasi.</t>
+          <t>BMKG mengungkap sebagian wilayah di Jakarta Selatan berpotensi hujan ringan hari ini.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604779/lrt-dukung-pramono-hubungkan-2-jpo-viral-dekat-tapi-tak-tersambung-di-rasuna</t>
+          <t>https://news.detik.com/berita/d-8604809/jakarta-selatan-diprediksi-hujan-ringan-sore-ini</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313180_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/30/ilustrasi-hujan_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Komisi V DPR Bakal Panggil Kemenhub Buntut Kebakaran KMP Mutiara Sentosa</t>
+          <t>MKD DPR Gelar Rapim Pekan Depan Bahas Laporan 'Kayak Sirkus' ke Deddy Sitorus</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:35:39 +0700</t>
+          <t>Wed, 05 Aug 2026 08:53:44 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Komisi V DPR RI akan memanggil Kemenhub terkait kebakaran KMP Mutiara Sentosa 2. Rapat dengan Kemenhub digelar seusai reses DPR RI.</t>
+          <t>Mahkamah Kehormatan Dewan DPR RI akan rapat menindaklanjuti laporan wartawan terhadap Deddy Sitorus.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604773/komisi-v-dpr-bakal-panggil-kemenhub-buntut-kebakaran-kmp-mutiara-sentosa</t>
+          <t>https://news.detik.com/berita/d-8604811/mkd-dpr-gelar-rapim-pekan-depan-bahas-laporan-kayak-sirkus-ke-deddy-sitorus</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mkd-1785865852673_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4966,28 +4966,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Jelang Kunjungan Trump, Pria Bersenjata Ditangkap di Lapangan Golf Los Angeles</t>
+          <t>Mendagri Wanti-wanti Kepala Daerah Jaga Integritas demi Cegah Korupsi</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:34:23 +0700</t>
+          <t>Wed, 05 Aug 2026 08:51:47 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Seorang pria bersenjata ditangkap di lapangan golf Trump di LA, dua hari sebelum kunjungannya. Penyelidik menemukan senjata dan catatan mencurigakan.</t>
+          <t>Mendagri Tito Karnavian menekankan pentingnya integritas kepala daerah dalam mencegah korupsi. Rakor di Surabaya bertujuan memperkuat tata kelola pemerintahan.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604771/jelang-kunjungan-trump-pria-bersenjata-ditangkap-di-lapangan-golf-los-angeles</t>
+          <t>https://news.detik.com/berita/d-8604793/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/trump-saat-berpidato-di-gedung-putih-pada-kamis-167-malam-1784277022942_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5004,28 +5004,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U-turn Depan Stasiun Depok Ditutup, Lalin Arah Jakarta Lancar Pagi Ini</t>
+          <t>LRT Dukung Pramono Hubungkan 2 JPO Viral Dekat tapi Tak Tersambung di Rasuna</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:43 +0700</t>
+          <t>Wed, 05 Aug 2026 08:45:13 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Satlantas Polres Metro Depok dan Dishub menutup U-turn di Jalan Kartini untuk mengurangi kemacetan. Penutupan berlaku pada jam sibuk, efektif mulai 3 Agustus.</t>
+          <t>Gubernur DKI Pramono berjanji menyambungkan dua JPO yang viral di Jalan HR Rasuna Said. LRT Jabodebek siap berkoordinasi.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604766/u-turn-depan-stasiun-depok-ditutup-lalin-arah-jakarta-lancar-pagi-ini</t>
+          <t>https://news.detik.com/berita/d-8604779/lrt-dukung-pramono-hubungkan-2-jpo-viral-dekat-tapi-tak-tersambung-di-rasuna</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/u-turn-putaran-balik-di-jalan-kartini-depok-ditutup-1785893424229_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313180_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5042,28 +5042,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sekda Konawe Selatan Tabrak Adik Saat Digerebek Bareng Selingkuhan di Mobil</t>
+          <t>Komisi V DPR Bakal Panggil Kemenhub Buntut Kebakaran KMP Mutiara Sentosa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:40 +0700</t>
+          <t>Wed, 05 Aug 2026 08:35:39 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sekda Konawe Selatan Ichsan Porosi (56) menabrak adik kandungnya, Andriani Porosi alias AP (50), saat digerebek berduaan diduga bareng selingkuhan di mobil.</t>
+          <t>Komisi V DPR RI akan memanggil Kemenhub terkait kebakaran KMP Mutiara Sentosa 2. Rapat dengan Kemenhub digelar seusai reses DPR RI.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604765/sekda-konawe-selatan-tabrak-adik-saat-digerebek-bareng-selingkuhan-di-mobil</t>
+          <t>https://news.detik.com/berita/d-8604773/komisi-v-dpr-bakal-panggil-kemenhub-buntut-kebakaran-kmp-mutiara-sentosa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5080,28 +5080,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Penjelasan BMKG soal Hujan di Jakarta Usai Berminggu-minggu Kering</t>
+          <t>Jelang Kunjungan Trump, Pria Bersenjata Ditangkap di Lapangan Golf Los Angeles</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:24:21 +0700</t>
+          <t>Wed, 05 Aug 2026 08:34:23 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hujan turun di Jakarta setelah kering berminggu-minggu. Ini penjelasan BMKG.</t>
+          <t>Seorang pria bersenjata ditangkap di lapangan golf Trump di LA, dua hari sebelum kunjungannya. Penyelidik menemukan senjata dan catatan mencurigakan.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604764/penjelasan-bmkg-soal-hujan-di-jakarta-usai-berminggu-minggu-kering</t>
+          <t>https://news.detik.com/internasional/d-8604771/jelang-kunjungan-trump-pria-bersenjata-ditangkap-di-lapangan-golf-los-angeles</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hujan-deras-guyur-jakarta-usai-berminggu-minggu-kering-1785846576327_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/trump-saat-berpidato-di-gedung-putih-pada-kamis-167-malam-1784277022942_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5118,28 +5118,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Puan Berduka KM Mutiara Terbakar: Keamanan Transportasi Laut RI Masih Minim</t>
+          <t>U-turn Depan Stasiun Depok Ditutup, Lalin Arah Jakarta Lancar Pagi Ini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:15:49 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:43 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KM Mutiara Sentosa 2 terbakar di Madura, menewaskan lima orang. Puan Maharani soroti minimnya keamanan transportasi laut.</t>
+          <t>Satlantas Polres Metro Depok dan Dishub menutup U-turn di Jalan Kartini untuk mengurangi kemacetan. Penutupan berlaku pada jam sibuk, efektif mulai 3 Agustus.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604759/puan-berduka-km-mutiara-terbakar-keamanan-transportasi-laut-ri-masih-minim</t>
+          <t>https://news.detik.com/berita/d-8604766/u-turn-depan-stasiun-depok-ditutup-lalin-arah-jakarta-lancar-pagi-ini</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/puan-maharani-1777615358543_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/u-turn-putaran-balik-di-jalan-kartini-depok-ditutup-1785893424229_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5156,28 +5156,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Duduk Perkara Pria di Tangerang Dipaksa Masturbasi hingga Disiksa</t>
+          <t>Sekda Konawe Selatan Tabrak Adik Saat Digerebek Bareng Selingkuhan di Mobil</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:04:14 +0700</t>
+          <t>Wed, 05 Aug 2026 08:30:40 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Seorang pria diduga dianiaya bos dan rekan kerjanya di Kabupaten Tangerang, Banten. Korban juga diduga dipaksa masturbasi sambil menonton film porno.</t>
+          <t>Sekda Konawe Selatan Ichsan Porosi (56) menabrak adik kandungnya, Andriani Porosi alias AP (50), saat digerebek berduaan diduga bareng selingkuhan di mobil.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604752/duduk-perkara-pria-di-tangerang-dipaksa-masturbasi-hingga-disiksa</t>
+          <t>https://news.detik.com/berita/d-8604765/sekda-konawe-selatan-tabrak-adik-saat-digerebek-bareng-selingkuhan-di-mobil</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5194,28 +5194,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ketua DPRD Surabaya Dorong Sinergi Warga-Aparat Jaga Kota Kondusif</t>
+          <t>Penjelasan BMKG soal Hujan di Jakarta Usai Berminggu-minggu Kering</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:02:41 +0700</t>
+          <t>Wed, 05 Aug 2026 08:24:21 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ketua DPRD Surabaya, Syaifudin Zuhri, menekankan pentingnya peran masyarakat dalam menjaga keamanan kota.</t>
+          <t>Hujan turun di Jakarta setelah kering berminggu-minggu. Ini penjelasan BMKG.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604677/ketua-dprd-surabaya-dorong-sinergi-warga-aparat-jaga-kota-kondusif</t>
+          <t>https://news.detik.com/berita/d-8604764/penjelasan-bmkg-soal-hujan-di-jakarta-usai-berminggu-minggu-kering</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dprd-surabaya-1785886861092_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hujan-deras-guyur-jakarta-usai-berminggu-minggu-kering-1785846576327_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5232,28 +5232,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Adrien Schneider, Buron High Profile Asal Prancis Ditangkap di Jakarta</t>
+          <t>Puan Berduka KM Mutiara Terbakar: Keamanan Transportasi Laut RI Masih Minim</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:02:31 +0700</t>
+          <t>Wed, 05 Aug 2026 08:15:49 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Buron high profile Prancis, Adrien Schneider, ditangkap di Jakarta. Dia terlibat pembunuhan dan kejahatan berat, kini dalam proses deportasi ke Prancis.</t>
+          <t>KM Mutiara Sentosa 2 terbakar di Madura, menewaskan lima orang. Puan Maharani soroti minimnya keamanan transportasi laut.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604749/adrien-schneider-buron-high-profile-asal-prancis-ditangkap-di-jakarta</t>
+          <t>https://news.detik.com/berita/d-8604759/puan-berduka-km-mutiara-terbakar-keamanan-transportasi-laut-ri-masih-minim</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adrien-schneider-buron-high-profile-asal-prancis-dideportasi-ke-negaranya-setelah-tertangkap-usai-bersembunyi-di-sumbawa-dan-b-1785891665606_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/puan-maharani-1777615358543_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5270,28 +5270,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Aksi Perekam Usher GIIAS Bikin Resah Kini Diusut Polisi</t>
+          <t>Duduk Perkara Pria di Tangerang Dipaksa Masturbasi hingga Disiksa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:55:46 +0700</t>
+          <t>Wed, 05 Aug 2026 08:04:14 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Polemik perekaman usher di GIIAS 2026 berlanjut. Polisi menyelidiki kasus ini setelah korban merasa tidak nyaman.</t>
+          <t>Seorang pria diduga dianiaya bos dan rekan kerjanya di Kabupaten Tangerang, Banten. Korban juga diduga dipaksa masturbasi sambil menonton film porno.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604735/aksi-perekam-usher-giias-bikin-resah-kini-diusut-polisi</t>
+          <t>https://news.detik.com/berita/d-8604752/duduk-perkara-pria-di-tangerang-dipaksa-masturbasi-hingga-disiksa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/video-yang-menjadikan-usher-spg-di-giias-2026-sebagai-objek-konten-berjudul-cara-mendekati-cewek-ramai-dikritik-ppembuat-konte-1785733892086_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/08/3fc3b526-7901-496f-a246-3044f7c11820_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5308,28 +5308,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2 Pengamen Pemukul Pengunjung GTC Cirebon Ditangkap</t>
+          <t>Ketua DPRD Surabaya Dorong Sinergi Warga-Aparat Jaga Kota Kondusif</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:54:18 +0700</t>
+          <t>Wed, 05 Aug 2026 08:02:41 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dua pengamen ditangkap polisi di Cirebon setelah terlibat keributan dengan pengunjung. Mereka terancam hukuman lima tahun penjara akibat kekerasan.</t>
+          <t>Ketua DPRD Surabaya, Syaifudin Zuhri, menekankan pentingnya peran masyarakat dalam menjaga keamanan kota.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604733/2-pengamen-pemukul-pengunjung-gtc-cirebon-ditangkap</t>
+          <t>https://news.detik.com/berita/d-8604677/ketua-dprd-surabaya-dorong-sinergi-warga-aparat-jaga-kota-kondusif</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-cirebon-kota-akbp-bimantoro-kurniawan-1785889392099_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dprd-surabaya-1785886861092_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ada Pengecoran Jalan, Jalan Raya Bogor Arah Pasar Rebo Jaktim Macet</t>
+          <t>Adrien Schneider, Buron High Profile Asal Prancis Ditangkap di Jakarta</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:36:58 +0700</t>
+          <t>Wed, 05 Aug 2026 08:02:31 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kemacetan terjadi di Jalan Raya Bogor, Jakarta Timur (Jaktim) pagi ini. Kemacetan itu imbas adanya pengecoran jalan.</t>
+          <t>Buron high profile Prancis, Adrien Schneider, ditangkap di Jakarta. Dia terlibat pembunuhan dan kejahatan berat, kini dalam proses deportasi ke Prancis.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604724/ada-pengecoran-jalan-jalan-raya-bogor-arah-pasar-rebo-jaktim-macet</t>
+          <t>https://news.detik.com/berita/d-8604749/adrien-schneider-buron-high-profile-asal-prancis-ditangkap-di-jakarta</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemacetan-terjadi-di-jalan-raya-bogor-jakarta-timur-jaktim-pagi-ini-kemacetan-itu-imbas-adanya-pengecoran-jalan-dok-tmc-polda--1785890168558_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adrien-schneider-buron-high-profile-asal-prancis-dideportasi-ke-negaranya-setelah-tertangkap-usai-bersembunyi-di-sumbawa-dan-b-1785891665606_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Patgulipat Bisnis Don Ritto Tempat Cuci Uang Febrie Diungkap</t>
+          <t>Aksi Perekam Usher GIIAS Bikin Resah Kini Diusut Polisi</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:32:33 +0700</t>
+          <t>Wed, 05 Aug 2026 07:55:46 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kejagung mengungkap perusahaan yang diduga terkait kasus TPPU eks Jampidsus Febrie Adriansyah. Perusahaan milik Don Ritto diduga menjadi tempat pencucian.</t>
+          <t>Polemik perekaman usher di GIIAS 2026 berlanjut. Polisi menyelidiki kasus ini setelah korban merasa tidak nyaman.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604720/patgulipat-bisnis-don-ritto-tempat-cuci-uang-febrie-diungkap</t>
+          <t>https://news.detik.com/berita/d-8604735/aksi-perekam-usher-giias-bikin-resah-kini-diusut-polisi</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/video-yang-menjadikan-usher-spg-di-giias-2026-sebagai-objek-konten-berjudul-cara-mendekati-cewek-ramai-dikritik-ppembuat-konte-1785733892086_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5422,28 +5422,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Momen 35 Orang Bantu Pemakaman Wanita Berbobot 300 Kg di Sragen</t>
+          <t>2 Pengamen Pemukul Pengunjung GTC Cirebon Ditangkap</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:16:37 +0700</t>
+          <t>Wed, 05 Aug 2026 07:54:18 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Perempuan berbobot 300 kg berinisial I (39), warga Sragen Tengah, Kabupaten Sragen, meninggal dunia usai mengalami sesak napas.</t>
+          <t>Dua pengamen ditangkap polisi di Cirebon setelah terlibat keributan dengan pengunjung. Mereka terancam hukuman lima tahun penjara akibat kekerasan.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604715/momen-35-orang-bantu-pemakaman-wanita-berbobot-300-kg-di-sragen</t>
+          <t>https://news.detik.com/berita/d-8604733/2-pengamen-pemukul-pengunjung-gtc-cirebon-ditangkap</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-cirebon-kota-akbp-bimantoro-kurniawan-1785889392099_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5460,28 +5460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Perkara Kopilot Kurir 26 Kg Ekstasi di Soetta Juga Diusut Malaysia</t>
+          <t>Ada Pengecoran Jalan, Jalan Raya Bogor Arah Pasar Rebo Jaktim Macet</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:55:26 +0700</t>
+          <t>Wed, 05 Aug 2026 07:36:58 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kopilot Malaysia Airlines ditangkap di Indonesia karena menyelundupkan 70 ribu butir ekstasi. Polisi Malaysia kini menyelidiki keterlibatan petugas bandara.</t>
+          <t>Kemacetan terjadi di Jalan Raya Bogor, Jakarta Timur (Jaktim) pagi ini. Kemacetan itu imbas adanya pengecoran jalan.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604681/perkara-kopilot-kurir-26-kg-ekstasi-di-soetta-juga-diusut-malaysia</t>
+          <t>https://news.detik.com/berita/d-8604724/ada-pengecoran-jalan-jalan-raya-bogor-arah-pasar-rebo-jaktim-macet</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemacetan-terjadi-di-jalan-raya-bogor-jakarta-timur-jaktim-pagi-ini-kemacetan-itu-imbas-adanya-pengecoran-jalan-dok-tmc-polda--1785890168558_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5498,28 +5498,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nasib 2 JPO 'Dekat tapi Tak Jadian' di Rasuna Said</t>
+          <t>Patgulipat Bisnis Don Ritto Tempat Cuci Uang Febrie Diungkap</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:36:52 +0700</t>
+          <t>Wed, 05 Aug 2026 07:32:33 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dua JPO di Jalan HR Rasuna Said, Jakarta, berdekatan tapi tak terhubung. Gubernur Pramono menindaklanjuti keluhan warga itu.</t>
+          <t>Kejagung mengungkap perusahaan yang diduga terkait kasus TPPU eks Jampidsus Febrie Adriansyah. Perusahaan milik Don Ritto diduga menjadi tempat pencucian.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604674/nasib-2-jpo-dekat-tapi-tak-jadian-di-rasuna-said</t>
+          <t>https://news.detik.com/berita/d-8604720/patgulipat-bisnis-don-ritto-tempat-cuci-uang-febrie-diungkap</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313058_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5536,28 +5536,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Drama Atlet Golf Jesslyn Wijaya Disetop Sebab Bukan Penculikan</t>
+          <t>Momen 35 Orang Bantu Pemakaman Wanita Berbobot 300 Kg di Sragen</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:59:57 +0700</t>
+          <t>Wed, 05 Aug 2026 07:16:37 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kabar atlet golf Jesslyn Wijaya (34) diculik telah terpatahkan. Penyidikan kasus itu kini akan disetop kepolisian.</t>
+          <t>Perempuan berbobot 300 kg berinisial I (39), warga Sragen Tengah, Kabupaten Sragen, meninggal dunia usai mengalami sesak napas.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604657/drama-atlet-golf-jesslyn-wijaya-disetop-sebab-bukan-penculikan</t>
+          <t>https://news.detik.com/berita/d-8604715/momen-35-orang-bantu-pemakaman-wanita-berbobot-300-kg-di-sragen</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/atlet-golf-putri-jesslyn-wijaya-lay-dok-ig-jesswijgolf-1784630812506_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5574,28 +5574,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ultimatum Trump Sebelum 'Pancung' Iran</t>
+          <t>Perkara Kopilot Kurir 26 Kg Ekstasi di Soetta Juga Diusut Malaysia</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:43:04 +0700</t>
+          <t>Wed, 05 Aug 2026 06:55:26 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trump marah pada Iran yang bantah negosiasi. Ia beri ultimatum: kesepakatan atau penyerahan total. Iran menegaskan tidak ada dialog dengan AS.</t>
+          <t>Kopilot Malaysia Airlines ditangkap di Indonesia karena menyelundupkan 70 ribu butir ekstasi. Polisi Malaysia kini menyelidiki keterlibatan petugas bandara.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604651/ultimatum-trump-sebelum-pancung-iran</t>
+          <t>https://news.detik.com/berita/d-8604681/perkara-kopilot-kurir-26-kg-ekstasi-di-soetta-juga-diusut-malaysia</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/tarif-10-berakhir-trump-berlakukan-bea-masuk-baru-terhadap-60-mitra-dagang-1784889297458_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5612,28 +5612,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Korban Tewas Gelombang Migran Ilegal di Ceuta Spanyol Jadi 77 orang</t>
+          <t>Nasib 2 JPO 'Dekat tapi Tak Jadian' di Rasuna Said</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:31:03 +0700</t>
+          <t>Wed, 05 Aug 2026 06:36:52 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Serbuan migran ilegal dari Maroko ke Ceuta, Spanyol, menyebabkan 77 tewas. Banyak yang tenggelam saat mencoba melewati penghalang Laut Mediterania.</t>
+          <t>Dua JPO di Jalan HR Rasuna Said, Jakarta, berdekatan tapi tak terhubung. Gubernur Pramono menindaklanjuti keluhan warga itu.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604650/korban-tewas-gelombang-migran-ilegal-di-ceuta-spanyol-jadi-77-orang</t>
+          <t>https://news.detik.com/berita/d-8604674/nasib-2-jpo-dekat-tapi-tak-jadian-di-rasuna-said</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/spanyol-kerahkan-militer-ke-ceuta-atasi-krisis-migran-1785493658510_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/penampakan-dua-jpo-deketan-tapi-tak-nyambung-di-rasuna-said-jaksel-kurniawandetikcom-1785817313058_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5650,28 +5650,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Operasi SAR Pencarian Korban KM Mutiara Sentosa 2 Ditutup</t>
+          <t>Drama Atlet Golf Jesslyn Wijaya Disetop Sebab Bukan Penculikan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:06:19 +0700</t>
+          <t>Wed, 05 Aug 2026 05:59:57 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Basarnas resmi menghentikan operasi SAR KM Mutiara Sentosa II setelah 238 orang berhasil didata. Operasi kini beralih ke kesiapsiagaan rutin.</t>
+          <t>Kabar atlet golf Jesslyn Wijaya (34) diculik telah terpatahkan. Penyidikan kasus itu kini akan disetop kepolisian.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604649/operasi-sar-pencarian-korban-km-mutiara-sentosa-2-ditutup</t>
+          <t>https://news.detik.com/berita/d-8604657/drama-atlet-golf-jesslyn-wijaya-disetop-sebab-bukan-penculikan</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785810542046_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/atlet-golf-putri-jesslyn-wijaya-lay-dok-ig-jesswijgolf-1784630812506_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5688,28 +5688,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Gempa M 5,6 Guncang Halmahera Barat Malut</t>
+          <t>Ultimatum Trump Sebelum 'Pancung' Iran</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 03:45:22 +0700</t>
+          <t>Wed, 05 Aug 2026 05:43:04 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Gempa magnitudo 5,6 mengguncang Halmahera Barat, Maluku Utara, pada kedalaman 25 km. BMKG memastikan tidak ada potensi tsunami.</t>
+          <t>Trump marah pada Iran yang bantah negosiasi. Ia beri ultimatum: kesepakatan atau penyerahan total. Iran menegaskan tidak ada dialog dengan AS.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604647/gempa-m-5-6-guncang-halmahera-barat-malut</t>
+          <t>https://news.detik.com/internasional/d-8604651/ultimatum-trump-sebelum-pancung-iran</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/tarif-10-berakhir-trump-berlakukan-bea-masuk-baru-terhadap-60-mitra-dagang-1784889297458_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5726,28 +5726,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Staf Bandara KLIA Diduga Bantu Kopilot yang Selundupkan Narkoba ke RI</t>
+          <t>Korban Tewas Gelombang Migran Ilegal di Ceuta Spanyol Jadi 77 orang</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 02:26:38 +0700</t>
+          <t>Wed, 05 Aug 2026 05:31:03 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kepolisian Malaysia mengidentifikasi staf Bandara KLIA yang diduga bantu kopilot selundupkan narkoba ke Indonesia. Penyelidikan terus dilakukan.</t>
+          <t>Serbuan migran ilegal dari Maroko ke Ceuta, Spanyol, menyebabkan 77 tewas. Banyak yang tenggelam saat mencoba melewati penghalang Laut Mediterania.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604644/staf-bandara-klia-diduga-bantu-kopilot-yang-selundupkan-narkoba-ke-ri</t>
+          <t>https://news.detik.com/internasional/d-8604650/korban-tewas-gelombang-migran-ilegal-di-ceuta-spanyol-jadi-77-orang</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/spanyol-kerahkan-militer-ke-ceuta-atasi-krisis-migran-1785493658510_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5764,28 +5764,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rumah Warga Ambruk 6 Bulan Belum Diperbaiki, Pemkot Serang Beri Bantuan</t>
+          <t>Operasi SAR Pencarian Korban KM Mutiara Sentosa 2 Ditutup</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:33:26 +0700</t>
+          <t>Wed, 05 Aug 2026 05:06:19 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rumah Nani di Serang ambruk akibat angin kencang. Pemkot Serang bantu Rp 30 juta untuk renovasi. Wali Kota kunjungi lokasi untuk pengecekan.</t>
+          <t>Basarnas resmi menghentikan operasi SAR KM Mutiara Sentosa II setelah 238 orang berhasil didata. Operasi kini beralih ke kesiapsiagaan rutin.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604642/rumah-warga-ambruk-6-bulan-belum-diperbaiki-pemkot-serang-beri-bantuan</t>
+          <t>https://news.detik.com/berita/d-8604649/operasi-sar-pencarian-korban-km-mutiara-sentosa-2-ditutup</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rumah-warga-serang-1785868326015_169.webp?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785810542046_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5802,28 +5802,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Pimpinan DPRD Ajak Warga Jaga Jakarta: Jadikan Rumah yang Aman bagi Semua</t>
+          <t>Gempa M 5,6 Guncang Halmahera Barat Malut</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:51:11 +0700</t>
+          <t>Wed, 05 Aug 2026 03:45:22 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Baco mendorong warga Jakarta untuk berbondong-bondong menjaga kotanya. Dia berpesan agar Jakarta menjadi rumah aman bagi semua warganya.</t>
+          <t>Gempa magnitudo 5,6 mengguncang Halmahera Barat, Maluku Utara, pada kedalaman 25 km. BMKG memastikan tidak ada potensi tsunami.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604639/pimpinan-dprd-ajak-warga-jaga-jakarta-jadikan-rumah-yang-aman-bagi-semua</t>
+          <t>https://news.detik.com/berita/d-8604647/gempa-m-5-6-guncang-halmahera-barat-malut</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/15/basri-baco-1778786025155_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5840,28 +5840,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Qatar Bilang Negosiasi AS-Iran Progresif, Draf Perjanjian Damai Lagi Dibahas</t>
+          <t>Staf Bandara KLIA Diduga Bantu Kopilot yang Selundupkan Narkoba ke RI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:22:56 +0700</t>
+          <t>Wed, 05 Aug 2026 02:26:38 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Qatar menyatakan upaya penyelesaian konflik AS-Iran sedang progresif. Draf perjanjian damai sedang diedarkan, dengan fokus pada resolusi jangka pendek.</t>
+          <t>Kepolisian Malaysia mengidentifikasi staf Bandara KLIA yang diduga bantu kopilot selundupkan narkoba ke Indonesia. Penyelidikan terus dilakukan.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604632/qatar-bilang-negosiasi-as-iran-progresif-draf-perjanjian-damai-lagi-dibahas</t>
+          <t>https://news.detik.com/berita/d-8604644/staf-bandara-klia-diduga-bantu-kopilot-yang-selundupkan-narkoba-ke-ri</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/uae-iran-us-israel-war-1783871173097_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5878,28 +5878,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ngambek Keinginan Tak Dituruti Ortu, Pemuda Bandung Bakar Motor dan 3 Rumah</t>
+          <t>Rumah Warga Ambruk 6 Bulan Belum Diperbaiki, Pemkot Serang Beri Bantuan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:20:10 +0700</t>
+          <t>Wed, 05 Aug 2026 01:33:26 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Polisi menangkap pemuda yang membakar motor dan tiga rumah di Babakan Ciparay. Motif pelaku lantaran keinginan tak dipenuhi ortu.</t>
+          <t>Rumah Nani di Serang ambruk akibat angin kencang. Pemkot Serang bantu Rp 30 juta untuk renovasi. Wali Kota kunjungi lokasi untuk pengecekan.</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604631/ngambek-keinginan-tak-dituruti-ortu-pemuda-bandung-bakar-motor-dan-3-rumah</t>
+          <t>https://news.detik.com/berita/d-8604642/rumah-warga-ambruk-6-bulan-belum-diperbaiki-pemkot-serang-beri-bantuan</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tampang-pemuda-yang-bakar-motor-hingga-api-menjalar-ke-3-rumah-1785851029166_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rumah-warga-serang-1785868326015_169.webp?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5911,33 +5911,33 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Jadwal Singapura Vs Indonesia di Piala AFF 2026</t>
+          <t>Pimpinan DPRD Ajak Warga Jaga Jakarta: Jadikan Rumah yang Aman bagi Semua</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 12:00:10 +0700</t>
+          <t>Wed, 05 Aug 2026 00:51:11 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Timnas Indonesia bertandang ke markas Singapura dalam matchday terakhir fase grup Piala AFF 2026. Berikut jadwal pertandingan selengkapnya!</t>
+          <t>Baco mendorong warga Jakarta untuk berbondong-bondong menjaga kotanya. Dia berpesan agar Jakarta menjadi rumah aman bagi semua warganya.</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605047/jadwal-singapura-vs-indonesia-di-piala-aff-2026</t>
+          <t>https://news.detik.com/berita/d-8604639/pimpinan-dprd-ajak-warga-jaga-jakarta-jadikan-rumah-yang-aman-bagi-semua</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/15/basri-baco-1778786025155_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5949,33 +5949,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
+          <t>Qatar Bilang Negosiasi AS-Iran Progresif, Draf Perjanjian Damai Lagi Dibahas</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
+          <t>Wed, 05 Aug 2026 00:22:56 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
+          <t>Qatar menyatakan upaya penyelesaian konflik AS-Iran sedang progresif. Draf perjanjian damai sedang diedarkan, dengan fokus pada resolusi jangka pendek.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
+          <t>https://news.detik.com/internasional/d-8604632/qatar-bilang-negosiasi-as-iran-progresif-draf-perjanjian-damai-lagi-dibahas</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/uae-iran-us-israel-war-1783871173097_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5987,33 +5987,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jadwal MotoGP Inggris 2026 Akhir Pekan Ini</t>
+          <t>Ngambek Keinginan Tak Dituruti Ortu, Pemuda Bandung Bakar Motor dan 3 Rumah</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:30:30 +0700</t>
+          <t>Wed, 05 Aug 2026 00:20:10 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>MotoGP 2026 akan kembali bergulir setelah jeda musim panas pada seri ke-12 di Sirkuit Silverstone, Inggris. Simak jadwalnya.</t>
+          <t>Polisi menangkap pemuda yang membakar motor dan tiga rumah di Babakan Ciparay. Motif pelaku lantaran keinginan tak dipenuhi ortu.</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604979/jadwal-motogp-inggris-2026-akhir-pekan-ini</t>
+          <t>https://news.detik.com/berita/d-8604631/ngambek-keinginan-tak-dituruti-ortu-pemuda-bandung-bakar-motor-dan-3-rumah</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-di-motogp-jerman-2026-1783857060263_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tampang-pemuda-yang-bakar-motor-hingga-api-menjalar-ke-3-rumah-1785851029166_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6025,33 +6025,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Jadwal Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
+          <t>Teknologi Heat Pump Bikin Pabrik RI Hemat Rp 744 Juta/Tahun</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:20:20 +0700</t>
+          <t>Wed, 05 Aug 2026 12:13:32 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Jadwal final Piala Presiden 2026 mempertemukan Persib Bandung vs Persebaya Surabaya.</t>
+          <t>Teknologi heat pump mulai menunjukkan potensinya sebagai solusi efisiensi energi sekaligus dekarbonisasi industri di Indonesia.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604949/jadwal-final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
+          <t>https://finance.detik.com/energi/d-8605102/teknologi-heat-pump-bikin-pabrik-ri-hemat-rp-744-juta-tahun</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/heat-pump-ditjen-ebtke-1785906771075_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6063,33 +6063,33 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Neymar di Persimpangan Jalan Kariernya</t>
+          <t>Kimia Farma Akhirnya Cetak Laba Rp 54 M</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 11:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:11:51 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kontrak Neymar di Santos tinggal tersisa beberapa bulan lagi. Neymar tengah mempertimbangkan kelanjutan kariernya sebagai pesepakbola, lanjut main atau pensiun.</t>
+          <t>PT Kimia Farma (Persero) Tbk (KAEF) berhasil mencetak laba bersih di semester I-2026, setelah rugi ratusan miliar di periode yang sama tahun sebelumnya.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604692/neymar-di-persimpangan-jalan-kariernya</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8605100/kimia-farma-akhirnya-cetak-laba-rp-54-m</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/neymar-menangis-akhiri-karier-bersama-timnas-brasil-1783314392616_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/07/12/picu-pro-dan-kontra-vaksin-covid-19-berbayar-ditunda-2_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6101,33 +6101,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Presiden FIFA Gianni Infantino Gelar Rapat Darurat!</t>
+          <t>Modus Misdeclaration Terbongkar, Harley-Davidson Bekas Ilegal Disita Bea Cukai</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:57:30 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Gianni Infantino dilaporkan menggelar rapat darurat. Hal ini dilakukan di tengah desakan agar dirinya mundur dari FIFA.</t>
+          <t>Bea Cukai Tanjung Priok menggagalkan penyelundupan lima Harley-Davidson bekas dan 20 rangka bekas asal China dengan modus misdeclaration.</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604767/presiden-fifa-gianni-infantino-gelar-rapat-darurat</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8605004/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai-1785903653401.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6139,33 +6139,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Belum Selesai Belanja, Chelsea Siap Gaet Pengganti Cucurella</t>
+          <t>Jumlah Pengangguran RI Turun Jadi 7,22 Juta Orang</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:20:00 +0700</t>
+          <t>Wed, 05 Aug 2026 11:55:15 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chelsea belum berhenti belanja musim panas ini. The Blues dilaporkan bakal mendatangkan pengganti Marc Cucurella.</t>
+          <t>Badan Pusat Statistik (BPS) mencatat, jumlah pengangguran di Indonesia per Mei 2026 sebanyak 7,22 juta orang.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604768/belum-selesai-belanja-chelsea-siap-gaet-pengganti-cucurella</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605071/jumlah-pengangguran-ri-turun-jadi-7-22-juta-orang</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pep-chavarriarayo-vallecanolaligaliga-spanyolchelsea-1785891772000_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/09/ilustrasi-pengangguran-atau-pencari-kerja-1746784722868_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6177,33 +6177,33 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Amorim Jelang Milan Vs Inter: Juara Pramusim Nggak Penting</t>
+          <t>Ekonomi RI Tumbuh 5,29%, Ini Motor Penggeraknya</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 10:00:15 +0700</t>
+          <t>Wed, 05 Aug 2026 11:33:09 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AC Milan akan menghadapi Inter Milan di laga uji coba pramusim. Pelatih Milan Ruben Amorim menyebut hasil akhir bukan yang paling utama.</t>
+          <t>Badan Pusat Statistik (BPS) mengumumkan pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604711/amorim-jelang-milan-vs-inter-juara-pramusim-nggak-penting</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605018/ekonomi-ri-tumbuh-5-29-ini-motor-penggeraknya</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ruben-amorim-1785887341737_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/05/27/bangkit-dari-pandemi-ekonomi-ri-kuartal-ii-2021-diramal-tembus-7-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6215,33 +6215,33 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Carragher Nilai Liverpool Belum Siap Bersaing Jadi Juara Premier League</t>
+          <t>Pembiayaan Komersial Bank Mega Syariah Tumbuh Jadi Rp 5,9 T</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:40:09 +0700</t>
+          <t>Wed, 05 Aug 2026 11:28:36 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Jamie Carragher menilai Liverpool belum cukup kuat untuk bersaing memperebutkan gelar juara Premier League. Menurutnya, skuad Liverpool belum lengkap.</t>
+          <t>PT Bank Mega Syariah mencatat pertumbuhan pembiayaan pada segmen komersial bank sepanjang semester I-2026.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604726/carragher-nilai-liverpool-belum-siap-bersaing-jadi-juara-premier-league</t>
+          <t>https://finance.detik.com/moneter/d-8605001/pembiayaan-komersial-bank-mega-syariah-tumbuh-jadi-rp-5-9-t</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/andoni-iraola-1785219269838_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/13/ini-pemenang-mobil-listrik-program-berkah-berlimpah-mega-syariah-4_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6253,33 +6253,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Kolo Muani Punya Urusan yang Belum Selesai di Juventus</t>
+          <t>BPS Umumkan Ekonomi RI Tumbuh 5,29% di Kuartal II</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:20:13 +0700</t>
+          <t>Wed, 05 Aug 2026 11:17:07 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Randal Kolo Muani amat gembira bisa kembali ke Juventus. Kolo Muani ingin menuntaskan apa yang sudah ia mulai di Turin.</t>
+          <t>Badan Pusat Statistik (BPS) mengumumkan, pertumbuhan ekonomi kuartal II 2026 sebesar 5,29% secara yoy.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604710/kolo-muani-punya-urusan-yang-belum-selesai-di-juventus</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604987/bps-umumkan-ekonomi-ri-tumbuh-5-29-di-kuartal-ii</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/09/randal-kolo-muani-1752056032311_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/deputi-bidang-neraca-dan-analisis-statistik-bps-edy-mahmud-1785902590386_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6291,33 +6291,33 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Kata-kata Erick Thohir soal Dukung Infantino Terus Pimpin FIFA</t>
+          <t>BNI Cetak Laba Bersih Rp 10,8 Triliun</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 09:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 10:58:49 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Ketua Umum PSSI, Erick Thohir, bikin pernyatan soal dukungannya ke Gianni Infantino. Ia menyebut Indonesia sudah banyak dibantu Presiden FIFA tersebut.</t>
+          <t>PT Bank Negara Indonesia (Persero) Tbk atau BNI membukukan laba bersih sebesar Rp 10,8 triliun hingga semester I 2026.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604792/kata-kata-erick-thohir-soal-dukung-infantino-terus-pimpin-fifa</t>
+          <t>https://finance.detik.com/moneter/d-8604965/bni-cetak-laba-bersih-rp-10-8-triliun</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/18/erick-thohir-dan-presiden-fifa-gianni-infantino-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/bni-1773200307513_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6329,33 +6329,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Inter Vs Milan di Pramusim, Chivu: Fokusnya ke Kebugaran</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Harley Bekas dari China</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:30:21 +0700</t>
+          <t>Wed, 05 Aug 2026 10:38:16 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Inter Milan melanjutkan tur pramusimnya dengan melawan AC Milan di Australia. Pelatih Nerazzurri Cristian Chivu menegaskan fokus timnya ke membangun kebugaran.</t>
+          <t>Barang impor ilegal tersebut berasal dari China.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604317/inter-vs-milan-di-pramusim-chivu-fokusnya-ke-kebugaran</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604938/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china-1785901058002_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6367,33 +6367,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dipercaya di Surabaya Marathon 2026, Le Minerale Hadir di 18 Water Station</t>
+          <t>Harga Emas Hari Ini Turun Lagi Sentuh Rp 2,59 Juta</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:22:43 +0700</t>
+          <t>Wed, 05 Aug 2026 10:10:07 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Le Minerale Surabaya Marathon 2026 diikuti 7.000 pelari, mengusung konsep City Run. Acara ini mendukung sport tourism dan hidrasi optimal dengan Le Minerale.</t>
+          <t>Hari ini, Rabu (5/8) harga emas Antam 24 karat turun Rp 4.000 per gram menjadi Rp 2.599.000 per gram.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sportstyle/d-8604762/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604895/harga-emas-hari-ini-turun-lagi-sentuh-rp-2-59-juta</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station-1785892907123.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/22/harga-emas-terjun-bebas-pasar-cikini-langsung-diserbu-pembeli-1761123863171_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6405,33 +6405,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mourinho Ingin Vinicius Selalu Bahagia di Madrid</t>
+          <t>Bea Cukai Gagalkan Penyelundupan Narkotika di Bandara Juanda</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 08:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 09:33:15 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Di tengah rumor Arsenal, Vinicius buka suara usai menjalani latihan pramusim bersama Real Madrid. Vinicius bilang Jose Mourinho ingin ia bahagia di Madrid.</t>
+          <t>Bea Cukai kembali menggagalkan penyelundupan narkotika.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604655/mourinho-ingin-vinicius-selalu-bahagia-di-madrid</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604848/bea-cukai-gagalkan-penyelundupan-narkotika-di-bandara-juanda</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/15/soccer-spain-rma-rso-1771110362377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-narkotika-1785897113589_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6443,33 +6443,33 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho Langsung 'Babak Belur' di Pramusim Aston Villa</t>
+          <t>Dolar AS Melemah ke Level Rp 17.971</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:30:00 +0700</t>
+          <t>Wed, 05 Aug 2026 09:21:24 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho baru pindah ke Aston Villa musim panas ini. Di laga pramusim, winger Argentina itu langsung babak belur.</t>
+          <t>Nilai tukar dolar Amerika Serikat (AS) terpantau melemah terhadap rupiah.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604654/alejandro-garnacho-langsung-babak-belur-di-pramusim-aston-villa</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604830/dolar-as-melemah-ke-level-rp-17-971</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/alejandro-garnachoaston-villabg-pathum-vs-aston-villapramusim-aston-villa-1785881271654_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338213_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6481,33 +6481,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Asosiasi Sepakbola Yordania Merasa Diperas FIFA!</t>
+          <t>IHSG Naik Tipis Pagi Ini ke Level 6.322</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 07:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 09:16:12 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Asosiasi Sepakbola Yordania (JFA) bikin pernyataan keras soal FIFA. Mereka mengaku diperas organisasi pimpinan Gianni Infantino tersebut.</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604652/asosiasi-sepakbola-yordania-merasa-diperas-fifa</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604824/ihsg-naik-tipis-pagi-ini-ke-level-6-322</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/11/logo-fifa_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/22/jelang-putusan-mk-ihsg-menguat-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6519,33 +6519,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Semifinal Piala Presiden 2026 yang Aman dan Seru!</t>
+          <t>Sri Mulyani Ditunjuk Bank Dunia Jadi Ketua Penggalangan Dana buat Negara Miskin</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:30:00 +0700</t>
+          <t>Wed, 05 Aug 2026 08:42:46 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Semifinal Piala Presiden 2026 sudah digelar. Rangkaian pertandingan berjalan aman dan seru, sesuai yang diharapkan.</t>
+          <t>Penunjukkan Sri Mulyani bukan tanpa alasan. Eks Bendahara Negara tersebut mempunyai pengalaman dalam bidang keuangan pembangunan internasional</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604648/semifinal-piala-presiden-2026-yang-aman-dan-seru</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604777/sri-mulyani-ditunjuk-bank-dunia-jadi-ketua-penggalangan-dana-buat-negara-miskin</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-semifinal-piala-presiden-2026-antara-persib-vs-persija-di-stadion-kapten-i-wayan-dipta-gianyar-bali-selasa-482026-1785862146465.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/10/mantan-menteri-keuangan-sri-mulyani-indrawati-1765362593072_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6557,33 +6557,33 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mohamed Salah Menuju Trabzonspor</t>
+          <t>BUMI Catat Laba Bersih Semester I-2026 Naik 188%, AMAR Tetapkan Dividen Interim</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 06:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 08:33:25 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mohamed Salah menuju Trabzonspor. Klub Turki itu mengonfirmasi bakal bernegosiasi dengan pemain asal Mesir tersebut.</t>
+          <t>IHSG ditutup naik 1,37% di tengah aksi beli asing. BUMI membukukan kenaikan laba bersih semester I-2026, sementara AMAR menetapkan dividen interim.</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604653/mohamed-salah-menuju-trabzonspor</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604770/bumi-catat-laba-bersih-semester-i-2026-naik-188-amar-tetapkan-dividen-interim</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/mohamed-salah-1781054944371_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bursa-dan-valas-1785893124-1785893124406.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6595,33 +6595,33 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Edisi Kedua! Ajang Lari Rekreasional di DIY Segera Digelar Lagi</t>
+          <t>Harga Minyak Turun Sedalam Ini Usai Sinyal Damai AS &amp;amp; Iran</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:15:25 +0700</t>
+          <t>Wed, 05 Aug 2026 08:10:37 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ajang lari rekresional di Daerah Istimewa Yogyakarta (DIY) edisi kedua, Jogja Run'nShine, akan kembali digelar. Inovasi dihadirkan dari evaluasi edisi perdana.</t>
+          <t>Harga minyak mentah dunia anjlok lebih dari 5% dan bertengger di level terendahnya dalam tiga minggu terakhir pada perdagangan Selasa.</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604536/edisi-kedua-ajang-lari-rekreasional-di-diy-segera-digelar-lagi</t>
+          <t>https://finance.detik.com/energi/d-8604727/harga-minyak-turun-sedalam-ini-usai-sinyal-damai-as-iran</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jogja-runnshine-1785853110207_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/16/ilustrasi-pengeboran-migas-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6633,33 +6633,33 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FIFA Bantah Infantino 'Dicuekin' Donald Trump</t>
+          <t>Rayuan Purbaya ke Toyota, Janji Kasih Insentif Banyak</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 05:00:18 +0700</t>
+          <t>Wed, 05 Aug 2026 07:58:00 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ada kabar Gianni Infantino tak bisa menghubungi Donald Trump usai wacana menjual saham Piala Dunia batal. FIFA membantah laporan tersebut.</t>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa meminta raksasa otomotif Jepang, Toyota, memindahkan pusat manufaktur utamanya ke Indonesia.</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604623/fifa-bantah-infantino-dicuekin-donald-trump</t>
+          <t>https://finance.detik.com/ekonomi-bisnis/d-8604540/rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/trump-tampak-didampingi-presiden-fifa-gianni-infantino-saat-berbicara-dalam-acara-fifa-yang-digelar-di-trump-tower-new-york-ci-1784348679880_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detik-pagi-rayuan-purbaya-ke-toyota-janji-kasih-insentif-banyak-1785856135943_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6671,33 +6671,33 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Bernardo Silva: Saat Madrid Memanggil, Mustahil Bilang Tidak</t>
+          <t>Purbaya Janji Ekonomi Tahun Ini Tumbuh Dekati 6%</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 04:00:04 +0700</t>
+          <t>Wed, 05 Aug 2026 07:24:33 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bernardo Silva tidak berpikir dua kali saat mendapat tawaran dari Real Madrid. Menolak Madrid diakui Silva merupakan hal yang mustahil.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa optimistis ekonomi tahun ini bisa tumbuh mendekati angka 6%.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604621/bernardo-silva-saat-madrid-memanggil-mustahil-bilang-tidak</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604612/purbaya-janji-ekonomi-tahun-ini-tumbuh-dekati-6</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/bernardo-silva-1759772326382_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962228_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6709,33 +6709,33 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hasil Uji Coba: AS Roma Gilas Newport County 4-1</t>
+          <t>Bank-bank di Rusia Mulai Krisis Uang Tunai</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 03:00:00 +0700</t>
+          <t>Wed, 05 Aug 2026 07:00:57 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AS Roma mengalahkan Newport County dalam laga uji coba pramusim. Serigala Ibu Kota menang telak 4-1.</t>
+          <t>Perbankan Rusia menghadapi tekanan likuiditas rubel, membatasi kemampuan menyerap obligasi pemerintah. Defisit anggaran membengkak.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604646/hasil-uji-coba-as-roma-gilas-newport-county-4-1</t>
+          <t>https://finance.detik.com/moneter/d-8604562/bank-bank-di-rusia-mulai-krisis-uang-tunai</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/as-romanewport-countylaga-pramusimlaga-uji-cobasantiago-castro-1785873342683_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/29/g7-tolak-pembayaran-gas-rusia-dengan-mata-uang-rubel_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6747,33 +6747,33 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>'Klan' Kluivert Berlanjut</t>
+          <t>Respons Bos BGN soal Anggaran MBG &amp;amp; Pendidikan Harus Dipisah</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 02:00:23 +0700</t>
+          <t>Wed, 05 Aug 2026 06:30:38 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Shane Kluivert debut di tim utama Barcelona. Shane lanjutkan jejak sang ayah Patrick Kluivert yang 28 tahun lalu juga main buat Barca.</t>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono merespons keputusan Mahkamah Konstitusi soal memisahkan anggaran MBG dengan pendidikan.</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604292/klan-kluivert-berlanjut</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604561/respons-bos-bgn-soal-anggaran-mbg-pendidikan-harus-dipisah</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/shane-kluivert-1785831287018.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6785,33 +6785,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Piala Presiden 2026: Merawat Sportivitas, Menjaga Integritas</t>
+          <t>Era Controlled Landfill, Penghasilan Pemulung Bantargebang Merosot Drastis</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:26:47 +0700</t>
+          <t>Wed, 05 Aug 2026 06:00:49 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Piala Presiden 2026 diharapkan mampu menjadi teladan penyelenggaraan pertandingan resmi sepakbola nasional.</t>
+          <t>Controlled landfill di TPST Bantargebang mengubah pemilahan sampah dan membuat penghasilan pemulung yang bergantung pada sampah menurun.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604636/piala-presiden-2026-merawat-sportivitas-menjaga-integritas</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8604299/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/piala-presiden-2026-1785863698077_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/era-controlled-landfill-penghasilan-pemulung-bantargebang-merosot-drastis-1785843094443_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6823,33 +6823,33 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Terus Kejar Guimaraes, Arsenal Negosiasi Langsung dengan Newcastle</t>
+          <t>Sentilan Keras Purbaya buat Moody's-Fitch</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 01:00:23 +0700</t>
+          <t>Wed, 05 Aug 2026 05:55:23 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Arsenal kini tengah bernegosiasi langsung dengan Newcastle United. Ini upaya lanjutan The Gunners untuk mendapatkan Bruno Guimaraes.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan sentilan keras kepada dua lembaga rating global.</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604610/terus-kejar-guimaraes-arsenal-negosiasi-langsung-dengan-newcastle</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604558/sentilan-keras-purbaya-buat-moodys-fitch</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/bruno-guimaraes-1783531838994_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786088_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6866,28 +6866,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PSSI Ikrarkan Dukungan ke Gianni Infantino Terus Pimpin FIFA</t>
+          <t>Klub Arab Saudi Mau Coba Bajak Mo Salah yang Lagi Menuju Liga Turki</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:30:00 +0700</t>
+          <t>Wed, 05 Aug 2026 12:20:35 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan dukungannya ke Gianni Infantino. FIFA, di bawah pimpinannya, disebut membantu Indonesia.</t>
+          <t>Mohamed Salah menuju Trabzonspor untuk lanjutkan kariernya. Al Ittihad yang sudah lama meminati sang winger, mau coba bajak!</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604633/pssi-ikrarkan-dukungan-ke-gianni-infantino-terus-pimpin-fifa</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8605051/klub-arab-saudi-mau-coba-bajak-mo-salah-yang-lagi-menuju-liga-turki</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/23/gianni-infantino-erick-thohir_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/09/mohamed-salah-1780987487837.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6904,28 +6904,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Emmanuel Macron Dukung UEFA Lawan Gianni Infantino</t>
+          <t>Jadwal Singapura Vs Indonesia di Piala AFF 2026</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:30 +0700</t>
+          <t>Wed, 05 Aug 2026 12:00:10 +0700</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Presiden Prancis Emmanuel Macron diketahui dukung UEFA untuk melawan Presiden FIFA Gianni Infantino. Mulai ada campur tangan politik negara-negara besar, nih!</t>
+          <t>Timnas Indonesia bertandang ke markas Singapura dalam matchday terakhir fase grup Piala AFF 2026. Berikut jadwal pertandingan selengkapnya!</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604322/emmanuel-macron-dukung-uefa-lawan-gianni-infantino</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605047/jadwal-singapura-vs-indonesia-di-piala-aff-2026</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/presiden-prancis-emmanuel-macron-1754969579570.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6937,1104 +6937,1000 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HeadlineBanding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 Miliar</t>
+          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BPS: Pertumbuhan Ekonomi Indonesia 5,29 Persen pada Kuartal II 2026Money</t>
+          <t>Jadwal MotoGP Inggris 2026 Akhir Pekan Ini</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 11:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>BPS mencatat pertumbuhan ekonomi Indonesia di Kuartal II 2026 mencapai 5,29% (yoy). Sektor pengadaan listrik &amp; gas memimpin, meski pertambangan terkontraksi.</t>
+          <t>MotoGP 2026 akan kembali bergulir setelah jeda musim panas pada seri ke-12 di Sirkuit Silverstone, Inggris. Simak jadwalnya.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/114132726/bps-pertumbuhan-ekonomi-indonesia-529-persen-pada-kuartal-ii-2026?source=headline</t>
+          <t>https://sport.detik.com/moto-gp/d-8604979/jadwal-motogp-inggris-2026-akhir-pekan-ini</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/tO31vuJAGVU9FYHw3s-ozVN7cRc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/08/05/689187ab3472b.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-di-motogp-jerman-2026-1783857060263_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>KMP Mutiara Sentosa 2 Disebut Punya Sekoci dan Life Raft, Kenapa Penumpang Lompat ke Laut?Regional</t>
+          <t>Jadwal Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 11:20:20 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Peralatan keselamatan diklaim tidak dapat digunakan karena api dengan cepat menjalar ke bagian belakang KMP Mutiara Sentosa 2.</t>
+          <t>Jadwal final Piala Presiden 2026 mempertemukan Persib Bandung vs Persebaya Surabaya.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/08/05/114100578/kmp-mutiara-sentosa-2-disebut-punya-sekoci-dan-life-raft-kenapa-penumpang?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604949/jadwal-final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/hlZkBMsoqbiFwrId5Gsswi-eJMk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7201b327072.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Chery Ungkap Penyebab Tiggo 8 CSH Berasap di Basement ICE BSDOtomotif</t>
+          <t>Neymar di Persimpangan Jalan Kariernya</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 11:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Chery memastikan asap pada Tiggo 8 CSH di basement ICE BSD dipicu salah isi bahan bakar, bukan masalah baterai atau kelistrikan.</t>
+          <t>Kontrak Neymar di Santos tinggal tersisa beberapa bulan lagi. Neymar tengah mempertimbangkan kelanjutan kariernya sebagai pesepakbola, lanjut main atau pensiun.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/083200115/chery-ungkap-penyebab-tiggo-8-csh-berasap-di-basement-ice-bsd?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604692/neymar-di-persimpangan-jalan-kariernya</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/Yx1CJ4ytDmvGio3VxuAhvw7mP8g=/150x75:1050x675/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a7266800baa4.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/neymar-menangis-akhiri-karier-bersama-timnas-brasil-1783314392616_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Penjelasan Kepala Desa soal Penyebab Jembatan Rusak Melengkung di KebumenRegional</t>
+          <t>Presiden FIFA Gianni Infantino Gelar Rapat Darurat!</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Jembatan Sirnoboyo di Kebumen rusak parah akibat penurunan fondasi, mengancam akses vital Bonorowo-Mirit.</t>
+          <t>Gianni Infantino dilaporkan menggelar rapat darurat. Hal ini dilakukan di tengah desakan agar dirinya mundur dari FIFA.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/113256178/penjelasan-kepala-desa-soal-penyebab-jembatan-rusak-melengkung-di-kebumen?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604767/presiden-fifa-gianni-infantino-gelar-rapat-darurat</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/YVYF8uUEiS7TviEWS2yVBg7NEhM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72b9d1b42f7.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Korlantas Bantah Kembali Berlalukan Tilang ManualNews</t>
+          <t>Belum Selesai Belanja, Chelsea Siap Gaet Pengganti Cucurella</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 10:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Korlantas Polri membantah kabar penerapan kembali tilang manual dan kenaikan denda hingga 150 persen, tipenindakan tetap utamakan ETLE</t>
+          <t>Chelsea belum berhenti belanja musim panas ini. The Blues dilaporkan bakal mendatangkan pengganti Marc Cucurella.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11242771/korlantas-bantah-kembali-berlalukan-tilang-manual?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604768/belum-selesai-belanja-chelsea-siap-gaet-pengganti-cucurella</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/KClVTsIhD8FAvYbBgwh17JRksb4=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/08/6a25ca9500411.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pep-chavarriarayo-vallecanolaligaliga-spanyolchelsea-1785891772000_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Kisah Keluarga di Padang Bertahan dari Banjir, Ban Pelampung Jadi Andalan Cari MakananRegional</t>
+          <t>Amorim Jelang Milan Vs Inter: Juara Pramusim Nggak Penting</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 10:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Saat banjir 2 meter merendam rumahnya, keluarga Yarman mengandalkan ban dalam bekas untuk mencari makanan dan bertahan hidup.</t>
+          <t>AC Milan akan menghadapi Inter Milan di laga uji coba pramusim. Pelatih Milan Ruben Amorim menyebut hasil akhir bukan yang paling utama.</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/111436278/kisah-keluarga-di-padang-bertahan-dari-banjir-ban-pelampung-jadi-andalan?source=headline</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604711/amorim-jelang-milan-vs-inter-juara-pramusim-nggak-penting</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/RcVt6y0zoU3CJ6RxmgNPLf80Qzk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ab031a7a1.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ruben-amorim-1785887341737_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Megapolitan</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1Saat Sampah ke Bantargebang Terus Berkurang, Krisis Diam-diam Menghantui Kampung PemulungNews</t>
+          <t>Carragher Nilai Liverpool Belum Siap Bersaing Jadi Juara Premier League</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 09:40:09 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ribuan warga Ciketing Udik, Bantargebang, menggantungkan hidup dari sampah. Kini, pasokan berkurang dan penutupan TPA mengancam masa depan mereka.</t>
+          <t>Jamie Carragher menilai Liverpool belum cukup kuat untuk bersaing memperebutkan gelar juara Premier League. Menurutnya, skuad Liverpool belum lengkap.</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://megapolitan.kompas.com/read/2026/08/05/09303171/saat-sampah-ke-bantargebang-terus-berkurang-krisis-diam-diam-menghantui?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604726/carragher-nilai-liverpool-belum-siap-bersaing-jadi-juara-premier-league</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/W85u3qy33e0n8iASk-DCYVTwYVA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72980672081.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/andoni-iraola-1785219269838_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2Pengaruh Politik Jokowi Masih BesarNews</t>
+          <t>Kolo Muani Punya Urusan yang Belum Selesai di Juventus</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 09:20:13 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pengaruh politik memang tidak identik dengan kekuasaan formal. Kekuasaan Jokowi sebagai presiden telah selesai, sedangkan pengaruhnya belum selesai.</t>
+          <t>Randal Kolo Muani amat gembira bisa kembali ke Juventus. Kolo Muani ingin menuntaskan apa yang sudah ia mulai di Turin.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/09290001/pengaruh-politik-jokowi-masih-besar?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604710/kolo-muani-punya-urusan-yang-belum-selesai-di-juventus</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/t7YT9gwrldsaAdH_b9qHJv1aBYw=/311x90:996x547/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/02/6a6f1955bc8cd.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/09/randal-kolo-muani-1752056032311_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3Kepala Daerah Tersandung Korupsi Tak Bisa Langsung Dipecat, Tito: Bukan Anak Kemarin SoreRegional</t>
+          <t>Kata-kata Erick Thohir soal Dukung Infantino Terus Pimpin FIFA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Mendagri Tito Karnavian menjelaskan bahwa pemberhentian kepala daerah korup tidak bisa langsung dilakukan karena ada mekanisme prosedural yang harus dilalui.</t>
+          <t>Ketua Umum PSSI, Erick Thohir, bikin pernyatan soal dukungannya ke Gianni Infantino. Ia menyebut Indonesia sudah banyak dibantu Presiden FIFA tersebut.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/08/05/103939478/kepala-daerah-tersandung-korupsi-tak-bisa-langsung-dipecat-tito-bukan-anak?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604792/kata-kata-erick-thohir-soal-dukung-infantino-terus-pimpin-fifa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/5lwMUiwTHlyFZAMnUTExWLoG1Tw=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a59c24c08.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/18/erick-thohir-dan-presiden-fifa-gianni-infantino-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>4Perputaran Uang Judi Online Tembus Rp 86,8 Triliun, PPATK: Modus Pelaku Makin CanggihMoney</t>
+          <t>Inter Vs Milan di Pramusim, Chivu: Fokusnya ke Kebugaran</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 08:30:21 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PPATK laporkan pelaku judi online makin camggih cara beroperasinya.</t>
+          <t>Inter Milan melanjutkan tur pramusimnya dengan melawan AC Milan di Australia. Pelatih Nerazzurri Cristian Chivu menegaskan fokus timnya ke membangun kebugaran.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/094834426/perputaran-uang-judi-online-tembus-rp-868-triliun-ppatk-modus-pelaku-makin?source=terpopuler</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604317/inter-vs-milan-di-pramusim-chivu-fokusnya-ke-kebugaran</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/-zA-jcUu2Y7LQxrwFToq04J-o04=/112x402:1010x1000/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a7299c6e53ea.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5Banding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 MiliarNews</t>
+          <t>Dipercaya di Surabaya Marathon 2026, Le Minerale Hadir di 18 Water Station</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 08:22:43 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+          <t>Le Minerale Surabaya Marathon 2026 diikuti 7.000 pelari, mengusung konsep City Run. Acara ini mendukung sport tourism dan hidrasi optimal dengan Le Minerale.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=terpopuler</t>
+          <t>https://sport.detik.com/sportstyle/d-8604762/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dipercaya-di-surabaya-marathon-2026-le-minerale-hadir-di-18-water-station-1785892907123.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Komparasi Changan Nevo Q05 Vs Jaecoo J5 EV, Pilih Mana?Otomotif</t>
+          <t>Mourinho Ingin Vinicius Selalu Bahagia di Madrid</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 08:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Duel dua SUV listrik Rp 300 jutaan. Simak perbandingan desain, fitur, baterai, jarak tempuh, performa, hingga harga.</t>
+          <t>Di tengah rumor Arsenal, Vinicius buka suara usai menjalani latihan pramusim bersama Real Madrid. Vinicius bilang Jose Mourinho ingin ia bahagia di Madrid.</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/110200815/komparasi-changan-nevo-q05-vs-jaecoo-j5-ev-pilih-mana-?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604655/mourinho-ingin-vinicius-selalu-bahagia-di-madrid</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/3f4DFDwFteW4JUX_XX4XDaXxMD0=/0x0:1264x843/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a72908834b4a.png</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/15/soccer-spain-rma-rso-1771110362377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lifestyle</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Apa Itu Friend Bombing? Ini Ciri dan Cara MenyikapinyaLifestyle</t>
+          <t>Alejandro Garnacho Langsung 'Babak Belur' di Pramusim Aston Villa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 07:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Friend-bombing menyerupai love-bombing, tetapi terjadi dalam ranah persahabatan sehingga sering kali lebih sulit disadari sejak awal.</t>
+          <t>Alejandro Garnacho baru pindah ke Aston Villa musim panas ini. Di laga pramusim, winger Argentina itu langsung babak belur.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://lifestyle.kompas.com/read/2026/08/05/110100820/apa-itu-friend-bombing-ini-ciri-dan-cara-menyikapinya?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604654/alejandro-garnacho-langsung-babak-belur-di-pramusim-aston-villa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/EoPbroI6It3crom92-hL9IYHOGA=/0x0:1417x945/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/29/697b90e878546.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/alejandro-garnachoaston-villabg-pathum-vs-aston-villapramusim-aston-villa-1785881271654_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tren Baru di China, Orangtua Rela Bayar Rp 34 Juta agar Anak Jadi "Warren Buffett Kecil"Tren</t>
+          <t>Asosiasi Sepakbola Yordania Merasa Diperas FIFA!</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 07:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Orangtua di China rela membayar Rp 34 juta untuk kursus finansial agar anak menjadi “Warren Buffett kecil”. Apa saja yang dipelajari anak-anak?</t>
+          <t>Asosiasi Sepakbola Yordania (JFA) bikin pernyataan keras soal FIFA. Mereka mengaku diperas organisasi pimpinan Gianni Infantino tersebut.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/tren/read/2026/08/05/110000965/tren-baru-di-china-orangtua-rela-bayar-rp-34-juta-agar-anak-jadi-warren?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604652/asosiasi-sepakbola-yordania-merasa-diperas-fifa</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/t6-jEBcH9eEWOjfSeuph37-AxtU=/0x0:4411x2941/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71bc5105128.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/11/logo-fifa_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OJK Tindak 15 Perusahaan Pialang Asuransi Ilegal, Sebagian Masuk Tahap SidangMoney</t>
+          <t>Semifinal Piala Presiden 2026 yang Aman dan Seru!</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 06:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OJK menemukan 15 pialang asuransi ilegal dan telah melakukan penindakan hukum. Langkah ini diikuti penguatan pengawasan melalui QR Code STDD.</t>
+          <t>Semifinal Piala Presiden 2026 sudah digelar. Rangkaian pertandingan berjalan aman dan seru, sesuai yang diharapkan.</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/111000226/ojk-tindak-15-perusahaan-pialang-asuransi-ilegal-sebagian-masuk-tahap-sidang?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604648/semifinal-piala-presiden-2026-yang-aman-dan-seru</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/YxKhv82UZiNeBll_taObKpFfJPg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/01/23/697329f06af52.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-semifinal-piala-presiden-2026-antara-persib-vs-persija-di-stadion-kapten-i-wayan-dipta-gianyar-bali-selasa-482026-1785862146465.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Indra Bekti Turun Berat Badan hingga 10 Kg, Kurangi Nasi dan RotiHype</t>
+          <t>Mohamed Salah Menuju Trabzonspor</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Indra Bekti berhasil menurunkan 10 kg berat badan berkat pola hidup sehat, mengurangi nasi dan makanan tinggi karbohidrat. Ia kini merasa lebih nyaman dan sehat.</t>
+          <t>Mohamed Salah menuju Trabzonspor. Klub Turki itu mengonfirmasi bakal bernegosiasi dengan pemain asal Mesir tersebut.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://entertainment.kompas.com/read/2026/08/05/105301166/indra-bekti-turun-berat-badan-hingga-10-kg-kurangi-nasi-dan-roti?source=sorotan</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604653/mohamed-salah-menuju-trabzonspor</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/HgKxpJUQrKNcgGV8Mee8gw7wU2A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/05/6a72ace08557d.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/mohamed-salah-1781054944371_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Megapolitan</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>News51 detik laluPria Korban Mutilasi di Depok: Kaki Dibuang ke Sungai, Badan Dibungkus Karung Beras</t>
+          <t>Edisi Kedua! Ajang Lari Rekreasional di DIY Segera Digelar Lagi</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 05:15:25 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Dalam pemeriksaan polisi, pelaku yang bernama Saepul (26) mengaku melukai perut dan leher korban, Kunaefi (51), sebelum melakukan tindakan mutilasi.</t>
+          <t>Ajang lari rekresional di Daerah Istimewa Yogyakarta (DIY) edisi kedua, Jogja Run'nShine, akan kembali digelar. Inovasi dihadirkan dari evaluasi edisi perdana.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://megapolitan.kompas.com/read/2026/08/05/12172651/pria-korban-mutilasi-di-depok-kaki-dibuang-ke-sungai-badan-dibungkus</t>
+          <t>https://sport.detik.com/sport-lain/d-8604536/edisi-kedua-ajang-lari-rekreasional-di-diy-segera-digelar-lagi</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/bYR6Jt-cK__Cvk6yd7suhr9dYl8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72c030387e5.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jogja-runnshine-1785853110207_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Regional1 menit laluTrenggiling Masuk Permukiman di Lereng Gunung Karang, Warga Serahkan ke BPBD Pandeglang</t>
+          <t>FIFA Bantah Infantino 'Dicuekin' Donald Trump</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 05:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Seekor trenggiling ditemukan berkeliaran di permukiman lereng Gunung Karang, Pandeglang. Satwa dilindungi itu kemudian dievakuasi BKSDA.</t>
+          <t>Ada kabar Gianni Infantino tak bisa menghubungi Donald Trump usai wacana menjual saham Piala Dunia batal. FIFA membantah laporan tersebut.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/08/05/121711178/trenggiling-masuk-permukiman-di-lereng-gunung-karang-warga-serahkan-ke-bpbd</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604623/fifa-bantah-infantino-dicuekin-donald-trump</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/BxGPdSCq9-jU04or7BRoih8cgV4=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bfc3e5d6e.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/trump-tampak-didampingi-presiden-fifa-gianni-infantino-saat-berbicara-dalam-acara-fifa-yang-digelar-di-trump-tower-new-york-ci-1784348679880_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Money4 menit laluBalik Untung dari Rugi, Kimia Farma (KAEF) Cetak Laba Bersih Rp 54 Miliar</t>
+          <t>Bernardo Silva: Saat Madrid Memanggil, Mustahil Bilang Tidak</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 04:00:04 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Kimia Farma (KAEF) sukses berbalik untung Rp 54,07 miliar pada Semester I-2026 dari rugi sebelumnya, didorong penguatan fundamental dan efisiensi. Ini Berita Baik!</t>
+          <t>Bernardo Silva tidak berpikir dua kali saat mendapat tawaran dari Real Madrid. Menolak Madrid diakui Silva merupakan hal yang mustahil.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/121400026/balik-untung-dari-rugi-kimia-farma-kaef-cetak-laba-bersih-rp-54-miliar</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604621/bernardo-silva-saat-madrid-memanggil-mustahil-bilang-tidak</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/7goGruQRBbllhejL1KbWUyjtVjU=/417x64:1183x575/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/04/30/69f2ee65aa8a4.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/07/bernardo-silva-1759772326382_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>News5 menit laluKPK Ajukan Banding atas Vonis Gubernur Riau Abdul Wahid dkk</t>
+          <t>Hasil Uji Coba: AS Roma Gilas Newport County 4-1</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 03:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>KPK ajukan banding atas vonis dua tahun bui terhadap Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa kasus korupsi lainnya.</t>
+          <t>AS Roma mengalahkan Newport County dalam laga uji coba pramusim. Serigala Ibu Kota menang telak 4-1.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/12132111/kpk-ajukan-banding-atas-vonis-gubernur-riau-abdul-wahid-dkk</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604646/hasil-uji-coba-as-roma-gilas-newport-county-4-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/lPdw0OjDmf-mtI5W44hEX1Buz4Q=/97x0:1057x640/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/19/6944ed9e2dd8c.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/as-romanewport-countylaga-pramusimlaga-uji-cobasantiago-castro-1785873342683_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Cek fakta6 menit lalu[HOAKS] Video Purbaya Bagikan Dana Bantuan Rp 50 Juta untuk 10 Orang</t>
+          <t>'Klan' Kluivert Berlanjut</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 02:00:23 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Beredar video yang menampilkan Menkeu Purbaya membagikan dana bantuan Rp 50 juta untuk 10 orang. Narasi itu hoaks.</t>
+          <t>Shane Kluivert debut di tim utama Barcelona. Shane lanjutkan jejak sang ayah Patrick Kluivert yang 28 tahun lalu juga main buat Barca.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/cekfakta/read/2026/08/05/121200382/-hoaks-video-purbaya-bagikan-dana-bantuan-rp-50-juta-untuk-10-orang</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8604292/klan-kluivert-berlanjut</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/g-VvO8HqZ-6UxzHMfISQFtcPYhQ=/0x36:1600x1103/1200x675/data/photo/2026/08/04/6a7186d6071ef.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/shane-kluivert-1785831287018.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Otomotif</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Otomotif6 menit laluBYD Ingatkan Dampak Pajak Mobil Listrik terhadap Adopsi EV</t>
+          <t>Piala Presiden 2026: Merawat Sportivitas, Menjaga Integritas</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 01:26:47 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>BYD khawatir pengenaan pajak mobil listrik terlalu cepat dapat menghambat tren positif elektrifikasi di Indonesia.</t>
+          <t>Piala Presiden 2026 diharapkan mampu menjadi teladan penyelenggaraan pertandingan resmi sepakbola nasional.</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://otomotif.kompas.com/read/2026/08/05/121200315/byd-ingatkan-dampak-pajak-mobil-listrik-terhadap-adopsi-ev</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604636/piala-presiden-2026-merawat-sportivitas-menjaga-integritas</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/mmgsH0plmX9Yekj5DwbJA3VJohE=/375x233:3657x2420/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a725367f1190.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/piala-presiden-2026-1785863698077_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Properti7 menit laluBUMN Karya Ini Tawarkan Properti Siap Huni, Harga Mulai Rp 300 Jutaan</t>
+          <t>Terus Kejar Guimaraes, Arsenal Negosiasi Langsung dengan Newcastle</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 01:00:23 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Direktur Utama PT HK Realtindo, Ekwan Hadyanto, menegaskan, mayoritas proyek yang dihadirkan merupakan hunian siap huni.</t>
+          <t>Arsenal kini tengah bernegosiasi langsung dengan Newcastle United. Ini upaya lanjutan The Gunners untuk mendapatkan Bruno Guimaraes.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/properti/read/2026/08/05/121136421/bumn-karya-ini-tawarkan-properti-siap-huni-harga-mulai-rp-300-jutaan</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604610/terus-kejar-guimaraes-arsenal-negosiasi-langsung-dengan-newcastle</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/aC6ZIxrDHBj9IR3J0dWKRmVIF2A=/432x0:3942x2340/1200x675/filters:watermark(data/photo/2026/01/30/697c81838452e.png,0,-0,1)/data/photo/2026/04/25/69ecb9a662099.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/bruno-guimaraes-1783531838994_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Berita Utama</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Global7 menit lalu80 Persen Stok Rudal Pencegat AS Terkuras, Trump Pilih Batal Serang Iran</t>
+          <t>PSSI Ikrarkan Dukungan ke Gianni Infantino Terus Pimpin FIFA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 00:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Militer AS dilaporkan telah menghabiskan hampir 80 persen amunisi pencegat untuk sistem pertahanan udara utama THAAD.</t>
+          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan dukungannya ke Gianni Infantino. FIFA, di bawah pimpinannya, disebut membantu Indonesia.</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.kompas.com/global/read/2026/08/05/121100270/80-persen-stok-rudal-pencegat-as-terkuras-trump-pilih-batal-serang-iran</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604633/pssi-ikrarkan-dukungan-ke-gianni-infantino-terus-pimpin-fifa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/DC_ROqcsEzmU1c0UipGQAnNR7AI=/0x0:1997x1331/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/02/03/69817653a6f21.jpg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/23/gianni-infantino-erick-thohir_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Regional8 menit laluBNN Bali Bongkar Paket Narkoba Jaringan Kamboja, Disamarkan dalam Knalpot Bekas</t>
+          <t>Emmanuel Macron Dukung UEFA Lawan Gianni Infantino</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Kompas Cyber Media</t>
-        </is>
-      </c>
+          <t>Wed, 05 Aug 2026 00:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>BNN Bali bongkar jaringan narkoba Kamboja. Pria berinisial GAS ditangkap setelah menerima paket narkoba yang disamarkan dalam knalpot motor bekas.</t>
+          <t>Presiden Prancis Emmanuel Macron diketahui dukung UEFA untuk melawan Presiden FIFA Gianni Infantino. Mulai ada campur tangan politik negara-negara besar, nih!</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://denpasar.kompas.com/read/2026/08/05/121034678/bnn-bali-bongkar-paket-narkoba-jaringan-kamboja-disamarkan-dalam-knalpot</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604322/emmanuel-macron-dukung-uefa-lawan-gianni-infantino</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/mFzxe5sm_MIydDJW_RxfAyOBCP8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72bca8504da.jpeg</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/presiden-prancis-emmanuel-macron-1754969579570.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Kompas</t>
+          <t>Detik</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>General</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dalam Semangat Kemerdekaan, Mandiri Donor Darah Kembali Hadir Dukung Ketersediaan Darah Nasional</t>
+          <t>KPK Ajukan Banding atas Vonis Gubernur Riau Abdul Wahid dkkNews13 menit lalu</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8049,17 +7945,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Menyambut HUT ke-81 RI dan usia 28 tahun melayani negeri, Bank Mandiri menggelar aksi 'Mandiri Donor Darah' serentak di 12 region se-Indonesia.</t>
+          <t>KPK ajukan banding atas vonis dua tahun bui terhadap Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa kasus korupsi lainnya.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/111451426/dalam-semangat-kemerdekaan-mandiri-donor-darah-kembali-hadir-dukung</t>
+          <t>http://nasional.kompas.com/read/2026/08/05/12132111/kpk-ajukan-banding-atas-vonis-gubernur-riau-abdul-wahid-dkk?source=wp_berita_terbaru</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/mFkRD0H1S6NeT7co-aFE7piNn7o=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72b60386b45.jpg</t>
+          <t>https://asset.kompas.com/crops/lPdw0OjDmf-mtI5W44hEX1Buz4Q=/97x0:1057x640/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/19/6944ed9e2dd8c.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -8071,12 +7967,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Money</t>
+          <t>General</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Komisi IV DPR RI Apresiasi Langkah Mentan Amran Bongkar Dugaan Mafia Beras Fortifikasi</t>
+          <t>Brankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan RakyatNews25 menit lalu</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8091,17 +7987,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Anggota Komisi IV DPR RI Endang S Tohari menilai praktik pengoplosan beras fortifikasi merupakan kejahatan serius yang tidak dapat ditoleransi.</t>
+          <t>Perang melawan korupsi seharusnya tidak dipahami semata sebagai agenda penegakan hukum.</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/08/05/104408026/komisi-iv-dpr-ri-apresiasi-langkah-mentan-amran-bongkar-dugaan-mafia-beras</t>
+          <t>http://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat?source=wp_berita_terbaru</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/B0W3J3lt6QD6y9DoQh2yxyGlFqI=/0x134:1599x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/05/6a72a85e917e8.jpeg</t>
+          <t>https://asset.kompas.com/crops/BxG7N1wef22vGuge6xZA46tILF0=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/27/6a66843ea3864.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -8113,12 +8009,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Nasional</t>
+          <t>General</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Mendagri: Integritas Kepala Daerah Jadi Kunci Wujudkan Tata Kelola Pemerintahan yang Bersih dan Akuntabel</t>
+          <t>Pinjol Kini Wajib Laporkan Seluruh Transaksi ke OJK, Apa Dampaknya?Money32 menit lalu</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8133,17 +8029,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Mendagri Tito menekankan, setiap kepala daerah dituntut untuk menjaga prinsip-prinsip antikorupsi serta tidak tergoda melakukan pelanggaran hukum.</t>
+          <t>Seluruh penyelenggara pindar diwajibkan membangun sistem pelaporan yang lebih rapi, akurat, dan terintegrasi.</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/10061371/mendagri-integritas-kepala-daerah-jadi-kunci-wujudkan-tata-kelola</t>
+          <t>http://money.kompas.com/read/2026/08/05/115451426/pinjol-kini-wajib-laporkan-seluruh-transaksi-ke-ojk-apa-dampaknya?source=wp_berita_terbaru</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://asset.kompas.com/crops/h9MDSqwCb1sZpxTWESiR3d6HydQ=/0x0:1599x1066/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72a4a9bd443.jpeg</t>
+          <t>https://asset.kompas.com/crops/b9E4nksax6w0K4NQvYXrBGeUcEc=/0x0:984x656/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2023/09/20/650b15bd7ee3d.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -8155,47 +8051,1139 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Komisi V DPR Panggil Kemenhub hingga KNKT Bahas Kebakaran KMP Mutiara Sentosa 2News1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Komisi V DPR RI panggil Kemenhub, KNKT, dan Pelindo bahas kebakaran KMP Mutiara Sentosa 2 yang tewaskan 5 orang.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>http://nasional.kompas.com/read/2026/08/05/11081571/komisi-v-dpr-panggil-kemenhub-hingga-knkt-bahas-kebakaran-kmp-mutiara?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/oZrznc7DWGKPjeAgM2qcUXFiA1Q=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/03/6a6fb41aa2879.jpeg</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Baru 1 Tersangka, Penyidikan Kasus Tunjangan Rumah DPRD Ponorogo Masih BerlanjutRegional1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Kejari Ponorogo tetapkan Kabag Keuangan Setwan DPRD tersangka korupsi tunjangan perumahan. Disebut bukan akhir dari penyidikan.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>http://surabaya.kompas.com/read/2026/08/05/105230578/baru-1-tersangka-penyidikan-kasus-tunjangan-rumah-dprd-ponorogo-masih?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/afeykV0_YBUbtY_N48PyZW73e38=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72acd211aeb.jpg</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Banjir Padang Berulang, Wali Kota Fadly Amran Minta Proyek Pengendali Sungai dan Drainase DipercepatRegional1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Padang kembali diterjang banjir. Wali Kota Fadly Amran mendesak percepatan infrastruktur pengendali dan koordinasi lintas sektor.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>http://regional.kompas.com/read/2026/08/05/105224378/banjir-padang-berulang-wali-kota-fadly-amran-minta-proyek-pengendali-sungai?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/PhZpNbQC2WI-nGeLYP_x8sXYb2E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7208ee2bedf.jpeg</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Pengembangan Kasus Pungli Rp 1,8 Miliar di Gowa, Bupati Husniah Talenrang Ikut Dipanggil PolisiRegional1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Usai Kadis Perkimtan ditahan, kini terseret kasus pungli Rp 1,8 miliar nama Bupati Gowa. Polisi layangkan surat panggilan pemeriksaan saksi.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>http://regional.kompas.com/read/2026/08/05/104505578/pengembangan-kasus-pungli-rp-18-miliar-di-gowa-bupati-husniah-talenrang?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/gs3rGfUp6298iP8yEGC1rkqOrqk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72aab2ac198.jpg</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Lantik 67 Pejabat Kemensos, Gus Ipul: Jangan Ada Korupsi Lagi!News1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Menteri Sosial Gus Ipul memperingatkan seluruh pejabat Kemensos untuk bekerja bersih tanpa korupsi. Simak selengkapnya di sini.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>http://nasional.kompas.com/read/2026/08/05/10424081/lantik-67-pejabat-kemensos-gus-ipul-jangan-ada-korupsi-lagi?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/9oDaBJP5fszDZY-yChrAddmiS4c=/137x21:1119x675/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/15/6a578405968e3.webp</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Bos Hugging Face Sebut China Unggul dalam Pengembangan AI, AS Terancam DisalipTekno1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>CEO Hugging Face beranggapan bahwa China berpeluang menyamai hingga menyalip perusahaan AI Amerika Serikat pada tahun ini.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>http://tekno.kompas.com/read/2026/08/05/10420077/bos-hugging-face-sebut-china-unggul-dalam-pengembangan-ai-as-terancam-disalip?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/SJk-KzwajD9fFsCDK52SG7xFoMI=/0x9:1200x809/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2026/08/04/6a71a3452b329.png</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Isuzu Traga Jadi Salon Berjalan di GIIAS 2026Otomotif1 jam lalu</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Kendaraan niaga memiliki potensi pemanfaatan yang jauh lebih luas dibanding sekadar mengangkut barang.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>http://otomotif.kompas.com/read/2026/08/05/104200215/isuzu-traga-jadi-salon-berjalan-di-giias-2026?source=wp_berita_terbaru</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/KaFsdb4OMiinrxC5ojw_yywp8QI=/0x52:1280x906/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/07/29/6a69bca24040f.jpeg</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HeadlineKisah Keluarga di Padang Bertahan dari Banjir, Ban Pelampung Jadi Andalan Cari Makanan</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Saat banjir 2 meter merendam rumahnya, keluarga Yarman mengandalkan ban dalam bekas untuk mencari makanan dan bertahan hidup.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/111436278/kisah-keluarga-di-padang-bertahan-dari-banjir-ban-pelampung-jadi-andalan?source=headline</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RcVt6y0zoU3CJ6RxmgNPLf80Qzk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ab031a7a1.jpeg</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
           <t>Nasional</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Brankas Febrie, Ketimpangan Ekonomi, dan Retaknya Piring Makan Rakyat</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Banding Kasus Chromebook, Kubu Nadiem Soroti Google hingga Uang Pengganti Rp 809 MiliarNews</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
         <is>
           <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Kompas Cyber Media</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Perang melawan korupsi seharusnya tidak dipahami semata sebagai agenda penegakan hukum.</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>https://nasional.kompas.com/read/2026/08/05/12020061/brankas-febrie-ketimpangan-ekonomi-dan-retaknya-piring-makan-rakyat?source=kolom</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://asset.kompas.com/crops/BxG7N1wef22vGuge6xZA46tILF0=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/27/6a66843ea3864.jpg</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Tim hukum Nadiem Makarim ajukan banding atas vonis korupsi Chromebook. Apa yang disorot?</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/11414241/banding-kasus-chromebook-kubu-nadiem-soroti-google-hingga-uang-pengganti-rp?source=headline</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/a7IZlpnmt08W_EumWCgfKR3jv4E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/09/6937c30a849cc.jpg</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t>Kompas</t>
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BPS: Pertumbuhan Ekonomi Indonesia 5,29 Persen pada Kuartal II 2026Money</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>BPS mencatat pertumbuhan ekonomi Indonesia di Kuartal II 2026 mencapai 5,29% (yoy). Sektor pengadaan listrik &amp; gas memimpin, meski pertambangan terkontraksi.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/114132726/bps-pertumbuhan-ekonomi-indonesia-529-persen-pada-kuartal-ii-2026?source=headline</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/tO31vuJAGVU9FYHw3s-ozVN7cRc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/08/05/689187ab3472b.jpeg</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Surabaya</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>KMP Mutiara Sentosa 2 Disebut Punya Sekoci dan Life Raft, Kenapa Penumpang Lompat ke Laut?Regional</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Peralatan keselamatan diklaim tidak dapat digunakan karena api dengan cepat menjalar ke bagian belakang KMP Mutiara Sentosa 2.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/05/114100578/kmp-mutiara-sentosa-2-disebut-punya-sekoci-dan-life-raft-kenapa-penumpang?source=headline</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/hlZkBMsoqbiFwrId5Gsswi-eJMk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a7201b327072.jpeg</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Chery Ungkap Penyebab Tiggo 8 CSH Berasap di Basement ICE BSDOtomotif</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Chery memastikan asap pada Tiggo 8 CSH di basement ICE BSD dipicu salah isi bahan bakar, bukan masalah baterai atau kelistrikan.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/05/083200115/chery-ungkap-penyebab-tiggo-8-csh-berasap-di-basement-ice-bsd?source=headline</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Yx1CJ4ytDmvGio3VxuAhvw7mP8g=/150x75:1050x675/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a7266800baa4.jpg</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Penjelasan Kepala Desa soal Penyebab Jembatan Rusak Melengkung di KebumenRegional</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Jembatan Sirnoboyo di Kebumen rusak parah akibat penurunan fondasi, mengancam akses vital Bonorowo-Mirit.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/113256178/penjelasan-kepala-desa-soal-penyebab-jembatan-rusak-melengkung-di-kebumen?source=headline</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/YVYF8uUEiS7TviEWS2yVBg7NEhM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72b9d1b42f7.jpg</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Korlantas Bantah Kembali Berlalukan Tilang ManualNews</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Korlantas Polri membantah kabar penerapan kembali tilang manual dan kenaikan denda hingga 150 persen, tipenindakan tetap utamakan ETLE</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/11242771/korlantas-bantah-kembali-berlalukan-tilang-manual?source=headline</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/KClVTsIhD8FAvYbBgwh17JRksb4=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/08/6a25ca9500411.jpeg</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1Harga Pertamax Turun, Pemprov Jateng Pertimbangkan Hentikan Kebijakan WFH bagi ASNRegional</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pemprov Jateng pertimbangkan untuk hentikan WFH bagi ASN usai harga Pertamax turun. Selain itu, tingkat pemanfaatan WFH juga dinilai rendah.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/060000678/harga-pertamax-turun-pemprov-jateng-pertimbangkan-hentikan-kebijakan-wfh?source=terpopuler</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/5L3A15Rj8HxVVigsff4lxoD68k0=/0x0:750x500/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/01/18/696c659f54b20.jpg</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Megapolitan</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2Mengapa KRL Nambo Selalu Penuh? 140.000 Penumpang Per Hari Hanya Dilayani 16 Perjalanan PPNews</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Selain frekuensi perjalanan yang terbatas, lintas Nambo juga masih memiliki jeda kedatangan antarkereta (headway) lebih dari satu jam.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/05/06030471/mengapa-krl-nambo-selalu-penuh-140000-penumpang-per-hari-hanya-dilayani?source=terpopuler</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Misrxk8GtQUmu7k_fmSt9Nn9yfs=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/06/26/685cfa807662c.jpg</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Berita Utama</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>3Saat UNDP Dikomplain karena Bungkus Mi Instan dari Indonesia Ditemukan di Pantai AfrikaTren</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>UNDP mengungkap sampah Indonesia dapat terbawa sungai ke laut hingga Afrika dan Vanuatu. Sungai Bengawan Solo disebut salah satu perantaranya.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/tren/read/2026/08/05/060000865/saat-undp-dikomplain-karena-bungkus-mi-instan-dari-indonesia-ditemukan-di?source=terpopuler</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/lC4xqMfYPJdWOWjhwaLPvXL8Wug=/0x45:1280x685/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71cc487a537.jpeg</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>4Hasil Piala AFF 2026: Myanmar Pesta Gol, Thailand Menuju SemifinalBola</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Hasil Piala AFF 2026 Timnas Myanmar dan Thailand berhasil meraih kemenangan</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/05/00021708/hasil-piala-aff-2026-myanmar-pesta-gol-thailand-menuju-semifinal?source=terpopuler</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Eemb0_MRuQfRud7Qc-_w1BdVcWc=/45x0:933x592/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/08/04/6a7219c64e2c2.png</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>510 Orang Terkaya Indonesia Versi Forbes, Taipan Asal Kalbar dan Jateng Dominasi 5 BesarRegional</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Daftar 10 orang terkaya Indonesia versi Forbes awal Agustus 2026, didominasi taipan asal Kalbar dan Jateng.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/060300278/10-orang-terkaya-indonesia-versi-forbes-taipan-asal-kalbar-dan-jateng?source=terpopuler</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/tpfbVhC-d3ktFA0x7n3tNl2p2QI=/0x145:1531x910/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a717be4d52c6.png</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Indra Bekti Turun Berat Badan hingga 10 Kg, Kurangi Nasi dan RotiHype</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Indra Bekti berhasil menurunkan 10 kg berat badan berkat pola hidup sehat, mengurangi nasi dan makanan tinggi karbohidrat. Ia kini merasa lebih nyaman dan sehat.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://entertainment.kompas.com/read/2026/08/05/105301166/indra-bekti-turun-berat-badan-hingga-10-kg-kurangi-nasi-dan-roti?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/HgKxpJUQrKNcgGV8Mee8gw7wU2A=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/08/05/6a72ace08557d.jpeg</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Komparasi Changan Nevo Q05 Vs Jaecoo J5 EV, Pilih Mana?Otomotif</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Duel dua SUV listrik Rp 300 jutaan. Simak perbandingan desain, fitur, baterai, jarak tempuh, performa, hingga harga.</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/05/110200815/komparasi-changan-nevo-q05-vs-jaecoo-j5-ev-pilih-mana-?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/3f4DFDwFteW4JUX_XX4XDaXxMD0=/0x0:1264x843/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a72908834b4a.png</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Apa Itu Friend Bombing? Ini Ciri dan Cara MenyikapinyaLifestyle</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Friend-bombing menyerupai love-bombing, tetapi terjadi dalam ranah persahabatan sehingga sering kali lebih sulit disadari sejak awal.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://lifestyle.kompas.com/read/2026/08/05/110100820/apa-itu-friend-bombing-ini-ciri-dan-cara-menyikapinya?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/EoPbroI6It3crom92-hL9IYHOGA=/0x0:1417x945/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/01/29/697b90e878546.jpeg</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Berita Utama</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Tren Baru di China, Orangtua Rela Bayar Rp 34 Juta agar Anak Jadi "Warren Buffett Kecil"Tren</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Orangtua di China rela membayar Rp 34 juta untuk kursus finansial agar anak menjadi “Warren Buffett kecil”. Apa saja yang dipelajari anak-anak?</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/tren/read/2026/08/05/110000965/tren-baru-di-china-orangtua-rela-bayar-rp-34-juta-agar-anak-jadi-warren?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/t6-jEBcH9eEWOjfSeuph37-AxtU=/0x0:4411x2941/1200x675/filters:watermark(data/photo/2026/01/30/697c818d0ca91.png,0,-0,1)/data/photo/2026/08/04/6a71bc5105128.jpg</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>OJK Tindak 15 Perusahaan Pialang Asuransi Ilegal, Sebagian Masuk Tahap SidangMoney</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>OJK menemukan 15 pialang asuransi ilegal dan telah melakukan penindakan hukum. Langkah ini diikuti penguatan pengawasan melalui QR Code STDD.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/111000226/ojk-tindak-15-perusahaan-pialang-asuransi-ilegal-sebagian-masuk-tahap-sidang?source=sorotan</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/YxKhv82UZiNeBll_taObKpFfJPg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/01/23/697329f06af52.jpg</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Money17 detik laluPemerintah Kebut Operasional Kopdes, Pembangunan 35.000 Unit Dipercepat</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pemerintah genjarkan pembangunan Koperasi Desa/Kelurahan Merah Putih (KDKMP) hingga Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/122700826/pemerintah-kebut-operasional-kopdes-pembangunan-35.000-unit-dipercepat</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/OUkOf07puy9Ei25f-MTAE5Ip7WM=/225x8:1032x547/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/07/22/6a603bea0884d.jpeg</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Regional31 detik laluNasib 29 Guru Non-ASN di Metro: Dirumahkan, Dicoret dari Dapodik, Kini Terancam Gagal Ikut Penataan Guru</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Puluhan guru dan tenaga kependidikan non-ASN di Kota Metro dirumahkan sejak Januari 2026 dan Dapodik dinonaktifkan.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/122646278/nasib-29-guru-non-asn-di-metro-dirumahkan-dicoret-dari-dapodik-kini</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/bQ7zKMuhphHa9VEMv4zGtnskqg8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ba645eb1c.jpg</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>News35 detik laluBareskrim Polri Limpahkan "Andre The Doctor" ke Kejaksaan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 00:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Bandar narkoba Andre Fernando Tjhandra alias The Doctor telah dilimpahkan Bareskrim Polri ke Kejaksaan Negeri Jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/12264201/bareskrim-polri-limpahkan-andre-the-doctor-ke-kejaksaan</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/27GLvLsYbLr6P3xqCJzT18qdgb0=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72c407ee248.jpg</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H201"/>
+  <autoFilter ref="A1:H227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$237</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -430,6 +430,7 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +474,11 @@
           <t>Media</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sentimen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +517,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +556,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +595,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +634,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,6 +673,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -701,6 +712,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -739,6 +751,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -777,6 +790,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -815,6 +829,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,6 +868,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -891,6 +907,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -929,6 +946,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -967,6 +985,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1005,6 +1024,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1043,6 +1063,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1081,6 +1102,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1119,6 +1141,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1157,6 +1180,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1195,6 +1219,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1233,6 +1258,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1271,6 +1297,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1309,6 +1336,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1347,6 +1375,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1385,6 +1414,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1423,6 +1453,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1461,6 +1492,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1499,6 +1531,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1537,6 +1570,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1575,6 +1609,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1613,6 +1648,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1651,6 +1687,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1689,6 +1726,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1727,6 +1765,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1765,6 +1804,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1803,6 +1843,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1841,6 +1882,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1879,6 +1921,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1917,6 +1960,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1955,6 +1999,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1993,6 +2038,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2031,6 +2077,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2069,6 +2116,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2107,6 +2155,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2145,6 +2194,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2183,6 +2233,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2221,6 +2272,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2259,6 +2311,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2297,6 +2350,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2335,6 +2389,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2373,6 +2428,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2411,6 +2467,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2449,6 +2506,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2487,6 +2545,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2525,6 +2584,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2563,6 +2623,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2601,6 +2662,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2639,6 +2701,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2677,6 +2740,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2715,6 +2779,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2753,6 +2818,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2791,6 +2857,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2829,6 +2896,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2867,6 +2935,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2905,6 +2974,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2943,6 +3013,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2981,6 +3052,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3019,6 +3091,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3057,6 +3130,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3095,6 +3169,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3133,6 +3208,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3171,6 +3247,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3209,6 +3286,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3247,6 +3325,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3285,6 +3364,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3323,6 +3403,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3361,6 +3442,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3399,6 +3481,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3437,6 +3520,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3475,6 +3559,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3513,6 +3598,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3551,6 +3637,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3589,6 +3676,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3627,6 +3715,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3665,6 +3754,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3703,6 +3793,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3741,6 +3832,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3779,6 +3871,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3817,6 +3910,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3855,6 +3949,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3893,6 +3988,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3931,6 +4027,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3969,6 +4066,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4007,6 +4105,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4045,6 +4144,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4083,6 +4183,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4121,6 +4222,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4159,6 +4261,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4197,6 +4300,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4235,6 +4339,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4273,6 +4378,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4311,6 +4417,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4349,6 +4456,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4387,6 +4495,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4425,6 +4534,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4463,6 +4573,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4501,6 +4612,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4539,6 +4651,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4577,6 +4690,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4615,6 +4729,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4653,6 +4768,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4691,6 +4807,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4729,6 +4846,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4767,6 +4885,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4805,6 +4924,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4843,6 +4963,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4881,6 +5002,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4919,6 +5041,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4957,6 +5080,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4995,6 +5119,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5033,6 +5158,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5071,6 +5197,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5109,6 +5236,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5147,6 +5275,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5185,6 +5314,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5223,6 +5353,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5261,6 +5392,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5299,6 +5431,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5337,6 +5470,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5375,6 +5509,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5413,6 +5548,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5451,6 +5587,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5489,6 +5626,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5527,6 +5665,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5565,6 +5704,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5603,6 +5743,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5641,6 +5782,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5679,6 +5821,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5717,6 +5860,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5755,6 +5899,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5793,6 +5938,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5831,6 +5977,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5869,6 +6016,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5907,6 +6055,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5945,6 +6094,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5983,6 +6133,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6021,6 +6172,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6059,6 +6211,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6097,6 +6250,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6135,6 +6289,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6173,6 +6328,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6211,6 +6367,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6249,6 +6406,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6287,6 +6445,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6325,6 +6484,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6363,6 +6523,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6401,6 +6562,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6439,6 +6601,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6477,6 +6640,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6515,6 +6679,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6553,6 +6718,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6591,6 +6757,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6629,6 +6796,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6667,6 +6835,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6705,6 +6874,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6743,6 +6913,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6781,6 +6952,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6819,6 +6991,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6857,6 +7030,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6895,6 +7069,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6933,6 +7108,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6971,6 +7147,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7009,6 +7186,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7047,6 +7225,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7085,6 +7264,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7123,6 +7303,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7161,6 +7342,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7199,6 +7381,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7237,6 +7420,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7275,6 +7459,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7313,6 +7498,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7351,6 +7537,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7389,6 +7576,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7427,6 +7615,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7465,6 +7654,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7503,6 +7693,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7541,6 +7732,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7579,6 +7771,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7617,6 +7810,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7655,6 +7849,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7693,6 +7888,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7731,6 +7927,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7769,6 +7966,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7807,6 +8005,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7845,6 +8044,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7883,6 +8083,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7921,6 +8122,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7963,6 +8165,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8005,6 +8208,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8047,6 +8251,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8089,6 +8294,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8131,6 +8337,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8173,6 +8380,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8215,6 +8423,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8257,6 +8466,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8299,6 +8509,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8341,6 +8552,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8383,6 +8595,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8425,6 +8638,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8467,6 +8681,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8509,6 +8724,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8551,6 +8767,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8593,6 +8810,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8635,6 +8853,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8677,6 +8896,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8719,6 +8939,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8761,6 +8982,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8803,6 +9025,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8845,6 +9068,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8887,6 +9111,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8929,6 +9154,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8971,6 +9197,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9013,6 +9240,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9055,6 +9283,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9097,6 +9326,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9139,6 +9369,7 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9181,9 +9412,472 @@
           <t>Kompas</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Dua legenda tinju desak David Benavidez hadapi Oleksandr Usyk</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:32:10 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Dua legenda tinju, Roy Jones dan Mike Tyson, mendesak juara dunia kelas penjelajah (maksimal 90,7 kg) versi World ...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680571/dua-legenda-tinju-desak-david-benavidez-hadapi-oleksandr-usyk</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/03/Tinju.jpg</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Trump sebut Selat Hormuz segera dibuka dan ancam Iran jika gagal</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:30:36 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump, Selasa (4/8) mengatakan Selat Hormuz akan kembali dibuka ...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680568/trump-sebut-selat-hormuz-segera-dibuka-dan-ancam-iran-jika-gagal</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/24/thumbs_b_c_69ac83c0b272e6cd92f7de849ca8f5cc.jpg</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>BNPB: Banjir Padang berangsur surut, warga mulai bersihkan rumah</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:29:46 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) menyatakan kondisi banjir yang melanda Kota Padang, Sumatera Barat, telah ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680564/bnpb-banjir-padang-berangsur-surut-warga-mulai-bersihkan-rumah</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/gpfob10b.jpg</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>BNI catat kredit tumbuh 24,4 persen, laba capai Rp10,8 triliun</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:28:47 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>PT Bank Negara Indonesia (Persero) Tbk (BNI) mencatat pertumbuhan kredit sebesar 24,4 persen secara tahunan (year on ...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680560/bni-catat-kredit-tumbuh-244-persen-laba-capai-rp108-triliun</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000177552.jpg</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>BPS catat kenaikan penyerapan tenaga kerja Februari-Mei 2026</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:27:35 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat adanya kenaikan dalam penyerapan tenaga kerja sepanjang Februari-Mei 2026, yaitu ...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680556/bps-catat-kenaikan-penyerapan-tenaga-kerja-februari-mei-2026</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/05/IMG_2496_1.jpeg</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Digagalkan Bea Cukai, Begini Modus Impor Ilegal Harley Bekas dari China</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:17:25 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Kepala KPU Bea dan Cukai Tipe A Tanjung Priok, Adhang Noegroho Adhi mengatakan barang ilegal tersebut berasal dari China.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605109/digagalkan-bea-cukai-begini-modus-impor-ilegal-harley-bekas-dari-china</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-bekas-dari-china-1785901058163_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Isi Rumah Sarwendah yang Kini Ditinggalkan, Ada Kompor Miliaran Rupiah hingga Aula</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:34:34 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Tim Redaksi Kompas.com</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://entertainment.kompas.com/read/2026/08/05/123416566/isi-rumah-sarwendah-yang-kini-ditinggalkan-ada-kompor-miliaran-rupiah</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>KPK Ajukan Banding atas Vonis Gubernur Riau Abdul Wahid dkk</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:34:35 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>KPK ajukan banding atas vonis dua tahun bui terhadap Gubernur Riau nonaktif Abdul Wahid dan dua terdakwa kasus korupsi lainnya.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/12132111/kpk-ajukan-banding-atas-vonis-gubernur-riau-abdul-wahid-dkk</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/lPdw0OjDmf-mtI5W44hEX1Buz4Q=/97x0:1057x640/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/12/19/6944ed9e2dd8c.jpg</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Pinjol Kini Wajib Laporkan Seluruh Transaksi ke OJK, Apa Dampaknya?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:34:39 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Seluruh penyelenggara pindar diwajibkan membangun sistem pelaporan yang lebih rapi, akurat, dan terintegrasi.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/05/115451426/pinjol-kini-wajib-laporkan-seluruh-transaksi-ke-ojk-apa-dampaknya</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/b9E4nksax6w0K4NQvYXrBGeUcEc=/0x0:984x656/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2023/09/20/650b15bd7ee3d.jpg</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H227"/>
+  <autoFilter ref="A1:I237"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$345</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I236"/>
+  <dimension ref="A1:I345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11525,8 +11525,5131 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Humaniora</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Gerhana Matahari total 12 Agustus 2026: Daftar negara yang warganya bisa saksikan</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:38:36 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Fenomena gerhana Matahari total akan kembali mewarnai langit pada Rabu, 12 Agustus 2026. Peristiwa astronomi yang ...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680887/gerhana-matahari-total-12-agustus-2026-daftar-negara-yang-warganya-bisa-saksikan</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/08/fenomena-gerhana-bulan-total-blood-moon-2618101.jpg</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Apakah pasien diabetes boleh minum susu? Ini penjelasannya</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:12:13 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Pasien diabetes tetap diperbolehkan mengonsumsi susu, tetapi perlu memperhatikan jenis, jumlah, serta kandungan gula di ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680756/apakah-pasien-diabetes-boleh-minum-susu-ini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/12/04/susu.jpg</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Gejala burnout, penyebab, dan cara mengatasinya</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:10:06 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Organisasi Kesehatan Dunia (WHO) memasukkan burnout dalam International Classification of Diseases (ICD-11) sebagai ...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5680748/gejala-burnout-penyebab-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/03/08/pexels-nataliya-vaitkevich-6837793.jpg</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sidang Tahunan MPR Digelar 14 Agustus, Undang Presiden Terdahulu-Ketum Parpol</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:17:03 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Sidang Tahunan MPR dan Sidang Bersama DPR dan DPD RI akan digelar 14 Agustus 2026. Acara ini mengundang presiden dan ketua umum partai politik.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605752/sidang-tahunan-mpr-digelar-14-agustus-undang-presiden-terdahulu-ketum-parpol</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-mpr-ahmad-muzani-dengan-pimpinan-mpr-lainnya-dwi-rahmawatidetikcom-1785924998212_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tangani Banjir Padang, Kementerian PU Kerahkan Pompa hingga Pulihkan Akses</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:14:33 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Kementerian PU tangani dampak banjir di Padang dengan pemulihan akses, perbaikan infrastruktur, dan distribusi air bersih. Fokus pada keselamatan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605746/tangani-banjir-padang-kementerian-pu-kerahkan-pompa-hingga-pulihkan-akses</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kementerian-pu-gerak-cepat-tangani-banjir-di-padang-kerahkan-pompa-hingga-pulihkan-akses-1785924700397.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Mendes PDT: Kita Perlu Memastikan Kopdes KDKMP Ini Berhasil</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:12:40 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>sls</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Mendes PDT: Kita Perlu Memastikan Kopdes KDKMP Ini Berhasil</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/adv-nhl-detikcom/d-8605744/mendes-pdt-kita-perlu-memastikan-kopdes-kdkmp-ini-berhasil</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/adv-kemendesa-1785924738625.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Mendes Yandri Ajak UMKM Kolaborasi dengan Kopdes Merah Putih</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Menteri Yandri Susanto menegaskan Koperasi Desa Kelurahan Merah Putih (KDKMP) tidak akan menutup warung warga, melainkan mendukung UMKM dan kolaborasi usaha.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605721/mendes-yandri-ajak-umkm-kolaborasi-dengan-kopdes-merah-putih</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pembukaan-seminar-nasional-kdkmp-di-ternate-maluku-utara-yang-digagas-kementerian-desa-dan-pembangunan-daerah-tertinggal-1785905012909.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Rudal Balistik Houthi Hantam Kapal Tanker Arab Saudi di Laut Merah</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:02:15 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Kelompok Houthi mengklaim telah menghantam kapal tanker minyak Arab Saudi di perairan utara Laut Merah, dengan sejumlah rudal balistik.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605719/rudal-balistik-houthi-hantam-kapal-tanker-arab-saudi-di-laut-merah</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/iran-crisisyemen-red-sea-1784765178388_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Menko Polkam Pastikan Situasi Nasional Terkendali, Minta Masyarakat Tak Terpengaruh Hoaks</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:01:40 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Andhika Prasetia</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Menko Polkam memastikan situasi keamanan nasional tetap terkendali dan mengimbau masyarakat tidak terpengaruh hoaks yang beredar di media sosial.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8605439/menko-polkam-pastikan-situasi-nasional-terkendali-minta-masyarakat-tak-terpengaruh-hoaks</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menko-polkam-pastikan-situasi-nasional-terkendali-minta-masyarakat-tak-terpengaruh-hoaks-1785916804972.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Polisi Masih Buru Pelaku Penganiayaan dan Paksa Onani Pria di Tangerang</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Polisi masih mengejar pelaku penganiayaan dan pemaksaan masturbasi atau onani terhadap PG di Panongan, Kabupaten Tangerang, Banten.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605717/polisi-masih-buru-pelaku-penganiayaan-dan-paksa-onani-pria-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/08/04/kekerasan-penganiayaan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Antrean TransJ Mengular Imbas Kebakaran Gedung di Cikini Jakpus</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:53:25 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Proses pemadaman kebakaran gedung di Jalan Cikini Raya, Jakarta Pusat, masih berlangsung. Imbas kebakaran ini, mobil TransJ mengantre di dekat lokasi.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605695/antrean-transj-mengular-imbas-kebakaran-gedung-di-cikini-jakpus</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/proses-pemadaman-kebakaran-gedung-di-cikini-masih-berlangsung-ibasnya-antrean-bus-transjakarta-mengular-di-sekitar-lokasi-1785923534839_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Antisipasi Kebakaran Lahan, Kapolres Serang Minta Jajaran Patroli Terpadu</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:43:40 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Kapolres Serang, AKBP Andri Kurniawan, minta jajarannya antisipasi kebakaran hutan. Apel kesiapsiagaan digelar bersama Bupati untuk sinergi lintas sektoral.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605669/antisipasi-kebakaran-lahan-kapolres-serang-minta-jajaran-patroli-terpadu</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolres-kbp-andri-kurniawan-bersama-bupati-serang-ratu-rachmatuzakiyah-menggelar-apel-kesiapsiagaan-1785922989712_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Polisi Dalami Motif Saepul Bunuh dan Mutilasi Pria di Depok</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:38:18 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Polisi menangkap Saepul yang membunuh dan memutilasi pria K di Depok. Motif masih didalami, pelaku mengaku kesal saat cekcok dengan korban.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605667/polisi-dalami-motif-saepul-bunuh-dan-mutilasi-pria-di-depok</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Rusia Kembali Serang Ibu Kota Ukraina, 15 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:36:49 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Deutsche Welle (DW)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Sedikitnya 15 orang tewas setelah rudal Rusia menghantam Kyiv dan sekitarnya. Serangan terbaru kian menegaskan agresi Moskow dalam membidik di ibu kota Ukraina.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/dw/d-8605654/rusia-kembali-serang-ibu-kota-ukraina-15-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rusia-kembali-serang-kyiv-sedikitnya-15-orang-tewas-1785922609538.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Pramono Akan Tambah Obligasi Jakarta Jadi Rp 5,2 T, Biayai LRT dan RS</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:32:43 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Pramono Anung mengatakan nilai rencana penerbitan obligasi Jakarta bertambah menjadi Rp 5,2 triliun yang akan digunakan untuk membiayai proyek LRT dan RS.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605643/pramono-akan-tambah-obligasi-jakarta-jadi-rp-5-2-t-biayai-lrt-dan-rs</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gubernur-dki-jakarta-pramono-anung-1785919690459_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Tema dan Logo HUT ke-59 ASEAN 2026: Makna hingga Filosofinya</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:30:56 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Widhia Arum Wibawana</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>HUT ke-59 ASEAN 2026 mengusung tema Navigating Our Future, Together dengan logo baru yang melambangkan perjalanan kolektif dan komitmen negara anggota.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605526/tema-dan-logo-hut-ke-59-asean-2026-makna-hingga-filosofinya</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/tema-dan-logo-hut-ke-59-asean-2026-1785912334425_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sejumlah Orang Terjebak di Atap Gedung yang Kebakaran di Cikini</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:29:50 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Bangunan di Cikini, Menteng, Jakarta Pusat (Jakpus), kebakaran. Sejumlah orang terlihat ada di atap bangunan tersebut.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605633/sejumlah-orang-terjebak-di-atap-gedung-yang-kebakaran-di-cikini</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bangunan-di-cikini-menteng-jakarta-pusat-jakpus-kebakaran-sejumlah-orang-terlihat-ada-di-atap-bangunan-tersebut-rizky-amdetikc-1785922073029_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Tawuran di Ciputat Dipicu Aksi Geber Motor Saat Warga Pasang Umbul-umbul</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:27:30 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Tawuran remaja terjadi di Ciputat, Tangerang Selatan, dipicu aksi geber motor saat pemasangan umbul-umbul.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605632/tawuran-di-ciputat-dipicu-aksi-geber-motor-saat-warga-pasang-umbul-umbul</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/01/04/b21d558e-c595-4bba-8042-536fa6d359fc_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Menko Polkam Pastikan Mal Pasang Pagar Tak Terkait Isu Gangguan Keamanan</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:18:36 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago menegaskan pemasangan pagar di mal tidak terkait potensi gangguan keamanan.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605620/menko-polkam-pastikan-mal-pasang-pagar-tak-terkait-isu-gangguan-keamanan</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menko-polkam-1785921455713_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Pramono Bangga Ekonomi Jakarta Tumbuh 5,52% di Tengah Tekanan Global</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:18:24 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Pramono Anung menyambut positif pertumbuhan ekonomi Jakarta 5,52%. Ia optimistis stabilitas ekonomi tetap terjaga.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605619/pramono-bangga-ekonomi-jakarta-tumbuh-5-52-di-tengah-tekanan-global</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gubernur-dki-jakarta-pramono-anung-brigittadetik-1785921464991_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Disita KPK, Ini Penampakan Mobil yang Digunakan Bupati Pemalang Saat Kena OTT</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:11:37 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>KPK menyita mobil Bupati Pemalang Anom Widiyantoro terkait kasus pemerasan. Mobil digunakan Anom saat kena OTT KPK.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605609/disita-kpk-ini-penampakan-mobil-yang-digunakan-bupati-pemalang-saat-kena-ott</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mobil-yang-dipakai-bupati-pemalang-saat-kena-ott-kpk-adrial-akbardetikcom-1785921078810_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Pemuda Pulang Kerja Tewas Terjebak Karhutla di Ketapang Kalbar</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:07:52 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Ocsya Ade CP</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Taufik Hidayat (26) ditemukan tewas di lokasi karhutla di Kecamatan Matan Hilir Selatan, Kabupaten Ketapang, Kalimantan Barat. Korban diduga terjebak.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605604/pemuda-pulang-kerja-tewas-terjebak-karhutla-di-ketapang-kalbar</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/jenazah-korban-dievakuasi-tim-sar-gabungan-dari-lokasi-karhutla-ketapang-dok-istimewa-1785911385068_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Puncak El Nino Diprediksi hingga Oktober, Pramono Akan Gencarkan Hujan Buatan</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:04:07 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Pemprov DKI akan intensifkan modifikasi cuaca hingga dua kali seminggu untuk antisipasi puncak El Nino. Fokus pada ketersediaan air dan pencegahan kebakaran.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605600/puncak-el-nino-diprediksi-hingga-oktober-pramono-akan-gencarkan-hujan-buatan</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gubernur-dki-jakarta-pramono-anung-1785919690459_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Kemendes dan Asoasiasi Desa Tingkatkan Literasi KDKMP di Malut</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:03:24 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Menteri Yandri Susanto menghadiri Seminar Koperasi Desa Merah Putih di Ternate. Seminar ini bertujuan menyampaikan informasi KDKMP untuk penggerak ekonomi desa.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605597/kemendes-dan-asoasiasi-desa-tingkatkan-literasi-kdkmp-di-malut</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pembukaan-seminar-nasional-kdkmp-di-ternate-maluku-utara-yang-digagas-kementerian-desa-dan-pembangunan-daerah-tertinggal-1785905012909.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Kontrakan Saepul Pelaku Mutilasi Pria di Depok Diberi Garis Polisi</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:01:10 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Kontrakan Saepul, pelaku pembunuhan dan mutilasi pria bernama Kunaefi di Depok diberi garis polisi.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605585/kontrakan-saepul-pelaku-mutilasi-pria-di-depok-diberi-garis-polisi</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kontrakan-saepul-pelaku-mutilasi-pria-di-depok-digaris-polisi-1785920194177_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Tegang, Helikopter Trump Terlibat Insiden dengan Pesawat Komersial</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Otoritas Penerbangan Federal AS atau FAA sedang menyelidiki insiden keamanan yang melibatkan sebuah helikopter militer yang membawa Presiden AS Donald Trump.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605584/tegang-helikopter-trump-terlibat-insiden-dengan-pesawat-komersial</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/marine-one-helikopter-kepresidenan-as-yang-membawa-presiden-donald-trump-1785919890435_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Imbas Kebakaran Gedung, Lalin Arah Cikini Jakpus Dialihkan</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:59:49 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung di Cikini, Jakarta Pusat. Lalu lintas dialihkan ke Cut Meutia.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605583/imbas-kebakaran-gedung-lalin-arah-cikini-jakpus-dialihkan</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kebakaran-gedung-di-cikini-jakarta-pusat-jakpus-dok-tmc-polda-metro-jaya-1785920371696.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Mendagri Ungkap Butuh Suntikan Dana Rp 14 T untuk Atasi Fiskal di 79 Daerah</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:59:14 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Mendagri Tito ungkap butuh Rp 14 triliun untuk atasi fiskal 79 daerah. Anggaran ini untuk mengatasi kekurangan belanja pegawai dan skema DBH.</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605582/mendagri-ungkap-butuh-suntikan-dana-rp-14-t-untuk-atasi-fiskal-di-79-daerah</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-tito-karnavian-eva-safitridetikcom-1785920328767_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Penampakan Gedung di Cikini Jakpus Kebakaran, Asap Hitam Tutupi Bangunan</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:57:27 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Kebakaran terjadi di sebuah bangunan daerah Cikini, Jakarta Pusat. Asap hitam membumbung tinggi menutupi area bangunan.</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605581/penampakan-gedung-di-cikini-jakpus-kebakaran-asap-hitam-tutupi-bangunan</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kebakaran-gedung-di-jakpus-rizkydetikcom-1785920224430_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Nama Stasiun LRT Pegangsaan Dua Diubah Jadi Kelapa Gading, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:52:02 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung mengubah nama Stasiun LRT Pegangsaan Dua menjadi Kelapa Gading untuk menghindari kebingungan.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605573/nama-stasiun-lrt-pegangsaan-dua-diubah-jadi-kelapa-gading-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/stasiun-lrt-kelapa-gading-1785919858797_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Sekda Konawe Selatan Dicopot Usai Tabrak Adik Saat Digerebek Selingkuh</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:51:13 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Nadhir Attamimi</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Ichsan Porosi (56) dicopot dari jabatan Sekretaris Daerah (Sekda) Kabupaten Konawe Selatan (Konsel).</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605570/sekda-konawe-selatan-dicopot-usai-tabrak-adik-saat-digerebek-selingkuh</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/sekda-kabupaten-konawe-selatan-ichsan-porosi-1785853215610_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung Geledah Rumah Don Ritto di Bandung Terkait Kasus TPPU Febrie</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:48:23 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejaksaan Agung melakukan penggeledahan terkait kasus dugaan tindak pidana pencucian uang (TPPU) yang menjerat mantan Jampidsus Febrie Adriansyah (FA).</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605562/tim-9-kejagung-geledah-rumah-don-ritto-di-bandung-terkait-kasus-tppu-febrie</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/don-ritto-ditahan-kejagung-rumondangdetikcom-1784285323964_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Polisi-TNI Padamkan Karhutla di Pelalawan, Heli Water Bombing Diturunkan</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:43:37 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Kebakaran lahan 27 hektare di Pelalawan, Riau, melibatkan Polres, TNI, dan BPBD dalam pemadaman. Upaya terus dilakukan meski cuaca panas dan angin kencang.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605547/polisi-tni-padamkan-karhutla-di-pelalawan-heli-water-bombing-diturunkan</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-tni-bpbd-hingga-manggala-agni-turun-memadamkan-karhutla-di-kerumutan-pelalawan-1785919383502_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Kemensos Kirim Bantuan Logistik Korban Banjir dan Longsor di Kota Padang</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:41:55 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Kemensos salurkan bantuan logistik senilai Rp 1,4 miliar untuk korban banjir dan longsor di Padang.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605545/kemensos-kirim-bantuan-logistik-korban-banjir-dan-longsor-di-kota-padang</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemensos-kirim-bantuan-logistik-korban-banjir-dan-longsor-di-kota-padang-1785919275006.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Dokter RSUD Samarinda yang Ikut Komentari Pasien BPJS Kini Diistirahatkan</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:40:01 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Muhammad Budi Kurniawan</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>RSUD IA Moeis Samarinda telah memeriksa dokter berinisial RM yang berkomentar dalam unggahan keluhan pasien pengguna BPJS.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605543/dokter-rsud-samarinda-yang-ikut-komentari-pasien-bpjs-kini-diistirahatkan</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rsud-ia-moeis-samarinda-1785915903792_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Gedung di Cikini Jakpus Terbakar, 18 Mobil Damkar Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:37:54 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Kebakaran terjadi di salah satu gedung di Cikini, Jakarta Pusat. Asap hitam tampak membubung di lokasi.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605542/gedung-di-cikini-jakpus-terbakar-18-mobil-damkar-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kebakaran-gedung-di-jakarta-pusat-dok-istimewa-1785919056970_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Trenggiling Masuk ke Permukiman Warga di Pandeglang, Diserahkan ke BKSDA</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:37:18 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Aris Rivaldo</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Warga Desa Pagar Batu heboh dengan kemunculan trenggiling. Hewan langka ini dievakuasi BPBD dan diserahkan ke BKSDA untuk perlindungan.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605538/trenggiling-masuk-ke-permukiman-warga-di-pandeglang-diserahkan-ke-bksda</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/trenggiling-masuk-ke-permukiman-warga-di-pandeglang-1785919007059_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Cara Cek Status Kepesertaan BPJS Ketenagakerjaan Lewat Aplikasi JMO</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:33:07 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Cek status kepesertaan BPJS Ketenagakerjaan bisa secara online lewat aplikasi JMO. Simak langkah-langkahnya!</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605529/cara-cek-status-kepesertaan-bpjs-ketenagakerjaan-lewat-aplikasi-jmo</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/03/05/ilustrasi-kartu-bpjs-ketenagakerjaan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Jangan Salah Sangka, Ternyata Ini Cerita di Balik Nama Kelurahan Bencongan</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:28:05 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Kelurahan Bencongan di Tangerang memiliki nama unik yang tidak terkait dengan istilah 'bencong'. Lurah menjelaskan asal-usul nama tersebut.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605519/jangan-salah-sangka-ternyata-ini-cerita-di-balik-nama-kelurahan-bencongan</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kelurahan-bencongan-di-tangerang-1785918374196_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2 Kelompok Suporter Bola Ribut Usai Nobar di Bogor, 1 Motor Dibuang ke Kali</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:26:30 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Pengendara motor yang ketakutan langsung pergi meninggalkan kendaraannya. Kendaraan tidak bertuan itu kemudian dibuang ke kali oleh kelompok suporter lainnya.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605516/2-kelompok-suporter-bola-ribut-usai-nobar-di-bogor-1-motor-dibuang-ke-kali</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/23/a9b65512-585d-4408-9485-c92f175b793e_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Kelurahan di Tangerang Ini Punya Nama Unik: Bencongan</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:24:45 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Sejumlah daerah di Indonesia dikenal karena punya nama unik. Salah satunya ada di Kabupaten Tangerang, yakni Kelurahan Bencongan.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605502/kelurahan-di-tangerang-ini-punya-nama-unik-bencongan</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kantor-kelurahan-bencongan-di-tangerang-adhfardetikcom-1785918274531_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Kapolri Pastikan Keamanan Jelang HUT Ke-81 RI Terkendali</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:14:30 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Sigit memastikan HUT ke-81 RI aman. Polri bersinergi dengan pemerintah untuk stabilitas keamanan.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605480/kapolri-pastikan-keamanan-jelang-hut-ke-81-ri-terkendali</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolri-jenderal-listyo-sigit-prabowo-rumondangdetik-1785917635995_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Jl Raya Serang Km 32 Rawan Kecelakaan, Polantas Edukasi Warga Patuhi Aturan</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:08:51 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Polisi pun bergerak mengimbau warga di Jalan Raya Serang Km 32 mematuhi aturan lalu lintas dan selalu berhati-hati saat berkendara.</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605458/jl-raya-serang-km-32-rawan-kecelakaan-polantas-edukasi-warga-patuhi-aturan</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-bergerak-mengimbau-warga-di-jalan-raya-serang-km-32-mematuhi-aturan-lalu-lintas-dan-selalu-berhati-hati-saat-berkendara-1785917267417_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Menko Polkam Tegaskan Video Demo Ricuh di Medsos Hoax: Kami Akan Tindak Tegas</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:08:03 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago menegaskan akan menindak penyebar hoaks di media sosial yang mengganggu stabilitas nasional</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605456/menko-polkam-tegaskan-video-demo-ricuh-di-medsos-hoax-kami-akan-tindak-tegas</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menko-polkam-pastikan-situasi-nasional-terkendali-minta-masyarakat-tak-terpengaruh-hoaks-1785916804844_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Qatar Serukan Dunia Tekan Israel yang Ogah Setop Serangan di Gaza</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:07:49 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Qatar menyalahkan Israel atas penundaan pelaksanaan ketentuan dalam kesepakatan yang mengatur fase kedua gencatan senjata Gaza tersebut.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605455/qatar-serukan-dunia-tekan-israel-yang-ogah-setop-serangan-di-gaza</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/01/25/juru-bicara-kementerian-luar-negeri-qatar-majed-al-ansari_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Ini Dugaan Penyebab Mahasiswa PPDS Unri Bunuh Diri</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:07:44 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Raja Adil Siregar</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Sorang mahasiswa PPDS Universitas Riau nekat mengakhiri hidup. Korban diduga meninggal dunia akibat tekanan psikologis hingga terlilit pinjaman online.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605454/ini-dugaan-penyebab-mahasiswa-ppds-unri-bunuh-diri</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kasat-reskrim-polres-siak-1785862261450_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>5 Polisi Teladan Penerima Hoegeng Awards 2026, Ini Kategori dan Kiprahnya</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:06:49 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Hoegeng Awards 2026 memberikan penghargaan kepada lima anggota Polri teladan atas dedikasi, inovasi, dan integritas dalam pengabdian kepada masyarakat.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/infografis/d-8605453/5-polisi-teladan-penerima-hoegeng-awards-2026-ini-kategori-dan-kiprahnya</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/5-polisi-teladan-penerima-hoegeng-awards-2026-ini-kategori-dan-kiprahnya-1785917132362_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Target 500 Ribu Pekerja Migran, KP2MI Siapkan Program SMK Go Global</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:06:44 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Menteri P2MI Mukhtarudin luncurkan Asta Mandala SMK Go Global untuk tingkatkan kompetensi pekerja migran Indonesia.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605452/target-500-ribu-pekerja-migran-kp2mi-siapkan-program-smk-go-global</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kp2mi-1785917153698_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Legislator NasDem Geram Nakes Diduga Hina Pasien BPJS: Tak Punya Moral</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:51:51 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Irma Suryani Chaniago menanggapi dugaan nakes menghina pasien BPJS. Ia mengatakan oknum yang terlibat di kolom komentar pasien itu tak memiliki moral dan etika.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605417/legislator-nasdem-geram-nakes-diduga-hina-pasien-bpjs-tak-punya-moral</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/28/anggota-komisi-ix-dpr-ri-irma-suryani-saat-kunker-ke-pemprov-ntb-rabu-2852025-foto-ahmad-viqidetikbali-1748420962833_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Pengemis yang Maksa di Menara Kudus Dirazia, Sehari Kantongi Rp 540 Ribu</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:49:06 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Dian Utoro Aji</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Hasil pemeriksaan petugas menemukan uang lebih dari Rp 500 ribu yang diakui J hasil dari mengemisnya dalam sehari.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605413/pengemis-yang-maksa-di-menara-kudus-dirazia-sehari-kantongi-rp-540-ribu</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pengemis-meresahkan-1785912739239_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Bersiap Hadapi Invasi China, Taiwan Gelar Latihan Perang Terbesar</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:48:28 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Rita Uli Hutapea</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Latihan militer terbesar Taiwan dimulai pada hari Rabu (5/8), seiring pulau itu berupaya mempersiapkan penduduknya untuk menghadapi potensi invasi China.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605412/bersiap-hadapi-invasi-china-taiwan-gelar-latihan-perang-terbesar</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/14/taiwan-gelar-latihan-militer-han-kuang-presiden-lai-tinjau-langsung-kesiapan-tempur-1752471653969_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2 Pendaki Gunung Piramid Bondowoso Ditemukan Meninggal, Dievakuasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:48:03 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Chuk Shatu W</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Dua pendaki Gunung Piramid di Bondowoso ditemukan meninggal dunia. Proses evakuasi akan dilakukan hari ini setelah kendala cuaca dan medan.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605411/2-pendaki-gunung-piramid-bondowoso-ditemukan-meninggal-dievakuasi-hari-ini</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pendaki-gunung-piramid-hilang-1785839850385_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Pengakuan Saepul Tega Mutilasi Pria Kenalan Medsos di Depok</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Saepul (26) ditangkap atas pembunuhan dan mutilasi pria berinisial K (51) di Depok. Ia mengaku membunuh karena kesal ditampar korban.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605390/pengakuan-saepul-tega-mutilasi-pria-kenalan-medsos-di-depok</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Pohon Tumbang Timpa Truk di Pandeglang, Tak Ada Korban Jiwa</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:41:38 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Aris Rivaldo</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Sebuah pohon tumbang menimpa truk di Jalan AMD Lintas Timur, Pandeglang, akibat tersenggol kendaraan. Tidak ada korban jiwa, arus lalu lintas kembali normal.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605388/pohon-tumbang-timpa-truk-di-pandeglang-tak-ada-korban-jiwa</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/evakuasi-pohon-tumbang-di-pandeglang-dokistimewa-1785915608376_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Geledah Kantor Imigrasi Jaksel Kasus Silmy Karim, KPK Sita Duit SGD 8.500</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:34:38 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>KPK menggeledah kantor Imigrasi Jakarta Selatan (Jaksel) terkait kasus yang menjerat Silmy Karim. KPK menyita mata uang asing SGD 8.500.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605362/geledah-kantor-imigrasi-jaksel-kasus-silmy-karim-kpk-sita-duit-sgd-8-500</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/28/69bae68b-1d8e-430c-b130-0bc9367b2f65_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Detik-detik Saepul Pelaku Mutilasi Pria di Depok Ditangkap Polisi</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:31:42 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Subdit Resmob Ditreskrimum Polda Metro Jaya menangkap Saepul (26), pelaku pembunuhan sekaligus mutilasi pria bernama KNF (51), di Cipayung, Kota Depok.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605359/detik-detik-saepul-pelaku-mutilasi-pria-di-depok-ditangkap-polisi</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/resmob-ditreskrimum-polda-metro-jaya-menangkap-saepul-26-pelaku-pembunuhan-sekaligus-mutilasi-pria-bernama-knf-51-di-cipayung--1785915042453_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Menko Polkam Pastikan Situasi dalam Negeri Terkendali: Sangat Mantap</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:24:17 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago memastikan situasi keamanan terkendali. Ia mengingatkan masyarakat untuk tidak percaya hoaks di media sosial.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605341/menko-polkam-pastikan-situasi-dalam-negeri-terkendali-sangat-mantap</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menko-polkam-djamari-chaniago-rumondang-naibahodetikcom-1785914634891_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Waka Komisi IX DPR Soroti Dugaan Nakes Hina Pasien BPJS, Minta Ada Sanksi</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:21:33 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Waka Komisi IX DPR, Charles Honoris, mengaku prihatin adanya nakes yang diduga menghina pasien BPJS. Charles meminta nakes tersebut diberi sanksi.</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605337/waka-komisi-ix-dpr-soroti-dugaan-nakes-hina-pasien-bpjs-minta-ada-sanksi</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/24/wakil-ketua-komisi-ix-charles-honoris-silviadetikcom_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Coba Nyusup ke Pangkalan Udara AS, 8 Mahasiswa Korsel Ditahan</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:16:30 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Delapan mahasiswa Korea Selatan (Korsel) ditahan dan sedang menjalani penyelidikan, setelah mencoba menyusup ke dalam pangkalan udara AS.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605328/coba-nyusup-ke-pangkalan-udara-as-8-mahasiswa-korsel-ditahan</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/16/ilustrasi-bendera-korsel-dan-as_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Fix! TJ Blok M-Soetta Dinamai Transbandara, Tarif Rp 15 Ribu Mulai 1 September</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:07:54 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Layanan Transjakarta rute Blok M-Bandara Soekarno-Hatta kini resmi berganti nama menjadi Transbandara. Rute itu akan mematok tarif Rp 15 ribu mulai 1 September.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605314/fix-tj-blok-m-soetta-dinamai-transbandara-tarif-rp-15-ribu-mulai-1-september</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/27/ilustrasi-bus-transjakarta-dok-transj_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Dramatis, Pemakaman Massal 112 Korban Tewas Serangan Israel di Gaza</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:04:01 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Rita Uli Hutapea</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Rakyat Palestina memadati Kota Gaza untuk pemakaman massal bagi 112 orang, sebagian besar perempuan dan anak-anak, yang tewas dalam serangan Israel pada 2023.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605297/dramatis-pemakaman-massal-112-korban-tewas-serangan-israel-di-gaza</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pemakaman-massal-di-gaza-1785913331247_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Ini Tampang Saepul Pelaku Mutilasi Pria di Depok</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:03:52 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Saepul, pelaku pembunuhan dan mutilasi Kunaefi di Depok, ditangkap polisi. Ini tampangnya.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605296/ini-tampang-saepul-pelaku-mutilasi-pria-di-depok</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-mutilasi-pria-di-depok-dok-istimewa-1785913385016_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Polisi Bongkar Gudang 46 Juta Butir Obat Keras di Jaktim, 2 Pelaku Ditangkap</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:57:56 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Polisi menggagalkan upaya peredaran obat keras ilegal sebanyak 46 juta butir yang diungkap dari mobil boks dan gudang di Jaktim.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605278/polisi-bongkar-gudang-46-juta-butir-obat-keras-di-jaktim-2-pelaku-ditangkap</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-menggagalkan-upaya-peredaran-obat-keras-ilegal-sebanyak-46-juta-butir-yang-diungkap-dari-mobil-boks-dan-gudang-di-jakti-1785913013218_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Libur 17 Agustus 2026 Berapa Hari? Cek Ketentuannya</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:52:36 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>HUT RI ke-81 jatuh pada tanggal 17 Agustus 2026, menjadi hari libur nasional. Berapa hari libur peringatan HUT RI?</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605268/libur-17-agustus-2026-berapa-hari-cek-ketentuannya</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/28/ilustrasi-kalender_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Mendes Ajak Warga Maluku Utara Perkuat Peran Koperasi Desa Merah Putih</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:50:35 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Menteri Yandri Susanto ajak masyarakat Maluku Utara sukseskan Koperasi Desa Merah Putih. Program ini bertujuan tingkatkan ekonomi dan kesejahteraan desa.</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605261/mendes-ajak-warga-maluku-utara-perkuat-peran-koperasi-desa-merah-putih</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menteri-desa-dan-pembangunan-daerah-tertinggal-mendes-pdt-yandri-susanto-usai-pembukaan-seminar-nasional-kdkmp-di-maluku-utara-1785907139700_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Tembak Pengusaha Singkawang, Pembunuh Bayaran Ngaku Terima Rp 90 Juta</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:50:11 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Ocsya Ade CP</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Pengusaha di Kota Singkawang, Kalimantan Barat (Kalbar), tewas ditembak pembunuh bayaran.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605260/tembak-pengusaha-singkawang-pembunuh-bayaran-ngaku-terima-rp-90-juta</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/barang-bukti-yang-diamankan-dalam-kasus-pembunuhan-pengusaha-singkawang-dok-resmob-polda-kalbar-1785842361402_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>RSUD di NTT Buka Suara Usai Viral Dokter Beni Hina Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:42:19 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Ambrosius Ardin</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Viral dokter Beni Christian Sihombing ikut menghina pasien BPJS Yurizal Tri Chaerawan di Threads. Manajemen RSUD Ruteng, Manggarai, NTT, buka suara.</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605245/rsud-di-ntt-buka-suara-usai-viral-dokter-beni-hina-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/beni-christian-sihombing-dokter-rsud-ruteng-yang-berkomentar-jahat-di-threads-yurizaltrich-tangkapan-layar-bennychrstn-1785907200397_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Truk Angkut Kayu Illegal Logging Dicegat di Pelalawan, 2 Pelaku Ditangkap</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:41:31 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Polres Pelalawan mencegat truk yang angkut kayu ilegal. Dua pelaku ditangkap, satu melarikan diri. Penyelidikan berlanjut untuk pengembangan kasus.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605244/truk-angkut-kayu-illegal-logging-dicegat-di-pelalawan-2-pelaku-ditangkap</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satreskrim-polres-pelalawan-mengamankan-truk-yang-mengangkut-12-meter-kubik-kayu-illegal-logging-di-jalan-lintas-bono-pelalawa-1785912058695_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Dua Tahun PM Hasina Lengser, Reformasi Bangladesh Masih Mandek</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Deutsche Welle (DW)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Dua tahun setelah pemberontakan yang dipimpin mahasiswa melengserkan PM Sheikh Hasina, para kritikus menyebut momentum reformasi Bangladesh memudar.</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/dw/d-8605239/dua-tahun-pm-hasina-lengser-reformasi-bangladesh-masih-mandek</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dw-1785912076238_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Purbaya Taruh Lagi Rp 70 Triliun di Bank</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:05:31 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa akan menyuntikkan likuiditas sebesar Rp 70 triliun ke perbankan.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8605734/purbaya-taruh-lagi-rp-70-triliun-di-bank</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menteri-keuangan-purbaya-yudhi-sadewa-1783697461932_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Purbaya Tegaskan Babinsa-Bhabinkamtibmas Tak Ikut Tagih Pajak</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:38:29 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Penggunaan Koramil sama Babinsa itu tidak pernah kita gunakan. Itu mungkin di sana salah kebijakan atau apa, yang jelas nggak akan kita pakai itu, katanya.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605647/purbaya-tegaskan-babinsa-bhabinkamtibmas-tak-ikut-tagih-pajak</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/purbaya-garuk-kepala-apbn-april-2026-defisit-rp1644-triliun-1779201435821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Pemerintah Bakal Kucurkan Rp 20,5 T Bantu 490 Pemda yang Keuangannya Seret</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:32:43 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa akan menggelontorkan dana sebesar Rp 20,5 triliun untuk 490 pemerintah daerah (Pemda) yang kesulitan keuangan.</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605644/pemerintah-bakal-kucurkan-rp-20-5-t-bantu-490-pemda-yang-keuangannya-seret</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/menkeu-purbaya-1784785896260_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>500 Ribu Orang RI Dapat Kerja pada Februari-Mei 2026</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:17:42 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Kepala BPS Amalia Adininggar Widyasanti menyebut 522 ribu orang di Indonesia dapat kerja pada periode Februari-Mei 2026.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605618/500-ribu-orang-ri-dapat-kerja-pada-februari-mei-2026</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/30/plt-kepala-bps-amalia-adininggar-widyasanti_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Viral Gaji Manajer Kopdes Rp 16 Juta, Purbaya: Pasti Salah, Kegedean Kayaknya</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:09:35 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Kalau Rp 16 juta pasti salah, kegedean kayaknya. Saya dengar UMP lebih sedikit saja masih ketinggian, ungkap Purbaya.</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605605/viral-gaji-manajer-kopdes-rp-16-juta-purbaya-pasti-salah-kegedean-kayaknya</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/05/tawa-purbaya-pastikan-ekonomi-hingga-mei-2026-masih-solid-1780655487362_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Petugas Tera Timbangan, Lindungi Hak Konsumen</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:58:56 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Grandyos Zafna</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Petugas metrologi menera ulang timbangan pedagang di Pasar Setonobetek, Kediri, guna memastikan akurasi alat ukur dan melindungi hak konsumen.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8605262/petugas-tera-timbangan-lindungi-hak-konsumen</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/tera-timbangan-dan-alat-ukur-di-pasar-tradisional-1785912274127.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Anak Muda RI Paling Banyak Jadi Pengangguran, Begini Datanya</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:50:41 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Data BPS mengungkapkan generasi muda Indonesia di rentang umur 15-24 tahun paling banyak menjadi pengangguran.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605567/anak-muda-ri-paling-banyak-jadi-pengangguran-begini-datanya</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/30/ribuan-pencari-kerja-serbu-job-fair-di-depk-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Purbaya Ambil Alih Utang Kereta Cepat!</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:43:43 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Purbaya mengatakan proses pengalihan tersebut ditargetkan akan rampung pada pertengahan September mendatang.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605549/purbaya-ambil-alih-utang-kereta-cepat</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962097_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Purbaya Tunda Pajak Toko Online!</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:37:38 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) menunda penerapan pajak e-commerce yang sebelumnya berlaku efektif mulai 1 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605541/purbaya-tunda-pajak-toko-online</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962163_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Kemenhut Raih Opini WTP dari BPK</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:26:13 +0700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan Raja Antoni menyampaikan terima kasih atas capaian WTP yang diberikan oleh BPK.</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605514/kemenhut-raih-opini-wtp-dari-bpk</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemenhut-raih-wtp-dari-bpk-1785918185817_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Bahlil Lantik 4 Pejabat Baru ESDM, Ada yang Bakal Kawal Impor Minyak</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:21:41 +0700</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia melantik empat sosok baru sebagai pejabat di bawah Kementerian BUMN.</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8605490/bahlil-lantik-4-pejabat-baru-esdm-ada-yang-bakal-kawal-impor-minyak</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/28/menteri-esdm-bahlil-lahadalia-1777385212721_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>BPS: Pertumbuhan Ekonomi 17 Provinsi Triwulan II-2026 di Atas Angka Nasional</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:18:27 +0700</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) merilis data pertumbuhan ekonomi terbaru untuk triwulan 2-2026 sebesar 5,29 persen (y-on-y).</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605487/bps-pertumbuhan-ekonomi-17-provinsi-triwulan-ii-2026-di-atas-angka-nasional</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/kepala-bps-amalia-adininggar-widyasanti-1777954089390_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>BPS Ungkap 1 Juta Lulusan S1-S3 di RI Masih Nganggur</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:16:03 +0700</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Jumlah pengangguran dari lulusan jenjang D4, S1 hingga S3 tembus 1,03 juta orang.</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605483/bps-ungkap-1-juta-lulusan-s1-s3-di-ri-masih-nganggur</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/15/ilustrasi-pengangguran-atau-pencari-kerja-1747296462543_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>BNI Raup Laba Rp10,8 Triliun pada Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:11:28 +0700</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Andhika Prasetia</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>BNI membukukan laba bersih Rp10,8 triliun hingga semester I 2026. Kinerja ditopang pertumbuhan kredit, pendapatan, dan kualitas aset yang terjaga.</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8605469/bni-raup-laba-rp10-8-triliun-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bni-raup-laba-rp108-triliun-pada-semester-i-2026-1785916823148.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Strategi Pertamina Dorong Pelaut RI Kerja di Perusahaan Global</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:05:08 +0700</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>PT Pertamina Marine Solutions (PMSol) menjalin dua kerja sama dengan perusahaan pelayaran asal Tiongkok.</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8605530/strategi-pertamina-dorong-pelaut-ri-kerja-di-perusahaan-global</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/02/ilustrasi-kapal-kargo_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Bahlil Sebut RI Siapkan Kontrak Jangka Panjang Impor Minyak Rusia</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:00:08 +0700</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia mengatakan Indonesia siap untuk melakukan kerja sama impor minyak dari Rusia.</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8605432/bahlil-sebut-ri-siapkan-kontrak-jangka-panjang-impor-minyak-rusia</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/09/harga-minyak-mentah-hampir-us110-dunia-dilanda-kepanikan-1773053712369_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Pasokan Semen di Aceh Seret, SIG Turun Tangan Percepat Distribusi</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:59:08 +0700</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>PT Semen Indonesia (Persero) Tbk (SIG) mempercepat penanganan pasokan semen di Aceh dengan mengoptimalkan produksi dan distribusi di jaringan SIG Group.</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8605431/pasokan-semen-di-aceh-seret-sig-turun-tangan-percepat-distribusi</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/23/ilustrasi-semen-1747986685374_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Industri Tambang Lesu, BPS Buka-bukaan Biang Keroknya</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:46:34 +0700</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mengungkapkan industri pertambangan mengalami kelesuan pada Juni 2026.</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8605409/industri-tambang-lesu-bps-buka-bukaan-biang-keroknya</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/29/harga-batu-bara-di-aceh-turun-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Kepala BP BUMN Sambangi Kantor Purbaya, Bahas Pemangkasan BUMN-Utang Whoosh</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:32:45 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pengaturan BUMN Dony Oskaria menyambangi kantor Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa siang ini.</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605361/kepala-bp-bumn-sambangi-kantor-purbaya-bahas-pemangkasan-bumn-utang-whoosh</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kepala-badan-pengaturan-bumn-dony-oskaria-1785914791431_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Tingkat Pengangguran Turun Jadi 4,65%, BPS: Terendah Sejak 1994</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:27:54 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) menilai tingkat pengangguran terbuka pada Mei 2026 menjadi yang terendah sejak 1994.</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605354/tingkat-pengangguran-turun-jadi-4-65-bps-terendah-sejak-1994</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/03/04/bursa-kerja-di-bekasi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Batas Garis Kemiskinan Naik Jadi Rp 669.235 per Kapita</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:52:57 +0700</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat kenaikan garis kemiskinan pada bulan Maret 2026.</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605271/batas-garis-kemiskinan-naik-jadi-rp-669-235-per-kapita</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/04/wajah-kemiskinan-yang-jadi-pr-pemerintah-prabowo-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Pelaku UMKM Susah Rapikan Keuangan Usaha? Kelas Akuntansi Ini Bantu dari Dasar</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:49:34 +0700</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Ghefira</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Jualan jalan terus tapi catatan keuangan usaha berantakan? Kamu nggak sendirian.</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605258/pelaku-umkm-susah-rapikan-keuangan-usaha-kelas-akuntansi-ini-bantu-dari-dasar</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kelas-akuntansi-1785912551977_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Belum Diresmikan, Mohamed Salah Sudah Berseragam Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:20:25 +0700</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>dok. Trabzonspor</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Mohamed Salah bergabung ke Trabzonspor, tapi belum diumumkan secara resmi oleh klub. Si Raja Mesir sudah memamerkan foto berseragam tim asal Turki itu.</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8605707/belum-diresmikan-mohamed-salah-sudah-berseragam-trabzonspor</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mohamed-salah-1785922663021_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Superkomputer Jagokan Arsenal Juara Liga Inggris 2026/2027</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Superkomputer menjagokan Arsenal sebagai kampiun Liga Inggris 2026/2027. Meriam London diunggulkan atas Manchester City dan Liverpool.</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8605540/superkomputer-jagokan-arsenal-juara-liga-inggris-2026-2027</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/27/arsenal-1779899094056_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Siasat Putri KW Hadapi 3 Turnamen Besar Beruntun, Mana yang Jadi Prioritas?</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:52:25 +0700</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Putri KW mengungkap strategi menghadapi tiga turnamen besar secara beruntun, mulai Kejuaraan Dunia, China Masters, hingga Asian Games 2026.</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8605679/siasat-putri-kw-hadapi-3-turnamen-besar-beruntun-mana-yang-jadi-prioritas</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/putri-kusuma-wardani-1784268637783_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: 2 Pilar The Lions yang Harus Diwaspadai Garuda!</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:40:05 +0700</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia akan melawan Timnas Singapura dalam lanjutan Piala AFF 2026. Skuad Garuda harus mewaspadai dua pemain The Lions ini.</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605462/singapura-vs-indonesia-2-pilar-the-lions-yang-harus-diwaspadai-garuda</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/timnas-singapura-1785158858882_43.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>10 Klub Terbaik Dunia saat Ini, Siapa Nomor 1?</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:20:40 +0700</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Model ranking Opta merilis daftar 10 klub terbaik di dunia saat ini. Tim mana yang menempati posisi pertama?</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/gila-bola/d-8605340/10-klub-terbaik-dunia-saat-ini-siapa-nomor-1</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/31/arsenal-1780241719681_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Kata-kata Ter Stegen yang Tinggalkan Barcelona (Lagi)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Marc-Andre ter Stegen tinggalkan Barcelona lagi, gabung ke Ajax Amsterdam. Sang kiper mau buka lembaran baru dalam kariernya.</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8605467/kata-kata-ter-stegen-yang-tinggalkan-barcelona-lagi</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/05/marc-andre-ter-stegen-1770277879760.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Piala AFF 2026: Singapura Punya Sejumlah Keuntungan Lawan Indonesia</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam lanjutan Piala AFF 2026. The Lions mempunyai satu keunggulan dibanding Skuad Garuda.</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605338/piala-aff-2026-singapura-punya-sejumlah-keuntungan-lawan-indonesia</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_43.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Pelatih Persib Keluhkan Jadwal Final Piala Presiden, Minim Waktu Istirahat!</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Pelatih Persib Igor Tolic mengeluhkan jadwal Piala Presiden 2026 karena timnya hanya memiliki waktu istirahat dua hari sebelum menghadapi Persebaya di final.</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605460/pelatih-persib-keluhkan-jadwal-final-piala-presiden-minim-waktu-istirahat</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/pelatih-persib-igor-tolic-1785285535771_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Statistik Singapura vs Indonesia: The Lions Punya Benteng Kukuh</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:00:35 +0700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia menjalani laga penting melawan Timnas Singapura di Piala AFF 2026. The Lions menunjukkan pertahanan yang solid.</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605335/statistik-singapura-vs-indonesia-the-lions-punya-benteng-kukuh</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/timnas-singapura-1785158858882_43.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Indonesia Terus Tambah Medali di Asian Taekwondo Indonesia Open 2026</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:50:29 +0700</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Kris FW</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Indonesia kembali menambah medali perak di Asian Taekwondo Indonesia Open 2026. Merah Putih masih memimpin klasemen sementara.</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8605416/indonesia-terus-tambah-medali-di-asian-taekwondo-indonesia-open-2026</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/taekwondo-adrian-kaiser-1785915874623_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Presiden DFB Kritik Infantino, Disebut Tak Bertanggung Jawab!</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:40:05 +0700</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Presiden Asosiasi Sepakbola Jerman (DFB) Bernd Neuendorf mengkritik Presiden FIFA Gianni Infantino. Kritiknya berkaitan wacana penjualan saham Piala Dunia.</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8605266/presiden-dfb-kritik-infantino-disebut-tak-bertanggung-jawab</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/11/10/jokowi-beri-bintang-jasa-pratama-ke-presiden-fifa-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Putri KW Ungkap Kunci Tumbangkan Wang Zhi Yi Jelang Kejuaraan Dunia 2026</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Putri Kusuma Wardani mengungkap kunci keberhasilannya mengalahkan Wang Zhi Yi jelang Kejuaraan Dunia 2026.</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8605259/putri-kw-ungkap-kunci-tumbangkan-wang-zhi-yi-jelang-kejuaraan-dunia-2026</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/putri-kusuma-wardani-1784612448886_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: Garuda Oke di Laga Pamungkas Fase Grup</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:20:05 +0700</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia akan melawan Timnas Singapura dalam laga pamungkas fase grup Piala AFF 2026. Skuad Garuda mempunyai rekor bagus di pertandingan terakhir.</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605240/singapura-vs-indonesia-garuda-oke-di-laga-pamungkas-fase-grup</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/25/8e039e10-080b-4b14-b32f-89208705860d_43.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Lagi-lagi Viral Messi Belanja, Tanpa Pengawalan Seperti Warga Biasa</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Lionel Messi menikmati betul hidupnya di Miami, AS. Messi sekali lagi kedapatan di tempat belanja, tanpa pengawalan layaknya warga biasa.</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/gila-bola/d-8605238/lagi-lagi-viral-messi-belanja-tanpa-pengawalan-seperti-warga-biasa</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/17/lionel-messi-1776390442563.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Putri KW Bidik Emas Kejuaraan Dunia 2026: Tak Mau Lagi Cuma Perunggu!</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:50:50 +0700</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Putri Kusuma Wardani menargetkan medali emas pada Kejuaraan Dunia Bulutangkis 2026 di India.</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8605237/putri-kw-bidik-emas-kejuaraan-dunia-2026-tak-mau-lagi-cuma-perunggu</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/putri-kusuma-wardani-1784612448825_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Pasar EV dan SUV Naik, Pilihan Ban Mobil Semakin Spesifik</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:32:51 +0700</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Tren kenaikan pasar kendaraan listrik dan SUV mendorong produsen ban menyesuaikan portofolio produk sesuai kebutuhan setiap jenis armada</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/05/173100715/pasar-ev-dan-suv-naik-pilihan-ban-mobil-semakin-spesifik</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/IARqB4Hi5qhCmTsudiNxYzq-0OM=/0x0:1500x1000/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/05/6a730f8281296.jpeg</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Air Kali Bekasi Menghitam dan Bau, PDAM Ubah Pengolahan hingga Kurangi Produksi Air Bersih</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:32:52 +0700</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Kali Bekasi menghitam dan berbau akibat pencemaran, memaksa Perumda Tirta Patriot mengubah proses pengolahan air, meningkatkan biaya, dan mengurangi produksi air bersih.</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/05/17153851/air-kali-bekasi-menghitam-dan-bau-pdam-ubah-pengolahan-hingga-kurangi</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/C0E7GR8TQga7RC3uebwwgBbC6k8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72ea44a43f4.jpg</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>'Kalau Warga Sakit Tak Bisa Berobat, yang Dosa Bupatinya' , Pesan Sang Ibu di Balik Home Care Jember</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:32:53 +0700</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Sang ibu secara tegas memperingatkan bahwa keselamatan dan kesehatan warga miskin Jember berada sepenuhnya di atas pundak Fawait sebagai bupati.</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/05/170000378/-kalau-warga-sakit-tak-bisa-berobat-yang-dosa-bupatinya-pesan-sang-ibu-di</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/StijpGeHdNEv847KPR4jCsjdzC0=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/04/01/69ccd124e3222.jpg</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I236"/>
+  <autoFilter ref="A1:I345"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$457</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I345"/>
+  <dimension ref="A1:I457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16648,8 +16648,5273 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Pemkot Pangkalpinang gandeng KP2MI cegah pekerja migran nonprosedural</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:29:35 +0700</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Pangkalpinang menandatangani nota kesepakatan dengan Kementerian Pelindungan Pekerja Migran ...</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681339/pemkot-pangkalpinang-gandeng-kp2mi-cegah-pekerja-migran-nonprosedural</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PEMKOT-PANGKALPINANG-GANDENG-KP2MI-CEGAH-PEKERJA-MIGRAN-NONPROSEDURAL.jpg</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Komisi III DPR apresiasi Polres Tangsel gagalkan peredaran 46 juta obat ilegal</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:29:13 +0700</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi III Dewan Perwakilan Rakyat (DPR) RI Moh. Rano Alfath mengapresiasi kinerja Polres Tangerang ...</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681368/komisi-iii-dpr-apresiasi-polres-tangsel-gagalkan-peredaran-46-juta-obat-ilegal</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000451151.jpg</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Danantara: Pupuk Indonesia, Pelindo hingga Angkasa Pura potensial IPO</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:27:44 +0700</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer (COO) Badan Pengelola Investasi Daya Anagata Nusantara (Danantara Indonesia), Dony Oskaria ...</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681365/danantara-pupuk-indonesia-pelindo-hingga-angkasa-pura-potensial-ipo</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-18.50.12.jpeg</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Taruna Akmil gembleng kemandirian siswa Sekolah Rakyat Pacitan</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:27:10 +0700</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Taruna Akademi Militer melatih kemandirian siswa Sekolah Rakyat Menengah Atas (SRMA) 46 Pacitan melalui pembiasaan ...</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681363/taruna-akmil-gembleng-kemandirian-siswa-sekolah-rakyat-pacitan</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/458666.jpg</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Ekonom sebut MBG turut topang pertumbuhan 5,29 persen pada triwulan II</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:26:45 +0700</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Kepala Departemen Riset Makroekonomi dan Pasar Keuangan Bank Permata Faisal Rachman menyebut Program Makan Bergizi ...</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681360/ekonom-sebut-mbg-turut-topang-pertumbuhan-529-persen-pada-triwulan-ii</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/22/1000232541.jpg</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>WIKA Terus Kebut Pembangunan Tol Jakarta–Cikampek II Selatan Paket 2A, Progres Capai 85,20%</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:26:39 +0700</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>PT Wijaya Karya (Persero) Tbk (WIKA) terus mempercepat penyelesaian pembangunan Jalan Tol Jakarta–Cikampek II ...</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681357/wika-terus-kebut-pembangunan-tol-jakarta-cikampek-ii-selatan-paket-2a-progres-capai-8520</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-19.21.34.jpeg</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Sayap pemuda Partai Golkar rekrut 10 ribu kader muda di Jakarta</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:26:05 +0700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Sayap pemuda Partai Golkar, Angkatan Muda Partai Golkar (AMPG), telah merekrut 10 ribu kader muda dari berbagai wilayah ...</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681356/sayap-pemuda-partai-golkar-rekrut-10-ribu-kader-muda-di-jakarta</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000580328.jpg</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Penonton MotoGP Indonesia 2026 ditargetkan meningkat 15,7 persen</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:25:56 +0700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>InJourney Tourism Development Corporation (ITDC) menargetkan penonton MotoGP Indonesia yang digelar di Sirkuit ...</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681352/penonton-motogp-indonesia-2026-ditargetkan-meningkat-157-persen</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1005735307.jpg</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Pemkot Solo perketat pengawasan SPPG akibat 108 siswa keracunan</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:24:34 +0700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Solo telah menerima hasil pemeriksaan laboratorium terkait dugaan gangguan kesehatan yang ...</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681297/pemkot-solo-perketat-pengawasan-sppg-akibat-108-siswa-keracunan</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-184913.jpg</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Airlangga: Ekonomi RI tumbuh di atas rata-rata global</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:23:02 +0700</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto menyatakan ekonomi Indonesia mampu tumbuh di atas rata-rata ...</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681348/airlangga-ekonomi-ri-tumbuh-di-atas-rata-rata-global</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-19.08.34.jpeg</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>BPKP: Transformasi digital harus mampu tingkatkan kualitas pengawasan</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:20:11 +0700</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pengawasan Keuangan dan Pembangunan (BPKP) Muhammad Yusuf Ateh mengatakan transformasi digital harus mampu ...</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681347/bpkp-transformasi-digital-harus-mampu-tingkatkan-kualitas-pengawasan</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/BPKP-Siskeudes.jpg</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Menko Polkam pastikan video demo besar jelang 17 Agustus adalah hoaks</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:18:16 +0700</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Koordinator bidang Politik dan Keamanan, Djamari Chaniago, di Jakarta, Rabu (5/8), memastikan, video ...</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681308/menko-polkam-pastikan-video-demo-besar-jelang-17-agustus-adalah-hoaks</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKO-POLKAM-PASTIKAN-VIDEO-DEMO-BESAR-JELANG-17-AGUSTUS-ADALAH-HOAKS.jpg</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>KemenPANRB: Kelola konflik kepentingan kunci birokrasi berintegritas</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:16:11 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Deputi Bidang Reformasi Birokrasi, Akuntabilitas Aparatur dan Pengawasan Kementerian Pendayagunaan Aparatur Negara dan ...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681341/kemenpanrb-kelola-konflik-kepentingan-kunci-birokrasi-berintegritas</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000580356.jpg</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>BKSDA kerahkan tim tangani kemunculan harimau di permukiman warga</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:15:37 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Balai Konservasi Sumber Daya Alam (BKSDA) Aceh mengerahkan tim untuk menangani kemunculan harimau sumatra (Panthera ...</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681337/bksda-kerahkan-tim-tangani-kemunculan-harimau-di-permukiman-warga</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/harimau-sp-jernih-atim.jpg</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Media: Iran sebut perundingan dengan Oman berlangsung positif</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:13:19 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Juru bicara Kementerian Luar Negeri Iran Esmaeil Baghaei pada Selasa (4/8) menyebut perundingan yang sedang ...</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681333/media-iran-sebut-perundingan-dengan-oman-berlangsung-positif</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/iran.jpg</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>KPDI 17 hasilkan rekomendasi untuk transformasi perpustakaan di era AI</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:11:01 +0700</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Konferensi Perpustakaan Digital Indonesia (KPDI) ke-17 yang diselenggarakan Forum Perpustakaan Digital Indonesia (FPDI) ...</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681331/kpdi-17-hasilkan-rekomendasi-untuk-transformasi-perpustakaan-di-era-ai</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG-20260805-WA0021_edit_2129834622078130.jpg</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Panas ekstrem Italia, 3 orang meninggal dan 27 kota siaga merah</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:09:32 +0700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Italia menetapkan 27 kota dalam status siaga panas tertinggi di tengah gelombang panas yang kembali melanda negara itu, ...</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681327/panas-ekstrem-italia-3-orang-meninggal-dan-27-kota-siaga-merah</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CmxztpE000013_20260803_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>BNPB optimalkan penguatan Desa Tangguh Bencana di Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:09:17 +0700</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ANTARA - ‎Badan Nasional Penanggulangan Bencana (BNPB) menggelar lokakarya ketangguhan masyarakat melalui program ...</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681307/bnpb-optimalkan-penguatan-desa-tangguh-bencana-di-jawa-timur</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BNPB-OPTIMALKAN-PENGUATAN-DESA-TANGGUH-BENCANA-DI-JAWA-TIMUR.jpg</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Nusron sebut kepuasan masyarakat jadi tolok ukur kualitas pelayanan</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:08:48 +0700</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa kepuasan ...</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681324/nusron-sebut-kepuasan-masyarakat-jadi-tolok-ukur-kualitas-pelayanan</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_184209.jpg</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>KAI Sumbar periksa jalur Stasiun Padang-Bukit Putus antisipasi cuaca</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:08:08 +0700</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia Divisi Regional II Sumatera Barat mengintensifkan pengawasan operasional dengan menggelar ...</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681320/kai-sumbar-periksa-jalur-stasiun-padang-bukit-putus-antisipasi-cuaca</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-18.35.26.jpeg</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Kemendukbangga dukung investasi pendidikan untuk bonus demografi</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:07:46 +0700</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga)/BKKBN mendukung investasi pada pendidikan dalam ...</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681316/kemendukbangga-dukung-investasi-pendidikan-untuk-bonus-demografi</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG-20260805-WA0010-1.jpg</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>MPR: Sidang tahunan digelar 14 Agustus, undang presiden terdahulu</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:07:41 +0700</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani mengatakan sidang tahunan MPR serta sidang bersama MPR, DPR, dan DPD digelar pada 14 Agustus ...</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681313/mpr-sidang-tahunan-digelar-14-agustus-undang-presiden-terdahulu</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_6191.jpeg</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Pimpinan Lembaga Aparatur Sipil ASEAN bertemu di Kamboja</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:07:31 +0700</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Para pimpinan lembaga aparatur sipil dari seluruh ASEAN berkumpul di Kamboja pada Rabu (5/8) untuk menghadiri acara ...</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681312/pimpinan-lembaga-aparatur-sipil-asean-bertemu-di-kamboja</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/16/un71003324.jpg</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Menhan nilai TNI sudah mampu jawab tantangan tugas</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:07:17 +0700</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Menteri Pertahanan Sjafrie Sjamsoeddin menyatakan semua jajaran TNI dari ketiga matranya sudah mampu menjawab ...</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681309/menhan-nilai-tni-sudah-mampu-jawab-tantangan-tugas</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/menhan-terima-warga-kehormatan-korps-marinir-tni-al-2834705.jpg</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Indonesia dan negara Islam bahas sikap bersama soal Yerusalem</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:01:24 +0700</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Para menteri luar (menlu) negeri dari Indonesia, negara Arab, dan negara Islam berkumpul di Yordania, ...</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681304/indonesia-dan-negara-islam-bahas-sikap-bersama-soal-yerusalem</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/08/309654_edited.jpegWisata-Kota-Suci-Tiga-Agama-13022026-Adm-16.jpg</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Sekolah Rakyat di Jateng tampung 2.692 siswa</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:56:13 +0700</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Tengah menyebutkan bahwa program Sekolah Rakyat di wilayah tersebut kini telah menampung 2.692 ...</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681291/sekolah-rakyat-di-jateng-tampung-2692-siswa</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002081267.jpg</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Kemenag luncurkan gerakan bersih-bersih masjid sambut HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:55:29 +0700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Kementerian Agama meluncurkan gerakan Bersih-Bersih Masjid Nasional (Geber Masjid) pada 10 Agustus 2026 yang menjadi ...</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681287/kemenag-luncurkan-gerakan-bersih-bersih-masjid-sambut-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000176660.jpg</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Pemprov Jateng siapkan dana cadangan Rp1,2 triliun untuk Pilkada 2029</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:54:03 +0700</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Tengah menyiapkan dana cadangan sekitar Rp1,2 triliun untuk membiayai penyelenggaraan ...</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681284/pemprov-jateng-siapkan-dana-cadangan-rp12-triliun-untuk-pilkada-2029</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1002081246.jpg</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Menhan pastikan kekuatan tempur TNI terpenuhi lewat latihan trimatra</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:52:39 +0700</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Pertahanan RI Sjafrie Sjamsoeddin menyebut pasukan TNI telah mampu menjawab tantangan tugas dalam ...</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681273/menhan-pastikan-kekuatan-tempur-tni-terpenuhi-lewat-latihan-trimatra</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-183715.jpg</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Kursus dan belajar sepanjang hayat menuju kemandirian</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:51:20 +0700</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>"Belajarnya menyenangkan dan sangat berdampak. Ini hal baru bagi saya, dan benar-benar menjadi bekal hidup," ...</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681283/kursus-dan-belajar-sepanjang-hayat-menuju-kemandirian</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/pelatihan-keterampilan-membatik-untuk-siswa-2659725.jpg</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Polres Cianjur: Masyarakat dapat hubungi 110 untuk layanan air bersih</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:49:09 +0700</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Kepolisian Resor Cianjur, Jawa Barat, membuka pelayanan pendistribusian air bersih dengan truk tangki ke sejumlah ...</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681279/polres-cianjur-masyarakat-dapat-hubungi-110-untuk-layanan-air-bersih</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/salurkan-air.jpg</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen: Partisipasi semesta hadirkan PAUD bagi Suku Anak Dalam</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:46:27 +0700</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) mengatakan partisipasi semesta berhasil menghadirkan layanan ...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681275/kemendikdasmen-partisipasi-semesta-hadirkan-paud-bagi-suku-anak-dalam</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000228352.jpg</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Pertambangan dan konsumsi dorong ekonomi Sumsel tumbuh 5,20 persen</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat perekonomian Sumatera Selatan tumbuh 5,20 persen pada triwulan II 2026 ...</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681267/pertambangan-dan-konsumsi-dorong-ekonomi-sumsel-tumbuh-520-persen</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PERTAMBANGAN-DAN-KONSUMSI-DORONG-EKONOMI-SUMSEL-TUMBUH-5-20-PERSEN.jpg</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Perkuat ketahanan energi, pemerintah percepat pembangunan jargas</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:43:08 +0700</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah mempercepat pembangunan jaringan gas rumah tangga atau jargas agar dapat memperkuat ketahanan ...</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681255/perkuat-ketahanan-energi-pemerintah-percepat-pembangunan-jargas</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-182913.jpg</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Ketua Komisi IV DPRD NTB divonis bebas dalam kasus gratifikasi</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:41:10 +0700</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Majelis hakim Pengadilan Tindak Pidana Korupsi pada Pengadilan Negeri Mataram menjatuhkan vonis bebas kepada Ketua ...</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681272/ketua-komisi-iv-dprd-ntb-divonis-bebas-dalam-kasus-gratifikasi</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/ketua-komisi-iv-dprd-ntb-hamdan-kasim.jpg</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Pelindo optimalkan sarana ekspor-impor di terminal peti kemas</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:38:49 +0700</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>ANTARA - PT Pelabuhan Indonesia (Pelindo) Regional 2 Pontianak terus meningkatkan kapasitas Terminal Peti Kemas ...</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681224/pelindo-optimalkan-sarana-ekspor-impor-di-terminal-peti-kemas</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-180950.jpg</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Pemerintah siap salurkan bantuan pusat Rp20,5 triliun ke daerah</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:36:57 +0700</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pemerintah akan menyalurkan bantuan pemerintah pusat senilai Rp20,5 ...</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681268/pemerintah-siap-salurkan-bantuan-pusat-rp205-triliun-ke-daerah</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Konferensi-pers-Kementerian-Keuangan-050826-Bay-01.jpg</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ASDP sterilisasi 5 pelabuhan utama tingkatkan ketertiban operasional</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:34:31 +0700</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>PT ASDP Indonesia Ferry secara resmi memberlakukan kebijakan sterilisasi kawasan pelabuhan dengan menerapkan sistem ...</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681264/asdp-sterilisasi-5-pelabuhan-utama-tingkatkan-ketertiban-operasional</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000873859.jpg</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Huawei debutkan MateBook Pro S diklaim jadi PC teringan di dunia</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:34:12 +0700</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Huawei secara resmi mendebutkan notebook anyar bernama MateBook Pro S yang diklaimnya sebagai PC teringan di ...</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681261/huawei-debutkan-matebook-pro-s-diklaim-jadi-pc-teringan-di-dunia</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_181445598.jpg</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>MPR kaji payung hukum paling tepat untuk PPHN</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:32:25 +0700</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Majelis Permusyawaratan Rakyat (MPR) RI tengah mengkaji payung hukum yang paling tepat agar pokok-pokok ...</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681260/mpr-kaji-payung-hukum-paling-tepat-untuk-pphn</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_6188.jpeg</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Fraksi Golkar gelar audiensi bahas akses Bendungan Lahor di Blitar</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:31:31 +0700</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Ketua Fraksi Partai Golkar DPR RI M. Sarmuji menerima audiensi Direktur Utama Perum Jasa Tirta I Fahmi Hidayat beserta ...</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681257/fraksi-golkar-gelar-audiensi-bahas-akses-bendungan-lahor-di-blitar</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000580305.jpg</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Kemensos perluas pendataan kuota siswa Sekolah Rakyat Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial memperluas pendataan keluarga sasaran untuk memenuhi kuota siswa Sekolah Rakyat (SR) permanen Kota ...</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681251/kemensos-perluas-pendataan-kuota-siswa-sekolah-rakyat-banjarbaru</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_1646.jpeg</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Gapasdap: Sterilisasi pelabuhan Ketapang-Gilimanuk perkuat tata kelola</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:29:02 +0700</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Gilimanuk (Bali) menjadi bagian dalam upaya memperkuat tata kelola pelabuhan.
+"Ini merupakan bagian ...</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681248/gapasdap-sterilisasi-pelabuhan-ketapang-gilimanuk-perkuat-tata-kelola</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG-20260805-WA0193.jpg</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Menag sebut ekosistem ekonomi syariah harus dibangun dengan kepatuhan</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:27:32 +0700</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Menteri Agama Nasaruddin Umar menegaskan penguatan ekonomi syariah Indonesia harus dibangun melalui ekosistem yang ...</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681247/menag-sebut-ekosistem-ekonomi-syariah-harus-dibangun-dengan-kepatuhan</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000176655_1.jpg</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Pasha Ungu salut Jakarta banyak ruang urban representasif anak muda</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:27:17 +0700</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Video musik (MV) lagu terbaru Ungu yang berjudul "Utara-Selatan" menyuguhkan visual berbagai sudut ruang ...</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681245/pasha-ungu-salut-jakarta-banyak-ruang-urban-representasif-anak-muda</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_174513.jpg</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Unggahan Modi diblokir, India beri Zuckerberg 3 hari untuk minta maaf</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:24:15 +0700</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Komite Parlemen India untuk Komunikasi dan Teknologi Informasi memberi waktu tiga hari kepada CEO Meta, Mark Zuckerberg ...</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681241/unggahan-modi-diblokir-india-beri-zuckerberg-3-hari-untuk-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/02/zuckerberg.jpg</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Kabar baik untuk peternak, pemerintah tunda kenaikan harga pakan ayam</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:22:53 +0700</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Peternak memberi pakan ayam petelur di Desa Karangsong, Kabupaten Indramayu, Jawa Barat, Rabu (5/8/2026). Kementerian ...</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5681240/kabar-baik-untuk-peternak-pemerintah-tunda-kenaikan-harga-pakan-ayam</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Kementan-Tunda-Kenaikan-Harga-Pakan-050826-DS-1A.jpg</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>MTN seni budaya jadi akses pelaku budaya tingkatkan kompetensi</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:21:19 +0700</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Pengembangan, Pemanfaatan, dan Pembinaan Kebudayaan Kementerian Kebudayaan Ahmad Mahendra mengatakan ...</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681239/mtn-seni-budaya-jadi-akses-pelaku-budaya-tingkatkan-kompetensi</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000591219.jpg</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Damkar berhasil padamkan kebakaran gedung lima lantai di Cikini</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:21:19 +0700</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Gulkarmat) Jakarta Pusat berhasil memadamkan kebakaran yang ...</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681235/damkar-berhasil-padamkan-kebakaran-gedung-lima-lantai-di-cikini</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000831959.jpg</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Pemerintah tekan pengiriman PMI ilegal lewat program SMK Go Global</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:20:25 +0700</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (KP2MI) berupaya mencegah pengiriman tenaga kerja migran Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681231/pemerintah-tekan-pengiriman-pmi-ilegal-lewat-program-smk-go-global</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/Target-80-ribu-lulusan-ikut-program-SMK-Go-Global-150626-bk-2.jpg</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan stimulus antisipasi dampak El Nino</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:44:13 +0700</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pemerintah tengah menyiapkan paket stimulus pada semester II-2026 ...</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681165/pemerintah-siapkan-stimulus-antisipasi-dampak-el-nino</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Konferensi-pers-Kementerian-Keuangan-050826-Bay-3-1.jpg</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>IHSG ditutup menguat ikuti bursa saham kawasan Asia</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:38:36 +0700</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Rabu sore ditutup naik mengikuti penguatan bursa ...</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681163/ihsg-ditutup-menguat-ikuti-bursa-saham-kawasan-asia</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-5.jpg</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Pameran Indo Healthcare Gakeslab Expo Hadirkan 60 Perusahaan dari 9 Negara</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:33:19 +0700</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>IndoHealthcare Gakeslab Expo 2026 mempertemukan 60 perusahaan dari 9 negara. Pameran ini fokus pada inovasi alat kesehatan dan program edukatif.</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605981/pameran-indo-healthcare-gakeslab-expo-hadirkan-60-perusahaan-dari-9-negara</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pameran-indo-healthcare-gakeslab-expo-hadirkan-60-perusahaan-dari-9-negara-1785933168745.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Korlantas Polri Catat Korban Tewas Laka Lantas Semester 1 Turun 22,92 Persen</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:31:00 +0700</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Herianto Batubara</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Satu bulan sejak kepemimpinan Kakorlantas Polri Irjen Wibowo, kinerja keselamatan lalu lintas menunjukkan tren positif.</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605979/korlantas-polri-catat-korban-tewas-laka-lantas-semester-1-turun-22-92-persen</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kakorlantas-polri-irjen-wibowo-1785932835877_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Legislator Gerindra Marlyn Maisarah Cek Pembangunan Jembatan Gantung Cibeber</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:29:55 +0700</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Dea Duta</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Anggota DPR Marlyn Maisarah meninjau pembangunan Jembatan Gantung Cibeber, memastikan aspirasi masyarakat terwujud untuk akses yang lebih aman dan layak.</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605978/legislator-gerindra-marlyn-maisarah-cek-pembangunan-jembatan-gantung-cibeber</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/legislator-gerindra-marlyn-maisarah-tinjau-jembatan-gantung-cibeber-pastikan-aspirasi-warga-terlaksana-1785932950128.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Pemprov Banten Ungkap Warga Pulau Tunda Hibahkan Lahan untuk Pembangunan PLTS</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:25:59 +0700</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Kepala Dinas ESDM Banten, Ari James, mengungkapkan warga Pulau Tunda menghibahkan tanah untuk pembangunan PLTS. Proyek diharapkan dimulai akhir Oktober.</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605977/pemprov-banten-ungkap-warga-pulau-tunda-hibahkan-lahan-untuk-pembangunan-plts</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/10/gapura-pulau-tunda-di-kabupaten-serang-banten-1778370076108_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Polda Riau Bekali 70 Polwan Kemampuan Public Speaking dan Negosiasi</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:24:49 +0700</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Kapolda Riau dorong profesionalisme polwan melalui pelatihan public speaking dan negosiasi untuk meningkatkan komunikasi dan pelayanan publik.</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/melindungi-tuah-marwah/d-8605969/polda-riau-bekali-70-polwan-kemampuan-public-speaking-dan-negosiasi</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/70-polwan-polda-riau-dilatih-untuk-meningkatkan-kemampuan-dalam-public-speaking-dan-negosiasi-1785932631610_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Subuh Keliling Jadi Strategi Polda Sumsel Perkuat Harkamtibmas Muara Enim</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:22:28 +0700</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Polda Sumsel intensifkan Program SULING untuk memperkuat keamanan masyarakat. Kegiatan ini melibatkan dialog langsung antara Polri dan warga.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8605966/subuh-keliling-jadi-strategi-polda-sumsel-perkuat-harkamtibmas-muara-enim</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/subuh-keliling-jadi-strategi-polda-sumsel-perkuat-harkamtibmas-di-muara-enim-1785932484815.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Wamendagri Minta Kepala Daerah Bangun Ekosistem KDKMP dengan Stakeholder</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:15:52 +0700</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Wamendagri mendorong kepala daerah untuk kolaborasi dalam membangun Koperasi Desa/Kelurahan Merah Putih, guna memperkuat ekonomi lokal dan kesejahteraan.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605958/wamendagri-minta-kepala-daerah-bangun-ekosistem-kdkmp-dengan-stakeholder</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/wamendagri-minta-kepala-daerah-bangun-ekosistem-kdkmp-dengan-stakeholder-1785932048004_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Ziarah ke Makam Bung Karno, Ketua MPR Tegaskan Indonesia Rumah Bersama</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:13:51 +0700</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani ziarah ke makam Bung Karno di Blitar, mengenang jasa proklamator dan menegaskan pentingnya persatuan bangsa menjelang HUT RI ke-81.</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605957/ziarah-ke-makam-bung-karno-ketua-mpr-tegaskan-indonesia-rumah-bersama</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-mpr-ri-ahmad-muzani-bersama-para-wakil-ketua-mpr-ri-bambang-wuryanto-lestari-moerdijat-hidayat-nur-wahid-eddy-soeparno-d-1785931848449.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Curi Kosmetik hingga Mobil Mainan di Minimarket, Pria di Bogor Ditangkap</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:02:08 +0700</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Pria berinisial FZ ditangkap setelah mencuri kosmetik dan mobil mainan di minimarket Bogor. Pelaku diamankan pegawai dan warga sebelum melarikan diri.</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605945/curi-kosmetik-hingga-mobil-mainan-di-minimarket-pria-di-bogor-ditangkap</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-sita-barang-hasil-curian-pelaku-di-minimarket-bogor-1785931301115_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>DPD Undang JK Hadiri Sidang Tahunan MPR: Kumpulkan Tokoh Bangsa</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:45:24 +0700</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Ketua DPD Sultan Najamudin mengundang Jusuf Kalla untuk hadir dalam Sidang Tahunan MPR pada 14 Agustus, menyambut HUT RI ke-81.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605927/dpd-undang-jk-hadiri-sidang-tahunan-mpr-kumpulkan-tokoh-bangsa</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-memberikan-undangan-sidang-tahunan-mpr-ke-jk-1785930226552_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Jejak Kematian Sutrimo di Klinik Kecantikan</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:42:19 +0700</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Ani Mardatila</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Spanduk sewa di Klinik Mordent mengarah ke Nurman Herin. Rekaman CCTV rumah sakit memperlihatkan empat pria yang mengantar Sutrimo, termasuk Febrio Adiono.</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/spotlight/d-8605924/jejak-kematian-sutrimo-di-klinik-kecantikan</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ilustrasi-1785929882493.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Gus Ipul Tekankan Tiga Prioritas Pengelolaan Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:41:25 +0700</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Menteri Sosial Gus Ipul mengingatkan kepala Sekolah Rakyat untuk fokus pada MPLS, menjaga aset negara, dan memperkuat dokumentasi publik.</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605920/gus-ipul-tekankan-tiga-prioritas-pengelolaan-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gus-ipul-tekankan-tiga-prioritas-pengelolaan-sekolah-rakyat-1785930007215.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Meneladani Sosok Jenderal Hoegeng di Era Modern</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:38:03 +0700</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Kita harapkan (polisi) terus mau bekerja di mana pun mereka berada</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/intermeso/d-8605918/meneladani-sosok-jenderal-hoegeng-di-era-modern</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/hoegeng-awards-2026-1785929835852_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>MPR Sudah Serahkan Konsep PPHN ke Prabowo, Harap Segera Jadi Produk Hukum</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:36:45 +0700</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani membahas Pokok-Pokok Haluan Negara (PPHN) dan menyerahkannya kepada Presiden Prabowo. PPHN diharapkan jadi produk hukum yang mengikat.</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605916/mpr-sudah-serahkan-konsep-pphn-ke-prabowo-harap-segera-jadi-produk-hukum</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-mpr-ahmad-muzani-dengan-pimpinan-mpr-lainnya-dwi-rahmawatidetikcom-1785924998212_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Viral Air Kali Cileungsi Bekasi Hitam Bak Oli, Diduga Tercemar</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:31:34 +0700</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Video air Kali Bekasi berwarna hitam mirip oli bekas viral di media sosial (medsos). Kualitas air tersebut menurun karena ada dugaan pencemaran.</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605905/viral-air-kali-cileungsi-bekasi-hitam-bak-oli-diduga-tercemar</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/video-air-kali-bekasi-berwarna-hitam-mirip-oli-bekas-viral-di-media-sosial-medsos-kualitas-air-tersebut-menurun-karena-ada-dug-1785929406139_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Warga Sempat Kaget Awal Pindah ke Tangerang Ada Kelurahan Bernama Bencongan</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:23:23 +0700</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Kelurahan Bencongan di Tangerang menarik perhatian warga karena namanya yang unik. Mahmud dan Anas berbagi cerita tentang asal-usul nama tersebut.</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605879/warga-sempat-kaget-awal-pindah-ke-tangerang-ada-kelurahan-bernama-bencongan</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kantor-kelurahan-bencongan-di-tangerang-adhfardetikcom-1785918274531_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Bedanya Istana Merdeka dan Istana Negara, Mana Lokasi Upacara HUT RI?</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:13:46 +0700</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Widhia Arum Wibawana</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Artikel ini membahas perbedaan Istana Merdeka dan Istana Negara, serta lokasi Upacara HUT ke-81 RI yang digelar di Istana Merdeka. Ketahui lebih lanjut!</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605733/bedanya-istana-merdeka-dan-istana-negara-mana-lokasi-upacara-hut-ri</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2014/08/18/cc9601cf-bb53-4886-b16d-cec8a3ea7845_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>IKEA Sesalkan Pengunjung Bikin Konten Dewasa di Tokonya</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:11:31 +0700</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>IKEA menyesalkan tindakan pembuatan konten dewasa oleh pengunjung di gerainya. Perusahaan menegaskan tidak mendukung perilaku tersebut.</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605860/ikea-sesalkan-pengunjung-bikin-konten-dewasa-di-tokonya</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/08/13/7c00899f-88c3-451b-8c7c-0db88735008d_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Selidiki Penyebab Kebakaran, Polisi Akan Olah TKP Gedung di Cikini</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:08:36 +0700</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung di Cikini, Jakarta Pusat. Polisi selidiki penyebab kebakaran.</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605857/selidiki-penyebab-kebakaran-polisi-akan-olah-tkp-gedung-di-cikini</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kapolsek-cikini-akbp-braiel-arnold-rondonuwu-dan-perwira-piket-damkar-subady-1785928065917_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Objek Misterius Bikin Penerbangan di Bandara Jerman Dialihkan</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:03:33 +0700</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Sebuah insiden terkait keamanan yang melibatkan objek misterius yang ditemukan di area bandara Jerman telah menyebabkan pengalihan penerbangan.</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605853/objek-misterius-bikin-penerbangan-di-bandara-jerman-dialihkan</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/03/10/sepi-sunyi-bandara-di-jerman-saat-petugas-mogok-kerja-1741602963617_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Kebakaran Gedung di Cikini Padam, Lalin Kembali Dibuka</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:57:26 +0700</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Kebakaran di gedung Jalan Cikini Raya, Jakarta Pusat, telah padam. Lalu lintas dibuka kembali.</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605847/kebakaran-gedung-di-cikini-padam-lalin-kembali-dibuka</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/lalu-lintas-di-depan-gedung-kebakaran-di-cikini-kembali-dibuka-1785927416107_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Kebakaran Gedung di Cikini, Damkar Duga Api Berasal dari Lantai Dasar</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:56:59 +0700</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Kebakaran terjadi di gedung Cikini, Jakarta Pusat. Damkar menduga api berasal dari lantai dasar.</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605836/kebakaran-gedung-di-cikini-damkar-duga-api-berasal-dari-lantai-dasar</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/petugas-telah-mengevakuasi-sejumlah-orang-yang-terjebak-di-atap-bangunan-di-cikini-menteng-jakpus-kebakaran-para-pekerja-dieva-1785926356880_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Waka MPR Ajak Kampus Ambil Peran Atasi Krisis Sampah Plastik</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:55:55 +0700</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Eddy Soeparno mendorong perguruan tinggi aktif dalam solusi perubahan iklim dan krisis sampah plastik melalui kebijakan berbasis ilmu pengetahuan.</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605833/waka-mpr-ajak-kampus-ambil-peran-atasi-krisis-sampah-plastik</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mpr-goes-to-campus-di-titik-ke-51-eddy-soeparno-kembali-tegaskan-urgensi-penerapan-extended-producer-responsibility-epr-1785927116413.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Ngeri, Influencer Ditembak Mati Saat Live TikTok</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:55:20 +0700</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Rita Uli Hutapea</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Mengerikan! Seorang influencer ditembak mati di luar sebuah restoran saat melakukan siaran langsung di media sosial.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605830/ngeri-influencer-ditembak-mati-saat-live-tiktok</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/17/ilustrasi-penembakan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Saepul Pemutilasi Pria di Depok Baru Ngontrak 7 Bulan Bareng Pria JJ</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Polisi menangkap Saepul, pembunuh dan pemutilasi Kunaefi di Depok. Pelaku mengontrak bersama pria JJ.</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605822/saepul-pemutilasi-pria-di-depok-baru-ngontrak-7-bulan-bareng-pria-jj</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kontrakan-saepul-pelaku-mutilasi-pria-di-depok-digaris-polisi-1785920194177_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Bareskrim Bongkar Peredaran Etomidate dari Thailand, 4 Orang Ditangkap</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:49:52 +0700</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri ungkap jaringan narkotika etomidate cair asal Thailand, menangkap empat pelaku dan menyita 210 ml cairan senilai Rp 630 juta.</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605821/bareskrim-bongkar-peredaran-etomidate-dari-thailand-4-orang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pelaku-peredaran-narkotika-etomidate-cair-dari-thailand-dok-istimewa-1785926969945_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>10 Pekerja yang Terjebak Dievakuasi dari Kebakaran Gedung di Cikini</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:39:54 +0700</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Petugas telah mengevakuasi sejumlah orang yang terjebak di atap bangunan di Cikini, Menteng, Jakpus kebakaran. Para pekerja dievakuasi dalam kondisi selamat.</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605795/10-pekerja-yang-terjebak-dievakuasi-dari-kebakaran-gedung-di-cikini</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/petugas-telah-mengevakuasi-sejumlah-orang-yang-terjebak-di-atap-bangunan-di-cikini-menteng-jakpus-kebakaran-para-pekerja-dieva-1785926356880_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Polisi Gagalkan Tawuran dan Balap Liar di Jaktim, Sita Sajam-Botol Air Keras</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:39:24 +0700</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Patroli rutin ini dilakukan dini hari tadi. Petugas awalnya menerima laporan adanya dugaan aksi tawuran di Jalan Kelurahan I, Duren Sawit, Jakarta Timur.</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605794/polisi-gagalkan-tawuran-dan-balap-liar-di-jaktim-sita-sajam-botol-air-keras</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-tangkap-pelaku-tawuran-dan-balap-liar-di-jaktim-dokistimewa-1785926327429_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Jakarta Terima Aset Rp 2,27 Triliun dari Penyerahan Fasos dan Fasum Pengembang</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:39:10 +0700</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta terima aset Rp 2,27 triliun dari pengembang untuk fasos dan fasum. Penyerahan ini mendukung ruang publik dan layanan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605793/jakarta-terima-aset-rp-2-27-triliun-dari-penyerahan-fasos-dan-fasum-pengembang</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gubernur-dki-jakarta-pramono-anung-di-balai-kota-dki-jakarta-rabu-582026-brigittadetik-1785926248398_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>5 Berita Terpopuler Internasional Hari Ini</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:39:01 +0700</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Rita Uli Hutapea</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Adik perempuan dari pemimpin Korea Utara Kim Jong Un, berkomentar sengit mengenai Jepang yang memperkuat militernya.</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605792/5-berita-terpopuler-internasional-hari-ini</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/02/10/956d0813-bc23-4e2d-b24d-d17d49027219_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Peneliti Monash University Ungkap Pola Video Lama Demo Diviralkan Lagi</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:38:22 +0700</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Rakhmad Hidayatulloh Permana</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Peneliti Monash University Indonesia mengungkap ada dugaan pola tertentu untuk menaikkan video lama aksi demo mahasiswa tersebut.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605791/peneliti-monash-university-ungkap-pola-video-lama-demo-diviralkan-lagi</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/04/logo-x-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Trump Yakin Bisa Segera Berdamai dengan Iran</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:32:25 +0700</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Deutsche Welle (DW)</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Presiden AS Donald Trump mengatakan kesepakatan terkait Selat Hormuz dapat tercapai secepatnya pekan ini.</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8605776/trump-yakin-bisa-segera-berdamai-dengan-iran</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/trump-yakin-bisa-segera-berdamai-dengan-iran-1785925945337.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Viral Tanggul Muara Baru Rembes, Pramono Minta Dinas SDA Cek Kondisi</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:30:50 +0700</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Pramono menanggapi kondisi becek di Jalan Muara Baru akibat rembesan air laut. Dia meminta Dinas SDA cek tanggul untuk mencegah kerusakan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605773/viral-tanggul-muara-baru-rembes-pramono-minta-dinas-sda-cek-kondisi</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gubernur-dki-jakarta-pramono-anung-1785925811298_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Kemlu RI Hormati Rencana AS Tutup Konsulat di Medan</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:27:54 +0700</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri RI menanggapi rencana AS menutup Konsulat di Medan, meyakini hubungan diplomatik tetap baik. Keputusan AS dihormati Indonesia.</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605769/kemlu-ri-hormati-rencana-as-tutup-konsulat-di-medan</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/14/ilustrasi-bendera-indonesia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Tito Minta 16 K/L Eksekusi Program Rehab-Rekon Pascabencana Sumatera</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:23:54 +0700</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian mendorong 16 kementerian segera eksekusi program rehabilitasi pascabencana Sumatera dengan anggaran Rp 100,1 triliun.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605762/tito-minta-16-k-l-eksekusi-program-rehab-rekon-pascabencana-sumatera</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/tito-minta-16-kl-eksekusi-program-rehab-rekon-pascabencana-sumatera-1785925375376.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Ringankan Beban Warga, Wali Kota New York Akan Buka Supermarket Murah</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:17:03 +0700</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>BBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Wali Kota New York, Zohran Mamdani, akan membuka supermarket milik pemerintah kota. Tujuannya, meringankan beban pengeluaran warga.</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/bbc-world/d-8605751/ringankan-beban-warga-wali-kota-new-york-akan-buka-supermarket-murah</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/seperti-apa-supermarket-harga-murah-yang-digagas-wali-kota-new-york-zohran-mamdani-1785925023853.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Catat! Pemerintah Janji Harga Pertalite Nggak Naik</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Pemerintah memastikan harga bahan bakar minyak (BBM) subsidi jenis Pertalite tidak mengalami kenaikan hingga akhir 2026.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8605983/catat-pemerintah-janji-harga-pertalite-nggak-naik</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/11/18/antrean-pemotor-di-spbu-tanah-abang-demi-pertalite-seharga-premium-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Bamsoet: Penguatan Sektor Properti Harus Jadi Bagian Strategi Nasional</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:01:41 +0700</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Bamsoet menegaskan sektor properti sebagai pilar ketahanan ekonomi Indonesia. Pertumbuhan properti dorong investasi dan lapangan kerja di tengah ketidakpastian.</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605944/bamsoet-penguatan-sektor-properti-harus-jadi-bagian-strategi-nasional</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/board-of-commissioners-meeting-pt-lippo-karawaci-tbk-di-menara-matahari-lippo-village-central-karawaci-tangerang-banten-rabu-5-1785931183239.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Toko Online Lega, Pemerintah Tunda Pajak Final 0,5 Persen</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:00:55 +0700</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Kemenkeu menunda penerapan PPh final 0,5 persen bagi pelaku usaha di marketplace dan toko digital yang semula berlaku pada Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8605901/toko-online-lega-pemerintah-tunda-pajak-final-0-5-persen</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/toko-online-lega-pemerintah-tunda-pajak-final-05-persen-1785929270255_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Airlangga Buka-bukaan Nasib Insentif Rp 100 M buat Kota Terbersih di RI</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Menko Perekonomian Airlangga Hartarto mengatakan pemerintah mulai menggodok insentif untuk kota terbersih di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605921/airlangga-buka-bukaan-nasib-insentif-rp-100-m-buat-kota-terbersih-di-ri</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/momen-airlangga-pamer-ekonomi-ri-tumbuh-lebih-tinggi-dari-as-china-1777977746006_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Jurang Ketimpangan Makin Lebar, Pemerintah Buka Suara</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:55:15 +0700</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Perekonomian Airlangga Hartarto merespons data gini ratio yang meningkat pada Maret 2026.</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605935/jurang-ketimpangan-makin-lebar-pemerintah-buka-suara</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/13/menko-perekonomian-airlangga-hartarto-1783940653691_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Insentif Kendaraan Listrik Segera Meluncur, Airlangga: Anggarannya Sudah Ada</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Menko Bidang Perekonomian Airlangga Hartarto menjamin anggaran insentif kendaraan listrik sudah disiapkan.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8605898/insentif-kendaraan-listrik-segera-meluncur-airlangga-anggarannya-sudah-ada</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/22/pemerintah-target-62-ribu-spklu-beroperasi-pada-2030-1779450647560_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Angka Penduduk Miskin RI Menurun, Kini Tercatat 22,93 Juta Orang</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:57:58 +0700</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Pradita Utama</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>BPS mencatat jumlah penduduk miskin di Indonesia pada Maret 2026 turun menjadi 22,93 juta orang atau 7,94 persen dari total penduduk.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8605398/angka-penduduk-miskin-ri-menurun-kini-tercatat-22-93-juta-orang</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketika-angka-kemiskinan-menurun-beban-hidup-warga-belum-ikut-berkurang-1785915493211.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Bocoran Bos Danantara soal IPO BUMN, Pegadaian-InJourney Airports Masuk Radar</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:57:43 +0700</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Terdapat sejumlah BUMN dengan kapitalisasi pasar besar yang layak melakukan IPO.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8605848/bocoran-bos-danantara-soal-ipo-bumn-pegadaian-injourney-airports-masuk-radar</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kepala-badan-pengaturan-bumn-dony-oskaria-1785914791431_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Ekonomi RI Tumbuh 5,2%, Airlangga Buka Suara</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:45:07 +0700</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Menko Bidang Perekonomian Airlangga Hartarto buka suara ekonomi Indonesia tumbuh hingga 5,2% di triwulan kedua 2026.</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605814/ekonomi-ri-tumbuh-5-2-airlangga-buka-suara</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menko-bidang-perekonomian-airlangga-hartarto-respons-pertumbuhan-ekonomi-ri-1785926581049_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>IHSG Ditutup Menguat ke 6.351</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:42:20 +0700</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) menguat hingga penutupan perdagangan Rabu (5/8/2026).</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8605797/ihsg-ditutup-menguat-ke-6-351</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Purbaya Jawab Kabar Batas Defisit APBN 3% Mau Dihapus</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:33:32 +0700</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa, menegaskan pemerintah tidak berniat untuk menghapus batas defisit APBN.</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8605779/purbaya-jawab-kabar-batas-defisit-apbn-3-mau-dihapus</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/apbn-jebol-defisit-tembus-rp1965-triliun-menkeu-purbaya-buka-suara-1784619962228_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Danantara Disebut Mau Beli Saham Bursa</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:27:42 +0700</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi (BPI) Daya Anagata Nusantara (Danantara) disebut telah mengajukan porsi saham Bursa Efek Indonesia (BEI).</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8605768/danantara-disebut-mau-beli-saham-bursa</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/30/wisma-danantara-indonesia-1751283332958_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Singapura vs Indonesia: Siapa Lebih Baik di 5 Laga Terakhir?</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Singapura berhadapan dengan Indonesia dalam lanjutan Piala AFF 2026. Dalam lima pertandingan terakhir, The Lions atau Skuad Garuda yang lebih baik?</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605778/singapura-vs-indonesia-siapa-lebih-baik-di-5-laga-terakhir</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Bezzecchi Tatap MotoGP Inggris usai Jeda Penuh Kerja Keras</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:10:25 +0700</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Rider Aprilia, Marco Bezzecchi, belum pulih sepenuhnya dari cedera patah tulang selangka. Italiano itu mengakui kondisinya belum 100 persen.</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8605813/bezzecchi-tatap-motogp-inggris-usai-jeda-penuh-kerja-keras</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/27/marco-bezzecchi-di-motogp-belanda-2026-1782564446798_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Rumor Transfer: Zirkzee Jadi Prioritas Juventus</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Kris FW</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Juventus kabarnya tengah menjadikan Joshua Zirkzee sebagai target utama untuk memperkuat lini depan.</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8605874/rumor-transfer-zirkzee-jadi-prioritas-juventus</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/01/joshua-zirkzee-1762014912962_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Neymar Bikin Ulah, Provokasi Ofisial dan Fans Lawan di Mixed Zone</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Neymar kembali membuat ulah di Brasil. Bintang Santos ini memprovokasi ofisial dan fans lawan di mixed zone usai pertandingan.</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8605672/neymar-bikin-ulah-provokasi-ofisial-dan-fans-lawan-di-mixed-zone</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/27/neymar-jr-1772168092330_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Pensiun Jadi Wasit, Anthony Taylor Langsung Dapat Kerjaan Baru di Turki</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Kris FW</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Dua pekan setelah pensiun sebagai wasit, Anthony Taylor langsung mendapat jabatan penting di Federasi Sepakbola Turki (TFF).</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8605675/pensiun-jadi-wasit-anthony-taylor-langsung-dapat-kerjaan-baru-di-turki</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/09/17/anthony-taylor_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Real Madrid Segera Kirim Mastantuono ke Fiorentina</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:15:30 +0700</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Real Madrid dan Fiorentina sudah menjalani kesepakatan terkait masa depan Franco Mastantuono. Pemain asal Argentina itu dikabarkan segera tiba di Italia.</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8605678/real-madrid-segera-kirim-mastantuono-ke-fiorentina</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/28/2237719373-1759046911317_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Persib vs Persebaya: Kerja Keras Menuju Tinta Emas Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Hasil semifinal Piala Presiden 2026 menelurkan Persib Bandung dan Persebaya Surabaya sebagai pemenang. Maung Bandung dan Bajul Ijo akan bersaing menjadi juara.</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605676/persib-vs-persebaya-kerja-keras-menuju-tinta-emas-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/laga-persebaya-surabaya-vs-arema-fc-1785855352715_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Pelatih Prioritaskan Kejuaraan Dunia dan Asian Games untuk Fajar/Fikri</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:50:30 +0700</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>PBSI menegaskan Kejuaraan Dunia dan Asian Games 2026 menjadi prioritas utama Fajar Alfian/Muhammad Shohibul Fikri.</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8605810/pelatih-prioritaskan-kejuaraan-dunia-dan-asian-games-untuk-fajar-fikri</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/25/fajar-alfianmuhammad-shohibul-fikri-1784957443929_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Heboh Jadon Sancho Latihan di Tim Divisi ke-10 Inggris</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Serius bukan hoax. Jadon Sancho latihan di tim divisi ke-10 Inggris, Flixton FC untuk jaga kebugaran. Sang winger masih belum punya klub baru.</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8605535/heboh-jadon-sancho-latihan-di-tim-divisi-ke-10-inggris</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/04/jadon-sancho_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Jenazah Korban Kebakaran KM Mutiara Sentosa 2 Asal Agam Tiba di Sumbar, Langsung Diserahkan ke Keluarga</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:42:51 +0700</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Jenazah korban kebakaran KM Mutiara Sentosa 2 asal Agam, Sumbar, tiba di Bandara Internasional Minangkabau (BIM) dan diserahkan ke keluarga.</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/194009778/jenazah-korban-kebakaran-km-mutiara-sentosa-2-asal-agam-tiba-di-sumbar</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/f7RS8n9kLHP-sMP5Gaw2TqwfV_M=/115x0:1195x720/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a732e48d06a5.jpeg</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Tawuran di Semarang Diduga Pakai Bom Molotov, Berlangsung 15 Menit dan Minim Saksi</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:42:53 +0700</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Polisi mengusut tawuran di Semarang yang diduga menggunakan bom molotov. Kejadian berlangsung 15 menit dan minim saksi.</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/192101678/tawuran-di-semarang-diduga-pakai-bom-molotov-berlangsung-15-menit-dan-minim</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Dd7svAsJGzn4qzjhKaKD5uCYThs=/0x0:750x500/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/06/21/68565084b1e38.jpeg</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>MPR Tetapkan Sidang Tahunan Digelar 14 Agustus 2026, Undang Presiden-Wapres Terdahulu</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:42:54 +0700</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>MPR menetapkan Sidang Tahunan dan Sidang Bersama DPR-DPD digelar 14 Agustus 2026. Presiden Prabowo Subianto akan berpidato kenegaraan dan sampaikan laporan kinerja.</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/05/19031051/mpr-tetapkan-sidang-tahunan-digelar-14-agustus-2026-undang-presiden-wapres</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/HmRWTiPcHgwoLz_OjyCqZ9YxbGI=/0x0:5568x3712/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2025/08/19/68a457189328a.jpg</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I345"/>
+  <autoFilter ref="A1:I457"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$457</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$559</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I457"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21913,8 +21913,4802 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Gubernur Sumut kembali berkantor di Nias guna percepat pembangunan</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:02:01 +0700</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Gubernur Sumatera Utara Bobby Nasution kembali berkantor di Kepulauan Nias sebagai wujud berkelanjutan pemerintah ...</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681629/gubernur-sumut-kembali-berkantor-di-nias-guna-percepat-pembangunan</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001032290.jpg</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>11 korban kebakaran KM Mutiara Sentosa II jalani perawatan medis</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:01:34 +0700</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>ANTARA - Dari total 238 korban kebakaran kapal penumpang KM Mutiara Sentosa II yang terevakuasi, sebelas orang di ...</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681625/11-korban-kebakaran-km-mutiara-sentosa-ii-jalani-perawatan-medis</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_11-KORBAN-KEBAKARAN-KM-MUTIARA-SENTOSA-II-JALANI-PERAWATAN-MEDIS.jpg</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Pemkot Solo siapkan kios bagi pedagang terdampak tutupnya PGS</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:01:32 +0700</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Solo menyiapkan kios dan los di sejumlah pasar tradisional bagi pedagang yang terdampak ...</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681600/pemkot-solo-siapkan-kios-bagi-pedagang-terdampak-tutupnya-pgs</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-SOLO-SIAPKAN-KIOS-BAGI-PEDAGANG-TERDAMPAK-TUTUPNYA-PGS.jpg</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Akademisi: Perlu ada sosialisasi dan evaluasi atas penerapan UU TPKS</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:00:39 +0700</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Akademisi dari Fakultas Hukum Universitas Katolik Parahyangan (Unpar) mengatakan perlu adanya sosialisasi dan evaluasi ...</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681627/akademisi-perlu-ada-sosialisasi-dan-evaluasi-atas-penerapan-uu-tpks</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000012935.jpg</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>KSP jelaskan alasan KDMP dibangun di kaki gunung Ciremai</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:56:56 +0700</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Staf Kepresidenan Dudung Abdurachman menyebut kehadiran Koperasi Desa Merah Putih atau KDMP di ...</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681552/ksp-jelaskan-alasan-kdmp-dibangun-di-kaki-gunung-ciremai</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-205638_1.jpg</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Indonesia jajaki peluang penempatan pekerja migran ke Slowakia</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:56:17 +0700</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (P2MI) menjajaki peluang perluasan penempatan pekerja migran Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681624/indonesia-jajaki-peluang-penempatan-pekerja-migran-ke-slowakia</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/405.jpg</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>SIG bidik penguatan pasar di Jawa Barat lewat Semen Kujang</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:53:49 +0700</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>PT Semen Indonesia (Persero) Tbk (SIG) memperkuat upaya dominasi pasar di Jawa Barat dengan menghadirkan kembali Semen ...</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681620/sig-bidik-penguatan-pasar-di-jawa-barat-lewat-semen-kujang</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-20.35.21.jpeg</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>KPK duga pejabat Kemenhut dapat 12.500 dolar Singapura dari Suhardiman</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:52:29 +0700</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi menduga pejabat di Kementerian Kehutanan mendapatkan penerimaan uang sebesar 12.500 dolar ...</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681619/kpk-duga-pejabat-kemenhut-dapat-12500-dolar-singapura-dari-suhardiman</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_7411.jpg</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>42 persen tiket terjual, MotoGP Indonesia 2026 dikemas lebih menarik</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:50:44 +0700</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>ANTARA - Penjualan tiket ajang balap motor bergengsi dunia, MotoGP seri Indonesia tahun 2026, mencatatkan ...</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681607/42-persen-tiket-terjual-motogp-indonesia-2026-dikemas-lebih-menarik</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_42-PERSEN-TIKET-TERJUAL-MOTOGP-INDONESIA-2026-DIKEMAS-LEBIH-MENARIK_1.jpg</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Pemprov DKI terima aset fasos-fasum senilai Rp2,27 triliun</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:47:56 +0700</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta menerima aset fasilitas sosial dan fasilitas umum (fasos/fasum) dari para ...</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681616/pemprov-dki-terima-aset-fasos-fasum-senilai-rp227-triliun</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000315242.jpg</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Kenapa pikiran selalu aktif saat mau tidur? Ini penyebab dan cara mengatasinya</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:47:44 +0700</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Tubuh sudah terasa lelah, mata mulai mengantuk, tetapi begitu berbaring di tempat tidur, pikiran justru semakin aktif. ...</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681613/kenapa-pikiran-selalu-aktif-saat-mau-tidur-ini-penyebab-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/15/banun.jpg</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Otto: Sistem kekayaan intelektual ideal beri manfaat sosial-ekonomi</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:47:14 +0700</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Koordinator Bidang Hukum, Hak Asasi Manusia, Imigrasi, dan Pemasyarakatan Otto Hasibuan mengatakan sistem ...</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681609/otto-sistem-kekayaan-intelektual-ideal-beri-manfaat-sosial-ekonomi</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000471686.jpg</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Pramono setuju modifikasi cuaca dilakukan dua kali sepekan</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:44:21 +0700</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta, Pramono Anung memberikan persetujuan untuk dilakukan operasi modifikasi cuaca (OMC) setiap satu ...</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681604/pramono-setuju-modifikasi-cuaca-dilakukan-dua-kali-sepekan</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000315232_1.jpg</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Pemkab Aceh Besar salurkan air bersih ke warga terdampak kekeringan</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:43:48 +0700</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>ANTARA - Kemarau yang melanda kabupaten Aceh Besar dalam beberapa pekan terakhir, menyebabkan pasokan air bersih ...</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681487/pemkab-aceh-besar-salurkan-air-bersih-ke-warga-terdampak-kekeringan</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKAB-ACEH-BESAR-SALURKAN-AIR-BERSIH-KE-WARGA-TERDAMPAK-KEKERINGAN.jpg</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Pembangunan MRT, Dishub DKI rekayasa lalin di kawasan Stasiun Kota</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:40:21 +0700</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Dinas Perhubungan (Dishub) DKI Jakarta menerapkan rekayasa lalu lintas di kawasan Stasiun Glodok dan Stasiun Kota ...</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681596/pembangunan-mrt-dishub-dki-rekayasa-lalin-di-kawasan-stasiun-kota</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/20/revitalisasi-stasiun-mrt-bundaran-hi-2775419.jpg</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Dudung: Koordinasi lintas sektor kunci penyelesaian program prioritas</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:40:18 +0700</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Kepala Staf Kepresidenan Jenderal TNI (Purn.) Dudung Abdurachman mengatakan koordinasi lintas sektor yang difasilitasi ...</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681595/dudung-koordinasi-lintas-sektor-kunci-penyelesaian-program-prioritas</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/482452.jpg</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya tak setuju gaji manajer KDKMP sebesar Rp16,25 juta</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:40:08 +0700</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>ANTARA - Beredar informasi di media sosial yang menyebut gaji manajer koperasi desa kelurahan merah putih (KDKMP) ...</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681512/menkeu-purbaya-tak-setuju-gaji-manajer-kdkmp-sebesar-rp1625-juta</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKEU-PURBAYA-TAK-SETUJU-GAJI-MANAJER-KDKMP-SEBESAR-RP16-25-JUTA.jpg</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Apa Itu sleep hygiene? Ini manfaat dan 10 cara menerapkannya agar tidur nyenyak</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:37:14 +0700</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Banyak orang mengira sulit tidur hanya disebabkan oleh stres atau terlalu banyak minum kopi. Padahal, kualitas tidur ...</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681593/apa-itu-sleep-hygiene-ini-manfaat-dan-10-cara-menerapkannya-agar-tidur-nyenyak</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/10/tidur.jpg</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Apple menduga banyak mantan karyawan bocorkan data rahasia ke OpenAI</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:36:39 +0700</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Apple menyatakan banyak mantan karyawannya diduga mengambil informasi rahasia perusahaan sebelum bergabung dengan ...</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681592/apple-menduga-banyak-mantan-karyawan-bocorkan-data-rahasia-ke-openai</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/thumbs_b_c_c48eb58d9c1e7c83fd91f3633ecd20ec.jpg</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Dubes Pakistan: RI punya peran penting dorong resolusi Kashmir</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:36:35 +0700</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Duta Besar Pakistan untuk Indonesia, Zahid Hafeez Chaudhri, menilai bahwa Indonesia memiliki peran penting bersama ...</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681589/dubes-pakistan-ri-punya-peran-penting-dorong-resolusi-kashmir</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000010449.jpg</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>KPK sebut saksi kasus KPP Banjarmasin kembalikan uang 530.000 dolar AS</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:36:15 +0700</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi menyatakan salah satu saksi dalam pengembangan kasus dugaan korupsi yang menjerat ...</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681585/kpk-sebut-saksi-kasus-kpp-banjarmasin-kembalikan-uang-530000-dolar-as</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/27/pemeriksaan-tersangka-kasus-korupsi-restitusi-pajak-2739814.jpg</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>KPK duga Menhut belum kembalikan seluruh uang Suhardiman Amby</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:33:20 +0700</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi menduga Menteri Kehutanan Raja Juli Antoni belum mengembalikan seluruh uang dalam amplop ...</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681581/kpk-duga-menhut-belum-kembalikan-seluruh-uang-suhardiman-amby</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/23/0e9984fc-378c-48cd-96a2-13ba508fcc3e.jpeg</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Menkum harap Rencana Induk KI Nasional 2027–2036 jadi PSN</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:33:15 +0700</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Menteri Hukum (Menkum) Supratman Andi Agtas mengharapkan Rencana Induk Kekayaan Intelektual (KI) Nasional ...</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681577/menkum-harap-rencana-induk-ki-nasional-2027-2036-jadi-psn</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000471680.jpg</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Sudinsos Jaksel distribusi 690 alat bantu fisik bagi warga yang butuh</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:31:31 +0700</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Suku Dinas Sosial Jakarta Selatan telah mendistribusikan sebanyak 690 alat bantu fisik kepada warga yang membutuhkan ...</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681576/sudinsos-jaksel-distribusi-690-alat-bantu-fisik-bagi-warga-yang-butuh</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001013673.jpg</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ASDP perkuat transformasi operasional lewat standar baru keselamatan</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:30:37 +0700</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>PT ASDP Indonesia Ferry (Persero) mengimplementasikan standar baru keselamatan melalui program sterilisasi pelabuhan ...</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681573/asdp-perkuat-transformasi-operasional-lewat-standar-baru-keselamatan</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-18.08.02.jpeg</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>7 cara mempersiapkan anak sambut kelahiran adik agar tidak cemburu</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:30:18 +0700</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Kehadiran anggota keluarga baru dapat menjadi momen bahagia sekaligus tantangan bagi anak pertama. Persiapan sejak dini ...</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681571/7-cara-mempersiapkan-anak-sambut-kelahiran-adik-agar-tidak-cemburu</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/15/pexels-migs-reyes-4205505.jpg</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Jumlah penduduk miskin di Jakarta 432 ribu orang pada Maret 2026</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:29:25 +0700</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) DKI Jakarta mengemukakan jumlah penduduk miskin di Jakarta sebanyak 432,62 ribu orang pada ...</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681568/jumlah-penduduk-miskin-di-jakarta-432-ribu-orang-pada-maret-2026</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000315200.jpg</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>KKP manfaatkan TKD untuk budi daya ikan tematik di DIY</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:24:44 +0700</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) akan meluncurkan Program Budi Daya Perikanan Tematik di 64 kalurahan ...</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681401/kkp-manfaatkan-tkd-untuk-budi-daya-ikan-tematik-di-diy</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-194302.jpg</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Sudinsos Jaksel jangkau 644 PPKS hingga Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:23:22 +0700</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Suku Dinas Sosial Jakarta Selatan mencatat telah menjangkau 644 Pemerlu Pelayanan Kesejahteraan Sosial (PPKS) sepanjang ...</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681565/sudinsos-jaksel-jangkau-644-ppks-hingga-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001013669.jpg</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Posisi tidur yang baik untuk kesehatan, mana yang paling dianjurkan?</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:21:18 +0700</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Tidur merupakan waktu bagi tubuh untuk memulihkan energi dan memperbaiki berbagai fungsi penting. Namun, selain durasi ...</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681564/posisi-tidur-yang-baik-untuk-kesehatan-mana-yang-paling-dianjurkan</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/atur.jpg</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Argentina sesalkan Brasil menurunkan tingkat hubungan diplomatik</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:21:06 +0700</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Argentina pada Selasa (4/8) menyatakan penyesalannya atas keputusan Brasil yang menurunkan hubungan diplomatik ...</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681563/argentina-sesalkan-brasil-menurunkan-tingkat-hubungan-diplomatik</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000023_20260805_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Menbud nilai perancang busana mampu promosikan wastra Indonesia</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:19:55 +0700</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan Fadli Zon menilai perancang busana mampu mempromosikan wastra Indonesia, termasuk batik, kepada ...</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681561/menbud-nilai-perancang-busana-mampu-promosikan-wastra-indonesia</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-04-at-05.45.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>PN gelar sidang praperadilan Febrie Adriansyah pada 18-19 Agustus</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:19:35 +0700</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Pengadilan Negeri (PN) Jakarta Selatan menjadwalkan sidang perdana dua gugatan praperadilan yang diajukan mantan Jaksa ...</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681557/pn-gelar-sidang-praperadilan-febrie-adriansyah-pada-18-19-agustus</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001013665.jpg</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Polres Cilegon siapkan kantong parkir tertibkan truk tambang</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:19:03 +0700</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>ANTARA - Polres Cilegon menyiapkan kantong parkir untuk menampung truk angkutan tambang yang melanggar jam operasional ...</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681476/polres-cilegon-siapkan-kantong-parkir-tertibkan-truk-tambang</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-203312.jpg</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Pemprov Jabar ubah skema layanan BRT hemat anggaran Rp10 miliar</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:16:11 +0700</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Jawa Barat mengubah skema pengelolaan layanan Bus Rapid Transit (BRT) Metro Jabar Trans ...</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681535/pemprov-jabar-ubah-skema-layanan-brt-hemat-anggaran-rp10-miliar</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PEMPROV-JABAR-UBAH-SKEMA-LAYANAN-BRT-HEMAT-ANGGARAN-RP10-MILIAR.jpg</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Menteri PPPA tekankan pentingnya pesantren ramah santri</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:16:00 +0700</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Pemberdayaan Perempuan dan Perlindungan Anak (PPPA) Arifatul Choiri Fauzi di Malang, Jawa Timur, Rabu ...</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681448/menteri-pppa-tekankan-pentingnya-pesantren-ramah-santri</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-201229.jpg</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Wamendagri minta daerah bangun ekosistem Koperasi Merah Putih</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:14:37 +0700</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Dalam Negeri (Wamendagri) Bima Arya Sugiarto meminta kepala daerah membangun ekosistem Koperasi ...</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681548/wamendagri-minta-daerah-bangun-ekosistem-koperasi-merah-putih</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000580528.jpg</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Job Fair Kabupaten Bogor sediakan 6.056 lowongan kerja</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:13:55 +0700</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kabupaten Bogor menggelar Job Fair Kabupaten Bogor 2026 dengan menyediakan 6.056 lowongan kerja ...</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681523/job-fair-kabupaten-bogor-sediakan-6056-lowongan-kerja</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_JOB-FAIR-KABUPATEN-BOGOR-SEDIAKAN-6.056-LOWONGAN-KERJA.jpg</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Balsa Sekulic bertekad membawa Persib juara Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:13:21 +0700</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Striker Persib Bandung Balsa Sekulic bertekad membawa timnya menjuarai Piala Presiden 2026 meski harus menghadapi ...</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681547/balsa-sekulic-bertekad-membawa-persib-juara-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG-20260805-WA0008_2.jpg</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya gagalkan peredaran empat kilogram ganja di Jakbar</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:13:06 +0700</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Direktorat Reserse Narkoba Polda Metro Jaya kembali berhasil menggagalkan peredaran narkotika jenis ganja seberat ...</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681543/polda-metro-jaya-gagalkan-peredaran-empat-kilogram-ganja-di-jakbar</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_203415.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Electronic Arts resmi diakuisisi Arab Saudi senilai Rp982 triliun</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:12:25 +0700</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Perusahaan gim Electronic Arts (EA) yang dikenal sebagai pencipta gim EA FC dan The Sims resmi menjadi perusahaan ...</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681540/electronic-arts-resmi-diakuisisi-arab-saudi-senilai-rp982-triliun</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000141394.jpg</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Mendagri: perbaikan fasum Padang akibat banjir gunakan dana presiden</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:12:06 +0700</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Dalam Negeri Tito Karnavian mengusulkan agar pemerintah daerah dapat memanfaatkan dana tambahan ...</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681492/mendagri-perbaikan-fasum-padang-akibat-banjir-gunakan-dana-presiden</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-204650.jpg</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Menteri PPPA: Nilai agama hingga etika lindungi tumbuh kembang anak</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:11:50 +0700</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Menteri Pemberdayaan Perempuan dan Perlindungan Anak (PPPA) Arifah Fauzi menyatakan penanaman nilai agama, budi ...</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681539/menteri-pppa-nilai-agama-hingga-etika-lindungi-tumbuh-kembang-anak</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001400813.jpg</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Bendera raksasa dikibarkan, Bogor gaungkan semangat nasionalisme</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:10:33 +0700</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>ANTARA - Menjelang HUT ke-81 Kemerdekaan RI, Pemerintah Kabupaten Bogor mengibarkan bendera Merah Putih berukuran 30 x ...</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681461/bendera-raksasa-dikibarkan-bogor-gaungkan-semangat-nasionalisme</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-202347.jpg</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>KPK sita 150.000 dolar AS terkait pengembangan kasus KPP Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:09:57 +0700</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi menyita uang tunai senilai 150.000 dolar AS dari penggeledahan di dua lokasi terkait ...</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681532/kpk-sita-150000-dolar-as-terkait-pengembangan-kasus-kpp-banjarmasin</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/15/pemeriksaan-tersangka-dian-jaya-demega-2772685.jpg</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Sudinhub Jakut tindak puluhan motor yang parkir liar di Sunter Agung</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:07:59 +0700</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Suku Dinas Perhubungan (Sudinhub) Jakarta Utara menindak tegas puluhan motor yang kedapatan parkir secara liar di ...</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681528/sudinhub-jakut-tindak-puluhan-motor-yang-parkir-liar-di-sunter-agung</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-20.26.54.jpeg</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Persebaya tak gentar hadapi Persib di final Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:07:38 +0700</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Pemain Persebaya Surabaya Francisco Rivera mengungkapkan timnya sudah siap menghadapi Persib Bandung pada final Piala ...</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681524/persebaya-tak-gentar-hadapi-persib-di-final-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG-20260805-WA0005.jpg</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Pemkab Bangka Barat perkuat ekonomi desa melalui Sekolah BUMDesa</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:06:16 +0700</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten (Pemkab) Bangka Barat, Provinsi Kepulauan Bangka Belitung (Babel), berupaya memperkuat ekonomi ...</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681520/pemkab-bangka-barat-perkuat-ekonomi-desa-melalui-sekolah-bumdesa</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_162408.jpg</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Satgas PRR minta 16 K/L segera eksekusi program rehab-rekon</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:04:30 +0700</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Muhammad Tito Karnavian selaku Ketua Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi ...</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681515/satgas-prr-minta-16-k-l-segera-eksekusi-program-rehab-rekon</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000580507.jpg</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Jumlah pengangguran di Jakarta turun 10 ribu orang pada Mei 2026</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:01:27 +0700</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) DKI Jakarta mencatat jumlah pengangguran di ibu kota mengalami penurunan 10 ribu orang pada ...</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681509/jumlah-pengangguran-di-jakarta-turun-10-ribu-orang-pada-mei-2026</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000315189.jpg</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>200 museum dan cagar budaya akan direvitalisasi, langkah Sumut diapresiasi</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:58:58 +0700</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan Fadli Zon mengatakan bahwa pada tahun ini pihaknya akan merevitalisasi hampir 200 museum dan ...</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681500/200-museum-dan-cagar-budaya-akan-direvitalisasi-langkah-sumut-diapresiasi</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/18/penunjukan-pelaksana-tugas-pengelolaan-keraton-kasunanan-solo-2707786.jpg</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>KSP pastikan kesiapan operasional Sekolah Rakyat Terintegrasi Bandung</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:19:29 +0700</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Kantor Staf Presiden (KSP) melakukan verifikasi lapangan guna memastikan kesiapan operasional Sekolah Rakyat ...</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681449/ksp-pastikan-kesiapan-operasional-sekolah-rakyat-terintegrasi-bandung</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0966.jpg</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>BP BUMN-Kemenkeu bahas relaksasi perpajakan untuk transformasi BUMN</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:06:16 +0700</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pengaturan (BP) BUMN sekaligus COO Danantara Dony Oskaria bertemu Menteri Keuangan Purbaya Yudhi ...</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681429/bp-bumn-kemenkeu-bahas-relaksasi-perpajakan-untuk-transformasi-bumn</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/COO-Danantara-temui-Menteri-Keuangan-050826-Bay-1.jpg</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Staf RSUD di Tasik Terancam Disanksi Gegara Ikut Nyinyir ke Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:05:04 +0700</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Faizal Amiruddin</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Seorang pegawai RSUD dr Soekardjo Tasikmalaya terancam sanksi setelah berkomentar kasar tentang pasien BPJS. Pihak rumah sakit sedang menindaklanjuti kasus ini.</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606160/staf-rsud-di-tasik-terancam-disanksi-gegara-ikut-nyinyir-ke-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/11/rsud-dr-soekardjo-tasikmalaya-1781150055801_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Gempa M 5,3 Terjadi di Pangandaran</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:03:43 +0700</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Lisye Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Gempa bumi dengan magnitudo (M) 5,3 terjadi di Pangandaran, Jawa Barat. Gempa ada pada kedalaman 18 kilometer.</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606157/gempa-m-5-3-terjadi-di-pangandaran</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Belasan Pekerja Dapur MBG di Bima Diduga Terpapar Hepatitis</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:02:21 +0700</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Rafiin</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Belasan relawan dapur Makan Bergizi Gratis di Bima diduga terinfeksi hepatitis. Puskesmas menemukan 15 orang reaktif setelah skrining kesehatan.</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606155/belasan-pekerja-dapur-mbg-di-bima-diduga-terpapar-hepatitis</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/27/32-ribu-pegawai-inti-mbg-bakal-diangkat-jadi-asn-pppk-1769488598657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Ekspedisi Merah Putih Hadirkan Nasionalisme, Cinta Alam &amp;amp; Ceria di Ujung Siak</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:59:48 +0700</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Tim Ekspedisi Merah Putih Polda Riau jangkau Kampung Teluk Lanus, menanam 1.000 mangrove, dan memberikan bansos serta peralatan sekolah untuk masyarakat.</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606152/ekspedisi-merah-putih-hadirkan-nasionalisme-cinta-alam-ceria-di-ujung-siak</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ekspedisi-merah-putih-jangkau-ujung-siak-menanam-1000-mangrove-dan-menyerahkan-bansos-kepada-masyarakat-1785941846802_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Ekspedisi Merah Putih Hadirkan Nasionalisme, Cinta Alam &amp;amp; Ceria di Ujung Siak</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:59:48 +0700</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Tim Ekspedisi Merah Putih Polda Riau menanam 1.000 mangrove, menyerahkan bansos di Kampung Teluk Lanus, meningkatkan semangat nasionalisme dan cinta alam.</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/melindungi-tuah-marwah/d-8606159/ekspedisi-merah-putih-hadirkan-nasionalisme-cinta-alam-ceria-di-ujung-siak</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ekspedisi-merah-putih-jangkau-ujung-siak-menanam-1000-mangrove-dan-menyerahkan-bansos-kepada-masyarakat-1785941846802_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Kemensos Tangguhkan 1,49 Juta Penerima Bansos Terindikasi Judi Online</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:46:55 +0700</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Kemensos tangguhkan 1.494.652 Keluarga Penerima Manfaat Program Sembako yang terindikasi judi online. Proses verifikasi dilakukan untuk memastikan kelayakan.</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606144/kemensos-tangguhkan-1-49-juta-penerima-bansos-terindikasi-judi-online</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemensos-tangguhkan-149-juta-penerima-bansos-terindikasi-judi-online-1785941114903_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>BPS Sebut Jumlah Orang Terserap Pasar Kerja Meningkat di Mei 2026</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:45:43 +0700</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>BPS melaporkan jumlah penduduk bekerja Mei 2026 mencapai 148,19 juta, meningkat 522 ribu. Sektor Akomodasi dan Makan Minum jadi penyerap tenaga kerja terbanyak.</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606075/bps-sebut-jumlah-orang-terserap-pasar-kerja-meningkat-di-mei-2026</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/kepala-bps-amalia-adininggar-widyasanti-1777954089390_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Mahasiswi PPDS Diduga Hina Pasien BPJS 'Orang Have', UGM Turun Tangan</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:43:00 +0700</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Serly Putri Jumbadi</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Viral komentar nyinyir mahasiswi UGM, Elda Putri, terkait pasien BPJS Kesehan. UGM investigasi dan sanksi akan dijatuhkan jika terbukti bersalah.</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606140/mahasiswi-ppds-diduga-hina-pasien-bpjs-orang-have-ugm-turun-tangan</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/15/ilustrasi-kamar-rumah-sakit_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap 3 Anggota Ormas Hendak Rebut Ruko Warga di Surabaya</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:25:37 +0700</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Aprilia Devi</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Polisi amankan tiga anggota ormas terkait penyerobotan ruko di Surabaya. Sementara pelaku lain masih diburu.</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606131/polisi-tangkap-3-anggota-ormas-hendak-rebut-ruko-warga-di-surabaya</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Waka MPR Ungkap Pentingnya Kolaborasi Pengelolaan Warisan Budaya</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:16:43 +0700</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Lestari Moerdijat menekankan pentingnya pelestarian warisan budaya. Kolaborasi pemerintah dan masyarakat penting dalam menjaga aset budaya.</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606119/waka-mpr-ungkap-pentingnya-kolaborasi-pengelolaan-warisan-budaya</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/03/03/lestari-moerdijat.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Hujan Buatan Jadi Harapan Saat Kemarau Berkepanjangan</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:13:26 +0700</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Haris Fadhil</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Kemarau telah memicu kekeringan di berbagai daerah di Indonesia. Kini, hujan buatan menjadi salah satu harapan untuk mengatasi kekeringan.</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606115/hujan-buatan-jadi-harapan-saat-kemarau-berkepanjangan</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/kemarau-ancam-ribuan-hektare-sawah-di-bekasi-kekeringan-berpotensi-meluas-1785576721983_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Kembangkan Kewirausahaan, Gubernur Sumsel Gagas Kampus Sekolah Ekspor</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:09:45 +0700</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Gubernur Sumsel luncurkan Kampus Sekolah Ekspor, kampus outdoor pertama di Indonesia, untuk dorong kewirausahaan dan pengusaha muda berorientasi ekspor.</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606103/kembangkan-kewirausahaan-gubernur-sumsel-gagas-kampus-sekolah-ekspor</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kembangkan-kewirausahaan-gubernur-sumsel-gagas-kampus-sekolah-ekspor-1785938837794_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>DLH Bogor Identifikasi Perusahaan Diduga Bikin Air Kali Bekasi Hitam Bak Oli</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:04:36 +0700</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Dinas LH Kabupaten Bogor uji laboratorium dan susur sungai terkait pencemaran air hitam di Sungai Cileungsi. Perusahaan terancam sanksi jika terbukti bersalah.</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606093/dlh-bogor-identifikasi-perusahaan-diduga-bikin-air-kali-bekasi-hitam-bak-oli</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/video-air-kali-bekasi-berwarna-hitam-mirip-oli-bekas-viral-di-media-sosial-medsos-kualitas-air-tersebut-menurun-karena-ada-dug-1785929406139_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Pemerintah Bakal Tindak Lanjuti Dugaan Keracunan Makanan di Jayapura</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:02:21 +0700</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulias</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk menegaskan perhatian pemerintah terhadap dugaan keracunan makanan di Jayapura. Tim akan turun untuk verifikasi dan evaluasi situasi.</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606089/pemerintah-bakal-tindak-lanjuti-dugaan-keracunan-makanan-di-jayapura</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/wakil-menteri-dalam-negeri-wamendagri-ribka-haluk-1785938501104.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Israel Gempur Lebanon Selatan, Tuduh Hizbullah Langgar Gencatan Senjata</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:01:12 +0700</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Lisye Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Militer Israel menyerang target di Lebanon selatan, menuduh Hizbullah melanggar gencatan senjata. Warga diminta mengungsi.</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606087/israel-gempur-lebanon-selatan-tuduh-hizbullah-langgar-gencatan-senjata</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/lebanon-israel-iran-us-war-1785938380565_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Latihan Gabungan TNI 2026 Peragakan Kemampuan Tempur Tiga Matra</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:56:06 +0700</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Grandyos Zafna</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>TNI menggelar Operasi Terintegrasi 2026 di Kepulauan Riau dengan simulasi tempur tiga matra yang melibatkan rudal, drone, dan pasukan marinir.</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8605344/latihan-gabungan-tni-2026-peragakan-kemampuan-tempur-tiga-matra</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/latihan-operasi-tni-terintegrasi-2026-1785913841495.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>KPK Geledah 2 Rumah Kasus Suap Pajak Banjarmasin, Amankan USD 150 Ribu</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:54:12 +0700</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>KPK menggeledah Kantor Pajak Pratama Banjarmasin, Bandung, dan Tangerang, menyita total USD 150 ribu terkait kasus korupsi restitusi pajak.</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606077/kpk-geledah-2-rumah-kasus-suap-pajak-banjarmasin-amankan-usd-150-ribu</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/12/jubir-kpk-budi-prasetyo-1778596449122_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Viral Anak Curhat Ibunya Meninggal Usai Ditolak Masuk IGD RS di Lampung</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:40:08 +0700</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Tommy Saputra</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Viral curhatan anak tentang ibunya yang diduga ditolak di IGD RSUDAM Lampung, kini ibu tersebut meninggal. RSUDAM bantah penolakan dan akan lakukan evaluasi.</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606065/viral-anak-curhat-ibunya-meninggal-usai-ditolak-masuk-igd-rs-di-lampung</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/11/ilustrasi-rumah-sakit_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>10 Hari Dirawat di RS, Istri Korban Pembunuhan Sekeluarga di Palu Meninggal</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:39:12 +0700</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Rangga Musabar</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Nurhanisa, istri Jamil yang menjadi korban pembunuhan di Palu, meninggal setelah 10 hari perawatan.</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606063/10-hari-dirawat-di-rs-istri-korban-pembunuhan-sekeluarga-di-palu-meninggal</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/pembunuhan-satu-keluarga-di-jalan-pdam-kelurahan-duyu-kecamatan-tatanga-kota-palu-1785135255984_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>BPS RI &amp;amp; MOSPI India Tandatangani Kerja Sama untuk Penguatan Statistik</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:37:07 +0700</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Kepala BPS RI Amalia Adininggar menghadiri pertemuan NSO BRICS di India, menandatangani LOI dengan India untuk kolaborasi statistik dan pengembangan digital.</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606061/bps-ri-mospi-india-tandatangani-kerja-sama-untuk-penguatan-statistik</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bps-ri-mospi-india-tandatangani-kerja-sama-untuk-penguatan-statistik-1785936933919_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Mendagri Minta Walkot Pakai Rp 200 M Perbaiki Saluran Air Imbas Banjir Padang</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:36:07 +0700</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Mendagri Tito memastikan penanganan banjir di Kota Padang. Dia juga meminta Wali Kota Padang memanfaatkan anggaran untuk membenahi infrastruktur imbas banjir.</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606058/mendagri-minta-walkot-pakai-rp-200-m-perbaiki-saluran-air-imbas-banjir-padang</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-tito-karnavian-eva-safitridetikcom-1785920328767_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Program JKN Jadi Penopang Harapan Herna di Balik Rutinitas Cuci Darah</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:30:42 +0700</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Herna Sumiratna, pasien hemodialisis, bersyukur atas dukungan Program JKN yang jamin biaya pengobatan. Ia berharap program ini terus berlanjut untuk masyarakat.</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606051/program-jkn-jadi-penopang-harapan-herna-di-balik-rutinitas-cuci-darah</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/jkn-menjadi-penopang-harapan-herna-di-balik-rutinitas-cuci-darah-1785936544109_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Yang Diketahui soal Rencana AS Tutup Konsulat di Medan</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:13:07 +0700</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>AS akan menutup lima misi diplomatik asing, termasuk Konsulat Jenderal AS di Medan, Indonesia. Kebijakan ini menjadi hal yang jarang terjadi. Apa alasannya?</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606027/yang-diketahui-soal-rencana-as-tutup-konsulat-di-medan</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/01/19/ribuan-bendera-as-meriahkan-pelantikan-joe-biden-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Menko Polkam Minta TNI-Polri Tingkatkan Patroli Cegah Warga Main Hakim Sendiri</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:11:01 +0700</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago menyoroti aksi warga main hakim sendiri. Ia minta peningkatan patroli TNI-Polri untuk pencegahan konflik.</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606024/menko-polkam-minta-tni-polri-tingkatkan-patroli-cegah-warga-main-hakim-sendiri</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/menko-polkam-pastikan-situasi-nasional-terkendali-minta-masyarakat-tak-terpengaruh-hoaks-1785916804844_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>136 Siswa hingga Kepala Sekolah SMPN 5 Rembang Alami Diare Massal</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:10:31 +0700</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Mukhammad Fadlil</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Sebanyak 136 siswa di SMP Negeri 5 Rembang dilaporkan mengalami diare. Sejumlah guru dan tenaga tata usaha (TU) juga mengalami keluhan serupa.</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606023/136-siswa-hingga-kepala-sekolah-smpn-5-rembang-alami-diare-massal</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/keracunan-mbg-1785927316244_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Saksi Kasus Suap Eks Kepala Kantor Pajak Banjarmasin Kembalikan Duit Rp 9,5 M</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:47:30 +0700</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>KPK periksa saksi dalam kasus korupsi pajak di Banjarmasin. Saksi kembalikan uang Rp 9,5 miliar.</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605991/saksi-kasus-suap-eks-kepala-kantor-pajak-banjarmasin-kembalikan-duit-rp-9-5-m</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Wamendagri Minta Pemda Papua Pastikan Penyaluran Dana Otsus Tepat Waktu</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:45:26 +0700</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk mendorong pemerintah daerah di Papua untuk segera menyelesaikan penyaluran Dana Otsus Tahap II 2026 secara akuntabel dan tepat waktu.</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605970/wamendagri-minta-pemda-papua-pastikan-penyaluran-dana-otsus-tepat-waktu</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/wamendagri-minta-pemda-papua-pastikan-penyaluran-dana-otsus-tepat-waktu-1785932810840_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Dukung Industri Kecantikan RI, IndoBeauty Expo 2026 Resmi Dibuka</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:42:15 +0700</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>IndoBeauty Expo 2026 resmi dibuka, menjadi platform strategis bagi industri kecantikan. Pameran ini mendorong inovasi, kolaborasi, dan peluang bisnis global.</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606045/dukung-industri-kecantikan-ri-indobeauty-expo-2026-resmi-dibuka</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/07/indobeauty-expo-2025-1754548154322.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Wanita Dilecehkan di KRL Tujuan Depok, KCI Akan Tindak Pelanggar</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:38:11 +0700</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Seorang wanita diduga menjadi korban pelecehan seksual di dalam KRL rute Jakarta Kota-Depok oleh seorang pria. KCI akan menindak pelaku pelecehan.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605985/wanita-dilecehkan-di-krl-tujuan-depok-kci-akan-tindak-pelanggar</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/30/ilustrasi-kereta-rel-listrik-krl-dok-kci_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Korlantas Polri Catat Korban Tewas Laka Lantas Semester I Turun 22,92 Persen</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:31:00 +0700</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Herianto Batubara</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Satu bulan sejak kepemimpinan Kakorlantas Polri Irjen Wibowo, kinerja keselamatan lalu lintas menunjukkan tren positif.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605979/korlantas-polri-catat-korban-tewas-laka-lantas-semester-i-turun-22-92-persen</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kakorlantas-polri-irjen-wibowo-1785932835877_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>DPD Undang JK Hadiri Sidang Tahunan: Kumpulkan Tokoh Bangsa</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:45:24 +0700</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Ketua DPD Sultan Najamudin mengundang Jusuf Kalla untuk hadir dalam Sidang Tahunan MPR pada 14 Agustus, menyambut HUT RI ke-81.</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8605927/dpd-undang-jk-hadiri-sidang-tahunan-kumpulkan-tokoh-bangsa</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ketua-dpd-memberikan-undangan-sidang-tahunan-mpr-ke-jk-1785930226552_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Dapur MBG Wajib Urus SLHS Paling Lambat 10 Agustus atau Tutup Permanen!</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:24:13 +0700</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>BGN mewajibkan semua Satuan Pelayanan Pemenuhan Gizi (SPPG) atau dapur program Makan Bergizi Gratis (MBG) memiliki Sertifikat Laik Higiene Sanitasi (SLHS)</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606129/dapur-mbg-wajib-urus-slhs-paling-lambat-10-agustus-atau-tutup-permanen</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/27/32-ribu-pegawai-inti-mbg-bakal-diangkat-jadi-asn-pppk-1769488598601_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Fundamental Solid, Ekonomi Indonesia Triwulan II-2026 Tumbuh 5,29%</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:55:50 +0700</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Ekonomi Indonesia tumbuh 5,29% pada triwulan 2-2026, didorong konsumsi rumah tangga dan industri pengolahan. Fundamental ekonomi tetap solid.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606079/fundamental-solid-ekonomi-indonesia-triwulan-ii-2026-tumbuh-5-29</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/kepala-bps-amalia-adininggar-widyasanti-1777954089390.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Satu Keluarga Keracunan MBG, Kepala BGN Ungkap Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:45:21 +0700</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN), Sudaryono mengungkap kasus keracunan Makan Begizi Gratis (MBG) yang menimpa satu keluarga.</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606069/satu-keluarga-keracunan-mbg-kepala-bgn-ungkap-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Beberapa Pabrik China Bakal Pindah ke Madura</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:09:33 +0700</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Beberapa pabrik asal China berencana direlokasi ke Kawasan Industri Madura di Bangkalan, Jawa Timur.</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8606022/beberapa-pabrik-china-bakal-pindah-ke-madura</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/07/31/ilustrasi-wanita-bekerja-di-pabrik_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Gaya Cristiano Ronaldo Jadi Pemilik Klub Spanyol</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Ronaldo nonton laga uji coba Al Nassr kontra Almeria di Portugal. Ronaldo menyaksikan dari tribune, dirinya adalah pemilik dari klub divisi dua Spanyol itu.</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/gila-bola/d-8605877/gaya-cristiano-ronaldo-jadi-pemilik-klub-spanyol</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/cristiano-ronaldo-almeria-1785914387259_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Bagaimana Nasib Mudryk di Chelsea? Ini Jawaban Xabi Alonso</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:45:35 +0700</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Mykhailo Mudryk sudah balik ke skuad Chelsea, ikut latihan di tur pramusim. Apa The Blues butuh tenaga sang winger, Xabi Alonso?</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8605875/bagaimana-nasib-mudryk-di-chelsea-ini-jawaban-xabi-alonso</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/25/myhailo-mudryk.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Audisi Umum PB Djarum 2026 Makassar Diikuti Peserta dari Berbagai Provinsi</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:35:30 +0700</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Audisi Umum PB Djarum 2026 berlangsung di Makassar, Sulawesi Selatan. Terakhir kali Kota Daeng disambangi terjadi satu dekade yang lalu.</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8605961/audisi-umum-pb-djarum-2026-makassar-diikuti-peserta-dari-berbagai-provinsi</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/bulutangkis-1785932121424_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Panitia soal Jadwal Padat Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:30:50 +0700</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Panitia Piala Presiden 2026 menjelaskan alasan penerapan jadwal padat. Ditegaskan bahwa turnamen pramusim ini bukan kompetisi di bawah naungan FIFA.</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606078/panitia-soal-jadwal-padat-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Yordania Merasa Sedang Diperas FIFA</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Presiden Asosiasi Sepakbola Yordania (JFA), Pangeran Ali bin Al Hussein, melontarkan kritik keras terhadap Presiden FIFA Gianni Infantino.</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8605871/yordania-merasa-sedang-diperas-fifa</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/fifa-logo-1784182664720_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Muaythai Naik Kelas, Menpora Puji Ketum PBMI</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:08:07 +0700</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Menteri Pemuda dan Olahraga (Menpora), Erick Thohir, memberikan apresiasi terhadap perkembangan Muaythai Indonesia.</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8606091/muaythai-naik-kelas-menpora-puji-ketum-pbmi</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/muaythai-1785938281839_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2 Pemain yang Mesti Direkrut Arsenal untuk Naik Level</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:00:40 +0700</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Arsenal disarankan untuk merekrut salah satu dari dua pemain oleh eks pemain Tottenham Hotspur, Toby Alderweireld. Lini depan The Gunners harus ditingkatkan.</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8605873/2-pemain-yang-mesti-direkrut-arsenal-untuk-naik-level</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/22/soccer-worldcup-bra-hti-1782126575886_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Piala AFF 2026: Singapura Jamu Indonesia Jelang HUT Kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:45:30 +0700</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Singapura menghadapi Indonesia pada laga penentuan Grup A Piala AFF 2026. The Lions menjamu Garuda dua hari jelang perayaan Hari Kemerdekaan.</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8605772/piala-aff-2026-singapura-jamu-indonesia-jelang-hut-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/12/26/egy-maulana-vikri-indonesia-vs-singapura_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Hasil Uji Coba Chelsea Vs Juventus: Bianconeri Menang 1-0</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:33:16 +0700</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Chelsea dan Juventus saling berhadapan di laga uji coba pramusim. Bianconeri yang berhasil menuntaskannya dengan kemenangan.</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606054/hasil-uji-coba-chelsea-vs-juventus-bianconeri-menang-1-0</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/uji-coba-1785936703617_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Hasil Uji Coba: City Kalahkan K-League All Stars, Inter dan Milan Imbang</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:11:40 +0700</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Manchester City mengalahkan K-League All Stars di laga uji coba. Sementara itu, laga Inter Milan melawan AC Milan berakhir imbang.</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606025/hasil-uji-coba-city-kalahkan-k-league-all-stars-inter-dan-milan-imbang</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/derby-milan-1785933385830_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Messi Donasi Rp1,7 Miliar untuk Korban Kebakaran Madrid</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:40:45 +0700</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Aksi amal dilakukan Lionel Messi untuk wilayah pedesaan di Madrid yang jadi korban kebakaran. Legenda Barcelona ini mengirim donasi senilai Rp1,7 miliar.</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/gila-bola/d-8605770/messi-donasi-rp1-7-miliar-untuk-korban-kebakaran-madrid</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/tangis-messi-usai-argentina-gagal-pertahankan-gelar-juara-dunia-1784505521511_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>373,6 Hektare Kavling Laut Temuan Kementerian, BP Batam Sebut Sedang Lakukan Verifikasi</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:18:41 +0700</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>BP Batam tengah melakukan verifikasi terkait follow up pernyataan Kementerian ATR/BPN terkait kavling laut Batam mencapai 373,6 hektar.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/221543678/3736-hektare-kavling-laut-temuan-kementerian-bp-batam-sebut-sedang-lakukan</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/zsbZJjf5cAtpRGhEEOWHKtmCLzs=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a730bb161773.jpg</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Sidang Korupsi Sudewo: Warga Pati Rela Berutang dan Habiskan Tabungan demi Mahar Perangkat Desa Rp 165 Juta</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:18:42 +0700</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Dia mengaku menjual perhiasan istrinya dan meminjam uang dari keluarga demi memenuhi permintaan uang Rp 165 juta untuk mengikuti seleksi perangkat.</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/05/213526378/sidang-korupsi-sudewo-warga-pati-rela-berutang-dan-habiskan-tabungan-demi</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/cKEvsm_2SpHUz6vBVfJKTS1KEcI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72e5cdb8810.jpg</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Terungkap Permintaan 'Aneh' Jared Leto Selama Syuting Film Tron: Ares</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:18:43 +0700</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Kebiasaan aneh Jared Leto saat syuting diungkap usai film dokumenternya jadi sorotan</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://entertainment.kompas.com/read/2026/08/05/210116766/terungkap-permintaan-aneh-jared-leto-selama-syuting-film-tron-ares</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/-brkW1MOHbYoZL3GlXnbAAHHkVA=/0x0:800x533/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2017/10/04/3868250227.jpg</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I457"/>
+  <autoFilter ref="A1:I559"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$559</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$605</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I559"/>
+  <dimension ref="A1:I605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -26707,8 +26707,2170 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Purbaya: Kemenkeu ambil alih kepemilikan 60 persen saham di Whoosh</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:52:43 +0700</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan Kementerian Keuangan (Kemenkeu) akan mengambil alih kepemilikan 60 ...</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681728/purbaya-kemenkeu-ambil-alih-kepemilikan-60-persen-saham-di-whoosh</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000716076.jpg</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>KAI hentikan perjalanan kereta api karena gempa magintudo 5.3</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:52:17 +0700</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) Daerah Operasi 2 Bandung, Jawa Barat, menghentikan perjalanan Kereta Api Siliwangi ...</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681725/kai-hentikan-perjalanan-kereta-api-karena-gempa-magintudo-53</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/cek-kereta.jpg</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Kejari Kabupaten Madiun musnahkan barang bukti 21 perkara pidana</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:49:47 +0700</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Kejaksaan Negeri (Kejari) Kabupaten Madiun, Jawa Timur memusnahkan barang bukti dari 21 perkara pidana yang telah ...</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681721/kejari-kabupaten-madiun-musnahkan-barang-bukti-21-perkara-pidana</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/kajari-mdn.jpg</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Menhut tegaskan perdagangan karbon tak komersialisasi taman nasional</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:49:43 +0700</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kehutanan Raja Juli Antoni di Jakarta, Rabu (5/8), menegaskan perdagangan karbon yang melibatkan hutan ...</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681715/menhut-tegaskan-perdagangan-karbon-tak-komersialisasi-taman-nasional</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENHUT-TEGASKAN-PERDAGANGAN-KARBON-TAK-KOMERSIALISASI-TAMAN-NASIONAL.jpg</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>CDC sebut Infeksi diare "eksplosif" merebak di 47 negara bagian AS</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:48:05 +0700</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Infeksi Siklosporiasis yang dapat menyebabkan diare "eksplosif" telah dilaporkan di 47 dari 50 negara bagian ...</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681719/cdc-sebut-infeksi-diare-eksplosif-merebak-di-47-negara-bagian-as</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>IPR: Masyarakat jangan terpancing soal konten hoaks aksi demonstrasi</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Direktur Indonesia Political Review (IPR) Iwan Setiawan mengajak masyarakat untuk tidak mudah terpancing oleh konten ...</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681717/ipr-masyarakat-jangan-terpancing-soal-konten-hoaks-aksi-demonstrasi</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/17/WhatsApp-Image-2026-07-17-at-18.02.04.jpeg</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Jabar jaga program prioritas di tengah defisit APBD</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:35:39 +0700</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Jawa Barat bersama DPRD Jawa Barat menyiapkan skema pinjaman daerah hingga Rp3,4 triliun ...</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681713/jabar-jaga-program-prioritas-di-tengah-defisit-apbd</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/JABAR-JAGA-PROGRAM-PRIORITAS-DI-TENGAH-DEFISIT-APBD.jpg</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Empat awak terluka dalam serangan terhadap kapal di Laut Hitam</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:29:13 +0700</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebuah kapal kargo milik perusahaan pelayaran Turki dilaporkan diserang drone saat berlayar di Laut Hitam, ...</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681415/empat-awak-terluka-dalam-serangan-terhadap-kapal-di-laut-hitam</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-195245.jpg</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Program sejuta vaksin HPV sasar ASN dan masyarakat di Sulteng</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:25:43 +0700</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>ANTARA - Program Nasional Sejuta Vaksin HPV di Palu, Sulawesi Tengah menyasar aparatur sipil negara (ASN) dan ...</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681697/program-sejuta-vaksin-hpv-sasar-asn-dan-masyarakat-di-sulteng</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PROGRAM-SEJUTA-VAKSIN-HPV-SASAR-ASN-DAN-MASYARAKAT-DI-SULTENG.jpg</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Hadiah juara 2, 3, dan 4 Piala Presiden 2026 naik Rp500 juta</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:19:53 +0700</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Ketua Steering Committee (SC) Piala Presiden 2026 Maruarar Sirait resmi menaikkan hadiah juara 2, 3 dan 4 sebesar Rp500 ...</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681709/hadiah-juara-2-3-dan-4-piala-presiden-2026-naik-rp500-juta</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG-20260805-WA0017_1.jpg</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Saba Fest 3 gali potensi seni anak sejak dini</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:17:54 +0700</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Kebudayaan Provinsi Sumatera Barat melalui unit pelaksana teknis daerah (UPTD) Taman Budaya ...</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681648/saba-fest-3-gali-potensi-seni-anak-sejak-dini</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_25_24_19.Still478.jpg</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>DJKA uji jembatan KA usai peningkatan jalur Jember–Kalisat</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:10:12 +0700</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>ANTARA - Direktorat Jenderal Perkeretaapian Kementerian Perhubungan melalui Balai Teknik Perkeretaapian Kelas I ...</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681667/djka-uji-jembatan-ka-usai-peningkatan-jalur-jember-kalisat</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_27_47_27.Still479.jpg</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Ditjenpas NTT semarakkan HUT RI untuk perkuat pembinaan warga binaan</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:07:45 +0700</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>ANTARA - Kantor Wilayah Direktorat Jenderal Pemasyarakatan Nusa Tenggara Timur menggelar rangkaian kegiatan HUT Ke-81 ...</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681653/ditjenpas-ntt-semarakkan-hut-ri-untuk-perkuat-pembinaan-warga-binaan</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_DITJENPAS-NTT-SEMARAKKAN-HUT-RI-UNTUK-PERKUAT-PEMBINAAN-WARGA-BINAAN.jpg</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>KSP pastikan kesiapan Sekolah Rakyat saat MPLS dimulai</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:05:47 +0700</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 560 siswa mengikuti Masa Pengenalan Lingkungan Sekolah (MPLS) di Sekolah Rakyat Terintegrasi 4 ...</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681649/ksp-pastikan-kesiapan-sekolah-rakyat-saat-mpls-dimulai</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KSP-PASTIKAN-KESIAPAN-SEKOLAH-RAKYAT-SAAT-MPLS-DIMULAI.jpg</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Menhut: 13 taman nasional jadi proyek percontohan pendanaan inovatif</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:57:28 +0700</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kehutanan  Raja Juli Antoni menyebut terdapat 13 taman nasional yang menjadi proyek percontohan ...</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681681/menhut-13-taman-nasional-jadi-proyek-percontohan-pendanaan-inovatif</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENHUT-13-TAMAN-NASIONAL-JADI-PROYEK-PERCONTOHAN-PENDANAAN-INOVATIF.jpg</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Hensa klarifikasi ke Ditjen Pajak buntut siniar undang Ferry Latuhihin</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:54:16 +0700</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Pengamat politik sekaligus pendiri Lembaga Survei KedaiKOPI Hendri Satrio (Hensa) memberikan klarifikasi perihal ...</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681705/hensa-klarifikasi-ke-ditjen-pajak-buntut-siniar-undang-ferry-latuhihin</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Zulkieflimansyah.jpg</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Italia dorong dialog soal Selat Hormuz terus berlanjut</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:52:20 +0700</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri (Menlu) Italia Antonio Tajani menekankan pentingnya dialog terkait Selat Hormuz dalam pembicaraan ...</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681701/italia-dorong-dialog-soal-selat-hormuz-terus-berlanjut</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/04/15/Menlu-Italia-Antonio-Tajani.jpg</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>MRT Jakarta kembangkan TOD untuk pertumbuhan ekonomi dan mobilitas perkotaan</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:51:46 +0700</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>PT MRT Jakarta terus mengembangkan kawasan berorientasi transit (Transit Oriented Development/TOD) ...</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681699/mrt-jakarta-kembangkan-tod-untuk-pertumbuhan-ekonomi-dan-mobilitas-perkotaan</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/22/Progres-pembangunan-MRT-Fase-2A-220726-fzn-9.jpg</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Brussels perpanjang status waspada kekeringan</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:46:48 +0700</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Otoritas di Brussels, Belgia, memperpanjang status waspada kekeringan level kuning menyusul terus menurunnya ...</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681695/brussels-perpanjang-status-waspada-kekeringan</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_59fbf283e2be22faf1b2d05596159eff.jpg</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Manufaktur lampaui ekonomi, Menperin: Industrialisasi di jalur tepat</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:44:14 +0700</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita menyatakan manufaktur triwulan II 2026 yang tumbuh 5,32 ...</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681693/manufaktur-lampaui-ekonomi-menperin-industrialisasi-di-jalur-tepat</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/3-1_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Purbaya: Babinsa-Bhabinkamtibmas tak dikerahkan untuk pemungutan pajak</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:41:48 +0700</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa menegaskan pemerintah tidak mengerahkan Bintara Pembina Desa (Babinsa) maupun dan ...</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681692/purbaya-babinsa-bhabinkamtibmas-tak-dikerahkan-untuk-pemungutan-pajak</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-15.09.52_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Timnas 3x3 putri fokus benahi ketahanan fisik menuju AG 2026</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:41:43 +0700</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Pelatih timnas bola basket 3x3 putri Indonesia Deny Sartika mengatakan para pemainnya akan fokus membenahi ketahanan ...</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681689/timnas-3x3-putri-fokus-benahi-ketahanan-fisik-menuju-ag-2026</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/1000455403.jpg</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>China berkomitmen bantu negara-negara Afrika untuk perangi Ebola</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:40:11 +0700</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Juru bicara Kementerian Luar Negeri China Lin Jian pada Selasa (4/8) mengatakan bahwa dengan wabah Ebola yang masih ...</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681685/china-berkomitmen-bantu-negara-negara-afrika-untuk-perangi-ebola</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000011_20260805_CBMFN0A001.jpeg</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Pria bersenjata ditangkap di Klub Golf Milik Trump</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:37:34 +0700</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Departemen Sheriff Wilayah Los Angeles mengatakan pada Selasa (4/8) bahwa mereka telah menyerahkan kasus seorang pria ...</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681683/pria-bersenjata-ditangkap-di-klub-golf-milik-trump</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/CjkinzN000024_20260805_CBMFN0A001.jpeg</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Kemenko Perekonomian nilai KI sumber pertumbuhan ekonomi masa depan</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:36:17 +0700</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Kementerian Koordinator (Kemenko) Bidang Perekonomian menilai kekayaan intelektual (KI) akan menjadi salah satu sumber ...</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681677/kemenko-perekonomian-nilai-ki-sumber-pertumbuhan-ekonomi-masa-depan</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000471691.jpg</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Wamenkop: Koperasi mampu kirim tenaga kerja profesional keluar negeri</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:34:12 +0700</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Koperasi (Wamenkop) Farida Farichah mengatakan koperasi mampu berperan dalam menyiapkan dan mengirim ...</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681675/wamenkop-koperasi-mampu-kirim-tenaga-kerja-profesional-keluar-negeri</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-19.09.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 diluncurkan, buah kerja sama Indonesia-China</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:33:31 +0700</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Perusahaan antariksa komersial China, STAR.VISION, berhasil meluncurkan satelit Oriental Smart Eye (OSE) ...</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681671/satelit-lampung-1-diluncurkan-buah-kerja-sama-indonesia-china</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/z_2.jpg</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>DLH Makassar ajak masyarakat olah sampah organik sistem komunal</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:33:14 +0700</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Lingkungan Hidup Kota Makassar mengajak masyarakat mengolah sampah organik melalui sistem komunal di ...</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681432/dlh-makassar-ajak-masyarakat-olah-sampah-organik-sistem-komunal</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-05-200329.jpg</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>China perketat kontrol ekspor "drone" ke AS</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:33:12 +0700</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>China mulai memperketat pengawasan ekspor pesawat nirawak (drone) dan barang dwiguna terkait ke Amerika ...</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681668/china-perketat-kontrol-ekspor-drone-ke-as</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/07/XxjpbeE000059_20260507_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>AS catat 10.000 lebih kasus infeksi siklosporiasis sejak Mei 2026</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:25:27 +0700</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Pusat Pengendalian dan Pencegahan Penyakit Amerika Serikat (CDC) mencatat lebih dari 10.000 kasus infeksi ...</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681663/as-catat-10000-lebih-kasus-infeksi-siklosporiasis-sejak-mei-2026</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Pengamat dorong ATPM perkuat strategi hadapi sensitivitas konsumen</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:24:58 +0700</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Pengamat Ekonomi Senior dari Perbanas, Josua Pardede menilai bahwa Agen Tunggal Pemegang Merek (ATPM) perlu ...</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5681660/pengamat-dorong-atpm-perkuat-strategi-hadapi-sensitivitas-konsumen</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/48fd4b05-978c-4c12-bcef-6adeace5984d.jpeg</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Chery resmi kenalkan Tiggo V di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:23:37 +0700</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>PT Chery Sales Indonesia (CSI) memperkenalkan mobil terbaru mereka Tiggo V pada ajang pameran otomotif ...</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5681657/chery-resmi-kenalkan-tiggo-v-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-22.01.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Polisi bantu kernet yang ditinggal sopir di Pelabuhan Tanjung Priok</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:20:12 +0700</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Kepolisian membantu seorang kernet bernama Akid, warga Cirebon, Jawa Barat yang kebingungan karena ditinggal ...</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681645/polisi-bantu-kernet-yang-ditinggal-sopir-di-pelabuhan-tanjung-priok</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-05-at-21.08.58.jpeg</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Otto: Kekayaan intelektual potensi harta RI yang mesti dioptimalkan</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:18:31 +0700</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Koordinator Bidang Hukum, HAM, Imigrasi, dan Pemasyarakatan Otto Hasibuan mengatakan kekayaan intelektual ...</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681643/otto-kekayaan-intelektual-potensi-harta-ri-yang-mesti-dioptimalkan</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000471688.jpg</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Kemenkeu ambil alih restrukturisasi utang dan pengelolaan kereta cepat</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:17:38 +0700</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>ANTARA -Proses penyelesaian restrukturisasi utang dan pengelolaan kereta cepat Jakarta-Bandung kini diambil alih oleh ...</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681633/kemenkeu-ambil-alih-restrukturisasi-utang-dan-pengelolaan-kereta-cepat</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_KEMENKEU-AMBIL-ALIH-RESTRUKTURISASI-UTANG-DAN-PENGELOLAAN-KERETA-CEPAT.jpg</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Pura-pura pesan makan, pria di Kebon Jeruk gasak hp penjaga warung</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:13:35 +0700</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Seorang pria mencuri handphone milik penjaga warung makan di Jalan Pahlawan, Kebon Jeruk, Jakarta Barat, dengan modus ...</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681639/pura-pura-pesan-makan-pria-di-kebonjeruk-gasak-hp-penjaga-warung</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/06/30/penurian-hape.jpg</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>PT MRT investasikan Rp300 miliar bangun pedestrian deck Dukuh Atas</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:08:06 +0700</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>PT MRT menginvestasikan anggaran sebesar Rp300 miliar lebih untuk membangun pedestrian deck Dukuh Atas yang akan ...</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681637/pt-mrt-investasikan-rp300-miliar-bangun-pedestrian-deck-dukuh-atas</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/202607311821-main.cropped_1785496880.jpg</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>KSAU dan CAF RAAF bermanuver gunakan pesawat tempur di Australia</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:07:29 +0700</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Kepala Staf TNI Angkatan Udara (KSAU) Marsekal TNI Mohamad Tonny Harjono bermanuver menggunakan pesawat tempur bersama ...</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681635/ksau-dan-caf-raaf-bermanuver-gunakan-pesawat-tempur-di-australia</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001559265.jpg</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Cuaca Cerah Dimanfaatkan Petani China untuk Olah Hasil Panen Cabai</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:00:49 +0700</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Grandyos Zafna</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Petani di Bozhou, China, memanfaatkan cuaca cerah musim panas untuk memanen, menjemur, dan menyiapkan cabai sebelum dipasarkan.</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8604880/cuaca-cerah-dimanfaatkan-petani-china-untuk-olah-hasil-panen-cabai</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/cuaca-cerah-dimanfaatkan-petani-china-untuk-olah-hasil-panen-cabai-1785898636641.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>BGN Bakal Bangun Dapur MBG di Wilayah Tinggi Stunting</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:27:45 +0700</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>BGN tengah memetakan wilayah dengan tingkat stunting tinggi dan tinggi sekali di Indonesia. Pemetaan dilakukan untuk menyediakan dapur Makan Bergizi Gratis.</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606180/bgn-bakal-bangun-dapur-mbg-di-wilayah-tinggi-stunting</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/usai-dilantik-sudaryono-langsung-pimpin-rapat-perdana-bersama-jajaran-bgn-1784718690795_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Ekonomi Kuartal II Tumbuh 5,29%, Purbaya Nilai Cukup Baik</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa buka suara merespons pertumbuhan ekonomi di kuartal II-2026.</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606174/ekonomi-kuartal-ii-tumbuh-5-29-purbaya-nilai-cukup-baik</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/toko-online-lega-pemerintah-tunda-pajak-final-05-persen-1785929270093_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Serapan Tenaga Kerja Tembus 1,45 Juta Orang di Tengah Badai PHK</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Jumlah serapan tenaga kerja sepanjang semester I 2026 tembus 1,45 juta orang.</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606145/serapan-tenaga-kerja-tembus-1-45-juta-orang-di-tengah-badai-phk</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/08/mengintip-pabrik-travo-karya-anak-bangsa-demi-kemudahan-akses-iistrik-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Muay Aerobik Nusantara Jadi Aset Intelektual PBMI</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Muay Aerobik Nusantara menjadi bagian dari aset intelektual Pengurus Besar Muaythai Indonesia (PBMI)</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8606128/muay-aerobik-nusantara-jadi-aset-intelektual-pbmi</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/muaythai-1785939576697_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Rashford Memilih Bertahan di MU?</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Marcus Rashford akan segera gabung latihan pramusim Manchester United. Pihak klub masih buka opsi penjualan tapi sang winger fokus bertahan dulu.</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8605880/rashford-memilih-bertahan-di-mu</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/marcus-rashford-1781749340756.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Salah Sudah Tiba di Turki, Disambut bak Raja</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:40:20 +0700</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Mohamed Salah sudah tiba di Turki untuk menuntaskan kepindahannya ke Trabzonspor. Raja Mesir benar-benar disambut meriah fans klub tersebut.</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606183/salah-sudah-tiba-di-turki-disambut-bak-raja</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mohamed-salah-1785943966122_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Real Madrid Panen Cuan dari Jualan Pemain La Fabrica</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:20:50 +0700</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Real Madrid tak hanya aktif dalam pembelian, tapi juga penjualan pemain. Los Merengues berhasil memecahkan rekor cuan dari penjualan penggawa-penggawa muda.</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8605631/real-madrid-panen-cuan-dari-jualan-pemain-la-fabrica</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/10/gonzalo-garcia-1754822037320_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I559"/>
+  <autoFilter ref="A1:I605"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$605</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$613</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I605"/>
+  <dimension ref="A1:I613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -28869,8 +28869,384 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2 Jenazah Pendaki Gunung Piramid Bondowoso Berhasil Dievakuasi</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:50:10 +0700</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Chuk Shatu W</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Tim SAR berhasil evakuasi jenazah Maliya Finda dan pemandunya dari Gunung Piramid Bondowoso setelah 13 jam.</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606215/2-jenazah-pendaki-gunung-piramid-bondowoso-berhasil-dievakuasi</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pendaki-gunung-piramid-1785945003710_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Israel Gerebek Kamp Pengungsi Palestina di Tepi Barat, 20 Orang Ditangkap</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:29:51 +0700</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Lisye Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Pasukan Israel menggerebek kamp pengungsian Palestina di Tepi Barat, menangkap 20 orang. Operasi ini dianggap sebagai intimidasi terhadap warga Palestina.</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606213/israel-gerebek-kamp-pengungsi-palestina-di-tepi-barat-20-orang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/palestinian-israel-conflict-1785944818381_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Polisi Bongkar Kasus Pabrik Miras Ilegal di Bogor, 1 Orang Ditangkap</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:29:29 +0700</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Polsek Cileungsi ungkap kasus miras ilegal di Sukaraja, amankan pelaku M dan ratusan botol miras siap edar. Pelaku meracik miras sendiri untuk dijual.</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606212/polisi-bongkar-kasus-pabrik-miras-ilegal-di-bogor-1-orang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polsek-cileungsi-membongkar-kasus-minuman-keras-miras-ilegal-yang-diracik-di-sebuah-rumah-di-sukaraja-kabupaten-bogor-jawa-bar-1785947251444_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Polisi Malaysia Identifikasi Pemasok Narkoba yang Dibawa Pilot ke RI</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:52:31 +0700</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Lisye Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Polisi Malaysia identifikasi terduga pemasok narkoba ekstasi yang dibawa kopilot Malaysia Airlines ke Soekarno-Hatta. Penyelidikan berlanjut.</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606191/polisi-malaysia-identifikasi-pemasok-narkoba-yang-dibawa-pilot-ke-ri</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571468_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Malaysia Kerahkan Polisi Jaga Bandara Buntut Pilot Selundupkan Narkoba ke RI</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:51:59 +0700</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Pemerintah Malaysia akan kerahkan polisi untuk perkuat keamanan bandara setelah penangkapan pilot yang menyelundupkan narkoba di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606189/malaysia-kerahkan-polisi-jaga-bandara-buntut-pilot-selundupkan-narkoba-ke-ri</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/04/01/masuk-fase-awal-endemi-covid-19-malaysia-buka-pintu-buat-turis-asing-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Mendagri Siapkan 3 Langkah Solusi Operasional Gaji Pegawai Pemda</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:19:12 +0700</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian mengumumkan tiga langkah untuk membantu daerah yang kesulitan membayar gaji pegawai, termasuk efisiensi anggaran dan insentif DAU.</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606176/mendagri-siapkan-3-langkah-solusi-operasional-gaji-pegawai-pemda</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kemendagri-1785943042201.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>4 Fakta Kebakaran Gedung di Cikini hingga Orang Terjebak Kepulan Asap</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:15:12 +0700</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung di Cikini, Jakarta Pusat. Berikut sejumlah fakta yang diketahui.</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606172/4-fakta-kebakaran-gedung-di-cikini-hingga-orang-terjebak-kepulan-asap</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kebakaran-gedung-di-cikini-jakarta-pusat-jakpus-dok-tmc-polda-metro-jaya-1785920371696.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>44.121 Huntap Akan Dibangun untuk Penyintas Bencana Sumatera</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:13:26 +0700</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Alfi Kholisdinuka</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Satgas PRR percepat pembangunan 44.121 hunian tetap untuk penyintas bencana di Aceh, Sumut, dan Sumbar. Fokus pada kualitas dan keamanan hunian.</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606170/44-121-huntap-akan-dibangun-untuk-penyintas-bencana-sumatera</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/44121-huntap-akan-dibangun-untuk-penyintas-bencana-1785942678207.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I605"/>
+  <autoFilter ref="A1:I613"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$613</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$615</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I613"/>
+  <dimension ref="A1:I615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -29245,8 +29245,102 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Pensiun Jadi Wasit, Anthony Taylor Langsung Dapat Kerjaan Baru di Turki</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Kris FW</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Dua pekan setelah pensiun sebagai wasit, Anthony Taylor langsung mendapat jabatan penting di Federasi Sepakbola Turki (TFF).</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8605675/pensiun-jadi-wasit-anthony-taylor-langsung-dapat-kerjaan-baru-di-turki</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/09/17/anthony-taylor_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Duh, FIFA Ditagih 'Utang' Kota-kota AS Tuan Rumah Piala Dunia 2026</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Bayu Baskoro</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>FIFA kabarnya menjanjikan dana bantuan jutaan dolar AS untuk kota-kota tuan rumah Piala Dunia 2026. Janji tersebut rupanya belum dipenuhi.</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604977/duh-fifa-ditagih-utang-kota-kota-as-tuan-rumah-piala-dunia-2026</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/logo-piala-dunia-2026-1781218052585_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I613"/>
+  <autoFilter ref="A1:I615"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$615</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$660</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I615"/>
+  <dimension ref="A1:I660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -29339,8 +29339,2123 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Update Gempa M5,3 Pangandaran, Guncangan Dilaporkan Terasa di Bandung</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:05:15 +0700</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Gempa bumi tektonik M5.3 mengguncang Pangandaran, Jawa Barat, pada 5 Agustus 2026. Tidak berpotensi tsunami.</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805225612-20-1389102/update-gempa-m53-pangandaran-guncangan-dilaporkan-terasa-di-bandung</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/07/07/6101e4a4-1ee2-47a5-9838-13986a0c8632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Anggota DPRD Bekasi Didakwa Lakukan Pengeroyokan hingga Korban Luka</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:50:21 +0700</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Jaksa menuntut anggota DPRD Bekasi, Nyumarno, dan dua lainnya atas kekerasan yang menyebabkan luka pada korban.</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805203837-12-1389081/anggota-dprd-bekasi-didakwa-lakukan-pengeroyokan-hingga-korban-luka</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/06/21/ilustrasi-hukum_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Ombak Tak Bersahabat, Warga Pulau Bawean Carter Pesawat Demi Rujuk Ibu</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:44:41 +0700</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Pengusaha di Pulau Bawean mencarter pesawat Rp110 juta demi ibunya guna dirujuk ke Surabaya karena gelombang tinggi yang membuat pelayaran terkendala.</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805202433-20-1389075/ombak-tak-bersahabat-warga-pulau-bawean-carter-pesawat-demi-rujuk-ibu</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/17/ilustrasi-pesawat-atr-atr-72-1768644498968_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Polisi Diduga Bunuh Nenek di Deliserdang Usai Ditolak Pinjam Uang</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:38:16 +0700</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Bripda RF, anggota polisi, membunuh nenek 70 tahun setelah ditolak meminjam uang Rp50 juta. Polresta telah mengungkapnya dalam tempo 2x24 jam.</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805164846-12-1388971/polisi-diduga-bunuh-nenek-di-deliserdang-usai-ditolak-pinjam-uang</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/08/09/ilustrasi-anggota-polisi-berseragam-dinas-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Gempa M5,3 di Pangandaran Jabar, Tak Berpotensi Tsunami</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:35:18 +0700</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Gempa berkekuatan M 5,3 terjadi di laut, sekitar 79 km barat daya Pangandaran, Jabar. tidak berpotensi tsunami.</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805223406-20-1389100/gempa-m53-di-pangandaran-jabar-tak-berpotensi-tsunami</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/11/16/6b71c58c-8a52-45c7-9e56-a1feb8e24c6a_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>FOTO: Penampakan JPO Kembar Rasuna Said, Berdampingan Tak Menyambung</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:17:43 +0700</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Dua jembatan penyeberangan orang (JPO) yang berdampingan di Jalan HR Rasuna Said, Jakarta Selatan, masih belum terhubung. Pemprov DKI berwacana menyambungnya.</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805200610-22-1389062/foto-penampakan-jpo-kembar-rasuna-said-berdampingan-tak-menyambung</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/jpo-kembar-rasuna-said-akan-terhubung-warga-tak-perlu-memutar-1785932475132_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Polisi Duga Pelaku Mutilasi di Depok adalah Penyuka Sesama Jenis</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:10:17 +0700</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Kasus mutilasi di Depok terungkap. Pelaku, Saepul, diduga penyuka sesama jenis atau LGBT dan mengaku terpaksa membunuh korban.</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805170415-12-1388979/polisi-duga-pelaku-mutilasi-di-depok-adalah-penyuka-sesama-jenis</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/09/26/ilustrasi-pasangan-lgbt_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Pengadilan Tipikor Mataram Vonis Bebas Ketua Komisi IV DPRD NTB</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:02:36 +0700</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Pengadilan Tipikor Mataram memvonis bebas Ketua Komisi IV DPRD NTB, Hamdan Kasim, dalam kasus gratifikasi. Hakim memulihkan hak-hak terdakwa.</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805200949-12-1389069/pengadilan-tipikor-mataram-vonis-bebas-ketua-komisi-iv-dprd-ntb</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/12/23/8f78cb8a-ccf2-4125-aa3a-a789a6b42b35_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Pemda DIY Tetapkan Raperda Larangan Perdagangan Daging Anjing</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:45:28 +0700</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Pemda DIY menetapkan Raperda larangan perdagangan daging anjing untuk melindungi kesehatan masyarakat dan mencegah penularan penyakit zoonosis.</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805175025-20-1388998/pemda-diy-tetapkan-raperda-larangan-perdagangan-daging-anjing</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/10/01/7fbc2857-28a1-415e-91c7-a13402daa01b_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Menkes Terima Kepala BGN, Didampingi Ahli Gizi Beri Masukan soal MBG</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:25:39 +0700</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Menkes Budi Gunadi Sadikin dan Kepala BGN Sudaryono bahas perbaikan program makan bergizi gratis. Ahli gizi diundang untuk masukan terkait menu dan layanan.</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805204317-20-1389085/menkes-terima-kepala-bgn-didampingi-ahli-gizi-beri-masukan-soal-mbg</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/menkes-terima-kepala-bgn-beri-masukan-soal-mbg-1785937187590_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Rektor Unsrat Manado Dicopot, Kemendikti Tunjuk Rektor Unhas Jadi Plt</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:20:27 +0700</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Rektor Universitas Hasanuddin, Prof Jamaluddin Jompa, ditunjuk sebagai Plt Rektor Universitas Sam Ratulangi, menggantikan Prof Oktovian yang dicopot.</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805145334-20-1388916/rektor-unsrat-manado-dicopot-kemendikti-tunjuk-rektor-unhas-jadi-plt</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/01/12/ilustrasi-toga-sarjana_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Dua Helikopter Dikerahkan Padamkan Kebakaran Bromo 80 Hektare</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:18:31 +0700</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>BNPB akan terjunkan helikopter dan drone untuk padamkan kebakaran hutan di Gunung Bromo. Kebakaran meluas hingga 80 hektare, penanganan ditargetkan cepat.</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805205427-20-1389087/dua-helikopter-dikerahkan-padamkan-kebakaran-bromo-80-hektare</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kebakaran-kawasan-bromo-meluas-hingga-80-hektare-pemadaman-pakai-drone-1785937271086_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Menkes Tanggapi Pasien BPJS Meninggal yang Sempat Dicibir Dokter</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:11:00 +0700</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>CNNIndonesia/Dela</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Menkes merespons beredarnya komentar sejumlah tenaga medis dan tenaga kesehatan di media sosial yang dinilai kurang berempati terhadap pasien BPJS.</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805202742-24-1389077/menkes-tanggapi-pasien-bpjs-meninggal-yang-sempat-dicibir-dokter</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kemenkes-tanggapi-kasus-pasien-bpjs-yang-meninggal-1785938018395_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>KPK Sebut Ada Penyerahan Sin$14.000 dari Bupati Kuansing ke Raja Juli</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:02:26 +0700</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>KPK mengungkap dugaan penyerahan uang Bupati Kuansing, Suhardiman Amby senilai Sin$14.000 ke Menhut Raja Juli.</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805194749-12-1389060/kpk-sebut-ada-penyerahan-sin-14000-dari-bupati-kuansing-ke-raja-juli</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/15/juru-bicara-kpk-budi-prasetyo-1755260853896_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Menkes Usai Pasien BPJS Dicibir Dokter Meninggal: Hati Saya Sedih</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:49:29 +0700</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Menkes Budi Gunadi merasa sedih atas meninggalnya pasien BPJS tak lama setelah dicibir dokter di media sosial.</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805202557-20-1389076/menkes-usai-pasien-bpjs-dicibir-dokter-meninggal-hati-saya-sedih</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/09/raker-komisi-ix-dpr-dengan-menkes-1780988911618_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Kebakaran Kawasan Bromo Meluas hingga 80 Hektare</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:40:14 +0700</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Gunung Bromo meluas hingga 80 hektare. Tim gabungan berupaya memadamkan api dengan drone water spray, akses wisata dibatasi demi keselamatan.</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805203717-20-1389080/kebakaran-kawasan-bromo-meluas-hingga-80-hektare</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/penutupan-sebagian-akses-wisata-bromo-1785849760126_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Kasus Dokter Cibir Pasien, UGM Dampingi Keluarga Pasien BPJS Meninggal</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:16:56 +0700</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>UGM memberikan pendampingan kepada keluarga pasien BPJS yang meninggal setelah komentar tak berempati dari dokter PPDS Elda Putri.</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805194541-12-1389059/kasus-dokter-cibir-pasien-ugm-dampingi-keluarga-pasien-bpjs-meninggal</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/05/15/universitas-gadjah-mada-1747298809962_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>FOTO: Pertengahan 2026, Penduduk Indonesia Tembus 290 Juta Jiwa</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:15:09 +0700</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Ditjen Dukcapil Kemendagri mencatat jumlah penduduk Indonesia mencapai 290.125.073 jiwa pada Juni 2026 atau pertengahan tahun ini.</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805184852-22-1389028/foto-pertengahan-2026-penduduk-indonesia-tembus-290-juta-jiwa</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/mobilitas-wni-di-saat-indonesia-capai-290-juta-jiwa-1785926921946_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Keluarga Mengaku Temukan Lebam di Jasad Mantan Istri Polisi Medan</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:06:27 +0700</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Kematian L (30) di Medan diduga bunuh diri, namun keluarga curiga. Mereka temukan luka lebam dan cekikan, menolak keterangan polisi.</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805192853-12-1389053/keluarga-mengaku-temukan-lebam-di-jasad-mantan-istri-polisi-medan</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/istri-polisi-diduga-bunuh-diri-pakai-senpi-di-medan-1785735979615_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Pejabat Kemenhut Terima Sin$12.500 dari Bupati Kuansing</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:00:29 +0700</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>KPK mengungkap dugaan suap Bupati Kuansing, Suhardiman Amby, dengan pemberian uang Sin$12.500 terkait pelepasan kawasan hutan. Penyidikan berlanjut.</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805183600-12-1389027/kpk-ungkap-pejabat-kemenhut-terima-sin-12500-dari-bupati-kuansing</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/01/kpk-menetapkan-bupati-kuantan-singingi-kuansing-periode-2025-2030-suhardiman-amby-dan-sekretaris-daerah-zulkarnain-sebagai-ter-1782896232826_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Kebakaran di Gedung Cikini Diduga Berasal dari Lantai 3</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:43:16 +0700</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Kebakaran di gedung Ruko Central, Cikini, Jakarta Pusat, diduga berasal dari lantai 3. 22 mobil pemadam dikerahkan, tidak ada korban jiwa.</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805191219-20-1389047/kebakaran-di-gedung-cikini-diduga-berasal-dari-lantai-3</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kebakaran-proyek-ruko-di-cikini-1785929084828_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>FOTO: Kebakaran Proyek Ruko Lima Lantai di Cikini</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:22:50 +0700</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda proyek pembangunan ruko lima lantai di kawasan Central Cikini, Jalan Cikini Raya, Menteng, Jakarta Pusat, Rabu (5/8) sore.</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805182542-22-1389016/foto-kebakaran-proyek-ruko-lima-lantai-di-cikini</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kebakaran-proyek-ruko-di-cikini-1785928654250_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>UGM Investigasi Kasus Dokter PPDS Cibir Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:46:19 +0700</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>UGM menyelidiki dugaan komentar nirempati dokter PPDS Elda Putri terhadap pasien BPJS. Fakultas menyebut pentingnya etika dan empati dalam pelayanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805182548-20-1389014/ugm-investigasi-kasus-dokter-ppds-cibir-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/05/15/universitas-gadjah-mada-1747298810268_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap Pria di Medan Produksi dan Jual Konten Gay Rp50 Ribu</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:20:14 +0700</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Polisi Medan menangkap BI alias Zilla, pria yang memproduksi dan menjual konten pornografi gay di aplikasi MiChat seharga Rp50.000.</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805175039-12-1388999/polisi-tangkap-pria-di-medan-produksi-dan-jual-konten-gay-rp50-ribu</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/07/24/0676200f-0af8-4c87-a754-bff6467e55d7_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Menko Polkam Buka Suara soal Fenomena Mal Pasang Pagar Tinggi</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:13:51 +0700</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Menko Polkam buka suara soal ramai pemasangan pagar tinggi di mall jelang isu demo Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805174510-12-1388997/menko-polkam-buka-suara-soal-fenomena-mal-pasang-pagar-tinggi</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kemenko-polkam-pastikan-situasi-nasional-aman-1785924470914_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Tito Imbau 16 K/L Segera Eksekusi Program Pascabencana Sumatra</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:52:20 +0700</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian mengumumkan 16 kementerian/lembaga telah menerima anggaran untuk rehabilitasi pascabencana Sumatra, Eksekusi program segera diperlukan.</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805174019-25-1388994/tito-imbau-16-k-l-segera-eksekusi-program-pascabencana-sumatra</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kemendagri-1785925591013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Diduga Sebar Hoaks Demo, Perempuan Asal Ciamis Terancam 12 Tahun Bui</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:50:11 +0700</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Perempuan usia 45 tahun terancam 12 tahun penjara karena menyebarkan hoaks ajakan berdemo menjelang 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805150239-12-1388932/diduga-sebar-hoaks-demo-perempuan-asal-ciamis-terancam-12-tahun-bui</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/09/08/ilustrasi-tindakan-kriminal-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Eks Jampidsus Febrie Resmi Ajukan Praperadilan ke PN Jaksel</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:28:40 +0700</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Mantan Jaksa Agung Muda, Febrie Adriansyah, ajukan gugatan praperadilan terkait kasus TPPU. Pengacara uji proses hukum dan penetapan tersangka</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805172249-12-1388991/eks-jampidsus-febrie-resmi-ajukan-praperadilan-ke-pn-jaksel</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/25/febrie-adriansyah-ditahan-di-rutan-kpk-1784914679962_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Menteri PU Percepat SRT Kuantan Singingi, Patikan Siswa Aman dan Nyaman</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:26:13 +0700</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Menteri PU, Dody Hanggodo, dorong percepatan pembangunan SRT 1 Kuantan Singingi di Riau, dukung akses pendidikan berkualitas dan infrastruktur yang memadai.</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805165626-25-1388975/menteri-pu-percepat-srt-kuantan-singingi-patikan-siswa-aman-nyaman</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kementerian-pu-1785923006116_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>KemenPU Tuntaskan Pembangunan, 4 Sekolah Rakyat Sulsel Masuk MPLS</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:24:53 +0700</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Keempat Sekolah Rakyat Terintegrasi tersebut berada di Kabupaten Barru, Sidenreng Rappang (Sidrap), Tana Toraja, dan Bone, yang kini mulai melayani 1.508 siswa</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805170652-25-1388981/kemenpu-tuntaskan-pembangunan-4-sekolah-rakyat-sulsel-masuk-mpls</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kementerian-pu-1785923220363_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>KPK Sita Sin$8.500 Usai Geledah Kantor Imigrasi Jaksel-Jakpus</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:22:00 +0700</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>KPK menyita barang bukti terkait dugaan pemerasan izin tinggal WNA di Jakarta. Delapan tersangka telah ditahan, termasuk mantan Wakil Menteri Imigrasi.</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805171052-12-1388983/kpk-sita-sin-8500-usai-geledah-kantor-imigrasi-jaksel-jakpus</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/04/12/ilustrasi-dolar-singapura_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Bakom Investigasi Makalah MBG Diajukan untuk Nobel Perdamaian</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:10:54 +0700</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Pemerintah RI menyelidiki makalah yang mengusulkan program Makan Bergizi Gratis (MBG) sebagai kandidat Nobel Perdamaian 2026, melibatkan Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805163645-20-1388967/bakom-investigasi-makalah-mbg-diajukan-untuk-nobel-perdamaian</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/28/kepala-bakom-ri-minta-publik-fokus-substansi-soal-londo-ireng-1785244644776_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Karyawan SPPG Kuningan Korbankan Diri Cegah Babi Hutan Seruduk Bocah</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:07:50 +0700</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Anas, relawan SPPG, berkorban menahan babi hutan agar tidak menyerang anak-anak. Ia mengalami luka akibat gigitan babi, berharap kejadian serupa tak terulang.</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805154655-20-1388950/karyawan-sppg-kuningan-korbankan-diri-cegah-babi-hutan-seruduk-bocah</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/09/06/acef15ca-b1af-4e27-941d-3bca09048df2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Gus Ipul Tekankan Tiga Prioritas Pengelolaan Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:05:57 +0700</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Mensos Saifullah Yusuf atau Gus Ipul mengingatkan seluruh kepala Sekolah Rakyat di Indonesia untuk memprioritaskan tiga hal penting dalam pengelolaan sekolah.</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805170056-20-1388977/gus-ipul-tekankan-tiga-prioritas-pengelolaan-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kementerian-sosial-1785924188518_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Mendagri Ungkap 79 Pemda Butuh Rp3,7 Triliun untuk Bayar Gaji Pegawai</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:55:13 +0700</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian ungkap kebutuhan dana Rp3,5 triliun untuk belanja pegawai di 79 daerah.</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805163552-20-1388966/mendagri-ungkap-79-pemda-butuh-rp37-triliun-untuk-bayar-gaji-pegawai</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/29/mendagri-tito-karnavian-1780053714883_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Pemkab Musi Banyuasin Usulkan Lahan Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:41:00 +0700</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial menerima usulan lahan pembangunan Sekolah Rakyat dari Pemerintah Kabupaten Musi Banyuasin.</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805163557-20-1388965/pemkab-musi-banyuasin-usulkan-lahan-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kementerian-sosial-1785922534771_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Kemenkes Buka Suara soal Kasus Dokter Cibir Pasien BPJS di Medsos</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:40:56 +0700</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Kemenkes menanggapi cibiran dokter terhadap pasien BPJS Kesehatan di media sosial.</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805163301-20-1388964/kemenkes-buka-suara-soal-kasus-dokter-cibir-pasien-bpjs-di-medsos</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/02/12/rscm-tetap-berikan-pelayanan-meski-polemik-bjps-pbi-1770892442987_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Gus Ipul: Program Sekolah Rakyat Butuh Kolaborasi</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:39:48 +0700</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Menteri Sosial Saifullah Yusuf atau Gus Ipul menegaskan bahwa Sekolah Rakyat merupakan tanggung jawab bersama seluruh Unit Kerja (UKE) di Kementerian Sosial.</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805163221-20-1388963/gus-ipul-program-sekolah-rakyat-butuh-kolaborasi</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kementerian-sosial-1785922534966_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Gedung di Cikini Jakpus Kebakaran, 22 Mobil Damkar Diterjunkan</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:26:07 +0700</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung Ruko Central di Cikini, Jakarta Pusat, pada Rabu sore. 22 unit mobil damkar dikerahkan untuk memadamkan api.</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805161904-20-1388959/gedung-di-cikini-jakpus-kebakaran-22-mobil-damkar-diterjunkan</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/01/01/2ab612fd-1f1a-4633-829b-795f0b6f1a1d_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Remaja di Buleleng Tepergok Diduga Curi Ayam Aduan, Berakhir Mediasi</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:22:55 +0700</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Dua remaja 16 tahun ditangkap karena mencuri ayam aduan di Buleleng, Bali. Mereka menjalani mediasi dan berjanji tidak mengulangi perbuatan.</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805153610-12-1388946/remaja-di-buleleng-tepergok-diduga-curi-ayam-aduan-berakhir-mediasi</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/03/31/68e08937-1493-47f7-8907-c81a726b33dc_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Kapolri Pastikan Tindak Pelaku Penyebaran Hoaks Demo</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:47:38 +0700</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Sigit memastikan pelaku penyebar hoaks demo akan ditindak. Masyarakat diingatkan untuk menyebarkan informasi yang akurat dan sesuai fakta.</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805151848-12-1388934/kapolri-pastikan-tindak-pelaku-penyebaran-hoaks-demo</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kumpulkan-panglima-tni-kapolri-menko-polkam-pastikan-kondisi-aman-terkendali-1785913030308_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>DPRD Beri Alarm soal Krisis Guru di Jabar, Kekurangan 6 Ribu Pengajar</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:40:52 +0700</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>DPRD Jabar soroti krisis kekurangan 6.000 guru. DPRD menilai hal itu bisa mengancam kualitas pendidikan dan masa depan generasi.</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805145755-20-1388920/dprd-beri-alarm-soal-krisis-guru-di-jabar-kekurangan-6-ribu-pengajar</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2016/08/09/2529fc07-7384-4cc6-9243-aa5c086272b5_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Menko Polkam Tegaskan Demo Diperbolehkan: Yang Dilarang Aksi Anarkis</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:26:29 +0700</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago mengizinkan aksi demonstrasi asalkan tertib. Ia menegaskan kritik masyarakat penting dan situasi di Indonesia aman.</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805150035-12-1388921/menko-polkam-tegaskan-demo-diperbolehkan-yang-dilarang-aksi-anarkis</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kumpulkan-panglima-tni-kapolri-menko-polkam-pastikan-kondisi-aman-terkendali-1785913030381_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2 Pendaki Gunung PIramid Bondowoso yang Sempat Hilang Ditemukan Tewas</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:24:08 +0700</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Dua pendaki di Gunung Piramid, Bondowoso, ditemukan meninggal. Proses evakuasi dilakukan oleh tim SAR setelah penyisiran di lokasi kejadian.</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805150034-20-1388933/2-pendaki-gunung-piramid-bondowoso-yang-sempat-hilang-ditemukan-tewas</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/08/tim-sar-gabungan-cari-puluhan-pendaki-yang-tersesat-saat-gunung-dokuno-erupsi-1778218263491_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Kapolri Respons Isu Surpres</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:59:08 +0700</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Kapolri Listyo Sigit Prabowo menyatakan pergantian pimpinan Polri adalah hak prerogatif Presiden.</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805140047-12-1388892/kapolri-respons-isu-surpres</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/23/bazar-kreasi-bhayangkari-nusantara-kbn-2026-1784772703536_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I615"/>
+  <autoFilter ref="A1:I660"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$660</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$684</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I660"/>
+  <dimension ref="A1:I684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -31454,8 +31454,1136 @@
         </is>
       </c>
     </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Petaka Baru Trump, Satu Dunia Bisa Rasakan Dampaknya</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Pemerintahan Trump akan menetapkan harga minimum impor dan tarif untuk polysilicon. Hal ini bisa berdampak ke mana-mana.</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805145947-37-756795/petaka-baru-trump-satu-dunia-bisa-rasakan-dampaknya</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/30/usa-trump-1785371156663_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Ojol Ungkap Penghasilan Sehari Setelah Libur Sekolah Selesai</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Libur sekolah usai, namun pengemudi ojol masih alami stagnasi pendapatan harian. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805151805-37-756803/ojol-ungkap-penghasilan-sehari-setelah-libur-sekolah-selesai</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/14/sekelompok-pengemudi-ojol-yang-bergabung-dalam-solidaritas-ojol-senusantara-sos-melakukan-aksi-ujuk-rasa-di-kawasan-monas-jaka-1768372595229_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Rekor, Warga Berebut HP Lipat Baru Samsung Padahal Barangnya Belum Ada</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Z Fold 8 dan Z Flip 8 mencetak rekor pemesanan awal tertinggi, mencapai 1,44 juta unit.</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805123831-37-756730/rekor-warga-berebut-hp-lipat-baru-samsung-padahal-barangnya-belum-ada</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/18/samsung-galaxy-z-fold8-dan-z-fold8-ultra-1784365937288_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Banyak Mainan Canggih, Cek Pameran Theme Park di JIExpo Kemayoran</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Industri taman rekreasi dan wahana hiburan terus berkembang seiring meningkatnya minat masyarakat terhadap destinasi wisata berbasis pengalaman.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805164824-38-756858/banyak-mainan-canggih-cek-pameran-theme-park-di-jiexpo-kemayoran</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/pengunjung-mencoba-wahana-permainan-dalam-pameran-fun-asia-expo-indonesia-2026-di-jiexpo-kemayoran-jakarta-rabu-582026-1785923072309_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Bumi Menuju Kiamat Makin Cepat, Situasinya Sudah Sangat Genting</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Studi baru menunjukkan pemanasan global semakin cepat, dengan suhu rata-rata dunia naik 0,35°C per dekade.</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805134942-37-756759/bumi-menuju-kiamat-makin-cepat-situasinya-sudah-sangat-genting</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/otoritas-korea-selatan-korsel-menyerukan-masyarakat-untuk-menghentikan-semua-aktivitas-luar-ruangan-outdoor-usai-negeri-ginsen-1785757410921_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Rekening Bobol Walau Tak Tersambung Internet, Rp 1,59 Triliun Lenyap</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Thea Arbar</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Serangan siber terhadap dompet kripto Coldcard mengakibatkan kehilangan aset senilai US$88,6 juta.</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805152612-37-756808/rekening-bobol-walau-tak-tersambung-internet-rp-159-triliun-lenyap</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/12/08/dompet-kripto-fisik-keluaran-ledger_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Sukses Road Trip Jawa-Bali, VinFast VF MPV 7 Pupuskan Range Anxiety</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:57:04 +0700</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Perjalanan 11 hari menggunakan VinFast VF MPV 7 dari Jakarta ke Bali mengungkap kemudahan pengisian daya dan performa mobil listrik di berbagai medan.</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805175136-37-756888/sukses-road-trip-jawa-bali-vinfast-vf-mpv-7-pupuskan-range-anxiety</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/vinfast-vf-mpv-7-ditampilkan-dalam-acara-giias-2026-di-ice-bsd-city-kabupaten-tangerang-banten-rabu-2972026-1785309135289_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>YouTuber Terkenal Ditemukan Tewas di Hotel, Begini Keterangan Polisi</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>YouTuber Thailand Hlun Solo ditemukan tewas di hotel Tbilisi, Georgia. Penyebab kematiannya masih diselidiki. Simak!</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805152250-37-756804/youtuber-terkenal-ditemukan-tewas-di-hotel-begini-keterangan-polisi</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/11/08/ilustrasi-mayat-dok-freepik-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Curhat Tak Terduga Driver Ojol Sebulan Setelah Komisi Naik Jadi 92%</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Pengemudi ojol mengeluhkan stagnasi pendapatan meski potongan aplikasi turun menjadi 8%. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805151032-37-756798/curhat-tak-terduga-driver-ojol-sebulan-setelah-komisi-naik-jadi-92</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/04/pengemudi-ojek-online-ojol-menunggu-orderan-penumpang-di-kawasan-stasiun-palmerah-jakarta-senin-452026-1777870908636_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Demo Besar-Besaran Tolak Data Center, 37 Orang Ditangkap Polisi</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Gelombang penolakan terhadap ekspansi pusat data di AS meningkat, memicu penangkapan warga. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805140259-37-756764/demo-besar-besaran-tolak-data-center-37-orang-ditangkap-polisi</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/gedung-data-center-meta-di-mansfield-as-1779441817711_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Menko Polkam Soal Viral Video Demo Agustus: Saya Nyatakan Tidak Benar!</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:02:45 +0700</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago menyatakan video ajakan demonstrasi yang beredar adalah hoaks. Ia menegaskan situasi dalam negeri aman dan terkendali.</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805160043-37-756826/menko-polkam-soal-viral-video-demo-agustus-saya-nyatakan-tidak-benar</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/menteri-koordinator-bidang-politik-dan-keamanan-djamari-chaniago-tengah-memberikan-keterangan-pers-di-kantor-kemenko-polkam-ja-1785910953762_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Amerika Ditinggalkan, Ulah Trump Bawa Berkah Tak Terduga Buat China</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Samsung dan SK Hynix evaluasi peralatan chip dari China, sebagai strategi menghadapi kontrol ekspor AS. Simak!</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805122727-37-756728/amerika-ditinggalkan-ulah-trump-bawa-berkah-tak-terduga-buat-china</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/15/presiden-china-xi-jinping-memperlihatkan-suasana-kompleks-bersejarah-zhongnanhai-kepada-presiden-amerika-serikat-donald-trump--1778835073981_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Apa Alasan Lampung Punya Satelit Sendiri? Ini Penjelasan Ahli</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Provinsi Lampung akan meluncurkan satelit Lampung-1 dengan kamera hyperspectral untuk observasi Bumi.</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805121903-37-756725/apa-alasan-lampung-punya-satelit-sendiri-ini-penjelasan-ahli</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/satelit-hiperspektral-lampung-1-resmi-lepas-landas-menumpang-roket-milik-star-vision-dan-lepas-landas-di-kawasan-perairan-shan-1785905833755_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>17 Perusahaan China Digerebek, 330 Intel Dikerahkan Amankan 114 Orang</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Taiwan meningkatkan penggerebekan terhadap perusahaan China yang diduga membajak talenta teknologi. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805120226-37-756719/17-perusahaan-china-digerebek-330-intel-dikerahkan-amankan-114-orang</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/05/08/ketegangan-china-dan-taiwan-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Video: Akselerasi AI Indonesia Hadapi Tantangan Data Silo, Solusinya?</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:25:05 +0700</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Akselerasi AI di Indonesia Hadapi Tantangan Data Silo, Apa Solusinya?</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805114717-39-756713/video-akselerasi-ai-indonesia-hadapi-tantangan-data-silo-solusinya</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/akselerasi-ai-di-indonesia-hadapi-tantangan-data-silo-apa-solusinya-1785908151606_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Pegawai Alfamart-Indomaret Terancam Punah, Tandanya Muncul di China</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Gelombang disrupsi AI mengguncang sektor ritel global, memicu potensi PHK massal. Tandanya sudah kencang di China. Simak!</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805112440-37-756700/pegawai-alfamart-indomaret-terancam-punah-tandanya-muncul-di-china</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/22/sebuah-toko-robot-otonom-sepenuhnya-di-tepi-laut-hung-hom-1782106050261_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Produk Asal China Mau Diblokir Total, Aturannya Lagi Disiapkan</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Pemerintahan Trump merancang larangan impor komponen data center asal China untuk melindungi infrastruktur nasional. Simak!</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805112923-37-756703/produk-asal-china-mau-diblokir-total-aturannya-lagi-disiapkan</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/15/presiden-china-xi-jinping-memperlihatkan-suasana-kompleks-bersejarah-zhongnanhai-kepada-presiden-amerika-serikat-donald-trump--1778835074284_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 Sukses Meluncur dari China, Roket Terbang dari Kapal</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 berhasil diluncurkan dari China, hasil kolaborasi BRIN dan Star Vision.</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805113123-37-756710/satelit-lampung-1-sukses-meluncur-dari-china-roket-terbang-dari-kapal</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/satelit-hiperspektral-lampung-1-resmi-lepas-landas-menumpang-roket-milik-star-vision-dan-lepas-landas-di-kawasan-perairan-shan-1785905834162_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Kuota Internet Tak Bakal Hangus Bisa Dipakai Habis, Begini Kata Opsel</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>MK memutuskan kuota internet yang dibeli masyarakat dapat digunakan hingga habis tanpa biaya tambahan. Begini respons opsel.</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805110647-37-756687/kuota-internet-tak-bakal-hangus-bisa-dipakai-habis-begini-kata-opsel</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/10/11/infografis-jangan-kelewat-bantuan-kuota-internet-cair-hari-ini-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>China Bawa Kiamat Driver Online Makin Luas, Sudah Sampai Negara Ini</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>WeRide, produsen robotaxi asal China, akan meluncurkan layanan taksi tanpa sopir di Denmark pada 2027, memperluas jangkauan di Eropa.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805110141-37-756685/china-bawa-kiamat-driver-online-makin-luas-sudah-sampai-negara-ini</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/08/08/kabin-depan-taksi-robot-tanpa-sopir-buatan-baidu_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>WhatsApp Salah Blokir Massal, Chat Pengguna Mulai Dibuka</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Meta mengonfirmasi bahwa sejumlah akun WhatsApp diblokir karena kesalahan sistem.</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805100607-37-756668/whatsapp-salah-blokir-massal-chat-pengguna-mulai-dibuka</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/03/whatsapp-reutersdado-ruvicillustrationfile-photo-1770118007754_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Sisa Manusia Ditemukan Terkubur Dalam di Balik Es Antartika</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:40:20 +0700</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Penelitian menemukan mikroplastik dan nanoplastik di tanah Antartika, menunjukkan polusi plastik telah mencapai lingkungan paling terpencil di Bumi.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805083723-37-756628/sisa-manusia-ditemukan-terkubur-dalam-di-balik-es-antartika</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/02/20/benua-antarktika-6_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Gebrakan Baru China Bisa Bikin Amerika Makin Ditinggalkan</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:45:08 +0700</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti Dewi</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>China menggebrak lagi dengan model AI yang canggih tapi termurah dan efisien energi.</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805063008-37-756604/gebrakan-baru-china-bisa-bikin-amerika-makin-ditinggalkan</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/05/13/usa-chinaai_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>5 Aplikasi yang Isinya Penuh Mata-Mata, Banyak yang Tidak Sadar</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>NordVPN mengungkap aplikasi populer yang berpotensi membahayakan privasi pengguna, termasuk Facebook dan aplikasi cuaca.</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805062455-37-756603/5-aplikasi-yang-isinya-penuh-mata-mata-banyak-yang-tidak-sadar</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/07/19/ilustrasi-warga-menggunakan-aplikasi-sosial-media-di-kawasan-ciputat-tangerang-selatan-selasa-1972022-cnbc-indonesiamuhammad-s-8_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I660"/>
+  <autoFilter ref="A1:I684"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$684</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$764</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I684"/>
+  <dimension ref="A1:I764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -32582,8 +32582,3768 @@
         </is>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Gemas! Rossa Ajak Anak Perempuan Manggung</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:01:02 +0700</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Penyanyi Rossa memukau 3.000 penonton di Soul Concert VII di Jakarta, tampil bersama putrinya, Raina. Momen emosional ini disambut meriah oleh penggemar.</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8605571/gemas-rossa-ajak-anak-perempuan-manggung</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rossa-1785919538768_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Violis Iskandar Widjaja dan Pianis Niu Niu Konser di Indonesia</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:35:06 +0700</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Iskandar Widjaja akan konser di Indonesia bersama pianis Niu Niu pada 28 Agustus 2026. Tiket mulai dari Rp 300 ribu. Temukan perjalanan musikal yang mendalam!</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8605518/violis-iskandar-widjaja-dan-pianis-niu-niu-konser-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/iskandar-widjaja-niu-niu-1785835163700_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Dian Ayu Lestari Alami Saraf Kejepit, 3 Bulan Gak Boleh Padel dan Naik Motor</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:02:47 +0700</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Presenter Dian Ayu Lestari dirawat di rumah sakit karena mengalami saraf kejepit. Istri Ananda Omesh itu 3 bulan harus libur padel dan tak boleh naik motor.</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605971/dian-ayu-lestari-alami-saraf-kejepit-3-bulan-gak-boleh-padel-dan-naik-motor</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/dian-ayu-lestari-1785930544467_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Selvi Kitty Hormati Keputusan Suami soal Gak Perlihatkan Wajah</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:05:26 +0700</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Selebritas Selvi Kitty menghormati keputusan suaminya, yang gak mau wajahnya diperlihatkan ke publik.</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605591/selvi-kitty-hormati-keputusan-suami-soal-gak-perlihatkan-wajah</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/03/selvi-kitty-1783097593674_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Asila Maisa Gak Masalah Dibilang Centil</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:09:37 +0700</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Asila Maisa nggak masalah dibilang centil. Imej yang melekat dengannya itu bukan sengaja dibuat.</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605658/asila-maisa-gak-masalah-dibilang-centil</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/asila-maisa-1785922363569_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Syarat Damai dari Pihak Eks ART untuk Erin</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:13:11 +0700</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Proses mediasi gugatan Nur Rohmah terhadap Erin di Pengadilan Jakarta Selatan berlanjut. Fokus pada pengembalian barang pribadi dan hak-hak Nur Rohmah.</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605316/syarat-damai-dari-pihak-eks-art-untuk-erin</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/erin-1778233126424_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Rina Nose Hati-hati Banget Bersihkan Hidung Usai Oplas</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:08:45 +0700</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Rina Nose mengaku sudah nggak pernah mengupil setelah hidung dioperasi. Rina menceritakan bagaimana dirinya menjaga kebersihan hidung.</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605495/rina-nose-hati-hati-banget-bersihkan-hidung-usai-oplas</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/06/rina-nose-1772768852087_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Rizky Billar Kehilangan Uang Rp 3,1 M</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:08:26 +0700</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Rizky Billar mengungkapkan kerugian Rp 3,1 miliar akibat penggelapan oleh orang terdekat. Ia siap ambil langkah hukum jika tidak ada penyelesaian.</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605433/rizky-billar-kehilangan-uang-rp-3-1-m</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/rizky-billar-1785477825510_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Birthday Trip Ummi Quary ke Singapura Sendiri: Apresiasi Diri</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:05:02 +0700</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Ummi Quary pertama kalinya jalan-jalan ke luar negeri sendiri. Ummi pergi ke Singapura sendiri untuk merayakan ulang tahunnya sebagai self reward.</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605299/birthday-trip-ummi-quary-ke-singapura-sendiri-apresiasi-diri</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ummi-quary-1785912369832_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Erin Bantah Tahan Barang hingga Gaji Eks ART dalam Proposal Mediasi</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:07:47 +0700</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Sidang kasus perdata antara Erin dan mantan ART, Nur Rohmah, berlanjut. Proposal perdamaian Erin memicu pertanyaan Nur soal penahanan barang pribadi dan gaji.</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605182/erin-bantah-tahan-barang-hingga-gaji-eks-art-dalam-proposal-mediasi</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/30/erin-taulany-1777549496526_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Obrolan Imel Putri dan Zaskia Gotik Saat Duduk Bareng Hadiri Kelulusan Anak</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:29:10 +0700</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Imel Putri dan Zaskia Gotik duduk bersama menghadiri kelulusan Aqila Ramadhani dari SMP. Aqila adalah putri Imel dengan Sirajuddin Mahmud Sabang, suami Zaskia.</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605125/obrolan-imel-putri-dan-zaskia-gotik-saat-duduk-bareng-hadiri-kelulusan-anak</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/imel-putri-cahyati-1785906989562_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Cerita Kebahagiaan Rossa Punya Anak Perempuan</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:01:27 +0700</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Rossa bahagia dengan kehadiran putri bungsunya, Raina. Ia merasa terpilih untuk membesarkan anak perempuan yang membawa kebahagiaan baru dalam keluarga.</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604820/cerita-kebahagiaan-rossa-punya-anak-perempuan</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/rossa-1785487993946_43.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Indra Bekti Kaget Lihat Sisi Asli Raisa: Kirain Jaim Ternyata Kocak Banget</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:33:29 +0700</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Indra Bekti kembali membawakan karakter Bagong di Pagelaran Sabang Merauke. Kehadiran Raisa Andriana membuat suasana latihan jadi lebih seru dan menyenangkan.</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604557/indra-bekti-kaget-lihat-sisi-asli-raisa-kirain-jaim-ternyata-kocak-banget</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/06/indra-bekti-11_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Ummi Quary Terinspirasi Zendaya dalam Penampilan</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:01:59 +0700</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Ummi Quary tampil lebih elegan dan fashionable dengan gaya clean look. Ia kini suka pakai heels untuk meningkatkan percaya diri dan memilih outfit terjangkau.</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604550/ummi-quary-terinspirasi-zendaya-dalam-penampilan</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/18/ummi-quary-1776512536202_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Alasan Eross Candra Pilih Radio Ketimbang Podcast: Ngomong Banyak Itu PR</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:01:18 +0700</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Eross Candra dari Sheila on 7 jelaskan keterikatan bandnya dengan radio, anggapnya sebagai pengantar karier. Ia rasa podcast lebih cocok untuk generasi muda.</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604534/alasan-eross-candra-pilih-radio-ketimbang-podcast-ngomong-banyak-itu-pr</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eross-candra-1785853023257_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Makin Harmonis, Indra Bekti Nikmati Quality Time Antar Anak Bareng Istri</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:09:33 +0700</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Indra Bekti sibuk di dunia hiburan, namun menemukan energi dari quality time bersama keluarga. Momen sederhana seperti antar anak sekolah jadi berharga.</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604478/makin-harmonis-indra-bekti-nikmati-quality-time-antar-anak-bareng-istri</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/12/indra-bekti-dan-aldila-jelita-1762938740496_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Ummi Quary Beli Rumah Cash, Wujudkan Punya Kamar Luas dengan Walk-In Closet</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:08:58 +0700</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Ummi Quary mewujudkan impian memiliki rumah sendiri dan dirancang sesuai keinginannya. Rumahnya bergaya kastel.</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604725/ummi-quary-beli-rumah-cash-wujudkan-punya-kamar-luas-dengan-walk-in-closet</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/15/potret-ummi-quary-berhasil-punya-rumah-di-usia-24-tahun-1776213360189_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Keren! Ririe Fairus Menantang Adrenalin di Gunung, Laut hingga Air Terjun</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:06:17 +0700</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Influencer Ririe Fairus menikmati perjalanan menantang. Ririe ketagihan mendaki gunung, bermain di laut, hingga waterfall rappeling.</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604694/keren-ririe-fairus-menantang-adrenalin-di-gunung-laut-hingga-air-terjun</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ririe-fairus-1785883787376_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Duh! Kunci Koper Maia Estianty Dijebol</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 06:08:24 +0700</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Maia Estianty memberikan kabar kurang menyenangkan. Kunci kopernya dijebol.</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603956/duh-kunci-koper-maia-estianty-dijebol</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/maia-estianty-1785832840675_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Ummi Quary Ungkap 'Jimat' yang Bikin Makin Bersinar di Dunia Hiburan</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 05:05:54 +0700</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Ummi Quary meraih puncak karier di industri hiburan, bersyukur atas pencapaian dan doa ibunya. Kini, ia menikmati hidup dan mewujudkan impian memiliki rumah.</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604485/ummi-quary-ungkap-jimat-yang-bikin-makin-bersinar-di-dunia-hiburan</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/15/potret-ummi-quary-berhasil-punya-rumah-di-usia-24-tahun-1776213293631_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>BGN Ancam Tutup Dapur MBG Tak Bersertifikat Higiene hingga 10 Agustus</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:07:00 +0700</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono memberikan tenggat hingga 10 Agustus 2026 bagi seluruh dapur MBG yang belum mengantongi Sertifikat Laik Higiene Sanitasi (SLHS).</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805205447-92-1389088/bgn-ancam-tutup-dapur-mbg-tak-bersertifikat-higiene-hingga-10-agustus</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bos-bgn-ultimatum-dapur-mbg-1785936867518_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>OJK Jatuhkan Denda Rp91 M ke Pelanggar Pasar Modal per Juli 2026</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:40:53 +0700</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>OJK menjatuhkan sanksi administratif berupa denda senilai Rp91,09 miliar kepada pelaku pasar modal yang melanggar ketentuan hingga Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805132956-78-1388871/ojk-jatuhkan-denda-rp91-m-ke-pelanggar-pasar-modal-per-juli-2026</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/03/22/27752e83-1458-4306-ac22-596dc4f3664e_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Mendag Bantah Gerai Ritel Tutup Gara-gara Daya Beli Lesu</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:19:33 +0700</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso membantah anggapan penutupan sejumlah gerai ritel modern belakangan ini disebabkan melemahnya daya beli masyarakat.</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805181811-92-1389012/mendag-bantah-gerai-ritel-tutup-gara-gara-daya-beli-lesu</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/mendag-bantah-gerai-ritel-tutup-karena-daya-beli-lesu-1785929042865_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Mengenal IDA, Badan Bank Dunia yang Kini Dipimpin Sri Mulyani</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:40:35 +0700</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Eks Menkeu Sri Mulyani ditunjuk Bank Dunia menjadi Ketua Bersama Independen Asosiasi Pembangunan Internasional atau International Development Association (IDA).</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805202341-532-1389072/mengenal-ida-badan-bank-dunia-yang-kini-dipimpin-sri-mulyani</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/international-development-association-ida-1785936624293_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Purbaya Tunda Pungut Pajak Pelapak di Marketplace Demi Jaga Daya Beli</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:20:18 +0700</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya menunda penerapan pemungutan Pajak Penghasilan (PPh) Pasal 22 bagi pedagang yang berjualan melalui lokapasar (marketplace).</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805201022-532-1389070/purbaya-tunda-pungut-pajak-pelapak-di-marketplace-demi-jaga-daya-beli</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/28/purbaya-yudhi-sadewa-1782630196255_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Airlangga soal Ekonomi Tumbuh 5,45% Semester I 2026: Top di Asean</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:55:05 +0700</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Menko Airlangga Hartarto mengungkapkan pertumbuhan ekonomi Indonesia pada semester I 2026 menjadi salah satu yang terbaik di kawasan Asia Tenggara (Asean).</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805193717-532-1389055/airlangga-soal-ekonomi-tumbuh-545-semester-i-2026-top-di-asean</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/03/kemenko-perekonomian-1783046333258_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Purbaya Tambah Likuiditas Bank BUMN Rp70 T Mulai Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:35:05 +0700</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya kembali mengguyur likuiditas ke perbankan sebesar Rp70 triliun bulan ini untuk memperkuat penyaluran kredit.</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805192206-532-1389051/purbaya-tambah-likuiditas-bank-bumn-rp70-t-mulai-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/06/menteri-keuangan-purbayaa-yudhi-sadewa-1780743317258_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>BPS dan MOSPI Kerja Sama Perkuat Statistik, Tindak Lanjut Prabowo-Modi</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:22:39 +0700</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>BPS dan MOSPI India tandatangani LoI untuk perkuat kerja sama statistik, fokus pada AI, digitalisasi, dan pertukaran praktik baik untuk sistem statistik.</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805181539-537-1389010/bps-dan-mospi-kerja-sama-perkuat-statistik-tindak-lanjut-prabowo-modi</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bps-1785927403439_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>BPS: Maluku Utara hingga Kepri Pimpin Pertumbuhan Ekonomi Nasional</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:05:51 +0700</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>BPS melaporkan pertumbuhan ekonomi Indonesia triwulan II-2026 mencapai 5,29%. Maluku Utara memimpin dengan 15,35%, didorong sektor industri pengolahan.</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805180951-537-1389006/bps-maluku-utara-hingga-kepri-pimpin-pertumbuhan-ekonomi-nasional</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/12/bps-1783826441497_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Pemerintah Siap Guyur 490 Daerah Bantuan Rp20,5 T, Cair Bulan Ini</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:03:55 +0700</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Pemerintah akan menggelontorkan bantuan sebesar Rp20,5 triliun kepada 490 pemerintah daerah (pemda).</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805183301-532-1389026/pemerintah-siap-guyur-490-daerah-bantuan-rp205-t-cair-bulan-ini</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/coo-danantara-temui-menteri-keuangan-1785924321444_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>BPS: Ekonomi Indonesia Semester I-2026 Tumbuh Lebih Cepat dari 2025</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Ekonomi Indonesia tumbuh stabil 5,29% pada triwulan II 2026, didorong oleh konsumsi, investasi, dan belanja pemerintah, Ketahanan ekonomi tetap terjaga.</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805182948-537-1389025/bps-ekonomi-indonesia-semester-i-2026-tumbuh-lebih-cepat-dari-2025</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/12/19/kepala-bps-amalia-adininggar-widyasanti-1766137649621_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>BPS: Pasar Kerja Serap Lebih dari Setengah Juta Orang dalam 3 Bulan</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:33:10 +0700</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>BPS RI mencatat, penduduk bekerja berjumlah 148,19 juta orang pada Mei 2026, atau meningkat sekitar 522 ribu orang dibandingkan Februari 2026.</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805180010-537-1389003/bps-pasar-kerja-serap-lebih-dari-setengah-juta-orang-dalam-3-bulan</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/12/bps-1783826441497_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>10 Pekerjaan dengan Gaji Terbesar di RI, Apa Saja?</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:16:56 +0700</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>BPS mencatat rata-rata upah buruh di Indonesia sebesar Rp3,39 juta per bulan. Upah tertinggi di sektor Pertambangan, sedangkan terendah di Kesenian.</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805165402-78-1388974/10-pekerjaan-dengan-gaji-terbesar-di-ri-apa-saja</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/11/28/8422f4f3-606f-4f0b-97f8-85a82fd94a7f_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Saham BUMN di Kereta Cepat Bakal Dialihkan ke SMV Kemenkeu</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:19:59 +0700</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Kepemilikan saham konsorsium BUMN di PT Kereta Cepat Indonesia China (KCIC) akan dialihkan ke Special Mission Vehicle (SMV) di bawah Kementerian Keuangan.</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805170906-532-1388982/saham-bumn-di-kereta-cepat-bakal-dialihkan-ke-smv-kemenkeu</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/coo-danantara-temui-menteri-keuangan-1785924321657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Bos Danantara Temui Purbaya Bahas Restrukturisasi Utang Kereta Cepat</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:03:31 +0700</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pengelola (BP) BUMN Dony Oskaria menemui Menteri Keuangan Purbaya Yudhi Sadewa di Kantor Kementerian Keuangan, Jakarta, Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805164956-92-1388972/bos-danantara-temui-purbaya-bahas-restrukturisasi-utang-kereta-cepat</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bp-bumn-temui-purbaya-bahas-penataan-bumn-hingga-restrukturisasi-kcic-1785922688583_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Stok Aman, Zulhas Minta Bulog Operasi Pasar Demi Tekan Harga Beras</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:49:16 +0700</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pangan Zulkifli Hasan memastikan stok beras nasional dalam kondisi aman. Persediaan beras saat ini mencapai sekitar 5,2 juta ton.</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260804193641-92-1388638/stok-aman-zulhas-minta-bulog-operasi-pasar-demi-tekan-harga-beras</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/20/zulhas-kopdes-merah-putih-bakal-tampung-gabah-petani-rp6500-per-kg-1784526893164_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>IHSG Terangkat ke 6.351 Rabu Sore, 406 Saham Menguat</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:34:34 +0700</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) ditutup menguat 0,5 persen ke 6.351 pada perdagangan Selasa (4/8) sore.</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805163119-92-1388962/ihsg-terangkat-ke-6351-rabu-sore-406-saham-menguat</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/05/11/1e656f7c-100b-45e5-b9d3-3d0904b21184_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Rupiah Perkasa ke Rp17.934 per Dolar AS usai Rilis Pertumbuhan Ekonomi</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:17:50 +0700</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah menguat ke Rp17.934 per dolar AS. Penguatan ini dipicu faktor eksternal dan internal, termasuk pertumbuhan ekonomi yang positif.</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805153443-78-1388939/rupiah-perkasa-ke-rp17934-per-dolar-as-usai-rilis-pertumbuhan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/05/d2aa234f-fd7d-44de-9d1d-f775c6554ff2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Bahlil Lantik Pejabat Baru ESDM, Kepala Badan Geologi hingga Lemigas</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:02:17 +0700</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia melantik sejumlah pejabat Eselon I dan II di lingkungan Kementerian ESDM, Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805154848-85-1388952/bahlil-lantik-pejabat-baru-esdm-kepala-badan-geologi-hingga-lemigas</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/28/bahlil-sebut-ri-masih-punya-11-ribu-desa-belum-berlistrik-1785235434491_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Ragam Solusi Keuangan Bank Mega Syariah di Islamic Travel Connect 2026</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:58:39 +0700</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Kehadiran Bank Mega Syariah sebagai Official Banking Partner Islamic Travel Connect 2026 menjadi upaya mendekatkan solusi keuangan syariah dengan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805155513-625-1388954/ragam-solusi-keuangan-bank-mega-syariah-di-islamic-travel-connect-2026</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/pembukaan-islamic-travel-connect-2026-1785310868817_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Bahlil Sebut Impor Minyak dari Rusia Tahap Pertama Mulai Jalan</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:41:48 +0700</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil mengonfirmasi tahap pertama impor minyak mentah dari Rusia telah dimulai. Indonesia akan mengimpor 150 juta barel sebagai cadangan energi.</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805145831-85-1388919/bahlil-sebut-impor-minyak-dari-rusia-tahap-pertama-mulai-jalan</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bahlil-ungkap-impor-minyak-dari-rusia-tahap-pertama-sudah-berjalan-1785916375920_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Pengangguran Tertinggi RI Lulusan SMK</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:15:11 +0700</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat masih ada 7,22 juta orang pengangguran di Indonesia hingga Mei 2026. Mayoritas adalah lulusan SMA.</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805142759-92-1388904/pengangguran-tertinggi-ri-lulusan-smk</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/05/19/bursa-kerja-upaya-menekan-laju-angka-pengangguran-1747633655678_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>OJK Amankan Rp723,7 M Dana Korban Scam, 604 Ribu Rekening Diblokir</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:47:16 +0700</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>OJK memblokir 604.923 rekening terkait penipuan, mengamankan dana Rp723,7 miliar. OJK juga menindak 951 entitas keuangan ilegal hingga Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805131428-78-1388852/ojk-amankan-rp7237-m-dana-korban-scam-604-ribu-rekening-diblokir</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/12/20/a60e002e-70a9-4597-a5cb-bc4b071d3d71_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Batas Garis Kemiskinan RI Naik Jadi Rp669 Ribu per Orang per Bulan</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:18:26 +0700</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>BPS mencatat batas garis kemiskinan naik 4,33 persen dari periode September 2025 sebesar Rp641.443 menjadi Rp669.235 per kapita per bulan pada Maret 2026.</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805140916-92-1388894/batas-garis-kemiskinan-ri-naik-jadi-rp669-ribu-per-orang-per-bulan</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/07/30/ilustrasi-uang-10_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>PLN Ungkap Proyek Pembangkit Hidro 11,7 GW Perlu Investasi Rp627 T</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:57:20 +0700</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Proyek pembangkit listrik tenaga air dan pembangkit listrik tenaga minihidro yang masuk dalam RUPTL 2025-2034 membutuhkan investasi sekitar US$35 miliar.</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805132655-85-1388862/pln-ungkap-proyek-pembangkit-hidro-117-gw-perlu-investasi-rp627-t</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/07/22/logo-pln-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>FOTO: Ramai-ramai Naik MRT hingga Transjakarta di Ibu Kota</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:44:34 +0700</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik DKI Jakarta mencatat penumpang MRT, LRT, dan Transjakarta serentak melonjak sepanjang Juni 2026.</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260804182115-94-1388591/foto-ramai-ramai-naik-mrt-hingga-transjakarta-di-ibu-kota</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/masyarakat-menggunakan-transportasi-umum-mrt-jakarta-1785841998220_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Wamenkeu Juda Sebut Ekonomi 5,29 Persen Cerminkan Gairah Masih Baik</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:19:50 +0700</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Wamenkeu Juda Agung sebut optimisme tetap tinggi saat ekonomi tumbuh 5,29 persen kuartal II-2026, dengan APBN yang sehat dan daya beli terjaga.</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805124932-532-1388840/wamenkeu-juda-sebut-ekonomi-529-persen-cerminkan-gairah-masih-baik</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/02/05/perkenalan-wamenkeu-juda-agung-1770289622306_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>BNI Perluas Akses KPR lewat Danantara Housing Expo 2026 di PIK 2</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:11:15 +0700</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>BNI mendukung Danantara Housing Expo 2026 untuk memperluas akses KPR, kolaborasi dengan Himbara dan pengembang mempermudah pembiayaan perumahan.</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805124428-625-1388838/bni-perluas-akses-kpr-lewat-danantara-housing-expo-2026-di-pik-2</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bni-1785908981699_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Bank Dunia Soroti Kinerja Perusahaan RI</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:53:36 +0700</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Bank Dunia melaporkan 25 persen perusahaan di Indonesia diduga melakukan penggelapan pajak. Rekomendasi untuk perbaikan administrasi perpajakan diungkapkan.</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805120437-532-1388824/bank-dunia-soroti-kinerja-perusahaan-ri</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/12/world-bank-1781267875563_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Bea Cukai Bongkar Modus Penyelundupan Motor Harley Bekas dari China</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:39:47 +0700</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Bea Cukai Tanjung Priok mengungkap penyelundupan 5 unit motor Harley-Davidson bekas dari China yang disamarkan sebagai suku cadang. Penindakan berlanjut.</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805110613-532-1388804/bea-cukai-bongkar-modus-penyelundupan-motor-harley-bekas-dari-china</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bea-cukai-bongkar-modus-harley-davidson-bekas-masuk-ri-berkedok-part-motor-1785904346118_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Bank Dunia: Potensi Pajak RI yang Belum Tergarap Capai 6 Persen</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:28:32 +0700</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Bank Dunia ungkap potensi penerimaan pajak Indonesia belum tergarap capai 6 persen terhadap PDB.</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805114543-532-1388817/bank-dunia-potensi-pajak-ri-yang-belum-tergarap-capai-6-persen</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/10/19/ilustrasi-logo-bank-dunia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Praktis dan Cepat, Naik MRT Jakarta Pakai BRI Kartu Kredit Contactless</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:22:45 +0700</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Kini, BRI Kartu Kredit berfitur contactless resmi dapat digunakan untuk melakukan pembayaran perjalanan di MRT Jakarta.</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805120119-625-1388826/praktis-dan-cepat-naik-mrt-jakarta-pakai-bri-kartu-kredit-contactless</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/20/liburan-di-luar-negeri-makin-hemat-bri-hadirkan-promo-kartu-kredit-dengan-cashback-menarik-v2-1776687059511_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Jumlah Penduduk Miskin RI Turun Jadi 22,93 Juta Orang per Maret 2026</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:13:29 +0700</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>BPS mencatat jumlah penduduk miskin RI sebanyak 22,93 juta orang per Maret 2026, turun 0,43 persen dibandingkan angka kemiskinan per September 2025.</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805115126-532-1388820/jumlah-penduduk-miskin-ri-turun-jadi-2293-juta-orang-per-maret-2026</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/05/11/d2e50ccf-fe1e-40ce-9967-9d6c19b33c8f_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Pengangguran RI Turun Jadi 7,22 Juta Orang per Mei 2026</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:49:42 +0700</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>BPS mencatat jumlah pengangguran di Indonesia turun 24 ribu orang menjadi 7,22 juta orang per Mei 2026 dibandingkan data pengangguran Februari 2026.</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805113458-532-1388810/pengangguran-ri-turun-jadi-722-juta-orang-per-mei-2026</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/07/17/berharap-pada-bursa-kerja-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Ekonomi RI Tumbuh 5,29 Persen pada Kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:22:51 +0700</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>BPS mencatat ekonomi Indonesia tumbuh 5,29 persen di kuartal II 2026 secara tahunan (yoy) bila dibandingkan kuartal II 2025, yang tumbuh 5,12 persen.</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805104538-532-1388799/ekonomi-ri-tumbuh-529-persen-pada-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/04/09/menjelang-lebaran-pasar-minggu-ramai-pembeli-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>BPKH Salurkan Rp2,06 Triliun Nilai Manfaat Tahap I Tahun 2026</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:17:20 +0700</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Pengelolaan dan penyaluran nilai manfaat dilakukan sesuai prinsip syariah dengan mengedepankan transparansi, dan kehati-hatian.</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805111336-625-1388806/bpkh-salurkan-rp206-triliun-nilai-manfaat-tahap-i-tahun-2026</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bpkh-1785903390498_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>VKTR Sebut Kendaraan Listrik Bisa Pangkas 40 Persen Biaya Operasional</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:08:31 +0700</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>PT VKTR Teknologi Mobilitas mengungkapkan bahwa kendaraan listrik komersial dapat mengurangi biaya operasional hingga 40 persen.</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805103419-92-1388791/vktr-sebut-kendaraan-listrik-bisa-pangkas-40-persen-biaya-operasional</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/yana-aditya-1785902774919_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>BPS Waspadai Lonjakan Harga Bawang Putih, Kini Meluas ke 248 Daerah</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:42:37 +0700</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>BPS mengingatkan kenaikan harga bawang putih yang meluas di Indonesia, berpotensi mendorong inflasi. Rata-rata harga mencapai Rp42.005/kg, di atas HAP.</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260804131444-92-1388434/bps-waspadai-lonjakan-harga-bawang-putih-kini-meluas-ke-248-daerah</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/12/16/indonesia-pengimpor-bawang-putih-terbesar-di-dunia-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Dekatkan Akses Perbankan, Agen BRILink Dukung Finansial Warga Alor NTT</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:35:07 +0700</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Kehadiran jaringan BRILink Agen di Kepulauan Alor, NTT memperlihatkan bahwa layanan perbankan dapat berpadu harmonis dengan kearifan lokal.</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805103158-625-1388789/dekatkan-akses-perbankan-agen-brilink-dukung-finansial-warga-alor-ntt</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/24/bri-1774327283986_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Harga Minyak Dunia Stabil di US$79, Pasar Pantau Negosiasi AS-Iran</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:29:45 +0700</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Harga minyak dunia bergerak stabil di US$79 pada Rabu (5/8), setelah anjlok dua hari beruntun. Pasar tengah mencermati perkembangan negosiasi AS-Iran.</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805101806-85-1388781/harga-minyak-dunia-stabil-di-us-79-pasar-pantau-negosiasi-as-iran</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/11/09/392f0742-2856-4ece-966c-1c95cfad4b54_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Turun Tipis Jadi Rp2,599 Juta per Gram</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:45:18 +0700</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Harga emas Antam turun Rp4.000 menjadi Rp2,599 juta per gram pada Rabu (5/8), harga buyback emas juga turun menjadi Rp2,370 juta per gram.</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805093038-92-1388771/harga-emas-antam-turun-tipis-jadi-rp2599-juta-per-gram</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/02/harga-logam-mulia-naik-di-atas-2-juta-rupiah-per-gram-1756793367276_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Rupiah Bangkit ke Rp17.974 per Dolar AS Pagi Ini</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:30:15 +0700</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah berada di level Rp17.974 per dolar AS pada Rabu (5/8) pagi, menguat 53 poin atau 0,29 persen dibandingkan penutupan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805092144-78-1388768/rupiah-bangkit-ke-rp17974-per-dolar-as-pagi-ini</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/06/29/3c4aeff7-59bb-409a-b013-ab97b5710d78_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Apa Tugas Sri Mulyani Pimpin Pendanaan Bank Dunia untuk Negara Miskin?</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:15:23 +0700</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Sri Mulyani mendapat tugas baru dari Bank Dunia. Ia ditunjuk sebagai Ketua Bersama Independen untuk pendanaan ke negara-negara termiskin. Apa saja tugasnya?</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805084930-78-1388753/apa-tugas-sri-mulyani-pimpin-pendanaan-bank-dunia-untuk-negara-miskin</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/02/07/pemberian-thr-dan-gaji-ke-13-asn-2024_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Bos BPKH Usulkan 3 Poin di Revisi UU Pengelolaan Keuangan Haji</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:10:25 +0700</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pelaksana BPKH Fadlul Imansyah menyampaikan 3 poin usulan dalam revisi UU Pengelolaan Keuangan Haji.</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805083135-78-1388739/bos-bpkh-usulkan-3-poin-di-revisi-uu-pengelolaan-keuangan-haji</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/22/kepala-badan-pengelola-keuangan-haji-bpkh-fadlul-imansyah-1784697917780_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Bos BPKH Ungkap Pentingnya Revisi UU Pengelolaan Keuangan Haji</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:30:49 +0700</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Kepala BPKH Fadlul Imansyah mengatakan revisi UU Pengelolaan Keuangan Haji mendesak untuk memperkuat lembaganya, maksimalkan pengelolaan keuangan haji.</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805075927-78-1388728/bos-bpkh-ungkap-pentingnya-revisi-uu-pengelolaan-keuangan-haji</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/22/kepala-badan-pengelola-keuangan-haji-bpkh-fadlul-imansyah-1784697917696_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Utang Pinjol Warga RI Tembus Rp105 T per Juni 2026</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:30:02 +0700</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>OJK mencatat utang pinjaman online (pinjol) warga RI mencapai Rp105,14 triliun pada Juni 2026, tumbuh nyaris 26 persen secara tahunan.</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805081754-78-1388736/utang-pinjol-warga-ri-tembus-rp105-t-per-juni-2026</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/03/10/51015286-ad27-4317-bedc-15681268fa6d_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Purbaya Bakal Jor-joran Kejar Pertumbuhan Ekonomi 6 Persen</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:15:34 +0700</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya akan mengerahkan seluruh instrumen kebijakan fiskal untuk mendorong laju ekonomi RI tembus 6 persen pada paruh kedua 2026.</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260804200138-532-1388644/purbaya-bakal-jor-joran-kejar-pertumbuhan-ekonomi-6-persen</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/28/purbaya-yudhi-sadewa-1782630196337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>PMI Pulih, Mampukah Industri Kembali Jadi Mesin Penyerap Tenaga Kerja?</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:45:56 +0700</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Endrapta Ibrahim Pramudhiaz</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>PMI manufaktur RI menunjukkan tanda pemulihan, tetapi kenaikan aktivitas industri tak otomatis diikuti lonjakan penyerapan tenaga kerja. Apa penghambatnya?</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805071603-92-1388716/pmi-pulih-mampukah-industri-kembali-jadi-mesin-penyerap-tenaga-kerja</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/10/28/target-produksi-gesits-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Bank Dunia Tunjuk Sri Mulyani Pimpin Pendanaan bagi Negara Miskin</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:13:40 +0700</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Bank Dunia menunjuk Sri Mulyani sebagai Ketua Bersama Independen IDA22 untuk memimpin proses pengisian kembali pendanaan bagi negara-negara termiskin.</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805063432-78-1388694/bank-dunia-tunjuk-sri-mulyani-pimpin-pendanaan-bagi-negara-miskin</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/03/19/menkeu-sampaikan-hasil-lelang-sun-1742354784054_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Bos BGN: Putusan MK Tegaskan MBG Program Konstitusional</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 06:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono menegaskan Putusan Mahkamah Konstitusi (MK) Nomor 40/PUU-XXIV/2026 tidak membatalkan program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260804204058-92-1388668/bos-bgn-putusan-mk-tegaskan-mbg-program-konstitusional</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/22/pelantikan-kepala-bgn-1784719019609_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>IHSG Berpeluang Menguat Hari Ini</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 06:18:50 +0700</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>IHSG masih berpeluang melanjutkan penguatan pada hari ini setelah berhasil ditutup di atas resistance Fibonacci pada perdagangan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805061137-92-1388690/ihsg-berpeluang-menguat-hari-ini</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/10/04/e0a11d43-eeec-4d3d-9942-e3eb583f1b92_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>DPRD Kota Bandung Dorong Pemkot Tempuh Jalur Pidana dan Gugatan Perdata usai Penebangan 10 Pohon</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:38:50 +0700</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>DPRD Kota Bandung mendesak Pemkot menempuh jalur pidana dan gugatan perdata atas dugaan penebangan 10 pohon terkait pembangunan lapangan padel.</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8262469/dprd-kota-bandung-dorong-pemkot-tempuh-jalur-pidana-dan-gugatan-perdata-usai-penebangan-10-pohon</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/UpP7sc1Ot5ohyIVX6YmqSx4Fjpg=/1x209:652x576/673x379/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316069/original/040533500_1785911653-WhatsApp_Image_2026-08-05_at_09.55.35.jpeg</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Misteri Belum Terungkap di Kasus Mutilasi Depok</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:40:48 +0700</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Hingga kini penyidik belum bisa memastikan motif pembunuhan.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263016/misteri-belum-terungkap-di-kasus-mutilasi-depok</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/3_XSuRpVsw7mR1OINb8kGSne_JA=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316566/original/060113700_1785945727-WhatsApp_Image_2026-08-05_at_22.56.47.jpeg</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BGN Buka Peluang Libatkan Polisi Tangani Kasus Keracunan MBG</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:10:56 +0700</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>BGN menerapkan zero tolerance terhadap kasus keracunan MBG dan membuka peluang proses hukum.</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263006/bgn-buka-peluang-libatkan-polisi-tangani-kasus-keracunan-mbg</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/ft5RpJQOKXVR5Bh-0hFTur8iEe4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316569/original/082983400_1785946244-IMG_20260805_192842_7.jpg</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Pembangunan Ulang JPO Tendean Segera Dimulai</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:51:59 +0700</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Pramono targetkan pembangunan JPO Tendean dimulai sebulan lagi dengan dana KLB.</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8262982/pembangunan-ulang-jpo-tendean-segera-dimulai</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/jcK08spOXGDFORgPIpvhIuxAg_s=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9296043/original/072828100_1784002054-jpo3.jpg</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Pelaku Ungkap Kejadian di Kontrakan Depok Sebelum Mutilasi Korban</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:12:06 +0700</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Mulanya ngobrol, keduanya lalu cekcok setelah pelaku tak terima perlukan korban.</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263008/pelaku-ungkap-kejadian-di-kontrakan-depok-sebelum-mutilasi-korban</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/nL-1NACsbaple0t5I0Qz46rte9U=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315667/original/014986000_1785849701-IMG-20260804-WA0059.jpg</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Menkes dan BGN Duduk Bareng Ahli Gizi, Bahas Perbaikan MBG</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 23:00:19 +0700</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Menkes dan Kepala BGN tampung masukan ahli gizi untuk menyempurnakan program Makan Bergizi Gratis.</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8262997/menkes-dan-bgn-duduk-bareng-ahli-gizi-bahas-perbaikan-mbg</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/ARGPzDf4e-K7LN1STvky-4rUwJ8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316561/original/079250100_1785945500-IMG_20260805_193900_073.jpg</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Pramono Akan Naikkan Obligasi Jakarta Jadi Rp 5,2 Triliun, Danai LRT dan RS</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:47:03 +0700</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Pramono siapkan tambahan obligasi Rp 5,2 triliun untuk transportasi dan layanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8262977/pramono-akan-naikkan-obligasi-jakarta-jadi-rp-52-triliun-danai-lrt-dan-rs</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/dzFIKCF_wDbyPkwkbAWNsU258Zk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9302848/original/085647000_1784609552-ab3b2fbd-8e35-4c1f-a920-756d2ae111d9.jpeg</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Mendagri Siapkan Tiga Langkah Atasi Kendala Gaji Pegawai Pemda</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:01:05 +0700</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Tito Karnavian siapkan solusi bagi daerah yang kesulitan membayar gaji pegawai dan PPPK.</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8262956/mendagri-siapkan-tiga-langkah-atasi-kendala-gaji-pegawai-pemda</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/JUNSBqHfo466X4m281T3pcQNcws=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316536/original/093294100_1785940101-WhatsApp_Image_2026-08-05_at_20.44.14.jpeg</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Modus 3 Wanita Malaysia Selundupkan Narkoba Lewat Soetta</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:12:00 +0700</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Bea Cukai Soetta mengamankan tiga wanita Malaysia yang membawa tiga jenis narkotika. Begini modusnya.</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8262951/modus-3-wanita-malaysia-selundupkan-narkoba-lewat-soetta</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/lFTAOjrr32zgtYxmWSivpa-4oN0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4248353/original/049118000_1670043673-sabu_sabu.jpg</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I684"/>
+  <autoFilter ref="A1:I764"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$798</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I764"/>
+  <dimension ref="A1:I798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -36342,8 +36342,1606 @@
         </is>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Detik-detik Kebakaran Besar Pabrik Kimia di Sao Paulo Brasil</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Kebakaran besar melanda sebuah pabrik kimia di Itaquaquecetuba, Sao Paulo, Brasil, Selasa (4/8).</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805084401-139-1388750/detik-detik-kebakaran-besar-pabrik-kimia-di-sao-paulo-brasil</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/thumbnail-video-1785894379508_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Penampakan Ratusan Migran dari Maroko Bertahan di Pantai Ceuta</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>REUTERS</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Ratusan migran yang berhasil menyeberang ke Ceuta, kota otonom Spanyol di Afrika Utara, bertahan di pantai pada Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805143408-139-1388909/penampakan-ratusan-migran-dari-maroko-bertahan-di-pantai-ceuta</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/thumbnail-video-1785915391266_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Polisi Korsel Geledah Kantor Starbucks buntut Kontroversi Iklan</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:30:15 +0700</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Kantor pusat Starbucks Korsel digeledah buntut kontroversi iklan "Tank Day", lantaran diresmikan bersamaan dengan Hari Gerakan Demokratisasi.</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805153946-113-1388948/polisi-korsel-geledah-kantor-starbucks-buntut-kontroversi-iklan</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/06/04/ilustrasi-bendera-korea-selatan-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Malaysia Kerahkan Polisi di Bandara usai Pilot Bawa Narkoba ke RI</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:00:25 +0700</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Malaysia bakal kerahkan polisi berjaga di bandara usai kasus pilot Malaysia Airlines ditangkap karena selundupkan narkoba ke Indonesia.</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805202348-106-1389073/malaysia-kerahkan-polisi-di-bandara-usai-pilot-bawa-narkoba-ke-ri</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/21/bandara-internasional-kuala-lumpur-1755751783753_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Putin Tunjuk Denis Lyamin Jadi Komandan Pasukan Drone Rusia</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Presiden Rusia Vladimir Putin menunjuk Denis Lyamin untuk memimpin Pasukan Sistem Tak Berawak Rusia.</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805193732-134-1389057/putin-tunjuk-denis-lyamin-jadi-komandan-pasukan-drone-rusia</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/ukraine-crisisrussia-putin-1785934461367_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Tukang Sampah di Italia Nemu Tiket Lotre Rp20 M yang Terbuang</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Seorang tukang sampah di Italia menemukan tiket lotre senilai satu juta euro (sekitar Rp20 miliar) yang terbuang di antara tumpukan sampah.</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805191140-134-1389046/tukang-sampah-di-italia-nemu-tiket-lotre-rp20-m-yang-terbuang</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/tukang-sampah-di-italia-1785932383182_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Trump Sesumbar Selat Hormuz Segera Dibuka: Jika Tidak, Kami Serang</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:11:08 +0700</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Trump sesumbar Selat Hormuz akan segera dibuka, ancam lanjut serang Iran jika perairan strategis itu tak dibuka.</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805124939-134-1388841/trump-sesumbar-selat-hormuz-segera-dibuka-jika-tidak-kami-serang</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/donald-trump-1783564607045_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Adik Kim Jong Un Tantrum Jepang Uji Tomahawk: Mereka Akan Menyesal</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:28:45 +0700</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Adik pemimpin Korut Kim Jong Un, Kim Yo Jong, mewanti-wanti akan mengadopsi opsi militer tambahan usai Jepang meluncurkan uji coba rudal Tomahawk buatan AS.</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805145149-113-1388915/adik-kim-jong-un-tantrum-jepang-uji-tomahawk-mereka-akan-menyesal</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/08/16/adik-kim-jong-un-kim-yo-jong_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>15 Gajah Mati di Kebun Binatang Kenya Diduga Keracunan Pestisida</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:50:23 +0700</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Belasan gajah di kebun binatang Kenya mati diduga keracunan sianida dalam pestisida yang disemprotkan pada tanaman tomat.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805170525-127-1388978/15-gajah-mati-di-kebun-binatang-kenya-diduga-keracunan-pestisida</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/03/28/323e0dff-d7d8-4ec9-921c-0720d6bd3118_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Daftar Ancaman Trump ke Iran yang Cuma Omong Kosong</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:20:02 +0700</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Trump lagi-lagi membatalkan ancamannya untuk menyerang Iran secara brutal, sebut negosiasi sedang berlanjut.</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805150205-134-1388922/daftar-ancaman-trump-ke-iran-yang-cuma-omong-kosong</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/18/topshot-fbl-wc-club-2025-match63-chelsea-psg-1752800527475_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>'In This Economy', Jepang Pangkas Pajak Makanan Jadi 1 Persen</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:49:26 +0700</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Pemerintah Jepang dukung rencana PM Takaichi pangkas pajak konsumsi bahan pangan jadi 1 persen, berlaku mulai April 2027.</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805162008-113-1388958/in-this-economy-jepang-pangkas-pajak-makanan-jadi-1-persen</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/10/21/sanae-takaichi-1761020717051_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Kasus Pilot Malaysia Bawa 26 Kg Ekstasi Dibahas di Rapat Kabinet Anwar</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:10:18 +0700</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Kasus pilot Malaysia yang membawa 26 kilogram ekstasi dibahas dalam rapat kabinet Perdana Menteri Malaysia Anwar Ibrahim, Rabu (5/8) waktu setempat.</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805155857-106-1388955/kasus-pilot-malaysia-bawa-26-kg-ekstasi-dibahas-di-rapat-kabinet-anwar</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/11/04/asean-summit-1762217054048_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Influencer Meksiko Tewas Ditembak saat Live Bareng Teman</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:33:06 +0700</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Influencer asal Meksiko Cesar Gastelum tewas ditembak saat siaran langsung bersama teman-temannya di luar restoran di Culiacan, Selasa (4/8).</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805152149-113-1388935/influencer-meksiko-tewas-ditembak-saat-live-bareng-teman</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/07/12/ilustrasi-penembakan-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>AS Panik Kehabisan Hampir 80 Persen Rudal Pertahanan Lawan Iran</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:41:44 +0700</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Amerika Serikat panik mulai kehabisan hampir 80 persen rudal pertahanan udara di tengah perang melawan Iran yang belum kunjung usai.</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805141638-120-1388897/as-panik-kehabisan-hampir-80-persen-rudal-pertahanan-lawan-iran</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/10/14/sistem-anti-rudal-jarak-jauh-as-thaad_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Dilarang China, Mangga Asal Taiwan Ludes Dijual di Eropa</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:13:07 +0700</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Mangga Irwin asal Taiwan ludes terjual di Prancis, dibanderol dengan harga €99,90 atau sekitar Rp2.073.000 per kilogram.</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804200954-113-1388647/dilarang-china-mangga-asal-taiwan-ludes-dijual-di-eropa</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/mangga-irwin-1785849977810_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Gempa M 6,3 Guncang Filipina, Warga Panik Berlarian</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:38:43 +0700</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 6,3 mengguncang wilayah lepas pantai Filipina selatan pada Rabu (5/8) siang. Gempa memicu kepanikan warga.</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805133148-106-1388872/gempa-m-63-guncang-filipina-warga-panik-berlarian</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/07/07/6101e4a4-1ee2-47a5-9838-13986a0c8632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Qatar Minta Dunia Desak Israel karena Gempur Gaza dan Ogah Gencatan</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Qatar meminta komunitas internasional untuk menekan Israel yang berusaha menggagalkan rencana implementasi fase kedua gencatan senjata di Jalur Gaza, Palestina.</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805125230-120-1388842/qatar-minta-dunia-desak-israel-karena-gempur-gaza-ogah-gencatan</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/09/16/ilustrasi-bendera-qatar_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Iran Klaim Bikin Hancur Fasilitas AS di Timteng dalam Perang 17 Hari</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:18:24 +0700</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Iran mengeklaim pasukan militer mereka barhasil meluluhlantakkan fasilitas militer AS di negara-negara Timur Tengah dalam perang 17 hari.</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805120744-120-1388827/iran-klaim-bikin-hancur-fasilitas-as-di-timteng-dalam-perang-17-hari</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/23/trump-kesulitan-lindungi-50-ribu-tentara-as-dari-serangan-iran-1784792921895_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Perang AS-Iran, Irak Masih Bisa Ekspor Minyak 30 Juta Barel via Hormuz</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:40:17 +0700</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Penutupan Selat Hormuz akibat perang Amerika Serikat dan Iran tampaknya tidak terlalu berpengaruh bagi Irak.</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805112830-120-1388809/perang-as-iran-irak-masih-bisa-ekspor-minyak-30-juta-barel-via-hormuz</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/03/kapal-kapal-di-selat-hormuz-1780451799971_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>China-AS Perang AI Buat Program Rencana Serangan Udara Masif</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>China dan Amerika Serikat semakin sengit perang program akal imitasi (AI) untuk membantu rencana serangan udara secara masif.</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804194309-113-1388639/china-as-perang-ai-buat-program-rencana-serangan-udara-masif</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/03/china-pamer-rudal-balistik-dan-peluru-kendali-berhulu-ledak-nuklir-1756882895972_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Thailand Mau Pecat Hampir 6 Ribu PNS yang Curang saat Ujian Masuk</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Thailand mengungkapkan sebanyak 5.925 pegawai negeri sipil (PNS) berpotensi kehilangan pekerjaan menyusul penemuan kecurangan dalam ujian masuk.</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805102033-106-1388782/tetangga-ri-mau-pecat-hampir-6-ribu-pns-imbas-curang-saat-ujian-masuk</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/20/megah-dan-sakral-intip-pesona-patung-emas-phra-dhammakaya-thep-mongkol-1779284748718_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Netanyahu Ogah Manut Trump, Tolak Gencatan dan Tarik Pasukan dari Gaza</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>PM Benjamin Netanyahu menolak gencatan senjata dan penarikan pasukan Israel dari Jalur Gaza, Palestina, sesuai usulan peta jalan AS di Board of Peace (BoP).</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805101229-120-1388778/netanyahu-ogah-manut-trump-tolak-gencatan-tarik-pasukan-dari-gaza</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/18/benjamin-netanyahu-1784376170985_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>AS Kelimpungan Stok Rudal Terancam Kosong Gegara Perang Trump vs Iran</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Militer AS dilaporkan telah menghabiskan sebagian besar persediaan global rudal jarak jauh berpresisi tinggi imbas memerangi Iran selama lima bulan terakhir.</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805085106-134-1388766/as-kelimpungan-stok-rudal-terancam-kosong-gegara-perang-trump-vs-iran</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/06/presiden-amerika-donald-trump-1780743428817_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Duka Pemakaman 112 Jenazah Keluarga Besar Gaza Korban Serangan Israel</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>REUTERS</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Warga Gaza menggelar pemakaman jenazah 112 anggota satu keluarga besar yang tewas dalam agresi Israel hampir tiga tahun lalu, Selasa (4/8).</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805070532-124-1388711/duka-pemakaman-112-jenazah-keluarga-besar-gaza-korban-serangan-israel</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/thumbnail-video-1785888476661_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Pria Bersenjata Ditangkap saat Menyusup Lapangan Golf Trump di LA</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 09:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Seorang pria bersenjata ditangkap di lapangan golf milik Presiden Amerika Serikat Donald Trump di Los Angeles, pada Minggu (2/8) akhir pekan lalu.</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805083257-134-1388749/pria-bersenjata-ditangkap-saat-menyusup-lapangan-golf-trump-di-la</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/06/17/canada-g7-summit-diplomacy-1750140219859_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Houthi Gempur Pangkalan Udara Arab Saudi, Bandara Setop Beroperasi</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:40:59 +0700</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Milisi Houthi Yaman melancarkan serangan udara menargetkan Bandara Najran di Arab Saudi pada Selasa (4/8) hingga operasional di bandara itu terpaksa dihentikan.</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805073409-120-1388726/houthi-gempur-pangkalan-udara-arab-saudi-bandara-setop-beroperasi</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/14/yemen-saudi-conflict-aviation-1783995473575_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Dalam Sepekan 5 WN Malaysia Dibekuk Imbas Selundupkan Narkoba ke RI</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:10:19 +0700</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Sebanyak lima warga negara Malaysia ditangkap dalam kurun waktu sepekan terakhir lantaran membawa narkoba ke Indonesia.</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805080707-106-1388731/dalam-sepekan-5-wn-malaysia-dibekuk-imbas-selundupkan-narkoba-ke-ri</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Serang Iran dari Dalam, Kenapa Kurdi Menentang Kekuasaan Ayatollah?</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Kekuatan militer Iran mulai mendapat perlawanan dari dalam negeri mereka sendiri, yakni dari etnis Kurdi.</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804204501-120-1388666/serang-iran-dari-dalam-kenapa-kurdi-menentang-kekuasaan-ayatollah</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/09/bentrokan-tentara-suriah-dan-milisi-kurdi-pecah-di-aleppo-1767941419019_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Malaysia Respons Warga Johor Ditangkap di RI Bawa 1.089 Ekstasi</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 07:06:43 +0700</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Kepolisian Malaysia mengonfirmasi warga asal Johor berinisial DI ditangkap di Bandara Juanda usai kedapatan membawa 1.089 ekstasi.</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805070012-106-1388702/malaysia-respons-warga-johor-ditangkap-di-ri-bawa-1089-ekstasi</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/07/24/ilustrasi-narkoba_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>RI Kecam Serangan Baru Israel ke Jalur Gaza: Sengaja Hambat Peace Plan</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 06:30:06 +0700</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Indonesia mengecam keras serangan militer Israel ke Jalur Gaza Palestina baru-baru ini yang kembali menambah korban tewas agresi brutal sejak Oktober 2023 lalu.</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805062652-106-1388693/ri-kecam-serangan-baru-israel-ke-jalur-gaza-sengaja-hambat-peace-plan</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/momen-serangan-udara-israel-hantam-masjid-di-gaza-1785308539451_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Presiden Iran Diisukan Mundur dan Malaysia Bingung Pilot Bawa Ekstasi</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 05:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Situasi politik Iran di tengah peperangan dengan AS hingga kasus pilot Malaysia membawa 26 Kg narkoba ke RI menjadi sorotan berita internasional, Selasa (4/8).</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805054642-113-1388689/presiden-iran-diisukan-mundur-dan-malaysia-bingung-pilot-bawa-ekstasi</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/06/presiden-iran-masoud-pezeshkian-1778042263339_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Pengadilan Israel Blokir Rencana Parit Buaya di Penjara Palestina</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 05:15:49 +0700</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Pengadilan Israel dilaporkan memblokir rencana penggalian parit berisi buaya di sekitar penjara yang menahan warga Palestina.</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804140816-120-1388470/pengadilan-israel-blokir-rencana-parit-buaya-di-penjara-palestina</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/11/25/ilustrasi-penjara-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Detik-detik Pesawat Nirawak Hantam Pantai Rusia</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 04:00:24 +0700</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Video Viral</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Pesawat nirawak menghantam area pantai di wilayah selatan Gelendzhik, Rusia pada Senin (3/8).</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804102846-139-1388337/detik-detik-pesawat-nirawak-hantam-pantai-rusia</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/thumbnail-video-1785814307057_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Detik-detik Kebakaran Dahsyat Hanguskan Gudang di China</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 03:00:47 +0700</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Asap hitam pekat membumbung tinggi di atas Kota Qingdao, China timur, setelah kebakaran melanda sebuah gudang logistik pada Sabtu (2/8) malam.</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804141330-117-1388472/detik-detik-kebakaran-dahsyat-hanguskan-gudang-di-china</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/thumbnail-video-1785827677546_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I764"/>
+  <autoFilter ref="A1:I798"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-05.xlsx
+++ b/data/berita_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$798</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$834</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I798"/>
+  <dimension ref="A1:I834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37940,8 +37940,1700 @@
         </is>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Laba Pengelola RS Hermina (HEAL) Anlok 14%, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:10:17 +0700</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>PT Medikaloka Hermina Tbk. (HEAL) mencatat penurunan laba bersih 14,08% di paruh pertama 2026 meski pendapatan tumbuh 6,51% menjadi Rp3,60 triliun.</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805171008-17-756877/laba-pengelola-rs-hermina--heal--anlok-14-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/10/11/presiden-joko-widodo-jokowi-meresmikan-rumah-sakit-hermina-di-nusantara-kalimantan-timur-jumat-11102024-ia-menyebut-rumah-saki-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Perkuat Peran Perbankan, BRI Dukung Kebijakan Penempatan Dana SAL</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:09:19 +0700</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>BRI menyambut positif kebijakan penempatan dana SAL pemerintah untuk stabilitas likuiditas. Fokus pada penyaluran kredit berkualitas, terutama untuk UMKM.</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805210257-17-756931/perkuat-peran-perbankan-bri-dukung-kebijakan-penempatan-dana-sal</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/bri-1785938937254_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Purbaya Beri Sinyal China Mau Garap KA Cepat Bandung-Surabaya</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:05:32 +0700</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengungkapkan ketertarikan China untuk proyek kereta cepat hingga Jawa Timur, didukung oleh Presiden Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805185106-17-756907/purbaya-beri-sinyal-china-mau-garap-ka-cepat-bandung-surabaya</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/16/kereta-cepat-whoosh-1758006445490_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>WIKA Kebut Proyek Tol Jakarta-Cikampek II Selatan, Progres 85,20%</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:13:58 +0700</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>PT Wijaya Karya (WIKA) percepat pembangunan Jalan Tol Jakarta-Cikampek II Selatan Paket 2A dengan progres 85,20% dan target selesai Kuartal I 2027.</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805190921-17-756919/wika-kebut-proyek-tol-jakarta-cikampek-ii-selatan-progres-8520</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/jalan-tol-jakarta-cikampek-ii-selatan-1785932015629_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Bos Danantara Bocorkan IPO Pegadaian, Pelindo hingga Injourney</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 19:12:34 +0700</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Sejumlah perusahaan pelat merah atau Badan Usaha Milik Negara (BUMN) akan didorong untuk menjadi perusahaan publik dalam waktu dekat.</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805191039-17-756920/bos-danantara-bocorkan-ipo-pegadaian-pelindo-hingga-injourney</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/31/kepala-bp-bumn-sekaligus-coo-danantara-indonesia-dony-oskaria-saat-ditemui-di-istana-merdeka-jakarta-jumat-3172026-1785502950718_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Bos Kopi FORE Kasih Bocoran Soal Dividen</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:20:41 +0700</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Fore Kopi Indonesia belum dapat membagikan dividen karena saldo laba ditahan negatif. Namun, perusahaan berkomitmen untuk membagikan dividen di masa depan.</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805170540-17-756872/bos-kopi-fore-kasih-bocoran-soal-dividen</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/01/08/fore-coffee-dok-gallery-fore-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Purbaya Tambah Suntikan SAL Rp 70 T di Himbara, BTN dan BSI Dapat Jatah</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:11:38 +0700</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Robertus Andrianto</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya Yudhi Sadewa menambah Rp70 triliun dana SAL ke Himbara. Suntikan dana dilakukan bertahap, dengan BTN dan BSI masing-masing Rp10 triliun.</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805180938-17-756903/purbaya-tambah-suntikan-sal-rp-70-t-di-himbara-btn-bsi-dapat-jatah</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/purbaya-yudhi-sadewa-menteri-keuangan-nufransa-wira-sakti-plt-direktur-jenderal-perimbangan-keuangan-dan-ubaidillah-amin-staf--1785916718720_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Video: Ekonomi RI H1-2026 Tumbuh 5,45%, Termasuk Tertinggi di ASEAN</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:49:07 +0700</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Airlangga: PDB RI H1-2026 Tumbuh 5,45%,Termasuk Tinggi di ASEAN</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805173341-19-756880/video-ekonomi-ri-h1-2026-tumbuh-545-termasuk-tertinggi-di-asean</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/airlangga-pdb-ri-h1-2026-tumbuh-545termasuk-tinggi-di-asean-1785926720666_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Pakai Strategi Ini, OJK Dorong BPD Kembangkan UMKM</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:45:11 +0700</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>OJK dorong BPD untuk kembangkan akses kredit bagi UMKM. Fokus pada ekosistem dan pendekatan community bank untuk memberdayakan masyarakat lokal.</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805172626-17-756878/pakai-strategi-ini-ojk-dorong-bpd-kembangkan-umkm</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/tak-hanya-andalkan-pemda-ojk-mau-bpd-kreatif-kumpulkan-dpk-ajak-warga-menabung-1785913789909_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Video: 3 Progam Grup KUB Bank Jatim, Dongkrak Kredit dan Digitalisasi</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:44:45 +0700</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>3 Progam Andalan Grup KUB Bank Jatim Dongkrak Kredit dan Layanan Digital BPD</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805161841-19-756842/video-3-progam-grup-kub-bank-jatim-dongkrak-kredit-digitalisasi</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/3-progam-andalan-grup-kub-bank-jatim-dongkrak-kredit-layanan-digital-bpd-1785922817327_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Laba Tembus Rp1,11 T, MTEL Genjot Pertumbuhan Bisnis di Luar Menara</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:28:19 +0700</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Mitratel mencatat pertumbuhan laba dan pendapatan yang solid di Semester I 2026, memperkuat transformasi menjadi Next-Gen Tower Company.</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805172455-17-756876/laba-tembus-rp111-t-mtel-genjot-pertumbuhan-bisnis-di-luar-menara</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/04/20/infrastruktur-digital_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>BEI Tambah Saham HSC, Ini Daftar Lengkap 54 Emiten Terbaru</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:20:21 +0700</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Mentari Puspadini</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia menambah 55 saham dengan High Shareholding Concentration (HSC). Saham dikuasai entitas terkonsentrasi, meningkatkan risiko bagi investor.</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805170021-17-756869/bei-tambah-saham-hsc-ini-daftar-lengkap-54-emiten-terbaru</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018492_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Bos BPD Ungkap Peluang Sinergi dengan BPR dan BPRS</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:12:24 +0700</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Teti Purwanti</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Industri BPD menjajaki kerja sama dengan BPR dan BPRS untuk sinergi yang saling menguntungkan. Kerja sama ini diharapkan mendorong akses layanan ke pasar mikro</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805165905-17-756868/bos-bpd-ungkap-peluang-sinergi-dengan-bpr-dan-bprs</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/direktur-utama-bank-jakarta-agus-haryoto-widodo-saat-menyampaikan-pemaparan-dalam-acara-regional-bank-summit-2026-di-jakarta-r-1785916201784_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Video: Bos Bank Jakarta: Ekonomi RI Tumbuh Positif, BPD Ikut Bertumbuh</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:12:00 +0700</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Bos Bank Jakarta: Ekonomi RI Tumbuh Positif, BPD Mampu Jaga Pertumbuhan Aset dan Laba</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805161851-19-756840/video-bos-bank-jakarta-ekonomi-ri-tumbuh-positif-bpd-ikut-bertumbuh</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/bos-bank-jakarta-ekonomi-ri-tumbuh-positif-bpd-mampu-jaga-pertumbuhan-aset-dan-laba-1785922735158_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Purbaya Tegaskan Kemenkeu Ambil Alih Seluruh Saham BUMN di Whoosh</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:51:53 +0700</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya Yudhi Sadewa memastikan utang KCIC akan diambil alih pemerintah. Konsorsium tetap ada, dengan 60% saham Indonesia dan 40% China.</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805164803-17-756853/purbaya-tegaskan-kemenkeu-ambil-alih-seluruh-saham-bumn-di-whoosh</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/purbaya-yudhi-sadewa-menteri-keuangan-nufransa-wira-sakti-plt-direktur-jenderal-perimbangan-keuangan-dan-ubaidillah-amin-staf--1785916718720_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Video: Bos Bank Jatim "Pamer" Keberhasilan Sinergi BPD Lewat KUB</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:49:07 +0700</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Bos Bank Jatim Pamer Keberhasilan Sinergi BPD Lewat KUB, Daya Saing Naik</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805161840-19-756838/video-bos-bank-jatim-pamer-keberhasilan-sinergi-bpd-lewat-kub</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/bos-bank-jatim-pamer-keberhasilan-sinergi-bpd-lewat-kub-daya-saing-naik-1785922771960_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Banyak Sentimen Positif, IHSG Menguat 0,5% ke Level 6.351</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:48:08 +0700</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>IHSG menguat 0,50% pada 5 Agustus 2026, didorong sentimen positif domestik dan global. Pertumbuhan ekonomi Indonesia kuartal II-2026 tumbuh 5,29% yoy.</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805163947-17-756851/banyak-sentimen-positif-ihsg-menguat-05-ke-level-6351</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019138_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Video: Bank Jakarta dan BanK Jatim Soal Peran BPD Jadi Community Bank</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:43:00 +0700</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>OJK Dorong Peran BPD Jadi Community Bank di Daerah, Bos Bank Jakarta dan Bank Jatim Buka Suara</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805161844-19-756844/video-bank-jakarta-bank-jatim-soal-peran-bpd-jadi-community-bank</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/ojk-dorong-peran-bpd-jadi-community-bank-di-daerah-bos-bank-jakarta-bank-jatim-buka-suara-1785922902717_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Mesin Bisnis BNI Ngebut! Simpanan Nasabah Naik Rp 200 Triliun Setahun</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>BNI (BBNI) mencatat pertumbuhan solid di semester I-2026, dengan DPK meningkat Rp200 triliun dalam satu tahun.</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805135845-17-756765/mesin-bisnis-bni-ngebut-simpanan-nasabah-naik-rp-200-triliun-setahun</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/06/19/gedung-bank-negara-indonesia-bni-5_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Bos Bank Jatim Ungkap Tiga Kunci Keberhasilan BPD</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:59:42 +0700</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Direktur Utama Bank Jatim, Winardi Legowo, menjelaskan keberhasilan BPD ditentukan oleh modal, sistem, dan SDM. KUB jadi strategi untuk tingkatkan daya saing.</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805155517-17-756825/bos-bank-jatim-ungkap-tiga-kunci-keberhasilan-bpd</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/direktur-utama-bank-jatim-winardi-legowo-saat-menyampaikan-pemaparan-dalam-acara-regional-bank-summit-2026-di-jakarta-rabu-582-1785917762527_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Kimia Farma (KAEF) Catat Laba Rp10,3 Miliar di Semester I-2026</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:51:13 +0700</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>PT Kimia Farma mencatat laba Rp10,32 miliar di semester I-2026, berbalik dari rugi Rp95,01 miliar tahun lalu, didorong peningkatan penjualan dan laba bruto.</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805154920-17-756820/kimia-farma--kaef--catat-laba-rp103-miliar-di-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/08/kimia-farma-1767867311774_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Rupiah Ditutup Menguat 0,50%, Dolar AS Turun ke Rp17.925</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:05:16 +0700</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah berhasil bangkit dan ditutup menguat terhadap dolar Amerika Serikat (AS).</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805145040-17-756793/rupiah-ditutup-menguat-050-dolar-as-turun-ke-rp17925</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342241_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Kredit BNI Nyaris Rp 1.000 Triliun, Tumbuh 24,4% Semester 1 2026</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:55:09 +0700</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>BNI menyalurkan kredit Rp968,5 triliun hingga semester I-2026, tumbuh 24,4% yoy.</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805131538-17-756746/kredit-bni-nyaris-rp-1000-triliun-tumbuh-244-semester-1-2026</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/09/26/gedung-bni_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Emiten Nagita Slavina (VISI) Rugi di Semester I-2026, Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:40:52 +0700</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Satu Visi Putra (VISI) mencatat rugi bersih Rp4,17 miliar di semester I-2026, meski laba kotor tumbuh. Neraca menyusut setelah divestasi aset Rp75 miliar.</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805143114-17-756786/emiten-nagita-slavina--visi--rugi-di-semester-i-2026-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018756_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Swipe Sekali, Rp23 M Melayang! Ini Sisi Gelap Startup Live Belanja</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 14:05:33 +0700</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Aplikasi belanja live streaming Whatnot menarik perhatian karena dampak adiktifnya. Pengguna menghabiskan jutaan dolar, memicu kritik dan gugatan hukum.</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805135155-17-756760/swipe-sekali-rp23-m-melayang-ini-sisi-gelap-startup-live-belanja</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/06/14/ilustrasi-belanja-online-dok-pixabay_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Asing Net Sell Rp65,81 Miliar di Sesi I, Ini Daftar Sahamnya</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 13:40:54 +0700</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>IHSG menguat 0,69% di tengah sentimen positif dari domestik dan global. Investor asing mencatat aksi jual bersih, terutama pada saham TLKM dan TPIA.</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805133258-17-756752/asing-net-sell-rp6581-miliar-di-sesi-i-ini-daftar-sahamnya</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013780_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Ada Kabar Baik dari Domestik dan Global, IHSG Naik 0,69% ke 6.363</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 12:36:50 +0700</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>IHSG menguat 0,69% di tengah sentimen positif dari domestik dan global. Ekonomi Indonesia tumbuh 5,29%, mendorong optimisme pasar. Baca selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805120636-17-756729/ada-kabar-baik-dari-domestik-global-ihsg-naik-069-ke-6363</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019966_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Breaking News! BNI (BBNI) Cetak Laba Rp10,8 T di Semester I-2026</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:31:03 +0700</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Bank Negara Indonesia (BNI) mencatat laba bersih Rp10,8 triliun di semester I-2026, tumbuh 5,94% yoy. Pendapatan bunga dan kualitas kredit juga meningkat.</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805112750-17-756702/breaking-news-bni--bbni--cetak-laba-rp108-t-di-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/09/26/gedung-bni_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Ekonomi RI Tumbuh 5,29%, IHSG Langsung Menguat 0,62%</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:26:21 +0700</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Gelson Kurniawan</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>BPS mengumumkan pertumbuhan ekonomi Indonesia kuartal II-2026 mencapai 5,29%, lebih tinggi dari ekspektasi. IHSG menguat 0,62% pasca pengumuman.</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805110849-17-756689/ekonomi-ri-tumbuh-529-ihsg-langsung-menguat-062</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019966_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Ekonomi RI Tumbuh 5,29% dan Nilai Tukar Rupiah Menguat ke Rp17.905/US$</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:21:02 +0700</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Rupiah Garuda semakin menguat terhadap dolar Amerika Serikat (AS) pasca BPS umumkan pertumbuhan ekonomi kuartal II-2026.</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805111238-17-756692/ekonomi-ri-tumbuh-529-nilai-tukar-rupiah-menguat-ke-rp17905-us-</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342395_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>OJK Wajibkan Pindar Lapor Transaksi dan Larang Jual Beli Data Nasabah</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:15:01 +0700</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>OJK memperkuat regulasi industri Pinjaman Daring (Pindar) melalui penerbitan Peraturan Otoritas Jasa Keuangan (POJK) Nomor 8 Tahun 2026.</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805104901-17-756678/ojk-wajibkan-pindar-lapor-transaksi-dan-larang-jual-beli-data-nasabah</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/ilustrasi-seseorang-melakukan-pinjaman-online-dok-freepik-1785901803783_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Video: Harapan Damai di Selat Hormuz, Harga Minyak Emas dan Emas Anjlok</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:09:09 +0700</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Harapan Damai di Selat Hormuz, Harga Minyak Emas dan Emas Anjlok</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805103958-19-756677/video-harapan-damai-di-selat-hormuz-harga-minyak-emas-emas-anjlok</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/harapan-damai-di-selat-hormuz-harga-minyak-emas-emas-anjlok-1785902842826_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Dikabarkan Mau Caplok Raksasa Tambang Australia, Bos BUMI Buka Suara</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:45:30 +0700</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Emiten Grup Bakrie dan Salim, PT Bumi Resources Tbk (BUMI) memberikan klarifikasi atas rencana perseroan mengakuisisi Loyal Metals Limited.</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805102950-17-756674/dikabarkan-mau-caplok-raksasa-tambang-australia-bos-bumi-buka-suara</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/12/23/dok-bumi-resources-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Rombak Manajemen, Ini Susunan Direksi Terbaru Bank UOB Indonesia</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:10:52 +0700</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>PT Bank UOB Indonesia melakukan perubahan susunan direksi setelah masa jabatan salah satu direkturnya berakhir.</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805095051-17-756664/rombak-manajemen-ini-susunan-direksi-terbaru-bank-uob-indonesia</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/10/04/gedung-uob-indonesia-dok-uob-indonesia_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Video: Jelang Rilis PDB, IHSG Menghijau dan Rupiah Menguat</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:07:54 +0700</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Jelang Rilis PDB, IHSG Dibuka Menghijau dan Rupiah Menguat ke Rp 17.960 per USD</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805094511-19-756656/video-jelang-rilis-pdb-ihsg-menghijau-dan-rupiah-menguat</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/jelang-rilis-pdb-ihsg-dibuka-menghijau-rupiah-menguat-ke-rp-17960-per-usd-1785899124183_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>BEI Gembok Saham MDIA dan WIKA, Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 10:00:49 +0700</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>BEI menghentikan sementara perdagangan (suspensi) saham PT Intermedia Capital Tbk (MDIA) dan memperpanjang suspensi saham PT Wijaya Karya (Persero) Tbk (WIKA).</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805094649-17-756657/bei-gembok-saham-mdia-dan-wika-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018492_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I798"/>
+  <autoFilter ref="A1:I834"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>